--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -24,8 +24,8 @@
     <definedName name="Interval_autoInsertMemento">FN!$A$10:$E$11</definedName>
     <definedName name="Interval_Dialogs">DIALOGS!$A$1:$D$21</definedName>
     <definedName name="Interval_autoInsertRoom">FN!$A$4:$D$5</definedName>
-    <definedName name="Interval_Memento_Parent">EVENTS!$A$40:$E$45</definedName>
-    <definedName name="Interval_Events">EVENTS!$A$1:$B$38</definedName>
+    <definedName name="Interval_Memento_Parent">EVENTS!$A$39:$E$44</definedName>
+    <definedName name="Interval_Events">EVENTS!$A$1:$B$37</definedName>
     <definedName name="Interval_Rooms">ROOMS!$A$1:$J$15</definedName>
     <definedName name="Interval_Name">NAMES!$A$1:$D$44</definedName>
     <definedName name="Interval_autoInsertItem">FN!$A$1:$J$2</definedName>
@@ -34,7 +34,7 @@
     <definedName name="Interval_sprites">SPRITES!$A$1:$C$60</definedName>
     <definedName name="Interval_Items">ITEMS!$A$1:$J$42</definedName>
     <definedName name="Interval_Dialog_Options">DIALOGS!$A$23:$H$53</definedName>
-    <definedName name="Interval_Memento">EVENTS!$A$47:$F$55</definedName>
+    <definedName name="Interval_Memento">EVENTS!$A$46:$F$54</definedName>
     <definedName name="Interval_autoInsertDialog">FN!$A$7:$I$8</definedName>
     <definedName name="Interval_Action_Conditions">ACTION_CONDS!$A$1:$K$62</definedName>
   </definedNames>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3828" uniqueCount="1385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3842" uniqueCount="1390">
   <si>
     <t>NewItem</t>
   </si>
@@ -1537,7 +1537,7 @@
     <t>EVENT_LAUNCH_SLEEP_DECISION</t>
   </si>
   <si>
-    <t>(NOT)EVENT_CAN_GO_SOUTH_NEIGH</t>
+    <t>(NOT)EVENT_ITEM_EXTRAPERLO_INVITATION_PICKABLE_TAKEN</t>
   </si>
   <si>
     <t>PHRASE_WONT_GO_SOUTH_NEIGH</t>
@@ -2371,6 +2371,24 @@
     <t>SOUND_OBSERVE_ITEM_EXTRAPERLO_INVITATION_DETAIL_SPANISH</t>
   </si>
   <si>
+    <t>SOUND_OBSERVE_ITEM_SHOELACE</t>
+  </si>
+  <si>
+    <t>SOUND_OBSERVE_ITEM_SHOELACE_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_FART_1</t>
+  </si>
+  <si>
+    <t>SOUND_POOR_MAN_BCKG_1</t>
+  </si>
+  <si>
+    <t>SOUND_POOR_MAN_BCKG_2</t>
+  </si>
+  <si>
+    <t>SOUND_POOR_MAN_BCKG_3</t>
+  </si>
+  <si>
     <t>SOUND_LAST</t>
   </si>
   <si>
@@ -4088,9 +4106,6 @@
   </si>
   <si>
     <t>EVENT_MASTER_CHANGE_MOMENT_DAY</t>
-  </si>
-  <si>
-    <t>EVENT_CAN_GO_SOUTH_NEIGH</t>
   </si>
   <si>
     <t>EVENT_PHARMACY_EMPTY</t>
@@ -5509,7 +5524,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D5" displayName="Table_sounds" name="Table_sounds" id="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D10" displayName="Table_sounds" name="Table_sounds" id="11">
   <tableColumns count="4">
     <tableColumn name="N" id="1"/>
     <tableColumn name="SOUND_ID" id="2"/>
@@ -5699,7 +5714,7 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:B38" displayName="Table_Events" name="Table_Events" id="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:B37" displayName="Table_Events" name="Table_Events" id="26">
   <tableColumns count="2">
     <tableColumn name="N" id="1"/>
     <tableColumn name="EVENT_ID" id="2"/>
@@ -5709,7 +5724,7 @@
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A40:E45" displayName="Table_Memento_Parent" name="Table_Memento_Parent" id="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A39:E44" displayName="Table_Memento_Parent" name="Table_Memento_Parent" id="27">
   <tableColumns count="5">
     <tableColumn name="N" id="1"/>
     <tableColumn name="MEMENTO_PARENT_ID" id="2"/>
@@ -5722,7 +5737,7 @@
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A47:F55" displayName="Table_Memento" name="Table_Memento" id="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A46:F54" displayName="Table_Memento" name="Table_Memento" id="28">
   <tableColumns count="6">
     <tableColumn name="N" id="1"/>
     <tableColumn name="MEMENTO_ID" id="2"/>
@@ -5736,7 +5751,7 @@
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A57:C58" displayName="Table_Memento_Combi" name="Table_Memento_Combi" id="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A56:C57" displayName="Table_Memento_Combi" name="Table_Memento_Combi" id="29">
   <tableColumns count="3">
     <tableColumn name="N" id="1"/>
     <tableColumn name="MEMENTO_COMBI_ID" id="2"/>
@@ -5764,7 +5779,7 @@
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A60:B170" displayName="Table_EventsCombi" name="Table_EventsCombi" id="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A59:B169" displayName="Table_EventsCombi" name="Table_EventsCombi" id="30">
   <tableColumns count="2">
     <tableColumn name="N" id="1"/>
     <tableColumn name="EVENT_COMBI_ID" id="2"/>
@@ -6335,13 +6350,13 @@
         <v>44</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="C1" s="57" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="D1" s="57" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
     </row>
     <row r="2">
@@ -6364,10 +6379,10 @@
         <v>279</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -6376,13 +6391,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
     </row>
     <row r="5">
@@ -6391,13 +6406,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
     </row>
     <row r="6">
@@ -6406,13 +6421,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -6424,10 +6439,10 @@
         <v>282</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
     </row>
     <row r="8">
@@ -6439,10 +6454,10 @@
         <v>303</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
     </row>
     <row r="9">
@@ -6454,10 +6469,10 @@
         <v>310</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
     </row>
     <row r="10">
@@ -6469,10 +6484,10 @@
         <v>288</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
     </row>
     <row r="11">
@@ -6481,13 +6496,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
     </row>
     <row r="12">
@@ -6496,13 +6511,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
     </row>
     <row r="13">
@@ -6514,10 +6529,10 @@
         <v>293</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
     </row>
     <row r="14">
@@ -6529,10 +6544,10 @@
         <v>300</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
     </row>
     <row r="15">
@@ -6541,13 +6556,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
     </row>
     <row r="16">
@@ -6559,10 +6574,10 @@
         <v>313</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
     </row>
     <row r="17">
@@ -6574,10 +6589,10 @@
         <v>318</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
     </row>
     <row r="18">
@@ -6589,10 +6604,10 @@
         <v>321</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
     </row>
     <row r="19">
@@ -6604,10 +6619,10 @@
         <v>325</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
     </row>
     <row r="20">
@@ -6619,10 +6634,10 @@
         <v>328</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
     </row>
     <row r="21">
@@ -6634,10 +6649,10 @@
         <v>331</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
     </row>
     <row r="22">
@@ -6649,10 +6664,10 @@
         <v>333</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
     </row>
     <row r="23">
@@ -6664,10 +6679,10 @@
         <v>335</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
     </row>
     <row r="24">
@@ -6679,10 +6694,10 @@
         <v>337</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
     </row>
     <row r="25">
@@ -6694,10 +6709,10 @@
         <v>339</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
     </row>
     <row r="26">
@@ -6709,10 +6724,10 @@
         <v>343</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
     </row>
     <row r="27">
@@ -6724,10 +6739,10 @@
         <v>348</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
     </row>
     <row r="28">
@@ -6739,10 +6754,10 @@
         <v>350</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
     </row>
     <row r="29">
@@ -6754,10 +6769,10 @@
         <v>354</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
     </row>
     <row r="30">
@@ -6766,13 +6781,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
     </row>
     <row r="31">
@@ -6784,10 +6799,10 @@
         <v>358</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
     </row>
     <row r="32">
@@ -6799,10 +6814,10 @@
         <v>360</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
     </row>
     <row r="33">
@@ -6811,13 +6826,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>41</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
     </row>
     <row r="34">
@@ -6829,10 +6844,10 @@
         <v>364</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
     </row>
     <row r="35">
@@ -6844,10 +6859,10 @@
         <v>368</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
     </row>
     <row r="36">
@@ -6859,10 +6874,10 @@
         <v>371</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
     </row>
     <row r="37">
@@ -6874,10 +6889,10 @@
         <v>376</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
     </row>
     <row r="38">
@@ -6889,10 +6904,10 @@
         <v>381</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
     </row>
     <row r="39">
@@ -6904,10 +6919,10 @@
         <v>385</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
     </row>
     <row r="40">
@@ -6919,10 +6934,10 @@
         <v>389</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
     </row>
     <row r="41">
@@ -6934,10 +6949,10 @@
         <v>393</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
     </row>
     <row r="42">
@@ -6949,10 +6964,10 @@
         <v>396</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
     </row>
     <row r="43">
@@ -6964,10 +6979,10 @@
         <v>11</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
     </row>
     <row r="44">
@@ -6979,10 +6994,10 @@
         <v>401</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
     </row>
   </sheetData>
@@ -7016,22 +7031,22 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
     </row>
     <row r="2">
@@ -7049,7 +7064,7 @@
         <v>744</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="F2" s="61"/>
       <c r="G2" s="37"/>
@@ -7060,7 +7075,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="C3" s="36">
         <v>0.0</v>
@@ -7069,13 +7084,13 @@
         <v>744</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
     </row>
     <row r="4">
@@ -7084,7 +7099,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="C4" s="36">
         <v>0.0</v>
@@ -7093,13 +7108,13 @@
         <v>744</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
     </row>
     <row r="5">
@@ -7108,7 +7123,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="C5" s="36">
         <v>0.0</v>
@@ -7117,13 +7132,13 @@
         <v>744</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
     </row>
     <row r="6">
@@ -7132,7 +7147,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="C6" s="36">
         <v>0.0</v>
@@ -7141,13 +7156,13 @@
         <v>744</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
     </row>
     <row r="7">
@@ -7156,7 +7171,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="C7" s="36">
         <v>0.0</v>
@@ -7165,13 +7180,13 @@
         <v>744</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
     </row>
     <row r="8">
@@ -7189,13 +7204,13 @@
         <v>744</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="G8" s="37" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
     </row>
     <row r="9">
@@ -7204,7 +7219,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="C9" s="36">
         <v>0.0</v>
@@ -7213,13 +7228,13 @@
         <v>744</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="G9" s="37" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
     </row>
     <row r="10">
@@ -7228,7 +7243,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="C10" s="36">
         <v>0.0</v>
@@ -7237,13 +7252,13 @@
         <v>744</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
     </row>
     <row r="11">
@@ -7252,7 +7267,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="C11" s="36">
         <v>1.0</v>
@@ -7261,13 +7276,13 @@
         <v>744</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
     </row>
     <row r="12">
@@ -7276,7 +7291,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="C12" s="36">
         <v>0.0</v>
@@ -7285,13 +7300,13 @@
         <v>744</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
     </row>
     <row r="13">
@@ -7300,7 +7315,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="C13" s="36">
         <v>0.0</v>
@@ -7309,13 +7324,13 @@
         <v>744</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="G13" s="37" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
     </row>
     <row r="14">
@@ -7324,7 +7339,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="C14" s="36">
         <v>1.0</v>
@@ -7333,13 +7348,13 @@
         <v>744</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
     </row>
     <row r="15">
@@ -7348,7 +7363,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="C15" s="36">
         <v>1.0</v>
@@ -7357,13 +7372,13 @@
         <v>744</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
     </row>
     <row r="16">
@@ -7372,7 +7387,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="C16" s="36">
         <v>1.0</v>
@@ -7381,13 +7396,13 @@
         <v>744</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
     </row>
     <row r="17">
@@ -7396,7 +7411,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="C17" s="36">
         <v>0.0</v>
@@ -7405,13 +7420,13 @@
         <v>744</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
     </row>
     <row r="18">
@@ -7429,13 +7444,13 @@
         <v>744</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
     </row>
     <row r="19">
@@ -7453,13 +7468,13 @@
         <v>744</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="G19" s="37" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
     </row>
     <row r="20">
@@ -7477,13 +7492,13 @@
         <v>744</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
     </row>
     <row r="21">
@@ -7501,13 +7516,13 @@
         <v>744</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="22">
@@ -7525,13 +7540,13 @@
         <v>744</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="23">
@@ -7549,13 +7564,13 @@
         <v>744</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="24">
@@ -7573,13 +7588,13 @@
         <v>744</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="25">
@@ -7597,13 +7612,13 @@
         <v>744</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="G25" s="37" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="26">
@@ -7612,7 +7627,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="C26" s="36">
         <v>0.0</v>
@@ -7621,13 +7636,13 @@
         <v>744</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="27">
@@ -7636,7 +7651,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="C27" s="36">
         <v>1.0</v>
@@ -7645,13 +7660,13 @@
         <v>744</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="28">
@@ -7660,7 +7675,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="C28" s="36">
         <v>0.0</v>
@@ -7669,13 +7684,13 @@
         <v>744</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="29">
@@ -7684,7 +7699,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="C29" s="36">
         <v>0.0</v>
@@ -7693,13 +7708,13 @@
         <v>744</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="30">
@@ -7708,7 +7723,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="C30" s="36">
         <v>0.0</v>
@@ -7717,13 +7732,13 @@
         <v>744</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="31">
@@ -7741,13 +7756,13 @@
         <v>744</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="32">
@@ -7756,7 +7771,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="C32" s="36">
         <v>0.0</v>
@@ -7765,13 +7780,13 @@
         <v>744</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="33">
@@ -7780,7 +7795,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="C33" s="36">
         <v>1.0</v>
@@ -7789,13 +7804,13 @@
         <v>744</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="34">
@@ -7804,7 +7819,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="C34" s="36">
         <v>1.0</v>
@@ -7813,13 +7828,13 @@
         <v>744</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="35">
@@ -7837,13 +7852,13 @@
         <v>744</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="36">
@@ -7852,7 +7867,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="C36" s="36">
         <v>0.0</v>
@@ -7861,13 +7876,13 @@
         <v>744</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="37">
@@ -7876,7 +7891,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="C37" s="36">
         <v>1.0</v>
@@ -7885,13 +7900,13 @@
         <v>744</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="38">
@@ -7900,7 +7915,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="C38" s="36">
         <v>0.0</v>
@@ -7909,13 +7924,13 @@
         <v>744</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="39">
@@ -7924,7 +7939,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
       <c r="C39" s="36">
         <v>1.0</v>
@@ -7933,13 +7948,13 @@
         <v>744</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="40">
@@ -7948,7 +7963,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="C40" s="36">
         <v>0.0</v>
@@ -7957,13 +7972,13 @@
         <v>744</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="41">
@@ -7972,7 +7987,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="C41" s="36">
         <v>1.0</v>
@@ -7981,13 +7996,13 @@
         <v>744</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="42">
@@ -7996,7 +8011,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="C42" s="36">
         <v>0.0</v>
@@ -8005,13 +8020,13 @@
         <v>744</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="43">
@@ -8020,7 +8035,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="C43" s="36">
         <v>1.0</v>
@@ -8029,13 +8044,13 @@
         <v>744</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="44">
@@ -8044,7 +8059,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="C44" s="36">
         <v>0.0</v>
@@ -8053,13 +8068,13 @@
         <v>744</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="45">
@@ -8068,7 +8083,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="C45" s="36">
         <v>1.0</v>
@@ -8077,13 +8092,13 @@
         <v>744</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="46">
@@ -8092,7 +8107,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="C46" s="36">
         <v>1.0</v>
@@ -8101,13 +8116,13 @@
         <v>744</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="47">
@@ -8116,7 +8131,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="C47" s="36">
         <v>0.0</v>
@@ -8125,13 +8140,13 @@
         <v>744</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="G47" s="37" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="48">
@@ -8140,7 +8155,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="C48" s="36">
         <v>1.0</v>
@@ -8149,13 +8164,13 @@
         <v>744</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="49">
@@ -8164,7 +8179,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="C49" s="36">
         <v>0.0</v>
@@ -8173,13 +8188,13 @@
         <v>744</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="G49" s="37" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="50">
@@ -8188,7 +8203,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="C50" s="36">
         <v>0.0</v>
@@ -8197,13 +8212,13 @@
         <v>744</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="G50" s="37" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="51">
@@ -8212,7 +8227,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="C51" s="36">
         <v>1.0</v>
@@ -8221,13 +8236,13 @@
         <v>744</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="52">
@@ -8236,7 +8251,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="C52" s="36">
         <v>1.0</v>
@@ -8245,13 +8260,13 @@
         <v>744</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="53">
@@ -8260,7 +8275,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="C53" s="36">
         <v>1.0</v>
@@ -8269,13 +8284,13 @@
         <v>744</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="54">
@@ -8284,7 +8299,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="C54" s="36">
         <v>0.0</v>
@@ -8293,13 +8308,13 @@
         <v>744</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="55">
@@ -8308,7 +8323,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="C55" s="36">
         <v>0.0</v>
@@ -8317,13 +8332,13 @@
         <v>744</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="G55" s="37" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="56">
@@ -8332,7 +8347,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="C56" s="36">
         <v>0.0</v>
@@ -8341,13 +8356,13 @@
         <v>744</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="57">
@@ -8356,7 +8371,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="C57" s="36">
         <v>1.0</v>
@@ -8365,13 +8380,13 @@
         <v>744</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="58">
@@ -8389,13 +8404,13 @@
         <v>744</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="59">
@@ -8404,7 +8419,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="C59" s="36">
         <v>0.0</v>
@@ -8413,13 +8428,13 @@
         <v>744</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="60">
@@ -8428,7 +8443,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="C60" s="36">
         <v>0.0</v>
@@ -8437,13 +8452,13 @@
         <v>744</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="61">
@@ -8452,7 +8467,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="C61" s="36">
         <v>0.0</v>
@@ -8461,13 +8476,13 @@
         <v>744</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="62">
@@ -8485,13 +8500,13 @@
         <v>744</v>
       </c>
       <c r="E62" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="63">
@@ -8500,22 +8515,22 @@
         <v>61</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="C63" s="36">
         <v>0.0</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="64">
@@ -8524,22 +8539,22 @@
         <v>62</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="C64" s="36">
         <v>0.0</v>
       </c>
       <c r="D64" s="38" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F64" s="37" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="G64" s="37" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="65">
@@ -8548,22 +8563,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="C65" s="36">
         <v>0.0</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="66">
@@ -8572,22 +8587,22 @@
         <v>64</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="C66" s="36">
         <v>0.0</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>744</v>
+        <v>754</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="67">
@@ -8596,7 +8611,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="C67" s="36">
         <v>0.0</v>
@@ -8605,13 +8620,13 @@
         <v>744</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="G67" s="37" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="68">
@@ -8620,7 +8635,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="C68" s="36">
         <v>1.0</v>
@@ -8629,13 +8644,13 @@
         <v>744</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="69">
@@ -8644,7 +8659,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="C69" s="36">
         <v>0.0</v>
@@ -8653,13 +8668,13 @@
         <v>744</v>
       </c>
       <c r="E69" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="70">
@@ -8668,7 +8683,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="C70" s="36">
         <v>1.0</v>
@@ -8677,13 +8692,13 @@
         <v>744</v>
       </c>
       <c r="E70" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="G70" s="37" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="71">
@@ -8692,7 +8707,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="C71" s="36">
         <v>0.0</v>
@@ -8701,13 +8716,13 @@
         <v>744</v>
       </c>
       <c r="E71" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="G71" s="37" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="72">
@@ -8716,7 +8731,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="C72" s="36">
         <v>1.0</v>
@@ -8725,13 +8740,13 @@
         <v>744</v>
       </c>
       <c r="E72" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F72" s="37" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="G72" s="37" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="73">
@@ -8740,7 +8755,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="C73" s="36">
         <v>0.0</v>
@@ -8749,13 +8764,13 @@
         <v>744</v>
       </c>
       <c r="E73" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F73" s="37" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
       <c r="G73" s="37" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="74">
@@ -8764,7 +8779,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="C74" s="36">
         <v>1.0</v>
@@ -8773,13 +8788,13 @@
         <v>744</v>
       </c>
       <c r="E74" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F74" s="37" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="G74" s="37" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="75">
@@ -8788,7 +8803,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="C75" s="36">
         <v>0.0</v>
@@ -8797,13 +8812,13 @@
         <v>744</v>
       </c>
       <c r="E75" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F75" s="37" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="G75" s="37" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="76">
@@ -8812,7 +8827,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
       <c r="C76" s="36">
         <v>1.0</v>
@@ -8821,13 +8836,13 @@
         <v>744</v>
       </c>
       <c r="E76" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F76" s="37" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="G76" s="37" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="77">
@@ -8836,7 +8851,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="C77" s="36">
         <v>0.0</v>
@@ -8845,13 +8860,13 @@
         <v>744</v>
       </c>
       <c r="E77" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F77" s="37" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="G77" s="37" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="78">
@@ -8860,7 +8875,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="C78" s="36">
         <v>0.0</v>
@@ -8869,13 +8884,13 @@
         <v>744</v>
       </c>
       <c r="E78" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F78" s="37" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="G78" s="37" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="79">
@@ -8884,7 +8899,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="C79" s="36">
         <v>1.0</v>
@@ -8893,13 +8908,13 @@
         <v>744</v>
       </c>
       <c r="E79" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F79" s="37" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="G79" s="37" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="80">
@@ -8908,7 +8923,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="C80" s="36">
         <v>1.0</v>
@@ -8917,13 +8932,13 @@
         <v>744</v>
       </c>
       <c r="E80" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F80" s="37" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="G80" s="37" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="81">
@@ -8932,7 +8947,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="C81" s="36">
         <v>1.0</v>
@@ -8941,13 +8956,13 @@
         <v>744</v>
       </c>
       <c r="E81" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F81" s="37" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="G81" s="37" t="s">
-        <v>1158</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="82">
@@ -8956,7 +8971,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="C82" s="36">
         <v>0.0</v>
@@ -8965,13 +8980,13 @@
         <v>744</v>
       </c>
       <c r="E82" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F82" s="37" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="G82" s="37" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="83">
@@ -8980,7 +8995,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="C83" s="36">
         <v>0.0</v>
@@ -8989,13 +9004,13 @@
         <v>744</v>
       </c>
       <c r="E83" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F83" s="37" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="G83" s="37" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="84">
@@ -9004,7 +9019,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="C84" s="36">
         <v>0.0</v>
@@ -9013,13 +9028,13 @@
         <v>744</v>
       </c>
       <c r="E84" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F84" s="37" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="G84" s="37" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="85">
@@ -9037,13 +9052,13 @@
         <v>744</v>
       </c>
       <c r="E85" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>1169</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="86">
@@ -9061,13 +9076,13 @@
         <v>744</v>
       </c>
       <c r="E86" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F86" s="37" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="G86" s="37" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="87">
@@ -9085,13 +9100,13 @@
         <v>744</v>
       </c>
       <c r="E87" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F87" s="37" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>1172</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="88">
@@ -9109,13 +9124,13 @@
         <v>744</v>
       </c>
       <c r="E88" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F88" s="37" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
       <c r="G88" s="37" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="89">
@@ -9133,13 +9148,13 @@
         <v>744</v>
       </c>
       <c r="E89" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F89" s="37" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="G89" s="37" t="s">
-        <v>1176</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="90">
@@ -9157,13 +9172,13 @@
         <v>744</v>
       </c>
       <c r="E90" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F90" s="37" t="s">
-        <v>1177</v>
+        <v>1183</v>
       </c>
       <c r="G90" s="37" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="91">
@@ -9181,13 +9196,13 @@
         <v>744</v>
       </c>
       <c r="E91" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F91" s="37" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="G91" s="37" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="92">
@@ -9205,13 +9220,13 @@
         <v>744</v>
       </c>
       <c r="E92" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F92" s="37" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
       <c r="G92" s="37" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="93">
@@ -9229,13 +9244,13 @@
         <v>744</v>
       </c>
       <c r="E93" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F93" s="37" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="G93" s="37" t="s">
-        <v>1184</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="94">
@@ -9250,16 +9265,16 @@
         <v>0.0</v>
       </c>
       <c r="D94" s="38" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="E94" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F94" s="37" t="s">
-        <v>1185</v>
+        <v>1191</v>
       </c>
       <c r="G94" s="37" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="95">
@@ -9277,13 +9292,13 @@
         <v>744</v>
       </c>
       <c r="E95" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F95" s="37" t="s">
-        <v>1187</v>
+        <v>1193</v>
       </c>
       <c r="G95" s="37" t="s">
-        <v>1188</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="96">
@@ -9301,13 +9316,13 @@
         <v>744</v>
       </c>
       <c r="E96" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F96" s="37" t="s">
-        <v>1189</v>
+        <v>1195</v>
       </c>
       <c r="G96" s="37" t="s">
-        <v>1190</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="97">
@@ -9325,13 +9340,13 @@
         <v>744</v>
       </c>
       <c r="E97" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F97" s="37" t="s">
-        <v>1191</v>
+        <v>1197</v>
       </c>
       <c r="G97" s="37" t="s">
-        <v>1192</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="98">
@@ -9349,13 +9364,13 @@
         <v>744</v>
       </c>
       <c r="E98" s="44" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="F98" s="37" t="s">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="G98" s="37" t="s">
-        <v>1194</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="99">
@@ -9373,13 +9388,13 @@
         <v>744</v>
       </c>
       <c r="E99" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F99" s="37" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="G99" s="37" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="100">
@@ -9397,13 +9412,13 @@
         <v>744</v>
       </c>
       <c r="E100" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F100" s="37" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="G100" s="37" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="101">
@@ -9421,13 +9436,13 @@
         <v>744</v>
       </c>
       <c r="E101" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F101" s="37" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="G101" s="37" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="102">
@@ -9436,7 +9451,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="36" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="C102" s="36">
         <v>0.0</v>
@@ -9445,13 +9460,13 @@
         <v>744</v>
       </c>
       <c r="E102" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F102" s="37" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="G102" s="37" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="103">
@@ -9460,7 +9475,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="36" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="C103" s="36">
         <v>1.0</v>
@@ -9469,13 +9484,13 @@
         <v>744</v>
       </c>
       <c r="E103" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F103" s="37" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="G103" s="37" t="s">
-        <v>1206</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="104">
@@ -9484,7 +9499,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="C104" s="36">
         <v>0.0</v>
@@ -9493,13 +9508,13 @@
         <v>744</v>
       </c>
       <c r="E104" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F104" s="37" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="G104" s="37" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="105">
@@ -9508,7 +9523,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="C105" s="36">
         <v>1.0</v>
@@ -9517,13 +9532,13 @@
         <v>744</v>
       </c>
       <c r="E105" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F105" s="37" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="G105" s="37" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="106">
@@ -9532,7 +9547,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="C106" s="36">
         <v>0.0</v>
@@ -9541,13 +9556,13 @@
         <v>744</v>
       </c>
       <c r="E106" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F106" s="37" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="G106" s="37" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="107">
@@ -9556,7 +9571,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="C107" s="36">
         <v>1.0</v>
@@ -9565,13 +9580,13 @@
         <v>744</v>
       </c>
       <c r="E107" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F107" s="37" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
       <c r="G107" s="37" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="108">
@@ -9580,7 +9595,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="C108" s="36">
         <v>0.0</v>
@@ -9589,13 +9604,13 @@
         <v>744</v>
       </c>
       <c r="E108" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F108" s="37" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="G108" s="37" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="109">
@@ -9604,7 +9619,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="C109" s="36">
         <v>1.0</v>
@@ -9613,13 +9628,13 @@
         <v>744</v>
       </c>
       <c r="E109" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F109" s="37" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="G109" s="37" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="110">
@@ -9628,7 +9643,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="C110" s="36">
         <v>0.0</v>
@@ -9637,13 +9652,13 @@
         <v>744</v>
       </c>
       <c r="E110" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F110" s="37" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="G110" s="37" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="111">
@@ -9652,7 +9667,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="C111" s="36">
         <v>1.0</v>
@@ -9661,13 +9676,13 @@
         <v>744</v>
       </c>
       <c r="E111" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F111" s="37" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="G111" s="37" t="s">
-        <v>1229</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="112">
@@ -9676,7 +9691,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="36" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="C112" s="36">
         <v>0.0</v>
@@ -9685,13 +9700,13 @@
         <v>744</v>
       </c>
       <c r="E112" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F112" s="37" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="G112" s="37" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="113">
@@ -9700,7 +9715,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="C113" s="36">
         <v>0.0</v>
@@ -9709,13 +9724,13 @@
         <v>744</v>
       </c>
       <c r="E113" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F113" s="37" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="G113" s="37" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="114">
@@ -9724,7 +9739,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="C114" s="36">
         <v>0.0</v>
@@ -9733,13 +9748,13 @@
         <v>744</v>
       </c>
       <c r="E114" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F114" s="37" t="s">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="G114" s="37" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="115">
@@ -9748,7 +9763,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="C115" s="36">
         <v>1.0</v>
@@ -9757,13 +9772,13 @@
         <v>744</v>
       </c>
       <c r="E115" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F115" s="37" t="s">
-        <v>1239</v>
+        <v>1245</v>
       </c>
       <c r="G115" s="37" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="116">
@@ -9781,13 +9796,13 @@
         <v>744</v>
       </c>
       <c r="E116" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F116" s="37" t="s">
-        <v>1241</v>
+        <v>1247</v>
       </c>
       <c r="G116" s="37" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="117">
@@ -9805,13 +9820,13 @@
         <v>747</v>
       </c>
       <c r="E117" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F117" s="37" t="s">
-        <v>1243</v>
+        <v>1249</v>
       </c>
       <c r="G117" s="37" t="s">
-        <v>1244</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="118">
@@ -9829,13 +9844,13 @@
         <v>744</v>
       </c>
       <c r="E118" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F118" s="37" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="G118" s="37" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="119">
@@ -9853,10 +9868,10 @@
         <v>744</v>
       </c>
       <c r="E119" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F119" s="37" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="G119" s="37" t="s">
         <v>14</v>
@@ -9868,7 +9883,7 @@
         <v>118</v>
       </c>
       <c r="B120" s="36" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="C120" s="36">
         <v>0.0</v>
@@ -9877,10 +9892,10 @@
         <v>744</v>
       </c>
       <c r="E120" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F120" s="37" t="s">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="G120" s="37" t="s">
         <v>32</v>
@@ -9892,7 +9907,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="C121" s="36">
         <v>0.0</v>
@@ -9901,13 +9916,13 @@
         <v>744</v>
       </c>
       <c r="E121" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F121" s="37" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
       <c r="G121" s="37" t="s">
-        <v>1250</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="122">
@@ -9916,7 +9931,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="36" t="s">
-        <v>1251</v>
+        <v>1257</v>
       </c>
       <c r="C122" s="36">
         <v>0.0</v>
@@ -9925,13 +9940,13 @@
         <v>744</v>
       </c>
       <c r="E122" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F122" s="37" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="G122" s="37" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="123">
@@ -9940,7 +9955,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
       <c r="C123" s="36">
         <v>0.0</v>
@@ -9949,13 +9964,13 @@
         <v>744</v>
       </c>
       <c r="E123" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F123" s="37" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
       <c r="G123" s="37" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="124">
@@ -9973,13 +9988,13 @@
         <v>744</v>
       </c>
       <c r="E124" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F124" s="37" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="G124" s="37" t="s">
-        <v>1258</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="125">
@@ -9997,13 +10012,13 @@
         <v>744</v>
       </c>
       <c r="E125" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F125" s="37" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="G125" s="37" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="126">
@@ -10012,7 +10027,7 @@
         <v>124</v>
       </c>
       <c r="B126" s="36" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
       <c r="C126" s="36">
         <v>0.0</v>
@@ -10021,13 +10036,13 @@
         <v>744</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F126" s="37" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="G126" s="37" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
     </row>
   </sheetData>
@@ -10070,31 +10085,31 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>1269</v>
+        <v>1275</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="J1" s="28" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="2" ht="186.0" customHeight="1">
@@ -10103,7 +10118,7 @@
         <v>-1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>1272</v>
+        <v>1278</v>
       </c>
       <c r="C2" s="63" t="s">
         <v>275</v>
@@ -10127,7 +10142,7 @@
         <v>277</v>
       </c>
       <c r="J2" s="35" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="3">
@@ -10136,7 +10151,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="C3" s="63" t="s">
         <v>672</v>
@@ -10145,10 +10160,10 @@
         <v>746</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>273</v>
@@ -10160,7 +10175,7 @@
         <v>277</v>
       </c>
       <c r="J3" s="35" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="4">
@@ -10169,19 +10184,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="C4" s="63" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="D4" s="34" t="s">
         <v>746</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>273</v>
@@ -10193,7 +10208,7 @@
         <v>277</v>
       </c>
       <c r="J4" s="35" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="5">
@@ -10202,19 +10217,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="D5" s="34" t="s">
         <v>746</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>273</v>
@@ -10226,7 +10241,7 @@
         <v>490</v>
       </c>
       <c r="J5" s="35" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="6">
@@ -10235,19 +10250,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>746</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>273</v>
@@ -10259,7 +10274,7 @@
         <v>490</v>
       </c>
       <c r="J6" s="35" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -10268,19 +10283,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="D7" s="34" t="s">
         <v>744</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>273</v>
@@ -10292,7 +10307,7 @@
         <v>277</v>
       </c>
       <c r="J7" s="35" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="8">
@@ -10301,19 +10316,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="D8" s="34" t="s">
         <v>744</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>273</v>
@@ -10325,7 +10340,7 @@
         <v>277</v>
       </c>
       <c r="J8" s="35" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="9">
@@ -10346,7 +10361,7 @@
         <v>705</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>273</v>
@@ -10358,7 +10373,7 @@
         <v>277</v>
       </c>
       <c r="J9" s="35" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="10">
@@ -10367,19 +10382,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="D10" s="34" t="s">
         <v>744</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>273</v>
@@ -10391,7 +10406,7 @@
         <v>485</v>
       </c>
       <c r="J10" s="35" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="11">
@@ -10400,19 +10415,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>744</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>1298</v>
+        <v>1304</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>273</v>
@@ -10424,7 +10439,7 @@
         <v>277</v>
       </c>
       <c r="J11" s="35" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="12">
@@ -10433,16 +10448,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="D12" s="34" t="s">
         <v>744</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="F12" s="35" t="s">
         <v>299</v>
@@ -10457,7 +10472,7 @@
         <v>277</v>
       </c>
       <c r="J12" s="35" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="13">
@@ -10466,16 +10481,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="D13" s="34" t="s">
         <v>744</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="F13" s="35" t="s">
         <v>299</v>
@@ -10490,7 +10505,7 @@
         <v>277</v>
       </c>
       <c r="J13" s="35" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="14">
@@ -10502,13 +10517,13 @@
         <v>20</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="D14" s="34" t="s">
         <v>744</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="F14" s="35" t="s">
         <v>299</v>
@@ -10523,7 +10538,7 @@
         <v>277</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="15">
@@ -10532,7 +10547,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="C15" s="63" t="s">
         <v>275</v>
@@ -10556,7 +10571,7 @@
         <v>277</v>
       </c>
       <c r="J15" s="35" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
   </sheetData>
@@ -10595,7 +10610,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="2">
@@ -10622,7 +10637,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1306</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="5">
@@ -10631,7 +10646,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="6">
@@ -10643,7 +10658,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="8">
@@ -10699,7 +10714,7 @@
         <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="16">
@@ -10717,7 +10732,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="18">
@@ -10762,7 +10777,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1311</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="23">
@@ -10788,7 +10803,7 @@
         <v>44</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1312</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="27">
@@ -10824,7 +10839,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="31">
@@ -10851,7 +10866,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="34">
@@ -10869,7 +10884,7 @@
         <v>8</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="36">
@@ -10896,7 +10911,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="40">
@@ -10904,7 +10919,7 @@
         <v>44</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="41">
@@ -10912,7 +10927,7 @@
         <v>0.0</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
     </row>
     <row r="42">
@@ -10920,7 +10935,7 @@
         <v>1.0</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
     </row>
     <row r="44">
@@ -10928,7 +10943,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1318</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="45">
@@ -10981,7 +10996,7 @@
         <v>44</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1319</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="52">
@@ -11046,12 +11061,12 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="36">
-        <f t="shared" ref="A2:A38" si="1">ROW()-ROW($A$2)</f>
+        <f t="shared" ref="A2:A37" si="1">ROW()-ROW($A$2)</f>
         <v>0</v>
       </c>
       <c r="B2" s="36" t="s">
@@ -11073,7 +11088,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1321</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="5">
@@ -11082,7 +11097,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6">
@@ -11091,7 +11106,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
     </row>
     <row r="7">
@@ -11181,7 +11196,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="17">
@@ -11190,7 +11205,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1323</v>
+        <v>801</v>
       </c>
     </row>
     <row r="18">
@@ -11199,7 +11214,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>795</v>
+        <v>625</v>
       </c>
     </row>
     <row r="19">
@@ -11208,7 +11223,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>625</v>
+        <v>484</v>
       </c>
     </row>
     <row r="20">
@@ -11217,7 +11232,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
     </row>
     <row r="21">
@@ -11226,7 +11241,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>501</v>
+        <v>636</v>
       </c>
     </row>
     <row r="22">
@@ -11235,7 +11250,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>636</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23">
@@ -11244,7 +11259,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
     </row>
     <row r="24">
@@ -11253,7 +11268,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25">
@@ -11262,7 +11277,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>506</v>
+        <v>519</v>
       </c>
     </row>
     <row r="26">
@@ -11271,7 +11286,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
     </row>
     <row r="27">
@@ -11280,7 +11295,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
     </row>
     <row r="28">
@@ -11289,7 +11304,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="29">
@@ -11298,7 +11313,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>541</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="30">
@@ -11307,7 +11322,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1324</v>
+        <v>824</v>
       </c>
     </row>
     <row r="31">
@@ -11316,7 +11331,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>818</v>
+        <v>646</v>
       </c>
     </row>
     <row r="32">
@@ -11325,7 +11340,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>646</v>
+        <v>551</v>
       </c>
     </row>
     <row r="33">
@@ -11334,7 +11349,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
     </row>
     <row r="34">
@@ -11343,7 +11358,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>563</v>
+        <v>648</v>
       </c>
     </row>
     <row r="35">
@@ -11352,7 +11367,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>648</v>
+        <v>553</v>
       </c>
     </row>
     <row r="36">
@@ -11361,7 +11376,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="37">
@@ -11370,166 +11385,178 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="36">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-      <c r="B38" s="36" t="s">
-        <v>1325</v>
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C39" s="65" t="s">
+        <v>264</v>
+      </c>
+      <c r="D39" s="65" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E39" s="65" t="s">
+        <v>1333</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>1326</v>
-      </c>
-      <c r="C40" s="65" t="s">
-        <v>264</v>
-      </c>
-      <c r="D40" s="65" t="s">
-        <v>1327</v>
-      </c>
-      <c r="E40" s="65" t="s">
-        <v>1328</v>
+      <c r="A40" s="36">
+        <f>ROW()-ROW(Table_Memento_Parent[N])</f>
+        <v>0</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C40" s="38" t="s">
+        <v>273</v>
+      </c>
+      <c r="D40" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="E40" s="66" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B40,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_NONE")</f>
+        <v>MEMENTO_NONE</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="36">
         <f>ROW()-ROW(Table_Memento_Parent[N])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>273</v>
+        <v>882</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>275</v>
+        <v>688</v>
       </c>
       <c r="E41" s="66" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B41,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_NONE")</f>
-        <v>MEMENTO_NONE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B41,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_JOB_FIND_1_1|MEMENTO_JOB_FIND_1_2")</f>
+        <v>MEMENTO_JOB_FIND_1_1|MEMENTO_JOB_FIND_1_2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="36">
         <f>ROW()-ROW(Table_Memento_Parent[N])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>876</v>
+        <v>913</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>688</v>
+        <v>716</v>
       </c>
       <c r="E42" s="66" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B42,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_JOB_FIND_1_1|MEMENTO_JOB_FIND_1_2")</f>
-        <v>MEMENTO_JOB_FIND_1_1|MEMENTO_JOB_FIND_1_2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B42,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_RECIPE_MISSION_1")</f>
+        <v>MEMENTO_RECIPE_MISSION_1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="36">
         <f>ROW()-ROW(Table_Memento_Parent[N])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1331</v>
+        <v>39</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>907</v>
+        <v>920</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>716</v>
+        <v>40</v>
       </c>
       <c r="E43" s="66" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B43,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_RECIPE_MISSION_1")</f>
-        <v>MEMENTO_RECIPE_MISSION_1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B43,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_POOR_MAN_WC_1|MEMENTO_POOR_MAN_WC_2|MEMENTO_POOR_MAN_WC_3")</f>
+        <v>MEMENTO_POOR_MAN_WC_1|MEMENTO_POOR_MAN_WC_2|MEMENTO_POOR_MAN_WC_3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="36">
         <f>ROW()-ROW(Table_Memento_Parent[N])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>39</v>
+        <v>1337</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>914</v>
+        <v>401</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>40</v>
+        <v>275</v>
       </c>
       <c r="E44" s="66" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B44,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_POOR_MAN_WC_1|MEMENTO_POOR_MAN_WC_2|MEMENTO_POOR_MAN_WC_3")</f>
-        <v>MEMENTO_POOR_MAN_WC_1|MEMENTO_POOR_MAN_WC_2|MEMENTO_POOR_MAN_WC_3</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="36">
-        <f>ROW()-ROW(Table_Memento_Parent[N])</f>
-        <v>4</v>
-      </c>
-      <c r="B45" s="36" t="s">
-        <v>1332</v>
-      </c>
-      <c r="C45" s="38" t="s">
-        <v>401</v>
-      </c>
-      <c r="D45" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="E45" s="66" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B45,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_LAST")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B44,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_LAST")</f>
         <v>MEMENTO_LAST</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C46" s="64" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D46" s="64" t="s">
+        <v>843</v>
+      </c>
+      <c r="E46" s="65" t="s">
+        <v>1340</v>
+      </c>
+      <c r="F46" s="64" t="s">
+        <v>1341</v>
+      </c>
+    </row>
     <row r="47">
-      <c r="A47" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C47" s="64" t="s">
+      <c r="A47" s="36">
+        <f>ROW()-ROW(Table_Memento[N])</f>
+        <v>0</v>
+      </c>
+      <c r="B47" s="36" t="s">
+        <v>586</v>
+      </c>
+      <c r="C47" s="44" t="s">
         <v>1334</v>
       </c>
-      <c r="D47" s="64" t="s">
-        <v>837</v>
-      </c>
-      <c r="E47" s="65" t="s">
-        <v>1335</v>
-      </c>
-      <c r="F47" s="64" t="s">
-        <v>1336</v>
+      <c r="D47" s="44" t="s">
+        <v>419</v>
+      </c>
+      <c r="E47" s="67" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F47" s="47" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="36">
         <f>ROW()-ROW(Table_Memento[N])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C48" s="44" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>419</v>
+        <v>990</v>
       </c>
       <c r="E48" s="67" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="F48" s="47" t="b">
         <v>0</v>
@@ -11538,19 +11565,19 @@
     <row r="49">
       <c r="A49" s="36">
         <f>ROW()-ROW(Table_Memento[N])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>590</v>
+        <v>612</v>
       </c>
       <c r="C49" s="44" t="s">
-        <v>1330</v>
+        <v>1335</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>984</v>
+        <v>436</v>
       </c>
       <c r="E49" s="67" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="F49" s="47" t="b">
         <v>0</v>
@@ -11559,19 +11586,19 @@
     <row r="50">
       <c r="A50" s="36">
         <f>ROW()-ROW(Table_Memento[N])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="C50" s="44" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>436</v>
+        <v>1092</v>
       </c>
       <c r="E50" s="67" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="F50" s="47" t="b">
         <v>0</v>
@@ -11580,19 +11607,19 @@
     <row r="51">
       <c r="A51" s="36">
         <f>ROW()-ROW(Table_Memento[N])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>1331</v>
+        <v>39</v>
       </c>
       <c r="D51" s="44" t="s">
-        <v>1086</v>
+        <v>1165</v>
       </c>
       <c r="E51" s="67" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="F51" s="47" t="b">
         <v>0</v>
@@ -11601,19 +11628,19 @@
     <row r="52">
       <c r="A52" s="36">
         <f>ROW()-ROW(Table_Memento[N])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>631</v>
+        <v>1343</v>
       </c>
       <c r="C52" s="44" t="s">
         <v>39</v>
       </c>
       <c r="D52" s="44" t="s">
-        <v>1159</v>
+        <v>1168</v>
       </c>
       <c r="E52" s="67" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="F52" s="47" t="b">
         <v>0</v>
@@ -11622,1095 +11649,1068 @@
     <row r="53">
       <c r="A53" s="36">
         <f>ROW()-ROW(Table_Memento[N])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1338</v>
+        <v>1344</v>
       </c>
       <c r="C53" s="44" t="s">
         <v>39</v>
       </c>
       <c r="D53" s="44" t="s">
-        <v>1162</v>
+        <v>1171</v>
       </c>
       <c r="E53" s="67" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="F53" s="47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="36">
         <f>ROW()-ROW(Table_Memento[N])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1339</v>
+        <v>1345</v>
       </c>
       <c r="C54" s="44" t="s">
-        <v>39</v>
+        <v>1337</v>
       </c>
       <c r="D54" s="44" t="s">
-        <v>1165</v>
+        <v>419</v>
       </c>
       <c r="E54" s="67" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="F54" s="47" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="36">
-        <f>ROW()-ROW(Table_Memento[N])</f>
-        <v>7</v>
-      </c>
-      <c r="B55" s="36" t="s">
-        <v>1340</v>
-      </c>
-      <c r="C55" s="44" t="s">
-        <v>1332</v>
-      </c>
-      <c r="D55" s="44" t="s">
-        <v>419</v>
-      </c>
-      <c r="E55" s="67" t="s">
-        <v>1337</v>
-      </c>
-      <c r="F55" s="47" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C56" s="28" t="s">
+        <v>1347</v>
+      </c>
+    </row>
     <row r="57">
-      <c r="A57" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C57" s="28" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="36">
+      <c r="A57" s="36">
         <f>ROW()-ROW(Table_Memento_Combi[N])</f>
         <v>0</v>
       </c>
-      <c r="B58" s="36" t="s">
-        <v>1337</v>
-      </c>
-      <c r="C58" s="68" t="s">
+      <c r="B57" s="36" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C57" s="68" t="s">
         <v>413</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
     <row r="60">
-      <c r="A60" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>1343</v>
+      <c r="A60" s="46">
+        <f>ROW()-ROW(Table_EventsCombi[N])</f>
+        <v>0</v>
+      </c>
+      <c r="B60" s="69" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(FLATTEN(Table_Events[EVENT_ID],""(NOT)""&amp;Table_Events[EVENT_ID]))"),"EVENT_NONE")</f>
+        <v>EVENT_NONE</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B61" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(FLATTEN(Table_Events[EVENT_ID],""(NOT)""&amp;Table_Events[EVENT_ID]))"),"EVENT_NONE")</f>
-        <v>EVENT_NONE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_MASTER_CHANGE_ROOM")</f>
+        <v>EVENT_MASTER_CHANGE_ROOM</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B62" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_MASTER_CHANGE_ROOM")</f>
-        <v>EVENT_MASTER_CHANGE_ROOM</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_MASTER_CHANGE_MOMENT_DAY")</f>
+        <v>EVENT_MASTER_CHANGE_MOMENT_DAY</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B63" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_MASTER_CHANGE_MOMENT_DAY")</f>
-        <v>EVENT_MASTER_CHANGE_MOMENT_DAY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_MASTER_PENDING_SLEEP_NAP")</f>
+        <v>EVENT_MASTER_PENDING_SLEEP_NAP</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B64" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_MASTER_PENDING_SLEEP_NAP")</f>
-        <v>EVENT_MASTER_PENDING_SLEEP_NAP</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_MASTER_PENDING_SLEEP_LONG")</f>
+        <v>EVENT_MASTER_PENDING_SLEEP_LONG</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B65" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_MASTER_PENDING_SLEEP_LONG")</f>
-        <v>EVENT_MASTER_PENDING_SLEEP_LONG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_FIRST")</f>
+        <v>EVENT_FIRST</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B66" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_FIRST")</f>
-        <v>EVENT_FIRST</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_HIVE1_CHEST_OPENED")</f>
+        <v>EVENT_HIVE1_CHEST_OPENED</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B67" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_HIVE1_CHEST_OPENED")</f>
-        <v>EVENT_HIVE1_CHEST_OPENED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_CARDS_PICKABLE_TAKEN")</f>
+        <v>EVENT_CARDS_PICKABLE_TAKEN</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B68" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_CARDS_PICKABLE_TAKEN")</f>
-        <v>EVENT_CARDS_PICKABLE_TAKEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_HIVE1_WARDROBE_OPENED")</f>
+        <v>EVENT_HIVE1_WARDROBE_OPENED</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B69" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_HIVE1_WARDROBE_OPENED")</f>
-        <v>EVENT_HIVE1_WARDROBE_OPENED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_HIVE1_AD_BOARD_OBSERVED_1")</f>
+        <v>EVENT_HIVE1_AD_BOARD_OBSERVED_1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B70" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_HIVE1_AD_BOARD_OBSERVED_1")</f>
-        <v>EVENT_HIVE1_AD_BOARD_OBSERVED_1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_HIVE1_USED_PERFUME")</f>
+        <v>EVENT_HIVE1_USED_PERFUME</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B71" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_HIVE1_USED_PERFUME")</f>
-        <v>EVENT_HIVE1_USED_PERFUME</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_HIVE1_USED_BASIN")</f>
+        <v>EVENT_HIVE1_USED_BASIN</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B72" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_HIVE1_USED_BASIN")</f>
-        <v>EVENT_HIVE1_USED_BASIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_SOAP_PICKABLE_TAKEN")</f>
+        <v>EVENT_SOAP_PICKABLE_TAKEN</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B73" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_SOAP_PICKABLE_TAKEN")</f>
-        <v>EVENT_SOAP_PICKABLE_TAKEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_LAUNCH_SLEEP_DECISION")</f>
+        <v>EVENT_LAUNCH_SLEEP_DECISION</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B74" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_LAUNCH_SLEEP_DECISION")</f>
-        <v>EVENT_LAUNCH_SLEEP_DECISION</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_PHARMACY_EMPTY")</f>
+        <v>EVENT_PHARMACY_EMPTY</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B75" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_CAN_GO_SOUTH_NEIGH")</f>
-        <v>EVENT_CAN_GO_SOUTH_NEIGH</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_MANYO_REFUSED_WORK")</f>
+        <v>EVENT_MANYO_REFUSED_WORK</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B76" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_PHARMACY_EMPTY")</f>
-        <v>EVENT_PHARMACY_EMPTY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_MANYO_LOOK_FOR_RECIPE_MISSION")</f>
+        <v>EVENT_MANYO_LOOK_FOR_RECIPE_MISSION</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B77" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_MANYO_REFUSED_WORK")</f>
-        <v>EVENT_MANYO_REFUSED_WORK</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_UMBRELLA_PICKABLE_TAKEN")</f>
+        <v>EVENT_UMBRELLA_PICKABLE_TAKEN</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B78" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_MANYO_LOOK_FOR_RECIPE_MISSION")</f>
-        <v>EVENT_MANYO_LOOK_FOR_RECIPE_MISSION</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_POOR_MAN_WC_NEED_WATER")</f>
+        <v>EVENT_POOR_MAN_WC_NEED_WATER</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B79" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_UMBRELLA_PICKABLE_TAKEN")</f>
-        <v>EVENT_UMBRELLA_PICKABLE_TAKEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_COCKROACH_CHEATED")</f>
+        <v>EVENT_COCKROACH_CHEATED</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B80" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_POOR_MAN_WC_NEED_WATER")</f>
-        <v>EVENT_POOR_MAN_WC_NEED_WATER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_PIPE_OBSERVATION_1")</f>
+        <v>EVENT_PIPE_OBSERVATION_1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B81" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_COCKROACH_CHEATED")</f>
-        <v>EVENT_COCKROACH_CHEATED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_PIPE_OBSERVATION_2")</f>
+        <v>EVENT_PIPE_OBSERVATION_2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B82" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_PIPE_OBSERVATION_1")</f>
-        <v>EVENT_PIPE_OBSERVATION_1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_COCKROACH_SCARED")</f>
+        <v>EVENT_COCKROACH_SCARED</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B83" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_PIPE_OBSERVATION_2")</f>
-        <v>EVENT_PIPE_OBSERVATION_2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_VALVE_BOX_NEED_OPEN")</f>
+        <v>EVENT_VALVE_BOX_NEED_OPEN</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B84" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_COCKROACH_SCARED")</f>
-        <v>EVENT_COCKROACH_SCARED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_ITEM_HIVE1_SHOELACE_PICKABLE_TAKEN")</f>
+        <v>EVENT_ITEM_HIVE1_SHOELACE_PICKABLE_TAKEN</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B85" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_VALVE_BOX_NEED_OPEN")</f>
-        <v>EVENT_VALVE_BOX_NEED_OPEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_VALVE_BOX_OPENED")</f>
+        <v>EVENT_VALVE_BOX_OPENED</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B86" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_ITEM_HIVE1_SHOELACE_PICKABLE_TAKEN")</f>
-        <v>EVENT_ITEM_HIVE1_SHOELACE_PICKABLE_TAKEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_HIVE1_VALVE_ACTIVATED")</f>
+        <v>EVENT_HIVE1_VALVE_ACTIVATED</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B87" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_VALVE_BOX_OPENED")</f>
-        <v>EVENT_VALVE_BOX_OPENED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_TALKED_ARTURO_HALL_INN_COMPLETED")</f>
+        <v>EVENT_TALKED_ARTURO_HALL_INN_COMPLETED</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B88" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_HIVE1_VALVE_ACTIVATED")</f>
-        <v>EVENT_HIVE1_VALVE_ACTIVATED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_TALKED_ARTURO_HALL_PUB")</f>
+        <v>EVENT_TALKED_ARTURO_HALL_PUB</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B89" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_TALKED_ARTURO_HALL_INN_COMPLETED")</f>
-        <v>EVENT_TALKED_ARTURO_HALL_INN_COMPLETED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_ITEM_EXTRAPERLO_INVITATION_PICKABLE_TAKEN")</f>
+        <v>EVENT_ITEM_EXTRAPERLO_INVITATION_PICKABLE_TAKEN</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B90" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_TALKED_ARTURO_HALL_PUB")</f>
-        <v>EVENT_TALKED_ARTURO_HALL_PUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_OBSERVED_INVITATION_RELIEF")</f>
+        <v>EVENT_OBSERVED_INVITATION_RELIEF</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B91" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_ITEM_EXTRAPERLO_INVITATION_PICKABLE_TAKEN")</f>
-        <v>EVENT_ITEM_EXTRAPERLO_INVITATION_PICKABLE_TAKEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_INKWELL_NOT_TOUCH_WARN")</f>
+        <v>EVENT_INKWELL_NOT_TOUCH_WARN</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B92" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_OBSERVED_INVITATION_RELIEF")</f>
-        <v>EVENT_OBSERVED_INVITATION_RELIEF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_INKWELL_WASTED")</f>
+        <v>EVENT_INKWELL_WASTED</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B93" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_INKWELL_NOT_TOUCH_WARN")</f>
-        <v>EVENT_INKWELL_NOT_TOUCH_WARN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_INVITATION_REVEALED")</f>
+        <v>EVENT_INVITATION_REVEALED</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B94" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_INKWELL_WASTED")</f>
-        <v>EVENT_INKWELL_WASTED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_INVITATION_UNDERSTOOD_PHRASE")</f>
+        <v>EVENT_INVITATION_UNDERSTOOD_PHRASE</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B95" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_INVITATION_REVEALED")</f>
-        <v>EVENT_INVITATION_REVEALED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_LAST")</f>
+        <v>EVENT_LAST</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B96" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_INVITATION_UNDERSTOOD_PHRASE")</f>
-        <v>EVENT_INVITATION_UNDERSTOOD_PHRASE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_NONE")</f>
+        <v>(NOT)EVENT_NONE</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B97" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EVENT_LAST")</f>
-        <v>EVENT_LAST</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_MASTER_CHANGE_ROOM")</f>
+        <v>(NOT)EVENT_MASTER_CHANGE_ROOM</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B98" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_NONE")</f>
-        <v>(NOT)EVENT_NONE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_MASTER_CHANGE_MOMENT_DAY")</f>
+        <v>(NOT)EVENT_MASTER_CHANGE_MOMENT_DAY</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B99" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_MASTER_CHANGE_ROOM")</f>
-        <v>(NOT)EVENT_MASTER_CHANGE_ROOM</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_MASTER_PENDING_SLEEP_NAP")</f>
+        <v>(NOT)EVENT_MASTER_PENDING_SLEEP_NAP</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B100" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_MASTER_CHANGE_MOMENT_DAY")</f>
-        <v>(NOT)EVENT_MASTER_CHANGE_MOMENT_DAY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_MASTER_PENDING_SLEEP_LONG")</f>
+        <v>(NOT)EVENT_MASTER_PENDING_SLEEP_LONG</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B101" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_MASTER_PENDING_SLEEP_NAP")</f>
-        <v>(NOT)EVENT_MASTER_PENDING_SLEEP_NAP</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_FIRST")</f>
+        <v>(NOT)EVENT_FIRST</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B102" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_MASTER_PENDING_SLEEP_LONG")</f>
-        <v>(NOT)EVENT_MASTER_PENDING_SLEEP_LONG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_HIVE1_CHEST_OPENED")</f>
+        <v>(NOT)EVENT_HIVE1_CHEST_OPENED</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B103" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_FIRST")</f>
-        <v>(NOT)EVENT_FIRST</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_CARDS_PICKABLE_TAKEN")</f>
+        <v>(NOT)EVENT_CARDS_PICKABLE_TAKEN</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B104" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_HIVE1_CHEST_OPENED")</f>
-        <v>(NOT)EVENT_HIVE1_CHEST_OPENED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_HIVE1_WARDROBE_OPENED")</f>
+        <v>(NOT)EVENT_HIVE1_WARDROBE_OPENED</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B105" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_CARDS_PICKABLE_TAKEN")</f>
-        <v>(NOT)EVENT_CARDS_PICKABLE_TAKEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_HIVE1_AD_BOARD_OBSERVED_1")</f>
+        <v>(NOT)EVENT_HIVE1_AD_BOARD_OBSERVED_1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B106" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_HIVE1_WARDROBE_OPENED")</f>
-        <v>(NOT)EVENT_HIVE1_WARDROBE_OPENED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_HIVE1_USED_PERFUME")</f>
+        <v>(NOT)EVENT_HIVE1_USED_PERFUME</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B107" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_HIVE1_AD_BOARD_OBSERVED_1")</f>
-        <v>(NOT)EVENT_HIVE1_AD_BOARD_OBSERVED_1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_HIVE1_USED_BASIN")</f>
+        <v>(NOT)EVENT_HIVE1_USED_BASIN</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B108" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_HIVE1_USED_PERFUME")</f>
-        <v>(NOT)EVENT_HIVE1_USED_PERFUME</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_SOAP_PICKABLE_TAKEN")</f>
+        <v>(NOT)EVENT_SOAP_PICKABLE_TAKEN</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B109" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_HIVE1_USED_BASIN")</f>
-        <v>(NOT)EVENT_HIVE1_USED_BASIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_LAUNCH_SLEEP_DECISION")</f>
+        <v>(NOT)EVENT_LAUNCH_SLEEP_DECISION</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B110" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_SOAP_PICKABLE_TAKEN")</f>
-        <v>(NOT)EVENT_SOAP_PICKABLE_TAKEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_PHARMACY_EMPTY")</f>
+        <v>(NOT)EVENT_PHARMACY_EMPTY</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B111" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_LAUNCH_SLEEP_DECISION")</f>
-        <v>(NOT)EVENT_LAUNCH_SLEEP_DECISION</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_MANYO_REFUSED_WORK")</f>
+        <v>(NOT)EVENT_MANYO_REFUSED_WORK</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B112" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_CAN_GO_SOUTH_NEIGH")</f>
-        <v>(NOT)EVENT_CAN_GO_SOUTH_NEIGH</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_MANYO_LOOK_FOR_RECIPE_MISSION")</f>
+        <v>(NOT)EVENT_MANYO_LOOK_FOR_RECIPE_MISSION</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B113" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_PHARMACY_EMPTY")</f>
-        <v>(NOT)EVENT_PHARMACY_EMPTY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_UMBRELLA_PICKABLE_TAKEN")</f>
+        <v>(NOT)EVENT_UMBRELLA_PICKABLE_TAKEN</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B114" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_MANYO_REFUSED_WORK")</f>
-        <v>(NOT)EVENT_MANYO_REFUSED_WORK</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_POOR_MAN_WC_NEED_WATER")</f>
+        <v>(NOT)EVENT_POOR_MAN_WC_NEED_WATER</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B115" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_MANYO_LOOK_FOR_RECIPE_MISSION")</f>
-        <v>(NOT)EVENT_MANYO_LOOK_FOR_RECIPE_MISSION</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_COCKROACH_CHEATED")</f>
+        <v>(NOT)EVENT_COCKROACH_CHEATED</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B116" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_UMBRELLA_PICKABLE_TAKEN")</f>
-        <v>(NOT)EVENT_UMBRELLA_PICKABLE_TAKEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_PIPE_OBSERVATION_1")</f>
+        <v>(NOT)EVENT_PIPE_OBSERVATION_1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B117" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_POOR_MAN_WC_NEED_WATER")</f>
-        <v>(NOT)EVENT_POOR_MAN_WC_NEED_WATER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_PIPE_OBSERVATION_2")</f>
+        <v>(NOT)EVENT_PIPE_OBSERVATION_2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B118" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_COCKROACH_CHEATED")</f>
-        <v>(NOT)EVENT_COCKROACH_CHEATED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_COCKROACH_SCARED")</f>
+        <v>(NOT)EVENT_COCKROACH_SCARED</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B119" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_PIPE_OBSERVATION_1")</f>
-        <v>(NOT)EVENT_PIPE_OBSERVATION_1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_VALVE_BOX_NEED_OPEN")</f>
+        <v>(NOT)EVENT_VALVE_BOX_NEED_OPEN</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B120" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_PIPE_OBSERVATION_2")</f>
-        <v>(NOT)EVENT_PIPE_OBSERVATION_2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_ITEM_HIVE1_SHOELACE_PICKABLE_TAKEN")</f>
+        <v>(NOT)EVENT_ITEM_HIVE1_SHOELACE_PICKABLE_TAKEN</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B121" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_COCKROACH_SCARED")</f>
-        <v>(NOT)EVENT_COCKROACH_SCARED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_VALVE_BOX_OPENED")</f>
+        <v>(NOT)EVENT_VALVE_BOX_OPENED</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B122" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_VALVE_BOX_NEED_OPEN")</f>
-        <v>(NOT)EVENT_VALVE_BOX_NEED_OPEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_HIVE1_VALVE_ACTIVATED")</f>
+        <v>(NOT)EVENT_HIVE1_VALVE_ACTIVATED</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B123" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_ITEM_HIVE1_SHOELACE_PICKABLE_TAKEN")</f>
-        <v>(NOT)EVENT_ITEM_HIVE1_SHOELACE_PICKABLE_TAKEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_TALKED_ARTURO_HALL_INN_COMPLETED")</f>
+        <v>(NOT)EVENT_TALKED_ARTURO_HALL_INN_COMPLETED</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B124" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_VALVE_BOX_OPENED")</f>
-        <v>(NOT)EVENT_VALVE_BOX_OPENED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_TALKED_ARTURO_HALL_PUB")</f>
+        <v>(NOT)EVENT_TALKED_ARTURO_HALL_PUB</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B125" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_HIVE1_VALVE_ACTIVATED")</f>
-        <v>(NOT)EVENT_HIVE1_VALVE_ACTIVATED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_ITEM_EXTRAPERLO_INVITATION_PICKABLE_TAKEN")</f>
+        <v>(NOT)EVENT_ITEM_EXTRAPERLO_INVITATION_PICKABLE_TAKEN</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B126" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_TALKED_ARTURO_HALL_INN_COMPLETED")</f>
-        <v>(NOT)EVENT_TALKED_ARTURO_HALL_INN_COMPLETED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_OBSERVED_INVITATION_RELIEF")</f>
+        <v>(NOT)EVENT_OBSERVED_INVITATION_RELIEF</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B127" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_TALKED_ARTURO_HALL_PUB")</f>
-        <v>(NOT)EVENT_TALKED_ARTURO_HALL_PUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_INKWELL_NOT_TOUCH_WARN")</f>
+        <v>(NOT)EVENT_INKWELL_NOT_TOUCH_WARN</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B128" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_ITEM_EXTRAPERLO_INVITATION_PICKABLE_TAKEN")</f>
-        <v>(NOT)EVENT_ITEM_EXTRAPERLO_INVITATION_PICKABLE_TAKEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_INKWELL_WASTED")</f>
+        <v>(NOT)EVENT_INKWELL_WASTED</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B129" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_OBSERVED_INVITATION_RELIEF")</f>
-        <v>(NOT)EVENT_OBSERVED_INVITATION_RELIEF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_INVITATION_REVEALED")</f>
+        <v>(NOT)EVENT_INVITATION_REVEALED</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B130" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_INKWELL_NOT_TOUCH_WARN")</f>
-        <v>(NOT)EVENT_INKWELL_NOT_TOUCH_WARN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_INVITATION_UNDERSTOOD_PHRASE")</f>
+        <v>(NOT)EVENT_INVITATION_UNDERSTOOD_PHRASE</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B131" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_INKWELL_WASTED")</f>
-        <v>(NOT)EVENT_INKWELL_WASTED</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_LAST")</f>
+        <v>(NOT)EVENT_LAST</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>71</v>
-      </c>
-      <c r="B132" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_INVITATION_REVEALED")</f>
-        <v>(NOT)EVENT_INVITATION_REVEALED</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B132" s="69"/>
     </row>
     <row r="133">
       <c r="A133" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>72</v>
-      </c>
-      <c r="B133" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_INVITATION_UNDERSTOOD_PHRASE")</f>
-        <v>(NOT)EVENT_INVITATION_UNDERSTOOD_PHRASE</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B133" s="69"/>
     </row>
     <row r="134">
       <c r="A134" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>73</v>
-      </c>
-      <c r="B134" s="69" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"(NOT)EVENT_LAST")</f>
-        <v>(NOT)EVENT_LAST</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="B134" s="69"/>
     </row>
     <row r="135">
       <c r="A135" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B135" s="69"/>
     </row>
     <row r="136">
       <c r="A136" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B136" s="69"/>
     </row>
     <row r="137">
       <c r="A137" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B137" s="69"/>
     </row>
     <row r="138">
       <c r="A138" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B138" s="69"/>
     </row>
     <row r="139">
       <c r="A139" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B139" s="69"/>
     </row>
     <row r="140">
       <c r="A140" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B140" s="69"/>
     </row>
     <row r="141">
       <c r="A141" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B141" s="69"/>
     </row>
     <row r="142">
       <c r="A142" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B142" s="69"/>
     </row>
     <row r="143">
       <c r="A143" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B143" s="69"/>
     </row>
     <row r="144">
       <c r="A144" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B144" s="69"/>
     </row>
     <row r="145">
       <c r="A145" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B145" s="69"/>
     </row>
     <row r="146">
       <c r="A146" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B146" s="69"/>
     </row>
     <row r="147">
       <c r="A147" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B147" s="69"/>
     </row>
     <row r="148">
       <c r="A148" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B148" s="69"/>
     </row>
     <row r="149">
       <c r="A149" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B149" s="69"/>
     </row>
     <row r="150">
       <c r="A150" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B150" s="69"/>
     </row>
     <row r="151">
       <c r="A151" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B151" s="69"/>
     </row>
     <row r="152">
       <c r="A152" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B152" s="69"/>
     </row>
     <row r="153">
       <c r="A153" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B153" s="69"/>
     </row>
     <row r="154">
       <c r="A154" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B154" s="69"/>
     </row>
     <row r="155">
       <c r="A155" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B155" s="69"/>
     </row>
     <row r="156">
       <c r="A156" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B156" s="69"/>
     </row>
     <row r="157">
       <c r="A157" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B157" s="69"/>
     </row>
     <row r="158">
       <c r="A158" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B158" s="69"/>
     </row>
     <row r="159">
       <c r="A159" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B159" s="69"/>
     </row>
     <row r="160">
       <c r="A160" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B160" s="69"/>
     </row>
     <row r="161">
       <c r="A161" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B161" s="69"/>
     </row>
     <row r="162">
       <c r="A162" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B162" s="69"/>
     </row>
     <row r="163">
       <c r="A163" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B163" s="69"/>
     </row>
     <row r="164">
       <c r="A164" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B164" s="69"/>
     </row>
     <row r="165">
       <c r="A165" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B165" s="69"/>
     </row>
     <row r="166">
       <c r="A166" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B166" s="69"/>
     </row>
     <row r="167">
       <c r="A167" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B167" s="69"/>
     </row>
     <row r="168">
       <c r="A168" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B168" s="69"/>
     </row>
     <row r="169">
       <c r="A169" s="46">
         <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B169" s="69"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="46">
-        <f>ROW()-ROW(Table_EventsCombi[N])</f>
-        <v>109</v>
-      </c>
-      <c r="B170" s="69"/>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="E48:E55">
+    <dataValidation type="list" allowBlank="1" sqref="E47:E54">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C41:D45 C48:D55 C58">
+    <dataValidation type="list" allowBlank="1" sqref="C40:D44 C47:D54 C57">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -12744,16 +12744,16 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1344</v>
+        <v>1349</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1347</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="2">
@@ -12765,7 +12765,7 @@
         <v>276</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1348</v>
+        <v>1353</v>
       </c>
       <c r="D2" s="70" t="s">
         <v>273</v>
@@ -12783,7 +12783,7 @@
         <v>391</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1349</v>
+        <v>1354</v>
       </c>
       <c r="D3" s="70" t="s">
         <v>273</v>
@@ -12798,10 +12798,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1350</v>
+        <v>1355</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1348</v>
+        <v>1353</v>
       </c>
       <c r="D4" s="70" t="s">
         <v>273</v>
@@ -12838,21 +12838,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1351</v>
+        <v>1356</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1352</v>
+        <v>1357</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="36" t="s">
-        <v>1355</v>
+        <v>1360</v>
       </c>
       <c r="B2" s="71">
         <v>1.0</v>
@@ -12866,7 +12866,7 @@
     </row>
     <row r="3">
       <c r="A3" s="36" t="s">
-        <v>1356</v>
+        <v>1361</v>
       </c>
       <c r="B3" s="71">
         <v>1.0</v>
@@ -12880,7 +12880,7 @@
     </row>
     <row r="4">
       <c r="A4" s="36" t="s">
-        <v>1357</v>
+        <v>1362</v>
       </c>
       <c r="B4" s="71">
         <v>3.0</v>
@@ -12894,7 +12894,7 @@
     </row>
     <row r="5">
       <c r="A5" s="36" t="s">
-        <v>1358</v>
+        <v>1363</v>
       </c>
       <c r="B5" s="71">
         <v>1.0</v>
@@ -12908,7 +12908,7 @@
     </row>
     <row r="6">
       <c r="A6" s="36" t="s">
-        <v>1359</v>
+        <v>1364</v>
       </c>
       <c r="B6" s="71">
         <v>3.0</v>
@@ -12922,7 +12922,7 @@
     </row>
     <row r="7">
       <c r="A7" s="36" t="s">
-        <v>1360</v>
+        <v>1365</v>
       </c>
       <c r="B7" s="71">
         <v>3.0</v>
@@ -12936,7 +12936,7 @@
     </row>
     <row r="8">
       <c r="A8" s="36" t="s">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="B8" s="71">
         <v>5.0</v>
@@ -12950,7 +12950,7 @@
     </row>
     <row r="9">
       <c r="A9" s="36" t="s">
-        <v>1362</v>
+        <v>1367</v>
       </c>
       <c r="B9" s="71">
         <v>4.0</v>
@@ -12964,7 +12964,7 @@
     </row>
     <row r="10">
       <c r="A10" s="36" t="s">
-        <v>1363</v>
+        <v>1368</v>
       </c>
       <c r="B10" s="71">
         <v>5.0</v>
@@ -12978,7 +12978,7 @@
     </row>
     <row r="11">
       <c r="A11" s="36" t="s">
-        <v>1364</v>
+        <v>1369</v>
       </c>
       <c r="B11" s="71">
         <v>4.0</v>
@@ -12992,7 +12992,7 @@
     </row>
     <row r="12">
       <c r="A12" s="36" t="s">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="B12" s="71">
         <v>1.0</v>
@@ -13006,7 +13006,7 @@
     </row>
     <row r="13">
       <c r="A13" s="36" t="s">
-        <v>1366</v>
+        <v>1371</v>
       </c>
       <c r="B13" s="71">
         <v>4.0</v>
@@ -13020,7 +13020,7 @@
     </row>
     <row r="14">
       <c r="A14" s="36" t="s">
-        <v>1367</v>
+        <v>1372</v>
       </c>
       <c r="B14" s="71">
         <v>1.0</v>
@@ -13034,7 +13034,7 @@
     </row>
     <row r="15">
       <c r="A15" s="36" t="s">
-        <v>1368</v>
+        <v>1373</v>
       </c>
       <c r="B15" s="71">
         <v>2.0</v>
@@ -13048,7 +13048,7 @@
     </row>
     <row r="16">
       <c r="A16" s="36" t="s">
-        <v>1369</v>
+        <v>1374</v>
       </c>
       <c r="B16" s="71">
         <v>3.0</v>
@@ -13062,7 +13062,7 @@
     </row>
     <row r="17">
       <c r="A17" s="36" t="s">
-        <v>1370</v>
+        <v>1375</v>
       </c>
       <c r="B17" s="71">
         <v>2.0</v>
@@ -13076,7 +13076,7 @@
     </row>
     <row r="18">
       <c r="A18" s="36" t="s">
-        <v>1371</v>
+        <v>1376</v>
       </c>
       <c r="B18" s="71">
         <v>2.0</v>
@@ -13090,7 +13090,7 @@
     </row>
     <row r="19">
       <c r="A19" s="36" t="s">
-        <v>1372</v>
+        <v>1377</v>
       </c>
       <c r="B19" s="71">
         <v>2.0</v>
@@ -13104,7 +13104,7 @@
     </row>
     <row r="20">
       <c r="A20" s="36" t="s">
-        <v>1373</v>
+        <v>1378</v>
       </c>
       <c r="B20" s="71">
         <v>2.0</v>
@@ -13118,7 +13118,7 @@
     </row>
     <row r="21">
       <c r="A21" s="36" t="s">
-        <v>1374</v>
+        <v>1379</v>
       </c>
       <c r="B21" s="71">
         <v>3.0</v>
@@ -13132,7 +13132,7 @@
     </row>
     <row r="22">
       <c r="A22" s="36" t="s">
-        <v>1375</v>
+        <v>1380</v>
       </c>
       <c r="B22" s="71">
         <v>2.0</v>
@@ -13146,7 +13146,7 @@
     </row>
     <row r="23">
       <c r="A23" s="36" t="s">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="B23" s="71">
         <v>2.0</v>
@@ -13160,7 +13160,7 @@
     </row>
     <row r="24">
       <c r="A24" s="36" t="s">
-        <v>1377</v>
+        <v>1382</v>
       </c>
       <c r="B24" s="71">
         <v>2.0</v>
@@ -13174,7 +13174,7 @@
     </row>
     <row r="25">
       <c r="A25" s="36" t="s">
-        <v>1378</v>
+        <v>1383</v>
       </c>
       <c r="B25" s="71">
         <v>2.0</v>
@@ -13188,7 +13188,7 @@
     </row>
     <row r="26">
       <c r="A26" s="36" t="s">
-        <v>1379</v>
+        <v>1384</v>
       </c>
       <c r="B26" s="71">
         <v>2.0</v>
@@ -13202,7 +13202,7 @@
     </row>
     <row r="27">
       <c r="A27" s="36" t="s">
-        <v>1380</v>
+        <v>1385</v>
       </c>
       <c r="B27" s="71">
         <v>2.0</v>
@@ -13216,7 +13216,7 @@
     </row>
     <row r="28">
       <c r="A28" s="36" t="s">
-        <v>1381</v>
+        <v>1386</v>
       </c>
       <c r="B28" s="71">
         <v>2.0</v>
@@ -13230,7 +13230,7 @@
     </row>
     <row r="29">
       <c r="A29" s="36" t="s">
-        <v>1382</v>
+        <v>1387</v>
       </c>
       <c r="B29" s="71">
         <v>4.0</v>
@@ -13244,7 +13244,7 @@
     </row>
     <row r="30">
       <c r="A30" s="36" t="s">
-        <v>1383</v>
+        <v>1388</v>
       </c>
       <c r="B30" s="71">
         <v>2.0</v>
@@ -13258,7 +13258,7 @@
     </row>
     <row r="31">
       <c r="A31" s="36" t="s">
-        <v>1384</v>
+        <v>1389</v>
       </c>
       <c r="B31" s="71">
         <v>3.0</v>
@@ -13272,7 +13272,7 @@
     </row>
     <row r="32">
       <c r="A32" s="36" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="B32" s="71">
         <v>5.0</v>
@@ -23732,8 +23732,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="16.14"/>
-    <col customWidth="1" min="3" max="4" width="16.57"/>
+    <col customWidth="1" min="2" max="2" width="57.14"/>
+    <col customWidth="1" min="3" max="3" width="16.57"/>
+    <col customWidth="1" min="4" max="4" width="66.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23801,6 +23802,81 @@
         <v>749</v>
       </c>
       <c r="C5" s="36" t="s">
+        <v>745</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="51">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>4</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>751</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>745</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="51">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>5</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>752</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>745</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="51">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>6</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>753</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>745</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="51">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>7</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>754</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>745</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="51">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>8</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>755</v>
+      </c>
+      <c r="C10" s="36" t="s">
         <v>745</v>
       </c>
     </row>
@@ -23835,13 +23911,13 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>24</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
     </row>
     <row r="2">
@@ -23856,7 +23932,7 @@
         <v>272</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
     </row>
     <row r="3">
@@ -23871,7 +23947,7 @@
         <v>272</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
     </row>
     <row r="4">
@@ -23886,7 +23962,7 @@
         <v>272</v>
       </c>
       <c r="D4" s="41" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
     </row>
     <row r="5">
@@ -23895,13 +23971,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="C5" s="41" t="s">
         <v>272</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
     </row>
     <row r="6">
@@ -23916,7 +23992,7 @@
         <v>272</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -23931,7 +24007,7 @@
         <v>272</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
     </row>
     <row r="8">
@@ -23940,13 +24016,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>272</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
     </row>
     <row r="9">
@@ -23961,7 +24037,7 @@
         <v>272</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
     </row>
     <row r="10">
@@ -23970,13 +24046,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="C10" s="41" t="s">
         <v>272</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
     </row>
     <row r="11">
@@ -23988,10 +24064,10 @@
         <v>480</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
     </row>
     <row r="12">
@@ -24006,7 +24082,7 @@
         <v>357</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
     </row>
     <row r="13">
@@ -24021,7 +24097,7 @@
         <v>359</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
     </row>
     <row r="14">
@@ -24030,13 +24106,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="C14" s="41" t="s">
         <v>272</v>
       </c>
       <c r="D14" s="41" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
     </row>
     <row r="15">
@@ -24051,7 +24127,7 @@
         <v>272</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
     </row>
     <row r="16">
@@ -24060,13 +24136,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="C16" s="41" t="s">
         <v>272</v>
       </c>
       <c r="D16" s="41" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
     </row>
     <row r="17">
@@ -24081,7 +24157,7 @@
         <v>272</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
     </row>
     <row r="18">
@@ -24096,7 +24172,7 @@
         <v>33</v>
       </c>
       <c r="D18" s="41" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
     </row>
     <row r="19">
@@ -24111,7 +24187,7 @@
         <v>272</v>
       </c>
       <c r="D19" s="41" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
     </row>
     <row r="20">
@@ -24120,13 +24196,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="C20" s="41" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
     </row>
     <row r="21">
@@ -24135,13 +24211,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="C21" s="41" t="s">
         <v>272</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
     </row>
     <row r="23">
@@ -24149,25 +24225,25 @@
         <v>44</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>404</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="H23" s="28" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
     </row>
     <row r="24">
@@ -24176,7 +24252,7 @@
         <v>0</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="C24" s="37" t="s">
         <v>413</v>
@@ -24203,7 +24279,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="C25" s="37" t="s">
         <v>413</v>
@@ -24230,7 +24306,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="C26" s="40" t="s">
         <v>413</v>
@@ -24242,13 +24318,13 @@
         <v>413</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="G26" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="40" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
     </row>
     <row r="27">
@@ -24257,7 +24333,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="C27" s="40" t="s">
         <v>413</v>
@@ -24269,13 +24345,13 @@
         <v>413</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="G27" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H27" s="40" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
     </row>
     <row r="28">
@@ -24284,7 +24360,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C28" s="40" t="s">
         <v>413</v>
@@ -24302,7 +24378,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="40" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
     </row>
     <row r="29">
@@ -24311,7 +24387,7 @@
         <v>5</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>413</v>
@@ -24329,7 +24405,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="40" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
     </row>
     <row r="30">
@@ -24338,7 +24414,7 @@
         <v>6</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>413</v>
@@ -24350,13 +24426,13 @@
         <v>413</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="G30" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="40" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
     </row>
     <row r="31">
@@ -24365,7 +24441,7 @@
         <v>7</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>413</v>
@@ -24383,7 +24459,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="40" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
     </row>
     <row r="32">
@@ -24392,7 +24468,7 @@
         <v>8</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C32" s="40" t="s">
         <v>413</v>
@@ -24404,13 +24480,13 @@
         <v>413</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="G32" s="53" t="b">
         <v>1</v>
       </c>
       <c r="H32" s="40" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
     </row>
     <row r="33">
@@ -24419,7 +24495,7 @@
         <v>9</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C33" s="40" t="s">
         <v>413</v>
@@ -24428,16 +24504,16 @@
         <v>479</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="G33" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H33" s="40" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
     </row>
     <row r="34">
@@ -24446,10 +24522,10 @@
         <v>10</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="D34" s="52" t="s">
         <v>479</v>
@@ -24458,13 +24534,13 @@
         <v>413</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="G34" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="40" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
     </row>
     <row r="35">
@@ -24473,7 +24549,7 @@
         <v>11</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="C35" s="40" t="s">
         <v>413</v>
@@ -24485,13 +24561,13 @@
         <v>413</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="G35" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H35" s="40" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
     </row>
     <row r="36">
@@ -24500,10 +24576,10 @@
         <v>12</v>
       </c>
       <c r="B36" s="36" t="s">
+        <v>807</v>
+      </c>
+      <c r="C36" s="40" t="s">
         <v>801</v>
-      </c>
-      <c r="C36" s="40" t="s">
-        <v>795</v>
       </c>
       <c r="D36" s="52" t="s">
         <v>482</v>
@@ -24512,13 +24588,13 @@
         <v>625</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="G36" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H36" s="40" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
     </row>
     <row r="37">
@@ -24527,7 +24603,7 @@
         <v>13</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="C37" s="40" t="s">
         <v>413</v>
@@ -24545,7 +24621,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="40" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
     </row>
     <row r="38">
@@ -24554,7 +24630,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="C38" s="40" t="s">
         <v>413</v>
@@ -24572,7 +24648,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="40" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
     </row>
     <row r="39">
@@ -24581,7 +24657,7 @@
         <v>15</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="C39" s="40" t="s">
         <v>413</v>
@@ -24599,7 +24675,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="40" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
     </row>
     <row r="40">
@@ -24608,7 +24684,7 @@
         <v>16</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="C40" s="40" t="s">
         <v>413</v>
@@ -24626,7 +24702,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="40" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
     </row>
     <row r="41">
@@ -24635,7 +24711,7 @@
         <v>17</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="C41" s="40" t="s">
         <v>413</v>
@@ -24647,13 +24723,13 @@
         <v>413</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="G41" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
     </row>
     <row r="42">
@@ -24662,7 +24738,7 @@
         <v>18</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="C42" s="40" t="s">
         <v>413</v>
@@ -24674,13 +24750,13 @@
         <v>413</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="G42" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H42" s="40" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
     </row>
     <row r="43">
@@ -24689,7 +24765,7 @@
         <v>19</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>413</v>
@@ -24701,13 +24777,13 @@
         <v>501</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="G43" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H43" s="40" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
     </row>
     <row r="44">
@@ -24716,7 +24792,7 @@
         <v>20</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>413</v>
@@ -24734,7 +24810,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="40" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
     </row>
     <row r="45">
@@ -24743,7 +24819,7 @@
         <v>21</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="C45" s="40" t="s">
         <v>413</v>
@@ -24755,13 +24831,13 @@
         <v>413</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="G45" s="53" t="b">
         <v>1</v>
       </c>
       <c r="H45" s="40" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
     </row>
     <row r="46">
@@ -24770,7 +24846,7 @@
         <v>22</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="C46" s="40" t="s">
         <v>413</v>
@@ -24779,16 +24855,16 @@
         <v>414</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="G46" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="40" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
     </row>
     <row r="47">
@@ -24797,25 +24873,25 @@
         <v>23</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="C47" s="40" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="D47" s="52" t="s">
         <v>414</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="G47" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H47" s="40" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
     </row>
     <row r="48">
@@ -24824,7 +24900,7 @@
         <v>24</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C48" s="40" t="s">
         <v>413</v>
@@ -24842,7 +24918,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="40" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
     </row>
     <row r="49">
@@ -24851,7 +24927,7 @@
         <v>25</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C49" s="40" t="s">
         <v>413</v>
@@ -24863,13 +24939,13 @@
         <v>413</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="G49" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H49" s="40" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
     </row>
     <row r="50">
@@ -24878,7 +24954,7 @@
         <v>26</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="C50" s="40" t="s">
         <v>413</v>
@@ -24896,7 +24972,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="40" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
     </row>
     <row r="51">
@@ -24905,7 +24981,7 @@
         <v>27</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="C51" s="40" t="s">
         <v>413</v>
@@ -24917,13 +24993,13 @@
         <v>648</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="G51" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H51" s="40" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
     </row>
     <row r="52">
@@ -24932,7 +25008,7 @@
         <v>28</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="C52" s="40" t="s">
         <v>413</v>
@@ -24950,7 +25026,7 @@
         <v>0</v>
       </c>
       <c r="H52" s="40" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
     </row>
     <row r="53">
@@ -24959,7 +25035,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="C53" s="37" t="s">
         <v>413</v>
@@ -25079,10 +25155,10 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="C1" s="55" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
     </row>
     <row r="2">
@@ -25094,7 +25170,7 @@
         <v>587</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
     </row>
     <row r="3">
@@ -25106,7 +25182,7 @@
         <v>617</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
     </row>
     <row r="4">
@@ -25115,10 +25191,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
     </row>
     <row r="6">
@@ -25126,13 +25202,13 @@
         <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7">
@@ -25141,7 +25217,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>419</v>
@@ -25156,10 +25232,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="D8" s="56" t="s">
         <v>413</v>
@@ -25171,13 +25247,13 @@
         <v>2</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
     </row>
     <row r="10">
@@ -25186,13 +25262,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
     </row>
     <row r="11">
@@ -25201,7 +25277,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>419</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -18,7 +18,8 @@
     <sheet state="visible" name="TYPES" sheetId="13" r:id="rId17"/>
     <sheet state="visible" name="EVENTS" sheetId="14" r:id="rId18"/>
     <sheet state="visible" name="DETAILS" sheetId="15" r:id="rId19"/>
-    <sheet state="visible" name="_TODO" sheetId="16" r:id="rId20"/>
+    <sheet state="visible" name="ANIMATIONS" sheetId="16" r:id="rId20"/>
+    <sheet state="visible" name="_TODO" sheetId="17" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="Interval_autoInsertMemento">FN!$A$10:$E$11</definedName>
@@ -122,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3915" uniqueCount="1395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3919" uniqueCount="1397">
   <si>
     <t>NewItem</t>
   </si>
@@ -4205,6 +4206,12 @@
   </si>
   <si>
     <t>DETAIL_LAST</t>
+  </si>
+  <si>
+    <t>ANIMATION_NONE</t>
+  </si>
+  <si>
+    <t>ANIMATION_LAST</t>
   </si>
   <si>
     <t>TASK</t>
@@ -4678,7 +4685,7 @@
       <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="32">
+  <tableStyles count="33">
     <tableStyle count="4" pivot="0" name="FN-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
@@ -4860,6 +4867,12 @@
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
     <tableStyle count="4" pivot="0" name="DETAILS-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+    <tableStyle count="4" pivot="0" name="ANIMATIONS-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -5473,6 +5486,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
@@ -5817,7 +5834,17 @@
 </file>
 
 <file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D32" displayName="Table_TODO" name="Table_TODO" id="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:B3" displayName="Table_Animations" name="Table_Animations" id="32">
+  <tableColumns count="2">
+    <tableColumn name="N" id="1"/>
+    <tableColumn name="ANIMATION_ID" id="2"/>
+  </tableColumns>
+  <tableStyleInfo name="ANIMATIONS-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D32" displayName="Table_TODO" name="Table_TODO" id="33">
   <tableColumns count="4">
     <tableColumn name="TASK" id="1"/>
     <tableColumn name="PRIO" id="2"/>
@@ -12843,6 +12870,51 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
+    <tabColor rgb="FF6FA8DC"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="19.0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="36">
+        <f>ROW()-ROW(Table_Animations[N])</f>
+        <v>0</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="36">
+        <f>ROW()-ROW(Table_Animations[N])</f>
+        <v>1</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
@@ -12855,21 +12927,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="36" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="B2" s="71">
         <v>1.0</v>
@@ -12883,7 +12955,7 @@
     </row>
     <row r="3">
       <c r="A3" s="36" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B3" s="71">
         <v>1.0</v>
@@ -12897,7 +12969,7 @@
     </row>
     <row r="4">
       <c r="A4" s="36" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="B4" s="71">
         <v>3.0</v>
@@ -12911,7 +12983,7 @@
     </row>
     <row r="5">
       <c r="A5" s="36" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="B5" s="71">
         <v>1.0</v>
@@ -12925,7 +12997,7 @@
     </row>
     <row r="6">
       <c r="A6" s="36" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="B6" s="71">
         <v>3.0</v>
@@ -12939,7 +13011,7 @@
     </row>
     <row r="7">
       <c r="A7" s="36" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="B7" s="71">
         <v>3.0</v>
@@ -12953,7 +13025,7 @@
     </row>
     <row r="8">
       <c r="A8" s="36" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="B8" s="71">
         <v>5.0</v>
@@ -12967,7 +13039,7 @@
     </row>
     <row r="9">
       <c r="A9" s="36" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="B9" s="71">
         <v>4.0</v>
@@ -12981,7 +13053,7 @@
     </row>
     <row r="10">
       <c r="A10" s="36" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="B10" s="71">
         <v>5.0</v>
@@ -12995,7 +13067,7 @@
     </row>
     <row r="11">
       <c r="A11" s="36" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="B11" s="71">
         <v>4.0</v>
@@ -13009,7 +13081,7 @@
     </row>
     <row r="12">
       <c r="A12" s="36" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="B12" s="71">
         <v>1.0</v>
@@ -13023,7 +13095,7 @@
     </row>
     <row r="13">
       <c r="A13" s="36" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="B13" s="71">
         <v>4.0</v>
@@ -13037,7 +13109,7 @@
     </row>
     <row r="14">
       <c r="A14" s="36" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="B14" s="71">
         <v>1.0</v>
@@ -13051,7 +13123,7 @@
     </row>
     <row r="15">
       <c r="A15" s="36" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="B15" s="71">
         <v>2.0</v>
@@ -13065,7 +13137,7 @@
     </row>
     <row r="16">
       <c r="A16" s="36" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="B16" s="71">
         <v>3.0</v>
@@ -13079,7 +13151,7 @@
     </row>
     <row r="17">
       <c r="A17" s="36" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="B17" s="71">
         <v>2.0</v>
@@ -13093,7 +13165,7 @@
     </row>
     <row r="18">
       <c r="A18" s="36" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="B18" s="71">
         <v>2.0</v>
@@ -13107,7 +13179,7 @@
     </row>
     <row r="19">
       <c r="A19" s="36" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="B19" s="71">
         <v>2.0</v>
@@ -13121,7 +13193,7 @@
     </row>
     <row r="20">
       <c r="A20" s="36" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="B20" s="71">
         <v>2.0</v>
@@ -13135,7 +13207,7 @@
     </row>
     <row r="21">
       <c r="A21" s="36" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="B21" s="71">
         <v>3.0</v>
@@ -13149,7 +13221,7 @@
     </row>
     <row r="22">
       <c r="A22" s="36" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="B22" s="71">
         <v>2.0</v>
@@ -13163,7 +13235,7 @@
     </row>
     <row r="23">
       <c r="A23" s="36" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="B23" s="71">
         <v>2.0</v>
@@ -13177,7 +13249,7 @@
     </row>
     <row r="24">
       <c r="A24" s="36" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="B24" s="71">
         <v>2.0</v>
@@ -13191,7 +13263,7 @@
     </row>
     <row r="25">
       <c r="A25" s="36" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="B25" s="71">
         <v>2.0</v>
@@ -13205,7 +13277,7 @@
     </row>
     <row r="26">
       <c r="A26" s="36" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="B26" s="71">
         <v>2.0</v>
@@ -13219,7 +13291,7 @@
     </row>
     <row r="27">
       <c r="A27" s="36" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="B27" s="71">
         <v>2.0</v>
@@ -13233,7 +13305,7 @@
     </row>
     <row r="28">
       <c r="A28" s="36" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="B28" s="71">
         <v>2.0</v>
@@ -13247,7 +13319,7 @@
     </row>
     <row r="29">
       <c r="A29" s="36" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B29" s="71">
         <v>4.0</v>
@@ -13261,7 +13333,7 @@
     </row>
     <row r="30">
       <c r="A30" s="36" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="B30" s="71">
         <v>2.0</v>
@@ -13275,7 +13347,7 @@
     </row>
     <row r="31">
       <c r="A31" s="36" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="B31" s="71">
         <v>3.0</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5072" uniqueCount="1555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5072" uniqueCount="1559">
   <si>
     <t>NewItem</t>
   </si>
@@ -392,6 +392,15 @@
     <t>CameraDispositionStruct_Default</t>
   </si>
   <si>
+    <t>DAY_MOMENT</t>
+  </si>
+  <si>
+    <t>MomentType</t>
+  </si>
+  <si>
+    <t>MomentType.MOMENT_MORNING</t>
+  </si>
+  <si>
     <t>ITEM_MENU_HOVER</t>
   </si>
   <si>
@@ -455,15 +464,6 @@
     <t>false</t>
   </si>
   <si>
-    <t>DAY_MOMENT</t>
-  </si>
-  <si>
-    <t>MomentType</t>
-  </si>
-  <si>
-    <t>MomentType.MOMENT_MORNING</t>
-  </si>
-  <si>
     <t>LAST_VARMAP_VAL</t>
   </si>
   <si>
@@ -2891,6 +2891,9 @@
     <t>DIALOG_OPTION_SIMPLE</t>
   </si>
   <si>
+    <t>ITEM_PLAYER_MAIN, ITEM_HIVE1_NPC_REME</t>
+  </si>
+  <si>
     <t>DIALOG_OPTION_REME_INTRO</t>
   </si>
   <si>
@@ -2903,6 +2906,9 @@
     <t>DIALOG_OPTION_REME_CARDS</t>
   </si>
   <si>
+    <t>ITEM_PLAYER_MAIN, ITEM_PHARMACY_NPC_OWNER</t>
+  </si>
+  <si>
     <t>DIALOG_OPTION_TRY_TALK_PHARMACIST</t>
   </si>
   <si>
@@ -2912,6 +2918,9 @@
     <t>DIALOG_OPTION_PHARMACIST_BUSY</t>
   </si>
   <si>
+    <t>ITEM_PLAYER_MAIN, ITEM_ELMANYO_OWNER</t>
+  </si>
+  <si>
     <t>DIALOG_OPTION_MANYO_ONWER_INTRO</t>
   </si>
   <si>
@@ -2921,9 +2930,6 @@
     <t>DIALOG_OPTION_MANYO_WORK_NOTE, DIALOG_OPTION_MANYO_WORKS_CITY, DIALOG_OPTION_MANYO_MENU_DAY, DIALOG_OPTION_MANYO_CROWD, DIALOG_OPTION_MANYO_BYE</t>
   </si>
   <si>
-    <t>ITEM_PLAYER_MAIN, ITEM_ELMANYO_OWNER</t>
-  </si>
-  <si>
     <t>DIALOG_OPTION_MANYO_UMBRELLA</t>
   </si>
   <si>
@@ -2936,6 +2942,9 @@
     <t>DIALOG_HIVE1_POOR_MAN_WC</t>
   </si>
   <si>
+    <t>ITEM_PLAYER_MAIN, ITEM_HIVE1_POOR_MAN_WC</t>
+  </si>
+  <si>
     <t>DIALOG_HIVE1_POOR_MAN_WC_OPTION_0, DIALOG_HIVE1_POOR_MAN_WC_OPTION_1, DIALOG_HIVE1_POOR_MAN_WC_OPTION_2, DIALOG_HIVE1_POOR_MAN_WC_OPTION_3</t>
   </si>
   <si>
@@ -2943,6 +2952,9 @@
   </si>
   <si>
     <t>DIALOG_ARTURO_HALL_INN</t>
+  </si>
+  <si>
+    <t>ITEM_PLAYER_MAIN, ITEM_HIVE1_MAN_WC_CURED</t>
   </si>
   <si>
     <t>DIALOG_ARTURO_HALL_INN_OPTION_0, DIALOG_ARTURO_HALL_INN_OPTION_1, DIALOG_ARTURO_HALL_INN_OPTION_2</t>
@@ -6881,13 +6893,13 @@
         <v>44</v>
       </c>
       <c r="B1" s="59" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="2">
@@ -6910,10 +6922,10 @@
         <v>300</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="4">
@@ -6922,13 +6934,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="5">
@@ -6937,13 +6949,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="6">
@@ -6952,13 +6964,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="7">
@@ -6970,10 +6982,10 @@
         <v>303</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="8">
@@ -6985,10 +6997,10 @@
         <v>324</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="9">
@@ -7000,10 +7012,10 @@
         <v>331</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="10">
@@ -7015,10 +7027,10 @@
         <v>309</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="11">
@@ -7027,13 +7039,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="12">
@@ -7042,13 +7054,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="13">
@@ -7060,10 +7072,10 @@
         <v>314</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="14">
@@ -7075,10 +7087,10 @@
         <v>321</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="15">
@@ -7087,13 +7099,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="16">
@@ -7105,10 +7117,10 @@
         <v>334</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="17">
@@ -7120,10 +7132,10 @@
         <v>339</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="18">
@@ -7135,10 +7147,10 @@
         <v>342</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="19">
@@ -7150,10 +7162,10 @@
         <v>346</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="20">
@@ -7165,10 +7177,10 @@
         <v>349</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="21">
@@ -7180,10 +7192,10 @@
         <v>352</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="22">
@@ -7195,10 +7207,10 @@
         <v>354</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="23">
@@ -7210,10 +7222,10 @@
         <v>356</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="24">
@@ -7225,10 +7237,10 @@
         <v>358</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="25">
@@ -7240,10 +7252,10 @@
         <v>360</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="26">
@@ -7255,10 +7267,10 @@
         <v>364</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="27">
@@ -7270,10 +7282,10 @@
         <v>369</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="28">
@@ -7285,10 +7297,10 @@
         <v>371</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="29">
@@ -7300,10 +7312,10 @@
         <v>375</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="30">
@@ -7312,13 +7324,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="31">
@@ -7330,10 +7342,10 @@
         <v>379</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="32">
@@ -7345,10 +7357,10 @@
         <v>381</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="33">
@@ -7357,13 +7369,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>41</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="34">
@@ -7375,10 +7387,10 @@
         <v>385</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="35">
@@ -7390,10 +7402,10 @@
         <v>389</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="36">
@@ -7405,10 +7417,10 @@
         <v>392</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="37">
@@ -7420,10 +7432,10 @@
         <v>397</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="38">
@@ -7435,10 +7447,10 @@
         <v>402</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="39">
@@ -7450,10 +7462,10 @@
         <v>406</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="40">
@@ -7465,10 +7477,10 @@
         <v>410</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="41">
@@ -7480,10 +7492,10 @@
         <v>414</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="42">
@@ -7495,10 +7507,10 @@
         <v>417</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="43">
@@ -7510,10 +7522,10 @@
         <v>11</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="44">
@@ -7525,10 +7537,10 @@
         <v>422</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
     </row>
   </sheetData>
@@ -7562,22 +7574,22 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="G1" s="61" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="2">
@@ -7595,7 +7607,7 @@
         <v>906</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="F2" s="62"/>
       <c r="G2" s="37"/>
@@ -7615,13 +7627,13 @@
         <v>906</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="4">
@@ -7639,13 +7651,13 @@
         <v>906</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="5">
@@ -7663,13 +7675,13 @@
         <v>906</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="6">
@@ -7678,7 +7690,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="C6" s="36">
         <v>0.0</v>
@@ -7687,13 +7699,13 @@
         <v>906</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="7">
@@ -7702,7 +7714,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="C7" s="36">
         <v>0.0</v>
@@ -7711,13 +7723,13 @@
         <v>906</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="8">
@@ -7735,13 +7747,13 @@
         <v>906</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="G8" s="37" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="9">
@@ -7750,7 +7762,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="C9" s="36">
         <v>0.0</v>
@@ -7759,13 +7771,13 @@
         <v>906</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="G9" s="37" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="10">
@@ -7774,7 +7786,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="C10" s="36">
         <v>0.0</v>
@@ -7783,13 +7795,13 @@
         <v>906</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="11">
@@ -7798,7 +7810,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="C11" s="36">
         <v>1.0</v>
@@ -7807,13 +7819,13 @@
         <v>906</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="12">
@@ -7822,7 +7834,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="C12" s="36">
         <v>0.0</v>
@@ -7831,13 +7843,13 @@
         <v>906</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="13">
@@ -7846,7 +7858,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="C13" s="36">
         <v>0.0</v>
@@ -7855,13 +7867,13 @@
         <v>906</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="G13" s="37" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="14">
@@ -7870,7 +7882,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="C14" s="36">
         <v>1.0</v>
@@ -7879,13 +7891,13 @@
         <v>906</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="15">
@@ -7894,7 +7906,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="C15" s="36">
         <v>1.0</v>
@@ -7903,13 +7915,13 @@
         <v>906</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="16">
@@ -7918,7 +7930,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="C16" s="36">
         <v>1.0</v>
@@ -7927,13 +7939,13 @@
         <v>906</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="17">
@@ -7942,7 +7954,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="C17" s="36">
         <v>0.0</v>
@@ -7951,13 +7963,13 @@
         <v>906</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="18">
@@ -7975,13 +7987,13 @@
         <v>906</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="19">
@@ -7999,13 +8011,13 @@
         <v>906</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="G19" s="37" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="20">
@@ -8023,13 +8035,13 @@
         <v>906</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="21">
@@ -8047,13 +8059,13 @@
         <v>906</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="22">
@@ -8071,13 +8083,13 @@
         <v>906</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="23">
@@ -8095,13 +8107,13 @@
         <v>906</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="24">
@@ -8119,13 +8131,13 @@
         <v>906</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="25">
@@ -8143,13 +8155,13 @@
         <v>906</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="G25" s="37" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="26">
@@ -8158,7 +8170,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="C26" s="36">
         <v>0.0</v>
@@ -8167,13 +8179,13 @@
         <v>906</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="27">
@@ -8182,7 +8194,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="C27" s="36">
         <v>1.0</v>
@@ -8191,13 +8203,13 @@
         <v>906</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="28">
@@ -8206,7 +8218,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="C28" s="36">
         <v>0.0</v>
@@ -8215,13 +8227,13 @@
         <v>906</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="29">
@@ -8230,7 +8242,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="C29" s="36">
         <v>0.0</v>
@@ -8239,13 +8251,13 @@
         <v>906</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="30">
@@ -8254,7 +8266,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="C30" s="36">
         <v>0.0</v>
@@ -8263,13 +8275,13 @@
         <v>906</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="31">
@@ -8287,13 +8299,13 @@
         <v>906</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="32">
@@ -8302,7 +8314,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="C32" s="36">
         <v>0.0</v>
@@ -8311,13 +8323,13 @@
         <v>906</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="33">
@@ -8326,7 +8338,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="C33" s="36">
         <v>1.0</v>
@@ -8335,13 +8347,13 @@
         <v>906</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="34">
@@ -8350,7 +8362,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="C34" s="36">
         <v>1.0</v>
@@ -8359,13 +8371,13 @@
         <v>906</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="35">
@@ -8383,13 +8395,13 @@
         <v>906</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="36">
@@ -8398,7 +8410,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="C36" s="36">
         <v>0.0</v>
@@ -8407,13 +8419,13 @@
         <v>906</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="37">
@@ -8422,7 +8434,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="C37" s="36">
         <v>1.0</v>
@@ -8431,13 +8443,13 @@
         <v>906</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="38">
@@ -8446,7 +8458,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="C38" s="36">
         <v>0.0</v>
@@ -8455,13 +8467,13 @@
         <v>906</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="39">
@@ -8470,7 +8482,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="C39" s="36">
         <v>1.0</v>
@@ -8479,13 +8491,13 @@
         <v>906</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="40">
@@ -8494,7 +8506,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="C40" s="36">
         <v>0.0</v>
@@ -8503,13 +8515,13 @@
         <v>906</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="41">
@@ -8518,7 +8530,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="C41" s="36">
         <v>1.0</v>
@@ -8527,13 +8539,13 @@
         <v>906</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="42">
@@ -8542,7 +8554,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="C42" s="36">
         <v>0.0</v>
@@ -8551,13 +8563,13 @@
         <v>906</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="43">
@@ -8566,7 +8578,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="C43" s="36">
         <v>1.0</v>
@@ -8575,13 +8587,13 @@
         <v>906</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="44">
@@ -8590,7 +8602,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="C44" s="36">
         <v>0.0</v>
@@ -8599,13 +8611,13 @@
         <v>906</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="45">
@@ -8614,7 +8626,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="C45" s="36">
         <v>1.0</v>
@@ -8623,13 +8635,13 @@
         <v>906</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="46">
@@ -8638,7 +8650,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="C46" s="36">
         <v>1.0</v>
@@ -8647,13 +8659,13 @@
         <v>906</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="47">
@@ -8662,7 +8674,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="C47" s="36">
         <v>0.0</v>
@@ -8671,13 +8683,13 @@
         <v>906</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="G47" s="37" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="48">
@@ -8686,7 +8698,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="C48" s="36">
         <v>1.0</v>
@@ -8695,13 +8707,13 @@
         <v>906</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="49">
@@ -8710,7 +8722,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="C49" s="36">
         <v>0.0</v>
@@ -8719,13 +8731,13 @@
         <v>906</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="G49" s="37" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="50">
@@ -8734,7 +8746,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="C50" s="36">
         <v>0.0</v>
@@ -8743,13 +8755,13 @@
         <v>906</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="G50" s="37" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="51">
@@ -8758,7 +8770,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="C51" s="36">
         <v>1.0</v>
@@ -8767,13 +8779,13 @@
         <v>906</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="52">
@@ -8782,7 +8794,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="C52" s="36">
         <v>1.0</v>
@@ -8791,13 +8803,13 @@
         <v>906</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="53">
@@ -8806,7 +8818,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="C53" s="36">
         <v>1.0</v>
@@ -8815,13 +8827,13 @@
         <v>906</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="54">
@@ -8830,7 +8842,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="C54" s="36">
         <v>0.0</v>
@@ -8839,13 +8851,13 @@
         <v>906</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="55">
@@ -8854,7 +8866,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="C55" s="36">
         <v>0.0</v>
@@ -8863,13 +8875,13 @@
         <v>906</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="G55" s="37" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="56">
@@ -8878,7 +8890,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="C56" s="36">
         <v>0.0</v>
@@ -8887,13 +8899,13 @@
         <v>906</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="57">
@@ -8902,7 +8914,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="C57" s="36">
         <v>1.0</v>
@@ -8911,13 +8923,13 @@
         <v>906</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="58">
@@ -8935,13 +8947,13 @@
         <v>906</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="59">
@@ -8950,7 +8962,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="C59" s="36">
         <v>0.0</v>
@@ -8959,13 +8971,13 @@
         <v>906</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="60">
@@ -8974,7 +8986,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="C60" s="36">
         <v>0.0</v>
@@ -8983,13 +8995,13 @@
         <v>906</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="61">
@@ -8998,7 +9010,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="C61" s="36">
         <v>0.0</v>
@@ -9007,13 +9019,13 @@
         <v>906</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="62">
@@ -9031,13 +9043,13 @@
         <v>906</v>
       </c>
       <c r="E62" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="63">
@@ -9046,7 +9058,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C63" s="36">
         <v>0.0</v>
@@ -9055,13 +9067,13 @@
         <v>913</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="64">
@@ -9070,7 +9082,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="C64" s="36">
         <v>0.0</v>
@@ -9079,13 +9091,13 @@
         <v>914</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F64" s="37" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="G64" s="37" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="65">
@@ -9094,7 +9106,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="C65" s="36">
         <v>0.0</v>
@@ -9103,13 +9115,13 @@
         <v>915</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="66">
@@ -9118,7 +9130,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="C66" s="36">
         <v>0.0</v>
@@ -9127,13 +9139,13 @@
         <v>916</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="67">
@@ -9142,7 +9154,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="C67" s="36">
         <v>0.0</v>
@@ -9151,13 +9163,13 @@
         <v>906</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="G67" s="37" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="68">
@@ -9166,7 +9178,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="C68" s="36">
         <v>1.0</v>
@@ -9175,13 +9187,13 @@
         <v>906</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="69">
@@ -9190,7 +9202,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="C69" s="36">
         <v>0.0</v>
@@ -9199,13 +9211,13 @@
         <v>906</v>
       </c>
       <c r="E69" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="70">
@@ -9214,7 +9226,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="C70" s="36">
         <v>1.0</v>
@@ -9223,13 +9235,13 @@
         <v>906</v>
       </c>
       <c r="E70" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="G70" s="37" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="71">
@@ -9238,7 +9250,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="C71" s="36">
         <v>0.0</v>
@@ -9247,13 +9259,13 @@
         <v>906</v>
       </c>
       <c r="E71" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="G71" s="37" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="72">
@@ -9262,7 +9274,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="C72" s="36">
         <v>1.0</v>
@@ -9271,13 +9283,13 @@
         <v>906</v>
       </c>
       <c r="E72" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F72" s="37" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="G72" s="37" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="73">
@@ -9286,7 +9298,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="C73" s="36">
         <v>0.0</v>
@@ -9295,13 +9307,13 @@
         <v>906</v>
       </c>
       <c r="E73" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F73" s="37" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="G73" s="37" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="74">
@@ -9310,7 +9322,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="C74" s="36">
         <v>1.0</v>
@@ -9319,13 +9331,13 @@
         <v>906</v>
       </c>
       <c r="E74" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F74" s="37" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="G74" s="37" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="75">
@@ -9334,7 +9346,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C75" s="36">
         <v>0.0</v>
@@ -9343,13 +9355,13 @@
         <v>906</v>
       </c>
       <c r="E75" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F75" s="37" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="G75" s="37" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="76">
@@ -9358,7 +9370,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="C76" s="36">
         <v>1.0</v>
@@ -9367,13 +9379,13 @@
         <v>906</v>
       </c>
       <c r="E76" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F76" s="37" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="G76" s="37" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="77">
@@ -9382,7 +9394,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="C77" s="36">
         <v>0.0</v>
@@ -9391,13 +9403,13 @@
         <v>906</v>
       </c>
       <c r="E77" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F77" s="37" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="G77" s="37" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="78">
@@ -9406,7 +9418,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="C78" s="36">
         <v>0.0</v>
@@ -9415,13 +9427,13 @@
         <v>906</v>
       </c>
       <c r="E78" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F78" s="37" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="G78" s="37" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="79">
@@ -9430,7 +9442,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="C79" s="36">
         <v>1.0</v>
@@ -9439,13 +9451,13 @@
         <v>906</v>
       </c>
       <c r="E79" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F79" s="37" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="G79" s="37" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="80">
@@ -9454,7 +9466,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="C80" s="36">
         <v>1.0</v>
@@ -9463,13 +9475,13 @@
         <v>906</v>
       </c>
       <c r="E80" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F80" s="37" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="G80" s="37" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="81">
@@ -9478,7 +9490,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="C81" s="36">
         <v>1.0</v>
@@ -9487,13 +9499,13 @@
         <v>906</v>
       </c>
       <c r="E81" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F81" s="37" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="G81" s="37" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="82">
@@ -9502,7 +9514,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="C82" s="36">
         <v>0.0</v>
@@ -9511,13 +9523,13 @@
         <v>906</v>
       </c>
       <c r="E82" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F82" s="37" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="G82" s="37" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="83">
@@ -9526,7 +9538,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="C83" s="36">
         <v>0.0</v>
@@ -9535,13 +9547,13 @@
         <v>906</v>
       </c>
       <c r="E83" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F83" s="37" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="G83" s="37" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="84">
@@ -9550,7 +9562,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="C84" s="36">
         <v>0.0</v>
@@ -9559,13 +9571,13 @@
         <v>906</v>
       </c>
       <c r="E84" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F84" s="37" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="G84" s="37" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="85">
@@ -9583,13 +9595,13 @@
         <v>906</v>
       </c>
       <c r="E85" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="86">
@@ -9607,13 +9619,13 @@
         <v>906</v>
       </c>
       <c r="E86" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F86" s="37" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="G86" s="37" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="87">
@@ -9631,13 +9643,13 @@
         <v>906</v>
       </c>
       <c r="E87" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F87" s="37" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="88">
@@ -9655,13 +9667,13 @@
         <v>906</v>
       </c>
       <c r="E88" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F88" s="37" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="G88" s="37" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="89">
@@ -9679,13 +9691,13 @@
         <v>906</v>
       </c>
       <c r="E89" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F89" s="37" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="G89" s="37" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="90">
@@ -9703,13 +9715,13 @@
         <v>906</v>
       </c>
       <c r="E90" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F90" s="37" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="G90" s="37" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="91">
@@ -9727,13 +9739,13 @@
         <v>906</v>
       </c>
       <c r="E91" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F91" s="37" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
       <c r="G91" s="37" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="92">
@@ -9751,13 +9763,13 @@
         <v>906</v>
       </c>
       <c r="E92" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F92" s="37" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="G92" s="37" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="93">
@@ -9775,13 +9787,13 @@
         <v>906</v>
       </c>
       <c r="E93" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F93" s="37" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="G93" s="37" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="94">
@@ -9799,13 +9811,13 @@
         <v>911</v>
       </c>
       <c r="E94" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F94" s="37" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="G94" s="37" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="95">
@@ -9823,13 +9835,13 @@
         <v>906</v>
       </c>
       <c r="E95" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F95" s="37" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="G95" s="37" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="96">
@@ -9847,13 +9859,13 @@
         <v>906</v>
       </c>
       <c r="E96" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F96" s="37" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="G96" s="37" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="97">
@@ -9871,13 +9883,13 @@
         <v>906</v>
       </c>
       <c r="E97" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F97" s="37" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="G97" s="37" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="98">
@@ -9895,13 +9907,13 @@
         <v>906</v>
       </c>
       <c r="E98" s="44" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="F98" s="37" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="G98" s="37" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="99">
@@ -9919,13 +9931,13 @@
         <v>906</v>
       </c>
       <c r="E99" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F99" s="37" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="G99" s="37" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="100">
@@ -9943,13 +9955,13 @@
         <v>906</v>
       </c>
       <c r="E100" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F100" s="37" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="G100" s="37" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="101">
@@ -9967,13 +9979,13 @@
         <v>906</v>
       </c>
       <c r="E101" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F101" s="37" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="G101" s="37" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="102">
@@ -9982,7 +9994,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="36" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
       <c r="C102" s="36">
         <v>0.0</v>
@@ -9991,13 +10003,13 @@
         <v>906</v>
       </c>
       <c r="E102" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F102" s="37" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="G102" s="37" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="103">
@@ -10006,7 +10018,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="36" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="C103" s="36">
         <v>1.0</v>
@@ -10015,13 +10027,13 @@
         <v>906</v>
       </c>
       <c r="E103" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F103" s="37" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="G103" s="37" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="104">
@@ -10030,7 +10042,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="C104" s="36">
         <v>0.0</v>
@@ -10039,13 +10051,13 @@
         <v>906</v>
       </c>
       <c r="E104" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F104" s="37" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="G104" s="37" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="105">
@@ -10054,7 +10066,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="C105" s="36">
         <v>1.0</v>
@@ -10063,13 +10075,13 @@
         <v>906</v>
       </c>
       <c r="E105" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F105" s="37" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="G105" s="37" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="106">
@@ -10078,7 +10090,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="C106" s="36">
         <v>0.0</v>
@@ -10087,13 +10099,13 @@
         <v>906</v>
       </c>
       <c r="E106" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F106" s="37" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="G106" s="37" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="107">
@@ -10102,7 +10114,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="C107" s="36">
         <v>1.0</v>
@@ -10111,13 +10123,13 @@
         <v>906</v>
       </c>
       <c r="E107" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F107" s="37" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="G107" s="37" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="108">
@@ -10126,7 +10138,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="C108" s="36">
         <v>0.0</v>
@@ -10135,13 +10147,13 @@
         <v>906</v>
       </c>
       <c r="E108" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F108" s="37" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="G108" s="37" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="109">
@@ -10150,7 +10162,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="C109" s="36">
         <v>1.0</v>
@@ -10159,13 +10171,13 @@
         <v>906</v>
       </c>
       <c r="E109" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F109" s="37" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="G109" s="37" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="110">
@@ -10174,7 +10186,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C110" s="36">
         <v>0.0</v>
@@ -10183,13 +10195,13 @@
         <v>906</v>
       </c>
       <c r="E110" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F110" s="37" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="G110" s="37" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="111">
@@ -10198,7 +10210,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="C111" s="36">
         <v>1.0</v>
@@ -10207,13 +10219,13 @@
         <v>906</v>
       </c>
       <c r="E111" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F111" s="37" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="G111" s="37" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="112">
@@ -10222,7 +10234,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="36" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="C112" s="36">
         <v>0.0</v>
@@ -10231,13 +10243,13 @@
         <v>906</v>
       </c>
       <c r="E112" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F112" s="37" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="G112" s="37" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="113">
@@ -10246,7 +10258,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="C113" s="36">
         <v>0.0</v>
@@ -10255,13 +10267,13 @@
         <v>906</v>
       </c>
       <c r="E113" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F113" s="37" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="G113" s="37" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="114">
@@ -10270,7 +10282,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="C114" s="36">
         <v>0.0</v>
@@ -10279,13 +10291,13 @@
         <v>906</v>
       </c>
       <c r="E114" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F114" s="37" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="G114" s="37" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="115">
@@ -10294,7 +10306,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="C115" s="36">
         <v>1.0</v>
@@ -10303,13 +10315,13 @@
         <v>906</v>
       </c>
       <c r="E115" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F115" s="37" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="G115" s="37" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="116">
@@ -10327,13 +10339,13 @@
         <v>906</v>
       </c>
       <c r="E116" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F116" s="37" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="G116" s="37" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="117">
@@ -10351,13 +10363,13 @@
         <v>909</v>
       </c>
       <c r="E117" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F117" s="37" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="G117" s="37" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="118">
@@ -10375,13 +10387,13 @@
         <v>906</v>
       </c>
       <c r="E118" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F118" s="37" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="G118" s="37" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="119">
@@ -10399,10 +10411,10 @@
         <v>906</v>
       </c>
       <c r="E119" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F119" s="37" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="G119" s="37" t="s">
         <v>14</v>
@@ -10414,7 +10426,7 @@
         <v>118</v>
       </c>
       <c r="B120" s="36" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="C120" s="36">
         <v>0.0</v>
@@ -10423,10 +10435,10 @@
         <v>906</v>
       </c>
       <c r="E120" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F120" s="37" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="G120" s="37" t="s">
         <v>32</v>
@@ -10438,7 +10450,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="C121" s="36">
         <v>0.0</v>
@@ -10447,13 +10459,13 @@
         <v>906</v>
       </c>
       <c r="E121" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F121" s="37" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="G121" s="37" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="122">
@@ -10462,7 +10474,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="36" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="C122" s="36">
         <v>0.0</v>
@@ -10471,13 +10483,13 @@
         <v>906</v>
       </c>
       <c r="E122" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F122" s="37" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="G122" s="37" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="123">
@@ -10486,7 +10498,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="C123" s="36">
         <v>0.0</v>
@@ -10495,13 +10507,13 @@
         <v>906</v>
       </c>
       <c r="E123" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F123" s="37" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="G123" s="37" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="124">
@@ -10519,13 +10531,13 @@
         <v>906</v>
       </c>
       <c r="E124" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F124" s="37" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="G124" s="37" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="125">
@@ -10543,13 +10555,13 @@
         <v>906</v>
       </c>
       <c r="E125" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F125" s="37" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="G125" s="37" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="126">
@@ -10558,7 +10570,7 @@
         <v>124</v>
       </c>
       <c r="B126" s="36" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="C126" s="36">
         <v>0.0</v>
@@ -10567,13 +10579,13 @@
         <v>906</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F126" s="37" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="G126" s="37" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
     </row>
   </sheetData>
@@ -10616,31 +10628,31 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="J1" s="28" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="2" ht="186.0" customHeight="1">
@@ -10649,7 +10661,7 @@
         <v>-1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="C2" s="64" t="s">
         <v>296</v>
@@ -10682,7 +10694,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="C3" s="64" t="s">
         <v>834</v>
@@ -10691,10 +10703,10 @@
         <v>908</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>294</v>
@@ -10715,19 +10727,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="D4" s="34" t="s">
         <v>908</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>294</v>
@@ -10748,19 +10760,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D5" s="34" t="s">
         <v>908</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>294</v>
@@ -10781,19 +10793,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>908</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>294</v>
@@ -10814,19 +10826,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D7" s="34" t="s">
         <v>906</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>294</v>
@@ -10847,19 +10859,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="D8" s="34" t="s">
         <v>906</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>294</v>
@@ -10892,7 +10904,7 @@
         <v>867</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>294</v>
@@ -10913,19 +10925,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="D10" s="34" t="s">
         <v>906</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>294</v>
@@ -10946,19 +10958,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>906</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>294</v>
@@ -10979,16 +10991,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="D12" s="34" t="s">
         <v>906</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="F12" s="35" t="s">
         <v>320</v>
@@ -11012,16 +11024,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="D13" s="34" t="s">
         <v>906</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="F13" s="35" t="s">
         <v>320</v>
@@ -11048,13 +11060,13 @@
         <v>20</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="D14" s="34" t="s">
         <v>906</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F14" s="35" t="s">
         <v>320</v>
@@ -11078,7 +11090,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="C15" s="64" t="s">
         <v>296</v>
@@ -11141,7 +11153,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="2">
@@ -11168,7 +11180,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="5">
@@ -11177,7 +11189,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="6">
@@ -11189,7 +11201,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="8">
@@ -11197,7 +11209,7 @@
         <v>0.0</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="9">
@@ -11205,7 +11217,7 @@
         <v>1.0</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="10">
@@ -11213,7 +11225,7 @@
         <v>2.0</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="11">
@@ -11221,7 +11233,7 @@
         <v>3.0</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="12">
@@ -11229,7 +11241,7 @@
         <v>4.0</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="13">
@@ -11237,7 +11249,7 @@
         <v>5.0</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="15">
@@ -11245,7 +11257,7 @@
         <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="16">
@@ -11263,7 +11275,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="18">
@@ -11308,7 +11320,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="23">
@@ -11334,7 +11346,7 @@
         <v>44</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="27">
@@ -11379,7 +11391,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="32">
@@ -11406,7 +11418,7 @@
         <v>7</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="35">
@@ -11424,7 +11436,7 @@
         <v>9</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="37">
@@ -11469,7 +11481,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="42">
@@ -11478,7 +11490,7 @@
         <v>15</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="43">
@@ -11495,7 +11507,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="46">
@@ -11503,7 +11515,7 @@
         <v>0.0</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="47">
@@ -11511,7 +11523,7 @@
         <v>1.0</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="49">
@@ -11519,7 +11531,7 @@
         <v>44</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="50">
@@ -11572,7 +11584,7 @@
         <v>44</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="57">
@@ -11637,7 +11649,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="2">
@@ -11655,7 +11667,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="4">
@@ -11664,7 +11676,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="5">
@@ -11745,7 +11757,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="14">
@@ -11934,7 +11946,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="36">
@@ -11942,16 +11954,16 @@
         <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="C36" s="66" t="s">
         <v>285</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="E36" s="66" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="37">
@@ -11960,7 +11972,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="C37" s="38" t="s">
         <v>294</v>
@@ -11979,10 +11991,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="D38" s="38" t="s">
         <v>850</v>
@@ -11998,10 +12010,10 @@
         <v>2</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="D39" s="38" t="s">
         <v>878</v>
@@ -12020,7 +12032,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="D40" s="38" t="s">
         <v>40</v>
@@ -12036,7 +12048,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>422</v>
@@ -12054,19 +12066,19 @@
         <v>44</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="C43" s="65" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="D43" s="65" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="E43" s="66" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="F43" s="65" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="44">
@@ -12078,13 +12090,13 @@
         <v>665</v>
       </c>
       <c r="C44" s="44" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="D44" s="44" t="s">
         <v>668</v>
       </c>
       <c r="E44" s="48" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="F44" s="43" t="b">
         <v>0</v>
@@ -12099,13 +12111,13 @@
         <v>677</v>
       </c>
       <c r="C45" s="44" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="F45" s="43" t="b">
         <v>0</v>
@@ -12120,13 +12132,13 @@
         <v>694</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="D46" s="44" t="s">
         <v>714</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="F46" s="43" t="b">
         <v>0</v>
@@ -12141,13 +12153,13 @@
         <v>699</v>
       </c>
       <c r="C47" s="44" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="F47" s="43" t="b">
         <v>0</v>
@@ -12165,10 +12177,10 @@
         <v>39</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="F48" s="43" t="b">
         <v>0</v>
@@ -12180,16 +12192,16 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>39</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="F49" s="43" t="b">
         <v>0</v>
@@ -12201,16 +12213,16 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>39</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="F50" s="43" t="b">
         <v>1</v>
@@ -12222,16 +12234,16 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="D51" s="44" t="s">
         <v>668</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="F51" s="43" t="b">
         <v>0</v>
@@ -12242,10 +12254,10 @@
         <v>44</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="54">
@@ -12254,7 +12266,7 @@
         <v>0</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="C54" s="51" t="s">
         <v>431</v>
@@ -12265,7 +12277,7 @@
         <v>44</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="57">
@@ -13275,16 +13287,16 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="2">
@@ -13296,7 +13308,7 @@
         <v>297</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D2" s="68" t="s">
         <v>294</v>
@@ -13314,7 +13326,7 @@
         <v>412</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="D3" s="68" t="s">
         <v>294</v>
@@ -13329,10 +13341,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D4" s="68" t="s">
         <v>294</v>
@@ -13370,7 +13382,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="2">
@@ -13388,7 +13400,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
     </row>
   </sheetData>
@@ -13414,21 +13426,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="B2" s="69">
         <v>1.0</v>
@@ -13442,7 +13454,7 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="B3" s="69">
         <v>1.0</v>
@@ -13456,7 +13468,7 @@
     </row>
     <row r="4">
       <c r="A4" s="37" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="B4" s="69">
         <v>3.0</v>
@@ -13470,7 +13482,7 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="B5" s="69">
         <v>1.0</v>
@@ -13484,7 +13496,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="B6" s="69">
         <v>3.0</v>
@@ -13498,7 +13510,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="B7" s="69">
         <v>3.0</v>
@@ -13512,7 +13524,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
       <c r="B8" s="69">
         <v>5.0</v>
@@ -13526,7 +13538,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="B9" s="69">
         <v>4.0</v>
@@ -13540,7 +13552,7 @@
     </row>
     <row r="10">
       <c r="A10" s="37" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
       <c r="B10" s="69">
         <v>5.0</v>
@@ -13554,7 +13566,7 @@
     </row>
     <row r="11">
       <c r="A11" s="37" t="s">
-        <v>1533</v>
+        <v>1537</v>
       </c>
       <c r="B11" s="69">
         <v>4.0</v>
@@ -13568,7 +13580,7 @@
     </row>
     <row r="12">
       <c r="A12" s="37" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="B12" s="69">
         <v>1.0</v>
@@ -13582,7 +13594,7 @@
     </row>
     <row r="13">
       <c r="A13" s="37" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="B13" s="69">
         <v>4.0</v>
@@ -13596,7 +13608,7 @@
     </row>
     <row r="14">
       <c r="A14" s="37" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="B14" s="69">
         <v>1.0</v>
@@ -13610,7 +13622,7 @@
     </row>
     <row r="15">
       <c r="A15" s="37" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="B15" s="69">
         <v>2.0</v>
@@ -13624,7 +13636,7 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
       <c r="B16" s="69">
         <v>3.0</v>
@@ -13638,7 +13650,7 @@
     </row>
     <row r="17">
       <c r="A17" s="37" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
       <c r="B17" s="69">
         <v>2.0</v>
@@ -13652,7 +13664,7 @@
     </row>
     <row r="18">
       <c r="A18" s="37" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="B18" s="69">
         <v>2.0</v>
@@ -13666,7 +13678,7 @@
     </row>
     <row r="19">
       <c r="A19" s="37" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="B19" s="69">
         <v>2.0</v>
@@ -13680,7 +13692,7 @@
     </row>
     <row r="20">
       <c r="A20" s="37" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="B20" s="69">
         <v>2.0</v>
@@ -13694,7 +13706,7 @@
     </row>
     <row r="21">
       <c r="A21" s="37" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
       <c r="B21" s="69">
         <v>3.0</v>
@@ -13708,7 +13720,7 @@
     </row>
     <row r="22">
       <c r="A22" s="37" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="B22" s="69">
         <v>2.0</v>
@@ -13722,7 +13734,7 @@
     </row>
     <row r="23">
       <c r="A23" s="37" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
       <c r="B23" s="69">
         <v>2.0</v>
@@ -13736,7 +13748,7 @@
     </row>
     <row r="24">
       <c r="A24" s="37" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="B24" s="69">
         <v>2.0</v>
@@ -13750,7 +13762,7 @@
     </row>
     <row r="25">
       <c r="A25" s="37" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="B25" s="69">
         <v>2.0</v>
@@ -13764,7 +13776,7 @@
     </row>
     <row r="26">
       <c r="A26" s="37" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="B26" s="69">
         <v>2.0</v>
@@ -13778,7 +13790,7 @@
     </row>
     <row r="27">
       <c r="A27" s="37" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="B27" s="69">
         <v>2.0</v>
@@ -13792,7 +13804,7 @@
     </row>
     <row r="28">
       <c r="A28" s="37" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
       <c r="B28" s="69">
         <v>2.0</v>
@@ -13806,7 +13818,7 @@
     </row>
     <row r="29">
       <c r="A29" s="37" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="B29" s="69">
         <v>4.0</v>
@@ -13820,7 +13832,7 @@
     </row>
     <row r="30">
       <c r="A30" s="37" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="B30" s="69">
         <v>2.0</v>
@@ -13834,7 +13846,7 @@
     </row>
     <row r="31">
       <c r="A31" s="37" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="B31" s="69">
         <v>3.0</v>
@@ -13848,7 +13860,7 @@
     </row>
     <row r="32">
       <c r="A32" s="37" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
       <c r="B32" s="69">
         <v>2.0</v>
@@ -13862,7 +13874,7 @@
     </row>
     <row r="33">
       <c r="A33" s="37" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="B33" s="69">
         <v>5.0</v>
@@ -14519,11 +14531,11 @@
         <v>91</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="12"/>
+        <v>65</v>
+      </c>
+      <c r="H11" s="17"/>
       <c r="I11" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J11" s="13" t="s">
         <v>67</v>
@@ -14532,25 +14544,25 @@
         <v>68</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M11" s="13" t="s">
         <v>67</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P11" s="13" t="s">
         <v>67</v>
       </c>
       <c r="Q11" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
@@ -14558,56 +14570,54 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
         <v>0.0</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="11">
         <v>0.0</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="I12" s="14" t="s">
+      <c r="H12" s="12"/>
+      <c r="I12" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="N12" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="K12" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="N12" s="14" t="s">
-        <v>75</v>
-      </c>
       <c r="O12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="P12" s="14" t="s">
-        <v>75</v>
+        <v>67</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="Q12" s="13" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="R12" s="13" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -14637,34 +14647,34 @@
         <v>66</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>68</v>
+        <v>75</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="P13" s="13" t="s">
-        <v>67</v>
+        <v>75</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14">
@@ -14693,16 +14703,16 @@
       <c r="H14" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="J14" s="14" t="s">
+      <c r="I14" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="13" t="s">
         <v>69</v>
       </c>
       <c r="K14" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="L14" s="13" t="s">
         <v>68</v>
       </c>
       <c r="M14" s="13" t="s">
@@ -14729,75 +14739,77 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="13">
+      <c r="C15" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="14">
         <v>0.0</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="12">
         <v>0.0</v>
       </c>
-      <c r="F15" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="G15" s="13" t="s">
+      <c r="F15" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="17"/>
+      <c r="H15" s="12" t="s">
+        <v>66</v>
+      </c>
       <c r="I15" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="J15" s="13" t="s">
-        <v>67</v>
+      <c r="J15" s="14" t="s">
+        <v>69</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>68</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="N15" s="13" t="s">
+      <c r="N15" s="14" t="s">
         <v>68</v>
       </c>
       <c r="O15" s="13" t="s">
         <v>67</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="Q15" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R15" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16">
       <c r="A16" s="11">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D16" s="13">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="E16" s="11">
         <v>0.0</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>44</v>
@@ -14810,22 +14822,22 @@
         <v>67</v>
       </c>
       <c r="K16" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="N16" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="L16" s="13" t="s">
+      <c r="O16" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="P16" s="13" t="s">
         <v>75</v>
-      </c>
-      <c r="M16" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="N16" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="O16" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="P16" s="13" t="s">
-        <v>67</v>
       </c>
       <c r="Q16" s="13" t="s">
         <v>68</v>
@@ -14840,19 +14852,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D17" s="13">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="E17" s="11">
         <v>0.0</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>44</v>
@@ -14865,7 +14877,7 @@
         <v>67</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>75</v>
@@ -14874,7 +14886,7 @@
         <v>67</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O17" s="13" t="s">
         <v>67</v>
@@ -14883,7 +14895,7 @@
         <v>67</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R17" s="13" t="s">
         <v>67</v>
@@ -14895,10 +14907,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D18" s="13">
         <v>0.0</v>
@@ -14907,7 +14919,7 @@
         <v>0.0</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>44</v>
@@ -14920,7 +14932,7 @@
         <v>67</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>75</v>
@@ -14929,7 +14941,7 @@
         <v>67</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O18" s="13" t="s">
         <v>67</v>
@@ -14961,7 +14973,7 @@
       <c r="E19" s="11">
         <v>0.0</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="11" t="s">
         <v>109</v>
       </c>
       <c r="G19" s="13" t="s">
@@ -14969,7 +14981,7 @@
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J19" s="13" t="s">
         <v>67</v>
@@ -14978,16 +14990,16 @@
         <v>68</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>67</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P19" s="13" t="s">
         <v>67</v>
@@ -14996,7 +15008,7 @@
         <v>67</v>
       </c>
       <c r="R19" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -15016,15 +15028,15 @@
       <c r="E20" s="11">
         <v>0.0</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="18" t="s">
         <v>112</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J20" s="13" t="s">
         <v>67</v>
@@ -15033,7 +15045,7 @@
         <v>68</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>67</v>
@@ -15048,10 +15060,10 @@
         <v>67</v>
       </c>
       <c r="Q20" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R20" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -15063,7 +15075,7 @@
         <v>113</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D21" s="13">
         <v>0.0</v>
@@ -15072,7 +15084,7 @@
         <v>0.0</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>44</v>
@@ -28933,10 +28945,10 @@
         <v>711</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>293</v>
+        <v>922</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="5">
@@ -28945,13 +28957,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>293</v>
+        <v>922</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="6">
@@ -28963,10 +28975,10 @@
         <v>725</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>293</v>
+        <v>922</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -28978,10 +28990,10 @@
         <v>727</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>293</v>
+        <v>927</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="8">
@@ -28990,13 +29002,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
+        <v>929</v>
+      </c>
+      <c r="C8" s="39" t="s">
         <v>927</v>
       </c>
-      <c r="C8" s="39" t="s">
-        <v>293</v>
-      </c>
       <c r="D8" s="39" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="9">
@@ -29008,10 +29020,10 @@
         <v>729</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>293</v>
+        <v>931</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
     </row>
     <row r="10">
@@ -29020,13 +29032,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>293</v>
+        <v>931</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
     </row>
     <row r="11">
@@ -29038,10 +29050,10 @@
         <v>730</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
     </row>
     <row r="12">
@@ -29056,7 +29068,7 @@
         <v>378</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="13">
@@ -29071,7 +29083,7 @@
         <v>380</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="14">
@@ -29080,13 +29092,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>293</v>
+        <v>939</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
     </row>
     <row r="15">
@@ -29098,10 +29110,10 @@
         <v>737</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>293</v>
+        <v>939</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="16">
@@ -29110,13 +29122,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>293</v>
+        <v>943</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
     </row>
     <row r="17">
@@ -29128,10 +29140,10 @@
         <v>762</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>293</v>
+        <v>943</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
     </row>
     <row r="18">
@@ -29146,7 +29158,7 @@
         <v>33</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
     </row>
     <row r="19">
@@ -29158,10 +29170,10 @@
         <v>771</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
     </row>
     <row r="20">
@@ -29170,13 +29182,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="C20" s="39" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
     </row>
     <row r="21">
@@ -29185,7 +29197,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="C21" s="39" t="s">
         <v>293</v>
@@ -29199,25 +29211,25 @@
         <v>44</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>425</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="H23" s="28" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
     </row>
     <row r="24">
@@ -29280,7 +29292,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C26" s="40" t="s">
         <v>431</v>
@@ -29292,13 +29304,13 @@
         <v>435</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="G26" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="40" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
     </row>
     <row r="27">
@@ -29307,7 +29319,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="C27" s="40" t="s">
         <v>431</v>
@@ -29319,13 +29331,13 @@
         <v>435</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="G27" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H27" s="40" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
     </row>
     <row r="28">
@@ -29334,7 +29346,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="C28" s="40" t="s">
         <v>431</v>
@@ -29352,7 +29364,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="40" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
     </row>
     <row r="29">
@@ -29361,7 +29373,7 @@
         <v>5</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>431</v>
@@ -29379,7 +29391,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="40" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
     </row>
     <row r="30">
@@ -29388,7 +29400,7 @@
         <v>6</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>431</v>
@@ -29400,13 +29412,13 @@
         <v>435</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="G30" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="40" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
     </row>
     <row r="31">
@@ -29415,7 +29427,7 @@
         <v>7</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>431</v>
@@ -29433,7 +29445,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="40" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="32">
@@ -29442,7 +29454,7 @@
         <v>8</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="C32" s="40" t="s">
         <v>431</v>
@@ -29454,13 +29466,13 @@
         <v>435</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="G32" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H32" s="40" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
     </row>
     <row r="33">
@@ -29469,7 +29481,7 @@
         <v>9</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="C33" s="40" t="s">
         <v>431</v>
@@ -29481,13 +29493,13 @@
         <v>794</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="G33" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H33" s="40" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
     </row>
     <row r="34">
@@ -29496,7 +29508,7 @@
         <v>10</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="C34" s="40" t="s">
         <v>795</v>
@@ -29508,13 +29520,13 @@
         <v>435</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="G34" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="40" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
     </row>
     <row r="35">
@@ -29523,7 +29535,7 @@
         <v>11</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="C35" s="40" t="s">
         <v>431</v>
@@ -29535,13 +29547,13 @@
         <v>435</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="G35" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H35" s="40" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
     </row>
     <row r="36">
@@ -29550,7 +29562,7 @@
         <v>12</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="C36" s="40" t="s">
         <v>795</v>
@@ -29559,16 +29571,16 @@
         <v>497</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="G36" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H36" s="40" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
     <row r="37">
@@ -29577,7 +29589,7 @@
         <v>13</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="C37" s="40" t="s">
         <v>431</v>
@@ -29595,7 +29607,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="40" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
     </row>
     <row r="38">
@@ -29604,7 +29616,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C38" s="40" t="s">
         <v>431</v>
@@ -29622,7 +29634,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="40" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
     </row>
     <row r="39">
@@ -29631,7 +29643,7 @@
         <v>15</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="C39" s="40" t="s">
         <v>431</v>
@@ -29649,7 +29661,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="40" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
     </row>
     <row r="40">
@@ -29658,7 +29670,7 @@
         <v>16</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C40" s="40" t="s">
         <v>431</v>
@@ -29676,7 +29688,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="40" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
     </row>
     <row r="41">
@@ -29685,7 +29697,7 @@
         <v>17</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="C41" s="40" t="s">
         <v>431</v>
@@ -29697,13 +29709,13 @@
         <v>435</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="G41" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
     </row>
     <row r="42">
@@ -29712,7 +29724,7 @@
         <v>18</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="C42" s="40" t="s">
         <v>431</v>
@@ -29724,13 +29736,13 @@
         <v>435</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="G42" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H42" s="40" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
     </row>
     <row r="43">
@@ -29739,7 +29751,7 @@
         <v>19</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>431</v>
@@ -29748,16 +29760,16 @@
         <v>432</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="G43" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H43" s="40" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
     </row>
     <row r="44">
@@ -29766,7 +29778,7 @@
         <v>20</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>431</v>
@@ -29784,7 +29796,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="40" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
     </row>
     <row r="45">
@@ -29793,7 +29805,7 @@
         <v>21</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C45" s="40" t="s">
         <v>431</v>
@@ -29805,13 +29817,13 @@
         <v>435</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="G45" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H45" s="40" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
     </row>
     <row r="46">
@@ -29820,7 +29832,7 @@
         <v>22</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="C46" s="40" t="s">
         <v>431</v>
@@ -29832,13 +29844,13 @@
         <v>799</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="G46" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="40" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
     </row>
     <row r="47">
@@ -29847,7 +29859,7 @@
         <v>23</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="C47" s="40" t="s">
         <v>800</v>
@@ -29856,16 +29868,16 @@
         <v>432</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="G47" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H47" s="40" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
     </row>
     <row r="48">
@@ -29874,7 +29886,7 @@
         <v>24</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="C48" s="40" t="s">
         <v>431</v>
@@ -29892,7 +29904,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="40" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
     </row>
     <row r="49">
@@ -29901,7 +29913,7 @@
         <v>25</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="C49" s="40" t="s">
         <v>431</v>
@@ -29913,13 +29925,13 @@
         <v>435</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="G49" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H49" s="40" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
     </row>
     <row r="50">
@@ -29928,7 +29940,7 @@
         <v>26</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="C50" s="40" t="s">
         <v>431</v>
@@ -29946,7 +29958,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="40" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
     </row>
     <row r="51">
@@ -29955,7 +29967,7 @@
         <v>27</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="C51" s="40" t="s">
         <v>431</v>
@@ -29967,13 +29979,13 @@
         <v>805</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="G51" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H51" s="40" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
     </row>
     <row r="52">
@@ -29982,7 +29994,7 @@
         <v>28</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="C52" s="40" t="s">
         <v>431</v>
@@ -30000,7 +30012,7 @@
         <v>0</v>
       </c>
       <c r="H52" s="40" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="53">
@@ -30009,7 +30021,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="C53" s="37" t="s">
         <v>431</v>
@@ -30126,10 +30138,10 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="C1" s="56" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="2">
@@ -30141,7 +30153,7 @@
         <v>666</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="3">
@@ -30153,7 +30165,7 @@
         <v>697</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="4">
@@ -30162,10 +30174,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="6">
@@ -30173,13 +30185,13 @@
         <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -30188,7 +30200,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>668</v>
@@ -30203,10 +30215,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="D8" s="57" t="s">
         <v>435</v>
@@ -30218,10 +30230,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="D9" s="57" t="s">
         <v>670</v>
@@ -30233,10 +30245,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="D10" s="57" t="s">
         <v>672</v>
@@ -30248,7 +30260,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>668</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -15051,7 +15051,7 @@
         <v>68</v>
       </c>
       <c r="O20" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P20" s="13" t="s">
         <v>67</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -31,10 +31,10 @@
     <definedName name="Interval_Name">NAMES!$A$1:$D$44</definedName>
     <definedName name="Interval_autoInsertItem">FN!$A$1:$J$2</definedName>
     <definedName name="Interval_Unchain_Conditions">ACTION_CONDS!$A$64:$G$89</definedName>
-    <definedName name="Interval_Phrases">PHRASES!$A$1:$G$126</definedName>
+    <definedName name="Interval_Phrases">PHRASES!$A$1:$G$127</definedName>
     <definedName name="Interval_sprites">SPRITES!$A$1:$C$60</definedName>
     <definedName name="Interval_Items">ITEMS!$A$1:$J$42</definedName>
-    <definedName name="Interval_Dialog_Options">DIALOGS!$A$23:$H$53</definedName>
+    <definedName name="Interval_Dialog_Options">DIALOGS!$A$23:$H$54</definedName>
     <definedName name="Interval_Memento">EVENTS!$A$43:$F$51</definedName>
     <definedName name="Interval_autoInsertDialog">FN!$A$7:$I$8</definedName>
     <definedName name="Interval_Action_Conditions">ACTION_CONDS!$A$1:$G$62</definedName>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4958" uniqueCount="1563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4982" uniqueCount="1570">
   <si>
     <t>NewItem</t>
   </si>
@@ -2576,6 +2576,15 @@
     <t>PHRASE_NONSENSE</t>
   </si>
   <si>
+    <t>ACTION_ANIMATE_REME_TEST</t>
+  </si>
+  <si>
+    <t>ACTION_TYPE_START_ANIMATION</t>
+  </si>
+  <si>
+    <t>ANIMATION_REME_TEST</t>
+  </si>
+  <si>
     <t>ACTION_LAST</t>
   </si>
   <si>
@@ -2915,7 +2924,7 @@
     <t>DIALOG_REME</t>
   </si>
   <si>
-    <t>DIALOG_OPTION_REME_1, DIALOG_OPTION_REME_2</t>
+    <t>DIALOG_OPTION_REME_1, DIALOG_OPTION_REME_2, DIALOG_OPTION_REME_3</t>
   </si>
   <si>
     <t>DIALOG_OPTION_REME_CARDS</t>
@@ -3026,6 +3035,15 @@
     <t>PHRASE_DIALOG_REME_2_1</t>
   </si>
   <si>
+    <t>DIALOG_OPTION_REME_3</t>
+  </si>
+  <si>
+    <t>ACTION_ANIMATE_REME_TEST, ACTION_DIALOGUE_OBSERVE_SHOEALCE</t>
+  </si>
+  <si>
+    <t>PHRASE_DIALOG_REME_3_TEST</t>
+  </si>
+  <si>
     <t>PHRASE_USE_CARDS_REME_1, PHRASE_USE_CARDS_REME_2</t>
   </si>
   <si>
@@ -3593,6 +3611,12 @@
     <t>Bueno! Que tengas un florido día Reme!</t>
   </si>
   <si>
+    <t>Dance for me. Reme!</t>
+  </si>
+  <si>
+    <t>Baila Baila para mí!</t>
+  </si>
+  <si>
     <t>PHRASE_MEMENTO_FIND_JOB_1</t>
   </si>
   <si>
@@ -4602,9 +4626,6 @@
   </si>
   <si>
     <t>ACTION_TYPE_NOTIF</t>
-  </si>
-  <si>
-    <t>ACTION_TYPE_START_ANIMATION</t>
   </si>
   <si>
     <t>DIALOG_ANIMATION_ID</t>
@@ -6043,7 +6064,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A91:N218" displayName="Table_Actions" name="Table_Actions" id="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A91:N219" displayName="Table_Actions" name="Table_Actions" id="10">
   <tableColumns count="14">
     <tableColumn name="N" id="1"/>
     <tableColumn name="ACTION_ID" id="2"/>
@@ -6100,7 +6121,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A23:H53" displayName="Table_Dialog_Options" name="Table_Dialog_Options" id="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A23:H54" displayName="Table_Dialog_Options" name="Table_Dialog_Options" id="14">
   <tableColumns count="8">
     <tableColumn name="N" id="1"/>
     <tableColumn name="DIALOG_OPTION_ID" id="2"/>
@@ -6151,7 +6172,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G126" displayName="Table_Phrases" name="Table_Phrases" id="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G127" displayName="Table_Phrases" name="Table_Phrases" id="18">
   <tableColumns count="7">
     <tableColumn name="N" id="1"/>
     <tableColumn name="PHRASE_ID" id="2"/>
@@ -6354,7 +6375,7 @@
 </file>
 
 <file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:B3" displayName="Table_Animations" name="Table_Animations" id="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:B4" displayName="Table_Animations" name="Table_Animations" id="33">
   <tableColumns count="2">
     <tableColumn name="N" id="1"/>
     <tableColumn name="ANIMATION_ID" id="2"/>
@@ -6905,13 +6926,13 @@
         <v>44</v>
       </c>
       <c r="B1" s="59" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="2">
@@ -6934,10 +6955,10 @@
         <v>305</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="4">
@@ -6946,13 +6967,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="5">
@@ -6961,13 +6982,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="6">
@@ -6976,13 +6997,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="7">
@@ -6994,10 +7015,10 @@
         <v>308</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="8">
@@ -7009,10 +7030,10 @@
         <v>329</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="9">
@@ -7024,10 +7045,10 @@
         <v>336</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="10">
@@ -7039,10 +7060,10 @@
         <v>314</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="11">
@@ -7051,13 +7072,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="12">
@@ -7066,13 +7087,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="13">
@@ -7084,10 +7105,10 @@
         <v>319</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="14">
@@ -7099,10 +7120,10 @@
         <v>326</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="15">
@@ -7111,13 +7132,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="16">
@@ -7129,10 +7150,10 @@
         <v>339</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="17">
@@ -7144,10 +7165,10 @@
         <v>344</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="18">
@@ -7159,10 +7180,10 @@
         <v>347</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="19">
@@ -7174,10 +7195,10 @@
         <v>351</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="20">
@@ -7189,10 +7210,10 @@
         <v>354</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="21">
@@ -7204,10 +7225,10 @@
         <v>357</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="22">
@@ -7219,10 +7240,10 @@
         <v>359</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="23">
@@ -7234,10 +7255,10 @@
         <v>361</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="24">
@@ -7249,10 +7270,10 @@
         <v>363</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="25">
@@ -7264,10 +7285,10 @@
         <v>365</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="26">
@@ -7279,10 +7300,10 @@
         <v>369</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="27">
@@ -7294,10 +7315,10 @@
         <v>374</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="28">
@@ -7309,10 +7330,10 @@
         <v>376</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="29">
@@ -7324,10 +7345,10 @@
         <v>380</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="30">
@@ -7336,13 +7357,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="31">
@@ -7354,10 +7375,10 @@
         <v>384</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="32">
@@ -7369,10 +7390,10 @@
         <v>386</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="33">
@@ -7381,13 +7402,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>41</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="34">
@@ -7399,10 +7420,10 @@
         <v>390</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="35">
@@ -7414,10 +7435,10 @@
         <v>394</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="36">
@@ -7429,10 +7450,10 @@
         <v>397</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="37">
@@ -7444,10 +7465,10 @@
         <v>402</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="38">
@@ -7459,10 +7480,10 @@
         <v>407</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="39">
@@ -7474,10 +7495,10 @@
         <v>411</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="40">
@@ -7489,10 +7510,10 @@
         <v>415</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="41">
@@ -7504,10 +7525,10 @@
         <v>419</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="42">
@@ -7519,10 +7540,10 @@
         <v>422</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="43">
@@ -7534,10 +7555,10 @@
         <v>11</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="44">
@@ -7549,10 +7570,10 @@
         <v>427</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
     </row>
   </sheetData>
@@ -7586,22 +7607,22 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="G1" s="61" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="2">
@@ -7616,10 +7637,10 @@
         <v>0.0</v>
       </c>
       <c r="D2" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="F2" s="62"/>
       <c r="G2" s="37"/>
@@ -7636,16 +7657,16 @@
         <v>0.0</v>
       </c>
       <c r="D3" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="4">
@@ -7660,16 +7681,16 @@
         <v>0.0</v>
       </c>
       <c r="D4" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="5">
@@ -7684,16 +7705,16 @@
         <v>0.0</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="6">
@@ -7702,22 +7723,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="C6" s="36">
         <v>0.0</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="7">
@@ -7726,22 +7747,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="C7" s="36">
         <v>0.0</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="8">
@@ -7756,16 +7777,16 @@
         <v>0.0</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="G8" s="37" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="9">
@@ -7774,22 +7795,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="C9" s="36">
         <v>0.0</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
       <c r="G9" s="37" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="10">
@@ -7798,22 +7819,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="C10" s="36">
         <v>0.0</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="11">
@@ -7822,22 +7843,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="C11" s="36">
         <v>1.0</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="12">
@@ -7846,22 +7867,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
       <c r="C12" s="36">
         <v>0.0</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="13">
@@ -7870,22 +7891,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="C13" s="36">
         <v>0.0</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="G13" s="37" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="14">
@@ -7894,22 +7915,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="C14" s="36">
         <v>1.0</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="15">
@@ -7918,22 +7939,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="C15" s="36">
         <v>1.0</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="16">
@@ -7942,22 +7963,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C16" s="36">
         <v>1.0</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="17">
@@ -7966,22 +7987,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1156</v>
+        <v>972</v>
       </c>
       <c r="C17" s="36">
         <v>0.0</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="18">
@@ -7990,22 +8011,22 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>719</v>
+        <v>1164</v>
       </c>
       <c r="C18" s="36">
         <v>0.0</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="19">
@@ -8014,22 +8035,22 @@
         <v>17</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C19" s="36">
         <v>0.0</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
       <c r="G19" s="37" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="20">
@@ -8038,22 +8059,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C20" s="36">
         <v>0.0</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="21">
@@ -8062,22 +8083,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C21" s="36">
         <v>0.0</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="22">
@@ -8086,22 +8107,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C22" s="36">
         <v>0.0</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="23">
@@ -8110,22 +8131,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C23" s="36">
         <v>0.0</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="24">
@@ -8134,22 +8155,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C24" s="36">
         <v>0.0</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1172</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="25">
@@ -8158,22 +8179,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C25" s="36">
         <v>0.0</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
       <c r="G25" s="37" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="26">
@@ -8182,22 +8203,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>1175</v>
+        <v>729</v>
       </c>
       <c r="C26" s="36">
         <v>0.0</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="27">
@@ -8206,22 +8227,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
       <c r="C27" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="28">
@@ -8230,22 +8251,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1016</v>
+        <v>1186</v>
       </c>
       <c r="C28" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="29">
@@ -8254,22 +8275,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="C29" s="36">
         <v>0.0</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>1184</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="30">
@@ -8278,22 +8299,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="C30" s="36">
         <v>0.0</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>1185</v>
+        <v>1191</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="31">
@@ -8302,22 +8323,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>731</v>
+        <v>1026</v>
       </c>
       <c r="C31" s="36">
         <v>0.0</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1187</v>
+        <v>1193</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>1188</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="32">
@@ -8326,22 +8347,22 @@
         <v>30</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>968</v>
+        <v>731</v>
       </c>
       <c r="C32" s="36">
         <v>0.0</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>1189</v>
+        <v>1195</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>1190</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="33">
@@ -8350,22 +8371,22 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1191</v>
+        <v>974</v>
       </c>
       <c r="C33" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="34">
@@ -8374,22 +8395,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="C34" s="36">
         <v>1.0</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="35">
@@ -8398,22 +8419,22 @@
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>733</v>
+        <v>1202</v>
       </c>
       <c r="C35" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="36">
@@ -8422,22 +8443,22 @@
         <v>34</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1199</v>
+        <v>733</v>
       </c>
       <c r="C36" s="36">
         <v>0.0</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="37">
@@ -8446,22 +8467,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="C37" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="38">
@@ -8470,22 +8491,22 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="C38" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="39">
@@ -8494,22 +8515,22 @@
         <v>37</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="C39" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1209</v>
+        <v>1214</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="40">
@@ -8518,22 +8539,22 @@
         <v>38</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="C40" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="41">
@@ -8542,22 +8563,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="C41" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="42">
@@ -8566,22 +8587,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="C42" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>1219</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="43">
@@ -8590,22 +8611,22 @@
         <v>41</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="C43" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="44">
@@ -8614,22 +8635,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="C44" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>1224</v>
+        <v>1229</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>1225</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="45">
@@ -8638,22 +8659,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="C45" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="46">
@@ -8662,22 +8683,22 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
       <c r="C46" s="36">
         <v>1.0</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="47">
@@ -8686,22 +8707,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="C47" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="G47" s="37" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="48">
@@ -8710,22 +8731,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="C48" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="49">
@@ -8734,22 +8755,22 @@
         <v>47</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="C49" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
       <c r="G49" s="37" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="50">
@@ -8758,22 +8779,22 @@
         <v>48</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="C50" s="36">
         <v>0.0</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="G50" s="37" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="51">
@@ -8782,22 +8803,22 @@
         <v>49</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="C51" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="52">
@@ -8806,22 +8827,22 @@
         <v>50</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="C52" s="36">
         <v>1.0</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="53">
@@ -8830,22 +8851,22 @@
         <v>51</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="C53" s="36">
         <v>1.0</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="54">
@@ -8854,22 +8875,22 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="C54" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="55">
@@ -8878,22 +8899,22 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>981</v>
+        <v>1261</v>
       </c>
       <c r="C55" s="36">
         <v>0.0</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="G55" s="37" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="56">
@@ -8902,22 +8923,22 @@
         <v>54</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1258</v>
+        <v>987</v>
       </c>
       <c r="C56" s="36">
         <v>0.0</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="57">
@@ -8926,22 +8947,22 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>982</v>
+        <v>1266</v>
       </c>
       <c r="C57" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="58">
@@ -8950,22 +8971,22 @@
         <v>56</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>737</v>
+        <v>988</v>
       </c>
       <c r="C58" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="59">
@@ -8974,22 +8995,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1265</v>
+        <v>737</v>
       </c>
       <c r="C59" s="36">
         <v>0.0</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="60">
@@ -8998,22 +9019,22 @@
         <v>58</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="C60" s="36">
         <v>0.0</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="61">
@@ -9022,22 +9043,22 @@
         <v>59</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="C61" s="36">
         <v>0.0</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="62">
@@ -9046,22 +9067,22 @@
         <v>60</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>740</v>
+        <v>1279</v>
       </c>
       <c r="C62" s="36">
         <v>0.0</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E62" s="44" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="63">
@@ -9070,22 +9091,22 @@
         <v>61</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>1276</v>
+        <v>740</v>
       </c>
       <c r="C63" s="36">
         <v>0.0</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="64">
@@ -9094,22 +9115,22 @@
         <v>62</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="C64" s="36">
         <v>0.0</v>
       </c>
       <c r="D64" s="38" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F64" s="37" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="G64" s="37" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="65">
@@ -9118,22 +9139,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="C65" s="36">
         <v>0.0</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="66">
@@ -9142,22 +9163,22 @@
         <v>64</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
       <c r="C66" s="36">
         <v>0.0</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="67">
@@ -9166,22 +9187,22 @@
         <v>65</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="C67" s="36">
         <v>0.0</v>
       </c>
       <c r="D67" s="38" t="s">
-        <v>911</v>
+        <v>924</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="G67" s="37" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="68">
@@ -9190,22 +9211,22 @@
         <v>66</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="C68" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D68" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="69">
@@ -9214,22 +9235,22 @@
         <v>67</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="C69" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D69" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E69" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="70">
@@ -9238,22 +9259,22 @@
         <v>68</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="C70" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E70" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="G70" s="37" t="s">
-        <v>1298</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="71">
@@ -9262,22 +9283,22 @@
         <v>69</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1299</v>
+        <v>1304</v>
       </c>
       <c r="C71" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E71" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="G71" s="37" t="s">
-        <v>1301</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="72">
@@ -9286,22 +9307,22 @@
         <v>70</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1302</v>
+        <v>1307</v>
       </c>
       <c r="C72" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D72" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E72" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F72" s="37" t="s">
-        <v>1303</v>
+        <v>1308</v>
       </c>
       <c r="G72" s="37" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="73">
@@ -9310,22 +9331,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="C73" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D73" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E73" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F73" s="37" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="G73" s="37" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="74">
@@ -9334,22 +9355,22 @@
         <v>72</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>1308</v>
+        <v>1313</v>
       </c>
       <c r="C74" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D74" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E74" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F74" s="37" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="G74" s="37" t="s">
-        <v>1310</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="75">
@@ -9358,22 +9379,22 @@
         <v>73</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>1311</v>
+        <v>1316</v>
       </c>
       <c r="C75" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D75" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E75" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F75" s="37" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="G75" s="37" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="76">
@@ -9382,22 +9403,22 @@
         <v>74</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="C76" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D76" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E76" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F76" s="37" t="s">
-        <v>1315</v>
+        <v>1320</v>
       </c>
       <c r="G76" s="37" t="s">
-        <v>1316</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="77">
@@ -9406,22 +9427,22 @@
         <v>75</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
       <c r="C77" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D77" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E77" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F77" s="37" t="s">
-        <v>1318</v>
+        <v>1323</v>
       </c>
       <c r="G77" s="37" t="s">
-        <v>1319</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="78">
@@ -9430,22 +9451,22 @@
         <v>76</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>993</v>
+        <v>1325</v>
       </c>
       <c r="C78" s="36">
         <v>0.0</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E78" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F78" s="37" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
       <c r="G78" s="37" t="s">
-        <v>1321</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="79">
@@ -9454,22 +9475,22 @@
         <v>77</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>1322</v>
+        <v>999</v>
       </c>
       <c r="C79" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D79" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E79" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F79" s="37" t="s">
-        <v>1323</v>
+        <v>1328</v>
       </c>
       <c r="G79" s="37" t="s">
-        <v>1324</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="80">
@@ -9478,22 +9499,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>1325</v>
+        <v>1330</v>
       </c>
       <c r="C80" s="36">
         <v>1.0</v>
       </c>
       <c r="D80" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E80" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F80" s="37" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
       <c r="G80" s="37" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="81">
@@ -9502,22 +9523,22 @@
         <v>79</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="C81" s="36">
         <v>1.0</v>
       </c>
       <c r="D81" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E81" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F81" s="37" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="G81" s="37" t="s">
-        <v>1330</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="82">
@@ -9526,22 +9547,22 @@
         <v>80</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="C82" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D82" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E82" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F82" s="37" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="G82" s="37" t="s">
-        <v>1333</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="83">
@@ -9550,22 +9571,22 @@
         <v>81</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="C83" s="36">
         <v>0.0</v>
       </c>
       <c r="D83" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E83" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F83" s="37" t="s">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="G83" s="37" t="s">
-        <v>1336</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="84">
@@ -9574,22 +9595,22 @@
         <v>82</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="C84" s="36">
         <v>0.0</v>
       </c>
       <c r="D84" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E84" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F84" s="37" t="s">
-        <v>1338</v>
+        <v>1343</v>
       </c>
       <c r="G84" s="37" t="s">
-        <v>1339</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="85">
@@ -9598,22 +9619,22 @@
         <v>83</v>
       </c>
       <c r="B85" s="36" t="s">
-        <v>743</v>
+        <v>1345</v>
       </c>
       <c r="C85" s="36">
         <v>0.0</v>
       </c>
       <c r="D85" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E85" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>1340</v>
+        <v>1346</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>1341</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="86">
@@ -9622,22 +9643,22 @@
         <v>84</v>
       </c>
       <c r="B86" s="36" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C86" s="36">
         <v>0.0</v>
       </c>
       <c r="D86" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E86" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F86" s="37" t="s">
-        <v>1342</v>
+        <v>1348</v>
       </c>
       <c r="G86" s="37" t="s">
-        <v>1342</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="87">
@@ -9646,22 +9667,22 @@
         <v>85</v>
       </c>
       <c r="B87" s="36" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C87" s="36">
         <v>0.0</v>
       </c>
       <c r="D87" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E87" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F87" s="37" t="s">
-        <v>1343</v>
+        <v>1350</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="88">
@@ -9670,22 +9691,22 @@
         <v>86</v>
       </c>
       <c r="B88" s="36" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C88" s="36">
         <v>0.0</v>
       </c>
       <c r="D88" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E88" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F88" s="37" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="G88" s="37" t="s">
-        <v>1346</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="89">
@@ -9694,22 +9715,22 @@
         <v>87</v>
       </c>
       <c r="B89" s="36" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="C89" s="36">
         <v>0.0</v>
       </c>
       <c r="D89" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E89" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F89" s="37" t="s">
-        <v>1347</v>
+        <v>1353</v>
       </c>
       <c r="G89" s="37" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="90">
@@ -9718,22 +9739,22 @@
         <v>88</v>
       </c>
       <c r="B90" s="36" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="C90" s="36">
         <v>0.0</v>
       </c>
       <c r="D90" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E90" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F90" s="37" t="s">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="G90" s="37" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="91">
@@ -9742,22 +9763,22 @@
         <v>89</v>
       </c>
       <c r="B91" s="36" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C91" s="36">
         <v>0.0</v>
       </c>
       <c r="D91" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E91" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F91" s="37" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="G91" s="37" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="92">
@@ -9766,22 +9787,22 @@
         <v>90</v>
       </c>
       <c r="B92" s="36" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C92" s="36">
         <v>0.0</v>
       </c>
       <c r="D92" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E92" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F92" s="37" t="s">
-        <v>1353</v>
+        <v>1359</v>
       </c>
       <c r="G92" s="37" t="s">
-        <v>1354</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="93">
@@ -9790,22 +9811,22 @@
         <v>91</v>
       </c>
       <c r="B93" s="36" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C93" s="36">
         <v>0.0</v>
       </c>
       <c r="D93" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E93" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F93" s="37" t="s">
-        <v>1355</v>
+        <v>1361</v>
       </c>
       <c r="G93" s="37" t="s">
-        <v>1356</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="94">
@@ -9814,22 +9835,22 @@
         <v>92</v>
       </c>
       <c r="B94" s="36" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C94" s="36">
         <v>0.0</v>
       </c>
       <c r="D94" s="38" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="E94" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F94" s="37" t="s">
-        <v>1357</v>
+        <v>1363</v>
       </c>
       <c r="G94" s="37" t="s">
-        <v>1358</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="95">
@@ -9838,22 +9859,22 @@
         <v>93</v>
       </c>
       <c r="B95" s="36" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C95" s="36">
         <v>0.0</v>
       </c>
       <c r="D95" s="38" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="E95" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F95" s="37" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
       <c r="G95" s="37" t="s">
-        <v>1360</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="96">
@@ -9862,22 +9883,22 @@
         <v>94</v>
       </c>
       <c r="B96" s="36" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C96" s="36">
         <v>0.0</v>
       </c>
       <c r="D96" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E96" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F96" s="37" t="s">
-        <v>1361</v>
+        <v>1367</v>
       </c>
       <c r="G96" s="37" t="s">
-        <v>1362</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="97">
@@ -9886,22 +9907,22 @@
         <v>95</v>
       </c>
       <c r="B97" s="36" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C97" s="36">
         <v>0.0</v>
       </c>
       <c r="D97" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E97" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F97" s="37" t="s">
-        <v>1363</v>
+        <v>1369</v>
       </c>
       <c r="G97" s="37" t="s">
-        <v>1364</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="98">
@@ -9910,22 +9931,22 @@
         <v>96</v>
       </c>
       <c r="B98" s="36" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C98" s="36">
         <v>0.0</v>
       </c>
       <c r="D98" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E98" s="44" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="F98" s="37" t="s">
-        <v>1365</v>
+        <v>1371</v>
       </c>
       <c r="G98" s="37" t="s">
-        <v>1366</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="99">
@@ -9934,22 +9955,22 @@
         <v>97</v>
       </c>
       <c r="B99" s="36" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C99" s="36">
         <v>0.0</v>
       </c>
       <c r="D99" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E99" s="44" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="F99" s="37" t="s">
-        <v>1367</v>
+        <v>1373</v>
       </c>
       <c r="G99" s="37" t="s">
-        <v>1368</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="100">
@@ -9958,22 +9979,22 @@
         <v>98</v>
       </c>
       <c r="B100" s="36" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C100" s="36">
         <v>0.0</v>
       </c>
       <c r="D100" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E100" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F100" s="37" t="s">
-        <v>1369</v>
+        <v>1375</v>
       </c>
       <c r="G100" s="37" t="s">
-        <v>1370</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="101">
@@ -9982,22 +10003,22 @@
         <v>99</v>
       </c>
       <c r="B101" s="36" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C101" s="36">
         <v>0.0</v>
       </c>
       <c r="D101" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E101" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F101" s="37" t="s">
-        <v>1371</v>
+        <v>1377</v>
       </c>
       <c r="G101" s="37" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="102">
@@ -10006,22 +10027,22 @@
         <v>100</v>
       </c>
       <c r="B102" s="36" t="s">
-        <v>1373</v>
+        <v>766</v>
       </c>
       <c r="C102" s="36">
         <v>0.0</v>
       </c>
       <c r="D102" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E102" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F102" s="37" t="s">
-        <v>1374</v>
+        <v>1379</v>
       </c>
       <c r="G102" s="37" t="s">
-        <v>1375</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="103">
@@ -10030,22 +10051,22 @@
         <v>101</v>
       </c>
       <c r="B103" s="36" t="s">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="C103" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D103" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E103" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F103" s="37" t="s">
-        <v>1377</v>
+        <v>1382</v>
       </c>
       <c r="G103" s="37" t="s">
-        <v>1378</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="104">
@@ -10054,22 +10075,22 @@
         <v>102</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>1379</v>
+        <v>1384</v>
       </c>
       <c r="C104" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D104" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E104" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F104" s="37" t="s">
-        <v>1380</v>
+        <v>1385</v>
       </c>
       <c r="G104" s="37" t="s">
-        <v>1381</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="105">
@@ -10078,22 +10099,22 @@
         <v>103</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>1382</v>
+        <v>1387</v>
       </c>
       <c r="C105" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D105" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E105" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F105" s="37" t="s">
-        <v>1383</v>
+        <v>1388</v>
       </c>
       <c r="G105" s="37" t="s">
-        <v>1384</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="106">
@@ -10102,22 +10123,22 @@
         <v>104</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>1385</v>
+        <v>1390</v>
       </c>
       <c r="C106" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D106" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E106" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F106" s="37" t="s">
-        <v>1386</v>
+        <v>1391</v>
       </c>
       <c r="G106" s="37" t="s">
-        <v>1387</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="107">
@@ -10126,22 +10147,22 @@
         <v>105</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>1388</v>
+        <v>1393</v>
       </c>
       <c r="C107" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D107" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E107" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F107" s="37" t="s">
-        <v>1389</v>
+        <v>1394</v>
       </c>
       <c r="G107" s="37" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="108">
@@ -10150,22 +10171,22 @@
         <v>106</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>1390</v>
+        <v>1396</v>
       </c>
       <c r="C108" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D108" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E108" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F108" s="37" t="s">
-        <v>1391</v>
+        <v>1397</v>
       </c>
       <c r="G108" s="37" t="s">
-        <v>1392</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="109">
@@ -10174,22 +10195,22 @@
         <v>107</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>1393</v>
+        <v>1398</v>
       </c>
       <c r="C109" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D109" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E109" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F109" s="37" t="s">
-        <v>1394</v>
+        <v>1399</v>
       </c>
       <c r="G109" s="37" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="110">
@@ -10198,22 +10219,22 @@
         <v>108</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>1396</v>
+        <v>1401</v>
       </c>
       <c r="C110" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D110" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E110" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F110" s="37" t="s">
-        <v>1397</v>
+        <v>1402</v>
       </c>
       <c r="G110" s="37" t="s">
-        <v>1398</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="111">
@@ -10222,22 +10243,22 @@
         <v>109</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>1399</v>
+        <v>1404</v>
       </c>
       <c r="C111" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D111" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E111" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F111" s="37" t="s">
-        <v>1400</v>
+        <v>1405</v>
       </c>
       <c r="G111" s="37" t="s">
-        <v>1401</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="112">
@@ -10246,22 +10267,22 @@
         <v>110</v>
       </c>
       <c r="B112" s="36" t="s">
-        <v>1402</v>
+        <v>1407</v>
       </c>
       <c r="C112" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D112" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E112" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F112" s="37" t="s">
-        <v>1403</v>
+        <v>1408</v>
       </c>
       <c r="G112" s="37" t="s">
-        <v>1404</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="113">
@@ -10270,22 +10291,22 @@
         <v>111</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>1001</v>
+        <v>1410</v>
       </c>
       <c r="C113" s="36">
         <v>0.0</v>
       </c>
       <c r="D113" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E113" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F113" s="37" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="G113" s="37" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="114">
@@ -10294,22 +10315,22 @@
         <v>112</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>1407</v>
+        <v>1007</v>
       </c>
       <c r="C114" s="36">
         <v>0.0</v>
       </c>
       <c r="D114" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E114" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F114" s="37" t="s">
-        <v>1408</v>
+        <v>1413</v>
       </c>
       <c r="G114" s="37" t="s">
-        <v>1409</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="115">
@@ -10318,22 +10339,22 @@
         <v>113</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="C115" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D115" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E115" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F115" s="37" t="s">
-        <v>1411</v>
+        <v>1416</v>
       </c>
       <c r="G115" s="37" t="s">
-        <v>1412</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="116">
@@ -10342,22 +10363,22 @@
         <v>114</v>
       </c>
       <c r="B116" s="36" t="s">
-        <v>769</v>
+        <v>1418</v>
       </c>
       <c r="C116" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D116" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E116" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F116" s="37" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="G116" s="37" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="117">
@@ -10366,7 +10387,7 @@
         <v>115</v>
       </c>
       <c r="B117" s="36" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C117" s="36">
         <v>0.0</v>
@@ -10375,13 +10396,13 @@
         <v>914</v>
       </c>
       <c r="E117" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F117" s="37" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="G117" s="37" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="118">
@@ -10390,22 +10411,22 @@
         <v>116</v>
       </c>
       <c r="B118" s="36" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C118" s="36">
         <v>0.0</v>
       </c>
       <c r="D118" s="38" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="E118" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F118" s="37" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="G118" s="37" t="s">
-        <v>1418</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="119">
@@ -10414,22 +10435,22 @@
         <v>117</v>
       </c>
       <c r="B119" s="36" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C119" s="36">
         <v>0.0</v>
       </c>
       <c r="D119" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E119" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F119" s="37" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="G119" s="37" t="s">
-        <v>14</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="120">
@@ -10438,22 +10459,22 @@
         <v>118</v>
       </c>
       <c r="B120" s="36" t="s">
-        <v>1003</v>
+        <v>773</v>
       </c>
       <c r="C120" s="36">
         <v>0.0</v>
       </c>
       <c r="D120" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E120" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F120" s="37" t="s">
-        <v>1420</v>
+        <v>1427</v>
       </c>
       <c r="G120" s="37" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121">
@@ -10462,22 +10483,22 @@
         <v>119</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="C121" s="36">
         <v>0.0</v>
       </c>
       <c r="D121" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E121" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F121" s="37" t="s">
-        <v>1421</v>
+        <v>1428</v>
       </c>
       <c r="G121" s="37" t="s">
-        <v>1422</v>
+        <v>32</v>
       </c>
     </row>
     <row r="122">
@@ -10486,22 +10507,22 @@
         <v>120</v>
       </c>
       <c r="B122" s="36" t="s">
-        <v>1423</v>
+        <v>1010</v>
       </c>
       <c r="C122" s="36">
         <v>0.0</v>
       </c>
       <c r="D122" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E122" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F122" s="37" t="s">
-        <v>1424</v>
+        <v>1429</v>
       </c>
       <c r="G122" s="37" t="s">
-        <v>1425</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="123">
@@ -10510,22 +10531,22 @@
         <v>121</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>1426</v>
+        <v>1431</v>
       </c>
       <c r="C123" s="36">
         <v>0.0</v>
       </c>
       <c r="D123" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E123" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F123" s="37" t="s">
-        <v>1427</v>
+        <v>1432</v>
       </c>
       <c r="G123" s="37" t="s">
-        <v>1428</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="124">
@@ -10534,22 +10555,22 @@
         <v>122</v>
       </c>
       <c r="B124" s="36" t="s">
-        <v>778</v>
+        <v>1434</v>
       </c>
       <c r="C124" s="36">
         <v>0.0</v>
       </c>
       <c r="D124" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E124" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F124" s="37" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="G124" s="37" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="125">
@@ -10558,22 +10579,22 @@
         <v>123</v>
       </c>
       <c r="B125" s="36" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C125" s="36">
         <v>0.0</v>
       </c>
       <c r="D125" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E125" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F125" s="37" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="G125" s="37" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="126">
@@ -10582,30 +10603,54 @@
         <v>124</v>
       </c>
       <c r="B126" s="36" t="s">
-        <v>1433</v>
+        <v>779</v>
       </c>
       <c r="C126" s="36">
         <v>0.0</v>
       </c>
       <c r="D126" s="38" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F126" s="37" t="s">
-        <v>1434</v>
+        <v>1439</v>
       </c>
       <c r="G126" s="37" t="s">
-        <v>1434</v>
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="36">
+        <f>ROW()-ROW(Table_Phrases[N])</f>
+        <v>125</v>
+      </c>
+      <c r="B127" s="36" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C127" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D127" s="38" t="s">
+        <v>914</v>
+      </c>
+      <c r="E127" s="44" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F127" s="37" t="s">
+        <v>1442</v>
+      </c>
+      <c r="G127" s="37" t="s">
+        <v>1442</v>
       </c>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E126">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E127">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D126">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D127">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -10640,31 +10685,31 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1435</v>
+        <v>1443</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>1436</v>
+        <v>1444</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1437</v>
+        <v>1445</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1438</v>
+        <v>1446</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>1439</v>
+        <v>1447</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>1440</v>
+        <v>1448</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>1441</v>
+        <v>1449</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>1442</v>
+        <v>1450</v>
       </c>
       <c r="J1" s="28" t="s">
-        <v>1443</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="2" ht="186.0" customHeight="1">
@@ -10673,13 +10718,13 @@
         <v>-1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>1444</v>
+        <v>1452</v>
       </c>
       <c r="C2" s="64" t="s">
         <v>301</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>301</v>
@@ -10691,7 +10736,7 @@
         <v>299</v>
       </c>
       <c r="H2" s="35" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="I2" s="35" t="s">
         <v>303</v>
@@ -10706,25 +10751,25 @@
         <v>0</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>1445</v>
+        <v>1453</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>1446</v>
+        <v>1454</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1447</v>
+        <v>1455</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H3" s="35" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="I3" s="35" t="s">
         <v>303</v>
@@ -10739,25 +10784,25 @@
         <v>1</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1448</v>
+        <v>1456</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>1449</v>
+        <v>1457</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1449</v>
+        <v>1457</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H4" s="35" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="I4" s="35" t="s">
         <v>303</v>
@@ -10772,25 +10817,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1451</v>
+        <v>1459</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>1452</v>
+        <v>1460</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1452</v>
+        <v>1460</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1453</v>
+        <v>1461</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H5" s="35" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="I5" s="35" t="s">
         <v>509</v>
@@ -10805,25 +10850,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1454</v>
+        <v>1462</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>1455</v>
+        <v>1463</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1455</v>
+        <v>1463</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1456</v>
+        <v>1464</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="I6" s="35" t="s">
         <v>509</v>
@@ -10838,25 +10883,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1457</v>
+        <v>1465</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>1459</v>
+        <v>1467</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="I7" s="35" t="s">
         <v>303</v>
@@ -10871,25 +10916,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>1460</v>
+        <v>1468</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>1461</v>
+        <v>1469</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>1461</v>
+        <v>1469</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>1462</v>
+        <v>1470</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="I8" s="35" t="s">
         <v>303</v>
@@ -10907,22 +10952,22 @@
         <v>16</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>1463</v>
+        <v>1471</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="I9" s="35" t="s">
         <v>303</v>
@@ -10937,25 +10982,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>1464</v>
+        <v>1472</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>1465</v>
+        <v>1473</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1465</v>
+        <v>1473</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1466</v>
+        <v>1474</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="I10" s="35" t="s">
         <v>504</v>
@@ -10970,25 +11015,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1467</v>
+        <v>1475</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1468</v>
+        <v>1476</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1468</v>
+        <v>1476</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>1469</v>
+        <v>1477</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="I11" s="35" t="s">
         <v>303</v>
@@ -11003,16 +11048,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1470</v>
+        <v>1478</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1471</v>
+        <v>1479</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>1471</v>
+        <v>1479</v>
       </c>
       <c r="F12" s="35" t="s">
         <v>325</v>
@@ -11021,7 +11066,7 @@
         <v>299</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="I12" s="35" t="s">
         <v>303</v>
@@ -11036,16 +11081,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>1472</v>
+        <v>1480</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1473</v>
+        <v>1481</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>1473</v>
+        <v>1481</v>
       </c>
       <c r="F13" s="35" t="s">
         <v>325</v>
@@ -11054,7 +11099,7 @@
         <v>299</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="I13" s="35" t="s">
         <v>303</v>
@@ -11072,13 +11117,13 @@
         <v>20</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>1474</v>
+        <v>1482</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>1474</v>
+        <v>1482</v>
       </c>
       <c r="F14" s="35" t="s">
         <v>325</v>
@@ -11087,7 +11132,7 @@
         <v>299</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="I14" s="35" t="s">
         <v>303</v>
@@ -11102,13 +11147,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1475</v>
+        <v>1483</v>
       </c>
       <c r="C15" s="64" t="s">
         <v>301</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E15" s="35" t="s">
         <v>428</v>
@@ -11120,7 +11165,7 @@
         <v>299</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="I15" s="35" t="s">
         <v>303</v>
@@ -11165,7 +11210,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1476</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="2">
@@ -11192,7 +11237,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1477</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="5">
@@ -11201,7 +11246,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1478</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="6">
@@ -11213,7 +11258,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1479</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="8">
@@ -11221,7 +11266,7 @@
         <v>0.0</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1480</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="9">
@@ -11229,7 +11274,7 @@
         <v>1.0</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1481</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="10">
@@ -11237,7 +11282,7 @@
         <v>2.0</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1482</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="11">
@@ -11245,7 +11290,7 @@
         <v>3.0</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1483</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="12">
@@ -11253,7 +11298,7 @@
         <v>4.0</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1484</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="13">
@@ -11261,7 +11306,7 @@
         <v>5.0</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1485</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="15">
@@ -11269,7 +11314,7 @@
         <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1486</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="16">
@@ -11287,7 +11332,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1487</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="18">
@@ -11332,7 +11377,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1488</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="23">
@@ -11358,7 +11403,7 @@
         <v>44</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1489</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="27">
@@ -11403,7 +11448,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1490</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="32">
@@ -11430,7 +11475,7 @@
         <v>7</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1491</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="35">
@@ -11448,7 +11493,7 @@
         <v>9</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1492</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="37">
@@ -11493,7 +11538,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1493</v>
+        <v>818</v>
       </c>
     </row>
     <row r="42">
@@ -11510,7 +11555,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1494</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="45">
@@ -11518,7 +11563,7 @@
         <v>0.0</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="46">
@@ -11526,7 +11571,7 @@
         <v>1.0</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="48">
@@ -11534,7 +11579,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1495</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="49">
@@ -11587,7 +11632,7 @@
         <v>44</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1496</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="56">
@@ -11652,7 +11697,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1497</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="2">
@@ -11670,7 +11715,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1498</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="4">
@@ -11679,7 +11724,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1499</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="5">
@@ -11760,7 +11805,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1500</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="14">
@@ -11949,7 +11994,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1501</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="36">
@@ -11957,16 +12002,16 @@
         <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1502</v>
+        <v>1509</v>
       </c>
       <c r="C36" s="66" t="s">
         <v>290</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>1503</v>
+        <v>1510</v>
       </c>
       <c r="E36" s="66" t="s">
-        <v>1504</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="37">
@@ -11975,7 +12020,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1505</v>
+        <v>1512</v>
       </c>
       <c r="C37" s="38" t="s">
         <v>299</v>
@@ -11994,13 +12039,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1506</v>
+        <v>1513</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="E38" s="67" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B38,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_JOB_FIND_1_1|MEMENTO_JOB_FIND_1_2")</f>
@@ -12013,13 +12058,13 @@
         <v>2</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1507</v>
+        <v>1514</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="E39" s="67" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B39,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_RECIPE_MISSION_1")</f>
@@ -12035,7 +12080,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="D40" s="38" t="s">
         <v>40</v>
@@ -12051,7 +12096,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1508</v>
+        <v>1515</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>427</v>
@@ -12069,19 +12114,19 @@
         <v>44</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1509</v>
+        <v>1516</v>
       </c>
       <c r="C43" s="65" t="s">
-        <v>1510</v>
+        <v>1517</v>
       </c>
       <c r="D43" s="65" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="E43" s="66" t="s">
-        <v>1511</v>
+        <v>1518</v>
       </c>
       <c r="F43" s="65" t="s">
-        <v>1512</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="44">
@@ -12093,13 +12138,13 @@
         <v>670</v>
       </c>
       <c r="C44" s="44" t="s">
-        <v>1505</v>
+        <v>1512</v>
       </c>
       <c r="D44" s="44" t="s">
         <v>673</v>
       </c>
       <c r="E44" s="48" t="s">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="F44" s="43" t="b">
         <v>0</v>
@@ -12114,13 +12159,13 @@
         <v>682</v>
       </c>
       <c r="C45" s="44" t="s">
-        <v>1506</v>
+        <v>1513</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="F45" s="43" t="b">
         <v>0</v>
@@ -12135,13 +12180,13 @@
         <v>699</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>1506</v>
+        <v>1513</v>
       </c>
       <c r="D46" s="44" t="s">
         <v>719</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="F46" s="43" t="b">
         <v>0</v>
@@ -12156,13 +12201,13 @@
         <v>704</v>
       </c>
       <c r="C47" s="44" t="s">
-        <v>1507</v>
+        <v>1514</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="F47" s="43" t="b">
         <v>0</v>
@@ -12180,10 +12225,10 @@
         <v>39</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>1331</v>
+        <v>1339</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="F48" s="43" t="b">
         <v>0</v>
@@ -12195,16 +12240,16 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1514</v>
+        <v>1521</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>39</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>1334</v>
+        <v>1342</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="F49" s="43" t="b">
         <v>0</v>
@@ -12216,16 +12261,16 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1515</v>
+        <v>1522</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>39</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="F50" s="43" t="b">
         <v>1</v>
@@ -12237,16 +12282,16 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1516</v>
+        <v>1523</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>1508</v>
+        <v>1515</v>
       </c>
       <c r="D51" s="44" t="s">
         <v>673</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="F51" s="43" t="b">
         <v>0</v>
@@ -12257,10 +12302,10 @@
         <v>44</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1517</v>
+        <v>1524</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>1518</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="54">
@@ -12269,7 +12314,7 @@
         <v>0</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="C54" s="51" t="s">
         <v>436</v>
@@ -12280,7 +12325,7 @@
         <v>44</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1519</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="57">
@@ -13290,16 +13335,16 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1520</v>
+        <v>1527</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1521</v>
+        <v>1528</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1522</v>
+        <v>1529</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1523</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="2">
@@ -13311,7 +13356,7 @@
         <v>302</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1524</v>
+        <v>1531</v>
       </c>
       <c r="D2" s="68" t="s">
         <v>299</v>
@@ -13329,7 +13374,7 @@
         <v>417</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1525</v>
+        <v>1532</v>
       </c>
       <c r="D3" s="68" t="s">
         <v>299</v>
@@ -13344,10 +13389,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1526</v>
+        <v>1533</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1524</v>
+        <v>1531</v>
       </c>
       <c r="D4" s="68" t="s">
         <v>299</v>
@@ -13377,7 +13422,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="19.0"/>
+    <col customWidth="1" min="2" max="2" width="24.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13385,7 +13430,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1479</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="2">
@@ -13403,7 +13448,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1527</v>
+        <v>819</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="36">
+        <f>ROW()-ROW(Table_Animations[N])</f>
+        <v>2</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>1534</v>
       </c>
     </row>
   </sheetData>
@@ -13429,21 +13483,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1528</v>
+        <v>1535</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1529</v>
+        <v>1536</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1530</v>
+        <v>1537</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1531</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="s">
-        <v>1532</v>
+        <v>1539</v>
       </c>
       <c r="B2" s="69">
         <v>1.0</v>
@@ -13457,7 +13511,7 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>1533</v>
+        <v>1540</v>
       </c>
       <c r="B3" s="69">
         <v>1.0</v>
@@ -13471,7 +13525,7 @@
     </row>
     <row r="4">
       <c r="A4" s="37" t="s">
-        <v>1534</v>
+        <v>1541</v>
       </c>
       <c r="B4" s="69">
         <v>3.0</v>
@@ -13485,7 +13539,7 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>1535</v>
+        <v>1542</v>
       </c>
       <c r="B5" s="69">
         <v>1.0</v>
@@ -13499,7 +13553,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>1536</v>
+        <v>1543</v>
       </c>
       <c r="B6" s="69">
         <v>3.0</v>
@@ -13513,7 +13567,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>1537</v>
+        <v>1544</v>
       </c>
       <c r="B7" s="69">
         <v>3.0</v>
@@ -13527,7 +13581,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>1538</v>
+        <v>1545</v>
       </c>
       <c r="B8" s="69">
         <v>5.0</v>
@@ -13541,7 +13595,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>1539</v>
+        <v>1546</v>
       </c>
       <c r="B9" s="69">
         <v>4.0</v>
@@ -13555,7 +13609,7 @@
     </row>
     <row r="10">
       <c r="A10" s="37" t="s">
-        <v>1540</v>
+        <v>1547</v>
       </c>
       <c r="B10" s="69">
         <v>5.0</v>
@@ -13569,7 +13623,7 @@
     </row>
     <row r="11">
       <c r="A11" s="37" t="s">
-        <v>1541</v>
+        <v>1548</v>
       </c>
       <c r="B11" s="69">
         <v>4.0</v>
@@ -13583,7 +13637,7 @@
     </row>
     <row r="12">
       <c r="A12" s="37" t="s">
-        <v>1542</v>
+        <v>1549</v>
       </c>
       <c r="B12" s="69">
         <v>1.0</v>
@@ -13597,7 +13651,7 @@
     </row>
     <row r="13">
       <c r="A13" s="37" t="s">
-        <v>1543</v>
+        <v>1550</v>
       </c>
       <c r="B13" s="69">
         <v>4.0</v>
@@ -13611,7 +13665,7 @@
     </row>
     <row r="14">
       <c r="A14" s="37" t="s">
-        <v>1544</v>
+        <v>1551</v>
       </c>
       <c r="B14" s="69">
         <v>1.0</v>
@@ -13625,7 +13679,7 @@
     </row>
     <row r="15">
       <c r="A15" s="37" t="s">
-        <v>1545</v>
+        <v>1552</v>
       </c>
       <c r="B15" s="69">
         <v>2.0</v>
@@ -13639,7 +13693,7 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="s">
-        <v>1546</v>
+        <v>1553</v>
       </c>
       <c r="B16" s="69">
         <v>3.0</v>
@@ -13653,7 +13707,7 @@
     </row>
     <row r="17">
       <c r="A17" s="37" t="s">
-        <v>1547</v>
+        <v>1554</v>
       </c>
       <c r="B17" s="69">
         <v>2.0</v>
@@ -13667,7 +13721,7 @@
     </row>
     <row r="18">
       <c r="A18" s="37" t="s">
-        <v>1548</v>
+        <v>1555</v>
       </c>
       <c r="B18" s="69">
         <v>2.0</v>
@@ -13681,7 +13735,7 @@
     </row>
     <row r="19">
       <c r="A19" s="37" t="s">
-        <v>1549</v>
+        <v>1556</v>
       </c>
       <c r="B19" s="69">
         <v>2.0</v>
@@ -13695,7 +13749,7 @@
     </row>
     <row r="20">
       <c r="A20" s="37" t="s">
-        <v>1550</v>
+        <v>1557</v>
       </c>
       <c r="B20" s="69">
         <v>2.0</v>
@@ -13709,7 +13763,7 @@
     </row>
     <row r="21">
       <c r="A21" s="37" t="s">
-        <v>1551</v>
+        <v>1558</v>
       </c>
       <c r="B21" s="69">
         <v>3.0</v>
@@ -13723,7 +13777,7 @@
     </row>
     <row r="22">
       <c r="A22" s="37" t="s">
-        <v>1552</v>
+        <v>1559</v>
       </c>
       <c r="B22" s="69">
         <v>2.0</v>
@@ -13737,7 +13791,7 @@
     </row>
     <row r="23">
       <c r="A23" s="37" t="s">
-        <v>1553</v>
+        <v>1560</v>
       </c>
       <c r="B23" s="69">
         <v>2.0</v>
@@ -13751,7 +13805,7 @@
     </row>
     <row r="24">
       <c r="A24" s="37" t="s">
-        <v>1554</v>
+        <v>1561</v>
       </c>
       <c r="B24" s="69">
         <v>2.0</v>
@@ -13765,7 +13819,7 @@
     </row>
     <row r="25">
       <c r="A25" s="37" t="s">
-        <v>1555</v>
+        <v>1562</v>
       </c>
       <c r="B25" s="69">
         <v>2.0</v>
@@ -13779,7 +13833,7 @@
     </row>
     <row r="26">
       <c r="A26" s="37" t="s">
-        <v>1556</v>
+        <v>1563</v>
       </c>
       <c r="B26" s="69">
         <v>2.0</v>
@@ -13793,7 +13847,7 @@
     </row>
     <row r="27">
       <c r="A27" s="37" t="s">
-        <v>1557</v>
+        <v>1564</v>
       </c>
       <c r="B27" s="69">
         <v>2.0</v>
@@ -13807,7 +13861,7 @@
     </row>
     <row r="28">
       <c r="A28" s="37" t="s">
-        <v>1558</v>
+        <v>1565</v>
       </c>
       <c r="B28" s="69">
         <v>2.0</v>
@@ -13821,7 +13875,7 @@
     </row>
     <row r="29">
       <c r="A29" s="37" t="s">
-        <v>1559</v>
+        <v>1566</v>
       </c>
       <c r="B29" s="69">
         <v>4.0</v>
@@ -13835,7 +13889,7 @@
     </row>
     <row r="30">
       <c r="A30" s="37" t="s">
-        <v>1560</v>
+        <v>1567</v>
       </c>
       <c r="B30" s="69">
         <v>2.0</v>
@@ -13849,7 +13903,7 @@
     </row>
     <row r="31">
       <c r="A31" s="37" t="s">
-        <v>1561</v>
+        <v>1568</v>
       </c>
       <c r="B31" s="69">
         <v>3.0</v>
@@ -13863,7 +13917,7 @@
     </row>
     <row r="32">
       <c r="A32" s="37" t="s">
-        <v>1562</v>
+        <v>1569</v>
       </c>
       <c r="B32" s="69">
         <v>2.0</v>
@@ -13877,7 +13931,7 @@
     </row>
     <row r="33">
       <c r="A33" s="37" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B33" s="69">
         <v>5.0</v>
@@ -19852,7 +19906,7 @@
     <col customWidth="1" min="1" max="1" width="6.29"/>
     <col customWidth="1" min="2" max="2" width="65.57"/>
     <col customWidth="1" min="3" max="3" width="52.29"/>
-    <col customWidth="1" min="4" max="4" width="39.29"/>
+    <col customWidth="1" min="4" max="4" width="44.57"/>
     <col customWidth="1" min="5" max="5" width="62.71"/>
     <col customWidth="1" min="6" max="6" width="55.71"/>
     <col customWidth="1" min="7" max="7" width="44.57"/>
@@ -19861,8 +19915,7 @@
     <col customWidth="1" min="10" max="10" width="71.14"/>
     <col customWidth="1" min="11" max="11" width="54.43"/>
     <col customWidth="1" min="12" max="12" width="71.14"/>
-    <col customWidth="1" min="13" max="13" width="24.71"/>
-    <col customWidth="1" min="14" max="14" width="24.29"/>
+    <col customWidth="1" min="13" max="14" width="24.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27962,10 +28015,10 @@
         <v>817</v>
       </c>
       <c r="C218" s="43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D218" s="44" t="s">
-        <v>669</v>
+        <v>818</v>
       </c>
       <c r="E218" s="44" t="s">
         <v>298</v>
@@ -27995,12 +28048,57 @@
         <v>673</v>
       </c>
       <c r="N218" s="44" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="47">
+        <f>ROW()-ROW(Table_Actions[N])</f>
+        <v>127</v>
+      </c>
+      <c r="B219" s="45" t="s">
+        <v>820</v>
+      </c>
+      <c r="C219" s="43" t="b">
+        <v>0</v>
+      </c>
+      <c r="D219" s="44" t="s">
+        <v>669</v>
+      </c>
+      <c r="E219" s="44" t="s">
+        <v>298</v>
+      </c>
+      <c r="F219" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="G219" s="44" t="s">
+        <v>438</v>
+      </c>
+      <c r="H219" s="44" t="s">
+        <v>670</v>
+      </c>
+      <c r="I219" s="48" t="s">
+        <v>436</v>
+      </c>
+      <c r="J219" s="44" t="s">
+        <v>671</v>
+      </c>
+      <c r="K219" s="44" t="s">
+        <v>437</v>
+      </c>
+      <c r="L219" s="44" t="s">
+        <v>672</v>
+      </c>
+      <c r="M219" s="44" t="s">
+        <v>673</v>
+      </c>
+      <c r="N219" s="44" t="s">
         <v>674</v>
       </c>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H62 H65:H89 I92:I218">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H62 H65:H89 I92:I219">
       <formula1>#REF!</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C2:C62">
@@ -28012,7 +28110,7 @@
     <dataValidation type="list" allowBlank="1" sqref="F65:F89">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:G62 G65:G89 D92:H218 J92:N218">
+    <dataValidation type="list" allowBlank="1" sqref="D2:G62 G65:G89 D92:H219 J92:N219">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -28043,10 +28141,10 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="2">
@@ -28067,7 +28165,7 @@
         <v>320</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
     </row>
     <row r="4">
@@ -28076,10 +28174,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
     </row>
     <row r="5">
@@ -28088,10 +28186,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="6">
@@ -28100,10 +28198,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7">
@@ -28112,10 +28210,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
     <row r="8">
@@ -28124,10 +28222,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
     </row>
     <row r="9">
@@ -28136,10 +28234,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="10">
@@ -28148,10 +28246,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
     </row>
     <row r="11">
@@ -28160,10 +28258,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="12">
@@ -28172,10 +28270,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
     </row>
     <row r="13">
@@ -28184,10 +28282,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="14">
@@ -28199,7 +28297,7 @@
         <v>311</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="15">
@@ -28211,7 +28309,7 @@
         <v>685</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
     </row>
     <row r="16">
@@ -28223,7 +28321,7 @@
         <v>315</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="17">
@@ -28235,7 +28333,7 @@
         <v>316</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="18">
@@ -28244,10 +28342,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
     </row>
     <row r="19">
@@ -28259,7 +28357,7 @@
         <v>323</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="20">
@@ -28268,10 +28366,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="21">
@@ -28283,7 +28381,7 @@
         <v>331</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
     </row>
     <row r="22">
@@ -28292,10 +28390,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="23">
@@ -28304,10 +28402,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
     </row>
     <row r="24">
@@ -28316,10 +28414,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="25">
@@ -28331,7 +28429,7 @@
         <v>348</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
     <row r="26">
@@ -28340,10 +28438,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="27">
@@ -28352,10 +28450,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="28">
@@ -28364,10 +28462,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="29">
@@ -28376,10 +28474,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="30">
@@ -28388,10 +28486,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="31">
@@ -28400,10 +28498,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="32">
@@ -28412,10 +28510,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="33">
@@ -28424,10 +28522,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
     <row r="34">
@@ -28439,7 +28537,7 @@
         <v>364</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
     </row>
     <row r="35">
@@ -28451,7 +28549,7 @@
         <v>366</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="36">
@@ -28460,10 +28558,10 @@
         <v>34</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="37">
@@ -28472,10 +28570,10 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="38">
@@ -28487,7 +28585,7 @@
         <v>370</v>
       </c>
       <c r="C38" s="36" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
     </row>
     <row r="39">
@@ -28499,7 +28597,7 @@
         <v>371</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
     </row>
     <row r="40">
@@ -28511,7 +28609,7 @@
         <v>377</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
     </row>
     <row r="41">
@@ -28520,10 +28618,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
     </row>
     <row r="42">
@@ -28535,7 +28633,7 @@
         <v>387</v>
       </c>
       <c r="C42" s="36" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
     </row>
     <row r="43">
@@ -28547,7 +28645,7 @@
         <v>40</v>
       </c>
       <c r="C43" s="36" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="44">
@@ -28559,7 +28657,7 @@
         <v>391</v>
       </c>
       <c r="C44" s="36" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
     </row>
     <row r="45">
@@ -28568,10 +28666,10 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
     </row>
     <row r="46">
@@ -28580,10 +28678,10 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="C46" s="36" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
     </row>
     <row r="47">
@@ -28595,7 +28693,7 @@
         <v>403</v>
       </c>
       <c r="C47" s="36" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="48">
@@ -28607,7 +28705,7 @@
         <v>404</v>
       </c>
       <c r="C48" s="36" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
     </row>
     <row r="49">
@@ -28619,7 +28717,7 @@
         <v>408</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
     </row>
     <row r="50">
@@ -28631,7 +28729,7 @@
         <v>412</v>
       </c>
       <c r="C50" s="36" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="51">
@@ -28643,7 +28741,7 @@
         <v>416</v>
       </c>
       <c r="C51" s="36" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="52">
@@ -28655,7 +28753,7 @@
         <v>423</v>
       </c>
       <c r="C52" s="36" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
     </row>
     <row r="53">
@@ -28667,7 +28765,7 @@
         <v>12</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="54">
@@ -28676,10 +28774,10 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C54" s="36" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="55">
@@ -28688,10 +28786,10 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
     </row>
     <row r="56">
@@ -28700,10 +28798,10 @@
         <v>54</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C56" s="36" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="57">
@@ -28712,10 +28810,10 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
     </row>
     <row r="58">
@@ -28727,7 +28825,7 @@
         <v>21</v>
       </c>
       <c r="C58" s="36" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
     </row>
     <row r="59">
@@ -28736,10 +28834,10 @@
         <v>57</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
     </row>
     <row r="60">
@@ -28780,13 +28878,13 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="2">
@@ -28795,10 +28893,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
     </row>
     <row r="3">
@@ -28807,13 +28905,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
     </row>
     <row r="4">
@@ -28822,13 +28920,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="5">
@@ -28837,13 +28935,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
     </row>
     <row r="6">
@@ -28852,13 +28950,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
     </row>
     <row r="7">
@@ -28867,13 +28965,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
     </row>
     <row r="8">
@@ -28882,13 +28980,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
     </row>
     <row r="9">
@@ -28897,13 +28995,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
     </row>
     <row r="10">
@@ -28912,10 +29010,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
     </row>
   </sheetData>
@@ -28949,13 +29047,13 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>24</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
     </row>
     <row r="2">
@@ -28970,7 +29068,7 @@
         <v>298</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
     </row>
     <row r="3">
@@ -28985,7 +29083,7 @@
         <v>298</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
     </row>
     <row r="4">
@@ -28997,10 +29095,10 @@
         <v>716</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
     </row>
     <row r="5">
@@ -29009,13 +29107,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="6">
@@ -29027,10 +29125,10 @@
         <v>730</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
     </row>
     <row r="7">
@@ -29042,10 +29140,10 @@
         <v>732</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
     </row>
     <row r="8">
@@ -29054,13 +29152,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="9">
@@ -29072,10 +29170,10 @@
         <v>734</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
     </row>
     <row r="10">
@@ -29084,13 +29182,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
     </row>
     <row r="11">
@@ -29102,10 +29200,10 @@
         <v>735</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
     </row>
     <row r="12">
@@ -29120,7 +29218,7 @@
         <v>383</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
     </row>
     <row r="13">
@@ -29135,7 +29233,7 @@
         <v>385</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
     </row>
     <row r="14">
@@ -29144,13 +29242,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="15">
@@ -29162,10 +29260,10 @@
         <v>742</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
     </row>
     <row r="16">
@@ -29174,13 +29272,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
     </row>
     <row r="17">
@@ -29192,10 +29290,10 @@
         <v>767</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
     </row>
     <row r="18">
@@ -29210,7 +29308,7 @@
         <v>33</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
     </row>
     <row r="19">
@@ -29225,7 +29323,7 @@
         <v>304</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
     </row>
     <row r="20">
@@ -29234,13 +29332,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="C20" s="39" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
     </row>
     <row r="21">
@@ -29249,13 +29347,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="C21" s="39" t="s">
         <v>298</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
     </row>
     <row r="23">
@@ -29263,25 +29361,25 @@
         <v>44</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>430</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="H23" s="28" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
     </row>
     <row r="24">
@@ -29290,7 +29388,7 @@
         <v>0</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="C24" s="37" t="s">
         <v>436</v>
@@ -29317,7 +29415,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C25" s="37" t="s">
         <v>436</v>
@@ -29344,7 +29442,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C26" s="40" t="s">
         <v>436</v>
@@ -29356,13 +29454,13 @@
         <v>440</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="G26" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="40" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="27">
@@ -29371,7 +29469,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="C27" s="40" t="s">
         <v>436</v>
@@ -29383,13 +29481,13 @@
         <v>440</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="G27" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H27" s="40" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="28">
@@ -29398,7 +29496,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="C28" s="40" t="s">
         <v>436</v>
@@ -29416,7 +29514,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="40" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
     </row>
     <row r="29">
@@ -29425,7 +29523,7 @@
         <v>5</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>931</v>
+        <v>970</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>436</v>
@@ -29434,7 +29532,7 @@
         <v>437</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>440</v>
+        <v>971</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>672</v>
@@ -29443,7 +29541,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="40" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
     </row>
     <row r="30">
@@ -29452,7 +29550,7 @@
         <v>6</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>436</v>
@@ -29464,13 +29562,13 @@
         <v>440</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>934</v>
+        <v>672</v>
       </c>
       <c r="G30" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="40" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
     </row>
     <row r="31">
@@ -29479,7 +29577,7 @@
         <v>7</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>436</v>
@@ -29491,13 +29589,13 @@
         <v>440</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>672</v>
+        <v>937</v>
       </c>
       <c r="G31" s="54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="40" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
     </row>
     <row r="32">
@@ -29506,7 +29604,7 @@
         <v>8</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C32" s="40" t="s">
         <v>436</v>
@@ -29518,13 +29616,13 @@
         <v>440</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>938</v>
+        <v>672</v>
       </c>
       <c r="G32" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H32" s="40" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
     </row>
     <row r="33">
@@ -29533,25 +29631,25 @@
         <v>9</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>971</v>
+        <v>940</v>
       </c>
       <c r="C33" s="40" t="s">
         <v>436</v>
       </c>
       <c r="D33" s="53" t="s">
-        <v>499</v>
+        <v>437</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>799</v>
+        <v>440</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="G33" s="54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="40" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
     </row>
     <row r="34">
@@ -29560,25 +29658,25 @@
         <v>10</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>800</v>
+        <v>436</v>
       </c>
       <c r="D34" s="53" t="s">
         <v>499</v>
       </c>
       <c r="E34" s="40" t="s">
-        <v>440</v>
+        <v>799</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="G34" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="40" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
     </row>
     <row r="35">
@@ -29587,25 +29685,25 @@
         <v>11</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="C35" s="40" t="s">
-        <v>436</v>
+        <v>800</v>
       </c>
       <c r="D35" s="53" t="s">
-        <v>437</v>
+        <v>499</v>
       </c>
       <c r="E35" s="40" t="s">
         <v>440</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="G35" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H35" s="40" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
     </row>
     <row r="36">
@@ -29614,25 +29712,25 @@
         <v>12</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>800</v>
+        <v>436</v>
       </c>
       <c r="D36" s="53" t="s">
-        <v>502</v>
+        <v>437</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>978</v>
+        <v>440</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="G36" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H36" s="40" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
     </row>
     <row r="37">
@@ -29641,25 +29739,25 @@
         <v>13</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C37" s="40" t="s">
-        <v>436</v>
+        <v>800</v>
       </c>
       <c r="D37" s="53" t="s">
-        <v>437</v>
+        <v>502</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>440</v>
+        <v>984</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>672</v>
+        <v>941</v>
       </c>
       <c r="G37" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H37" s="40" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
     </row>
     <row r="38">
@@ -29668,7 +29766,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>940</v>
+        <v>986</v>
       </c>
       <c r="C38" s="40" t="s">
         <v>436</v>
@@ -29686,7 +29784,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="40" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
     </row>
     <row r="39">
@@ -29695,7 +29793,7 @@
         <v>15</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="C39" s="40" t="s">
         <v>436</v>
@@ -29710,10 +29808,10 @@
         <v>672</v>
       </c>
       <c r="G39" s="54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="40" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
     </row>
     <row r="40">
@@ -29722,7 +29820,7 @@
         <v>16</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C40" s="40" t="s">
         <v>436</v>
@@ -29740,7 +29838,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="40" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
     </row>
     <row r="41">
@@ -29749,7 +29847,7 @@
         <v>17</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>985</v>
+        <v>945</v>
       </c>
       <c r="C41" s="40" t="s">
         <v>436</v>
@@ -29761,13 +29859,13 @@
         <v>440</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>943</v>
+        <v>672</v>
       </c>
       <c r="G41" s="54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
     </row>
     <row r="42">
@@ -29776,7 +29874,7 @@
         <v>18</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="C42" s="40" t="s">
         <v>436</v>
@@ -29788,13 +29886,13 @@
         <v>440</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="G42" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H42" s="40" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
     </row>
     <row r="43">
@@ -29803,7 +29901,7 @@
         <v>19</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>436</v>
@@ -29812,16 +29910,16 @@
         <v>437</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>990</v>
+        <v>440</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="G43" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H43" s="40" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
     </row>
     <row r="44">
@@ -29830,7 +29928,7 @@
         <v>20</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>436</v>
@@ -29839,16 +29937,16 @@
         <v>437</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>440</v>
+        <v>996</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>672</v>
+        <v>946</v>
       </c>
       <c r="G44" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H44" s="40" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
     </row>
     <row r="45">
@@ -29857,7 +29955,7 @@
         <v>21</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>946</v>
+        <v>998</v>
       </c>
       <c r="C45" s="40" t="s">
         <v>436</v>
@@ -29869,13 +29967,13 @@
         <v>440</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>943</v>
+        <v>672</v>
       </c>
       <c r="G45" s="54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="40" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
     </row>
     <row r="46">
@@ -29884,7 +29982,7 @@
         <v>22</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>995</v>
+        <v>949</v>
       </c>
       <c r="C46" s="40" t="s">
         <v>436</v>
@@ -29893,16 +29991,16 @@
         <v>437</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>804</v>
+        <v>440</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G46" s="54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="40" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="47">
@@ -29911,25 +30009,25 @@
         <v>23</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="C47" s="40" t="s">
-        <v>805</v>
+        <v>436</v>
       </c>
       <c r="D47" s="53" t="s">
         <v>437</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>998</v>
+        <v>804</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="G47" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H47" s="40" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="48">
@@ -29938,25 +30036,25 @@
         <v>24</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="C48" s="40" t="s">
-        <v>436</v>
+        <v>805</v>
       </c>
       <c r="D48" s="53" t="s">
         <v>437</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>440</v>
+        <v>1004</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>672</v>
+        <v>950</v>
       </c>
       <c r="G48" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="40" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="49">
@@ -29965,7 +30063,7 @@
         <v>25</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>950</v>
+        <v>1006</v>
       </c>
       <c r="C49" s="40" t="s">
         <v>436</v>
@@ -29977,13 +30075,13 @@
         <v>440</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>947</v>
+        <v>672</v>
       </c>
       <c r="G49" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H49" s="40" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="50">
@@ -29992,7 +30090,7 @@
         <v>26</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C50" s="40" t="s">
         <v>436</v>
@@ -30004,13 +30102,13 @@
         <v>440</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>672</v>
+        <v>950</v>
       </c>
       <c r="G50" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H50" s="40" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="51">
@@ -30019,7 +30117,7 @@
         <v>27</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C51" s="40" t="s">
         <v>436</v>
@@ -30028,16 +30126,16 @@
         <v>437</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>810</v>
+        <v>440</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>953</v>
+        <v>672</v>
       </c>
       <c r="G51" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H51" s="40" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="52">
@@ -30046,7 +30144,7 @@
         <v>28</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C52" s="40" t="s">
         <v>436</v>
@@ -30055,16 +30153,16 @@
         <v>437</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>440</v>
+        <v>810</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>672</v>
+        <v>956</v>
       </c>
       <c r="G52" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="40" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="53">
@@ -30073,9 +30171,9 @@
         <v>29</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C53" s="37" t="s">
+        <v>957</v>
+      </c>
+      <c r="C53" s="40" t="s">
         <v>436</v>
       </c>
       <c r="D53" s="53" t="s">
@@ -30090,17 +30188,36 @@
       <c r="G53" s="54" t="b">
         <v>0</v>
       </c>
-      <c r="H53" s="37" t="s">
+      <c r="H53" s="40" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="36">
+        <f>ROW()-ROW(Table_Dialog_Options[N])</f>
+        <v>30</v>
+      </c>
+      <c r="B54" s="36" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C54" s="37" t="s">
+        <v>436</v>
+      </c>
+      <c r="D54" s="53" t="s">
+        <v>437</v>
+      </c>
+      <c r="E54" s="40" t="s">
+        <v>440</v>
+      </c>
+      <c r="F54" s="38" t="s">
+        <v>672</v>
+      </c>
+      <c r="G54" s="54" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="37" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="55"/>
-      <c r="B55" s="55"/>
-      <c r="C55" s="55"/>
-      <c r="D55" s="55"/>
-      <c r="E55" s="55"/>
-      <c r="F55" s="55"/>
     </row>
     <row r="56">
       <c r="A56" s="55"/>
@@ -30142,24 +30259,32 @@
       <c r="E60" s="55"/>
       <c r="F60" s="55"/>
     </row>
+    <row r="61">
+      <c r="A61" s="55"/>
+      <c r="B61" s="55"/>
+      <c r="C61" s="55"/>
+      <c r="D61" s="55"/>
+      <c r="E61" s="55"/>
+      <c r="F61" s="55"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C21 E24:E53">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C21 E24:E54">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H24:H53">
+    <dataValidation type="list" allowBlank="1" sqref="H24:H54">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F24:F53">
+    <dataValidation type="list" allowBlank="1" sqref="F24:F54">
       <formula1>Table_Dialogs[DIALOG_ID]</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C24:C53">
+    <dataValidation type="list" allowBlank="1" sqref="C24:C54">
       <formula1>#REF!</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D21">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D24:D53">
+    <dataValidation type="list" allowBlank="1" sqref="D24:D54">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -30190,10 +30315,10 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="C1" s="56" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="2">
@@ -30205,7 +30330,7 @@
         <v>671</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="3">
@@ -30217,7 +30342,7 @@
         <v>702</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="4">
@@ -30226,10 +30351,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="6">
@@ -30237,13 +30362,13 @@
         <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
     </row>
     <row r="7">
@@ -30252,7 +30377,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>673</v>
@@ -30267,10 +30392,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="D8" s="57" t="s">
         <v>440</v>
@@ -30282,10 +30407,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="D9" s="57" t="s">
         <v>675</v>
@@ -30297,10 +30422,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="D10" s="57" t="s">
         <v>677</v>
@@ -30312,7 +30437,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>673</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -11596,8 +11596,8 @@
         <f>ROW()-ROW(Table_Item_Family_Type[N])</f>
         <v>1</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>327</v>
+      <c r="B50" s="36" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="51">
@@ -11605,8 +11605,8 @@
         <f>ROW()-ROW(Table_Item_Family_Type[N])</f>
         <v>2</v>
       </c>
-      <c r="B51" s="36" t="s">
-        <v>306</v>
+      <c r="B51" s="1" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="52">

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4982" uniqueCount="1570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4982" uniqueCount="1571">
   <si>
     <t>NewItem</t>
   </si>
@@ -4563,6 +4563,9 @@
   </si>
   <si>
     <t>BACKGROUND_CITY1_SOUTH_STREET_1, BACKGROUND_CITY1_SOUTH_STREET_1_NIGHT</t>
+  </si>
+  <si>
+    <t>ITEM_GENERIC_DOOR1, ITEM_GENERIC_DOOR2</t>
   </si>
   <si>
     <t>CITY1_SOUTH_STREET_2</t>
@@ -10669,7 +10672,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="20.0"/>
+    <col customWidth="1" min="2" max="2" width="25.0"/>
     <col customWidth="1" min="3" max="3" width="45.71"/>
     <col customWidth="1" min="4" max="4" width="25.29"/>
     <col customWidth="1" min="5" max="5" width="41.71"/>
@@ -11060,7 +11063,7 @@
         <v>1479</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>325</v>
+        <v>1480</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>299</v>
@@ -11081,16 +11084,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="D13" s="34" t="s">
         <v>914</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="F13" s="35" t="s">
         <v>325</v>
@@ -11117,13 +11120,13 @@
         <v>20</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="D14" s="34" t="s">
         <v>914</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="F14" s="35" t="s">
         <v>325</v>
@@ -11147,7 +11150,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="C15" s="64" t="s">
         <v>301</v>
@@ -11210,7 +11213,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="2">
@@ -11237,7 +11240,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="5">
@@ -11246,7 +11249,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="6">
@@ -11258,7 +11261,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="8">
@@ -11266,7 +11269,7 @@
         <v>0.0</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="9">
@@ -11274,7 +11277,7 @@
         <v>1.0</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="10">
@@ -11282,7 +11285,7 @@
         <v>2.0</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="11">
@@ -11290,7 +11293,7 @@
         <v>3.0</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="12">
@@ -11298,7 +11301,7 @@
         <v>4.0</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="13">
@@ -11306,7 +11309,7 @@
         <v>5.0</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="15">
@@ -11314,7 +11317,7 @@
         <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="16">
@@ -11332,7 +11335,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="18">
@@ -11377,7 +11380,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="23">
@@ -11403,7 +11406,7 @@
         <v>44</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="27">
@@ -11448,7 +11451,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="32">
@@ -11475,7 +11478,7 @@
         <v>7</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="35">
@@ -11493,7 +11496,7 @@
         <v>9</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="37">
@@ -11555,7 +11558,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="45">
@@ -11579,7 +11582,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="49">
@@ -11632,7 +11635,7 @@
         <v>44</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="56">
@@ -11697,7 +11700,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="2">
@@ -11715,7 +11718,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="4">
@@ -11724,7 +11727,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="5">
@@ -11805,7 +11808,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="14">
@@ -11994,7 +11997,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="36">
@@ -12002,16 +12005,16 @@
         <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="C36" s="66" t="s">
         <v>290</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="E36" s="66" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="37">
@@ -12020,7 +12023,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="C37" s="38" t="s">
         <v>299</v>
@@ -12039,7 +12042,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="C38" s="38" t="s">
         <v>1057</v>
@@ -12058,7 +12061,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="C39" s="38" t="s">
         <v>1088</v>
@@ -12096,7 +12099,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>427</v>
@@ -12114,19 +12117,19 @@
         <v>44</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="C43" s="65" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="D43" s="65" t="s">
         <v>1020</v>
       </c>
       <c r="E43" s="66" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="F43" s="65" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="44">
@@ -12138,13 +12141,13 @@
         <v>670</v>
       </c>
       <c r="C44" s="44" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="D44" s="44" t="s">
         <v>673</v>
       </c>
       <c r="E44" s="48" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="F44" s="43" t="b">
         <v>0</v>
@@ -12159,13 +12162,13 @@
         <v>682</v>
       </c>
       <c r="C45" s="44" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="D45" s="44" t="s">
         <v>1164</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="F45" s="43" t="b">
         <v>0</v>
@@ -12180,13 +12183,13 @@
         <v>699</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="D46" s="44" t="s">
         <v>719</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="F46" s="43" t="b">
         <v>0</v>
@@ -12201,13 +12204,13 @@
         <v>704</v>
       </c>
       <c r="C47" s="44" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="D47" s="44" t="s">
         <v>1266</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="F47" s="43" t="b">
         <v>0</v>
@@ -12228,7 +12231,7 @@
         <v>1339</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="F48" s="43" t="b">
         <v>0</v>
@@ -12240,7 +12243,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>39</v>
@@ -12249,7 +12252,7 @@
         <v>1342</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="F49" s="43" t="b">
         <v>0</v>
@@ -12261,7 +12264,7 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>39</v>
@@ -12270,7 +12273,7 @@
         <v>1345</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="F50" s="43" t="b">
         <v>1</v>
@@ -12282,16 +12285,16 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="D51" s="44" t="s">
         <v>673</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="F51" s="43" t="b">
         <v>0</v>
@@ -12302,10 +12305,10 @@
         <v>44</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="54">
@@ -12314,7 +12317,7 @@
         <v>0</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="C54" s="51" t="s">
         <v>436</v>
@@ -12325,7 +12328,7 @@
         <v>44</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="57">
@@ -13335,16 +13338,16 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="2">
@@ -13356,7 +13359,7 @@
         <v>302</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="D2" s="68" t="s">
         <v>299</v>
@@ -13374,7 +13377,7 @@
         <v>417</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="D3" s="68" t="s">
         <v>299</v>
@@ -13389,10 +13392,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="D4" s="68" t="s">
         <v>299</v>
@@ -13430,7 +13433,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="2">
@@ -13457,7 +13460,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
   </sheetData>
@@ -13483,21 +13486,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B2" s="69">
         <v>1.0</v>
@@ -13511,7 +13514,7 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B3" s="69">
         <v>1.0</v>
@@ -13525,7 +13528,7 @@
     </row>
     <row r="4">
       <c r="A4" s="37" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B4" s="69">
         <v>3.0</v>
@@ -13539,7 +13542,7 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B5" s="69">
         <v>1.0</v>
@@ -13553,7 +13556,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B6" s="69">
         <v>3.0</v>
@@ -13567,7 +13570,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B7" s="69">
         <v>3.0</v>
@@ -13581,7 +13584,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B8" s="69">
         <v>5.0</v>
@@ -13595,7 +13598,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B9" s="69">
         <v>4.0</v>
@@ -13609,7 +13612,7 @@
     </row>
     <row r="10">
       <c r="A10" s="37" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B10" s="69">
         <v>5.0</v>
@@ -13623,7 +13626,7 @@
     </row>
     <row r="11">
       <c r="A11" s="37" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B11" s="69">
         <v>4.0</v>
@@ -13637,7 +13640,7 @@
     </row>
     <row r="12">
       <c r="A12" s="37" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B12" s="69">
         <v>1.0</v>
@@ -13651,7 +13654,7 @@
     </row>
     <row r="13">
       <c r="A13" s="37" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B13" s="69">
         <v>4.0</v>
@@ -13665,7 +13668,7 @@
     </row>
     <row r="14">
       <c r="A14" s="37" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B14" s="69">
         <v>1.0</v>
@@ -13679,7 +13682,7 @@
     </row>
     <row r="15">
       <c r="A15" s="37" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B15" s="69">
         <v>2.0</v>
@@ -13693,7 +13696,7 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B16" s="69">
         <v>3.0</v>
@@ -13707,7 +13710,7 @@
     </row>
     <row r="17">
       <c r="A17" s="37" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B17" s="69">
         <v>2.0</v>
@@ -13721,7 +13724,7 @@
     </row>
     <row r="18">
       <c r="A18" s="37" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B18" s="69">
         <v>2.0</v>
@@ -13735,7 +13738,7 @@
     </row>
     <row r="19">
       <c r="A19" s="37" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B19" s="69">
         <v>2.0</v>
@@ -13749,7 +13752,7 @@
     </row>
     <row r="20">
       <c r="A20" s="37" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B20" s="69">
         <v>2.0</v>
@@ -13763,7 +13766,7 @@
     </row>
     <row r="21">
       <c r="A21" s="37" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B21" s="69">
         <v>3.0</v>
@@ -13777,7 +13780,7 @@
     </row>
     <row r="22">
       <c r="A22" s="37" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B22" s="69">
         <v>2.0</v>
@@ -13791,7 +13794,7 @@
     </row>
     <row r="23">
       <c r="A23" s="37" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B23" s="69">
         <v>2.0</v>
@@ -13805,7 +13808,7 @@
     </row>
     <row r="24">
       <c r="A24" s="37" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B24" s="69">
         <v>2.0</v>
@@ -13819,7 +13822,7 @@
     </row>
     <row r="25">
       <c r="A25" s="37" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B25" s="69">
         <v>2.0</v>
@@ -13833,7 +13836,7 @@
     </row>
     <row r="26">
       <c r="A26" s="37" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B26" s="69">
         <v>2.0</v>
@@ -13847,7 +13850,7 @@
     </row>
     <row r="27">
       <c r="A27" s="37" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B27" s="69">
         <v>2.0</v>
@@ -13861,7 +13864,7 @@
     </row>
     <row r="28">
       <c r="A28" s="37" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B28" s="69">
         <v>2.0</v>
@@ -13875,7 +13878,7 @@
     </row>
     <row r="29">
       <c r="A29" s="37" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B29" s="69">
         <v>4.0</v>
@@ -13889,7 +13892,7 @@
     </row>
     <row r="30">
       <c r="A30" s="37" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B30" s="69">
         <v>2.0</v>
@@ -13903,7 +13906,7 @@
     </row>
     <row r="31">
       <c r="A31" s="37" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B31" s="69">
         <v>3.0</v>
@@ -13917,7 +13920,7 @@
     </row>
     <row r="32">
       <c r="A32" s="37" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B32" s="69">
         <v>2.0</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5012" uniqueCount="1579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5024" uniqueCount="1584">
   <si>
     <t>NewItem</t>
   </si>
@@ -2918,6 +2918,18 @@
     <t>SOUND_POOR_MAN_BCKG_3</t>
   </si>
   <si>
+    <t>MUSIC_PHARMACY</t>
+  </si>
+  <si>
+    <t>MUSIC_SOUTH_NEIGH</t>
+  </si>
+  <si>
+    <t>MUSIC_MANYO</t>
+  </si>
+  <si>
+    <t>SOUND_AMBIENCE_MANYO_NIGHT</t>
+  </si>
+  <si>
     <t>SOUND_LAST</t>
   </si>
   <si>
@@ -4569,6 +4581,9 @@
   </si>
   <si>
     <t>ITEM_CITY1_UMBRELLA, ITEM_GENERIC_DOOR1, ITEM_ELMANYO_OWNER, ITEM_STUFFED_DEER, ITEM_ELMANYO_OWNER_NIGHT, ITEM_ELMANYO_CROWD</t>
+  </si>
+  <si>
+    <t>MUSIC_MANYO, SOUND_AMBIENCE_MANYO_NIGHT</t>
   </si>
   <si>
     <t>HIVE1_BACKALLEY</t>
@@ -6124,7 +6139,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D10" displayName="Table_sounds" name="Table_sounds" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D14" displayName="Table_sounds" name="Table_sounds" id="12">
   <tableColumns count="4">
     <tableColumn name="N" id="1"/>
     <tableColumn name="SOUND_ID" id="2"/>
@@ -6953,13 +6968,13 @@
         <v>44</v>
       </c>
       <c r="B1" s="59" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="2">
@@ -6982,10 +6997,10 @@
         <v>305</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="4">
@@ -6994,13 +7009,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="5">
@@ -7009,13 +7024,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="6">
@@ -7024,13 +7039,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="7">
@@ -7042,10 +7057,10 @@
         <v>308</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="8">
@@ -7057,10 +7072,10 @@
         <v>329</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="9">
@@ -7072,10 +7087,10 @@
         <v>336</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="10">
@@ -7087,10 +7102,10 @@
         <v>314</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="11">
@@ -7099,13 +7114,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="12">
@@ -7114,13 +7129,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="13">
@@ -7132,10 +7147,10 @@
         <v>319</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="14">
@@ -7147,10 +7162,10 @@
         <v>326</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="15">
@@ -7159,13 +7174,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="16">
@@ -7177,10 +7192,10 @@
         <v>339</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="17">
@@ -7192,10 +7207,10 @@
         <v>344</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="18">
@@ -7207,10 +7222,10 @@
         <v>347</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="19">
@@ -7222,10 +7237,10 @@
         <v>351</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="20">
@@ -7237,10 +7252,10 @@
         <v>354</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="21">
@@ -7252,10 +7267,10 @@
         <v>357</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="22">
@@ -7267,10 +7282,10 @@
         <v>359</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="23">
@@ -7282,10 +7297,10 @@
         <v>361</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="24">
@@ -7297,10 +7312,10 @@
         <v>363</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="25">
@@ -7312,10 +7327,10 @@
         <v>365</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="26">
@@ -7327,10 +7342,10 @@
         <v>369</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="27">
@@ -7342,10 +7357,10 @@
         <v>374</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="28">
@@ -7357,10 +7372,10 @@
         <v>376</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="29">
@@ -7372,10 +7387,10 @@
         <v>380</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="30">
@@ -7384,13 +7399,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="31">
@@ -7402,10 +7417,10 @@
         <v>384</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="32">
@@ -7417,10 +7432,10 @@
         <v>386</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="33">
@@ -7429,13 +7444,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>41</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="34">
@@ -7447,10 +7462,10 @@
         <v>390</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="35">
@@ -7462,10 +7477,10 @@
         <v>394</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="36">
@@ -7477,10 +7492,10 @@
         <v>397</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="37">
@@ -7492,10 +7507,10 @@
         <v>402</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="38">
@@ -7507,10 +7522,10 @@
         <v>407</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="39">
@@ -7522,10 +7537,10 @@
         <v>411</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="40">
@@ -7537,10 +7552,10 @@
         <v>415</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="41">
@@ -7552,10 +7567,10 @@
         <v>419</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="42">
@@ -7567,10 +7582,10 @@
         <v>422</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="43">
@@ -7582,10 +7597,10 @@
         <v>11</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="44">
@@ -7597,10 +7612,10 @@
         <v>427</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="45">
@@ -7612,10 +7627,10 @@
         <v>430</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
     </row>
   </sheetData>
@@ -7649,22 +7664,22 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="G1" s="61" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="2">
@@ -7682,7 +7697,7 @@
         <v>920</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="F2" s="62"/>
       <c r="G2" s="37"/>
@@ -7702,13 +7717,13 @@
         <v>920</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="4">
@@ -7726,13 +7741,13 @@
         <v>920</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="5">
@@ -7750,13 +7765,13 @@
         <v>920</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="6">
@@ -7765,7 +7780,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="C6" s="36">
         <v>0.0</v>
@@ -7774,13 +7789,13 @@
         <v>920</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="7">
@@ -7789,7 +7804,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="C7" s="36">
         <v>0.0</v>
@@ -7798,13 +7813,13 @@
         <v>920</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="8">
@@ -7822,13 +7837,13 @@
         <v>920</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="G8" s="37" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="9">
@@ -7837,7 +7852,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="C9" s="36">
         <v>0.0</v>
@@ -7846,13 +7861,13 @@
         <v>920</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="G9" s="37" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="10">
@@ -7861,7 +7876,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="C10" s="36">
         <v>0.0</v>
@@ -7870,13 +7885,13 @@
         <v>920</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="11">
@@ -7885,7 +7900,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="C11" s="36">
         <v>1.0</v>
@@ -7894,13 +7909,13 @@
         <v>920</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="12">
@@ -7909,7 +7924,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="C12" s="36">
         <v>0.0</v>
@@ -7918,13 +7933,13 @@
         <v>920</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="13">
@@ -7933,7 +7948,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="C13" s="36">
         <v>0.0</v>
@@ -7942,13 +7957,13 @@
         <v>920</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="G13" s="37" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="14">
@@ -7957,7 +7972,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="C14" s="36">
         <v>1.0</v>
@@ -7966,13 +7981,13 @@
         <v>920</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="15">
@@ -7981,7 +7996,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="C15" s="36">
         <v>1.0</v>
@@ -7990,13 +8005,13 @@
         <v>920</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="16">
@@ -8005,7 +8020,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="C16" s="36">
         <v>1.0</v>
@@ -8014,13 +8029,13 @@
         <v>920</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="17">
@@ -8029,7 +8044,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="C17" s="36">
         <v>0.0</v>
@@ -8038,13 +8053,13 @@
         <v>920</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="18">
@@ -8053,7 +8068,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="C18" s="36">
         <v>0.0</v>
@@ -8062,13 +8077,13 @@
         <v>920</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="19">
@@ -8086,13 +8101,13 @@
         <v>920</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="G19" s="37" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="20">
@@ -8110,13 +8125,13 @@
         <v>920</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="21">
@@ -8134,13 +8149,13 @@
         <v>920</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="22">
@@ -8158,13 +8173,13 @@
         <v>920</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="23">
@@ -8182,13 +8197,13 @@
         <v>920</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="24">
@@ -8206,13 +8221,13 @@
         <v>920</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="25">
@@ -8230,13 +8245,13 @@
         <v>920</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="G25" s="37" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="26">
@@ -8254,13 +8269,13 @@
         <v>920</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="27">
@@ -8269,7 +8284,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="C27" s="36">
         <v>0.0</v>
@@ -8278,13 +8293,13 @@
         <v>920</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="28">
@@ -8293,7 +8308,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="C28" s="36">
         <v>1.0</v>
@@ -8302,13 +8317,13 @@
         <v>920</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="29">
@@ -8317,7 +8332,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C29" s="36">
         <v>0.0</v>
@@ -8326,13 +8341,13 @@
         <v>920</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="30">
@@ -8341,7 +8356,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="C30" s="36">
         <v>0.0</v>
@@ -8350,13 +8365,13 @@
         <v>920</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="31">
@@ -8365,7 +8380,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C31" s="36">
         <v>0.0</v>
@@ -8374,13 +8389,13 @@
         <v>920</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="32">
@@ -8398,13 +8413,13 @@
         <v>920</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="33">
@@ -8413,7 +8428,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="C33" s="36">
         <v>0.0</v>
@@ -8422,13 +8437,13 @@
         <v>920</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="34">
@@ -8437,7 +8452,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="C34" s="36">
         <v>1.0</v>
@@ -8446,13 +8461,13 @@
         <v>920</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="35">
@@ -8461,7 +8476,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="C35" s="36">
         <v>1.0</v>
@@ -8470,13 +8485,13 @@
         <v>920</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="36">
@@ -8494,13 +8509,13 @@
         <v>920</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="37">
@@ -8509,7 +8524,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="C37" s="36">
         <v>0.0</v>
@@ -8518,13 +8533,13 @@
         <v>920</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="38">
@@ -8533,7 +8548,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="C38" s="36">
         <v>1.0</v>
@@ -8542,13 +8557,13 @@
         <v>920</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="39">
@@ -8557,7 +8572,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="C39" s="36">
         <v>0.0</v>
@@ -8566,13 +8581,13 @@
         <v>920</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="40">
@@ -8581,7 +8596,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="C40" s="36">
         <v>1.0</v>
@@ -8590,13 +8605,13 @@
         <v>920</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="41">
@@ -8605,7 +8620,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="C41" s="36">
         <v>0.0</v>
@@ -8614,13 +8629,13 @@
         <v>920</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="42">
@@ -8629,7 +8644,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="C42" s="36">
         <v>1.0</v>
@@ -8638,13 +8653,13 @@
         <v>920</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="43">
@@ -8653,7 +8668,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="C43" s="36">
         <v>0.0</v>
@@ -8662,13 +8677,13 @@
         <v>920</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="44">
@@ -8677,7 +8692,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="C44" s="36">
         <v>1.0</v>
@@ -8686,13 +8701,13 @@
         <v>920</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="45">
@@ -8701,7 +8716,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="C45" s="36">
         <v>0.0</v>
@@ -8710,13 +8725,13 @@
         <v>920</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="46">
@@ -8725,7 +8740,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="C46" s="36">
         <v>1.0</v>
@@ -8734,13 +8749,13 @@
         <v>920</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="47">
@@ -8749,7 +8764,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="C47" s="36">
         <v>1.0</v>
@@ -8758,13 +8773,13 @@
         <v>920</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="G47" s="37" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="48">
@@ -8773,7 +8788,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="C48" s="36">
         <v>0.0</v>
@@ -8782,13 +8797,13 @@
         <v>920</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="49">
@@ -8797,7 +8812,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="C49" s="36">
         <v>1.0</v>
@@ -8806,13 +8821,13 @@
         <v>920</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="G49" s="37" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="50">
@@ -8821,7 +8836,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="C50" s="36">
         <v>0.0</v>
@@ -8830,13 +8845,13 @@
         <v>920</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="G50" s="37" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="51">
@@ -8845,7 +8860,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="C51" s="36">
         <v>0.0</v>
@@ -8854,13 +8869,13 @@
         <v>920</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="52">
@@ -8869,7 +8884,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="C52" s="36">
         <v>1.0</v>
@@ -8878,13 +8893,13 @@
         <v>920</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="53">
@@ -8893,7 +8908,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="C53" s="36">
         <v>1.0</v>
@@ -8902,13 +8917,13 @@
         <v>920</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="54">
@@ -8917,7 +8932,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="C54" s="36">
         <v>1.0</v>
@@ -8926,13 +8941,13 @@
         <v>920</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="55">
@@ -8941,7 +8956,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="C55" s="36">
         <v>0.0</v>
@@ -8950,13 +8965,13 @@
         <v>920</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="G55" s="37" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="56">
@@ -8965,7 +8980,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="C56" s="36">
         <v>0.0</v>
@@ -8974,13 +8989,13 @@
         <v>920</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="57">
@@ -8989,7 +9004,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="C57" s="36">
         <v>0.0</v>
@@ -8998,13 +9013,13 @@
         <v>920</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="58">
@@ -9013,7 +9028,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="C58" s="36">
         <v>1.0</v>
@@ -9022,13 +9037,13 @@
         <v>920</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="59">
@@ -9046,13 +9061,13 @@
         <v>920</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="60">
@@ -9061,7 +9076,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C60" s="36">
         <v>0.0</v>
@@ -9070,13 +9085,13 @@
         <v>920</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="61">
@@ -9085,7 +9100,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="C61" s="36">
         <v>0.0</v>
@@ -9094,13 +9109,13 @@
         <v>920</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="62">
@@ -9109,7 +9124,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="C62" s="36">
         <v>0.0</v>
@@ -9118,13 +9133,13 @@
         <v>920</v>
       </c>
       <c r="E62" s="44" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="63">
@@ -9142,13 +9157,13 @@
         <v>920</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="64">
@@ -9157,7 +9172,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="C64" s="36">
         <v>0.0</v>
@@ -9166,13 +9181,13 @@
         <v>927</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F64" s="37" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="G64" s="37" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="65">
@@ -9181,7 +9196,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="C65" s="36">
         <v>0.0</v>
@@ -9190,13 +9205,13 @@
         <v>928</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="66">
@@ -9205,7 +9220,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="C66" s="36">
         <v>0.0</v>
@@ -9214,13 +9229,13 @@
         <v>929</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="67">
@@ -9229,7 +9244,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="C67" s="36">
         <v>0.0</v>
@@ -9238,13 +9253,13 @@
         <v>930</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="G67" s="37" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="68">
@@ -9253,7 +9268,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C68" s="36">
         <v>0.0</v>
@@ -9262,13 +9277,13 @@
         <v>920</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="69">
@@ -9277,7 +9292,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="C69" s="36">
         <v>1.0</v>
@@ -9286,13 +9301,13 @@
         <v>920</v>
       </c>
       <c r="E69" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="70">
@@ -9301,7 +9316,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="C70" s="36">
         <v>0.0</v>
@@ -9310,13 +9325,13 @@
         <v>920</v>
       </c>
       <c r="E70" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="G70" s="37" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="71">
@@ -9325,7 +9340,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="C71" s="36">
         <v>1.0</v>
@@ -9334,13 +9349,13 @@
         <v>920</v>
       </c>
       <c r="E71" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="G71" s="37" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="72">
@@ -9349,7 +9364,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="C72" s="36">
         <v>0.0</v>
@@ -9358,13 +9373,13 @@
         <v>920</v>
       </c>
       <c r="E72" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F72" s="37" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="G72" s="37" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="73">
@@ -9373,7 +9388,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="C73" s="36">
         <v>1.0</v>
@@ -9382,13 +9397,13 @@
         <v>920</v>
       </c>
       <c r="E73" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F73" s="37" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="G73" s="37" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="74">
@@ -9397,7 +9412,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="C74" s="36">
         <v>0.0</v>
@@ -9406,13 +9421,13 @@
         <v>920</v>
       </c>
       <c r="E74" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F74" s="37" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="G74" s="37" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="75">
@@ -9421,7 +9436,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="C75" s="36">
         <v>1.0</v>
@@ -9430,13 +9445,13 @@
         <v>920</v>
       </c>
       <c r="E75" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F75" s="37" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="G75" s="37" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="76">
@@ -9445,7 +9460,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="C76" s="36">
         <v>0.0</v>
@@ -9454,13 +9469,13 @@
         <v>920</v>
       </c>
       <c r="E76" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F76" s="37" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="G76" s="37" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="77">
@@ -9469,7 +9484,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="C77" s="36">
         <v>1.0</v>
@@ -9478,13 +9493,13 @@
         <v>920</v>
       </c>
       <c r="E77" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F77" s="37" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="G77" s="37" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="78">
@@ -9493,7 +9508,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="C78" s="36">
         <v>0.0</v>
@@ -9502,13 +9517,13 @@
         <v>920</v>
       </c>
       <c r="E78" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F78" s="37" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="G78" s="37" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="79">
@@ -9517,7 +9532,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="C79" s="36">
         <v>0.0</v>
@@ -9526,13 +9541,13 @@
         <v>920</v>
       </c>
       <c r="E79" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F79" s="37" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="G79" s="37" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="80">
@@ -9541,7 +9556,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="C80" s="36">
         <v>1.0</v>
@@ -9550,13 +9565,13 @@
         <v>920</v>
       </c>
       <c r="E80" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F80" s="37" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="G80" s="37" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="81">
@@ -9565,7 +9580,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="C81" s="36">
         <v>1.0</v>
@@ -9574,13 +9589,13 @@
         <v>920</v>
       </c>
       <c r="E81" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F81" s="37" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="G81" s="37" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="82">
@@ -9589,7 +9604,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="C82" s="36">
         <v>1.0</v>
@@ -9598,13 +9613,13 @@
         <v>920</v>
       </c>
       <c r="E82" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F82" s="37" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="G82" s="37" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="83">
@@ -9613,7 +9628,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="C83" s="36">
         <v>0.0</v>
@@ -9622,13 +9637,13 @@
         <v>920</v>
       </c>
       <c r="E83" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F83" s="37" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="G83" s="37" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="84">
@@ -9637,7 +9652,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="C84" s="36">
         <v>0.0</v>
@@ -9646,13 +9661,13 @@
         <v>920</v>
       </c>
       <c r="E84" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F84" s="37" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="G84" s="37" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="85">
@@ -9661,7 +9676,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="36" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="C85" s="36">
         <v>0.0</v>
@@ -9670,13 +9685,13 @@
         <v>920</v>
       </c>
       <c r="E85" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="86">
@@ -9694,13 +9709,13 @@
         <v>920</v>
       </c>
       <c r="E86" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F86" s="37" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="G86" s="37" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="87">
@@ -9718,13 +9733,13 @@
         <v>920</v>
       </c>
       <c r="E87" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F87" s="37" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="88">
@@ -9742,13 +9757,13 @@
         <v>920</v>
       </c>
       <c r="E88" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F88" s="37" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="G88" s="37" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="89">
@@ -9766,13 +9781,13 @@
         <v>920</v>
       </c>
       <c r="E89" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F89" s="37" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="G89" s="37" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="90">
@@ -9790,13 +9805,13 @@
         <v>920</v>
       </c>
       <c r="E90" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F90" s="37" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="G90" s="37" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="91">
@@ -9814,13 +9829,13 @@
         <v>920</v>
       </c>
       <c r="E91" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F91" s="37" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
       <c r="G91" s="37" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="92">
@@ -9838,13 +9853,13 @@
         <v>920</v>
       </c>
       <c r="E92" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F92" s="37" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="G92" s="37" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="93">
@@ -9862,13 +9877,13 @@
         <v>920</v>
       </c>
       <c r="E93" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F93" s="37" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="G93" s="37" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="94">
@@ -9886,13 +9901,13 @@
         <v>920</v>
       </c>
       <c r="E94" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F94" s="37" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="G94" s="37" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="95">
@@ -9910,13 +9925,13 @@
         <v>925</v>
       </c>
       <c r="E95" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F95" s="37" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="G95" s="37" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="96">
@@ -9934,13 +9949,13 @@
         <v>920</v>
       </c>
       <c r="E96" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F96" s="37" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="G96" s="37" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="97">
@@ -9958,13 +9973,13 @@
         <v>920</v>
       </c>
       <c r="E97" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F97" s="37" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="G97" s="37" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="98">
@@ -9982,13 +9997,13 @@
         <v>920</v>
       </c>
       <c r="E98" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F98" s="37" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="G98" s="37" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="99">
@@ -10006,13 +10021,13 @@
         <v>920</v>
       </c>
       <c r="E99" s="44" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="F99" s="37" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="G99" s="37" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="100">
@@ -10030,13 +10045,13 @@
         <v>920</v>
       </c>
       <c r="E100" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F100" s="37" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="G100" s="37" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="101">
@@ -10054,13 +10069,13 @@
         <v>920</v>
       </c>
       <c r="E101" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F101" s="37" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="G101" s="37" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="102">
@@ -10078,13 +10093,13 @@
         <v>920</v>
       </c>
       <c r="E102" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F102" s="37" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="G102" s="37" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="103">
@@ -10093,7 +10108,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="36" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="C103" s="36">
         <v>0.0</v>
@@ -10102,13 +10117,13 @@
         <v>920</v>
       </c>
       <c r="E103" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F103" s="37" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="G103" s="37" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="104">
@@ -10117,7 +10132,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="C104" s="36">
         <v>1.0</v>
@@ -10126,13 +10141,13 @@
         <v>920</v>
       </c>
       <c r="E104" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F104" s="37" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="G104" s="37" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="105">
@@ -10141,7 +10156,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="C105" s="36">
         <v>0.0</v>
@@ -10150,13 +10165,13 @@
         <v>920</v>
       </c>
       <c r="E105" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F105" s="37" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="G105" s="37" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="106">
@@ -10165,7 +10180,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="C106" s="36">
         <v>1.0</v>
@@ -10174,13 +10189,13 @@
         <v>920</v>
       </c>
       <c r="E106" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F106" s="37" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="G106" s="37" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="107">
@@ -10189,7 +10204,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="C107" s="36">
         <v>0.0</v>
@@ -10198,13 +10213,13 @@
         <v>920</v>
       </c>
       <c r="E107" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F107" s="37" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="G107" s="37" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="108">
@@ -10213,7 +10228,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="C108" s="36">
         <v>1.0</v>
@@ -10222,13 +10237,13 @@
         <v>920</v>
       </c>
       <c r="E108" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F108" s="37" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="G108" s="37" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="109">
@@ -10237,7 +10252,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="C109" s="36">
         <v>0.0</v>
@@ -10246,13 +10261,13 @@
         <v>920</v>
       </c>
       <c r="E109" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F109" s="37" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="G109" s="37" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="110">
@@ -10261,7 +10276,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="C110" s="36">
         <v>1.0</v>
@@ -10270,13 +10285,13 @@
         <v>920</v>
       </c>
       <c r="E110" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F110" s="37" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="G110" s="37" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="111">
@@ -10285,7 +10300,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="C111" s="36">
         <v>0.0</v>
@@ -10294,13 +10309,13 @@
         <v>920</v>
       </c>
       <c r="E111" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F111" s="37" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="G111" s="37" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="112">
@@ -10309,7 +10324,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="36" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="C112" s="36">
         <v>1.0</v>
@@ -10318,13 +10333,13 @@
         <v>920</v>
       </c>
       <c r="E112" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F112" s="37" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="G112" s="37" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="113">
@@ -10333,7 +10348,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="C113" s="36">
         <v>0.0</v>
@@ -10342,13 +10357,13 @@
         <v>920</v>
       </c>
       <c r="E113" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F113" s="37" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="G113" s="37" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="114">
@@ -10357,7 +10372,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="C114" s="36">
         <v>0.0</v>
@@ -10366,13 +10381,13 @@
         <v>920</v>
       </c>
       <c r="E114" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F114" s="37" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="G114" s="37" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="115">
@@ -10381,7 +10396,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="C115" s="36">
         <v>0.0</v>
@@ -10390,13 +10405,13 @@
         <v>920</v>
       </c>
       <c r="E115" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F115" s="37" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="G115" s="37" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="116">
@@ -10405,7 +10420,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="36" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="C116" s="36">
         <v>1.0</v>
@@ -10414,13 +10429,13 @@
         <v>920</v>
       </c>
       <c r="E116" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F116" s="37" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="G116" s="37" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="117">
@@ -10438,13 +10453,13 @@
         <v>920</v>
       </c>
       <c r="E117" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F117" s="37" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="G117" s="37" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="118">
@@ -10462,13 +10477,13 @@
         <v>923</v>
       </c>
       <c r="E118" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F118" s="37" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="G118" s="37" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="119">
@@ -10486,13 +10501,13 @@
         <v>920</v>
       </c>
       <c r="E119" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F119" s="37" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="G119" s="37" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="120">
@@ -10510,10 +10525,10 @@
         <v>920</v>
       </c>
       <c r="E120" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F120" s="37" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="G120" s="37" t="s">
         <v>14</v>
@@ -10525,7 +10540,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="C121" s="36">
         <v>0.0</v>
@@ -10534,10 +10549,10 @@
         <v>920</v>
       </c>
       <c r="E121" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F121" s="37" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="G121" s="37" t="s">
         <v>32</v>
@@ -10549,7 +10564,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="36" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="C122" s="36">
         <v>0.0</v>
@@ -10558,13 +10573,13 @@
         <v>920</v>
       </c>
       <c r="E122" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F122" s="37" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="G122" s="37" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="123">
@@ -10573,7 +10588,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="C123" s="36">
         <v>0.0</v>
@@ -10582,13 +10597,13 @@
         <v>920</v>
       </c>
       <c r="E123" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F123" s="37" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="G123" s="37" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="124">
@@ -10597,7 +10612,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="36" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="C124" s="36">
         <v>0.0</v>
@@ -10606,13 +10621,13 @@
         <v>920</v>
       </c>
       <c r="E124" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F124" s="37" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="G124" s="37" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="125">
@@ -10630,13 +10645,13 @@
         <v>920</v>
       </c>
       <c r="E125" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F125" s="37" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="G125" s="37" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="126">
@@ -10654,13 +10669,13 @@
         <v>920</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F126" s="37" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="G126" s="37" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="127">
@@ -10669,7 +10684,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="36" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="C127" s="36">
         <v>0.0</v>
@@ -10678,13 +10693,13 @@
         <v>920</v>
       </c>
       <c r="E127" s="44" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F127" s="37" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="G127" s="37" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
     </row>
   </sheetData>
@@ -10727,31 +10742,31 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="J1" s="28" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="2" ht="186.0" customHeight="1">
@@ -10760,7 +10775,7 @@
         <v>-1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="C2" s="64" t="s">
         <v>301</v>
@@ -10793,7 +10808,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="C3" s="64" t="s">
         <v>847</v>
@@ -10802,10 +10817,10 @@
         <v>922</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>299</v>
@@ -10826,19 +10841,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="D4" s="34" t="s">
         <v>922</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>299</v>
@@ -10859,19 +10874,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="D5" s="34" t="s">
         <v>922</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>299</v>
@@ -10892,19 +10907,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>922</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>299</v>
@@ -10925,19 +10940,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="D7" s="34" t="s">
         <v>920</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>299</v>
@@ -10958,19 +10973,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="D8" s="34" t="s">
         <v>920</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>299</v>
@@ -10997,19 +11012,19 @@
         <v>880</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="E9" s="35" t="s">
         <v>880</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="I9" s="35" t="s">
         <v>303</v>
@@ -11024,25 +11039,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>920</v>
+        <v>933</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>920</v>
+        <v>1486</v>
       </c>
       <c r="I10" s="35" t="s">
         <v>507</v>
@@ -11057,19 +11072,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1482</v>
+        <v>1487</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1483</v>
+        <v>1488</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>920</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1483</v>
+        <v>1488</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>1484</v>
+        <v>1489</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>299</v>
@@ -11090,25 +11105,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1485</v>
+        <v>1490</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1486</v>
+        <v>1491</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>920</v>
+        <v>932</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>1486</v>
+        <v>1491</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>1487</v>
+        <v>1492</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>920</v>
+        <v>932</v>
       </c>
       <c r="I12" s="35" t="s">
         <v>303</v>
@@ -11123,25 +11138,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>1488</v>
+        <v>1493</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1489</v>
+        <v>1494</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>920</v>
+        <v>932</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>1489</v>
+        <v>1494</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>1490</v>
+        <v>1495</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>920</v>
+        <v>932</v>
       </c>
       <c r="I13" s="35" t="s">
         <v>303</v>
@@ -11159,13 +11174,13 @@
         <v>20</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>1491</v>
+        <v>1496</v>
       </c>
       <c r="D14" s="34" t="s">
         <v>920</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>1491</v>
+        <v>1496</v>
       </c>
       <c r="F14" s="35" t="s">
         <v>325</v>
@@ -11189,7 +11204,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1492</v>
+        <v>1497</v>
       </c>
       <c r="C15" s="64" t="s">
         <v>301</v>
@@ -11252,7 +11267,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1493</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="2">
@@ -11279,7 +11294,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1494</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="5">
@@ -11288,7 +11303,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1495</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6">
@@ -11300,7 +11315,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1496</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="8">
@@ -11308,7 +11323,7 @@
         <v>0.0</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1497</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="9">
@@ -11316,7 +11331,7 @@
         <v>1.0</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1498</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="10">
@@ -11324,7 +11339,7 @@
         <v>2.0</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1499</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="11">
@@ -11332,7 +11347,7 @@
         <v>3.0</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1500</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="12">
@@ -11340,7 +11355,7 @@
         <v>4.0</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1501</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="13">
@@ -11348,7 +11363,7 @@
         <v>5.0</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1502</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="15">
@@ -11356,7 +11371,7 @@
         <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1503</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="16">
@@ -11374,7 +11389,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1504</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="18">
@@ -11419,7 +11434,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1505</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="23">
@@ -11445,7 +11460,7 @@
         <v>44</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1506</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="27">
@@ -11490,7 +11505,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1507</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="32">
@@ -11517,7 +11532,7 @@
         <v>7</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1508</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="35">
@@ -11535,7 +11550,7 @@
         <v>9</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1509</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="37">
@@ -11597,7 +11612,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1510</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="45">
@@ -11605,7 +11620,7 @@
         <v>0.0</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="46">
@@ -11613,7 +11628,7 @@
         <v>1.0</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="48">
@@ -11621,7 +11636,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1511</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="49">
@@ -11674,7 +11689,7 @@
         <v>44</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1512</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="56">
@@ -11739,7 +11754,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1513</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="2">
@@ -11757,7 +11772,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1514</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="4">
@@ -11766,7 +11781,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="5">
@@ -11847,7 +11862,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1516</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="14">
@@ -12036,7 +12051,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1517</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="36">
@@ -12044,16 +12059,16 @@
         <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1518</v>
+        <v>1523</v>
       </c>
       <c r="C36" s="66" t="s">
         <v>290</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>1519</v>
+        <v>1524</v>
       </c>
       <c r="E36" s="66" t="s">
-        <v>1520</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="37">
@@ -12062,7 +12077,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1521</v>
+        <v>1526</v>
       </c>
       <c r="C37" s="38" t="s">
         <v>299</v>
@@ -12081,10 +12096,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1522</v>
+        <v>1527</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="D38" s="38" t="s">
         <v>863</v>
@@ -12100,10 +12115,10 @@
         <v>2</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1523</v>
+        <v>1528</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="D39" s="38" t="s">
         <v>891</v>
@@ -12122,7 +12137,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="D40" s="38" t="s">
         <v>40</v>
@@ -12138,7 +12153,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1524</v>
+        <v>1529</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>430</v>
@@ -12156,19 +12171,19 @@
         <v>44</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1525</v>
+        <v>1530</v>
       </c>
       <c r="C43" s="65" t="s">
-        <v>1526</v>
+        <v>1531</v>
       </c>
       <c r="D43" s="65" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="E43" s="66" t="s">
-        <v>1527</v>
+        <v>1532</v>
       </c>
       <c r="F43" s="65" t="s">
-        <v>1528</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="44">
@@ -12180,13 +12195,13 @@
         <v>675</v>
       </c>
       <c r="C44" s="44" t="s">
-        <v>1521</v>
+        <v>1526</v>
       </c>
       <c r="D44" s="44" t="s">
         <v>678</v>
       </c>
       <c r="E44" s="48" t="s">
-        <v>1529</v>
+        <v>1534</v>
       </c>
       <c r="F44" s="43" t="b">
         <v>0</v>
@@ -12201,13 +12216,13 @@
         <v>687</v>
       </c>
       <c r="C45" s="44" t="s">
-        <v>1522</v>
+        <v>1527</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>1529</v>
+        <v>1534</v>
       </c>
       <c r="F45" s="43" t="b">
         <v>0</v>
@@ -12222,13 +12237,13 @@
         <v>704</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>1522</v>
+        <v>1527</v>
       </c>
       <c r="D46" s="44" t="s">
         <v>724</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>1529</v>
+        <v>1534</v>
       </c>
       <c r="F46" s="43" t="b">
         <v>0</v>
@@ -12243,13 +12258,13 @@
         <v>709</v>
       </c>
       <c r="C47" s="44" t="s">
-        <v>1523</v>
+        <v>1528</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>1529</v>
+        <v>1534</v>
       </c>
       <c r="F47" s="43" t="b">
         <v>0</v>
@@ -12267,10 +12282,10 @@
         <v>39</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>1529</v>
+        <v>1534</v>
       </c>
       <c r="F48" s="43" t="b">
         <v>0</v>
@@ -12282,16 +12297,16 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1530</v>
+        <v>1535</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>39</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>1529</v>
+        <v>1534</v>
       </c>
       <c r="F49" s="43" t="b">
         <v>0</v>
@@ -12303,16 +12318,16 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1531</v>
+        <v>1536</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>39</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>1529</v>
+        <v>1534</v>
       </c>
       <c r="F50" s="43" t="b">
         <v>1</v>
@@ -12324,16 +12339,16 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1532</v>
+        <v>1537</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>1524</v>
+        <v>1529</v>
       </c>
       <c r="D51" s="44" t="s">
         <v>678</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>1529</v>
+        <v>1534</v>
       </c>
       <c r="F51" s="43" t="b">
         <v>0</v>
@@ -12344,10 +12359,10 @@
         <v>44</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1533</v>
+        <v>1538</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>1534</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="54">
@@ -12356,7 +12371,7 @@
         <v>0</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1529</v>
+        <v>1534</v>
       </c>
       <c r="C54" s="51" t="s">
         <v>439</v>
@@ -12367,7 +12382,7 @@
         <v>44</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1535</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="57">
@@ -13377,16 +13392,16 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1536</v>
+        <v>1541</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1537</v>
+        <v>1542</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1538</v>
+        <v>1543</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1539</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="2">
@@ -13398,7 +13413,7 @@
         <v>302</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="D2" s="68" t="s">
         <v>299</v>
@@ -13416,7 +13431,7 @@
         <v>417</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="D3" s="68" t="s">
         <v>299</v>
@@ -13431,10 +13446,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1542</v>
+        <v>1547</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="D4" s="68" t="s">
         <v>299</v>
@@ -13472,7 +13487,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1496</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2">
@@ -13499,7 +13514,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1543</v>
+        <v>1548</v>
       </c>
     </row>
   </sheetData>
@@ -13525,21 +13540,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1544</v>
+        <v>1549</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1545</v>
+        <v>1550</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1546</v>
+        <v>1551</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1547</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="s">
-        <v>1548</v>
+        <v>1553</v>
       </c>
       <c r="B2" s="69">
         <v>1.0</v>
@@ -13553,7 +13568,7 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>1549</v>
+        <v>1554</v>
       </c>
       <c r="B3" s="69">
         <v>1.0</v>
@@ -13567,7 +13582,7 @@
     </row>
     <row r="4">
       <c r="A4" s="37" t="s">
-        <v>1550</v>
+        <v>1555</v>
       </c>
       <c r="B4" s="69">
         <v>3.0</v>
@@ -13581,7 +13596,7 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>1551</v>
+        <v>1556</v>
       </c>
       <c r="B5" s="69">
         <v>1.0</v>
@@ -13595,7 +13610,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>1552</v>
+        <v>1557</v>
       </c>
       <c r="B6" s="69">
         <v>3.0</v>
@@ -13609,7 +13624,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>1553</v>
+        <v>1558</v>
       </c>
       <c r="B7" s="69">
         <v>3.0</v>
@@ -13623,7 +13638,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>1554</v>
+        <v>1559</v>
       </c>
       <c r="B8" s="69">
         <v>5.0</v>
@@ -13637,7 +13652,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>1555</v>
+        <v>1560</v>
       </c>
       <c r="B9" s="69">
         <v>4.0</v>
@@ -13651,7 +13666,7 @@
     </row>
     <row r="10">
       <c r="A10" s="37" t="s">
-        <v>1556</v>
+        <v>1561</v>
       </c>
       <c r="B10" s="69">
         <v>5.0</v>
@@ -13665,7 +13680,7 @@
     </row>
     <row r="11">
       <c r="A11" s="37" t="s">
-        <v>1557</v>
+        <v>1562</v>
       </c>
       <c r="B11" s="69">
         <v>4.0</v>
@@ -13679,7 +13694,7 @@
     </row>
     <row r="12">
       <c r="A12" s="37" t="s">
-        <v>1558</v>
+        <v>1563</v>
       </c>
       <c r="B12" s="69">
         <v>1.0</v>
@@ -13693,7 +13708,7 @@
     </row>
     <row r="13">
       <c r="A13" s="37" t="s">
-        <v>1559</v>
+        <v>1564</v>
       </c>
       <c r="B13" s="69">
         <v>4.0</v>
@@ -13707,7 +13722,7 @@
     </row>
     <row r="14">
       <c r="A14" s="37" t="s">
-        <v>1560</v>
+        <v>1565</v>
       </c>
       <c r="B14" s="69">
         <v>1.0</v>
@@ -13721,7 +13736,7 @@
     </row>
     <row r="15">
       <c r="A15" s="37" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="B15" s="69">
         <v>2.0</v>
@@ -13735,7 +13750,7 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="B16" s="69">
         <v>3.0</v>
@@ -13749,7 +13764,7 @@
     </row>
     <row r="17">
       <c r="A17" s="37" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="B17" s="69">
         <v>2.0</v>
@@ -13763,7 +13778,7 @@
     </row>
     <row r="18">
       <c r="A18" s="37" t="s">
-        <v>1564</v>
+        <v>1569</v>
       </c>
       <c r="B18" s="69">
         <v>2.0</v>
@@ -13777,7 +13792,7 @@
     </row>
     <row r="19">
       <c r="A19" s="37" t="s">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="B19" s="69">
         <v>2.0</v>
@@ -13791,7 +13806,7 @@
     </row>
     <row r="20">
       <c r="A20" s="37" t="s">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="B20" s="69">
         <v>2.0</v>
@@ -13805,7 +13820,7 @@
     </row>
     <row r="21">
       <c r="A21" s="37" t="s">
-        <v>1567</v>
+        <v>1572</v>
       </c>
       <c r="B21" s="69">
         <v>3.0</v>
@@ -13819,7 +13834,7 @@
     </row>
     <row r="22">
       <c r="A22" s="37" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="B22" s="69">
         <v>2.0</v>
@@ -13833,7 +13848,7 @@
     </row>
     <row r="23">
       <c r="A23" s="37" t="s">
-        <v>1569</v>
+        <v>1574</v>
       </c>
       <c r="B23" s="69">
         <v>2.0</v>
@@ -13847,7 +13862,7 @@
     </row>
     <row r="24">
       <c r="A24" s="37" t="s">
-        <v>1570</v>
+        <v>1575</v>
       </c>
       <c r="B24" s="69">
         <v>2.0</v>
@@ -13861,7 +13876,7 @@
     </row>
     <row r="25">
       <c r="A25" s="37" t="s">
-        <v>1571</v>
+        <v>1576</v>
       </c>
       <c r="B25" s="69">
         <v>2.0</v>
@@ -13875,7 +13890,7 @@
     </row>
     <row r="26">
       <c r="A26" s="37" t="s">
-        <v>1572</v>
+        <v>1577</v>
       </c>
       <c r="B26" s="69">
         <v>2.0</v>
@@ -13889,7 +13904,7 @@
     </row>
     <row r="27">
       <c r="A27" s="37" t="s">
-        <v>1573</v>
+        <v>1578</v>
       </c>
       <c r="B27" s="69">
         <v>2.0</v>
@@ -13903,7 +13918,7 @@
     </row>
     <row r="28">
       <c r="A28" s="37" t="s">
-        <v>1574</v>
+        <v>1579</v>
       </c>
       <c r="B28" s="69">
         <v>2.0</v>
@@ -13917,7 +13932,7 @@
     </row>
     <row r="29">
       <c r="A29" s="37" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="B29" s="69">
         <v>4.0</v>
@@ -13931,7 +13946,7 @@
     </row>
     <row r="30">
       <c r="A30" s="37" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="B30" s="69">
         <v>2.0</v>
@@ -13945,7 +13960,7 @@
     </row>
     <row r="31">
       <c r="A31" s="37" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="B31" s="69">
         <v>3.0</v>
@@ -13959,7 +13974,7 @@
     </row>
     <row r="32">
       <c r="A32" s="37" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="B32" s="69">
         <v>2.0</v>
@@ -13973,7 +13988,7 @@
     </row>
     <row r="33">
       <c r="A33" s="37" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="B33" s="69">
         <v>5.0</v>
@@ -18129,7 +18144,7 @@
         <v>67</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="J37" s="13" t="s">
         <v>67</v>
@@ -18150,7 +18165,7 @@
         <v>67</v>
       </c>
       <c r="P37" s="13" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38">
@@ -18199,7 +18214,7 @@
         <v>67</v>
       </c>
       <c r="P38" s="13" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39">
@@ -29174,6 +29189,66 @@
       <c r="C10" s="36" t="s">
         <v>921</v>
       </c>
+      <c r="D10" s="36" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>9</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>932</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>921</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>10</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>933</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>921</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>11</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>934</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>921</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>12</v>
+      </c>
+      <c r="B14" s="36" t="s">
+        <v>935</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>921</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -29206,13 +29281,13 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>24</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
     </row>
     <row r="2">
@@ -29227,7 +29302,7 @@
         <v>298</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
     </row>
     <row r="3">
@@ -29242,7 +29317,7 @@
         <v>298</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
     </row>
     <row r="4">
@@ -29254,10 +29329,10 @@
         <v>721</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
     </row>
     <row r="5">
@@ -29266,13 +29341,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
     </row>
     <row r="6">
@@ -29284,10 +29359,10 @@
         <v>735</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7">
@@ -29299,10 +29374,10 @@
         <v>737</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
     </row>
     <row r="8">
@@ -29311,13 +29386,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
     </row>
     <row r="9">
@@ -29329,10 +29404,10 @@
         <v>739</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
     </row>
     <row r="10">
@@ -29341,13 +29416,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
     </row>
     <row r="11">
@@ -29359,10 +29434,10 @@
         <v>740</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
     </row>
     <row r="12">
@@ -29377,7 +29452,7 @@
         <v>383</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="13">
@@ -29392,7 +29467,7 @@
         <v>385</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
     </row>
     <row r="14">
@@ -29401,13 +29476,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
     </row>
     <row r="15">
@@ -29419,10 +29494,10 @@
         <v>747</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
     </row>
     <row r="16">
@@ -29431,13 +29506,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
     </row>
     <row r="17">
@@ -29449,10 +29524,10 @@
         <v>772</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
     </row>
     <row r="18">
@@ -29467,7 +29542,7 @@
         <v>33</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="19">
@@ -29482,7 +29557,7 @@
         <v>304</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
     </row>
     <row r="20">
@@ -29491,13 +29566,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="C20" s="39" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
     </row>
     <row r="21">
@@ -29506,13 +29581,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="C21" s="39" t="s">
         <v>298</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
     </row>
     <row r="23">
@@ -29520,25 +29595,25 @@
         <v>44</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>433</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="H23" s="28" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
     <row r="24">
@@ -29547,7 +29622,7 @@
         <v>0</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="C24" s="37" t="s">
         <v>439</v>
@@ -29574,7 +29649,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="C25" s="37" t="s">
         <v>439</v>
@@ -29601,7 +29676,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="C26" s="40" t="s">
         <v>439</v>
@@ -29613,13 +29688,13 @@
         <v>443</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="G26" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="40" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
     </row>
     <row r="27">
@@ -29628,7 +29703,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="C27" s="40" t="s">
         <v>439</v>
@@ -29640,13 +29715,13 @@
         <v>443</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="G27" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H27" s="40" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
     </row>
     <row r="28">
@@ -29655,7 +29730,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="C28" s="40" t="s">
         <v>439</v>
@@ -29673,7 +29748,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="40" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
     </row>
     <row r="29">
@@ -29682,7 +29757,7 @@
         <v>5</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>439</v>
@@ -29691,7 +29766,7 @@
         <v>440</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>677</v>
@@ -29700,7 +29775,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="40" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
     </row>
     <row r="30">
@@ -29709,7 +29784,7 @@
         <v>6</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>439</v>
@@ -29727,7 +29802,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="40" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
     </row>
     <row r="31">
@@ -29736,7 +29811,7 @@
         <v>7</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>439</v>
@@ -29748,13 +29823,13 @@
         <v>443</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="G31" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H31" s="40" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
     </row>
     <row r="32">
@@ -29763,7 +29838,7 @@
         <v>8</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="C32" s="40" t="s">
         <v>439</v>
@@ -29781,7 +29856,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="40" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
     </row>
     <row r="33">
@@ -29790,7 +29865,7 @@
         <v>9</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="C33" s="40" t="s">
         <v>439</v>
@@ -29802,13 +29877,13 @@
         <v>443</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="G33" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H33" s="40" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
     </row>
     <row r="34">
@@ -29817,7 +29892,7 @@
         <v>10</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="C34" s="40" t="s">
         <v>439</v>
@@ -29829,13 +29904,13 @@
         <v>804</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="G34" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="40" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
     </row>
     <row r="35">
@@ -29844,7 +29919,7 @@
         <v>11</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="C35" s="40" t="s">
         <v>805</v>
@@ -29856,13 +29931,13 @@
         <v>443</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="G35" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H35" s="40" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
     </row>
     <row r="36">
@@ -29871,7 +29946,7 @@
         <v>12</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="C36" s="40" t="s">
         <v>439</v>
@@ -29883,13 +29958,13 @@
         <v>443</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="G36" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H36" s="40" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
     </row>
     <row r="37">
@@ -29898,7 +29973,7 @@
         <v>13</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="C37" s="40" t="s">
         <v>805</v>
@@ -29907,16 +29982,16 @@
         <v>505</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="G37" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H37" s="40" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="38">
@@ -29925,7 +30000,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="C38" s="40" t="s">
         <v>439</v>
@@ -29943,7 +30018,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="40" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
     </row>
     <row r="39">
@@ -29952,7 +30027,7 @@
         <v>15</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="C39" s="40" t="s">
         <v>439</v>
@@ -29970,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="40" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
     </row>
     <row r="40">
@@ -29979,7 +30054,7 @@
         <v>16</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="C40" s="40" t="s">
         <v>439</v>
@@ -29997,7 +30072,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="40" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
     </row>
     <row r="41">
@@ -30006,7 +30081,7 @@
         <v>17</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="C41" s="40" t="s">
         <v>439</v>
@@ -30024,7 +30099,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="42">
@@ -30033,7 +30108,7 @@
         <v>18</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="C42" s="40" t="s">
         <v>439</v>
@@ -30045,13 +30120,13 @@
         <v>443</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="G42" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H42" s="40" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="43">
@@ -30060,7 +30135,7 @@
         <v>19</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>439</v>
@@ -30072,13 +30147,13 @@
         <v>443</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="G43" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H43" s="40" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="44">
@@ -30087,7 +30162,7 @@
         <v>20</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>439</v>
@@ -30096,16 +30171,16 @@
         <v>440</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="G44" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H44" s="40" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="45">
@@ -30114,7 +30189,7 @@
         <v>21</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="C45" s="40" t="s">
         <v>439</v>
@@ -30132,7 +30207,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="40" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="46">
@@ -30141,7 +30216,7 @@
         <v>22</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="C46" s="40" t="s">
         <v>439</v>
@@ -30153,13 +30228,13 @@
         <v>443</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="G46" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H46" s="40" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="47">
@@ -30168,7 +30243,7 @@
         <v>23</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="C47" s="40" t="s">
         <v>439</v>
@@ -30180,13 +30255,13 @@
         <v>809</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="G47" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H47" s="40" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="48">
@@ -30195,7 +30270,7 @@
         <v>24</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="C48" s="40" t="s">
         <v>810</v>
@@ -30204,16 +30279,16 @@
         <v>440</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="G48" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="40" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="49">
@@ -30222,7 +30297,7 @@
         <v>25</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="C49" s="40" t="s">
         <v>439</v>
@@ -30240,7 +30315,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="40" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="50">
@@ -30249,7 +30324,7 @@
         <v>26</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="C50" s="40" t="s">
         <v>439</v>
@@ -30261,13 +30336,13 @@
         <v>443</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="G50" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H50" s="40" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="51">
@@ -30276,7 +30351,7 @@
         <v>27</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="C51" s="40" t="s">
         <v>439</v>
@@ -30294,7 +30369,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="40" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="52">
@@ -30303,7 +30378,7 @@
         <v>28</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="C52" s="40" t="s">
         <v>439</v>
@@ -30315,13 +30390,13 @@
         <v>815</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="G52" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="40" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="53">
@@ -30330,7 +30405,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="C53" s="40" t="s">
         <v>439</v>
@@ -30348,7 +30423,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="40" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="54">
@@ -30357,7 +30432,7 @@
         <v>30</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="C54" s="37" t="s">
         <v>439</v>
@@ -30474,10 +30549,10 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="C1" s="56" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="2">
@@ -30489,7 +30564,7 @@
         <v>676</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="3">
@@ -30501,7 +30576,7 @@
         <v>707</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="4">
@@ -30510,10 +30585,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="6">
@@ -30521,13 +30596,13 @@
         <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
     </row>
     <row r="7">
@@ -30536,7 +30611,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>678</v>
@@ -30551,10 +30626,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D8" s="57" t="s">
         <v>443</v>
@@ -30566,10 +30641,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="D9" s="57" t="s">
         <v>680</v>
@@ -30581,10 +30656,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D10" s="57" t="s">
         <v>682</v>
@@ -30596,7 +30671,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>678</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5024" uniqueCount="1584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5033" uniqueCount="1588">
   <si>
     <t>NewItem</t>
   </si>
@@ -2930,6 +2930,15 @@
     <t>SOUND_AMBIENCE_MANYO_NIGHT</t>
   </si>
   <si>
+    <t>SOUND_AMBIENCE_CITY_DAY</t>
+  </si>
+  <si>
+    <t>SOUND_AMBIENCE_CITY_NIGHT</t>
+  </si>
+  <si>
+    <t>MUSIC_INN</t>
+  </si>
+  <si>
     <t>SOUND_LAST</t>
   </si>
   <si>
@@ -4557,6 +4566,9 @@
   </si>
   <si>
     <t>BACKGROUND_CITY1_STREET1, BACKGROUND_CITY1_STREET1_N</t>
+  </si>
+  <si>
+    <t>SOUND_AMBIENCE_CITY_DAY, SOUND_AMBIENCE_CITY_NIGHT</t>
   </si>
   <si>
     <t>ITEM_GENERIC_DOOR1, ITEM_STREET1_STH_DOOR, ITEM_STREET1_CENTER_DOOR</t>
@@ -4960,7 +4972,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -5150,6 +5162,9 @@
     </xf>
     <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -6139,7 +6154,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D14" displayName="Table_sounds" name="Table_sounds" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D17" displayName="Table_sounds" name="Table_sounds" id="12">
   <tableColumns count="4">
     <tableColumn name="N" id="1"/>
     <tableColumn name="SOUND_ID" id="2"/>
@@ -6968,13 +6983,13 @@
         <v>44</v>
       </c>
       <c r="B1" s="59" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="2">
@@ -6997,10 +7012,10 @@
         <v>305</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="4">
@@ -7009,13 +7024,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="5">
@@ -7024,13 +7039,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="6">
@@ -7039,13 +7054,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="7">
@@ -7057,10 +7072,10 @@
         <v>308</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="8">
@@ -7072,10 +7087,10 @@
         <v>329</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="9">
@@ -7087,10 +7102,10 @@
         <v>336</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="10">
@@ -7102,10 +7117,10 @@
         <v>314</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="11">
@@ -7114,13 +7129,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="12">
@@ -7129,13 +7144,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="13">
@@ -7147,10 +7162,10 @@
         <v>319</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="14">
@@ -7162,10 +7177,10 @@
         <v>326</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="15">
@@ -7174,13 +7189,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="16">
@@ -7192,10 +7207,10 @@
         <v>339</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="17">
@@ -7207,10 +7222,10 @@
         <v>344</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="18">
@@ -7222,10 +7237,10 @@
         <v>347</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="19">
@@ -7237,10 +7252,10 @@
         <v>351</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="20">
@@ -7252,10 +7267,10 @@
         <v>354</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="21">
@@ -7267,10 +7282,10 @@
         <v>357</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="22">
@@ -7282,10 +7297,10 @@
         <v>359</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="23">
@@ -7297,10 +7312,10 @@
         <v>361</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="24">
@@ -7312,10 +7327,10 @@
         <v>363</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="25">
@@ -7327,10 +7342,10 @@
         <v>365</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="26">
@@ -7342,10 +7357,10 @@
         <v>369</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="27">
@@ -7357,10 +7372,10 @@
         <v>374</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="28">
@@ -7372,10 +7387,10 @@
         <v>376</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="29">
@@ -7387,10 +7402,10 @@
         <v>380</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="30">
@@ -7399,13 +7414,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="31">
@@ -7417,10 +7432,10 @@
         <v>384</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="32">
@@ -7432,10 +7447,10 @@
         <v>386</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="33">
@@ -7444,13 +7459,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>41</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="34">
@@ -7462,10 +7477,10 @@
         <v>390</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="35">
@@ -7477,10 +7492,10 @@
         <v>394</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="36">
@@ -7492,10 +7507,10 @@
         <v>397</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="37">
@@ -7507,10 +7522,10 @@
         <v>402</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="38">
@@ -7522,10 +7537,10 @@
         <v>407</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="39">
@@ -7537,10 +7552,10 @@
         <v>411</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="40">
@@ -7552,10 +7567,10 @@
         <v>415</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="41">
@@ -7567,10 +7582,10 @@
         <v>419</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="42">
@@ -7582,10 +7597,10 @@
         <v>422</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="43">
@@ -7597,10 +7612,10 @@
         <v>11</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="44">
@@ -7612,10 +7627,10 @@
         <v>427</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="45">
@@ -7627,10 +7642,10 @@
         <v>430</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
     </row>
   </sheetData>
@@ -7664,22 +7679,22 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="G1" s="61" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="2">
@@ -7697,7 +7712,7 @@
         <v>920</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="F2" s="62"/>
       <c r="G2" s="37"/>
@@ -7717,13 +7732,13 @@
         <v>920</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="4">
@@ -7741,13 +7756,13 @@
         <v>920</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="5">
@@ -7765,13 +7780,13 @@
         <v>920</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="6">
@@ -7780,7 +7795,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="C6" s="36">
         <v>0.0</v>
@@ -7789,13 +7804,13 @@
         <v>920</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="7">
@@ -7804,7 +7819,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="C7" s="36">
         <v>0.0</v>
@@ -7813,13 +7828,13 @@
         <v>920</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="8">
@@ -7837,13 +7852,13 @@
         <v>920</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="G8" s="37" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="9">
@@ -7852,7 +7867,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="C9" s="36">
         <v>0.0</v>
@@ -7861,13 +7876,13 @@
         <v>920</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="G9" s="37" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="10">
@@ -7876,7 +7891,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="C10" s="36">
         <v>0.0</v>
@@ -7885,13 +7900,13 @@
         <v>920</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="11">
@@ -7900,7 +7915,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="C11" s="36">
         <v>1.0</v>
@@ -7909,13 +7924,13 @@
         <v>920</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="12">
@@ -7924,7 +7939,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="C12" s="36">
         <v>0.0</v>
@@ -7933,13 +7948,13 @@
         <v>920</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="13">
@@ -7948,7 +7963,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="C13" s="36">
         <v>0.0</v>
@@ -7957,13 +7972,13 @@
         <v>920</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="G13" s="37" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="14">
@@ -7972,7 +7987,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="C14" s="36">
         <v>1.0</v>
@@ -7981,13 +7996,13 @@
         <v>920</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="15">
@@ -7996,7 +8011,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="C15" s="36">
         <v>1.0</v>
@@ -8005,13 +8020,13 @@
         <v>920</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="16">
@@ -8020,7 +8035,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="C16" s="36">
         <v>1.0</v>
@@ -8029,13 +8044,13 @@
         <v>920</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="17">
@@ -8044,7 +8059,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C17" s="36">
         <v>0.0</v>
@@ -8053,13 +8068,13 @@
         <v>920</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="18">
@@ -8068,7 +8083,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="C18" s="36">
         <v>0.0</v>
@@ -8077,13 +8092,13 @@
         <v>920</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="19">
@@ -8101,13 +8116,13 @@
         <v>920</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="G19" s="37" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="20">
@@ -8125,13 +8140,13 @@
         <v>920</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="21">
@@ -8149,13 +8164,13 @@
         <v>920</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="22">
@@ -8173,13 +8188,13 @@
         <v>920</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="23">
@@ -8197,13 +8212,13 @@
         <v>920</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="24">
@@ -8221,13 +8236,13 @@
         <v>920</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="25">
@@ -8245,13 +8260,13 @@
         <v>920</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="G25" s="37" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="26">
@@ -8269,13 +8284,13 @@
         <v>920</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="27">
@@ -8284,7 +8299,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="C27" s="36">
         <v>0.0</v>
@@ -8293,13 +8308,13 @@
         <v>920</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="28">
@@ -8308,7 +8323,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="C28" s="36">
         <v>1.0</v>
@@ -8317,13 +8332,13 @@
         <v>920</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="29">
@@ -8332,7 +8347,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="C29" s="36">
         <v>0.0</v>
@@ -8341,13 +8356,13 @@
         <v>920</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="30">
@@ -8356,7 +8371,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="C30" s="36">
         <v>0.0</v>
@@ -8365,13 +8380,13 @@
         <v>920</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="31">
@@ -8380,7 +8395,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C31" s="36">
         <v>0.0</v>
@@ -8389,13 +8404,13 @@
         <v>920</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="32">
@@ -8413,13 +8428,13 @@
         <v>920</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="33">
@@ -8428,7 +8443,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C33" s="36">
         <v>0.0</v>
@@ -8437,13 +8452,13 @@
         <v>920</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="34">
@@ -8452,7 +8467,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="C34" s="36">
         <v>1.0</v>
@@ -8461,13 +8476,13 @@
         <v>920</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="35">
@@ -8476,7 +8491,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="C35" s="36">
         <v>1.0</v>
@@ -8485,13 +8500,13 @@
         <v>920</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="36">
@@ -8509,13 +8524,13 @@
         <v>920</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="37">
@@ -8524,7 +8539,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="C37" s="36">
         <v>0.0</v>
@@ -8533,13 +8548,13 @@
         <v>920</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="38">
@@ -8548,7 +8563,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="C38" s="36">
         <v>1.0</v>
@@ -8557,13 +8572,13 @@
         <v>920</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="39">
@@ -8572,7 +8587,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="C39" s="36">
         <v>0.0</v>
@@ -8581,13 +8596,13 @@
         <v>920</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="40">
@@ -8596,7 +8611,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="C40" s="36">
         <v>1.0</v>
@@ -8605,13 +8620,13 @@
         <v>920</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="41">
@@ -8620,7 +8635,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="C41" s="36">
         <v>0.0</v>
@@ -8629,13 +8644,13 @@
         <v>920</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="42">
@@ -8644,7 +8659,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="C42" s="36">
         <v>1.0</v>
@@ -8653,13 +8668,13 @@
         <v>920</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="43">
@@ -8668,7 +8683,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="C43" s="36">
         <v>0.0</v>
@@ -8677,13 +8692,13 @@
         <v>920</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="44">
@@ -8692,7 +8707,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="C44" s="36">
         <v>1.0</v>
@@ -8701,13 +8716,13 @@
         <v>920</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="45">
@@ -8716,7 +8731,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="C45" s="36">
         <v>0.0</v>
@@ -8725,13 +8740,13 @@
         <v>920</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="46">
@@ -8740,7 +8755,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="C46" s="36">
         <v>1.0</v>
@@ -8749,13 +8764,13 @@
         <v>920</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="47">
@@ -8764,7 +8779,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="C47" s="36">
         <v>1.0</v>
@@ -8773,13 +8788,13 @@
         <v>920</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="G47" s="37" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="48">
@@ -8788,7 +8803,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="C48" s="36">
         <v>0.0</v>
@@ -8797,13 +8812,13 @@
         <v>920</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="49">
@@ -8812,7 +8827,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="C49" s="36">
         <v>1.0</v>
@@ -8821,13 +8836,13 @@
         <v>920</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="G49" s="37" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="50">
@@ -8836,7 +8851,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="C50" s="36">
         <v>0.0</v>
@@ -8845,13 +8860,13 @@
         <v>920</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="G50" s="37" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="51">
@@ -8860,7 +8875,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="C51" s="36">
         <v>0.0</v>
@@ -8869,13 +8884,13 @@
         <v>920</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="52">
@@ -8884,7 +8899,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="C52" s="36">
         <v>1.0</v>
@@ -8893,13 +8908,13 @@
         <v>920</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="53">
@@ -8908,7 +8923,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="C53" s="36">
         <v>1.0</v>
@@ -8917,13 +8932,13 @@
         <v>920</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="54">
@@ -8932,7 +8947,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="C54" s="36">
         <v>1.0</v>
@@ -8941,13 +8956,13 @@
         <v>920</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="55">
@@ -8956,7 +8971,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="C55" s="36">
         <v>0.0</v>
@@ -8965,13 +8980,13 @@
         <v>920</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="G55" s="37" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="56">
@@ -8980,7 +8995,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="C56" s="36">
         <v>0.0</v>
@@ -8989,13 +9004,13 @@
         <v>920</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="57">
@@ -9004,7 +9019,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="C57" s="36">
         <v>0.0</v>
@@ -9013,13 +9028,13 @@
         <v>920</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="58">
@@ -9028,7 +9043,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="C58" s="36">
         <v>1.0</v>
@@ -9037,13 +9052,13 @@
         <v>920</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="59">
@@ -9061,13 +9076,13 @@
         <v>920</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="60">
@@ -9076,7 +9091,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="C60" s="36">
         <v>0.0</v>
@@ -9085,13 +9100,13 @@
         <v>920</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="61">
@@ -9100,7 +9115,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="C61" s="36">
         <v>0.0</v>
@@ -9109,13 +9124,13 @@
         <v>920</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="62">
@@ -9124,7 +9139,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="C62" s="36">
         <v>0.0</v>
@@ -9133,13 +9148,13 @@
         <v>920</v>
       </c>
       <c r="E62" s="44" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="63">
@@ -9157,13 +9172,13 @@
         <v>920</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="64">
@@ -9172,7 +9187,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="C64" s="36">
         <v>0.0</v>
@@ -9181,13 +9196,13 @@
         <v>927</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F64" s="37" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="G64" s="37" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="65">
@@ -9196,7 +9211,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="C65" s="36">
         <v>0.0</v>
@@ -9205,13 +9220,13 @@
         <v>928</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="66">
@@ -9220,7 +9235,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="C66" s="36">
         <v>0.0</v>
@@ -9229,13 +9244,13 @@
         <v>929</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="67">
@@ -9244,7 +9259,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="C67" s="36">
         <v>0.0</v>
@@ -9253,13 +9268,13 @@
         <v>930</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="G67" s="37" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="68">
@@ -9268,7 +9283,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="C68" s="36">
         <v>0.0</v>
@@ -9277,13 +9292,13 @@
         <v>920</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="69">
@@ -9292,7 +9307,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="C69" s="36">
         <v>1.0</v>
@@ -9301,13 +9316,13 @@
         <v>920</v>
       </c>
       <c r="E69" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="70">
@@ -9316,7 +9331,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="C70" s="36">
         <v>0.0</v>
@@ -9325,13 +9340,13 @@
         <v>920</v>
       </c>
       <c r="E70" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="G70" s="37" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="71">
@@ -9340,7 +9355,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="C71" s="36">
         <v>1.0</v>
@@ -9349,13 +9364,13 @@
         <v>920</v>
       </c>
       <c r="E71" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="G71" s="37" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="72">
@@ -9364,7 +9379,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="C72" s="36">
         <v>0.0</v>
@@ -9373,13 +9388,13 @@
         <v>920</v>
       </c>
       <c r="E72" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F72" s="37" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="G72" s="37" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="73">
@@ -9388,7 +9403,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="C73" s="36">
         <v>1.0</v>
@@ -9397,13 +9412,13 @@
         <v>920</v>
       </c>
       <c r="E73" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F73" s="37" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="G73" s="37" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="74">
@@ -9412,7 +9427,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="C74" s="36">
         <v>0.0</v>
@@ -9421,13 +9436,13 @@
         <v>920</v>
       </c>
       <c r="E74" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F74" s="37" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="G74" s="37" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="75">
@@ -9436,7 +9451,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="C75" s="36">
         <v>1.0</v>
@@ -9445,13 +9460,13 @@
         <v>920</v>
       </c>
       <c r="E75" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F75" s="37" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="G75" s="37" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="76">
@@ -9460,7 +9475,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="C76" s="36">
         <v>0.0</v>
@@ -9469,13 +9484,13 @@
         <v>920</v>
       </c>
       <c r="E76" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F76" s="37" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="G76" s="37" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="77">
@@ -9484,7 +9499,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="C77" s="36">
         <v>1.0</v>
@@ -9493,13 +9508,13 @@
         <v>920</v>
       </c>
       <c r="E77" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F77" s="37" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="G77" s="37" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="78">
@@ -9508,7 +9523,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="C78" s="36">
         <v>0.0</v>
@@ -9517,13 +9532,13 @@
         <v>920</v>
       </c>
       <c r="E78" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F78" s="37" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="G78" s="37" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="79">
@@ -9532,7 +9547,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="C79" s="36">
         <v>0.0</v>
@@ -9541,13 +9556,13 @@
         <v>920</v>
       </c>
       <c r="E79" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F79" s="37" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="G79" s="37" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="80">
@@ -9556,7 +9571,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="C80" s="36">
         <v>1.0</v>
@@ -9565,13 +9580,13 @@
         <v>920</v>
       </c>
       <c r="E80" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F80" s="37" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="G80" s="37" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="81">
@@ -9580,7 +9595,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="C81" s="36">
         <v>1.0</v>
@@ -9589,13 +9604,13 @@
         <v>920</v>
       </c>
       <c r="E81" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F81" s="37" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="G81" s="37" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="82">
@@ -9604,7 +9619,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="C82" s="36">
         <v>1.0</v>
@@ -9613,13 +9628,13 @@
         <v>920</v>
       </c>
       <c r="E82" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F82" s="37" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="G82" s="37" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="83">
@@ -9628,7 +9643,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="C83" s="36">
         <v>0.0</v>
@@ -9637,13 +9652,13 @@
         <v>920</v>
       </c>
       <c r="E83" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F83" s="37" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="G83" s="37" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="84">
@@ -9652,7 +9667,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="C84" s="36">
         <v>0.0</v>
@@ -9661,13 +9676,13 @@
         <v>920</v>
       </c>
       <c r="E84" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F84" s="37" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="G84" s="37" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="85">
@@ -9676,7 +9691,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="36" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="C85" s="36">
         <v>0.0</v>
@@ -9685,13 +9700,13 @@
         <v>920</v>
       </c>
       <c r="E85" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="86">
@@ -9709,13 +9724,13 @@
         <v>920</v>
       </c>
       <c r="E86" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F86" s="37" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="G86" s="37" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="87">
@@ -9733,13 +9748,13 @@
         <v>920</v>
       </c>
       <c r="E87" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F87" s="37" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="88">
@@ -9757,13 +9772,13 @@
         <v>920</v>
       </c>
       <c r="E88" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F88" s="37" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="G88" s="37" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="89">
@@ -9781,13 +9796,13 @@
         <v>920</v>
       </c>
       <c r="E89" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F89" s="37" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="G89" s="37" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="90">
@@ -9805,13 +9820,13 @@
         <v>920</v>
       </c>
       <c r="E90" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F90" s="37" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="G90" s="37" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="91">
@@ -9829,13 +9844,13 @@
         <v>920</v>
       </c>
       <c r="E91" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F91" s="37" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="G91" s="37" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="92">
@@ -9853,13 +9868,13 @@
         <v>920</v>
       </c>
       <c r="E92" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F92" s="37" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="G92" s="37" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="93">
@@ -9877,13 +9892,13 @@
         <v>920</v>
       </c>
       <c r="E93" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F93" s="37" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="G93" s="37" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="94">
@@ -9901,13 +9916,13 @@
         <v>920</v>
       </c>
       <c r="E94" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F94" s="37" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="G94" s="37" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="95">
@@ -9925,13 +9940,13 @@
         <v>925</v>
       </c>
       <c r="E95" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F95" s="37" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="G95" s="37" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="96">
@@ -9949,13 +9964,13 @@
         <v>920</v>
       </c>
       <c r="E96" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F96" s="37" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="G96" s="37" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="97">
@@ -9973,13 +9988,13 @@
         <v>920</v>
       </c>
       <c r="E97" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F97" s="37" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="G97" s="37" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="98">
@@ -9997,13 +10012,13 @@
         <v>920</v>
       </c>
       <c r="E98" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F98" s="37" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="G98" s="37" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="99">
@@ -10021,13 +10036,13 @@
         <v>920</v>
       </c>
       <c r="E99" s="44" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="F99" s="37" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="G99" s="37" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="100">
@@ -10045,13 +10060,13 @@
         <v>920</v>
       </c>
       <c r="E100" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F100" s="37" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="G100" s="37" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="101">
@@ -10069,13 +10084,13 @@
         <v>920</v>
       </c>
       <c r="E101" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F101" s="37" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="G101" s="37" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="102">
@@ -10093,13 +10108,13 @@
         <v>920</v>
       </c>
       <c r="E102" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F102" s="37" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="G102" s="37" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="103">
@@ -10108,7 +10123,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="36" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="C103" s="36">
         <v>0.0</v>
@@ -10117,13 +10132,13 @@
         <v>920</v>
       </c>
       <c r="E103" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F103" s="37" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="G103" s="37" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="104">
@@ -10132,7 +10147,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="C104" s="36">
         <v>1.0</v>
@@ -10141,13 +10156,13 @@
         <v>920</v>
       </c>
       <c r="E104" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F104" s="37" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="G104" s="37" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="105">
@@ -10156,7 +10171,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="C105" s="36">
         <v>0.0</v>
@@ -10165,13 +10180,13 @@
         <v>920</v>
       </c>
       <c r="E105" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F105" s="37" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="G105" s="37" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="106">
@@ -10180,7 +10195,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="C106" s="36">
         <v>1.0</v>
@@ -10189,13 +10204,13 @@
         <v>920</v>
       </c>
       <c r="E106" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F106" s="37" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="G106" s="37" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="107">
@@ -10204,7 +10219,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="C107" s="36">
         <v>0.0</v>
@@ -10213,13 +10228,13 @@
         <v>920</v>
       </c>
       <c r="E107" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F107" s="37" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="G107" s="37" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="108">
@@ -10228,7 +10243,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="C108" s="36">
         <v>1.0</v>
@@ -10237,13 +10252,13 @@
         <v>920</v>
       </c>
       <c r="E108" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F108" s="37" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="G108" s="37" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="109">
@@ -10252,7 +10267,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="C109" s="36">
         <v>0.0</v>
@@ -10261,13 +10276,13 @@
         <v>920</v>
       </c>
       <c r="E109" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F109" s="37" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="G109" s="37" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="110">
@@ -10276,7 +10291,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="C110" s="36">
         <v>1.0</v>
@@ -10285,13 +10300,13 @@
         <v>920</v>
       </c>
       <c r="E110" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F110" s="37" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="G110" s="37" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="111">
@@ -10300,7 +10315,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="C111" s="36">
         <v>0.0</v>
@@ -10309,13 +10324,13 @@
         <v>920</v>
       </c>
       <c r="E111" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F111" s="37" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="G111" s="37" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="112">
@@ -10324,7 +10339,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="36" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
       <c r="C112" s="36">
         <v>1.0</v>
@@ -10333,13 +10348,13 @@
         <v>920</v>
       </c>
       <c r="E112" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F112" s="37" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="G112" s="37" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="113">
@@ -10348,7 +10363,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="C113" s="36">
         <v>0.0</v>
@@ -10357,13 +10372,13 @@
         <v>920</v>
       </c>
       <c r="E113" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F113" s="37" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="G113" s="37" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="114">
@@ -10372,7 +10387,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="C114" s="36">
         <v>0.0</v>
@@ -10381,13 +10396,13 @@
         <v>920</v>
       </c>
       <c r="E114" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F114" s="37" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="G114" s="37" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="115">
@@ -10396,7 +10411,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="C115" s="36">
         <v>0.0</v>
@@ -10405,13 +10420,13 @@
         <v>920</v>
       </c>
       <c r="E115" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F115" s="37" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="G115" s="37" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="116">
@@ -10420,7 +10435,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="36" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="C116" s="36">
         <v>1.0</v>
@@ -10429,13 +10444,13 @@
         <v>920</v>
       </c>
       <c r="E116" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F116" s="37" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="G116" s="37" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="117">
@@ -10453,13 +10468,13 @@
         <v>920</v>
       </c>
       <c r="E117" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F117" s="37" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="G117" s="37" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="118">
@@ -10477,13 +10492,13 @@
         <v>923</v>
       </c>
       <c r="E118" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F118" s="37" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="G118" s="37" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="119">
@@ -10501,13 +10516,13 @@
         <v>920</v>
       </c>
       <c r="E119" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F119" s="37" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="G119" s="37" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="120">
@@ -10525,10 +10540,10 @@
         <v>920</v>
       </c>
       <c r="E120" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F120" s="37" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="G120" s="37" t="s">
         <v>14</v>
@@ -10540,7 +10555,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C121" s="36">
         <v>0.0</v>
@@ -10549,10 +10564,10 @@
         <v>920</v>
       </c>
       <c r="E121" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F121" s="37" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
       <c r="G121" s="37" t="s">
         <v>32</v>
@@ -10564,7 +10579,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="36" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="C122" s="36">
         <v>0.0</v>
@@ -10573,13 +10588,13 @@
         <v>920</v>
       </c>
       <c r="E122" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F122" s="37" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="G122" s="37" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="123">
@@ -10588,7 +10603,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="C123" s="36">
         <v>0.0</v>
@@ -10597,13 +10612,13 @@
         <v>920</v>
       </c>
       <c r="E123" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F123" s="37" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="G123" s="37" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="124">
@@ -10612,7 +10627,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="36" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="C124" s="36">
         <v>0.0</v>
@@ -10621,13 +10636,13 @@
         <v>920</v>
       </c>
       <c r="E124" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F124" s="37" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="G124" s="37" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="125">
@@ -10645,13 +10660,13 @@
         <v>920</v>
       </c>
       <c r="E125" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F125" s="37" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="G125" s="37" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="126">
@@ -10669,13 +10684,13 @@
         <v>920</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F126" s="37" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="G126" s="37" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="127">
@@ -10684,7 +10699,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="36" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="C127" s="36">
         <v>0.0</v>
@@ -10693,13 +10708,13 @@
         <v>920</v>
       </c>
       <c r="E127" s="44" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F127" s="37" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="G127" s="37" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
     </row>
   </sheetData>
@@ -10742,31 +10757,31 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1456</v>
+        <v>1459</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1457</v>
+        <v>1460</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>1458</v>
+        <v>1461</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>1460</v>
+        <v>1463</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>1461</v>
+        <v>1464</v>
       </c>
       <c r="J1" s="28" t="s">
-        <v>1462</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="2" ht="186.0" customHeight="1">
@@ -10775,12 +10790,12 @@
         <v>-1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
       <c r="C2" s="64" t="s">
         <v>301</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="65" t="s">
         <v>920</v>
       </c>
       <c r="E2" s="35" t="s">
@@ -10808,25 +10823,25 @@
         <v>0</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="C3" s="64" t="s">
         <v>847</v>
       </c>
-      <c r="D3" s="34" t="s">
-        <v>922</v>
+      <c r="D3" s="65" t="s">
+        <v>937</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H3" s="35" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
       <c r="I3" s="35" t="s">
         <v>303</v>
@@ -10841,25 +10856,25 @@
         <v>1</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>1468</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>922</v>
+        <v>1471</v>
+      </c>
+      <c r="D4" s="65" t="s">
+        <v>937</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H4" s="35" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
       <c r="I4" s="35" t="s">
         <v>303</v>
@@ -10874,25 +10889,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>1471</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>922</v>
+        <v>1474</v>
+      </c>
+      <c r="D5" s="65" t="s">
+        <v>937</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1472</v>
+        <v>1475</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H5" s="35" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
       <c r="I5" s="35" t="s">
         <v>512</v>
@@ -10907,25 +10922,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1473</v>
+        <v>1476</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>1474</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>922</v>
+        <v>1477</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>937</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
       <c r="I6" s="35" t="s">
         <v>512</v>
@@ -10940,25 +10955,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1477</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>920</v>
+        <v>1480</v>
+      </c>
+      <c r="D7" s="65" t="s">
+        <v>1481</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>920</v>
+        <v>1481</v>
       </c>
       <c r="I7" s="35" t="s">
         <v>303</v>
@@ -10973,25 +10988,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>1480</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>920</v>
+        <v>1484</v>
+      </c>
+      <c r="D8" s="65" t="s">
+        <v>1481</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>920</v>
+        <v>1481</v>
       </c>
       <c r="I8" s="35" t="s">
         <v>303</v>
@@ -11011,14 +11026,14 @@
       <c r="C9" s="32" t="s">
         <v>880</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="65" t="s">
         <v>931</v>
       </c>
       <c r="E9" s="35" t="s">
         <v>880</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>299</v>
@@ -11039,25 +11054,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>1484</v>
-      </c>
-      <c r="D10" s="34" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D10" s="65" t="s">
         <v>933</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
       <c r="I10" s="35" t="s">
         <v>507</v>
@@ -11072,25 +11087,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>920</v>
+        <v>1492</v>
+      </c>
+      <c r="D11" s="65" t="s">
+        <v>1481</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>299</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>920</v>
+        <v>1481</v>
       </c>
       <c r="I11" s="35" t="s">
         <v>303</v>
@@ -11105,19 +11120,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1491</v>
-      </c>
-      <c r="D12" s="34" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D12" s="65" t="s">
         <v>932</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>299</v>
@@ -11138,19 +11153,19 @@
         <v>10</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D13" s="34" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D13" s="65" t="s">
         <v>932</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>299</v>
@@ -11174,13 +11189,13 @@
         <v>20</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>1496</v>
-      </c>
-      <c r="D14" s="34" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D14" s="65" t="s">
         <v>920</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="F14" s="35" t="s">
         <v>325</v>
@@ -11204,12 +11219,12 @@
         <v>12</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="C15" s="64" t="s">
         <v>301</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="65" t="s">
         <v>920</v>
       </c>
       <c r="E15" s="35" t="s">
@@ -11233,10 +11248,7 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C15 E2:J15">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D15">
+    <dataValidation type="list" allowBlank="1" sqref="C2:J15">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -11267,7 +11279,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="2">
@@ -11294,7 +11306,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="5">
@@ -11303,7 +11315,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="6">
@@ -11315,7 +11327,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="8">
@@ -11323,7 +11335,7 @@
         <v>0.0</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="9">
@@ -11331,7 +11343,7 @@
         <v>1.0</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="10">
@@ -11339,7 +11351,7 @@
         <v>2.0</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="11">
@@ -11347,7 +11359,7 @@
         <v>3.0</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="12">
@@ -11355,7 +11367,7 @@
         <v>4.0</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="13">
@@ -11363,7 +11375,7 @@
         <v>5.0</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="15">
@@ -11371,7 +11383,7 @@
         <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="16">
@@ -11389,7 +11401,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="18">
@@ -11434,7 +11446,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="23">
@@ -11460,7 +11472,7 @@
         <v>44</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="27">
@@ -11505,7 +11517,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="32">
@@ -11532,7 +11544,7 @@
         <v>7</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="35">
@@ -11550,7 +11562,7 @@
         <v>9</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="37">
@@ -11612,7 +11624,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="45">
@@ -11620,7 +11632,7 @@
         <v>0.0</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="46">
@@ -11628,7 +11640,7 @@
         <v>1.0</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="48">
@@ -11636,7 +11648,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="49">
@@ -11680,7 +11692,7 @@
         <f>ROW()-ROW(Table_Item_Family_Type[N])</f>
         <v>4</v>
       </c>
-      <c r="B53" s="65" t="s">
+      <c r="B53" s="66" t="s">
         <v>309</v>
       </c>
     </row>
@@ -11689,7 +11701,7 @@
         <v>44</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="56">
@@ -11754,7 +11766,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="2">
@@ -11772,7 +11784,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="4">
@@ -11781,7 +11793,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="5">
@@ -11862,7 +11874,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="14">
@@ -12051,7 +12063,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="36">
@@ -12059,16 +12071,16 @@
         <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1523</v>
-      </c>
-      <c r="C36" s="66" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C36" s="67" t="s">
         <v>290</v>
       </c>
-      <c r="D36" s="66" t="s">
-        <v>1524</v>
-      </c>
-      <c r="E36" s="66" t="s">
-        <v>1525</v>
+      <c r="D36" s="67" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E36" s="67" t="s">
+        <v>1529</v>
       </c>
     </row>
     <row r="37">
@@ -12077,7 +12089,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="C37" s="38" t="s">
         <v>299</v>
@@ -12085,7 +12097,7 @@
       <c r="D37" s="38" t="s">
         <v>301</v>
       </c>
-      <c r="E37" s="67" t="str">
+      <c r="E37" s="68" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B37,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_NONE")</f>
         <v>MEMENTO_NONE</v>
       </c>
@@ -12096,15 +12108,15 @@
         <v>1</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="D38" s="38" t="s">
         <v>863</v>
       </c>
-      <c r="E38" s="67" t="str">
+      <c r="E38" s="68" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B38,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_JOB_FIND_1_1|MEMENTO_JOB_FIND_1_2")</f>
         <v>MEMENTO_JOB_FIND_1_1|MEMENTO_JOB_FIND_1_2</v>
       </c>
@@ -12115,15 +12127,15 @@
         <v>2</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="D39" s="38" t="s">
         <v>891</v>
       </c>
-      <c r="E39" s="67" t="str">
+      <c r="E39" s="68" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B39,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_RECIPE_MISSION_1")</f>
         <v>MEMENTO_RECIPE_MISSION_1</v>
       </c>
@@ -12137,12 +12149,12 @@
         <v>39</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D40" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="E40" s="67" t="str">
+      <c r="E40" s="68" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B40,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_POOR_MAN_WC_1|MEMENTO_POOR_MAN_WC_2|MEMENTO_POOR_MAN_WC_3")</f>
         <v>MEMENTO_POOR_MAN_WC_1|MEMENTO_POOR_MAN_WC_2|MEMENTO_POOR_MAN_WC_3</v>
       </c>
@@ -12153,7 +12165,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>430</v>
@@ -12161,7 +12173,7 @@
       <c r="D41" s="38" t="s">
         <v>301</v>
       </c>
-      <c r="E41" s="67" t="str">
+      <c r="E41" s="68" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B41,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_LAST")</f>
         <v>MEMENTO_LAST</v>
       </c>
@@ -12171,19 +12183,19 @@
         <v>44</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1530</v>
-      </c>
-      <c r="C43" s="65" t="s">
-        <v>1531</v>
-      </c>
-      <c r="D43" s="65" t="s">
-        <v>1030</v>
-      </c>
-      <c r="E43" s="66" t="s">
-        <v>1532</v>
-      </c>
-      <c r="F43" s="65" t="s">
-        <v>1533</v>
+        <v>1534</v>
+      </c>
+      <c r="C43" s="66" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D43" s="66" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E43" s="67" t="s">
+        <v>1536</v>
+      </c>
+      <c r="F43" s="66" t="s">
+        <v>1537</v>
       </c>
     </row>
     <row r="44">
@@ -12195,13 +12207,13 @@
         <v>675</v>
       </c>
       <c r="C44" s="44" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="D44" s="44" t="s">
         <v>678</v>
       </c>
       <c r="E44" s="48" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="F44" s="43" t="b">
         <v>0</v>
@@ -12216,13 +12228,13 @@
         <v>687</v>
       </c>
       <c r="C45" s="44" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="F45" s="43" t="b">
         <v>0</v>
@@ -12237,13 +12249,13 @@
         <v>704</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="D46" s="44" t="s">
         <v>724</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="F46" s="43" t="b">
         <v>0</v>
@@ -12258,13 +12270,13 @@
         <v>709</v>
       </c>
       <c r="C47" s="44" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="F47" s="43" t="b">
         <v>0</v>
@@ -12282,10 +12294,10 @@
         <v>39</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="F48" s="43" t="b">
         <v>0</v>
@@ -12297,16 +12309,16 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>39</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="F49" s="43" t="b">
         <v>0</v>
@@ -12318,16 +12330,16 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>39</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="F50" s="43" t="b">
         <v>1</v>
@@ -12339,16 +12351,16 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="D51" s="44" t="s">
         <v>678</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="F51" s="43" t="b">
         <v>0</v>
@@ -12359,10 +12371,10 @@
         <v>44</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="54">
@@ -12371,7 +12383,7 @@
         <v>0</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="C54" s="51" t="s">
         <v>439</v>
@@ -12382,7 +12394,7 @@
         <v>44</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="57">
@@ -13392,16 +13404,16 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="2">
@@ -13413,12 +13425,12 @@
         <v>302</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1545</v>
-      </c>
-      <c r="D2" s="68" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D2" s="69" t="s">
         <v>299</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="69" t="s">
         <v>678</v>
       </c>
     </row>
@@ -13431,12 +13443,12 @@
         <v>417</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1546</v>
-      </c>
-      <c r="D3" s="68" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D3" s="69" t="s">
         <v>299</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="69" t="s">
         <v>678</v>
       </c>
     </row>
@@ -13446,15 +13458,15 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1545</v>
-      </c>
-      <c r="D4" s="68" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D4" s="69" t="s">
         <v>299</v>
       </c>
-      <c r="E4" s="68" t="s">
+      <c r="E4" s="69" t="s">
         <v>678</v>
       </c>
     </row>
@@ -13487,7 +13499,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="2">
@@ -13514,7 +13526,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
     </row>
   </sheetData>
@@ -13540,23 +13552,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="s">
-        <v>1553</v>
-      </c>
-      <c r="B2" s="69">
+        <v>1557</v>
+      </c>
+      <c r="B2" s="70">
         <v>1.0</v>
       </c>
       <c r="C2" s="36" t="b">
@@ -13568,9 +13580,9 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>1554</v>
-      </c>
-      <c r="B3" s="69">
+        <v>1558</v>
+      </c>
+      <c r="B3" s="70">
         <v>1.0</v>
       </c>
       <c r="C3" s="36" t="b">
@@ -13582,9 +13594,9 @@
     </row>
     <row r="4">
       <c r="A4" s="37" t="s">
-        <v>1555</v>
-      </c>
-      <c r="B4" s="69">
+        <v>1559</v>
+      </c>
+      <c r="B4" s="70">
         <v>3.0</v>
       </c>
       <c r="C4" s="36" t="b">
@@ -13596,9 +13608,9 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>1556</v>
-      </c>
-      <c r="B5" s="69">
+        <v>1560</v>
+      </c>
+      <c r="B5" s="70">
         <v>1.0</v>
       </c>
       <c r="C5" s="36" t="b">
@@ -13610,9 +13622,9 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>1557</v>
-      </c>
-      <c r="B6" s="69">
+        <v>1561</v>
+      </c>
+      <c r="B6" s="70">
         <v>3.0</v>
       </c>
       <c r="C6" s="36" t="b">
@@ -13624,9 +13636,9 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>1558</v>
-      </c>
-      <c r="B7" s="69">
+        <v>1562</v>
+      </c>
+      <c r="B7" s="70">
         <v>3.0</v>
       </c>
       <c r="C7" s="36" t="b">
@@ -13638,9 +13650,9 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>1559</v>
-      </c>
-      <c r="B8" s="69">
+        <v>1563</v>
+      </c>
+      <c r="B8" s="70">
         <v>5.0</v>
       </c>
       <c r="C8" s="36" t="b">
@@ -13652,9 +13664,9 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>1560</v>
-      </c>
-      <c r="B9" s="69">
+        <v>1564</v>
+      </c>
+      <c r="B9" s="70">
         <v>4.0</v>
       </c>
       <c r="C9" s="36" t="b">
@@ -13666,9 +13678,9 @@
     </row>
     <row r="10">
       <c r="A10" s="37" t="s">
-        <v>1561</v>
-      </c>
-      <c r="B10" s="69">
+        <v>1565</v>
+      </c>
+      <c r="B10" s="70">
         <v>5.0</v>
       </c>
       <c r="C10" s="36" t="b">
@@ -13680,9 +13692,9 @@
     </row>
     <row r="11">
       <c r="A11" s="37" t="s">
-        <v>1562</v>
-      </c>
-      <c r="B11" s="69">
+        <v>1566</v>
+      </c>
+      <c r="B11" s="70">
         <v>4.0</v>
       </c>
       <c r="C11" s="36" t="b">
@@ -13694,9 +13706,9 @@
     </row>
     <row r="12">
       <c r="A12" s="37" t="s">
-        <v>1563</v>
-      </c>
-      <c r="B12" s="69">
+        <v>1567</v>
+      </c>
+      <c r="B12" s="70">
         <v>1.0</v>
       </c>
       <c r="C12" s="36" t="b">
@@ -13708,9 +13720,9 @@
     </row>
     <row r="13">
       <c r="A13" s="37" t="s">
-        <v>1564</v>
-      </c>
-      <c r="B13" s="69">
+        <v>1568</v>
+      </c>
+      <c r="B13" s="70">
         <v>4.0</v>
       </c>
       <c r="C13" s="36" t="b">
@@ -13722,9 +13734,9 @@
     </row>
     <row r="14">
       <c r="A14" s="37" t="s">
-        <v>1565</v>
-      </c>
-      <c r="B14" s="69">
+        <v>1569</v>
+      </c>
+      <c r="B14" s="70">
         <v>1.0</v>
       </c>
       <c r="C14" s="36" t="b">
@@ -13736,9 +13748,9 @@
     </row>
     <row r="15">
       <c r="A15" s="37" t="s">
-        <v>1566</v>
-      </c>
-      <c r="B15" s="69">
+        <v>1570</v>
+      </c>
+      <c r="B15" s="70">
         <v>2.0</v>
       </c>
       <c r="C15" s="36" t="b">
@@ -13750,9 +13762,9 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="s">
-        <v>1567</v>
-      </c>
-      <c r="B16" s="69">
+        <v>1571</v>
+      </c>
+      <c r="B16" s="70">
         <v>3.0</v>
       </c>
       <c r="C16" s="36" t="b">
@@ -13764,9 +13776,9 @@
     </row>
     <row r="17">
       <c r="A17" s="37" t="s">
-        <v>1568</v>
-      </c>
-      <c r="B17" s="69">
+        <v>1572</v>
+      </c>
+      <c r="B17" s="70">
         <v>2.0</v>
       </c>
       <c r="C17" s="36" t="b">
@@ -13778,9 +13790,9 @@
     </row>
     <row r="18">
       <c r="A18" s="37" t="s">
-        <v>1569</v>
-      </c>
-      <c r="B18" s="69">
+        <v>1573</v>
+      </c>
+      <c r="B18" s="70">
         <v>2.0</v>
       </c>
       <c r="C18" s="36" t="b">
@@ -13792,9 +13804,9 @@
     </row>
     <row r="19">
       <c r="A19" s="37" t="s">
-        <v>1570</v>
-      </c>
-      <c r="B19" s="69">
+        <v>1574</v>
+      </c>
+      <c r="B19" s="70">
         <v>2.0</v>
       </c>
       <c r="C19" s="36" t="b">
@@ -13806,9 +13818,9 @@
     </row>
     <row r="20">
       <c r="A20" s="37" t="s">
-        <v>1571</v>
-      </c>
-      <c r="B20" s="69">
+        <v>1575</v>
+      </c>
+      <c r="B20" s="70">
         <v>2.0</v>
       </c>
       <c r="C20" s="36" t="b">
@@ -13820,9 +13832,9 @@
     </row>
     <row r="21">
       <c r="A21" s="37" t="s">
-        <v>1572</v>
-      </c>
-      <c r="B21" s="69">
+        <v>1576</v>
+      </c>
+      <c r="B21" s="70">
         <v>3.0</v>
       </c>
       <c r="C21" s="36" t="b">
@@ -13834,9 +13846,9 @@
     </row>
     <row r="22">
       <c r="A22" s="37" t="s">
-        <v>1573</v>
-      </c>
-      <c r="B22" s="69">
+        <v>1577</v>
+      </c>
+      <c r="B22" s="70">
         <v>2.0</v>
       </c>
       <c r="C22" s="36" t="b">
@@ -13848,9 +13860,9 @@
     </row>
     <row r="23">
       <c r="A23" s="37" t="s">
-        <v>1574</v>
-      </c>
-      <c r="B23" s="69">
+        <v>1578</v>
+      </c>
+      <c r="B23" s="70">
         <v>2.0</v>
       </c>
       <c r="C23" s="36" t="b">
@@ -13862,9 +13874,9 @@
     </row>
     <row r="24">
       <c r="A24" s="37" t="s">
-        <v>1575</v>
-      </c>
-      <c r="B24" s="69">
+        <v>1579</v>
+      </c>
+      <c r="B24" s="70">
         <v>2.0</v>
       </c>
       <c r="C24" s="36" t="b">
@@ -13876,9 +13888,9 @@
     </row>
     <row r="25">
       <c r="A25" s="37" t="s">
-        <v>1576</v>
-      </c>
-      <c r="B25" s="69">
+        <v>1580</v>
+      </c>
+      <c r="B25" s="70">
         <v>2.0</v>
       </c>
       <c r="C25" s="36" t="b">
@@ -13890,9 +13902,9 @@
     </row>
     <row r="26">
       <c r="A26" s="37" t="s">
-        <v>1577</v>
-      </c>
-      <c r="B26" s="69">
+        <v>1581</v>
+      </c>
+      <c r="B26" s="70">
         <v>2.0</v>
       </c>
       <c r="C26" s="36" t="b">
@@ -13904,9 +13916,9 @@
     </row>
     <row r="27">
       <c r="A27" s="37" t="s">
-        <v>1578</v>
-      </c>
-      <c r="B27" s="69">
+        <v>1582</v>
+      </c>
+      <c r="B27" s="70">
         <v>2.0</v>
       </c>
       <c r="C27" s="36" t="b">
@@ -13918,9 +13930,9 @@
     </row>
     <row r="28">
       <c r="A28" s="37" t="s">
-        <v>1579</v>
-      </c>
-      <c r="B28" s="69">
+        <v>1583</v>
+      </c>
+      <c r="B28" s="70">
         <v>2.0</v>
       </c>
       <c r="C28" s="36" t="b">
@@ -13932,9 +13944,9 @@
     </row>
     <row r="29">
       <c r="A29" s="37" t="s">
-        <v>1580</v>
-      </c>
-      <c r="B29" s="69">
+        <v>1584</v>
+      </c>
+      <c r="B29" s="70">
         <v>4.0</v>
       </c>
       <c r="C29" s="36" t="b">
@@ -13946,9 +13958,9 @@
     </row>
     <row r="30">
       <c r="A30" s="37" t="s">
-        <v>1581</v>
-      </c>
-      <c r="B30" s="69">
+        <v>1585</v>
+      </c>
+      <c r="B30" s="70">
         <v>2.0</v>
       </c>
       <c r="C30" s="36" t="b">
@@ -13960,9 +13972,9 @@
     </row>
     <row r="31">
       <c r="A31" s="37" t="s">
-        <v>1582</v>
-      </c>
-      <c r="B31" s="69">
+        <v>1586</v>
+      </c>
+      <c r="B31" s="70">
         <v>3.0</v>
       </c>
       <c r="C31" s="36" t="b">
@@ -13974,9 +13986,9 @@
     </row>
     <row r="32">
       <c r="A32" s="37" t="s">
-        <v>1583</v>
-      </c>
-      <c r="B32" s="69">
+        <v>1587</v>
+      </c>
+      <c r="B32" s="70">
         <v>2.0</v>
       </c>
       <c r="C32" s="36" t="b">
@@ -13988,9 +14000,9 @@
     </row>
     <row r="33">
       <c r="A33" s="37" t="s">
-        <v>1126</v>
-      </c>
-      <c r="B33" s="69">
+        <v>1129</v>
+      </c>
+      <c r="B33" s="70">
         <v>5.0</v>
       </c>
       <c r="C33" s="36" t="b">
@@ -14661,7 +14673,7 @@
         <v>68</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N11" s="13" t="s">
         <v>68</v>
@@ -29249,6 +29261,51 @@
       <c r="C14" s="36" t="s">
         <v>921</v>
       </c>
+      <c r="D14" s="36" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>13</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>936</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>921</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>14</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>937</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>921</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>15</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>938</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>921</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -29281,13 +29338,13 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>24</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
     </row>
     <row r="2">
@@ -29302,7 +29359,7 @@
         <v>298</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="3">
@@ -29317,7 +29374,7 @@
         <v>298</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
     </row>
     <row r="4">
@@ -29329,10 +29386,10 @@
         <v>721</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
     </row>
     <row r="5">
@@ -29341,13 +29398,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
     </row>
     <row r="6">
@@ -29359,10 +29416,10 @@
         <v>735</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -29374,10 +29431,10 @@
         <v>737</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
     </row>
     <row r="8">
@@ -29386,13 +29443,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
     </row>
     <row r="9">
@@ -29404,10 +29461,10 @@
         <v>739</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
     </row>
     <row r="10">
@@ -29416,13 +29473,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
     </row>
     <row r="11">
@@ -29434,10 +29491,10 @@
         <v>740</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
     </row>
     <row r="12">
@@ -29452,7 +29509,7 @@
         <v>383</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
     </row>
     <row r="13">
@@ -29467,7 +29524,7 @@
         <v>385</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
     </row>
     <row r="14">
@@ -29476,13 +29533,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
     </row>
     <row r="15">
@@ -29494,10 +29551,10 @@
         <v>747</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
     </row>
     <row r="16">
@@ -29506,13 +29563,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="17">
@@ -29524,10 +29581,10 @@
         <v>772</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
     </row>
     <row r="18">
@@ -29542,7 +29599,7 @@
         <v>33</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="19">
@@ -29557,7 +29614,7 @@
         <v>304</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
     </row>
     <row r="20">
@@ -29566,13 +29623,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C20" s="39" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
     </row>
     <row r="21">
@@ -29581,13 +29638,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="C21" s="39" t="s">
         <v>298</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="23">
@@ -29595,25 +29652,25 @@
         <v>44</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>433</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="H23" s="28" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="24">
@@ -29622,7 +29679,7 @@
         <v>0</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C24" s="37" t="s">
         <v>439</v>
@@ -29649,7 +29706,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C25" s="37" t="s">
         <v>439</v>
@@ -29676,7 +29733,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="C26" s="40" t="s">
         <v>439</v>
@@ -29688,13 +29745,13 @@
         <v>443</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="G26" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="40" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
     </row>
     <row r="27">
@@ -29703,7 +29760,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="C27" s="40" t="s">
         <v>439</v>
@@ -29715,13 +29772,13 @@
         <v>443</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="G27" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H27" s="40" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="28">
@@ -29730,7 +29787,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="C28" s="40" t="s">
         <v>439</v>
@@ -29748,7 +29805,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="40" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
     </row>
     <row r="29">
@@ -29757,7 +29814,7 @@
         <v>5</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>439</v>
@@ -29766,7 +29823,7 @@
         <v>440</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>677</v>
@@ -29775,7 +29832,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="40" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="30">
@@ -29784,7 +29841,7 @@
         <v>6</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>439</v>
@@ -29802,7 +29859,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="40" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
     </row>
     <row r="31">
@@ -29811,7 +29868,7 @@
         <v>7</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>439</v>
@@ -29823,13 +29880,13 @@
         <v>443</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="G31" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H31" s="40" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
     <row r="32">
@@ -29838,7 +29895,7 @@
         <v>8</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C32" s="40" t="s">
         <v>439</v>
@@ -29856,7 +29913,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="40" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="33">
@@ -29865,7 +29922,7 @@
         <v>9</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="C33" s="40" t="s">
         <v>439</v>
@@ -29877,13 +29934,13 @@
         <v>443</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="G33" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H33" s="40" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="34">
@@ -29892,7 +29949,7 @@
         <v>10</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C34" s="40" t="s">
         <v>439</v>
@@ -29904,13 +29961,13 @@
         <v>804</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="G34" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="40" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
     </row>
     <row r="35">
@@ -29919,7 +29976,7 @@
         <v>11</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="C35" s="40" t="s">
         <v>805</v>
@@ -29931,13 +29988,13 @@
         <v>443</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="G35" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H35" s="40" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
     </row>
     <row r="36">
@@ -29946,7 +30003,7 @@
         <v>12</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="C36" s="40" t="s">
         <v>439</v>
@@ -29958,13 +30015,13 @@
         <v>443</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="G36" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H36" s="40" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="37">
@@ -29973,7 +30030,7 @@
         <v>13</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="C37" s="40" t="s">
         <v>805</v>
@@ -29982,16 +30039,16 @@
         <v>505</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="G37" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H37" s="40" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="38">
@@ -30000,7 +30057,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="C38" s="40" t="s">
         <v>439</v>
@@ -30018,7 +30075,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="40" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="39">
@@ -30027,7 +30084,7 @@
         <v>15</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="C39" s="40" t="s">
         <v>439</v>
@@ -30045,7 +30102,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="40" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="40">
@@ -30054,7 +30111,7 @@
         <v>16</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="C40" s="40" t="s">
         <v>439</v>
@@ -30072,7 +30129,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="40" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="41">
@@ -30081,7 +30138,7 @@
         <v>17</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="C41" s="40" t="s">
         <v>439</v>
@@ -30099,7 +30156,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="42">
@@ -30108,7 +30165,7 @@
         <v>18</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="C42" s="40" t="s">
         <v>439</v>
@@ -30120,13 +30177,13 @@
         <v>443</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="G42" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H42" s="40" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="43">
@@ -30135,7 +30192,7 @@
         <v>19</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>439</v>
@@ -30147,13 +30204,13 @@
         <v>443</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="G43" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H43" s="40" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="44">
@@ -30162,7 +30219,7 @@
         <v>20</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>439</v>
@@ -30171,16 +30228,16 @@
         <v>440</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="G44" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H44" s="40" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="45">
@@ -30189,7 +30246,7 @@
         <v>21</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C45" s="40" t="s">
         <v>439</v>
@@ -30207,7 +30264,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="40" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="46">
@@ -30216,7 +30273,7 @@
         <v>22</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C46" s="40" t="s">
         <v>439</v>
@@ -30228,13 +30285,13 @@
         <v>443</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="G46" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H46" s="40" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="47">
@@ -30243,7 +30300,7 @@
         <v>23</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C47" s="40" t="s">
         <v>439</v>
@@ -30255,13 +30312,13 @@
         <v>809</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="G47" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H47" s="40" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="48">
@@ -30270,7 +30327,7 @@
         <v>24</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="C48" s="40" t="s">
         <v>810</v>
@@ -30279,16 +30336,16 @@
         <v>440</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="G48" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="40" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="49">
@@ -30297,7 +30354,7 @@
         <v>25</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="C49" s="40" t="s">
         <v>439</v>
@@ -30315,7 +30372,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="40" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="50">
@@ -30324,7 +30381,7 @@
         <v>26</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="C50" s="40" t="s">
         <v>439</v>
@@ -30336,13 +30393,13 @@
         <v>443</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="G50" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H50" s="40" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="51">
@@ -30351,7 +30408,7 @@
         <v>27</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="C51" s="40" t="s">
         <v>439</v>
@@ -30369,7 +30426,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="40" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="52">
@@ -30378,7 +30435,7 @@
         <v>28</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="C52" s="40" t="s">
         <v>439</v>
@@ -30390,13 +30447,13 @@
         <v>815</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="G52" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="40" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="53">
@@ -30405,7 +30462,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="C53" s="40" t="s">
         <v>439</v>
@@ -30423,7 +30480,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="40" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="54">
@@ -30432,7 +30489,7 @@
         <v>30</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="C54" s="37" t="s">
         <v>439</v>
@@ -30549,10 +30606,10 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="C1" s="56" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="2">
@@ -30564,7 +30621,7 @@
         <v>676</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="3">
@@ -30576,7 +30633,7 @@
         <v>707</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="4">
@@ -30585,10 +30642,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="6">
@@ -30596,13 +30653,13 @@
         <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7">
@@ -30611,7 +30668,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>678</v>
@@ -30626,10 +30683,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="D8" s="57" t="s">
         <v>443</v>
@@ -30641,10 +30698,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="D9" s="57" t="s">
         <v>680</v>
@@ -30656,10 +30713,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="D10" s="57" t="s">
         <v>682</v>
@@ -30671,7 +30728,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>678</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -101,32 +101,8 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
-    <comment authorId="0" ref="A20">
-      <text>
-        <t xml:space="preserve">NullReferenceException: Object reference not set to an instance of an object
-Gob3AQ.GameMenu.Dialog.DialogOptionButtonClass.SetOptionText (System.String&amp; text) (at Assets/Scripts/Menu/DialogOptionButtonClass.cs:27)
-Gob3AQ.GameMenu.GameMenuClass.ShowDialogueService (System.ReadOnlySpan`1[T] defaultTalkers, Gob3AQ.VARMAP.Types.DialogType dialog, Gob3AQ.VARMAP.Types.DialogPhrase phrase) (at Assets/Scripts/Master/GameMenuClass.cs:93)
-Gob3AQ.GameMaster.GameMasterClass.EnableDialogueService (System.Boolean enable, System.ReadOnlySpan`1[T] talkers, Gob3AQ.VARMAP.Types.DialogType dialog, Gob3AQ.VARMAP.Types.DialogPhrase phrase) (at Assets/Scripts/Master/GameMasterClass.cs:232)
-Gob3AQ.LevelMaster.LevelMasterClass.PlayerReachedWaypointService (Gob3AQ.VARMAP.Types.CharacterType character) (at Assets/Scripts/Master/LevelMasterClass.cs:183)
-Gob3AQ.GameElement.PlayableChar.PlayableCharScript.StartBufferedInteraction () (at Assets/Scripts/GameElement/PlayableCharScript.cs:351)
-Gob3AQ.GameElement.PlayableChar.PlayableCharScript.Execute_Walk () (at Assets/Scripts/GameElement/PlayableCharScript.cs:279)
-Gob3AQ.GameElement.PlayableChar.PlayableCharScript.Execute_Play () (at Assets/Scripts/GameElement/PlayableCharScript.cs:234)
-Gob3AQ.GameElement.PlayableChar.PlayableCharScript.Update () (at Assets/Scripts/GameElement/PlayableCharScript.cs:164)
-</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5035" uniqueCount="1590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5011" uniqueCount="1566">
   <si>
     <t>NewItem</t>
   </si>
@@ -4805,97 +4781,25 @@
     <t>ONGOING</t>
   </si>
   <si>
-    <t>Talk with characters</t>
-  </si>
-  <si>
-    <t>Plot (1st part)</t>
-  </si>
-  <si>
-    <t>Improve Waypoint Tool (naming)</t>
-  </si>
-  <si>
-    <t>Language files</t>
-  </si>
-  <si>
-    <t>Background objects layers</t>
-  </si>
-  <si>
-    <t>Bug with menu of items (not selecting)</t>
-  </si>
-  <si>
-    <t>Loading screen between rooms</t>
-  </si>
-  <si>
-    <t>Main event list (Tomba style)</t>
-  </si>
-  <si>
     <t>Parry - Notifications - Max 4 queue</t>
   </si>
   <si>
     <t>Trophies</t>
   </si>
   <si>
-    <t>Observe items, NPCs, trigger events</t>
-  </si>
-  <si>
-    <t>Seealso in services. Add owner in descr</t>
-  </si>
-  <si>
-    <t>Avoid services modifying VARMAP</t>
-  </si>
-  <si>
-    <t>Normalize menu items with dialog opts</t>
-  </si>
-  <si>
-    <t>Use Dictionaries for LevelManager</t>
-  </si>
-  <si>
-    <t>State change deactivation/activation</t>
-  </si>
-  <si>
-    <t>Adressables instead of Resources</t>
-  </si>
-  <si>
-    <t>Sprite Atlas addressable</t>
-  </si>
-  <si>
-    <t>Enshorten stack</t>
-  </si>
-  <si>
-    <t>Re-think usage of ITEM_TAKE, USE_TALK</t>
-  </si>
-  <si>
-    <t>Spawn/Despawn conditions</t>
-  </si>
-  <si>
-    <t>Drag with mouse</t>
-  </si>
-  <si>
-    <t>Zoom</t>
-  </si>
-  <si>
-    <t>More upper button commands</t>
-  </si>
-  <si>
-    <t>Waypoint numeration in Editor</t>
-  </si>
-  <si>
-    <t>Use one raycast for all objets (Input)</t>
-  </si>
-  <si>
-    <t>Make character go slower on far depths</t>
-  </si>
-  <si>
     <t>Waypoints only reachable for actions</t>
   </si>
   <si>
-    <t>Decission actions (like dialogs)</t>
-  </si>
-  <si>
     <t>Reduce cond stackallocs (they use JIT)</t>
   </si>
   <si>
-    <t>If you click on player many times when he's facing to a door it appears unselected in next room</t>
+    <t>Character 'Señor desubicado'</t>
+  </si>
+  <si>
+    <t>Questioning 'Mosca puñetera'</t>
+  </si>
+  <si>
+    <t>Fade to black between scenes</t>
   </si>
 </sst>
 </file>
@@ -6452,7 +6356,7 @@
 </file>
 
 <file path=xl/tables/table34.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D33" displayName="Table_TODO" name="Table_TODO" id="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D9" displayName="Table_TODO" name="Table_TODO" id="34">
   <tableColumns count="4">
     <tableColumn name="TASK" id="1"/>
     <tableColumn name="PRIO" id="2"/>
@@ -13585,13 +13489,13 @@
         <v>1559</v>
       </c>
       <c r="B2" s="70">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="C2" s="36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -13599,13 +13503,13 @@
         <v>1560</v>
       </c>
       <c r="B3" s="70">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="C3" s="36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -13613,13 +13517,13 @@
         <v>1561</v>
       </c>
       <c r="B4" s="70">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C4" s="36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13627,13 +13531,13 @@
         <v>1562</v>
       </c>
       <c r="B5" s="70">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="C5" s="36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13641,13 +13545,13 @@
         <v>1563</v>
       </c>
       <c r="B6" s="70">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="C6" s="36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13655,13 +13559,13 @@
         <v>1564</v>
       </c>
       <c r="B7" s="70">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="C7" s="36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -13669,10 +13573,10 @@
         <v>1565</v>
       </c>
       <c r="B8" s="70">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="C8" s="36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="36" t="b">
         <v>1</v>
@@ -13680,356 +13584,20 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>1566</v>
+        <v>1131</v>
       </c>
       <c r="B9" s="70">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C9" s="36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="37" t="s">
-        <v>1567</v>
-      </c>
-      <c r="B10" s="70">
-        <v>5.0</v>
-      </c>
-      <c r="C10" s="36" t="b">
         <v>0</v>
       </c>
-      <c r="D10" s="36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="37" t="s">
-        <v>1568</v>
-      </c>
-      <c r="B11" s="70">
-        <v>4.0</v>
-      </c>
-      <c r="C11" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="37" t="s">
-        <v>1569</v>
-      </c>
-      <c r="B12" s="70">
-        <v>1.0</v>
-      </c>
-      <c r="C12" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D12" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="37" t="s">
-        <v>1570</v>
-      </c>
-      <c r="B13" s="70">
-        <v>4.0</v>
-      </c>
-      <c r="C13" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D13" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="37" t="s">
-        <v>1571</v>
-      </c>
-      <c r="B14" s="70">
-        <v>1.0</v>
-      </c>
-      <c r="C14" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D14" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="37" t="s">
-        <v>1572</v>
-      </c>
-      <c r="B15" s="70">
-        <v>2.0</v>
-      </c>
-      <c r="C15" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D15" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="37" t="s">
-        <v>1573</v>
-      </c>
-      <c r="B16" s="70">
-        <v>3.0</v>
-      </c>
-      <c r="C16" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D16" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="37" t="s">
-        <v>1574</v>
-      </c>
-      <c r="B17" s="70">
-        <v>2.0</v>
-      </c>
-      <c r="C17" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D17" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="37" t="s">
-        <v>1575</v>
-      </c>
-      <c r="B18" s="70">
-        <v>2.0</v>
-      </c>
-      <c r="C18" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D18" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="37" t="s">
-        <v>1576</v>
-      </c>
-      <c r="B19" s="70">
-        <v>2.0</v>
-      </c>
-      <c r="C19" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D19" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="37" t="s">
-        <v>1577</v>
-      </c>
-      <c r="B20" s="70">
-        <v>2.0</v>
-      </c>
-      <c r="C20" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D20" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="37" t="s">
-        <v>1578</v>
-      </c>
-      <c r="B21" s="70">
-        <v>3.0</v>
-      </c>
-      <c r="C21" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D21" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="37" t="s">
-        <v>1579</v>
-      </c>
-      <c r="B22" s="70">
-        <v>2.0</v>
-      </c>
-      <c r="C22" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D22" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="37" t="s">
-        <v>1580</v>
-      </c>
-      <c r="B23" s="70">
-        <v>2.0</v>
-      </c>
-      <c r="C23" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D23" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="37" t="s">
-        <v>1581</v>
-      </c>
-      <c r="B24" s="70">
-        <v>2.0</v>
-      </c>
-      <c r="C24" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D24" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="37" t="s">
-        <v>1582</v>
-      </c>
-      <c r="B25" s="70">
-        <v>2.0</v>
-      </c>
-      <c r="C25" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D25" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="37" t="s">
-        <v>1583</v>
-      </c>
-      <c r="B26" s="70">
-        <v>2.0</v>
-      </c>
-      <c r="C26" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D26" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="37" t="s">
-        <v>1584</v>
-      </c>
-      <c r="B27" s="70">
-        <v>2.0</v>
-      </c>
-      <c r="C27" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D27" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="37" t="s">
-        <v>1585</v>
-      </c>
-      <c r="B28" s="70">
-        <v>2.0</v>
-      </c>
-      <c r="C28" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D28" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="37" t="s">
-        <v>1586</v>
-      </c>
-      <c r="B29" s="70">
-        <v>4.0</v>
-      </c>
-      <c r="C29" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29" s="36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="37" t="s">
-        <v>1587</v>
-      </c>
-      <c r="B30" s="70">
-        <v>2.0</v>
-      </c>
-      <c r="C30" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D30" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="37" t="s">
-        <v>1588</v>
-      </c>
-      <c r="B31" s="70">
-        <v>3.0</v>
-      </c>
-      <c r="C31" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" s="36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="37" t="s">
-        <v>1589</v>
-      </c>
-      <c r="B32" s="70">
-        <v>2.0</v>
-      </c>
-      <c r="C32" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D32" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="37" t="s">
-        <v>1131</v>
-      </c>
-      <c r="B33" s="70">
-        <v>5.0</v>
-      </c>
-      <c r="C33" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="D33" s="36" t="b">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B33">
+  <conditionalFormatting sqref="B2:B9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="formula" val="1"/>
@@ -14041,20 +13609,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A33">
+  <conditionalFormatting sqref="A2:A9">
     <cfRule type="expression" dxfId="5" priority="2">
       <formula>$C2=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="B2:B33">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="B2:B9">
       <formula1>AND(ISNUMBER(B2),(NOT(OR(NOT(ISERROR(DATEVALUE(B2))), AND(ISNUMBER(B2), LEFT(CELL("format", B2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -13585,7 +13585,7 @@
         <v>2.0</v>
       </c>
       <c r="C8" s="36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="36" t="b">
         <v>1</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -34,7 +34,7 @@
     <definedName name="Interval_Unchain_Conditions">ACTION_CONDS!$A$62:$I$91</definedName>
     <definedName name="Interval_Actions">ACTION_CONDS!$A$93:$N$222</definedName>
     <definedName name="Interval_Phrases">PHRASES!$A$1:$G$127</definedName>
-    <definedName name="Interval_sprites">SPRITES!$A$1:$C$61</definedName>
+    <definedName name="Interval_sprites">SPRITES!$A$1:$C$62</definedName>
     <definedName name="Interval_Items">ITEMS!$A$1:$J$43</definedName>
     <definedName name="Interval_Dialog_Options">DIALOGS!$A$23:$H$54</definedName>
     <definedName name="Interval_Memento">EVENTS!$A$43:$F$51</definedName>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5055" uniqueCount="1543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5117" uniqueCount="1570">
   <si>
     <t>NewItem</t>
   </si>
@@ -2624,6 +2624,12 @@
     <t>PATH</t>
   </si>
   <si>
+    <t>ATLAS</t>
+  </si>
+  <si>
+    <t>SPRITE_ATLAS_UI_0</t>
+  </si>
+  <si>
     <t>SPRITE_CURSOR_NORMAL</t>
   </si>
   <si>
@@ -2669,6 +2675,9 @@
     <t>BACKGROUND_HIVE1_ROOM1</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_HIVE1_0</t>
+  </si>
+  <si>
     <t>SPRITE_HIVE1_CHEST_CLOSED</t>
   </si>
   <si>
@@ -2681,6 +2690,9 @@
     <t>SPRITE_PICKABLE_CARDS</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_PICKABLE_0</t>
+  </si>
+  <si>
     <t>SPRITE_ITEM_DECO_BED_LAYER</t>
   </si>
   <si>
@@ -2693,15 +2705,24 @@
     <t>BACKGROUND_HIVE1_CORRIDOR1</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_HIVE1_1</t>
+  </si>
+  <si>
     <t>SPRITE_HIVE1_REME_IDLE</t>
   </si>
   <si>
     <t>BACKGROUND_HIVE1_HALL1</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_HIVE1_2</t>
+  </si>
+  <si>
     <t>BACKGROUND_HIVE1_WC</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_HIVE1_3</t>
+  </si>
+  <si>
     <t>SPRITE_MEMENTO_JOB</t>
   </si>
   <si>
@@ -2711,39 +2732,63 @@
     <t>BACKGROUND_HIVE1_CORRIDOR1_NIGHT</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_HIVE1_4</t>
+  </si>
+  <si>
     <t>BACKGROUND_HIVE1_HALL1_N</t>
   </si>
   <si>
     <t>BACKGROUND_HIVE1_HALL1_NIGHT</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_HIVE1_5</t>
+  </si>
+  <si>
     <t>BACKGROUND_HIVE1_WC_N</t>
   </si>
   <si>
     <t>BACKGROUND_HIVE1_WC_NIGHT</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_HIVE1_6</t>
+  </si>
+  <si>
     <t>BACKGROUND_CITY1_STREET1</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_CITY1_1</t>
+  </si>
+  <si>
     <t>BACKGROUND_CITY1_STREET1_N</t>
   </si>
   <si>
     <t>BACKGROUND_CITY1_STREET1_NIGHT</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_CITY1_2</t>
+  </si>
+  <si>
     <t>BACKGROUND_CITY1_STREET2</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_CITY2_1</t>
+  </si>
+  <si>
     <t>BACKGROUND_CITY1_STREET2_N</t>
   </si>
   <si>
     <t>BACKGROUND_CITY1_STREET2_NIGHT</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_CITY2_2</t>
+  </si>
+  <si>
     <t>BACKGROUND_PHARMACY1</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_PHARMACY1_1</t>
+  </si>
+  <si>
     <t>SPRITE_PHARMACY_QUEUE_1</t>
   </si>
   <si>
@@ -2753,9 +2798,15 @@
     <t>BACKGROUND_CITY1_MANYO</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_MANYO_0</t>
+  </si>
+  <si>
     <t>BACKGROUND_CITY1_MANYO_NIGHT</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_MANYO_1</t>
+  </si>
+  <si>
     <t>SPRITE_MEMENTO_RECIPE</t>
   </si>
   <si>
@@ -2765,28 +2816,58 @@
     <t>BACKGROUND_HIVE1_BACKALLEY</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_HIVE1_7</t>
+  </si>
+  <si>
     <t>BACKGROUND_BACKALLEY_NIGHT</t>
   </si>
   <si>
     <t>BACKGROUND_HIVE1_BACKALLEY_NIGHT</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_HIVE1_8</t>
+  </si>
+  <si>
     <t>SPRITE_PICKABLE_SHOELACE</t>
   </si>
   <si>
     <t>BACKGROUND_CITY1_SOUTH_STREET_1</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_CITY3_1</t>
+  </si>
+  <si>
     <t>BACKGROUND_CITY1_SOUTH_STREET_1_NIGHT</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_CITY3_2</t>
+  </si>
+  <si>
     <t>BACKGROUND_CITY1_SOUTH_STREET_2</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_CITY4_1</t>
+  </si>
+  <si>
     <t>BACKGROUND_CITY1_SOUTH_STREET_2_NIGHT</t>
   </si>
   <si>
+    <t>SPRITE_ATLAS_CITY4_2</t>
+  </si>
+  <si>
+    <t>SPRITE_ATLAS_EXTRAPERLO1</t>
+  </si>
+  <si>
     <t>SPRITE_EXTRAPERLO_BAR_FOREGROUND</t>
+  </si>
+  <si>
+    <t>SPRITE_ATLAS_FIK_1</t>
+  </si>
+  <si>
+    <t>SPRITE_MAINCHAR_STEADY</t>
+  </si>
+  <si>
+    <t>SPRITE_ATLAS_MAINCHAR_1</t>
   </si>
   <si>
     <t>SOUND_ID</t>
@@ -5990,11 +6071,12 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C61" displayName="Table_sprites" name="Table_sprites" id="11">
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D62" displayName="Table_sprites" name="Table_sprites" id="11">
+  <tableColumns count="4">
     <tableColumn name="N" id="1"/>
     <tableColumn name="SPRITE_ID" id="2"/>
     <tableColumn name="PATH" id="3"/>
+    <tableColumn name="ATLAS" id="4"/>
   </tableColumns>
   <tableStyleInfo name="SPRITES-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -6839,13 +6921,13 @@
         <v>46</v>
       </c>
       <c r="B1" s="59" t="s">
-        <v>1017</v>
+        <v>1044</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>1018</v>
+        <v>1045</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>1019</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="2">
@@ -6868,10 +6950,10 @@
         <v>316</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1020</v>
+        <v>1047</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>1020</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="4">
@@ -6880,13 +6962,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1021</v>
+        <v>1048</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1022</v>
+        <v>1049</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>1023</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="5">
@@ -6895,13 +6977,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1024</v>
+        <v>1051</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>1025</v>
+        <v>1052</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>1026</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="6">
@@ -6910,13 +6992,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1027</v>
+        <v>1054</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>1028</v>
+        <v>1055</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>1029</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="7">
@@ -6928,10 +7010,10 @@
         <v>319</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>1030</v>
+        <v>1057</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>1031</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="8">
@@ -6943,10 +7025,10 @@
         <v>340</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1032</v>
+        <v>1059</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>1032</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="9">
@@ -6958,10 +7040,10 @@
         <v>347</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>1033</v>
+        <v>1060</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>1034</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="10">
@@ -6973,10 +7055,10 @@
         <v>325</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>1035</v>
+        <v>1062</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>1036</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="11">
@@ -6985,13 +7067,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1037</v>
+        <v>1064</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>1038</v>
+        <v>1065</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>1039</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="12">
@@ -7000,13 +7082,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1040</v>
+        <v>1067</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>1041</v>
+        <v>1068</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>1042</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="13">
@@ -7018,10 +7100,10 @@
         <v>330</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>1043</v>
+        <v>1070</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>1044</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="14">
@@ -7033,10 +7115,10 @@
         <v>337</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>1045</v>
+        <v>1072</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>1046</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="15">
@@ -7045,13 +7127,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1047</v>
+        <v>1074</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>1048</v>
+        <v>1075</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>1049</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="16">
@@ -7063,10 +7145,10 @@
         <v>350</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>1050</v>
+        <v>1077</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>1051</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="17">
@@ -7078,10 +7160,10 @@
         <v>355</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>1052</v>
+        <v>1079</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>1053</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="18">
@@ -7093,10 +7175,10 @@
         <v>358</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>1054</v>
+        <v>1081</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>1055</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="19">
@@ -7108,10 +7190,10 @@
         <v>362</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>1056</v>
+        <v>1083</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>1057</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="20">
@@ -7123,10 +7205,10 @@
         <v>365</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>1058</v>
+        <v>1085</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>1059</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="21">
@@ -7138,10 +7220,10 @@
         <v>368</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>1060</v>
+        <v>1087</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>1061</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="22">
@@ -7153,10 +7235,10 @@
         <v>370</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>1062</v>
+        <v>1089</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>1063</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="23">
@@ -7168,10 +7250,10 @@
         <v>372</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>1064</v>
+        <v>1091</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>1065</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="24">
@@ -7183,10 +7265,10 @@
         <v>374</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>1066</v>
+        <v>1093</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>1067</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="25">
@@ -7198,10 +7280,10 @@
         <v>376</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>1068</v>
+        <v>1095</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>1069</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="26">
@@ -7213,10 +7295,10 @@
         <v>380</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>1070</v>
+        <v>1097</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>1071</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="27">
@@ -7228,10 +7310,10 @@
         <v>385</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>1072</v>
+        <v>1099</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>1073</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="28">
@@ -7243,10 +7325,10 @@
         <v>387</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>1074</v>
+        <v>1101</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="29">
@@ -7258,10 +7340,10 @@
         <v>391</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>1076</v>
+        <v>1103</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>1077</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="30">
@@ -7270,13 +7352,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>1078</v>
+        <v>1105</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>1079</v>
+        <v>1106</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>1080</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="31">
@@ -7288,10 +7370,10 @@
         <v>395</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>1081</v>
+        <v>1108</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>1082</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="32">
@@ -7303,10 +7385,10 @@
         <v>397</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>1083</v>
+        <v>1110</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>1084</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="33">
@@ -7315,13 +7397,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>1085</v>
+        <v>1112</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>43</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>1086</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="34">
@@ -7333,10 +7415,10 @@
         <v>401</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>1087</v>
+        <v>1114</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>1088</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="35">
@@ -7348,10 +7430,10 @@
         <v>405</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>1089</v>
+        <v>1116</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>1090</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="36">
@@ -7363,10 +7445,10 @@
         <v>408</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>1091</v>
+        <v>1118</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>1092</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="37">
@@ -7378,10 +7460,10 @@
         <v>413</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>1093</v>
+        <v>1120</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>1094</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="38">
@@ -7393,10 +7475,10 @@
         <v>418</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>1095</v>
+        <v>1122</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>1096</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="39">
@@ -7408,10 +7490,10 @@
         <v>422</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>1097</v>
+        <v>1124</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>1097</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="40">
@@ -7423,10 +7505,10 @@
         <v>426</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>1098</v>
+        <v>1125</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>1099</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="41">
@@ -7438,10 +7520,10 @@
         <v>430</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>1100</v>
+        <v>1127</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>1101</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="42">
@@ -7453,10 +7535,10 @@
         <v>433</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>1102</v>
+        <v>1129</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>1103</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="43">
@@ -7468,10 +7550,10 @@
         <v>11</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>1102</v>
+        <v>1129</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>1104</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="44">
@@ -7483,10 +7565,10 @@
         <v>438</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>1105</v>
+        <v>1132</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>1105</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="45">
@@ -7498,10 +7580,10 @@
         <v>441</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>1107</v>
+        <v>1134</v>
       </c>
     </row>
   </sheetData>
@@ -7535,22 +7617,22 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1108</v>
+        <v>1135</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1109</v>
+        <v>1136</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1110</v>
+        <v>1137</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1111</v>
+        <v>1138</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1112</v>
+        <v>1139</v>
       </c>
       <c r="G1" s="61" t="s">
-        <v>1113</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="2">
@@ -7565,10 +7647,10 @@
         <v>0.0</v>
       </c>
       <c r="D2" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>1114</v>
+        <v>1141</v>
       </c>
       <c r="F2" s="62"/>
       <c r="G2" s="37"/>
@@ -7585,16 +7667,16 @@
         <v>0.0</v>
       </c>
       <c r="D3" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>1116</v>
+        <v>1143</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>1117</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="4">
@@ -7609,16 +7691,16 @@
         <v>0.0</v>
       </c>
       <c r="D4" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>1118</v>
+        <v>1145</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1119</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="5">
@@ -7633,16 +7715,16 @@
         <v>0.0</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>1120</v>
+        <v>1147</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1121</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="6">
@@ -7651,22 +7733,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1122</v>
+        <v>1149</v>
       </c>
       <c r="C6" s="36">
         <v>0.0</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>1123</v>
+        <v>1150</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>1124</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="7">
@@ -7675,22 +7757,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1125</v>
+        <v>1152</v>
       </c>
       <c r="C7" s="36">
         <v>0.0</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>1126</v>
+        <v>1153</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>1127</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="8">
@@ -7705,16 +7787,16 @@
         <v>0.0</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>1128</v>
+        <v>1155</v>
       </c>
       <c r="G8" s="37" t="s">
-        <v>1129</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="9">
@@ -7723,22 +7805,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1130</v>
+        <v>1157</v>
       </c>
       <c r="C9" s="36">
         <v>0.0</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>1131</v>
+        <v>1158</v>
       </c>
       <c r="G9" s="37" t="s">
-        <v>1132</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="10">
@@ -7747,22 +7829,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1133</v>
+        <v>1160</v>
       </c>
       <c r="C10" s="36">
         <v>0.0</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>1134</v>
+        <v>1161</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1135</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="11">
@@ -7771,22 +7853,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1136</v>
+        <v>1163</v>
       </c>
       <c r="C11" s="36">
         <v>1.0</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>1137</v>
+        <v>1164</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>1138</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="12">
@@ -7795,22 +7877,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1139</v>
+        <v>1166</v>
       </c>
       <c r="C12" s="36">
         <v>0.0</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1140</v>
+        <v>1167</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1141</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="13">
@@ -7819,22 +7901,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1142</v>
+        <v>1169</v>
       </c>
       <c r="C13" s="36">
         <v>0.0</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>1143</v>
+        <v>1170</v>
       </c>
       <c r="G13" s="37" t="s">
-        <v>1144</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="14">
@@ -7843,22 +7925,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1145</v>
+        <v>1172</v>
       </c>
       <c r="C14" s="36">
         <v>1.0</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>1146</v>
+        <v>1173</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>1147</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="15">
@@ -7867,22 +7949,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>1148</v>
+        <v>1175</v>
       </c>
       <c r="C15" s="36">
         <v>1.0</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1149</v>
+        <v>1176</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1150</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="16">
@@ -7891,22 +7973,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>959</v>
+        <v>986</v>
       </c>
       <c r="C16" s="36">
         <v>1.0</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>1151</v>
+        <v>1178</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>1152</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="17">
@@ -7915,22 +7997,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="C17" s="36">
         <v>0.0</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>1153</v>
+        <v>1180</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>1154</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="18">
@@ -7939,22 +8021,22 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1155</v>
+        <v>1182</v>
       </c>
       <c r="C18" s="36">
         <v>0.0</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>1156</v>
+        <v>1183</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>1157</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="19">
@@ -7969,16 +8051,16 @@
         <v>0.0</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>1158</v>
+        <v>1185</v>
       </c>
       <c r="G19" s="37" t="s">
-        <v>1159</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="20">
@@ -7993,16 +8075,16 @@
         <v>0.0</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>1160</v>
+        <v>1187</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>1161</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="21">
@@ -8017,16 +8099,16 @@
         <v>0.0</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>1162</v>
+        <v>1189</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>1163</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="22">
@@ -8041,16 +8123,16 @@
         <v>0.0</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1165</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="23">
@@ -8065,16 +8147,16 @@
         <v>0.0</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>1166</v>
+        <v>1193</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>1167</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="24">
@@ -8089,16 +8171,16 @@
         <v>0.0</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1168</v>
+        <v>1195</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1169</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="25">
@@ -8113,16 +8195,16 @@
         <v>0.0</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="G25" s="37" t="s">
-        <v>1171</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="26">
@@ -8137,16 +8219,16 @@
         <v>0.0</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>1172</v>
+        <v>1199</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>1173</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="27">
@@ -8155,22 +8237,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1174</v>
+        <v>1201</v>
       </c>
       <c r="C27" s="36">
         <v>0.0</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>1175</v>
+        <v>1202</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>1176</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="28">
@@ -8179,22 +8261,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1177</v>
+        <v>1204</v>
       </c>
       <c r="C28" s="36">
         <v>1.0</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>1178</v>
+        <v>1205</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>1179</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="29">
@@ -8203,22 +8285,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>1012</v>
+        <v>1039</v>
       </c>
       <c r="C29" s="36">
         <v>0.0</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>1180</v>
+        <v>1207</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>1181</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="30">
@@ -8227,22 +8309,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C30" s="36">
         <v>0.0</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>1182</v>
+        <v>1209</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>1183</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="31">
@@ -8251,22 +8333,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1016</v>
+        <v>1043</v>
       </c>
       <c r="C31" s="36">
         <v>0.0</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1184</v>
+        <v>1211</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="32">
@@ -8281,16 +8363,16 @@
         <v>0.0</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>1186</v>
+        <v>1213</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>1187</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="33">
@@ -8299,22 +8381,22 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>964</v>
+        <v>991</v>
       </c>
       <c r="C33" s="36">
         <v>0.0</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1188</v>
+        <v>1215</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1189</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="34">
@@ -8323,22 +8405,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1190</v>
+        <v>1217</v>
       </c>
       <c r="C34" s="36">
         <v>1.0</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>1191</v>
+        <v>1218</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>1192</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="35">
@@ -8347,22 +8429,22 @@
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1193</v>
+        <v>1220</v>
       </c>
       <c r="C35" s="36">
         <v>1.0</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>1194</v>
+        <v>1221</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>1195</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="36">
@@ -8377,16 +8459,16 @@
         <v>0.0</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>1196</v>
+        <v>1223</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>1197</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="37">
@@ -8395,22 +8477,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1198</v>
+        <v>1225</v>
       </c>
       <c r="C37" s="36">
         <v>0.0</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>1199</v>
+        <v>1226</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>1200</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="38">
@@ -8419,22 +8501,22 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1201</v>
+        <v>1228</v>
       </c>
       <c r="C38" s="36">
         <v>1.0</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>1202</v>
+        <v>1229</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>1203</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="39">
@@ -8443,22 +8525,22 @@
         <v>37</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1204</v>
+        <v>1231</v>
       </c>
       <c r="C39" s="36">
         <v>0.0</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1205</v>
+        <v>1232</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1206</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="40">
@@ -8467,22 +8549,22 @@
         <v>38</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1207</v>
+        <v>1234</v>
       </c>
       <c r="C40" s="36">
         <v>1.0</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1208</v>
+        <v>1235</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1209</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="41">
@@ -8491,22 +8573,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1210</v>
+        <v>1237</v>
       </c>
       <c r="C41" s="36">
         <v>0.0</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>1211</v>
+        <v>1238</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>1212</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="42">
@@ -8515,22 +8597,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1213</v>
+        <v>1240</v>
       </c>
       <c r="C42" s="36">
         <v>1.0</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>1214</v>
+        <v>1241</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>1215</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="43">
@@ -8539,22 +8621,22 @@
         <v>41</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1216</v>
+        <v>1243</v>
       </c>
       <c r="C43" s="36">
         <v>0.0</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>1217</v>
+        <v>1244</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>1218</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="44">
@@ -8563,22 +8645,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1219</v>
+        <v>1246</v>
       </c>
       <c r="C44" s="36">
         <v>1.0</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>1220</v>
+        <v>1247</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>1221</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="45">
@@ -8587,22 +8669,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1222</v>
+        <v>1249</v>
       </c>
       <c r="C45" s="36">
         <v>0.0</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>1223</v>
+        <v>1250</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>1224</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="46">
@@ -8611,22 +8693,22 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1225</v>
+        <v>1252</v>
       </c>
       <c r="C46" s="36">
         <v>1.0</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1226</v>
+        <v>1253</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1227</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="47">
@@ -8635,22 +8717,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1228</v>
+        <v>1255</v>
       </c>
       <c r="C47" s="36">
         <v>1.0</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>1229</v>
+        <v>1256</v>
       </c>
       <c r="G47" s="37" t="s">
-        <v>1230</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="48">
@@ -8659,22 +8741,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1231</v>
+        <v>1258</v>
       </c>
       <c r="C48" s="36">
         <v>0.0</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>1232</v>
+        <v>1259</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>1233</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="49">
@@ -8683,22 +8765,22 @@
         <v>47</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1234</v>
+        <v>1261</v>
       </c>
       <c r="C49" s="36">
         <v>1.0</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>1235</v>
+        <v>1262</v>
       </c>
       <c r="G49" s="37" t="s">
-        <v>1236</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="50">
@@ -8707,22 +8789,22 @@
         <v>48</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1237</v>
+        <v>1264</v>
       </c>
       <c r="C50" s="36">
         <v>0.0</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>1238</v>
+        <v>1265</v>
       </c>
       <c r="G50" s="37" t="s">
-        <v>1239</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="51">
@@ -8731,22 +8813,22 @@
         <v>49</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1240</v>
+        <v>1267</v>
       </c>
       <c r="C51" s="36">
         <v>0.0</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>1241</v>
+        <v>1268</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>1242</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="52">
@@ -8755,22 +8837,22 @@
         <v>50</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1243</v>
+        <v>1270</v>
       </c>
       <c r="C52" s="36">
         <v>1.0</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>1244</v>
+        <v>1271</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>1245</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="53">
@@ -8779,22 +8861,22 @@
         <v>51</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1246</v>
+        <v>1273</v>
       </c>
       <c r="C53" s="36">
         <v>1.0</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>1247</v>
+        <v>1274</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>1248</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="54">
@@ -8803,22 +8885,22 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1249</v>
+        <v>1276</v>
       </c>
       <c r="C54" s="36">
         <v>1.0</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>1250</v>
+        <v>1277</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>1251</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="55">
@@ -8827,22 +8909,22 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1252</v>
+        <v>1279</v>
       </c>
       <c r="C55" s="36">
         <v>0.0</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>1253</v>
+        <v>1280</v>
       </c>
       <c r="G55" s="37" t="s">
-        <v>1254</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="56">
@@ -8851,22 +8933,22 @@
         <v>54</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>977</v>
+        <v>1004</v>
       </c>
       <c r="C56" s="36">
         <v>0.0</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>1255</v>
+        <v>1282</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>1256</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="57">
@@ -8875,22 +8957,22 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1257</v>
+        <v>1284</v>
       </c>
       <c r="C57" s="36">
         <v>0.0</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>1258</v>
+        <v>1285</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>1259</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="58">
@@ -8899,22 +8981,22 @@
         <v>56</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>978</v>
+        <v>1005</v>
       </c>
       <c r="C58" s="36">
         <v>1.0</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>1260</v>
+        <v>1287</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>1261</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="59">
@@ -8929,16 +9011,16 @@
         <v>0.0</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>1262</v>
+        <v>1289</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>1263</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="60">
@@ -8947,22 +9029,22 @@
         <v>58</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1264</v>
+        <v>1291</v>
       </c>
       <c r="C60" s="36">
         <v>0.0</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>1114</v>
+        <v>1141</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>1265</v>
+        <v>1292</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>1266</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="61">
@@ -8971,22 +9053,22 @@
         <v>59</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1267</v>
+        <v>1294</v>
       </c>
       <c r="C61" s="36">
         <v>0.0</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>1114</v>
+        <v>1141</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>1268</v>
+        <v>1295</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>1269</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="62">
@@ -8995,22 +9077,22 @@
         <v>60</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1270</v>
+        <v>1297</v>
       </c>
       <c r="C62" s="36">
         <v>0.0</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E62" s="44" t="s">
-        <v>1114</v>
+        <v>1141</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>1271</v>
+        <v>1298</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>1272</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="63">
@@ -9025,16 +9107,16 @@
         <v>0.0</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>1273</v>
+        <v>1300</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>1274</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="64">
@@ -9043,22 +9125,22 @@
         <v>62</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1275</v>
+        <v>1302</v>
       </c>
       <c r="C64" s="36">
         <v>0.0</v>
       </c>
       <c r="D64" s="38" t="s">
-        <v>904</v>
+        <v>931</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F64" s="37" t="s">
-        <v>1276</v>
+        <v>1303</v>
       </c>
       <c r="G64" s="37" t="s">
-        <v>1276</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="65">
@@ -9067,22 +9149,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1277</v>
+        <v>1304</v>
       </c>
       <c r="C65" s="36">
         <v>0.0</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>905</v>
+        <v>932</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>1278</v>
+        <v>1305</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>1279</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="66">
@@ -9091,22 +9173,22 @@
         <v>64</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1280</v>
+        <v>1307</v>
       </c>
       <c r="C66" s="36">
         <v>0.0</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>906</v>
+        <v>933</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>1281</v>
+        <v>1308</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>1282</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="67">
@@ -9115,22 +9197,22 @@
         <v>65</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1283</v>
+        <v>1310</v>
       </c>
       <c r="C67" s="36">
         <v>0.0</v>
       </c>
       <c r="D67" s="38" t="s">
-        <v>907</v>
+        <v>934</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>1284</v>
+        <v>1311</v>
       </c>
       <c r="G67" s="37" t="s">
-        <v>1285</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="68">
@@ -9139,22 +9221,22 @@
         <v>66</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1286</v>
+        <v>1313</v>
       </c>
       <c r="C68" s="36">
         <v>0.0</v>
       </c>
       <c r="D68" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>1287</v>
+        <v>1314</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>1288</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="69">
@@ -9163,22 +9245,22 @@
         <v>67</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1289</v>
+        <v>1316</v>
       </c>
       <c r="C69" s="36">
         <v>1.0</v>
       </c>
       <c r="D69" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E69" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>1290</v>
+        <v>1317</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>1291</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="70">
@@ -9187,22 +9269,22 @@
         <v>68</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1292</v>
+        <v>1319</v>
       </c>
       <c r="C70" s="36">
         <v>0.0</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E70" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>1293</v>
+        <v>1320</v>
       </c>
       <c r="G70" s="37" t="s">
-        <v>1294</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="71">
@@ -9211,22 +9293,22 @@
         <v>69</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1295</v>
+        <v>1322</v>
       </c>
       <c r="C71" s="36">
         <v>1.0</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E71" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>1296</v>
+        <v>1323</v>
       </c>
       <c r="G71" s="37" t="s">
-        <v>1297</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="72">
@@ -9235,22 +9317,22 @@
         <v>70</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1298</v>
+        <v>1325</v>
       </c>
       <c r="C72" s="36">
         <v>0.0</v>
       </c>
       <c r="D72" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E72" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F72" s="37" t="s">
-        <v>1299</v>
+        <v>1326</v>
       </c>
       <c r="G72" s="37" t="s">
-        <v>1300</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="73">
@@ -9259,22 +9341,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>1301</v>
+        <v>1328</v>
       </c>
       <c r="C73" s="36">
         <v>1.0</v>
       </c>
       <c r="D73" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E73" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F73" s="37" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
       <c r="G73" s="37" t="s">
-        <v>1303</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="74">
@@ -9283,22 +9365,22 @@
         <v>72</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>1304</v>
+        <v>1331</v>
       </c>
       <c r="C74" s="36">
         <v>0.0</v>
       </c>
       <c r="D74" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E74" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F74" s="37" t="s">
-        <v>1305</v>
+        <v>1332</v>
       </c>
       <c r="G74" s="37" t="s">
-        <v>1306</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="75">
@@ -9307,22 +9389,22 @@
         <v>73</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>1307</v>
+        <v>1334</v>
       </c>
       <c r="C75" s="36">
         <v>1.0</v>
       </c>
       <c r="D75" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E75" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F75" s="37" t="s">
-        <v>1308</v>
+        <v>1335</v>
       </c>
       <c r="G75" s="37" t="s">
-        <v>1309</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="76">
@@ -9331,22 +9413,22 @@
         <v>74</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1310</v>
+        <v>1337</v>
       </c>
       <c r="C76" s="36">
         <v>0.0</v>
       </c>
       <c r="D76" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E76" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F76" s="37" t="s">
-        <v>1311</v>
+        <v>1338</v>
       </c>
       <c r="G76" s="37" t="s">
-        <v>1312</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="77">
@@ -9355,22 +9437,22 @@
         <v>75</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1313</v>
+        <v>1340</v>
       </c>
       <c r="C77" s="36">
         <v>1.0</v>
       </c>
       <c r="D77" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E77" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F77" s="37" t="s">
-        <v>1314</v>
+        <v>1341</v>
       </c>
       <c r="G77" s="37" t="s">
-        <v>1315</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="78">
@@ -9379,22 +9461,22 @@
         <v>76</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>1316</v>
+        <v>1343</v>
       </c>
       <c r="C78" s="36">
         <v>0.0</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E78" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F78" s="37" t="s">
-        <v>1317</v>
+        <v>1344</v>
       </c>
       <c r="G78" s="37" t="s">
-        <v>1318</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="79">
@@ -9403,22 +9485,22 @@
         <v>77</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>989</v>
+        <v>1016</v>
       </c>
       <c r="C79" s="36">
         <v>0.0</v>
       </c>
       <c r="D79" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E79" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F79" s="37" t="s">
-        <v>1319</v>
+        <v>1346</v>
       </c>
       <c r="G79" s="37" t="s">
-        <v>1320</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="80">
@@ -9427,22 +9509,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>1321</v>
+        <v>1348</v>
       </c>
       <c r="C80" s="36">
         <v>1.0</v>
       </c>
       <c r="D80" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E80" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F80" s="37" t="s">
-        <v>1322</v>
+        <v>1349</v>
       </c>
       <c r="G80" s="37" t="s">
-        <v>1323</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="81">
@@ -9451,22 +9533,22 @@
         <v>79</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1324</v>
+        <v>1351</v>
       </c>
       <c r="C81" s="36">
         <v>1.0</v>
       </c>
       <c r="D81" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E81" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F81" s="37" t="s">
-        <v>1325</v>
+        <v>1352</v>
       </c>
       <c r="G81" s="37" t="s">
-        <v>1326</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="82">
@@ -9475,22 +9557,22 @@
         <v>80</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>1327</v>
+        <v>1354</v>
       </c>
       <c r="C82" s="36">
         <v>1.0</v>
       </c>
       <c r="D82" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E82" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F82" s="37" t="s">
-        <v>1328</v>
+        <v>1355</v>
       </c>
       <c r="G82" s="37" t="s">
-        <v>1329</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="83">
@@ -9499,22 +9581,22 @@
         <v>81</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>1330</v>
+        <v>1357</v>
       </c>
       <c r="C83" s="36">
         <v>0.0</v>
       </c>
       <c r="D83" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E83" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F83" s="37" t="s">
-        <v>1331</v>
+        <v>1358</v>
       </c>
       <c r="G83" s="37" t="s">
-        <v>1332</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="84">
@@ -9523,22 +9605,22 @@
         <v>82</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>1333</v>
+        <v>1360</v>
       </c>
       <c r="C84" s="36">
         <v>0.0</v>
       </c>
       <c r="D84" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E84" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F84" s="37" t="s">
-        <v>1334</v>
+        <v>1361</v>
       </c>
       <c r="G84" s="37" t="s">
-        <v>1335</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="85">
@@ -9547,22 +9629,22 @@
         <v>83</v>
       </c>
       <c r="B85" s="36" t="s">
-        <v>1336</v>
+        <v>1363</v>
       </c>
       <c r="C85" s="36">
         <v>0.0</v>
       </c>
       <c r="D85" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E85" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>1337</v>
+        <v>1364</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>1338</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="86">
@@ -9577,16 +9659,16 @@
         <v>0.0</v>
       </c>
       <c r="D86" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E86" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F86" s="37" t="s">
-        <v>1339</v>
+        <v>1366</v>
       </c>
       <c r="G86" s="37" t="s">
-        <v>1340</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="87">
@@ -9601,16 +9683,16 @@
         <v>0.0</v>
       </c>
       <c r="D87" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E87" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F87" s="37" t="s">
-        <v>1341</v>
+        <v>1368</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>1341</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="88">
@@ -9625,16 +9707,16 @@
         <v>0.0</v>
       </c>
       <c r="D88" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E88" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F88" s="37" t="s">
-        <v>1342</v>
+        <v>1369</v>
       </c>
       <c r="G88" s="37" t="s">
-        <v>1343</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="89">
@@ -9649,16 +9731,16 @@
         <v>0.0</v>
       </c>
       <c r="D89" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E89" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F89" s="37" t="s">
-        <v>1344</v>
+        <v>1371</v>
       </c>
       <c r="G89" s="37" t="s">
-        <v>1345</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="90">
@@ -9673,16 +9755,16 @@
         <v>0.0</v>
       </c>
       <c r="D90" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E90" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F90" s="37" t="s">
-        <v>1346</v>
+        <v>1373</v>
       </c>
       <c r="G90" s="37" t="s">
-        <v>1347</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="91">
@@ -9697,16 +9779,16 @@
         <v>0.0</v>
       </c>
       <c r="D91" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E91" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F91" s="37" t="s">
-        <v>1348</v>
+        <v>1375</v>
       </c>
       <c r="G91" s="37" t="s">
-        <v>1349</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="92">
@@ -9721,16 +9803,16 @@
         <v>0.0</v>
       </c>
       <c r="D92" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E92" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F92" s="37" t="s">
-        <v>1350</v>
+        <v>1377</v>
       </c>
       <c r="G92" s="37" t="s">
-        <v>1351</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="93">
@@ -9745,16 +9827,16 @@
         <v>0.0</v>
       </c>
       <c r="D93" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E93" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F93" s="37" t="s">
-        <v>1352</v>
+        <v>1379</v>
       </c>
       <c r="G93" s="37" t="s">
-        <v>1353</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="94">
@@ -9769,16 +9851,16 @@
         <v>0.0</v>
       </c>
       <c r="D94" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E94" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F94" s="37" t="s">
-        <v>1354</v>
+        <v>1381</v>
       </c>
       <c r="G94" s="37" t="s">
-        <v>1355</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="95">
@@ -9793,16 +9875,16 @@
         <v>0.0</v>
       </c>
       <c r="D95" s="38" t="s">
-        <v>902</v>
+        <v>929</v>
       </c>
       <c r="E95" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F95" s="37" t="s">
-        <v>1356</v>
+        <v>1383</v>
       </c>
       <c r="G95" s="37" t="s">
-        <v>1357</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="96">
@@ -9817,16 +9899,16 @@
         <v>0.0</v>
       </c>
       <c r="D96" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E96" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F96" s="37" t="s">
-        <v>1358</v>
+        <v>1385</v>
       </c>
       <c r="G96" s="37" t="s">
-        <v>1359</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="97">
@@ -9841,16 +9923,16 @@
         <v>0.0</v>
       </c>
       <c r="D97" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E97" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F97" s="37" t="s">
-        <v>1360</v>
+        <v>1387</v>
       </c>
       <c r="G97" s="37" t="s">
-        <v>1361</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="98">
@@ -9865,16 +9947,16 @@
         <v>0.0</v>
       </c>
       <c r="D98" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E98" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F98" s="37" t="s">
-        <v>1362</v>
+        <v>1389</v>
       </c>
       <c r="G98" s="37" t="s">
-        <v>1363</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="99">
@@ -9889,16 +9971,16 @@
         <v>0.0</v>
       </c>
       <c r="D99" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E99" s="44" t="s">
-        <v>1114</v>
+        <v>1141</v>
       </c>
       <c r="F99" s="37" t="s">
-        <v>1364</v>
+        <v>1391</v>
       </c>
       <c r="G99" s="37" t="s">
-        <v>1365</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="100">
@@ -9913,16 +9995,16 @@
         <v>0.0</v>
       </c>
       <c r="D100" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E100" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F100" s="37" t="s">
-        <v>1366</v>
+        <v>1393</v>
       </c>
       <c r="G100" s="37" t="s">
-        <v>1367</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="101">
@@ -9937,16 +10019,16 @@
         <v>0.0</v>
       </c>
       <c r="D101" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E101" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F101" s="37" t="s">
-        <v>1368</v>
+        <v>1395</v>
       </c>
       <c r="G101" s="37" t="s">
-        <v>1369</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="102">
@@ -9961,16 +10043,16 @@
         <v>0.0</v>
       </c>
       <c r="D102" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E102" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F102" s="37" t="s">
-        <v>1370</v>
+        <v>1397</v>
       </c>
       <c r="G102" s="37" t="s">
-        <v>1371</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="103">
@@ -9979,22 +10061,22 @@
         <v>101</v>
       </c>
       <c r="B103" s="36" t="s">
-        <v>1372</v>
+        <v>1399</v>
       </c>
       <c r="C103" s="36">
         <v>0.0</v>
       </c>
       <c r="D103" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E103" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F103" s="37" t="s">
-        <v>1373</v>
+        <v>1400</v>
       </c>
       <c r="G103" s="37" t="s">
-        <v>1374</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="104">
@@ -10003,22 +10085,22 @@
         <v>102</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>1375</v>
+        <v>1402</v>
       </c>
       <c r="C104" s="36">
         <v>1.0</v>
       </c>
       <c r="D104" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E104" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F104" s="37" t="s">
-        <v>1376</v>
+        <v>1403</v>
       </c>
       <c r="G104" s="37" t="s">
-        <v>1377</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="105">
@@ -10027,22 +10109,22 @@
         <v>103</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>1378</v>
+        <v>1405</v>
       </c>
       <c r="C105" s="36">
         <v>0.0</v>
       </c>
       <c r="D105" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E105" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F105" s="37" t="s">
-        <v>1379</v>
+        <v>1406</v>
       </c>
       <c r="G105" s="37" t="s">
-        <v>1380</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="106">
@@ -10051,22 +10133,22 @@
         <v>104</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>1381</v>
+        <v>1408</v>
       </c>
       <c r="C106" s="36">
         <v>1.0</v>
       </c>
       <c r="D106" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E106" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F106" s="37" t="s">
-        <v>1382</v>
+        <v>1409</v>
       </c>
       <c r="G106" s="37" t="s">
-        <v>1383</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="107">
@@ -10075,22 +10157,22 @@
         <v>105</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>1384</v>
+        <v>1411</v>
       </c>
       <c r="C107" s="36">
         <v>0.0</v>
       </c>
       <c r="D107" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E107" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F107" s="37" t="s">
-        <v>1385</v>
+        <v>1412</v>
       </c>
       <c r="G107" s="37" t="s">
-        <v>1386</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="108">
@@ -10099,22 +10181,22 @@
         <v>106</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>1387</v>
+        <v>1414</v>
       </c>
       <c r="C108" s="36">
         <v>1.0</v>
       </c>
       <c r="D108" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E108" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F108" s="37" t="s">
-        <v>1388</v>
+        <v>1415</v>
       </c>
       <c r="G108" s="37" t="s">
-        <v>1388</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="109">
@@ -10123,22 +10205,22 @@
         <v>107</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>1389</v>
+        <v>1416</v>
       </c>
       <c r="C109" s="36">
         <v>0.0</v>
       </c>
       <c r="D109" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E109" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F109" s="37" t="s">
-        <v>1390</v>
+        <v>1417</v>
       </c>
       <c r="G109" s="37" t="s">
-        <v>1391</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="110">
@@ -10147,22 +10229,22 @@
         <v>108</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>1392</v>
+        <v>1419</v>
       </c>
       <c r="C110" s="36">
         <v>1.0</v>
       </c>
       <c r="D110" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E110" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F110" s="37" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="G110" s="37" t="s">
-        <v>1394</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="111">
@@ -10171,22 +10253,22 @@
         <v>109</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>1395</v>
+        <v>1422</v>
       </c>
       <c r="C111" s="36">
         <v>0.0</v>
       </c>
       <c r="D111" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E111" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F111" s="37" t="s">
-        <v>1396</v>
+        <v>1423</v>
       </c>
       <c r="G111" s="37" t="s">
-        <v>1397</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="112">
@@ -10195,22 +10277,22 @@
         <v>110</v>
       </c>
       <c r="B112" s="36" t="s">
-        <v>1398</v>
+        <v>1425</v>
       </c>
       <c r="C112" s="36">
         <v>1.0</v>
       </c>
       <c r="D112" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E112" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F112" s="37" t="s">
-        <v>1399</v>
+        <v>1426</v>
       </c>
       <c r="G112" s="37" t="s">
-        <v>1400</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="113">
@@ -10219,22 +10301,22 @@
         <v>111</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>1401</v>
+        <v>1428</v>
       </c>
       <c r="C113" s="36">
         <v>0.0</v>
       </c>
       <c r="D113" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E113" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F113" s="37" t="s">
-        <v>1402</v>
+        <v>1429</v>
       </c>
       <c r="G113" s="37" t="s">
-        <v>1403</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="114">
@@ -10243,22 +10325,22 @@
         <v>112</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>997</v>
+        <v>1024</v>
       </c>
       <c r="C114" s="36">
         <v>0.0</v>
       </c>
       <c r="D114" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E114" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F114" s="37" t="s">
-        <v>1404</v>
+        <v>1431</v>
       </c>
       <c r="G114" s="37" t="s">
-        <v>1405</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="115">
@@ -10267,22 +10349,22 @@
         <v>113</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>1406</v>
+        <v>1433</v>
       </c>
       <c r="C115" s="36">
         <v>0.0</v>
       </c>
       <c r="D115" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E115" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F115" s="37" t="s">
-        <v>1407</v>
+        <v>1434</v>
       </c>
       <c r="G115" s="37" t="s">
-        <v>1408</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="116">
@@ -10291,22 +10373,22 @@
         <v>114</v>
       </c>
       <c r="B116" s="36" t="s">
-        <v>1409</v>
+        <v>1436</v>
       </c>
       <c r="C116" s="36">
         <v>1.0</v>
       </c>
       <c r="D116" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E116" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F116" s="37" t="s">
-        <v>1410</v>
+        <v>1437</v>
       </c>
       <c r="G116" s="37" t="s">
-        <v>1411</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="117">
@@ -10321,16 +10403,16 @@
         <v>0.0</v>
       </c>
       <c r="D117" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E117" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F117" s="37" t="s">
-        <v>1412</v>
+        <v>1439</v>
       </c>
       <c r="G117" s="37" t="s">
-        <v>1413</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="118">
@@ -10345,16 +10427,16 @@
         <v>0.0</v>
       </c>
       <c r="D118" s="38" t="s">
-        <v>900</v>
+        <v>927</v>
       </c>
       <c r="E118" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F118" s="37" t="s">
-        <v>1414</v>
+        <v>1441</v>
       </c>
       <c r="G118" s="37" t="s">
-        <v>1415</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="119">
@@ -10369,16 +10451,16 @@
         <v>0.0</v>
       </c>
       <c r="D119" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E119" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F119" s="37" t="s">
-        <v>1416</v>
+        <v>1443</v>
       </c>
       <c r="G119" s="37" t="s">
-        <v>1417</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="120">
@@ -10393,13 +10475,13 @@
         <v>0.0</v>
       </c>
       <c r="D120" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E120" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F120" s="37" t="s">
-        <v>1418</v>
+        <v>1445</v>
       </c>
       <c r="G120" s="37" t="s">
         <v>14</v>
@@ -10411,19 +10493,19 @@
         <v>119</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>999</v>
+        <v>1026</v>
       </c>
       <c r="C121" s="36">
         <v>0.0</v>
       </c>
       <c r="D121" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E121" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F121" s="37" t="s">
-        <v>1419</v>
+        <v>1446</v>
       </c>
       <c r="G121" s="37" t="s">
         <v>34</v>
@@ -10435,22 +10517,22 @@
         <v>120</v>
       </c>
       <c r="B122" s="36" t="s">
-        <v>1000</v>
+        <v>1027</v>
       </c>
       <c r="C122" s="36">
         <v>0.0</v>
       </c>
       <c r="D122" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E122" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F122" s="37" t="s">
-        <v>1420</v>
+        <v>1447</v>
       </c>
       <c r="G122" s="37" t="s">
-        <v>1421</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="123">
@@ -10459,22 +10541,22 @@
         <v>121</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>1422</v>
+        <v>1449</v>
       </c>
       <c r="C123" s="36">
         <v>0.0</v>
       </c>
       <c r="D123" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E123" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F123" s="37" t="s">
-        <v>1423</v>
+        <v>1450</v>
       </c>
       <c r="G123" s="37" t="s">
-        <v>1424</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="124">
@@ -10483,22 +10565,22 @@
         <v>122</v>
       </c>
       <c r="B124" s="36" t="s">
-        <v>1425</v>
+        <v>1452</v>
       </c>
       <c r="C124" s="36">
         <v>0.0</v>
       </c>
       <c r="D124" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E124" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F124" s="37" t="s">
-        <v>1426</v>
+        <v>1453</v>
       </c>
       <c r="G124" s="37" t="s">
-        <v>1427</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="125">
@@ -10513,16 +10595,16 @@
         <v>0.0</v>
       </c>
       <c r="D125" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E125" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F125" s="37" t="s">
-        <v>1428</v>
+        <v>1455</v>
       </c>
       <c r="G125" s="37" t="s">
-        <v>1429</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="126">
@@ -10537,16 +10619,16 @@
         <v>0.0</v>
       </c>
       <c r="D126" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F126" s="37" t="s">
-        <v>1430</v>
+        <v>1457</v>
       </c>
       <c r="G126" s="37" t="s">
-        <v>1431</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="127">
@@ -10555,22 +10637,22 @@
         <v>125</v>
       </c>
       <c r="B127" s="36" t="s">
-        <v>1432</v>
+        <v>1459</v>
       </c>
       <c r="C127" s="36">
         <v>0.0</v>
       </c>
       <c r="D127" s="38" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E127" s="44" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F127" s="37" t="s">
-        <v>1433</v>
+        <v>1460</v>
       </c>
       <c r="G127" s="37" t="s">
-        <v>1433</v>
+        <v>1460</v>
       </c>
     </row>
   </sheetData>
@@ -10615,34 +10697,34 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1434</v>
+        <v>1461</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>1435</v>
+        <v>1462</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1436</v>
+        <v>1463</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1437</v>
+        <v>1464</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>1438</v>
+        <v>1465</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>1439</v>
+        <v>1466</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>1440</v>
+        <v>1467</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>1441</v>
+        <v>1468</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="K1" s="63" t="s">
-        <v>1443</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="2" ht="186.0" customHeight="1">
@@ -10651,13 +10733,13 @@
         <v>-1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>1444</v>
+        <v>1471</v>
       </c>
       <c r="C2" s="65" t="s">
         <v>312</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>312</v>
@@ -10669,7 +10751,7 @@
         <v>310</v>
       </c>
       <c r="H2" s="35" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="I2" s="35" t="s">
         <v>604</v>
@@ -10687,25 +10769,25 @@
         <v>0</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>1445</v>
+        <v>1472</v>
       </c>
       <c r="C3" s="65" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>1446</v>
+        <v>1473</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1447</v>
+        <v>1474</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H3" s="35" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
       <c r="I3" s="35" t="s">
         <v>604</v>
@@ -10723,25 +10805,25 @@
         <v>1</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1448</v>
+        <v>1475</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>1449</v>
+        <v>1476</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1449</v>
+        <v>1476</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1450</v>
+        <v>1477</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H4" s="35" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
       <c r="I4" s="35" t="s">
         <v>604</v>
@@ -10759,25 +10841,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1451</v>
+        <v>1478</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>1452</v>
+        <v>1479</v>
       </c>
       <c r="D5" s="66" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1452</v>
+        <v>1479</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1453</v>
+        <v>1480</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H5" s="35" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
       <c r="I5" s="35" t="s">
         <v>669</v>
@@ -10795,25 +10877,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1454</v>
+        <v>1481</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>1455</v>
+        <v>1482</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1455</v>
+        <v>1482</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1456</v>
+        <v>1483</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
       <c r="I6" s="35" t="s">
         <v>669</v>
@@ -10831,25 +10913,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1457</v>
+        <v>1484</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1458</v>
+        <v>1485</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>1458</v>
+        <v>1485</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>1460</v>
+        <v>1487</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="I7" s="35" t="s">
         <v>604</v>
@@ -10867,25 +10949,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>1461</v>
+        <v>1488</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>1462</v>
+        <v>1489</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>1462</v>
+        <v>1489</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>1463</v>
+        <v>1490</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="I8" s="35" t="s">
         <v>604</v>
@@ -10906,22 +10988,22 @@
         <v>16</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>879</v>
+        <v>893</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>908</v>
+        <v>935</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>879</v>
+        <v>893</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>1464</v>
+        <v>1491</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>908</v>
+        <v>935</v>
       </c>
       <c r="I9" s="35" t="s">
         <v>604</v>
@@ -10939,25 +11021,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>1465</v>
+        <v>1492</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>1466</v>
+        <v>1493</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>910</v>
+        <v>937</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1466</v>
+        <v>1493</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1467</v>
+        <v>1494</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>1468</v>
+        <v>1495</v>
       </c>
       <c r="I10" s="35" t="s">
         <v>667</v>
@@ -10975,25 +11057,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1469</v>
+        <v>1496</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1470</v>
+        <v>1497</v>
       </c>
       <c r="D11" s="66" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1470</v>
+        <v>1497</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>1471</v>
+        <v>1498</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="I11" s="35" t="s">
         <v>604</v>
@@ -11011,25 +11093,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1472</v>
+        <v>1499</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1473</v>
+        <v>1500</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>909</v>
+        <v>936</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>1473</v>
+        <v>1500</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>1474</v>
+        <v>1501</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>909</v>
+        <v>936</v>
       </c>
       <c r="I12" s="35" t="s">
         <v>604</v>
@@ -11047,25 +11129,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>1475</v>
+        <v>1502</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1476</v>
+        <v>1503</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>909</v>
+        <v>936</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>1476</v>
+        <v>1503</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>1477</v>
+        <v>1504</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>909</v>
+        <v>936</v>
       </c>
       <c r="I13" s="35" t="s">
         <v>604</v>
@@ -11086,13 +11168,13 @@
         <v>21</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>1478</v>
+        <v>1505</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>1478</v>
+        <v>1505</v>
       </c>
       <c r="F14" s="35" t="s">
         <v>336</v>
@@ -11101,7 +11183,7 @@
         <v>310</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="I14" s="35" t="s">
         <v>604</v>
@@ -11119,13 +11201,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1479</v>
+        <v>1506</v>
       </c>
       <c r="C15" s="65" t="s">
         <v>312</v>
       </c>
       <c r="D15" s="66" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E15" s="35" t="s">
         <v>442</v>
@@ -11137,7 +11219,7 @@
         <v>310</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="I15" s="35" t="s">
         <v>604</v>
@@ -11182,7 +11264,7 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1480</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="2">
@@ -11209,7 +11291,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1481</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="5">
@@ -11218,7 +11300,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1482</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="6">
@@ -11230,7 +11312,7 @@
         <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1483</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="8">
@@ -11238,7 +11320,7 @@
         <v>0.0</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1484</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="9">
@@ -11246,7 +11328,7 @@
         <v>1.0</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1485</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="10">
@@ -11254,7 +11336,7 @@
         <v>2.0</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1486</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="11">
@@ -11262,7 +11344,7 @@
         <v>3.0</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1487</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="12">
@@ -11270,7 +11352,7 @@
         <v>4.0</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1488</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="13">
@@ -11278,7 +11360,7 @@
         <v>5.0</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1489</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="15">
@@ -11286,7 +11368,7 @@
         <v>46</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1490</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="16">
@@ -11304,7 +11386,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1491</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="18">
@@ -11349,7 +11431,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1492</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="23">
@@ -11366,7 +11448,7 @@
         <v>46</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1493</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="26">
@@ -11411,7 +11493,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1494</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="31">
@@ -11438,7 +11520,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1495</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="34">
@@ -11456,7 +11538,7 @@
         <v>9</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1496</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="36">
@@ -11518,7 +11600,7 @@
         <v>46</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1497</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="44">
@@ -11526,7 +11608,7 @@
         <v>0.0</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1114</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="45">
@@ -11534,7 +11616,7 @@
         <v>1.0</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="47">
@@ -11542,7 +11624,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1498</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="48">
@@ -11595,7 +11677,7 @@
         <v>46</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1499</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="55">
@@ -11660,7 +11742,7 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1500</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="2">
@@ -11678,7 +11760,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1501</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="4">
@@ -11687,7 +11769,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1502</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="5">
@@ -11768,7 +11850,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1503</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="14">
@@ -11813,7 +11895,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1504</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="19">
@@ -11957,7 +12039,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1505</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="36">
@@ -11965,16 +12047,16 @@
         <v>46</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1506</v>
+        <v>1533</v>
       </c>
       <c r="C36" s="68" t="s">
         <v>301</v>
       </c>
       <c r="D36" s="68" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
       <c r="E36" s="68" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="37">
@@ -11983,7 +12065,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1509</v>
+        <v>1536</v>
       </c>
       <c r="C37" s="38" t="s">
         <v>310</v>
@@ -12002,13 +12084,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1047</v>
+        <v>1074</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="E38" s="69" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B38,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_JOB_FIND_1_1|MEMENTO_JOB_FIND_1_2")</f>
@@ -12021,13 +12103,13 @@
         <v>2</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1511</v>
+        <v>1538</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1078</v>
+        <v>1105</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>884</v>
+        <v>901</v>
       </c>
       <c r="E39" s="69" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("ArrayFormula(SUBSTITUTE(SUBSTITUTE(JOIN(""|"",UNIQUE(IF(Table_Memento[Parent]=B39,Table_Memento[MEMENTO_ID],""Ñ""))),""Ñ|"",""""),""|Ñ"",""""))"),"MEMENTO_RECIPE_MISSION_1")</f>
@@ -12043,7 +12125,7 @@
         <v>41</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1085</v>
+        <v>1112</v>
       </c>
       <c r="D40" s="38" t="s">
         <v>42</v>
@@ -12059,7 +12141,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1512</v>
+        <v>1539</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>441</v>
@@ -12077,19 +12159,19 @@
         <v>46</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1513</v>
+        <v>1540</v>
       </c>
       <c r="C43" s="67" t="s">
-        <v>1514</v>
+        <v>1541</v>
       </c>
       <c r="D43" s="67" t="s">
-        <v>1010</v>
+        <v>1037</v>
       </c>
       <c r="E43" s="68" t="s">
-        <v>1515</v>
+        <v>1542</v>
       </c>
       <c r="F43" s="67" t="s">
-        <v>1516</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="44">
@@ -12101,13 +12183,13 @@
         <v>686</v>
       </c>
       <c r="C44" s="44" t="s">
-        <v>1509</v>
+        <v>1536</v>
       </c>
       <c r="D44" s="44" t="s">
         <v>689</v>
       </c>
       <c r="E44" s="48" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="F44" s="43" t="b">
         <v>0</v>
@@ -12122,13 +12204,13 @@
         <v>698</v>
       </c>
       <c r="C45" s="44" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>1155</v>
+        <v>1182</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="F45" s="43" t="b">
         <v>0</v>
@@ -12143,13 +12225,13 @@
         <v>715</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
       <c r="D46" s="44" t="s">
         <v>735</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="F46" s="43" t="b">
         <v>0</v>
@@ -12164,13 +12246,13 @@
         <v>720</v>
       </c>
       <c r="C47" s="44" t="s">
-        <v>1511</v>
+        <v>1538</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>1257</v>
+        <v>1284</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="F47" s="43" t="b">
         <v>0</v>
@@ -12188,10 +12270,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>1330</v>
+        <v>1357</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="F48" s="43" t="b">
         <v>0</v>
@@ -12203,16 +12285,16 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>1333</v>
+        <v>1360</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="F49" s="43" t="b">
         <v>0</v>
@@ -12224,16 +12306,16 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1519</v>
+        <v>1546</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>41</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>1336</v>
+        <v>1363</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="F50" s="43" t="b">
         <v>1</v>
@@ -12245,16 +12327,16 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1520</v>
+        <v>1547</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>1512</v>
+        <v>1539</v>
       </c>
       <c r="D51" s="44" t="s">
         <v>689</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="F51" s="43" t="b">
         <v>0</v>
@@ -12265,10 +12347,10 @@
         <v>46</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1521</v>
+        <v>1548</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>1522</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="54">
@@ -12277,7 +12359,7 @@
         <v>0</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="C54" s="51" t="s">
         <v>450</v>
@@ -12288,7 +12370,7 @@
         <v>46</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1523</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="57">
@@ -13298,16 +13380,16 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1524</v>
+        <v>1551</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1525</v>
+        <v>1552</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1526</v>
+        <v>1553</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1527</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="2">
@@ -13319,7 +13401,7 @@
         <v>313</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1528</v>
+        <v>1555</v>
       </c>
       <c r="D2" s="70" t="s">
         <v>310</v>
@@ -13337,7 +13419,7 @@
         <v>428</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1529</v>
+        <v>1556</v>
       </c>
       <c r="D3" s="70" t="s">
         <v>310</v>
@@ -13352,10 +13434,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1530</v>
+        <v>1557</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1528</v>
+        <v>1555</v>
       </c>
       <c r="D4" s="70" t="s">
         <v>310</v>
@@ -13393,7 +13475,7 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1483</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="2">
@@ -13420,7 +13502,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1531</v>
+        <v>1558</v>
       </c>
     </row>
   </sheetData>
@@ -13446,21 +13528,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1532</v>
+        <v>1559</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1533</v>
+        <v>1560</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1534</v>
+        <v>1561</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1535</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="s">
-        <v>1536</v>
+        <v>1563</v>
       </c>
       <c r="B2" s="71">
         <v>5.0</v>
@@ -13474,7 +13556,7 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>1537</v>
+        <v>1564</v>
       </c>
       <c r="B3" s="71">
         <v>4.0</v>
@@ -13488,7 +13570,7 @@
     </row>
     <row r="4">
       <c r="A4" s="37" t="s">
-        <v>1538</v>
+        <v>1565</v>
       </c>
       <c r="B4" s="71">
         <v>2.0</v>
@@ -13502,7 +13584,7 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>1539</v>
+        <v>1566</v>
       </c>
       <c r="B5" s="71">
         <v>5.0</v>
@@ -13516,7 +13598,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>1540</v>
+        <v>1567</v>
       </c>
       <c r="B6" s="71">
         <v>4.0</v>
@@ -13530,7 +13612,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>1541</v>
+        <v>1568</v>
       </c>
       <c r="B7" s="71">
         <v>4.0</v>
@@ -13544,7 +13626,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>1542</v>
+        <v>1569</v>
       </c>
       <c r="B8" s="71">
         <v>2.0</v>
@@ -13558,7 +13640,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="B9" s="71">
         <v>5.0</v>
@@ -28077,9 +28159,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="46.71"/>
-    <col customWidth="1" min="3" max="3" width="73.0"/>
-    <col customWidth="1" min="4" max="4" width="26.0"/>
+    <col customWidth="1" min="2" max="3" width="46.71"/>
+    <col customWidth="1" min="4" max="4" width="30.71"/>
+    <col customWidth="1" min="16" max="16" width="42.14"/>
+    <col customWidth="1" min="17" max="17" width="63.29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28092,6 +28175,9 @@
       <c r="C1" s="1" t="s">
         <v>839</v>
       </c>
+      <c r="D1" s="46" t="s">
+        <v>840</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="36">
@@ -28113,6 +28199,9 @@
       <c r="C3" s="52" t="s">
         <v>331</v>
       </c>
+      <c r="D3" s="52" t="s">
+        <v>841</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="36">
@@ -28120,10 +28209,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>840</v>
+        <v>842</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="5">
@@ -28132,9 +28224,12 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C5" s="52" t="s">
+        <v>843</v>
+      </c>
+      <c r="D5" s="52" t="s">
         <v>841</v>
       </c>
     </row>
@@ -28144,10 +28239,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>842</v>
+        <v>844</v>
+      </c>
+      <c r="D6" s="52" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="7">
@@ -28156,10 +28254,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>843</v>
+        <v>845</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="8">
@@ -28168,10 +28269,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>845</v>
+        <v>847</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="9">
@@ -28180,10 +28284,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>847</v>
+        <v>849</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="10">
@@ -28192,10 +28299,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>849</v>
+        <v>851</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="11">
@@ -28204,10 +28314,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>851</v>
+        <v>853</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="12">
@@ -28216,10 +28329,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>853</v>
+        <v>855</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="13">
@@ -28228,10 +28344,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>854</v>
+        <v>856</v>
+      </c>
+      <c r="D13" s="52" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="14">
@@ -28243,7 +28362,10 @@
         <v>322</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>855</v>
+        <v>858</v>
+      </c>
+      <c r="D14" s="52" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="15">
@@ -28255,7 +28377,10 @@
         <v>701</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>856</v>
+        <v>859</v>
+      </c>
+      <c r="D15" s="52" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="16">
@@ -28267,6 +28392,9 @@
         <v>326</v>
       </c>
       <c r="C16" s="52" t="s">
+        <v>860</v>
+      </c>
+      <c r="D16" s="52" t="s">
         <v>857</v>
       </c>
     </row>
@@ -28279,7 +28407,10 @@
         <v>327</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>858</v>
+        <v>861</v>
+      </c>
+      <c r="D17" s="52" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="18">
@@ -28288,10 +28419,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>860</v>
+        <v>864</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="19">
@@ -28303,7 +28437,10 @@
         <v>334</v>
       </c>
       <c r="C19" s="52" t="s">
-        <v>861</v>
+        <v>865</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="20">
@@ -28312,10 +28449,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>862</v>
+        <v>866</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="21">
@@ -28327,7 +28467,10 @@
         <v>342</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>863</v>
+        <v>868</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="22">
@@ -28336,10 +28479,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>864</v>
+        <v>869</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>870</v>
       </c>
     </row>
     <row r="23">
@@ -28348,10 +28494,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>865</v>
+        <v>871</v>
+      </c>
+      <c r="D23" s="52" t="s">
+        <v>872</v>
       </c>
     </row>
     <row r="24">
@@ -28360,10 +28509,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>866</v>
+        <v>873</v>
+      </c>
+      <c r="D24" s="52" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="25">
@@ -28377,6 +28529,9 @@
       <c r="C25" s="52" t="s">
         <v>359</v>
       </c>
+      <c r="D25" s="52" t="s">
+        <v>862</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="36">
@@ -28384,10 +28539,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="C26" s="52" t="s">
-        <v>868</v>
+        <v>875</v>
+      </c>
+      <c r="D26" s="52" t="s">
+        <v>876</v>
       </c>
     </row>
     <row r="27">
@@ -28396,10 +28554,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="C27" s="52" t="s">
-        <v>870</v>
+        <v>878</v>
+      </c>
+      <c r="D27" s="52" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="28">
@@ -28408,10 +28569,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>871</v>
+        <v>880</v>
       </c>
       <c r="C28" s="52" t="s">
-        <v>872</v>
+        <v>881</v>
+      </c>
+      <c r="D28" s="52" t="s">
+        <v>882</v>
       </c>
     </row>
     <row r="29">
@@ -28420,10 +28584,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>873</v>
+        <v>883</v>
       </c>
       <c r="C29" s="52" t="s">
-        <v>873</v>
+        <v>883</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>884</v>
       </c>
     </row>
     <row r="30">
@@ -28432,10 +28599,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>874</v>
+        <v>885</v>
       </c>
       <c r="C30" s="52" t="s">
-        <v>875</v>
+        <v>886</v>
+      </c>
+      <c r="D30" s="52" t="s">
+        <v>887</v>
       </c>
     </row>
     <row r="31">
@@ -28444,10 +28614,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="C31" s="52" t="s">
-        <v>876</v>
+        <v>888</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>889</v>
       </c>
     </row>
     <row r="32">
@@ -28456,10 +28629,13 @@
         <v>30</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>877</v>
+        <v>890</v>
       </c>
       <c r="C32" s="52" t="s">
-        <v>878</v>
+        <v>891</v>
+      </c>
+      <c r="D32" s="52" t="s">
+        <v>892</v>
       </c>
     </row>
     <row r="33">
@@ -28468,10 +28644,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>879</v>
+        <v>893</v>
       </c>
       <c r="C33" s="52" t="s">
-        <v>879</v>
+        <v>893</v>
+      </c>
+      <c r="D33" s="52" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="34">
@@ -28483,7 +28662,10 @@
         <v>375</v>
       </c>
       <c r="C34" s="52" t="s">
-        <v>880</v>
+        <v>895</v>
+      </c>
+      <c r="D34" s="52" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="35">
@@ -28495,7 +28677,10 @@
         <v>377</v>
       </c>
       <c r="C35" s="52" t="s">
-        <v>881</v>
+        <v>896</v>
+      </c>
+      <c r="D35" s="52" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="36">
@@ -28504,10 +28689,13 @@
         <v>34</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="C36" s="52" t="s">
-        <v>882</v>
+        <v>897</v>
+      </c>
+      <c r="D36" s="52" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="37">
@@ -28516,10 +28704,13 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>883</v>
+        <v>899</v>
       </c>
       <c r="C37" s="52" t="s">
-        <v>883</v>
+        <v>899</v>
+      </c>
+      <c r="D37" s="52" t="s">
+        <v>900</v>
       </c>
     </row>
     <row r="38">
@@ -28533,6 +28724,9 @@
       <c r="C38" s="52" t="s">
         <v>381</v>
       </c>
+      <c r="D38" s="52" t="s">
+        <v>898</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="36">
@@ -28545,6 +28739,9 @@
       <c r="C39" s="52" t="s">
         <v>382</v>
       </c>
+      <c r="D39" s="52" t="s">
+        <v>862</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="36">
@@ -28557,6 +28754,9 @@
       <c r="C40" s="52" t="s">
         <v>388</v>
       </c>
+      <c r="D40" s="52" t="s">
+        <v>898</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="36">
@@ -28564,10 +28764,13 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>884</v>
+        <v>901</v>
       </c>
       <c r="C41" s="52" t="s">
-        <v>884</v>
+        <v>901</v>
+      </c>
+      <c r="D41" s="52" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="42">
@@ -28581,6 +28784,9 @@
       <c r="C42" s="52" t="s">
         <v>398</v>
       </c>
+      <c r="D42" s="52" t="s">
+        <v>882</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="36">
@@ -28591,7 +28797,10 @@
         <v>42</v>
       </c>
       <c r="C43" s="52" t="s">
-        <v>866</v>
+        <v>873</v>
+      </c>
+      <c r="D43" s="52" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="44">
@@ -28605,6 +28814,9 @@
       <c r="C44" s="52" t="s">
         <v>402</v>
       </c>
+      <c r="D44" s="52" t="s">
+        <v>882</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="36">
@@ -28612,10 +28824,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>885</v>
+        <v>902</v>
       </c>
       <c r="C45" s="52" t="s">
-        <v>886</v>
+        <v>903</v>
+      </c>
+      <c r="D45" s="52" t="s">
+        <v>904</v>
       </c>
     </row>
     <row r="46">
@@ -28624,10 +28839,13 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="C46" s="52" t="s">
-        <v>888</v>
+        <v>906</v>
+      </c>
+      <c r="D46" s="52" t="s">
+        <v>907</v>
       </c>
     </row>
     <row r="47">
@@ -28641,6 +28859,9 @@
       <c r="C47" s="52" t="s">
         <v>414</v>
       </c>
+      <c r="D47" s="52" t="s">
+        <v>870</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="36">
@@ -28651,7 +28872,10 @@
         <v>415</v>
       </c>
       <c r="C48" s="52" t="s">
-        <v>889</v>
+        <v>908</v>
+      </c>
+      <c r="D48" s="52" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="49">
@@ -28665,6 +28889,9 @@
       <c r="C49" s="52" t="s">
         <v>419</v>
       </c>
+      <c r="D49" s="52" t="s">
+        <v>904</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="36">
@@ -28677,6 +28904,9 @@
       <c r="C50" s="52" t="s">
         <v>423</v>
       </c>
+      <c r="D50" s="52" t="s">
+        <v>879</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="36">
@@ -28689,6 +28919,9 @@
       <c r="C51" s="52" t="s">
         <v>427</v>
       </c>
+      <c r="D51" s="52" t="s">
+        <v>862</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="36">
@@ -28701,6 +28934,9 @@
       <c r="C52" s="52" t="s">
         <v>434</v>
       </c>
+      <c r="D52" s="52" t="s">
+        <v>894</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="36">
@@ -28713,6 +28949,9 @@
       <c r="C53" s="52" t="s">
         <v>12</v>
       </c>
+      <c r="D53" s="52" t="s">
+        <v>894</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="36">
@@ -28720,10 +28959,13 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
       <c r="C54" s="52" t="s">
-        <v>890</v>
+        <v>909</v>
+      </c>
+      <c r="D54" s="52" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="55">
@@ -28732,10 +28974,13 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>891</v>
+        <v>911</v>
       </c>
       <c r="C55" s="52" t="s">
-        <v>891</v>
+        <v>911</v>
+      </c>
+      <c r="D55" s="52" t="s">
+        <v>912</v>
       </c>
     </row>
     <row r="56">
@@ -28744,10 +28989,13 @@
         <v>54</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>892</v>
+        <v>913</v>
       </c>
       <c r="C56" s="52" t="s">
-        <v>892</v>
+        <v>913</v>
+      </c>
+      <c r="D56" s="52" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="57">
@@ -28756,10 +29004,13 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>893</v>
+        <v>915</v>
       </c>
       <c r="C57" s="52" t="s">
-        <v>893</v>
+        <v>915</v>
+      </c>
+      <c r="D57" s="52" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="58">
@@ -28773,6 +29024,9 @@
       <c r="C58" s="52" t="s">
         <v>22</v>
       </c>
+      <c r="D58" s="52" t="s">
+        <v>917</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="36">
@@ -28780,10 +29034,13 @@
         <v>57</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>894</v>
+        <v>918</v>
       </c>
       <c r="C59" s="52" t="s">
-        <v>894</v>
+        <v>918</v>
+      </c>
+      <c r="D59" s="52" t="s">
+        <v>917</v>
       </c>
     </row>
     <row r="60">
@@ -28797,6 +29054,9 @@
       <c r="C60" s="52" t="s">
         <v>439</v>
       </c>
+      <c r="D60" s="36" t="s">
+        <v>919</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="36">
@@ -28804,9 +29064,24 @@
         <v>59</v>
       </c>
       <c r="B61" s="36" t="s">
+        <v>920</v>
+      </c>
+      <c r="C61" s="36" t="s">
+        <v>920</v>
+      </c>
+      <c r="D61" s="36" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="36">
+        <f>ROW()-ROW(Table_sprites[N])</f>
+        <v>60</v>
+      </c>
+      <c r="B62" s="36" t="s">
         <v>442</v>
       </c>
-      <c r="C61" s="36" t="s">
+      <c r="C62" s="36" t="s">
         <v>442</v>
       </c>
     </row>
@@ -28836,10 +29111,10 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>895</v>
+        <v>922</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>896</v>
+        <v>923</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>839</v>
@@ -28851,10 +29126,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
     </row>
     <row r="3">
@@ -28863,13 +29138,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>899</v>
+        <v>926</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>899</v>
+        <v>926</v>
       </c>
     </row>
     <row r="4">
@@ -28878,13 +29153,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>900</v>
+        <v>927</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>901</v>
+        <v>928</v>
       </c>
     </row>
     <row r="5">
@@ -28893,13 +29168,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>902</v>
+        <v>929</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>903</v>
+        <v>930</v>
       </c>
     </row>
     <row r="6">
@@ -28908,13 +29183,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>904</v>
+        <v>931</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>904</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7">
@@ -28923,13 +29198,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>905</v>
+        <v>932</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>905</v>
+        <v>932</v>
       </c>
     </row>
     <row r="8">
@@ -28938,13 +29213,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>906</v>
+        <v>933</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>906</v>
+        <v>933</v>
       </c>
     </row>
     <row r="9">
@@ -28953,13 +29228,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>907</v>
+        <v>934</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>907</v>
+        <v>934</v>
       </c>
     </row>
     <row r="10">
@@ -28968,13 +29243,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>908</v>
+        <v>935</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>908</v>
+        <v>935</v>
       </c>
     </row>
     <row r="11">
@@ -28983,13 +29258,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>909</v>
+        <v>936</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>909</v>
+        <v>936</v>
       </c>
     </row>
     <row r="12">
@@ -28998,13 +29273,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>910</v>
+        <v>937</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>910</v>
+        <v>937</v>
       </c>
     </row>
     <row r="13">
@@ -29013,13 +29288,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>911</v>
+        <v>938</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>911</v>
+        <v>938</v>
       </c>
     </row>
     <row r="14">
@@ -29028,13 +29303,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>912</v>
+        <v>939</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>912</v>
+        <v>939</v>
       </c>
     </row>
     <row r="15">
@@ -29043,13 +29318,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>913</v>
+        <v>940</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>913</v>
+        <v>940</v>
       </c>
     </row>
     <row r="16">
@@ -29058,13 +29333,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
     </row>
     <row r="17">
@@ -29073,10 +29348,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>915</v>
+        <v>942</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
     </row>
   </sheetData>
@@ -29110,13 +29385,13 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>916</v>
+        <v>943</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>26</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>917</v>
+        <v>944</v>
       </c>
     </row>
     <row r="2">
@@ -29131,7 +29406,7 @@
         <v>309</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>918</v>
+        <v>945</v>
       </c>
     </row>
     <row r="3">
@@ -29146,7 +29421,7 @@
         <v>309</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>919</v>
+        <v>946</v>
       </c>
     </row>
     <row r="4">
@@ -29158,10 +29433,10 @@
         <v>732</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>920</v>
+        <v>947</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>921</v>
+        <v>948</v>
       </c>
     </row>
     <row r="5">
@@ -29170,13 +29445,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>922</v>
+        <v>949</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>920</v>
+        <v>947</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>923</v>
+        <v>950</v>
       </c>
     </row>
     <row r="6">
@@ -29188,10 +29463,10 @@
         <v>746</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>920</v>
+        <v>947</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
     </row>
     <row r="7">
@@ -29203,10 +29478,10 @@
         <v>748</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>926</v>
+        <v>953</v>
       </c>
     </row>
     <row r="8">
@@ -29215,13 +29490,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>927</v>
+        <v>954</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>928</v>
+        <v>955</v>
       </c>
     </row>
     <row r="9">
@@ -29233,10 +29508,10 @@
         <v>750</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>930</v>
+        <v>957</v>
       </c>
     </row>
     <row r="10">
@@ -29245,13 +29520,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>931</v>
+        <v>958</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>932</v>
+        <v>959</v>
       </c>
     </row>
     <row r="11">
@@ -29263,10 +29538,10 @@
         <v>751</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
     </row>
     <row r="12">
@@ -29281,7 +29556,7 @@
         <v>394</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>934</v>
+        <v>961</v>
       </c>
     </row>
     <row r="13">
@@ -29296,7 +29571,7 @@
         <v>396</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>935</v>
+        <v>962</v>
       </c>
     </row>
     <row r="14">
@@ -29305,13 +29580,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>936</v>
+        <v>963</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>937</v>
+        <v>964</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>938</v>
+        <v>965</v>
       </c>
     </row>
     <row r="15">
@@ -29323,10 +29598,10 @@
         <v>758</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>937</v>
+        <v>964</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>939</v>
+        <v>966</v>
       </c>
     </row>
     <row r="16">
@@ -29335,13 +29610,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>940</v>
+        <v>967</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>941</v>
+        <v>968</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>942</v>
+        <v>969</v>
       </c>
     </row>
     <row r="17">
@@ -29353,10 +29628,10 @@
         <v>783</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>941</v>
+        <v>968</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>943</v>
+        <v>970</v>
       </c>
     </row>
     <row r="18">
@@ -29371,7 +29646,7 @@
         <v>35</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>944</v>
+        <v>971</v>
       </c>
     </row>
     <row r="19">
@@ -29386,7 +29661,7 @@
         <v>315</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>945</v>
+        <v>972</v>
       </c>
     </row>
     <row r="20">
@@ -29395,13 +29670,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>946</v>
+        <v>973</v>
       </c>
       <c r="C20" s="39" t="s">
         <v>35</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>947</v>
+        <v>974</v>
       </c>
     </row>
     <row r="21">
@@ -29410,13 +29685,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>948</v>
+        <v>975</v>
       </c>
       <c r="C21" s="39" t="s">
         <v>309</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>918</v>
+        <v>945</v>
       </c>
     </row>
     <row r="23">
@@ -29424,25 +29699,25 @@
         <v>46</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>949</v>
+        <v>976</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>444</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>950</v>
+        <v>977</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>951</v>
+        <v>978</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>952</v>
+        <v>979</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>953</v>
+        <v>980</v>
       </c>
       <c r="H23" s="28" t="s">
-        <v>954</v>
+        <v>981</v>
       </c>
     </row>
     <row r="24">
@@ -29451,7 +29726,7 @@
         <v>0</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="C24" s="37" t="s">
         <v>450</v>
@@ -29478,7 +29753,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>919</v>
+        <v>946</v>
       </c>
       <c r="C25" s="37" t="s">
         <v>450</v>
@@ -29505,7 +29780,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>921</v>
+        <v>948</v>
       </c>
       <c r="C26" s="40" t="s">
         <v>450</v>
@@ -29517,13 +29792,13 @@
         <v>454</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>922</v>
+        <v>949</v>
       </c>
       <c r="G26" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="40" t="s">
-        <v>955</v>
+        <v>982</v>
       </c>
     </row>
     <row r="27">
@@ -29532,7 +29807,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>956</v>
+        <v>983</v>
       </c>
       <c r="C27" s="40" t="s">
         <v>450</v>
@@ -29544,13 +29819,13 @@
         <v>454</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>922</v>
+        <v>949</v>
       </c>
       <c r="G27" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H27" s="40" t="s">
-        <v>957</v>
+        <v>984</v>
       </c>
     </row>
     <row r="28">
@@ -29559,7 +29834,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>958</v>
+        <v>985</v>
       </c>
       <c r="C28" s="40" t="s">
         <v>450</v>
@@ -29577,7 +29852,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="40" t="s">
-        <v>959</v>
+        <v>986</v>
       </c>
     </row>
     <row r="29">
@@ -29586,7 +29861,7 @@
         <v>5</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>960</v>
+        <v>987</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>450</v>
@@ -29595,7 +29870,7 @@
         <v>451</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>961</v>
+        <v>988</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>688</v>
@@ -29604,7 +29879,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="40" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
     </row>
     <row r="30">
@@ -29613,7 +29888,7 @@
         <v>6</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>450</v>
@@ -29631,7 +29906,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="40" t="s">
-        <v>963</v>
+        <v>990</v>
       </c>
     </row>
     <row r="31">
@@ -29640,7 +29915,7 @@
         <v>7</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>926</v>
+        <v>953</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>450</v>
@@ -29652,13 +29927,13 @@
         <v>454</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>927</v>
+        <v>954</v>
       </c>
       <c r="G31" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H31" s="40" t="s">
-        <v>964</v>
+        <v>991</v>
       </c>
     </row>
     <row r="32">
@@ -29667,7 +29942,7 @@
         <v>8</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>928</v>
+        <v>955</v>
       </c>
       <c r="C32" s="40" t="s">
         <v>450</v>
@@ -29685,7 +29960,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="40" t="s">
-        <v>965</v>
+        <v>992</v>
       </c>
     </row>
     <row r="33">
@@ -29694,7 +29969,7 @@
         <v>9</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>930</v>
+        <v>957</v>
       </c>
       <c r="C33" s="40" t="s">
         <v>450</v>
@@ -29706,13 +29981,13 @@
         <v>454</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>931</v>
+        <v>958</v>
       </c>
       <c r="G33" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H33" s="40" t="s">
-        <v>966</v>
+        <v>993</v>
       </c>
     </row>
     <row r="34">
@@ -29721,7 +29996,7 @@
         <v>10</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>967</v>
+        <v>994</v>
       </c>
       <c r="C34" s="40" t="s">
         <v>450</v>
@@ -29733,13 +30008,13 @@
         <v>816</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>931</v>
+        <v>958</v>
       </c>
       <c r="G34" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="40" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
     </row>
     <row r="35">
@@ -29748,7 +30023,7 @@
         <v>11</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>969</v>
+        <v>996</v>
       </c>
       <c r="C35" s="40" t="s">
         <v>817</v>
@@ -29760,13 +30035,13 @@
         <v>454</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>931</v>
+        <v>958</v>
       </c>
       <c r="G35" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H35" s="40" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
     </row>
     <row r="36">
@@ -29775,7 +30050,7 @@
         <v>12</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>971</v>
+        <v>998</v>
       </c>
       <c r="C36" s="40" t="s">
         <v>450</v>
@@ -29787,13 +30062,13 @@
         <v>454</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>931</v>
+        <v>958</v>
       </c>
       <c r="G36" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H36" s="40" t="s">
-        <v>972</v>
+        <v>999</v>
       </c>
     </row>
     <row r="37">
@@ -29802,7 +30077,7 @@
         <v>13</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>973</v>
+        <v>1000</v>
       </c>
       <c r="C37" s="40" t="s">
         <v>817</v>
@@ -29811,16 +30086,16 @@
         <v>516</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>974</v>
+        <v>1001</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>931</v>
+        <v>958</v>
       </c>
       <c r="G37" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H37" s="40" t="s">
-        <v>975</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="38">
@@ -29829,7 +30104,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>976</v>
+        <v>1003</v>
       </c>
       <c r="C38" s="40" t="s">
         <v>450</v>
@@ -29847,7 +30122,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="40" t="s">
-        <v>977</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="39">
@@ -29856,7 +30131,7 @@
         <v>15</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="C39" s="40" t="s">
         <v>450</v>
@@ -29874,7 +30149,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="40" t="s">
-        <v>978</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="40">
@@ -29883,7 +30158,7 @@
         <v>16</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>934</v>
+        <v>961</v>
       </c>
       <c r="C40" s="40" t="s">
         <v>450</v>
@@ -29901,7 +30176,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="40" t="s">
-        <v>979</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="41">
@@ -29910,7 +30185,7 @@
         <v>17</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>935</v>
+        <v>962</v>
       </c>
       <c r="C41" s="40" t="s">
         <v>450</v>
@@ -29928,7 +30203,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>980</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="42">
@@ -29937,7 +30212,7 @@
         <v>18</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>981</v>
+        <v>1008</v>
       </c>
       <c r="C42" s="40" t="s">
         <v>450</v>
@@ -29949,13 +30224,13 @@
         <v>454</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>936</v>
+        <v>963</v>
       </c>
       <c r="G42" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H42" s="40" t="s">
-        <v>982</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="43">
@@ -29964,7 +30239,7 @@
         <v>19</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>983</v>
+        <v>1010</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>450</v>
@@ -29976,13 +30251,13 @@
         <v>454</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>936</v>
+        <v>963</v>
       </c>
       <c r="G43" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H43" s="40" t="s">
-        <v>984</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="44">
@@ -29991,7 +30266,7 @@
         <v>20</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>985</v>
+        <v>1012</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>450</v>
@@ -30000,16 +30275,16 @@
         <v>451</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>986</v>
+        <v>1013</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>936</v>
+        <v>963</v>
       </c>
       <c r="G44" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H44" s="40" t="s">
-        <v>987</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="45">
@@ -30018,7 +30293,7 @@
         <v>21</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>988</v>
+        <v>1015</v>
       </c>
       <c r="C45" s="40" t="s">
         <v>450</v>
@@ -30036,7 +30311,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="40" t="s">
-        <v>989</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="46">
@@ -30045,7 +30320,7 @@
         <v>22</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>939</v>
+        <v>966</v>
       </c>
       <c r="C46" s="40" t="s">
         <v>450</v>
@@ -30057,13 +30332,13 @@
         <v>454</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>936</v>
+        <v>963</v>
       </c>
       <c r="G46" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H46" s="40" t="s">
-        <v>990</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="47">
@@ -30072,7 +30347,7 @@
         <v>23</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>991</v>
+        <v>1018</v>
       </c>
       <c r="C47" s="40" t="s">
         <v>450</v>
@@ -30084,13 +30359,13 @@
         <v>821</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>940</v>
+        <v>967</v>
       </c>
       <c r="G47" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H47" s="40" t="s">
-        <v>992</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="48">
@@ -30099,7 +30374,7 @@
         <v>24</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>993</v>
+        <v>1020</v>
       </c>
       <c r="C48" s="40" t="s">
         <v>822</v>
@@ -30108,16 +30383,16 @@
         <v>451</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>994</v>
+        <v>1021</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>940</v>
+        <v>967</v>
       </c>
       <c r="G48" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="40" t="s">
-        <v>995</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="49">
@@ -30126,7 +30401,7 @@
         <v>25</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>996</v>
+        <v>1023</v>
       </c>
       <c r="C49" s="40" t="s">
         <v>450</v>
@@ -30144,7 +30419,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="40" t="s">
-        <v>997</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="50">
@@ -30153,7 +30428,7 @@
         <v>26</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>943</v>
+        <v>970</v>
       </c>
       <c r="C50" s="40" t="s">
         <v>450</v>
@@ -30165,13 +30440,13 @@
         <v>454</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>940</v>
+        <v>967</v>
       </c>
       <c r="G50" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H50" s="40" t="s">
-        <v>998</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="51">
@@ -30180,7 +30455,7 @@
         <v>27</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>944</v>
+        <v>971</v>
       </c>
       <c r="C51" s="40" t="s">
         <v>450</v>
@@ -30198,7 +30473,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="40" t="s">
-        <v>999</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="52">
@@ -30207,7 +30482,7 @@
         <v>28</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>945</v>
+        <v>972</v>
       </c>
       <c r="C52" s="40" t="s">
         <v>450</v>
@@ -30219,13 +30494,13 @@
         <v>827</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>946</v>
+        <v>973</v>
       </c>
       <c r="G52" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="40" t="s">
-        <v>1000</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="53">
@@ -30234,7 +30509,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>947</v>
+        <v>974</v>
       </c>
       <c r="C53" s="40" t="s">
         <v>450</v>
@@ -30252,7 +30527,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="40" t="s">
-        <v>1001</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="54">
@@ -30261,7 +30536,7 @@
         <v>30</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1002</v>
+        <v>1029</v>
       </c>
       <c r="C54" s="37" t="s">
         <v>450</v>
@@ -30378,10 +30653,10 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1003</v>
+        <v>1030</v>
       </c>
       <c r="C1" s="56" t="s">
-        <v>1004</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="2">
@@ -30393,7 +30668,7 @@
         <v>687</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>1005</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="3">
@@ -30405,7 +30680,7 @@
         <v>718</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>1006</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="4">
@@ -30414,10 +30689,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1007</v>
+        <v>1034</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>1008</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="6">
@@ -30425,13 +30700,13 @@
         <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1009</v>
+        <v>1036</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1010</v>
+        <v>1037</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>951</v>
+        <v>978</v>
       </c>
     </row>
     <row r="7">
@@ -30440,7 +30715,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1005</v>
+        <v>1032</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>689</v>
@@ -30455,10 +30730,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1011</v>
+        <v>1038</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>1012</v>
+        <v>1039</v>
       </c>
       <c r="D8" s="57" t="s">
         <v>454</v>
@@ -30470,10 +30745,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1013</v>
+        <v>1040</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="D9" s="57" t="s">
         <v>691</v>
@@ -30485,10 +30760,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1015</v>
+        <v>1042</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>1016</v>
+        <v>1043</v>
       </c>
       <c r="D10" s="57" t="s">
         <v>693</v>
@@ -30500,7 +30775,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1008</v>
+        <v>1035</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>689</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5117" uniqueCount="1570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5131" uniqueCount="1584">
   <si>
     <t>NewItem</t>
   </si>
@@ -3518,7 +3518,7 @@
     <t>Sound</t>
   </si>
   <si>
-    <t>CharAnimation</t>
+    <t>AnimationTrigger</t>
   </si>
   <si>
     <t>Text_English</t>
@@ -3527,10 +3527,10 @@
     <t>Text_Spanish</t>
   </si>
   <si>
-    <t>DIALOG_ANIMATION_NONE</t>
-  </si>
-  <si>
-    <t>DIALOG_ANIMATION_TALK</t>
+    <t>ANIMATION_TRIGGER_NONE</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_TALK</t>
   </si>
   <si>
     <t>That has no sense!</t>
@@ -4676,7 +4676,49 @@
     <t>ACTION_TYPE_NOTIF</t>
   </si>
   <si>
-    <t>DIALOG_ANIMATION_ID</t>
+    <t>ANIMATION_TRIGGER_ID</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_ONE</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_TWO</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_THREE</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_FOUR</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_FIVE</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_SIX</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_SPECIAL_ONE</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_SPECIAL_TWO</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_STEADY</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_WALK_FRONT</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_WALK_BACK</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_WALK_CORNERBACK</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_WALK_CORNERFRONT</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_WALK_SIDE</t>
   </si>
   <si>
     <t>ITEM_FAMILY_TYPE_ID</t>
@@ -6164,7 +6206,7 @@
     <tableColumn name="PHRASE_ID" id="2"/>
     <tableColumn name="TalkerIndex" id="3"/>
     <tableColumn name="Sound" id="4"/>
-    <tableColumn name="CharAnimation" id="5"/>
+    <tableColumn name="AnimationTrigger" id="5"/>
     <tableColumn name="Text_English" id="6"/>
     <tableColumn name="Text_Spanish" id="7"/>
   </tableColumns>
@@ -6245,17 +6287,17 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A43:B45" displayName="Table_Dialog_Animation" name="Table_Dialog_Animation" id="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A43:B59" displayName="Table_Animation_Trigger" name="Table_Animation_Trigger" id="24">
   <tableColumns count="2">
     <tableColumn name="N" id="1"/>
-    <tableColumn name="DIALOG_ANIMATION_ID" id="2"/>
+    <tableColumn name="ANIMATION_TRIGGER_ID" id="2"/>
   </tableColumns>
   <tableStyleInfo name="TYPES-style 5" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A47:B52" displayName="Table_Item_Family_Type" name="Table_Item_Family_Type" id="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A61:B66" displayName="Table_Item_Family_Type" name="Table_Item_Family_Type" id="25">
   <tableColumns count="2">
     <tableColumn name="N" id="1"/>
     <tableColumn name="ITEM_FAMILY_TYPE_ID" id="2"/>
@@ -6265,7 +6307,7 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A54:B57" displayName="Table_Moment_Day" name="Table_Moment_Day" id="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A68:B71" displayName="Table_Moment_Day" name="Table_Moment_Day" id="26">
   <tableColumns count="2">
     <tableColumn name="N" id="1"/>
     <tableColumn name="MOMENT_TYPE_ID" id="2"/>
@@ -7605,7 +7647,7 @@
     <col customWidth="1" min="2" max="2" width="65.43"/>
     <col customWidth="1" min="3" max="3" width="15.57"/>
     <col customWidth="1" min="4" max="4" width="26.86"/>
-    <col customWidth="1" min="5" max="5" width="32.86"/>
+    <col customWidth="1" min="5" max="5" width="34.14"/>
     <col customWidth="1" min="6" max="6" width="50.29"/>
     <col customWidth="1" min="7" max="7" width="58.43"/>
     <col customWidth="1" min="8" max="8" width="32.86"/>
@@ -10657,10 +10699,7 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E127">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D127">
+    <dataValidation type="list" allowBlank="1" sqref="D2:E127">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -11252,7 +11291,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="40.29"/>
+    <col customWidth="1" min="2" max="2" width="44.0"/>
     <col customWidth="1" min="3" max="3" width="38.86"/>
     <col customWidth="1" min="4" max="4" width="23.29"/>
     <col customWidth="1" min="6" max="6" width="38.86"/>
@@ -11605,7 +11644,8 @@
     </row>
     <row r="44">
       <c r="A44" s="36">
-        <v>0.0</v>
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>0</v>
       </c>
       <c r="B44" s="36" t="s">
         <v>1141</v>
@@ -11613,97 +11653,224 @@
     </row>
     <row r="45">
       <c r="A45" s="36">
-        <v>1.0</v>
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>1</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1142</v>
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="36">
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>2</v>
+      </c>
+      <c r="B46" s="36" t="s">
+        <v>1526</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>1525</v>
+      <c r="A47" s="36">
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>3</v>
+      </c>
+      <c r="B47" s="36" t="s">
+        <v>1527</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="36">
-        <f>ROW()-ROW(Table_Item_Family_Type[N])</f>
-        <v>0</v>
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>4</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>311</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="36">
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>5</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="36">
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>6</v>
+      </c>
+      <c r="B50" s="36" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="36">
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>7</v>
+      </c>
+      <c r="B51" s="36" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="36">
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>8</v>
+      </c>
+      <c r="B52" s="36" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="36">
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>9</v>
+      </c>
+      <c r="B53" s="36" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="36">
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>10</v>
+      </c>
+      <c r="B54" s="36" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="36">
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>11</v>
+      </c>
+      <c r="B55" s="36" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="36">
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>12</v>
+      </c>
+      <c r="B56" s="36" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="36">
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>13</v>
+      </c>
+      <c r="B57" s="36" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="36">
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>14</v>
+      </c>
+      <c r="B58" s="36" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="36">
+        <f>ROW()-ROW(Table_Animation_Trigger[N])</f>
+        <v>15</v>
+      </c>
+      <c r="B59" s="36" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="36">
+        <f>ROW()-ROW(Table_Item_Family_Type[N])</f>
+        <v>0</v>
+      </c>
+      <c r="B62" s="36" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="36">
         <f>ROW()-ROW(Table_Item_Family_Type[N])</f>
         <v>1</v>
       </c>
-      <c r="B49" s="36" t="s">
+      <c r="B63" s="36" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="36">
+    <row r="64">
+      <c r="A64" s="36">
         <f>ROW()-ROW(Table_Item_Family_Type[N])</f>
         <v>2</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="36">
+    <row r="65">
+      <c r="A65" s="36">
         <f>ROW()-ROW(Table_Item_Family_Type[N])</f>
         <v>3</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="36">
+    <row r="66">
+      <c r="A66" s="36">
         <f>ROW()-ROW(Table_Item_Family_Type[N])</f>
         <v>4</v>
       </c>
-      <c r="B52" s="67" t="s">
+      <c r="B66" s="67" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="s">
+    <row r="68">
+      <c r="A68" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>1526</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="36">
+      <c r="B68" s="1" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="36">
         <f>ROW()-ROW(Table_Moment_Day[N])</f>
         <v>0</v>
       </c>
-      <c r="B55" s="36" t="s">
+      <c r="B69" s="36" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="36">
+    <row r="70">
+      <c r="A70" s="36">
         <f>ROW()-ROW(Table_Moment_Day[N])</f>
         <v>1</v>
       </c>
-      <c r="B56" s="36" t="s">
+      <c r="B70" s="36" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="36">
+    <row r="71">
+      <c r="A71" s="36">
         <f>ROW()-ROW(Table_Moment_Day[N])</f>
         <v>2</v>
       </c>
-      <c r="B57" s="36" t="s">
+      <c r="B71" s="36" t="s">
         <v>451</v>
       </c>
     </row>
@@ -11742,7 +11909,7 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1527</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="2">
@@ -11760,7 +11927,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1528</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="4">
@@ -11769,7 +11936,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1529</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="5">
@@ -11850,7 +12017,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1530</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="14">
@@ -11895,7 +12062,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1531</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="19">
@@ -12039,7 +12206,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1532</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="36">
@@ -12047,16 +12214,16 @@
         <v>46</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1533</v>
+        <v>1547</v>
       </c>
       <c r="C36" s="68" t="s">
         <v>301</v>
       </c>
       <c r="D36" s="68" t="s">
-        <v>1534</v>
+        <v>1548</v>
       </c>
       <c r="E36" s="68" t="s">
-        <v>1535</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="37">
@@ -12065,7 +12232,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1536</v>
+        <v>1550</v>
       </c>
       <c r="C37" s="38" t="s">
         <v>310</v>
@@ -12084,7 +12251,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1537</v>
+        <v>1551</v>
       </c>
       <c r="C38" s="38" t="s">
         <v>1074</v>
@@ -12103,7 +12270,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C39" s="38" t="s">
         <v>1105</v>
@@ -12141,7 +12308,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>441</v>
@@ -12159,19 +12326,19 @@
         <v>46</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1540</v>
+        <v>1554</v>
       </c>
       <c r="C43" s="67" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="D43" s="67" t="s">
         <v>1037</v>
       </c>
       <c r="E43" s="68" t="s">
-        <v>1542</v>
+        <v>1556</v>
       </c>
       <c r="F43" s="67" t="s">
-        <v>1543</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="44">
@@ -12183,13 +12350,13 @@
         <v>686</v>
       </c>
       <c r="C44" s="44" t="s">
-        <v>1536</v>
+        <v>1550</v>
       </c>
       <c r="D44" s="44" t="s">
         <v>689</v>
       </c>
       <c r="E44" s="48" t="s">
-        <v>1544</v>
+        <v>1558</v>
       </c>
       <c r="F44" s="43" t="b">
         <v>0</v>
@@ -12204,13 +12371,13 @@
         <v>698</v>
       </c>
       <c r="C45" s="44" t="s">
-        <v>1537</v>
+        <v>1551</v>
       </c>
       <c r="D45" s="44" t="s">
         <v>1182</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>1544</v>
+        <v>1558</v>
       </c>
       <c r="F45" s="43" t="b">
         <v>0</v>
@@ -12225,13 +12392,13 @@
         <v>715</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>1537</v>
+        <v>1551</v>
       </c>
       <c r="D46" s="44" t="s">
         <v>735</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>1544</v>
+        <v>1558</v>
       </c>
       <c r="F46" s="43" t="b">
         <v>0</v>
@@ -12246,13 +12413,13 @@
         <v>720</v>
       </c>
       <c r="C47" s="44" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="D47" s="44" t="s">
         <v>1284</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>1544</v>
+        <v>1558</v>
       </c>
       <c r="F47" s="43" t="b">
         <v>0</v>
@@ -12273,7 +12440,7 @@
         <v>1357</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>1544</v>
+        <v>1558</v>
       </c>
       <c r="F48" s="43" t="b">
         <v>0</v>
@@ -12285,7 +12452,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1545</v>
+        <v>1559</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>41</v>
@@ -12294,7 +12461,7 @@
         <v>1360</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>1544</v>
+        <v>1558</v>
       </c>
       <c r="F49" s="43" t="b">
         <v>0</v>
@@ -12306,7 +12473,7 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1546</v>
+        <v>1560</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>41</v>
@@ -12315,7 +12482,7 @@
         <v>1363</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>1544</v>
+        <v>1558</v>
       </c>
       <c r="F50" s="43" t="b">
         <v>1</v>
@@ -12327,16 +12494,16 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1547</v>
+        <v>1561</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="D51" s="44" t="s">
         <v>689</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>1544</v>
+        <v>1558</v>
       </c>
       <c r="F51" s="43" t="b">
         <v>0</v>
@@ -12347,10 +12514,10 @@
         <v>46</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1548</v>
+        <v>1562</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>1549</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="54">
@@ -12359,7 +12526,7 @@
         <v>0</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1544</v>
+        <v>1558</v>
       </c>
       <c r="C54" s="51" t="s">
         <v>450</v>
@@ -12370,7 +12537,7 @@
         <v>46</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="57">
@@ -13380,16 +13547,16 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1551</v>
+        <v>1565</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1552</v>
+        <v>1566</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1553</v>
+        <v>1567</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1554</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="2">
@@ -13401,7 +13568,7 @@
         <v>313</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="D2" s="70" t="s">
         <v>310</v>
@@ -13419,7 +13586,7 @@
         <v>428</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1556</v>
+        <v>1570</v>
       </c>
       <c r="D3" s="70" t="s">
         <v>310</v>
@@ -13434,10 +13601,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1557</v>
+        <v>1571</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="D4" s="70" t="s">
         <v>310</v>
@@ -13502,7 +13669,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1558</v>
+        <v>1572</v>
       </c>
     </row>
   </sheetData>
@@ -13528,21 +13695,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1559</v>
+        <v>1573</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1560</v>
+        <v>1574</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1561</v>
+        <v>1575</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1562</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="s">
-        <v>1563</v>
+        <v>1577</v>
       </c>
       <c r="B2" s="71">
         <v>5.0</v>
@@ -13556,7 +13723,7 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>1564</v>
+        <v>1578</v>
       </c>
       <c r="B3" s="71">
         <v>4.0</v>
@@ -13570,7 +13737,7 @@
     </row>
     <row r="4">
       <c r="A4" s="37" t="s">
-        <v>1565</v>
+        <v>1579</v>
       </c>
       <c r="B4" s="71">
         <v>2.0</v>
@@ -13584,7 +13751,7 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>1566</v>
+        <v>1580</v>
       </c>
       <c r="B5" s="71">
         <v>5.0</v>
@@ -13598,7 +13765,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>1567</v>
+        <v>1581</v>
       </c>
       <c r="B6" s="71">
         <v>4.0</v>
@@ -13612,7 +13779,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>1568</v>
+        <v>1582</v>
       </c>
       <c r="B7" s="71">
         <v>4.0</v>
@@ -13626,7 +13793,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>1569</v>
+        <v>1583</v>
       </c>
       <c r="B8" s="71">
         <v>2.0</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -33,7 +33,7 @@
     <definedName name="Interval_autoInsertItem">FN!$A$1:$J$2</definedName>
     <definedName name="Interval_Unchain_Conditions">ACTION_CONDS!$A$62:$I$91</definedName>
     <definedName name="Interval_Actions">ACTION_CONDS!$A$93:$N$222</definedName>
-    <definedName name="Interval_Phrases">PHRASES!$A$1:$G$127</definedName>
+    <definedName name="Interval_Phrases">PHRASES!$A$1:$I$127</definedName>
     <definedName name="Interval_sprites">SPRITES!$A$1:$C$62</definedName>
     <definedName name="Interval_Items">ITEMS!$A$1:$J$43</definedName>
     <definedName name="Interval_Dialog_Options">DIALOGS!$A$23:$H$54</definedName>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5131" uniqueCount="1584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5385" uniqueCount="1586">
   <si>
     <t>NewItem</t>
   </si>
@@ -3518,7 +3518,13 @@
     <t>Sound</t>
   </si>
   <si>
-    <t>AnimationTrigger</t>
+    <t>AnimationTriggerTalker1</t>
+  </si>
+  <si>
+    <t>AnimationTriggerTalker2</t>
+  </si>
+  <si>
+    <t>AnimationTriggerTalker3</t>
   </si>
   <si>
     <t>Text_English</t>
@@ -3596,6 +3602,9 @@
     <t>PHRASE_DIALOG_REME_INTRO_2</t>
   </si>
   <si>
+    <t>ANIMATION_TRIGGER_STEADY</t>
+  </si>
+  <si>
     <t>Be careful! It's just cleaned</t>
   </si>
   <si>
@@ -4701,9 +4710,6 @@
   </si>
   <si>
     <t>ANIMATION_TRIGGER_SPECIAL_TWO</t>
-  </si>
-  <si>
-    <t>ANIMATION_TRIGGER_STEADY</t>
   </si>
   <si>
     <t>ANIMATION_TRIGGER_WALK_FRONT</t>
@@ -6200,15 +6206,17 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G127" displayName="Table_Phrases" name="Table_Phrases" id="18">
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I127" displayName="Table_Phrases" name="Table_Phrases" id="18">
+  <tableColumns count="9">
     <tableColumn name="N" id="1"/>
     <tableColumn name="PHRASE_ID" id="2"/>
     <tableColumn name="TalkerIndex" id="3"/>
     <tableColumn name="Sound" id="4"/>
-    <tableColumn name="AnimationTrigger" id="5"/>
-    <tableColumn name="Text_English" id="6"/>
-    <tableColumn name="Text_Spanish" id="7"/>
+    <tableColumn name="AnimationTriggerTalker1" id="5"/>
+    <tableColumn name="AnimationTriggerTalker2" id="6"/>
+    <tableColumn name="AnimationTriggerTalker3" id="7"/>
+    <tableColumn name="Text_English" id="8"/>
+    <tableColumn name="Text_Spanish" id="9"/>
   </tableColumns>
   <tableStyleInfo name="PHRASES-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -7647,11 +7655,12 @@
     <col customWidth="1" min="2" max="2" width="65.43"/>
     <col customWidth="1" min="3" max="3" width="15.57"/>
     <col customWidth="1" min="4" max="4" width="26.86"/>
-    <col customWidth="1" min="5" max="5" width="34.14"/>
-    <col customWidth="1" min="6" max="6" width="50.29"/>
-    <col customWidth="1" min="7" max="7" width="58.43"/>
-    <col customWidth="1" min="8" max="8" width="32.86"/>
-    <col customWidth="1" min="9" max="9" width="24.14"/>
+    <col customWidth="1" min="5" max="5" width="36.14"/>
+    <col customWidth="1" min="6" max="7" width="34.14"/>
+    <col customWidth="1" min="8" max="8" width="50.29"/>
+    <col customWidth="1" min="9" max="9" width="58.43"/>
+    <col customWidth="1" min="10" max="10" width="32.86"/>
+    <col customWidth="1" min="11" max="11" width="24.14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7670,11 +7679,17 @@
       <c r="E1" s="28" t="s">
         <v>1138</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="2" t="s">
         <v>1140</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="I1" s="61" t="s">
+        <v>1142</v>
       </c>
     </row>
     <row r="2">
@@ -7692,10 +7707,16 @@
         <v>924</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F2" s="62"/>
-      <c r="G2" s="37"/>
+        <v>1143</v>
+      </c>
+      <c r="F2" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G2" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H2" s="62"/>
+      <c r="I2" s="37"/>
     </row>
     <row r="3">
       <c r="A3" s="36">
@@ -7712,13 +7733,19 @@
         <v>924</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F3" s="37" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F3" s="38" t="s">
         <v>1143</v>
       </c>
-      <c r="G3" s="37" t="s">
-        <v>1144</v>
+      <c r="G3" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>1145</v>
+      </c>
+      <c r="I3" s="37" t="s">
+        <v>1146</v>
       </c>
     </row>
     <row r="4">
@@ -7736,13 +7763,19 @@
         <v>924</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F4" s="37" t="s">
-        <v>1145</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>1146</v>
+        <v>1144</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G4" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>1147</v>
+      </c>
+      <c r="I4" s="37" t="s">
+        <v>1148</v>
       </c>
     </row>
     <row r="5">
@@ -7760,13 +7793,19 @@
         <v>924</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F5" s="37" t="s">
-        <v>1147</v>
-      </c>
-      <c r="G5" s="37" t="s">
-        <v>1148</v>
+        <v>1144</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H5" s="37" t="s">
+        <v>1149</v>
+      </c>
+      <c r="I5" s="37" t="s">
+        <v>1150</v>
       </c>
     </row>
     <row r="6">
@@ -7775,7 +7814,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="C6" s="36">
         <v>0.0</v>
@@ -7784,13 +7823,19 @@
         <v>924</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F6" s="37" t="s">
-        <v>1150</v>
-      </c>
-      <c r="G6" s="37" t="s">
-        <v>1151</v>
+        <v>1144</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>1152</v>
+      </c>
+      <c r="I6" s="37" t="s">
+        <v>1153</v>
       </c>
     </row>
     <row r="7">
@@ -7799,7 +7844,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="C7" s="36">
         <v>0.0</v>
@@ -7808,13 +7853,19 @@
         <v>924</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F7" s="37" t="s">
-        <v>1153</v>
-      </c>
-      <c r="G7" s="37" t="s">
-        <v>1154</v>
+        <v>1144</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>1155</v>
+      </c>
+      <c r="I7" s="37" t="s">
+        <v>1156</v>
       </c>
     </row>
     <row r="8">
@@ -7832,13 +7883,19 @@
         <v>924</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F8" s="37" t="s">
-        <v>1155</v>
-      </c>
-      <c r="G8" s="37" t="s">
-        <v>1156</v>
+        <v>1144</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H8" s="37" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I8" s="37" t="s">
+        <v>1158</v>
       </c>
     </row>
     <row r="9">
@@ -7847,7 +7904,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="C9" s="36">
         <v>0.0</v>
@@ -7856,13 +7913,19 @@
         <v>924</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F9" s="37" t="s">
-        <v>1158</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>1159</v>
+        <v>1144</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I9" s="37" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="10">
@@ -7871,7 +7934,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="C10" s="36">
         <v>0.0</v>
@@ -7880,13 +7943,19 @@
         <v>924</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>1161</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>1162</v>
+        <v>1144</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>1163</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>1164</v>
       </c>
     </row>
     <row r="11">
@@ -7895,7 +7964,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C11" s="36">
         <v>1.0</v>
@@ -7904,13 +7973,19 @@
         <v>924</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F11" s="37" t="s">
-        <v>1164</v>
-      </c>
-      <c r="G11" s="37" t="s">
-        <v>1165</v>
+        <v>1166</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H11" s="37" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I11" s="37" t="s">
+        <v>1168</v>
       </c>
     </row>
     <row r="12">
@@ -7919,7 +7994,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="C12" s="36">
         <v>0.0</v>
@@ -7928,13 +8003,19 @@
         <v>924</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F12" s="37" t="s">
-        <v>1167</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>1168</v>
+        <v>1144</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>1170</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>1171</v>
       </c>
     </row>
     <row r="13">
@@ -7943,7 +8024,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="C13" s="36">
         <v>0.0</v>
@@ -7952,13 +8033,19 @@
         <v>924</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F13" s="37" t="s">
-        <v>1170</v>
-      </c>
-      <c r="G13" s="37" t="s">
-        <v>1171</v>
+        <v>1144</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H13" s="37" t="s">
+        <v>1173</v>
+      </c>
+      <c r="I13" s="37" t="s">
+        <v>1174</v>
       </c>
     </row>
     <row r="14">
@@ -7967,7 +8054,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="C14" s="36">
         <v>1.0</v>
@@ -7976,13 +8063,19 @@
         <v>924</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F14" s="37" t="s">
-        <v>1173</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>1174</v>
+        <v>1166</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>1176</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>1177</v>
       </c>
     </row>
     <row r="15">
@@ -7991,7 +8084,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="C15" s="36">
         <v>1.0</v>
@@ -8000,13 +8093,19 @@
         <v>924</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F15" s="37" t="s">
-        <v>1176</v>
-      </c>
-      <c r="G15" s="37" t="s">
-        <v>1177</v>
+        <v>1166</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I15" s="37" t="s">
+        <v>1180</v>
       </c>
     </row>
     <row r="16">
@@ -8018,19 +8117,25 @@
         <v>986</v>
       </c>
       <c r="C16" s="36">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D16" s="38" t="s">
         <v>924</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F16" s="37" t="s">
-        <v>1178</v>
-      </c>
-      <c r="G16" s="37" t="s">
-        <v>1179</v>
+        <v>1144</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>1182</v>
       </c>
     </row>
     <row r="17">
@@ -8048,13 +8153,19 @@
         <v>924</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F17" s="37" t="s">
-        <v>1180</v>
-      </c>
-      <c r="G17" s="37" t="s">
-        <v>1181</v>
+        <v>1144</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H17" s="37" t="s">
+        <v>1183</v>
+      </c>
+      <c r="I17" s="37" t="s">
+        <v>1184</v>
       </c>
     </row>
     <row r="18">
@@ -8063,7 +8174,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="C18" s="36">
         <v>0.0</v>
@@ -8072,13 +8183,19 @@
         <v>924</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>1183</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>1184</v>
+        <v>1144</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G18" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>1186</v>
+      </c>
+      <c r="I18" s="37" t="s">
+        <v>1187</v>
       </c>
     </row>
     <row r="19">
@@ -8096,13 +8213,19 @@
         <v>924</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F19" s="37" t="s">
-        <v>1185</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>1186</v>
+        <v>1144</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I19" s="37" t="s">
+        <v>1189</v>
       </c>
     </row>
     <row r="20">
@@ -8120,13 +8243,19 @@
         <v>924</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>1187</v>
-      </c>
-      <c r="G20" s="37" t="s">
-        <v>1188</v>
+        <v>1144</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>1190</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>1191</v>
       </c>
     </row>
     <row r="21">
@@ -8144,13 +8273,19 @@
         <v>924</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>1189</v>
-      </c>
-      <c r="G21" s="37" t="s">
-        <v>1190</v>
+        <v>1144</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G21" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>1192</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>1193</v>
       </c>
     </row>
     <row r="22">
@@ -8168,13 +8303,19 @@
         <v>924</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F22" s="37" t="s">
-        <v>1191</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>1192</v>
+        <v>1144</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>1194</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>1195</v>
       </c>
     </row>
     <row r="23">
@@ -8192,13 +8333,19 @@
         <v>924</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F23" s="37" t="s">
-        <v>1193</v>
-      </c>
-      <c r="G23" s="37" t="s">
-        <v>1194</v>
+        <v>1144</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>1196</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>1197</v>
       </c>
     </row>
     <row r="24">
@@ -8216,13 +8363,19 @@
         <v>924</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>1195</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>1196</v>
+        <v>1144</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G24" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>1199</v>
       </c>
     </row>
     <row r="25">
@@ -8240,13 +8393,19 @@
         <v>924</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>1197</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>1198</v>
+        <v>1144</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G25" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H25" s="37" t="s">
+        <v>1200</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>1201</v>
       </c>
     </row>
     <row r="26">
@@ -8264,13 +8423,19 @@
         <v>924</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>1199</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>1200</v>
+        <v>1144</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G26" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>1202</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>1203</v>
       </c>
     </row>
     <row r="27">
@@ -8279,7 +8444,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="C27" s="36">
         <v>0.0</v>
@@ -8288,13 +8453,19 @@
         <v>924</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>1202</v>
-      </c>
-      <c r="G27" s="37" t="s">
-        <v>1203</v>
+        <v>1144</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G27" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H27" s="37" t="s">
+        <v>1205</v>
+      </c>
+      <c r="I27" s="37" t="s">
+        <v>1206</v>
       </c>
     </row>
     <row r="28">
@@ -8303,7 +8474,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="C28" s="36">
         <v>1.0</v>
@@ -8312,13 +8483,19 @@
         <v>924</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>1205</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>1206</v>
+        <v>1166</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G28" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>1208</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>1209</v>
       </c>
     </row>
     <row r="29">
@@ -8336,13 +8513,19 @@
         <v>924</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>1207</v>
-      </c>
-      <c r="G29" s="37" t="s">
-        <v>1208</v>
+        <v>1144</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I29" s="37" t="s">
+        <v>1211</v>
       </c>
     </row>
     <row r="30">
@@ -8360,13 +8543,19 @@
         <v>924</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F30" s="37" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>1210</v>
+        <v>1144</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G30" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H30" s="37" t="s">
+        <v>1212</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>1213</v>
       </c>
     </row>
     <row r="31">
@@ -8384,13 +8573,19 @@
         <v>924</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>1211</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>1212</v>
+        <v>1144</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H31" s="37" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I31" s="37" t="s">
+        <v>1215</v>
       </c>
     </row>
     <row r="32">
@@ -8408,13 +8603,19 @@
         <v>924</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>1214</v>
+        <v>1144</v>
+      </c>
+      <c r="F32" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G32" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H32" s="37" t="s">
+        <v>1216</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>1217</v>
       </c>
     </row>
     <row r="33">
@@ -8432,13 +8633,19 @@
         <v>924</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>1215</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>1216</v>
+        <v>1144</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G33" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>1218</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>1219</v>
       </c>
     </row>
     <row r="34">
@@ -8447,7 +8654,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="C34" s="36">
         <v>1.0</v>
@@ -8456,13 +8663,19 @@
         <v>924</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G34" s="37" t="s">
-        <v>1219</v>
+        <v>1166</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G34" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>1222</v>
       </c>
     </row>
     <row r="35">
@@ -8471,7 +8684,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="C35" s="36">
         <v>1.0</v>
@@ -8480,13 +8693,19 @@
         <v>924</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>1221</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>1222</v>
+        <v>1166</v>
+      </c>
+      <c r="F35" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G35" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>1225</v>
       </c>
     </row>
     <row r="36">
@@ -8504,13 +8723,19 @@
         <v>924</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G36" s="37" t="s">
-        <v>1224</v>
+        <v>1144</v>
+      </c>
+      <c r="F36" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G36" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H36" s="37" t="s">
+        <v>1226</v>
+      </c>
+      <c r="I36" s="37" t="s">
+        <v>1227</v>
       </c>
     </row>
     <row r="37">
@@ -8519,7 +8744,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="C37" s="36">
         <v>0.0</v>
@@ -8528,13 +8753,19 @@
         <v>924</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>1226</v>
-      </c>
-      <c r="G37" s="37" t="s">
-        <v>1227</v>
+        <v>1144</v>
+      </c>
+      <c r="F37" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G37" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H37" s="37" t="s">
+        <v>1229</v>
+      </c>
+      <c r="I37" s="37" t="s">
+        <v>1230</v>
       </c>
     </row>
     <row r="38">
@@ -8543,7 +8774,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="C38" s="36">
         <v>1.0</v>
@@ -8552,13 +8783,19 @@
         <v>924</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F38" s="37" t="s">
-        <v>1229</v>
-      </c>
-      <c r="G38" s="37" t="s">
-        <v>1230</v>
+        <v>1166</v>
+      </c>
+      <c r="F38" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G38" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H38" s="37" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I38" s="37" t="s">
+        <v>1233</v>
       </c>
     </row>
     <row r="39">
@@ -8567,7 +8804,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="C39" s="36">
         <v>0.0</v>
@@ -8576,13 +8813,19 @@
         <v>924</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F39" s="37" t="s">
-        <v>1232</v>
-      </c>
-      <c r="G39" s="37" t="s">
-        <v>1233</v>
+        <v>1144</v>
+      </c>
+      <c r="F39" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G39" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>1235</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>1236</v>
       </c>
     </row>
     <row r="40">
@@ -8591,7 +8834,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="C40" s="36">
         <v>1.0</v>
@@ -8600,13 +8843,19 @@
         <v>924</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>1235</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>1236</v>
+        <v>1166</v>
+      </c>
+      <c r="F40" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G40" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>1238</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>1239</v>
       </c>
     </row>
     <row r="41">
@@ -8615,7 +8864,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="C41" s="36">
         <v>0.0</v>
@@ -8624,13 +8873,19 @@
         <v>924</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>1239</v>
+        <v>1144</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G41" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>1241</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>1242</v>
       </c>
     </row>
     <row r="42">
@@ -8639,7 +8894,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="C42" s="36">
         <v>1.0</v>
@@ -8648,13 +8903,19 @@
         <v>924</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>1241</v>
-      </c>
-      <c r="G42" s="37" t="s">
-        <v>1242</v>
+        <v>1166</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G42" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H42" s="37" t="s">
+        <v>1244</v>
+      </c>
+      <c r="I42" s="37" t="s">
+        <v>1245</v>
       </c>
     </row>
     <row r="43">
@@ -8663,7 +8924,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="C43" s="36">
         <v>0.0</v>
@@ -8672,13 +8933,19 @@
         <v>924</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F43" s="37" t="s">
-        <v>1244</v>
-      </c>
-      <c r="G43" s="37" t="s">
-        <v>1245</v>
+        <v>1144</v>
+      </c>
+      <c r="F43" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G43" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H43" s="37" t="s">
+        <v>1247</v>
+      </c>
+      <c r="I43" s="37" t="s">
+        <v>1248</v>
       </c>
     </row>
     <row r="44">
@@ -8687,7 +8954,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="C44" s="36">
         <v>1.0</v>
@@ -8696,13 +8963,19 @@
         <v>924</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F44" s="37" t="s">
-        <v>1247</v>
-      </c>
-      <c r="G44" s="37" t="s">
-        <v>1248</v>
+        <v>1166</v>
+      </c>
+      <c r="F44" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G44" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H44" s="37" t="s">
+        <v>1250</v>
+      </c>
+      <c r="I44" s="37" t="s">
+        <v>1251</v>
       </c>
     </row>
     <row r="45">
@@ -8711,7 +8984,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="C45" s="36">
         <v>0.0</v>
@@ -8720,13 +8993,19 @@
         <v>924</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F45" s="37" t="s">
-        <v>1250</v>
-      </c>
-      <c r="G45" s="37" t="s">
-        <v>1251</v>
+        <v>1144</v>
+      </c>
+      <c r="F45" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G45" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H45" s="37" t="s">
+        <v>1253</v>
+      </c>
+      <c r="I45" s="37" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="46">
@@ -8735,7 +9014,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="C46" s="36">
         <v>1.0</v>
@@ -8744,13 +9023,19 @@
         <v>924</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F46" s="37" t="s">
-        <v>1253</v>
-      </c>
-      <c r="G46" s="37" t="s">
-        <v>1254</v>
+        <v>1166</v>
+      </c>
+      <c r="F46" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G46" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H46" s="37" t="s">
+        <v>1256</v>
+      </c>
+      <c r="I46" s="37" t="s">
+        <v>1257</v>
       </c>
     </row>
     <row r="47">
@@ -8759,7 +9044,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="C47" s="36">
         <v>1.0</v>
@@ -8768,13 +9053,19 @@
         <v>924</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F47" s="37" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G47" s="37" t="s">
-        <v>1257</v>
+        <v>1166</v>
+      </c>
+      <c r="F47" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G47" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H47" s="37" t="s">
+        <v>1259</v>
+      </c>
+      <c r="I47" s="37" t="s">
+        <v>1260</v>
       </c>
     </row>
     <row r="48">
@@ -8783,7 +9074,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="C48" s="36">
         <v>0.0</v>
@@ -8792,13 +9083,19 @@
         <v>924</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F48" s="37" t="s">
-        <v>1259</v>
-      </c>
-      <c r="G48" s="37" t="s">
-        <v>1260</v>
+        <v>1144</v>
+      </c>
+      <c r="F48" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G48" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H48" s="37" t="s">
+        <v>1262</v>
+      </c>
+      <c r="I48" s="37" t="s">
+        <v>1263</v>
       </c>
     </row>
     <row r="49">
@@ -8807,7 +9104,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="C49" s="36">
         <v>1.0</v>
@@ -8816,13 +9113,19 @@
         <v>924</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F49" s="37" t="s">
-        <v>1262</v>
-      </c>
-      <c r="G49" s="37" t="s">
-        <v>1263</v>
+        <v>1166</v>
+      </c>
+      <c r="F49" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G49" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H49" s="37" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I49" s="37" t="s">
+        <v>1266</v>
       </c>
     </row>
     <row r="50">
@@ -8831,7 +9134,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="C50" s="36">
         <v>0.0</v>
@@ -8840,13 +9143,19 @@
         <v>924</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F50" s="37" t="s">
-        <v>1265</v>
-      </c>
-      <c r="G50" s="37" t="s">
-        <v>1266</v>
+        <v>1144</v>
+      </c>
+      <c r="F50" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G50" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H50" s="37" t="s">
+        <v>1268</v>
+      </c>
+      <c r="I50" s="37" t="s">
+        <v>1269</v>
       </c>
     </row>
     <row r="51">
@@ -8855,7 +9164,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="C51" s="36">
         <v>0.0</v>
@@ -8864,13 +9173,19 @@
         <v>924</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F51" s="37" t="s">
-        <v>1268</v>
-      </c>
-      <c r="G51" s="37" t="s">
-        <v>1269</v>
+        <v>1144</v>
+      </c>
+      <c r="F51" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G51" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H51" s="37" t="s">
+        <v>1271</v>
+      </c>
+      <c r="I51" s="37" t="s">
+        <v>1272</v>
       </c>
     </row>
     <row r="52">
@@ -8879,7 +9194,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="C52" s="36">
         <v>1.0</v>
@@ -8888,13 +9203,19 @@
         <v>924</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F52" s="37" t="s">
-        <v>1271</v>
-      </c>
-      <c r="G52" s="37" t="s">
-        <v>1272</v>
+        <v>1166</v>
+      </c>
+      <c r="F52" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G52" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H52" s="37" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I52" s="37" t="s">
+        <v>1275</v>
       </c>
     </row>
     <row r="53">
@@ -8903,7 +9224,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="C53" s="36">
         <v>1.0</v>
@@ -8912,13 +9233,19 @@
         <v>924</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F53" s="37" t="s">
-        <v>1274</v>
-      </c>
-      <c r="G53" s="37" t="s">
-        <v>1275</v>
+        <v>1166</v>
+      </c>
+      <c r="F53" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G53" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H53" s="37" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I53" s="37" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="54">
@@ -8927,7 +9254,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="C54" s="36">
         <v>1.0</v>
@@ -8936,13 +9263,19 @@
         <v>924</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F54" s="37" t="s">
-        <v>1277</v>
-      </c>
-      <c r="G54" s="37" t="s">
-        <v>1278</v>
+        <v>1166</v>
+      </c>
+      <c r="F54" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G54" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H54" s="37" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I54" s="37" t="s">
+        <v>1281</v>
       </c>
     </row>
     <row r="55">
@@ -8951,7 +9284,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="C55" s="36">
         <v>0.0</v>
@@ -8960,13 +9293,19 @@
         <v>924</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F55" s="37" t="s">
-        <v>1280</v>
-      </c>
-      <c r="G55" s="37" t="s">
-        <v>1281</v>
+        <v>1144</v>
+      </c>
+      <c r="F55" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G55" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H55" s="37" t="s">
+        <v>1283</v>
+      </c>
+      <c r="I55" s="37" t="s">
+        <v>1284</v>
       </c>
     </row>
     <row r="56">
@@ -8984,13 +9323,19 @@
         <v>924</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F56" s="37" t="s">
-        <v>1282</v>
-      </c>
-      <c r="G56" s="37" t="s">
-        <v>1283</v>
+        <v>1144</v>
+      </c>
+      <c r="F56" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G56" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H56" s="37" t="s">
+        <v>1285</v>
+      </c>
+      <c r="I56" s="37" t="s">
+        <v>1286</v>
       </c>
     </row>
     <row r="57">
@@ -8999,7 +9344,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="C57" s="36">
         <v>0.0</v>
@@ -9008,13 +9353,19 @@
         <v>924</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F57" s="37" t="s">
-        <v>1285</v>
-      </c>
-      <c r="G57" s="37" t="s">
-        <v>1286</v>
+        <v>1144</v>
+      </c>
+      <c r="F57" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G57" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H57" s="37" t="s">
+        <v>1288</v>
+      </c>
+      <c r="I57" s="37" t="s">
+        <v>1289</v>
       </c>
     </row>
     <row r="58">
@@ -9032,13 +9383,19 @@
         <v>924</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F58" s="37" t="s">
-        <v>1287</v>
-      </c>
-      <c r="G58" s="37" t="s">
-        <v>1288</v>
+        <v>1166</v>
+      </c>
+      <c r="F58" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G58" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H58" s="37" t="s">
+        <v>1290</v>
+      </c>
+      <c r="I58" s="37" t="s">
+        <v>1291</v>
       </c>
     </row>
     <row r="59">
@@ -9056,13 +9413,19 @@
         <v>924</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F59" s="37" t="s">
-        <v>1289</v>
-      </c>
-      <c r="G59" s="37" t="s">
-        <v>1290</v>
+        <v>1144</v>
+      </c>
+      <c r="F59" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G59" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H59" s="37" t="s">
+        <v>1292</v>
+      </c>
+      <c r="I59" s="37" t="s">
+        <v>1293</v>
       </c>
     </row>
     <row r="60">
@@ -9071,7 +9434,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="C60" s="36">
         <v>0.0</v>
@@ -9080,13 +9443,19 @@
         <v>924</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F60" s="37" t="s">
-        <v>1292</v>
-      </c>
-      <c r="G60" s="37" t="s">
-        <v>1293</v>
+        <v>1143</v>
+      </c>
+      <c r="F60" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G60" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H60" s="37" t="s">
+        <v>1295</v>
+      </c>
+      <c r="I60" s="37" t="s">
+        <v>1296</v>
       </c>
     </row>
     <row r="61">
@@ -9095,7 +9464,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="C61" s="36">
         <v>0.0</v>
@@ -9104,13 +9473,19 @@
         <v>924</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F61" s="37" t="s">
-        <v>1295</v>
-      </c>
-      <c r="G61" s="37" t="s">
-        <v>1296</v>
+        <v>1143</v>
+      </c>
+      <c r="F61" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G61" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H61" s="37" t="s">
+        <v>1298</v>
+      </c>
+      <c r="I61" s="37" t="s">
+        <v>1299</v>
       </c>
     </row>
     <row r="62">
@@ -9119,7 +9494,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="C62" s="36">
         <v>0.0</v>
@@ -9128,13 +9503,19 @@
         <v>924</v>
       </c>
       <c r="E62" s="44" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F62" s="37" t="s">
-        <v>1298</v>
-      </c>
-      <c r="G62" s="37" t="s">
-        <v>1299</v>
+        <v>1143</v>
+      </c>
+      <c r="F62" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G62" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H62" s="37" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I62" s="37" t="s">
+        <v>1302</v>
       </c>
     </row>
     <row r="63">
@@ -9152,13 +9533,19 @@
         <v>924</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F63" s="37" t="s">
-        <v>1300</v>
-      </c>
-      <c r="G63" s="37" t="s">
-        <v>1301</v>
+        <v>1144</v>
+      </c>
+      <c r="F63" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G63" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H63" s="37" t="s">
+        <v>1303</v>
+      </c>
+      <c r="I63" s="37" t="s">
+        <v>1304</v>
       </c>
     </row>
     <row r="64">
@@ -9167,7 +9554,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="C64" s="36">
         <v>0.0</v>
@@ -9176,13 +9563,19 @@
         <v>931</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F64" s="37" t="s">
-        <v>1303</v>
-      </c>
-      <c r="G64" s="37" t="s">
-        <v>1303</v>
+        <v>1144</v>
+      </c>
+      <c r="F64" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G64" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H64" s="37" t="s">
+        <v>1306</v>
+      </c>
+      <c r="I64" s="37" t="s">
+        <v>1306</v>
       </c>
     </row>
     <row r="65">
@@ -9191,7 +9584,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="C65" s="36">
         <v>0.0</v>
@@ -9200,13 +9593,19 @@
         <v>932</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F65" s="37" t="s">
-        <v>1305</v>
-      </c>
-      <c r="G65" s="37" t="s">
-        <v>1306</v>
+        <v>1144</v>
+      </c>
+      <c r="F65" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G65" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H65" s="37" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I65" s="37" t="s">
+        <v>1309</v>
       </c>
     </row>
     <row r="66">
@@ -9215,7 +9614,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="C66" s="36">
         <v>0.0</v>
@@ -9224,13 +9623,19 @@
         <v>933</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F66" s="37" t="s">
-        <v>1308</v>
-      </c>
-      <c r="G66" s="37" t="s">
-        <v>1309</v>
+        <v>1144</v>
+      </c>
+      <c r="F66" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G66" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H66" s="37" t="s">
+        <v>1311</v>
+      </c>
+      <c r="I66" s="37" t="s">
+        <v>1312</v>
       </c>
     </row>
     <row r="67">
@@ -9239,7 +9644,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="C67" s="36">
         <v>0.0</v>
@@ -9248,13 +9653,19 @@
         <v>934</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F67" s="37" t="s">
-        <v>1311</v>
-      </c>
-      <c r="G67" s="37" t="s">
-        <v>1312</v>
+        <v>1144</v>
+      </c>
+      <c r="F67" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G67" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H67" s="37" t="s">
+        <v>1314</v>
+      </c>
+      <c r="I67" s="37" t="s">
+        <v>1315</v>
       </c>
     </row>
     <row r="68">
@@ -9263,7 +9674,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="C68" s="36">
         <v>0.0</v>
@@ -9272,13 +9683,19 @@
         <v>924</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F68" s="37" t="s">
-        <v>1314</v>
-      </c>
-      <c r="G68" s="37" t="s">
-        <v>1315</v>
+        <v>1144</v>
+      </c>
+      <c r="F68" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G68" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H68" s="37" t="s">
+        <v>1317</v>
+      </c>
+      <c r="I68" s="37" t="s">
+        <v>1318</v>
       </c>
     </row>
     <row r="69">
@@ -9287,7 +9704,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="C69" s="36">
         <v>1.0</v>
@@ -9296,13 +9713,19 @@
         <v>924</v>
       </c>
       <c r="E69" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F69" s="37" t="s">
-        <v>1317</v>
-      </c>
-      <c r="G69" s="37" t="s">
-        <v>1318</v>
+        <v>1166</v>
+      </c>
+      <c r="F69" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G69" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H69" s="37" t="s">
+        <v>1320</v>
+      </c>
+      <c r="I69" s="37" t="s">
+        <v>1321</v>
       </c>
     </row>
     <row r="70">
@@ -9311,7 +9734,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="C70" s="36">
         <v>0.0</v>
@@ -9320,13 +9743,19 @@
         <v>924</v>
       </c>
       <c r="E70" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F70" s="37" t="s">
-        <v>1320</v>
-      </c>
-      <c r="G70" s="37" t="s">
-        <v>1321</v>
+        <v>1144</v>
+      </c>
+      <c r="F70" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G70" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H70" s="37" t="s">
+        <v>1323</v>
+      </c>
+      <c r="I70" s="37" t="s">
+        <v>1324</v>
       </c>
     </row>
     <row r="71">
@@ -9335,7 +9764,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="C71" s="36">
         <v>1.0</v>
@@ -9344,13 +9773,19 @@
         <v>924</v>
       </c>
       <c r="E71" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F71" s="37" t="s">
-        <v>1323</v>
-      </c>
-      <c r="G71" s="37" t="s">
-        <v>1324</v>
+        <v>1166</v>
+      </c>
+      <c r="F71" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G71" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H71" s="37" t="s">
+        <v>1326</v>
+      </c>
+      <c r="I71" s="37" t="s">
+        <v>1327</v>
       </c>
     </row>
     <row r="72">
@@ -9359,7 +9794,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="C72" s="36">
         <v>0.0</v>
@@ -9368,13 +9803,19 @@
         <v>924</v>
       </c>
       <c r="E72" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F72" s="37" t="s">
-        <v>1326</v>
-      </c>
-      <c r="G72" s="37" t="s">
-        <v>1327</v>
+        <v>1144</v>
+      </c>
+      <c r="F72" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G72" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H72" s="37" t="s">
+        <v>1329</v>
+      </c>
+      <c r="I72" s="37" t="s">
+        <v>1330</v>
       </c>
     </row>
     <row r="73">
@@ -9383,7 +9824,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="C73" s="36">
         <v>1.0</v>
@@ -9392,13 +9833,19 @@
         <v>924</v>
       </c>
       <c r="E73" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F73" s="37" t="s">
-        <v>1329</v>
-      </c>
-      <c r="G73" s="37" t="s">
-        <v>1330</v>
+        <v>1166</v>
+      </c>
+      <c r="F73" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G73" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H73" s="37" t="s">
+        <v>1332</v>
+      </c>
+      <c r="I73" s="37" t="s">
+        <v>1333</v>
       </c>
     </row>
     <row r="74">
@@ -9407,7 +9854,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="C74" s="36">
         <v>0.0</v>
@@ -9416,13 +9863,19 @@
         <v>924</v>
       </c>
       <c r="E74" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F74" s="37" t="s">
-        <v>1332</v>
-      </c>
-      <c r="G74" s="37" t="s">
-        <v>1333</v>
+        <v>1144</v>
+      </c>
+      <c r="F74" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G74" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H74" s="37" t="s">
+        <v>1335</v>
+      </c>
+      <c r="I74" s="37" t="s">
+        <v>1336</v>
       </c>
     </row>
     <row r="75">
@@ -9431,7 +9884,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="C75" s="36">
         <v>1.0</v>
@@ -9440,13 +9893,19 @@
         <v>924</v>
       </c>
       <c r="E75" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F75" s="37" t="s">
-        <v>1335</v>
-      </c>
-      <c r="G75" s="37" t="s">
-        <v>1336</v>
+        <v>1166</v>
+      </c>
+      <c r="F75" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G75" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H75" s="37" t="s">
+        <v>1338</v>
+      </c>
+      <c r="I75" s="37" t="s">
+        <v>1339</v>
       </c>
     </row>
     <row r="76">
@@ -9455,7 +9914,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="C76" s="36">
         <v>0.0</v>
@@ -9464,13 +9923,19 @@
         <v>924</v>
       </c>
       <c r="E76" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F76" s="37" t="s">
-        <v>1338</v>
-      </c>
-      <c r="G76" s="37" t="s">
-        <v>1339</v>
+        <v>1144</v>
+      </c>
+      <c r="F76" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G76" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H76" s="37" t="s">
+        <v>1341</v>
+      </c>
+      <c r="I76" s="37" t="s">
+        <v>1342</v>
       </c>
     </row>
     <row r="77">
@@ -9479,7 +9944,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="C77" s="36">
         <v>1.0</v>
@@ -9488,13 +9953,19 @@
         <v>924</v>
       </c>
       <c r="E77" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F77" s="37" t="s">
-        <v>1341</v>
-      </c>
-      <c r="G77" s="37" t="s">
-        <v>1342</v>
+        <v>1166</v>
+      </c>
+      <c r="F77" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G77" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H77" s="37" t="s">
+        <v>1344</v>
+      </c>
+      <c r="I77" s="37" t="s">
+        <v>1345</v>
       </c>
     </row>
     <row r="78">
@@ -9503,7 +9974,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="C78" s="36">
         <v>0.0</v>
@@ -9512,13 +9983,19 @@
         <v>924</v>
       </c>
       <c r="E78" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F78" s="37" t="s">
-        <v>1344</v>
-      </c>
-      <c r="G78" s="37" t="s">
-        <v>1345</v>
+        <v>1144</v>
+      </c>
+      <c r="F78" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G78" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H78" s="37" t="s">
+        <v>1347</v>
+      </c>
+      <c r="I78" s="37" t="s">
+        <v>1348</v>
       </c>
     </row>
     <row r="79">
@@ -9536,13 +10013,19 @@
         <v>924</v>
       </c>
       <c r="E79" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F79" s="37" t="s">
-        <v>1346</v>
-      </c>
-      <c r="G79" s="37" t="s">
-        <v>1347</v>
+        <v>1144</v>
+      </c>
+      <c r="F79" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G79" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H79" s="37" t="s">
+        <v>1349</v>
+      </c>
+      <c r="I79" s="37" t="s">
+        <v>1350</v>
       </c>
     </row>
     <row r="80">
@@ -9551,7 +10034,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C80" s="36">
         <v>1.0</v>
@@ -9560,13 +10043,19 @@
         <v>924</v>
       </c>
       <c r="E80" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F80" s="37" t="s">
-        <v>1349</v>
-      </c>
-      <c r="G80" s="37" t="s">
-        <v>1350</v>
+        <v>1166</v>
+      </c>
+      <c r="F80" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G80" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H80" s="37" t="s">
+        <v>1352</v>
+      </c>
+      <c r="I80" s="37" t="s">
+        <v>1353</v>
       </c>
     </row>
     <row r="81">
@@ -9575,7 +10064,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="C81" s="36">
         <v>1.0</v>
@@ -9584,13 +10073,19 @@
         <v>924</v>
       </c>
       <c r="E81" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F81" s="37" t="s">
-        <v>1352</v>
-      </c>
-      <c r="G81" s="37" t="s">
-        <v>1353</v>
+        <v>1166</v>
+      </c>
+      <c r="F81" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G81" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H81" s="37" t="s">
+        <v>1355</v>
+      </c>
+      <c r="I81" s="37" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="82">
@@ -9599,7 +10094,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="C82" s="36">
         <v>1.0</v>
@@ -9608,13 +10103,19 @@
         <v>924</v>
       </c>
       <c r="E82" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F82" s="37" t="s">
-        <v>1355</v>
-      </c>
-      <c r="G82" s="37" t="s">
-        <v>1356</v>
+        <v>1166</v>
+      </c>
+      <c r="F82" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G82" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H82" s="37" t="s">
+        <v>1358</v>
+      </c>
+      <c r="I82" s="37" t="s">
+        <v>1359</v>
       </c>
     </row>
     <row r="83">
@@ -9623,7 +10124,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="C83" s="36">
         <v>0.0</v>
@@ -9632,13 +10133,19 @@
         <v>924</v>
       </c>
       <c r="E83" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F83" s="37" t="s">
-        <v>1358</v>
-      </c>
-      <c r="G83" s="37" t="s">
-        <v>1359</v>
+        <v>1144</v>
+      </c>
+      <c r="F83" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G83" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H83" s="37" t="s">
+        <v>1361</v>
+      </c>
+      <c r="I83" s="37" t="s">
+        <v>1362</v>
       </c>
     </row>
     <row r="84">
@@ -9647,7 +10154,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="C84" s="36">
         <v>0.0</v>
@@ -9656,13 +10163,19 @@
         <v>924</v>
       </c>
       <c r="E84" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F84" s="37" t="s">
-        <v>1361</v>
-      </c>
-      <c r="G84" s="37" t="s">
-        <v>1362</v>
+        <v>1144</v>
+      </c>
+      <c r="F84" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G84" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H84" s="37" t="s">
+        <v>1364</v>
+      </c>
+      <c r="I84" s="37" t="s">
+        <v>1365</v>
       </c>
     </row>
     <row r="85">
@@ -9671,7 +10184,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="36" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="C85" s="36">
         <v>0.0</v>
@@ -9680,13 +10193,19 @@
         <v>924</v>
       </c>
       <c r="E85" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F85" s="37" t="s">
-        <v>1364</v>
-      </c>
-      <c r="G85" s="37" t="s">
-        <v>1365</v>
+        <v>1144</v>
+      </c>
+      <c r="F85" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G85" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H85" s="37" t="s">
+        <v>1367</v>
+      </c>
+      <c r="I85" s="37" t="s">
+        <v>1368</v>
       </c>
     </row>
     <row r="86">
@@ -9704,13 +10223,19 @@
         <v>924</v>
       </c>
       <c r="E86" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F86" s="37" t="s">
-        <v>1366</v>
-      </c>
-      <c r="G86" s="37" t="s">
-        <v>1367</v>
+        <v>1144</v>
+      </c>
+      <c r="F86" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G86" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H86" s="37" t="s">
+        <v>1369</v>
+      </c>
+      <c r="I86" s="37" t="s">
+        <v>1370</v>
       </c>
     </row>
     <row r="87">
@@ -9728,13 +10253,19 @@
         <v>924</v>
       </c>
       <c r="E87" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F87" s="37" t="s">
-        <v>1368</v>
-      </c>
-      <c r="G87" s="37" t="s">
-        <v>1368</v>
+        <v>1144</v>
+      </c>
+      <c r="F87" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G87" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H87" s="37" t="s">
+        <v>1371</v>
+      </c>
+      <c r="I87" s="37" t="s">
+        <v>1371</v>
       </c>
     </row>
     <row r="88">
@@ -9752,13 +10283,19 @@
         <v>924</v>
       </c>
       <c r="E88" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F88" s="37" t="s">
-        <v>1369</v>
-      </c>
-      <c r="G88" s="37" t="s">
-        <v>1370</v>
+        <v>1144</v>
+      </c>
+      <c r="F88" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G88" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H88" s="37" t="s">
+        <v>1372</v>
+      </c>
+      <c r="I88" s="37" t="s">
+        <v>1373</v>
       </c>
     </row>
     <row r="89">
@@ -9776,13 +10313,19 @@
         <v>924</v>
       </c>
       <c r="E89" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F89" s="37" t="s">
-        <v>1371</v>
-      </c>
-      <c r="G89" s="37" t="s">
-        <v>1372</v>
+        <v>1144</v>
+      </c>
+      <c r="F89" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G89" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H89" s="37" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I89" s="37" t="s">
+        <v>1375</v>
       </c>
     </row>
     <row r="90">
@@ -9800,13 +10343,19 @@
         <v>924</v>
       </c>
       <c r="E90" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F90" s="37" t="s">
-        <v>1373</v>
-      </c>
-      <c r="G90" s="37" t="s">
-        <v>1374</v>
+        <v>1144</v>
+      </c>
+      <c r="F90" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G90" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H90" s="37" t="s">
+        <v>1376</v>
+      </c>
+      <c r="I90" s="37" t="s">
+        <v>1377</v>
       </c>
     </row>
     <row r="91">
@@ -9824,13 +10373,19 @@
         <v>924</v>
       </c>
       <c r="E91" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F91" s="37" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G91" s="37" t="s">
-        <v>1376</v>
+        <v>1144</v>
+      </c>
+      <c r="F91" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G91" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H91" s="37" t="s">
+        <v>1378</v>
+      </c>
+      <c r="I91" s="37" t="s">
+        <v>1379</v>
       </c>
     </row>
     <row r="92">
@@ -9848,13 +10403,19 @@
         <v>924</v>
       </c>
       <c r="E92" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F92" s="37" t="s">
-        <v>1377</v>
-      </c>
-      <c r="G92" s="37" t="s">
-        <v>1378</v>
+        <v>1144</v>
+      </c>
+      <c r="F92" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G92" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H92" s="37" t="s">
+        <v>1380</v>
+      </c>
+      <c r="I92" s="37" t="s">
+        <v>1381</v>
       </c>
     </row>
     <row r="93">
@@ -9872,13 +10433,19 @@
         <v>924</v>
       </c>
       <c r="E93" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F93" s="37" t="s">
-        <v>1379</v>
-      </c>
-      <c r="G93" s="37" t="s">
-        <v>1380</v>
+        <v>1144</v>
+      </c>
+      <c r="F93" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G93" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H93" s="37" t="s">
+        <v>1382</v>
+      </c>
+      <c r="I93" s="37" t="s">
+        <v>1383</v>
       </c>
     </row>
     <row r="94">
@@ -9896,13 +10463,19 @@
         <v>924</v>
       </c>
       <c r="E94" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F94" s="37" t="s">
-        <v>1381</v>
-      </c>
-      <c r="G94" s="37" t="s">
-        <v>1382</v>
+        <v>1144</v>
+      </c>
+      <c r="F94" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G94" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H94" s="37" t="s">
+        <v>1384</v>
+      </c>
+      <c r="I94" s="37" t="s">
+        <v>1385</v>
       </c>
     </row>
     <row r="95">
@@ -9920,13 +10493,19 @@
         <v>929</v>
       </c>
       <c r="E95" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F95" s="37" t="s">
-        <v>1383</v>
-      </c>
-      <c r="G95" s="37" t="s">
-        <v>1384</v>
+        <v>1144</v>
+      </c>
+      <c r="F95" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G95" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H95" s="37" t="s">
+        <v>1386</v>
+      </c>
+      <c r="I95" s="37" t="s">
+        <v>1387</v>
       </c>
     </row>
     <row r="96">
@@ -9944,13 +10523,19 @@
         <v>924</v>
       </c>
       <c r="E96" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F96" s="37" t="s">
-        <v>1385</v>
-      </c>
-      <c r="G96" s="37" t="s">
-        <v>1386</v>
+        <v>1144</v>
+      </c>
+      <c r="F96" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G96" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H96" s="37" t="s">
+        <v>1388</v>
+      </c>
+      <c r="I96" s="37" t="s">
+        <v>1389</v>
       </c>
     </row>
     <row r="97">
@@ -9968,13 +10553,19 @@
         <v>924</v>
       </c>
       <c r="E97" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F97" s="37" t="s">
-        <v>1387</v>
-      </c>
-      <c r="G97" s="37" t="s">
-        <v>1388</v>
+        <v>1144</v>
+      </c>
+      <c r="F97" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G97" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H97" s="37" t="s">
+        <v>1390</v>
+      </c>
+      <c r="I97" s="37" t="s">
+        <v>1391</v>
       </c>
     </row>
     <row r="98">
@@ -9992,13 +10583,19 @@
         <v>924</v>
       </c>
       <c r="E98" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F98" s="37" t="s">
-        <v>1389</v>
-      </c>
-      <c r="G98" s="37" t="s">
-        <v>1390</v>
+        <v>1144</v>
+      </c>
+      <c r="F98" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G98" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H98" s="37" t="s">
+        <v>1392</v>
+      </c>
+      <c r="I98" s="37" t="s">
+        <v>1393</v>
       </c>
     </row>
     <row r="99">
@@ -10016,13 +10613,19 @@
         <v>924</v>
       </c>
       <c r="E99" s="44" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F99" s="37" t="s">
-        <v>1391</v>
-      </c>
-      <c r="G99" s="37" t="s">
-        <v>1392</v>
+        <v>1143</v>
+      </c>
+      <c r="F99" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G99" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H99" s="37" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I99" s="37" t="s">
+        <v>1395</v>
       </c>
     </row>
     <row r="100">
@@ -10040,13 +10643,19 @@
         <v>924</v>
       </c>
       <c r="E100" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F100" s="37" t="s">
-        <v>1393</v>
-      </c>
-      <c r="G100" s="37" t="s">
-        <v>1394</v>
+        <v>1144</v>
+      </c>
+      <c r="F100" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G100" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H100" s="37" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I100" s="37" t="s">
+        <v>1397</v>
       </c>
     </row>
     <row r="101">
@@ -10064,13 +10673,19 @@
         <v>924</v>
       </c>
       <c r="E101" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F101" s="37" t="s">
-        <v>1395</v>
-      </c>
-      <c r="G101" s="37" t="s">
-        <v>1396</v>
+        <v>1144</v>
+      </c>
+      <c r="F101" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G101" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H101" s="37" t="s">
+        <v>1398</v>
+      </c>
+      <c r="I101" s="37" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="102">
@@ -10088,13 +10703,19 @@
         <v>924</v>
       </c>
       <c r="E102" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F102" s="37" t="s">
-        <v>1397</v>
-      </c>
-      <c r="G102" s="37" t="s">
-        <v>1398</v>
+        <v>1144</v>
+      </c>
+      <c r="F102" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G102" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H102" s="37" t="s">
+        <v>1400</v>
+      </c>
+      <c r="I102" s="37" t="s">
+        <v>1401</v>
       </c>
     </row>
     <row r="103">
@@ -10103,7 +10724,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="36" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="C103" s="36">
         <v>0.0</v>
@@ -10112,13 +10733,19 @@
         <v>924</v>
       </c>
       <c r="E103" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F103" s="37" t="s">
-        <v>1400</v>
-      </c>
-      <c r="G103" s="37" t="s">
-        <v>1401</v>
+        <v>1144</v>
+      </c>
+      <c r="F103" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G103" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H103" s="37" t="s">
+        <v>1403</v>
+      </c>
+      <c r="I103" s="37" t="s">
+        <v>1404</v>
       </c>
     </row>
     <row r="104">
@@ -10127,7 +10754,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="C104" s="36">
         <v>1.0</v>
@@ -10136,13 +10763,19 @@
         <v>924</v>
       </c>
       <c r="E104" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F104" s="37" t="s">
-        <v>1403</v>
-      </c>
-      <c r="G104" s="37" t="s">
-        <v>1404</v>
+        <v>1166</v>
+      </c>
+      <c r="F104" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G104" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H104" s="37" t="s">
+        <v>1406</v>
+      </c>
+      <c r="I104" s="37" t="s">
+        <v>1407</v>
       </c>
     </row>
     <row r="105">
@@ -10151,7 +10784,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="C105" s="36">
         <v>0.0</v>
@@ -10160,13 +10793,19 @@
         <v>924</v>
       </c>
       <c r="E105" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F105" s="37" t="s">
-        <v>1406</v>
-      </c>
-      <c r="G105" s="37" t="s">
-        <v>1407</v>
+        <v>1144</v>
+      </c>
+      <c r="F105" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G105" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H105" s="37" t="s">
+        <v>1409</v>
+      </c>
+      <c r="I105" s="37" t="s">
+        <v>1410</v>
       </c>
     </row>
     <row r="106">
@@ -10175,7 +10814,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="C106" s="36">
         <v>1.0</v>
@@ -10184,13 +10823,19 @@
         <v>924</v>
       </c>
       <c r="E106" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F106" s="37" t="s">
-        <v>1409</v>
-      </c>
-      <c r="G106" s="37" t="s">
-        <v>1410</v>
+        <v>1166</v>
+      </c>
+      <c r="F106" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G106" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H106" s="37" t="s">
+        <v>1412</v>
+      </c>
+      <c r="I106" s="37" t="s">
+        <v>1413</v>
       </c>
     </row>
     <row r="107">
@@ -10199,7 +10844,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="C107" s="36">
         <v>0.0</v>
@@ -10208,13 +10853,19 @@
         <v>924</v>
       </c>
       <c r="E107" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F107" s="37" t="s">
-        <v>1412</v>
-      </c>
-      <c r="G107" s="37" t="s">
-        <v>1413</v>
+        <v>1144</v>
+      </c>
+      <c r="F107" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G107" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H107" s="37" t="s">
+        <v>1415</v>
+      </c>
+      <c r="I107" s="37" t="s">
+        <v>1416</v>
       </c>
     </row>
     <row r="108">
@@ -10223,7 +10874,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="C108" s="36">
         <v>1.0</v>
@@ -10232,13 +10883,19 @@
         <v>924</v>
       </c>
       <c r="E108" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F108" s="37" t="s">
-        <v>1415</v>
-      </c>
-      <c r="G108" s="37" t="s">
-        <v>1415</v>
+        <v>1166</v>
+      </c>
+      <c r="F108" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G108" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H108" s="37" t="s">
+        <v>1418</v>
+      </c>
+      <c r="I108" s="37" t="s">
+        <v>1418</v>
       </c>
     </row>
     <row r="109">
@@ -10247,7 +10904,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="C109" s="36">
         <v>0.0</v>
@@ -10256,13 +10913,19 @@
         <v>924</v>
       </c>
       <c r="E109" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F109" s="37" t="s">
-        <v>1417</v>
-      </c>
-      <c r="G109" s="37" t="s">
-        <v>1418</v>
+        <v>1144</v>
+      </c>
+      <c r="F109" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G109" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H109" s="37" t="s">
+        <v>1420</v>
+      </c>
+      <c r="I109" s="37" t="s">
+        <v>1421</v>
       </c>
     </row>
     <row r="110">
@@ -10271,7 +10934,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="C110" s="36">
         <v>1.0</v>
@@ -10280,13 +10943,19 @@
         <v>924</v>
       </c>
       <c r="E110" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F110" s="37" t="s">
-        <v>1420</v>
-      </c>
-      <c r="G110" s="37" t="s">
-        <v>1421</v>
+        <v>1166</v>
+      </c>
+      <c r="F110" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G110" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H110" s="37" t="s">
+        <v>1423</v>
+      </c>
+      <c r="I110" s="37" t="s">
+        <v>1424</v>
       </c>
     </row>
     <row r="111">
@@ -10295,7 +10964,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="C111" s="36">
         <v>0.0</v>
@@ -10304,13 +10973,19 @@
         <v>924</v>
       </c>
       <c r="E111" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F111" s="37" t="s">
-        <v>1423</v>
-      </c>
-      <c r="G111" s="37" t="s">
-        <v>1424</v>
+        <v>1144</v>
+      </c>
+      <c r="F111" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G111" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H111" s="37" t="s">
+        <v>1426</v>
+      </c>
+      <c r="I111" s="37" t="s">
+        <v>1427</v>
       </c>
     </row>
     <row r="112">
@@ -10319,7 +10994,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="36" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
       <c r="C112" s="36">
         <v>1.0</v>
@@ -10328,13 +11003,19 @@
         <v>924</v>
       </c>
       <c r="E112" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F112" s="37" t="s">
-        <v>1426</v>
-      </c>
-      <c r="G112" s="37" t="s">
-        <v>1427</v>
+        <v>1166</v>
+      </c>
+      <c r="F112" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G112" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H112" s="37" t="s">
+        <v>1429</v>
+      </c>
+      <c r="I112" s="37" t="s">
+        <v>1430</v>
       </c>
     </row>
     <row r="113">
@@ -10343,7 +11024,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="C113" s="36">
         <v>0.0</v>
@@ -10352,13 +11033,19 @@
         <v>924</v>
       </c>
       <c r="E113" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F113" s="37" t="s">
-        <v>1429</v>
-      </c>
-      <c r="G113" s="37" t="s">
-        <v>1430</v>
+        <v>1144</v>
+      </c>
+      <c r="F113" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G113" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H113" s="37" t="s">
+        <v>1432</v>
+      </c>
+      <c r="I113" s="37" t="s">
+        <v>1433</v>
       </c>
     </row>
     <row r="114">
@@ -10376,13 +11063,19 @@
         <v>924</v>
       </c>
       <c r="E114" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F114" s="37" t="s">
-        <v>1431</v>
-      </c>
-      <c r="G114" s="37" t="s">
-        <v>1432</v>
+        <v>1144</v>
+      </c>
+      <c r="F114" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G114" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H114" s="37" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I114" s="37" t="s">
+        <v>1435</v>
       </c>
     </row>
     <row r="115">
@@ -10391,7 +11084,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="C115" s="36">
         <v>0.0</v>
@@ -10400,13 +11093,19 @@
         <v>924</v>
       </c>
       <c r="E115" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F115" s="37" t="s">
-        <v>1434</v>
-      </c>
-      <c r="G115" s="37" t="s">
-        <v>1435</v>
+        <v>1144</v>
+      </c>
+      <c r="F115" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G115" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H115" s="37" t="s">
+        <v>1437</v>
+      </c>
+      <c r="I115" s="37" t="s">
+        <v>1438</v>
       </c>
     </row>
     <row r="116">
@@ -10415,7 +11114,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="36" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="C116" s="36">
         <v>1.0</v>
@@ -10424,13 +11123,19 @@
         <v>924</v>
       </c>
       <c r="E116" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F116" s="37" t="s">
-        <v>1437</v>
-      </c>
-      <c r="G116" s="37" t="s">
-        <v>1438</v>
+        <v>1166</v>
+      </c>
+      <c r="F116" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G116" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H116" s="37" t="s">
+        <v>1440</v>
+      </c>
+      <c r="I116" s="37" t="s">
+        <v>1441</v>
       </c>
     </row>
     <row r="117">
@@ -10448,13 +11153,19 @@
         <v>924</v>
       </c>
       <c r="E117" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F117" s="37" t="s">
-        <v>1439</v>
-      </c>
-      <c r="G117" s="37" t="s">
-        <v>1440</v>
+        <v>1144</v>
+      </c>
+      <c r="F117" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G117" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H117" s="37" t="s">
+        <v>1442</v>
+      </c>
+      <c r="I117" s="37" t="s">
+        <v>1443</v>
       </c>
     </row>
     <row r="118">
@@ -10472,13 +11183,19 @@
         <v>927</v>
       </c>
       <c r="E118" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F118" s="37" t="s">
-        <v>1441</v>
-      </c>
-      <c r="G118" s="37" t="s">
-        <v>1442</v>
+        <v>1144</v>
+      </c>
+      <c r="F118" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G118" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H118" s="37" t="s">
+        <v>1444</v>
+      </c>
+      <c r="I118" s="37" t="s">
+        <v>1445</v>
       </c>
     </row>
     <row r="119">
@@ -10496,13 +11213,19 @@
         <v>924</v>
       </c>
       <c r="E119" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F119" s="37" t="s">
-        <v>1443</v>
-      </c>
-      <c r="G119" s="37" t="s">
-        <v>1444</v>
+        <v>1144</v>
+      </c>
+      <c r="F119" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G119" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H119" s="37" t="s">
+        <v>1446</v>
+      </c>
+      <c r="I119" s="37" t="s">
+        <v>1447</v>
       </c>
     </row>
     <row r="120">
@@ -10520,12 +11243,18 @@
         <v>924</v>
       </c>
       <c r="E120" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F120" s="37" t="s">
-        <v>1445</v>
-      </c>
-      <c r="G120" s="37" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F120" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G120" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H120" s="37" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I120" s="37" t="s">
         <v>14</v>
       </c>
     </row>
@@ -10544,12 +11273,18 @@
         <v>924</v>
       </c>
       <c r="E121" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F121" s="37" t="s">
-        <v>1446</v>
-      </c>
-      <c r="G121" s="37" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F121" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G121" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H121" s="37" t="s">
+        <v>1449</v>
+      </c>
+      <c r="I121" s="37" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10568,13 +11303,19 @@
         <v>924</v>
       </c>
       <c r="E122" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F122" s="37" t="s">
-        <v>1447</v>
-      </c>
-      <c r="G122" s="37" t="s">
-        <v>1448</v>
+        <v>1144</v>
+      </c>
+      <c r="F122" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G122" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H122" s="37" t="s">
+        <v>1450</v>
+      </c>
+      <c r="I122" s="37" t="s">
+        <v>1451</v>
       </c>
     </row>
     <row r="123">
@@ -10583,7 +11324,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="C123" s="36">
         <v>0.0</v>
@@ -10592,13 +11333,19 @@
         <v>924</v>
       </c>
       <c r="E123" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F123" s="37" t="s">
-        <v>1450</v>
-      </c>
-      <c r="G123" s="37" t="s">
-        <v>1451</v>
+        <v>1144</v>
+      </c>
+      <c r="F123" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G123" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H123" s="37" t="s">
+        <v>1453</v>
+      </c>
+      <c r="I123" s="37" t="s">
+        <v>1454</v>
       </c>
     </row>
     <row r="124">
@@ -10607,7 +11354,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="36" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="C124" s="36">
         <v>0.0</v>
@@ -10616,13 +11363,19 @@
         <v>924</v>
       </c>
       <c r="E124" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F124" s="37" t="s">
-        <v>1453</v>
-      </c>
-      <c r="G124" s="37" t="s">
-        <v>1454</v>
+        <v>1144</v>
+      </c>
+      <c r="F124" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G124" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H124" s="37" t="s">
+        <v>1456</v>
+      </c>
+      <c r="I124" s="37" t="s">
+        <v>1457</v>
       </c>
     </row>
     <row r="125">
@@ -10640,13 +11393,19 @@
         <v>924</v>
       </c>
       <c r="E125" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F125" s="37" t="s">
-        <v>1455</v>
-      </c>
-      <c r="G125" s="37" t="s">
-        <v>1456</v>
+        <v>1144</v>
+      </c>
+      <c r="F125" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G125" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H125" s="37" t="s">
+        <v>1458</v>
+      </c>
+      <c r="I125" s="37" t="s">
+        <v>1459</v>
       </c>
     </row>
     <row r="126">
@@ -10664,13 +11423,19 @@
         <v>924</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F126" s="37" t="s">
-        <v>1457</v>
-      </c>
-      <c r="G126" s="37" t="s">
-        <v>1458</v>
+        <v>1144</v>
+      </c>
+      <c r="F126" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G126" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H126" s="37" t="s">
+        <v>1460</v>
+      </c>
+      <c r="I126" s="37" t="s">
+        <v>1461</v>
       </c>
     </row>
     <row r="127">
@@ -10679,7 +11444,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="36" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
       <c r="C127" s="36">
         <v>0.0</v>
@@ -10688,18 +11453,24 @@
         <v>924</v>
       </c>
       <c r="E127" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F127" s="37" t="s">
-        <v>1460</v>
-      </c>
-      <c r="G127" s="37" t="s">
-        <v>1460</v>
+        <v>1144</v>
+      </c>
+      <c r="F127" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G127" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H127" s="37" t="s">
+        <v>1463</v>
+      </c>
+      <c r="I127" s="37" t="s">
+        <v>1463</v>
       </c>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="D2:E127">
+    <dataValidation type="list" allowBlank="1" sqref="D2:G127">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -10736,34 +11507,34 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1461</v>
+        <v>1464</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>1462</v>
+        <v>1465</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="K1" s="63" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="2" ht="186.0" customHeight="1">
@@ -10772,7 +11543,7 @@
         <v>-1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
       <c r="C2" s="65" t="s">
         <v>312</v>
@@ -10808,7 +11579,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>1472</v>
+        <v>1475</v>
       </c>
       <c r="C3" s="65" t="s">
         <v>856</v>
@@ -10817,10 +11588,10 @@
         <v>941</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>1473</v>
+        <v>1476</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>310</v>
@@ -10844,19 +11615,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="D4" s="66" t="s">
         <v>941</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>310</v>
@@ -10880,19 +11651,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="D5" s="66" t="s">
         <v>941</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1480</v>
+        <v>1483</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>310</v>
@@ -10916,19 +11687,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="D6" s="66" t="s">
         <v>941</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1483</v>
+        <v>1486</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>310</v>
@@ -10952,25 +11723,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1484</v>
+        <v>1487</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1485</v>
+        <v>1488</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>1485</v>
+        <v>1488</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>1487</v>
+        <v>1490</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="I7" s="35" t="s">
         <v>604</v>
@@ -10988,25 +11759,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>1488</v>
+        <v>1491</v>
       </c>
       <c r="C8" s="32" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D8" s="66" t="s">
         <v>1489</v>
       </c>
-      <c r="D8" s="66" t="s">
-        <v>1486</v>
-      </c>
       <c r="E8" s="35" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="I8" s="35" t="s">
         <v>604</v>
@@ -11036,7 +11807,7 @@
         <v>893</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>310</v>
@@ -11060,25 +11831,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="D10" s="66" t="s">
         <v>937</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1494</v>
+        <v>1497</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="I10" s="35" t="s">
         <v>667</v>
@@ -11096,25 +11867,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1496</v>
+        <v>1499</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="D11" s="66" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>310</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="I11" s="35" t="s">
         <v>604</v>
@@ -11132,19 +11903,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="D12" s="66" t="s">
         <v>936</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>310</v>
@@ -11168,19 +11939,19 @@
         <v>10</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="D13" s="66" t="s">
         <v>936</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>310</v>
@@ -11207,13 +11978,13 @@
         <v>21</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
       <c r="D14" s="66" t="s">
         <v>924</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
       <c r="F14" s="35" t="s">
         <v>336</v>
@@ -11240,7 +12011,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="C15" s="65" t="s">
         <v>312</v>
@@ -11303,7 +12074,7 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="2">
@@ -11330,7 +12101,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="5">
@@ -11339,7 +12110,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="6">
@@ -11351,7 +12122,7 @@
         <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="8">
@@ -11359,7 +12130,7 @@
         <v>0.0</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="9">
@@ -11367,7 +12138,7 @@
         <v>1.0</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="10">
@@ -11375,7 +12146,7 @@
         <v>2.0</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="11">
@@ -11383,7 +12154,7 @@
         <v>3.0</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="12">
@@ -11391,7 +12162,7 @@
         <v>4.0</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1515</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="13">
@@ -11399,7 +12170,7 @@
         <v>5.0</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="15">
@@ -11407,7 +12178,7 @@
         <v>46</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1517</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="16">
@@ -11425,7 +12196,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1518</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="18">
@@ -11470,7 +12241,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1519</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="23">
@@ -11487,7 +12258,7 @@
         <v>46</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="26">
@@ -11532,7 +12303,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1521</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="31">
@@ -11559,7 +12330,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1522</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="34">
@@ -11577,7 +12348,7 @@
         <v>9</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1523</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="36">
@@ -11639,7 +12410,7 @@
         <v>46</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1524</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="44">
@@ -11648,7 +12419,7 @@
         <v>0</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="45">
@@ -11657,7 +12428,7 @@
         <v>1</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1525</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="46">
@@ -11666,7 +12437,7 @@
         <v>2</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1526</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="47">
@@ -11675,7 +12446,7 @@
         <v>3</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1527</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="48">
@@ -11684,7 +12455,7 @@
         <v>4</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1528</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="49">
@@ -11693,7 +12464,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1529</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="50">
@@ -11702,7 +12473,7 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1530</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="51">
@@ -11711,7 +12482,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1531</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="52">
@@ -11720,7 +12491,7 @@
         <v>8</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1532</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="53">
@@ -11729,7 +12500,7 @@
         <v>9</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1533</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="54">
@@ -11738,7 +12509,7 @@
         <v>10</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="55">
@@ -11747,7 +12518,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="56">
@@ -11756,7 +12527,7 @@
         <v>12</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="57">
@@ -11765,7 +12536,7 @@
         <v>13</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="58">
@@ -11774,7 +12545,7 @@
         <v>14</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="59">
@@ -11783,7 +12554,7 @@
         <v>15</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="61">
@@ -11791,7 +12562,7 @@
         <v>46</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="62">
@@ -11844,7 +12615,7 @@
         <v>46</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="69">
@@ -11909,7 +12680,7 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="2">
@@ -11927,7 +12698,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="4">
@@ -11936,7 +12707,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="5">
@@ -12017,7 +12788,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="14">
@@ -12062,7 +12833,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="19">
@@ -12206,7 +12977,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="36">
@@ -12214,16 +12985,16 @@
         <v>46</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="C36" s="68" t="s">
         <v>301</v>
       </c>
       <c r="D36" s="68" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="E36" s="68" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="37">
@@ -12232,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="C37" s="38" t="s">
         <v>310</v>
@@ -12251,7 +13022,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="C38" s="38" t="s">
         <v>1074</v>
@@ -12270,7 +13041,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="C39" s="38" t="s">
         <v>1105</v>
@@ -12308,7 +13079,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>441</v>
@@ -12326,19 +13097,19 @@
         <v>46</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="C43" s="67" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="D43" s="67" t="s">
         <v>1037</v>
       </c>
       <c r="E43" s="68" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="F43" s="67" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="44">
@@ -12350,13 +13121,13 @@
         <v>686</v>
       </c>
       <c r="C44" s="44" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="D44" s="44" t="s">
         <v>689</v>
       </c>
       <c r="E44" s="48" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="F44" s="43" t="b">
         <v>0</v>
@@ -12371,13 +13142,13 @@
         <v>698</v>
       </c>
       <c r="C45" s="44" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="F45" s="43" t="b">
         <v>0</v>
@@ -12392,13 +13163,13 @@
         <v>715</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="D46" s="44" t="s">
         <v>735</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="F46" s="43" t="b">
         <v>0</v>
@@ -12413,13 +13184,13 @@
         <v>720</v>
       </c>
       <c r="C47" s="44" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="F47" s="43" t="b">
         <v>0</v>
@@ -12437,10 +13208,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="F48" s="43" t="b">
         <v>0</v>
@@ -12452,16 +13223,16 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="F49" s="43" t="b">
         <v>0</v>
@@ -12473,16 +13244,16 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>41</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="F50" s="43" t="b">
         <v>1</v>
@@ -12494,16 +13265,16 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="D51" s="44" t="s">
         <v>689</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="F51" s="43" t="b">
         <v>0</v>
@@ -12514,10 +13285,10 @@
         <v>46</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="54">
@@ -12526,7 +13297,7 @@
         <v>0</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="C54" s="51" t="s">
         <v>450</v>
@@ -12537,7 +13308,7 @@
         <v>46</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="57">
@@ -13547,16 +14318,16 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="2">
@@ -13568,7 +14339,7 @@
         <v>313</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="D2" s="70" t="s">
         <v>310</v>
@@ -13586,7 +14357,7 @@
         <v>428</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="D3" s="70" t="s">
         <v>310</v>
@@ -13601,10 +14372,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>1571</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>1569</v>
       </c>
       <c r="D4" s="70" t="s">
         <v>310</v>
@@ -13642,7 +14413,7 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="2">
@@ -13669,7 +14440,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
     </row>
   </sheetData>
@@ -13695,21 +14466,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="B2" s="71">
         <v>5.0</v>
@@ -13723,7 +14494,7 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="B3" s="71">
         <v>4.0</v>
@@ -13737,7 +14508,7 @@
     </row>
     <row r="4">
       <c r="A4" s="37" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="B4" s="71">
         <v>2.0</v>
@@ -13751,7 +14522,7 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="B5" s="71">
         <v>5.0</v>
@@ -13765,7 +14536,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="B6" s="71">
         <v>4.0</v>
@@ -13779,7 +14550,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="B7" s="71">
         <v>4.0</v>
@@ -13793,7 +14564,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="B8" s="71">
         <v>2.0</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -39,7 +39,7 @@
     <definedName name="Interval_Dialog_Options">DIALOGS!$A$25:$H$61</definedName>
     <definedName name="Interval_Memento">EVENTS!$A$43:$F$51</definedName>
     <definedName name="Interval_autoInsertDialog">FN!$A$7:$I$8</definedName>
-    <definedName name="Interval_Sounds">SOUNDS!$A$1:$D$22</definedName>
+    <definedName name="Interval_Sounds">SOUNDS!$A$1:$D$26</definedName>
     <definedName name="Interval_Action_Conditions">ACTION_CONDS!$A$1:$H$61</definedName>
   </definedNames>
   <calcPr/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5549" uniqueCount="1641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5561" uniqueCount="1649">
   <si>
     <t>NewItem</t>
   </si>
@@ -2987,22 +2987,46 @@
     <t>SOUND_FIK_INTRO_2_SPANISH</t>
   </si>
   <si>
+    <t>SOUND_FIK_1_OP_0_0</t>
+  </si>
+  <si>
+    <t>SOUND_FIK_1_OP_0_0_SPANISH</t>
+  </si>
+  <si>
     <t>SOUND_FIK_1_OP_0_1</t>
   </si>
   <si>
     <t>SOUND_FIK_1_OP_0_1_SPANISH</t>
   </si>
   <si>
+    <t>SOUND_FIK_1_OP_1_0</t>
+  </si>
+  <si>
+    <t>SOUND_FIK_1_OP_1_0_SPANISH</t>
+  </si>
+  <si>
     <t>SOUND_FIK_1_OP_1_1</t>
   </si>
   <si>
     <t>SOUND_FIK_1_OP_1_1_SPANISH</t>
   </si>
   <si>
+    <t>SOUND_FIK_1_OP_2_0</t>
+  </si>
+  <si>
+    <t>SOUND_FIK_1_OP_2_0_SPANISH</t>
+  </si>
+  <si>
     <t>SOUND_FIK_1_OP_2_1</t>
   </si>
   <si>
     <t>SOUND_FIK_1_OP_2_1_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_FIK_1_OP_3_0</t>
+  </si>
+  <si>
+    <t>SOUND_FIK_1_OP_3_0_SPANISH</t>
   </si>
   <si>
     <t>SOUND_LAST</t>
@@ -6296,7 +6320,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D22" displayName="Table_sounds" name="Table_sounds" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D26" displayName="Table_sounds" name="Table_sounds" id="12">
   <tableColumns count="4">
     <tableColumn name="N" id="1"/>
     <tableColumn name="SOUND_ID" id="2"/>
@@ -7142,13 +7166,13 @@
         <v>49</v>
       </c>
       <c r="B1" s="59" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="2">
@@ -7171,10 +7195,10 @@
         <v>327</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="4">
@@ -7183,13 +7207,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="5">
@@ -7198,13 +7222,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="6">
@@ -7213,13 +7237,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="7">
@@ -7231,10 +7255,10 @@
         <v>330</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="8">
@@ -7246,10 +7270,10 @@
         <v>351</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="9">
@@ -7261,10 +7285,10 @@
         <v>358</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="10">
@@ -7276,10 +7300,10 @@
         <v>336</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="11">
@@ -7288,13 +7312,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="12">
@@ -7303,13 +7327,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="13">
@@ -7321,10 +7345,10 @@
         <v>341</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="14">
@@ -7336,10 +7360,10 @@
         <v>348</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="15">
@@ -7348,13 +7372,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="16">
@@ -7366,10 +7390,10 @@
         <v>361</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="17">
@@ -7381,10 +7405,10 @@
         <v>366</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="18">
@@ -7396,10 +7420,10 @@
         <v>369</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="19">
@@ -7411,10 +7435,10 @@
         <v>373</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="20">
@@ -7426,10 +7450,10 @@
         <v>376</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="21">
@@ -7441,10 +7465,10 @@
         <v>379</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="22">
@@ -7456,10 +7480,10 @@
         <v>381</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="23">
@@ -7471,10 +7495,10 @@
         <v>383</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="24">
@@ -7486,10 +7510,10 @@
         <v>385</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="25">
@@ -7501,10 +7525,10 @@
         <v>388</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="26">
@@ -7516,10 +7540,10 @@
         <v>392</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="27">
@@ -7531,10 +7555,10 @@
         <v>397</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="28">
@@ -7546,10 +7570,10 @@
         <v>399</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="29">
@@ -7561,10 +7585,10 @@
         <v>403</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="30">
@@ -7573,13 +7597,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="31">
@@ -7591,10 +7615,10 @@
         <v>407</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="32">
@@ -7606,10 +7630,10 @@
         <v>409</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="33">
@@ -7618,13 +7642,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="34">
@@ -7636,10 +7660,10 @@
         <v>413</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="35">
@@ -7651,10 +7675,10 @@
         <v>417</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="36">
@@ -7666,10 +7690,10 @@
         <v>420</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="37">
@@ -7681,10 +7705,10 @@
         <v>425</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="38">
@@ -7696,10 +7720,10 @@
         <v>430</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="39">
@@ -7711,10 +7735,10 @@
         <v>434</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="40">
@@ -7726,10 +7750,10 @@
         <v>438</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="41">
@@ -7741,10 +7765,10 @@
         <v>442</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="42">
@@ -7756,10 +7780,10 @@
         <v>445</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="43">
@@ -7771,10 +7795,10 @@
         <v>11</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="44">
@@ -7786,10 +7810,10 @@
         <v>450</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="45">
@@ -7801,10 +7825,10 @@
         <v>454</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
     </row>
   </sheetData>
@@ -7839,28 +7863,28 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="I1" s="61" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="2">
@@ -7878,13 +7902,13 @@
         <v>939</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="F2" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H2" s="62"/>
       <c r="I2" s="37"/>
@@ -7904,19 +7928,19 @@
         <v>939</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F3" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="I3" s="37" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="4">
@@ -7934,19 +7958,19 @@
         <v>939</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G4" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="5">
@@ -7964,19 +7988,19 @@
         <v>939</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="I5" s="37" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="6">
@@ -7985,7 +8009,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="C6" s="36">
         <v>0.0</v>
@@ -7994,19 +8018,19 @@
         <v>939</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="I6" s="37" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="7">
@@ -8015,7 +8039,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="C7" s="36">
         <v>0.0</v>
@@ -8024,19 +8048,19 @@
         <v>939</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="8">
@@ -8054,19 +8078,19 @@
         <v>939</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="I8" s="37" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="9">
@@ -8075,7 +8099,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="C9" s="36">
         <v>0.0</v>
@@ -8084,19 +8108,19 @@
         <v>939</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
       <c r="I9" s="37" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="10">
@@ -8105,7 +8129,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="C10" s="36">
         <v>0.0</v>
@@ -8114,19 +8138,19 @@
         <v>939</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="11">
@@ -8135,7 +8159,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="C11" s="36">
         <v>1.0</v>
@@ -8144,19 +8168,19 @@
         <v>939</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="I11" s="37" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="12">
@@ -8165,7 +8189,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="C12" s="36">
         <v>0.0</v>
@@ -8174,19 +8198,19 @@
         <v>939</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="13">
@@ -8195,7 +8219,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="C13" s="36">
         <v>0.0</v>
@@ -8204,19 +8228,19 @@
         <v>939</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H13" s="37" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="I13" s="37" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="14">
@@ -8225,7 +8249,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="C14" s="36">
         <v>1.0</v>
@@ -8234,19 +8258,19 @@
         <v>939</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="15">
@@ -8255,7 +8279,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="C15" s="36">
         <v>1.0</v>
@@ -8264,19 +8288,19 @@
         <v>939</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="16">
@@ -8285,7 +8309,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="C16" s="36">
         <v>0.0</v>
@@ -8294,19 +8318,19 @@
         <v>939</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="17">
@@ -8315,7 +8339,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="C17" s="36">
         <v>0.0</v>
@@ -8324,19 +8348,19 @@
         <v>939</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="I17" s="37" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="18">
@@ -8345,7 +8369,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="C18" s="36">
         <v>0.0</v>
@@ -8354,19 +8378,19 @@
         <v>939</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="19">
@@ -8384,19 +8408,19 @@
         <v>939</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="20">
@@ -8414,19 +8438,19 @@
         <v>939</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="21">
@@ -8444,19 +8468,19 @@
         <v>939</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="22">
@@ -8474,19 +8498,19 @@
         <v>939</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="23">
@@ -8504,19 +8528,19 @@
         <v>939</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="24">
@@ -8534,19 +8558,19 @@
         <v>939</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G24" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="25">
@@ -8564,19 +8588,19 @@
         <v>939</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="26">
@@ -8594,19 +8618,19 @@
         <v>939</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G26" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="27">
@@ -8615,7 +8639,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="C27" s="36">
         <v>0.0</v>
@@ -8624,19 +8648,19 @@
         <v>939</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="I27" s="37" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="28">
@@ -8645,7 +8669,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="C28" s="36">
         <v>1.0</v>
@@ -8654,19 +8678,19 @@
         <v>939</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="29">
@@ -8675,7 +8699,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="C29" s="36">
         <v>0.0</v>
@@ -8684,19 +8708,19 @@
         <v>939</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="30">
@@ -8705,7 +8729,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="C30" s="36">
         <v>0.0</v>
@@ -8714,19 +8738,19 @@
         <v>939</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="31">
@@ -8735,7 +8759,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="C31" s="36">
         <v>0.0</v>
@@ -8744,19 +8768,19 @@
         <v>939</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="32">
@@ -8774,19 +8798,19 @@
         <v>939</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G32" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="33">
@@ -8795,7 +8819,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="C33" s="36">
         <v>0.0</v>
@@ -8804,19 +8828,19 @@
         <v>939</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="34">
@@ -8825,7 +8849,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="C34" s="36">
         <v>1.0</v>
@@ -8834,19 +8858,19 @@
         <v>939</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G34" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="35">
@@ -8855,7 +8879,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="C35" s="36">
         <v>1.0</v>
@@ -8864,19 +8888,19 @@
         <v>939</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G35" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="36">
@@ -8894,19 +8918,19 @@
         <v>939</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G36" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="37">
@@ -8915,7 +8939,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="C37" s="36">
         <v>0.0</v>
@@ -8924,19 +8948,19 @@
         <v>939</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G37" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="38">
@@ -8945,7 +8969,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
       <c r="C38" s="36">
         <v>1.0</v>
@@ -8954,19 +8978,19 @@
         <v>939</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G38" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="39">
@@ -8975,7 +8999,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="C39" s="36">
         <v>0.0</v>
@@ -8984,19 +9008,19 @@
         <v>939</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G39" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="I39" s="37" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="40">
@@ -9005,7 +9029,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="C40" s="36">
         <v>1.0</v>
@@ -9014,19 +9038,19 @@
         <v>939</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G40" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="41">
@@ -9035,7 +9059,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="C41" s="36">
         <v>0.0</v>
@@ -9044,19 +9068,19 @@
         <v>939</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G41" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="42">
@@ -9065,7 +9089,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="C42" s="36">
         <v>1.0</v>
@@ -9074,19 +9098,19 @@
         <v>939</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G42" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="43">
@@ -9095,7 +9119,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="C43" s="36">
         <v>0.0</v>
@@ -9104,19 +9128,19 @@
         <v>939</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G43" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="44">
@@ -9125,7 +9149,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="C44" s="36">
         <v>1.0</v>
@@ -9134,19 +9158,19 @@
         <v>939</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G44" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="45">
@@ -9155,7 +9179,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="C45" s="36">
         <v>0.0</v>
@@ -9164,19 +9188,19 @@
         <v>939</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G45" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="46">
@@ -9185,7 +9209,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="C46" s="36">
         <v>1.0</v>
@@ -9194,19 +9218,19 @@
         <v>939</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G46" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="47">
@@ -9215,7 +9239,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="C47" s="36">
         <v>1.0</v>
@@ -9224,19 +9248,19 @@
         <v>939</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G47" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H47" s="37" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
       <c r="I47" s="37" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="48">
@@ -9245,7 +9269,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="C48" s="36">
         <v>0.0</v>
@@ -9254,19 +9278,19 @@
         <v>939</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G48" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="49">
@@ -9275,7 +9299,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="C49" s="36">
         <v>1.0</v>
@@ -9284,19 +9308,19 @@
         <v>939</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G49" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
       <c r="I49" s="37" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="50">
@@ -9305,7 +9329,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="C50" s="36">
         <v>0.0</v>
@@ -9314,19 +9338,19 @@
         <v>939</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G50" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="I50" s="37" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="51">
@@ -9335,7 +9359,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
       <c r="C51" s="36">
         <v>0.0</v>
@@ -9344,19 +9368,19 @@
         <v>939</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G51" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H51" s="37" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="I51" s="37" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="52">
@@ -9365,7 +9389,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="C52" s="36">
         <v>1.0</v>
@@ -9374,19 +9398,19 @@
         <v>939</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G52" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H52" s="37" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="I52" s="37" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="53">
@@ -9395,7 +9419,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="C53" s="36">
         <v>1.0</v>
@@ -9404,19 +9428,19 @@
         <v>939</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G53" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="54">
@@ -9425,7 +9449,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="C54" s="36">
         <v>1.0</v>
@@ -9434,19 +9458,19 @@
         <v>939</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G54" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="I54" s="37" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="55">
@@ -9455,7 +9479,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
       <c r="C55" s="36">
         <v>0.0</v>
@@ -9464,19 +9488,19 @@
         <v>939</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F55" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G55" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="56">
@@ -9485,7 +9509,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="C56" s="36">
         <v>0.0</v>
@@ -9494,19 +9518,19 @@
         <v>939</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F56" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G56" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H56" s="37" t="s">
-        <v>1321</v>
+        <v>1329</v>
       </c>
       <c r="I56" s="37" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="57">
@@ -9515,7 +9539,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="C57" s="36">
         <v>0.0</v>
@@ -9524,19 +9548,19 @@
         <v>939</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F57" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G57" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>1324</v>
+        <v>1332</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="58">
@@ -9545,7 +9569,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="C58" s="36">
         <v>1.0</v>
@@ -9554,19 +9578,19 @@
         <v>939</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G58" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>1327</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="59">
@@ -9584,19 +9608,19 @@
         <v>939</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G59" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
       <c r="I59" s="37" t="s">
-        <v>1329</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="60">
@@ -9605,7 +9629,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="C60" s="36">
         <v>0.0</v>
@@ -9614,19 +9638,19 @@
         <v>939</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="F60" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G60" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>1331</v>
+        <v>1339</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>1332</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="61">
@@ -9635,7 +9659,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1333</v>
+        <v>1341</v>
       </c>
       <c r="C61" s="36">
         <v>0.0</v>
@@ -9644,19 +9668,19 @@
         <v>939</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="F61" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G61" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>1334</v>
+        <v>1342</v>
       </c>
       <c r="I61" s="37" t="s">
-        <v>1335</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="62">
@@ -9665,7 +9689,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
       <c r="C62" s="36">
         <v>0.0</v>
@@ -9674,19 +9698,19 @@
         <v>939</v>
       </c>
       <c r="E62" s="44" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="F62" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G62" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="63">
@@ -9704,19 +9728,19 @@
         <v>939</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F63" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G63" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
       <c r="I63" s="37" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="64">
@@ -9725,7 +9749,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
       <c r="C64" s="36">
         <v>0.0</v>
@@ -9734,19 +9758,19 @@
         <v>946</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F64" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G64" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
       <c r="I64" s="37" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="65">
@@ -9755,7 +9779,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1343</v>
+        <v>1351</v>
       </c>
       <c r="C65" s="36">
         <v>0.0</v>
@@ -9764,19 +9788,19 @@
         <v>947</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F65" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G65" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
       <c r="I65" s="37" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="66">
@@ -9785,7 +9809,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="C66" s="36">
         <v>0.0</v>
@@ -9794,19 +9818,19 @@
         <v>948</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F66" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G66" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>1347</v>
+        <v>1355</v>
       </c>
       <c r="I66" s="37" t="s">
-        <v>1348</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="67">
@@ -9815,7 +9839,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1349</v>
+        <v>1357</v>
       </c>
       <c r="C67" s="36">
         <v>0.0</v>
@@ -9824,19 +9848,19 @@
         <v>949</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F67" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G67" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H67" s="37" t="s">
-        <v>1350</v>
+        <v>1358</v>
       </c>
       <c r="I67" s="37" t="s">
-        <v>1351</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="68">
@@ -9845,7 +9869,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1352</v>
+        <v>1360</v>
       </c>
       <c r="C68" s="36">
         <v>0.0</v>
@@ -9854,19 +9878,19 @@
         <v>939</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F68" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G68" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>1353</v>
+        <v>1361</v>
       </c>
       <c r="I68" s="37" t="s">
-        <v>1354</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="69">
@@ -9875,7 +9899,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1355</v>
+        <v>1363</v>
       </c>
       <c r="C69" s="36">
         <v>1.0</v>
@@ -9884,19 +9908,19 @@
         <v>939</v>
       </c>
       <c r="E69" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F69" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G69" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H69" s="37" t="s">
-        <v>1356</v>
+        <v>1364</v>
       </c>
       <c r="I69" s="37" t="s">
-        <v>1357</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="70">
@@ -9905,7 +9929,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1358</v>
+        <v>1366</v>
       </c>
       <c r="C70" s="36">
         <v>0.0</v>
@@ -9914,19 +9938,19 @@
         <v>939</v>
       </c>
       <c r="E70" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F70" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>1359</v>
+        <v>1367</v>
       </c>
       <c r="I70" s="37" t="s">
-        <v>1360</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="71">
@@ -9935,7 +9959,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1361</v>
+        <v>1369</v>
       </c>
       <c r="C71" s="36">
         <v>1.0</v>
@@ -9944,19 +9968,19 @@
         <v>939</v>
       </c>
       <c r="E71" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G71" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H71" s="37" t="s">
-        <v>1362</v>
+        <v>1370</v>
       </c>
       <c r="I71" s="37" t="s">
-        <v>1363</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="72">
@@ -9965,7 +9989,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1364</v>
+        <v>1372</v>
       </c>
       <c r="C72" s="36">
         <v>0.0</v>
@@ -9974,19 +9998,19 @@
         <v>939</v>
       </c>
       <c r="E72" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F72" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G72" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H72" s="37" t="s">
-        <v>1365</v>
+        <v>1373</v>
       </c>
       <c r="I72" s="37" t="s">
-        <v>1366</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="73">
@@ -9995,7 +10019,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>1367</v>
+        <v>1375</v>
       </c>
       <c r="C73" s="36">
         <v>1.0</v>
@@ -10004,19 +10028,19 @@
         <v>939</v>
       </c>
       <c r="E73" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F73" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G73" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H73" s="37" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="I73" s="37" t="s">
-        <v>1369</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="74">
@@ -10025,7 +10049,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>1370</v>
+        <v>1378</v>
       </c>
       <c r="C74" s="36">
         <v>0.0</v>
@@ -10034,19 +10058,19 @@
         <v>939</v>
       </c>
       <c r="E74" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F74" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G74" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H74" s="37" t="s">
-        <v>1371</v>
+        <v>1379</v>
       </c>
       <c r="I74" s="37" t="s">
-        <v>1372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="75">
@@ -10055,7 +10079,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>1373</v>
+        <v>1381</v>
       </c>
       <c r="C75" s="36">
         <v>1.0</v>
@@ -10064,19 +10088,19 @@
         <v>939</v>
       </c>
       <c r="E75" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F75" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G75" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H75" s="37" t="s">
-        <v>1374</v>
+        <v>1382</v>
       </c>
       <c r="I75" s="37" t="s">
-        <v>1375</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="76">
@@ -10085,7 +10109,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1376</v>
+        <v>1384</v>
       </c>
       <c r="C76" s="36">
         <v>0.0</v>
@@ -10094,19 +10118,19 @@
         <v>939</v>
       </c>
       <c r="E76" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F76" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G76" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H76" s="37" t="s">
-        <v>1377</v>
+        <v>1385</v>
       </c>
       <c r="I76" s="37" t="s">
-        <v>1378</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="77">
@@ -10115,7 +10139,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1379</v>
+        <v>1387</v>
       </c>
       <c r="C77" s="36">
         <v>1.0</v>
@@ -10124,19 +10148,19 @@
         <v>939</v>
       </c>
       <c r="E77" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F77" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G77" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H77" s="37" t="s">
-        <v>1380</v>
+        <v>1388</v>
       </c>
       <c r="I77" s="37" t="s">
-        <v>1381</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="78">
@@ -10145,7 +10169,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>1382</v>
+        <v>1390</v>
       </c>
       <c r="C78" s="36">
         <v>0.0</v>
@@ -10154,19 +10178,19 @@
         <v>939</v>
       </c>
       <c r="E78" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F78" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G78" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H78" s="37" t="s">
-        <v>1383</v>
+        <v>1391</v>
       </c>
       <c r="I78" s="37" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="79">
@@ -10175,7 +10199,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="C79" s="36">
         <v>0.0</v>
@@ -10184,19 +10208,19 @@
         <v>939</v>
       </c>
       <c r="E79" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F79" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G79" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H79" s="37" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="I79" s="37" t="s">
-        <v>1386</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="80">
@@ -10205,7 +10229,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>1387</v>
+        <v>1395</v>
       </c>
       <c r="C80" s="36">
         <v>1.0</v>
@@ -10214,19 +10238,19 @@
         <v>939</v>
       </c>
       <c r="E80" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F80" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G80" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H80" s="37" t="s">
-        <v>1388</v>
+        <v>1396</v>
       </c>
       <c r="I80" s="37" t="s">
-        <v>1389</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="81">
@@ -10235,7 +10259,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1390</v>
+        <v>1398</v>
       </c>
       <c r="C81" s="36">
         <v>1.0</v>
@@ -10244,19 +10268,19 @@
         <v>939</v>
       </c>
       <c r="E81" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F81" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G81" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H81" s="37" t="s">
-        <v>1391</v>
+        <v>1399</v>
       </c>
       <c r="I81" s="37" t="s">
-        <v>1392</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="82">
@@ -10265,7 +10289,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>1393</v>
+        <v>1401</v>
       </c>
       <c r="C82" s="36">
         <v>1.0</v>
@@ -10274,19 +10298,19 @@
         <v>939</v>
       </c>
       <c r="E82" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F82" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G82" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H82" s="37" t="s">
-        <v>1394</v>
+        <v>1402</v>
       </c>
       <c r="I82" s="37" t="s">
-        <v>1395</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="83">
@@ -10295,7 +10319,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>1396</v>
+        <v>1404</v>
       </c>
       <c r="C83" s="36">
         <v>0.0</v>
@@ -10304,19 +10328,19 @@
         <v>939</v>
       </c>
       <c r="E83" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F83" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G83" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H83" s="37" t="s">
-        <v>1397</v>
+        <v>1405</v>
       </c>
       <c r="I83" s="37" t="s">
-        <v>1398</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="84">
@@ -10325,7 +10349,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>1399</v>
+        <v>1407</v>
       </c>
       <c r="C84" s="36">
         <v>0.0</v>
@@ -10334,19 +10358,19 @@
         <v>939</v>
       </c>
       <c r="E84" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F84" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G84" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H84" s="37" t="s">
-        <v>1400</v>
+        <v>1408</v>
       </c>
       <c r="I84" s="37" t="s">
-        <v>1401</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="85">
@@ -10355,7 +10379,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="36" t="s">
-        <v>1402</v>
+        <v>1410</v>
       </c>
       <c r="C85" s="36">
         <v>0.0</v>
@@ -10364,19 +10388,19 @@
         <v>939</v>
       </c>
       <c r="E85" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F85" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G85" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H85" s="37" t="s">
-        <v>1403</v>
+        <v>1411</v>
       </c>
       <c r="I85" s="37" t="s">
-        <v>1404</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="86">
@@ -10394,19 +10418,19 @@
         <v>939</v>
       </c>
       <c r="E86" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F86" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G86" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H86" s="37" t="s">
-        <v>1405</v>
+        <v>1413</v>
       </c>
       <c r="I86" s="37" t="s">
-        <v>1406</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="87">
@@ -10424,19 +10448,19 @@
         <v>939</v>
       </c>
       <c r="E87" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F87" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G87" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H87" s="37" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="I87" s="37" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="88">
@@ -10454,19 +10478,19 @@
         <v>939</v>
       </c>
       <c r="E88" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F88" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G88" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H88" s="37" t="s">
-        <v>1408</v>
+        <v>1416</v>
       </c>
       <c r="I88" s="37" t="s">
-        <v>1409</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="89">
@@ -10484,19 +10508,19 @@
         <v>939</v>
       </c>
       <c r="E89" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F89" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G89" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H89" s="37" t="s">
-        <v>1410</v>
+        <v>1418</v>
       </c>
       <c r="I89" s="37" t="s">
-        <v>1411</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="90">
@@ -10514,19 +10538,19 @@
         <v>939</v>
       </c>
       <c r="E90" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F90" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G90" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H90" s="37" t="s">
-        <v>1412</v>
+        <v>1420</v>
       </c>
       <c r="I90" s="37" t="s">
-        <v>1413</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="91">
@@ -10544,19 +10568,19 @@
         <v>939</v>
       </c>
       <c r="E91" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F91" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G91" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H91" s="37" t="s">
-        <v>1414</v>
+        <v>1422</v>
       </c>
       <c r="I91" s="37" t="s">
-        <v>1415</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="92">
@@ -10574,19 +10598,19 @@
         <v>939</v>
       </c>
       <c r="E92" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F92" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G92" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H92" s="37" t="s">
-        <v>1416</v>
+        <v>1424</v>
       </c>
       <c r="I92" s="37" t="s">
-        <v>1417</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="93">
@@ -10604,19 +10628,19 @@
         <v>939</v>
       </c>
       <c r="E93" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F93" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G93" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H93" s="37" t="s">
-        <v>1418</v>
+        <v>1426</v>
       </c>
       <c r="I93" s="37" t="s">
-        <v>1419</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="94">
@@ -10634,19 +10658,19 @@
         <v>939</v>
       </c>
       <c r="E94" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F94" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G94" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H94" s="37" t="s">
-        <v>1420</v>
+        <v>1428</v>
       </c>
       <c r="I94" s="37" t="s">
-        <v>1421</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="95">
@@ -10664,19 +10688,19 @@
         <v>944</v>
       </c>
       <c r="E95" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F95" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G95" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H95" s="37" t="s">
-        <v>1422</v>
+        <v>1430</v>
       </c>
       <c r="I95" s="37" t="s">
-        <v>1423</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="96">
@@ -10694,19 +10718,19 @@
         <v>939</v>
       </c>
       <c r="E96" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F96" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G96" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H96" s="37" t="s">
-        <v>1424</v>
+        <v>1432</v>
       </c>
       <c r="I96" s="37" t="s">
-        <v>1425</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="97">
@@ -10724,19 +10748,19 @@
         <v>939</v>
       </c>
       <c r="E97" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F97" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G97" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H97" s="37" t="s">
-        <v>1426</v>
+        <v>1434</v>
       </c>
       <c r="I97" s="37" t="s">
-        <v>1427</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="98">
@@ -10754,19 +10778,19 @@
         <v>939</v>
       </c>
       <c r="E98" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F98" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G98" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H98" s="37" t="s">
-        <v>1428</v>
+        <v>1436</v>
       </c>
       <c r="I98" s="37" t="s">
-        <v>1429</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="99">
@@ -10784,19 +10808,19 @@
         <v>939</v>
       </c>
       <c r="E99" s="44" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="F99" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G99" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H99" s="37" t="s">
-        <v>1430</v>
+        <v>1438</v>
       </c>
       <c r="I99" s="37" t="s">
-        <v>1431</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="100">
@@ -10814,19 +10838,19 @@
         <v>939</v>
       </c>
       <c r="E100" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F100" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G100" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H100" s="37" t="s">
-        <v>1432</v>
+        <v>1440</v>
       </c>
       <c r="I100" s="37" t="s">
-        <v>1433</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="101">
@@ -10844,19 +10868,19 @@
         <v>939</v>
       </c>
       <c r="E101" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F101" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G101" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H101" s="37" t="s">
-        <v>1434</v>
+        <v>1442</v>
       </c>
       <c r="I101" s="37" t="s">
-        <v>1435</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="102">
@@ -10874,19 +10898,19 @@
         <v>939</v>
       </c>
       <c r="E102" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F102" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G102" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H102" s="37" t="s">
-        <v>1436</v>
+        <v>1444</v>
       </c>
       <c r="I102" s="37" t="s">
-        <v>1437</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="103">
@@ -10895,7 +10919,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="36" t="s">
-        <v>1438</v>
+        <v>1446</v>
       </c>
       <c r="C103" s="36">
         <v>0.0</v>
@@ -10904,19 +10928,19 @@
         <v>939</v>
       </c>
       <c r="E103" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F103" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G103" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H103" s="37" t="s">
-        <v>1439</v>
+        <v>1447</v>
       </c>
       <c r="I103" s="37" t="s">
-        <v>1440</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="104">
@@ -10925,7 +10949,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>1441</v>
+        <v>1449</v>
       </c>
       <c r="C104" s="36">
         <v>1.0</v>
@@ -10934,19 +10958,19 @@
         <v>939</v>
       </c>
       <c r="E104" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F104" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G104" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H104" s="37" t="s">
-        <v>1442</v>
+        <v>1450</v>
       </c>
       <c r="I104" s="37" t="s">
-        <v>1443</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="105">
@@ -10955,7 +10979,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>1444</v>
+        <v>1452</v>
       </c>
       <c r="C105" s="36">
         <v>0.0</v>
@@ -10964,19 +10988,19 @@
         <v>939</v>
       </c>
       <c r="E105" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F105" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G105" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H105" s="37" t="s">
-        <v>1445</v>
+        <v>1453</v>
       </c>
       <c r="I105" s="37" t="s">
-        <v>1446</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="106">
@@ -10985,7 +11009,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>1447</v>
+        <v>1455</v>
       </c>
       <c r="C106" s="36">
         <v>1.0</v>
@@ -10994,19 +11018,19 @@
         <v>939</v>
       </c>
       <c r="E106" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F106" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G106" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H106" s="37" t="s">
-        <v>1448</v>
+        <v>1456</v>
       </c>
       <c r="I106" s="37" t="s">
-        <v>1449</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="107">
@@ -11015,7 +11039,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="C107" s="36">
         <v>0.0</v>
@@ -11024,19 +11048,19 @@
         <v>939</v>
       </c>
       <c r="E107" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F107" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G107" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H107" s="37" t="s">
-        <v>1451</v>
+        <v>1459</v>
       </c>
       <c r="I107" s="37" t="s">
-        <v>1452</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="108">
@@ -11045,7 +11069,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>1453</v>
+        <v>1461</v>
       </c>
       <c r="C108" s="36">
         <v>1.0</v>
@@ -11054,19 +11078,19 @@
         <v>939</v>
       </c>
       <c r="E108" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F108" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G108" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H108" s="37" t="s">
-        <v>1454</v>
+        <v>1462</v>
       </c>
       <c r="I108" s="37" t="s">
-        <v>1454</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="109">
@@ -11075,7 +11099,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>1455</v>
+        <v>1463</v>
       </c>
       <c r="C109" s="36">
         <v>0.0</v>
@@ -11084,19 +11108,19 @@
         <v>939</v>
       </c>
       <c r="E109" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F109" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G109" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H109" s="37" t="s">
-        <v>1456</v>
+        <v>1464</v>
       </c>
       <c r="I109" s="37" t="s">
-        <v>1457</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="110">
@@ -11105,7 +11129,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="C110" s="36">
         <v>1.0</v>
@@ -11114,19 +11138,19 @@
         <v>939</v>
       </c>
       <c r="E110" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F110" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G110" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H110" s="37" t="s">
-        <v>1459</v>
+        <v>1467</v>
       </c>
       <c r="I110" s="37" t="s">
-        <v>1460</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="111">
@@ -11135,7 +11159,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>1461</v>
+        <v>1469</v>
       </c>
       <c r="C111" s="36">
         <v>0.0</v>
@@ -11144,19 +11168,19 @@
         <v>939</v>
       </c>
       <c r="E111" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F111" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G111" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H111" s="37" t="s">
-        <v>1462</v>
+        <v>1470</v>
       </c>
       <c r="I111" s="37" t="s">
-        <v>1463</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="112">
@@ -11165,7 +11189,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="36" t="s">
-        <v>1464</v>
+        <v>1472</v>
       </c>
       <c r="C112" s="36">
         <v>1.0</v>
@@ -11174,19 +11198,19 @@
         <v>939</v>
       </c>
       <c r="E112" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F112" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G112" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H112" s="37" t="s">
-        <v>1465</v>
+        <v>1473</v>
       </c>
       <c r="I112" s="37" t="s">
-        <v>1466</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="113">
@@ -11195,7 +11219,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>1467</v>
+        <v>1475</v>
       </c>
       <c r="C113" s="36">
         <v>0.0</v>
@@ -11204,19 +11228,19 @@
         <v>939</v>
       </c>
       <c r="E113" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F113" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G113" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H113" s="37" t="s">
-        <v>1468</v>
+        <v>1476</v>
       </c>
       <c r="I113" s="37" t="s">
-        <v>1469</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="114">
@@ -11225,7 +11249,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="C114" s="36">
         <v>0.0</v>
@@ -11234,19 +11258,19 @@
         <v>939</v>
       </c>
       <c r="E114" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F114" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G114" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H114" s="37" t="s">
-        <v>1470</v>
+        <v>1478</v>
       </c>
       <c r="I114" s="37" t="s">
-        <v>1471</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="115">
@@ -11255,7 +11279,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>1472</v>
+        <v>1480</v>
       </c>
       <c r="C115" s="36">
         <v>0.0</v>
@@ -11264,19 +11288,19 @@
         <v>939</v>
       </c>
       <c r="E115" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F115" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G115" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H115" s="37" t="s">
-        <v>1473</v>
+        <v>1481</v>
       </c>
       <c r="I115" s="37" t="s">
-        <v>1474</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="116">
@@ -11285,7 +11309,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="36" t="s">
-        <v>1475</v>
+        <v>1483</v>
       </c>
       <c r="C116" s="36">
         <v>1.0</v>
@@ -11294,19 +11318,19 @@
         <v>939</v>
       </c>
       <c r="E116" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F116" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G116" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H116" s="37" t="s">
-        <v>1476</v>
+        <v>1484</v>
       </c>
       <c r="I116" s="37" t="s">
-        <v>1477</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="117">
@@ -11324,19 +11348,19 @@
         <v>939</v>
       </c>
       <c r="E117" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F117" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G117" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H117" s="37" t="s">
-        <v>1478</v>
+        <v>1486</v>
       </c>
       <c r="I117" s="37" t="s">
-        <v>1479</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="118">
@@ -11354,19 +11378,19 @@
         <v>942</v>
       </c>
       <c r="E118" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F118" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G118" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H118" s="37" t="s">
-        <v>1480</v>
+        <v>1488</v>
       </c>
       <c r="I118" s="37" t="s">
-        <v>1481</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="119">
@@ -11384,19 +11408,19 @@
         <v>939</v>
       </c>
       <c r="E119" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F119" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G119" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H119" s="37" t="s">
-        <v>1482</v>
+        <v>1490</v>
       </c>
       <c r="I119" s="37" t="s">
-        <v>1483</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="120">
@@ -11414,16 +11438,16 @@
         <v>939</v>
       </c>
       <c r="E120" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F120" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G120" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H120" s="37" t="s">
-        <v>1484</v>
+        <v>1492</v>
       </c>
       <c r="I120" s="37" t="s">
         <v>14</v>
@@ -11435,7 +11459,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C121" s="36">
         <v>0.0</v>
@@ -11444,19 +11468,19 @@
         <v>939</v>
       </c>
       <c r="E121" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F121" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G121" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H121" s="37" t="s">
-        <v>1485</v>
+        <v>1493</v>
       </c>
       <c r="I121" s="37" t="s">
-        <v>1486</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="122">
@@ -11465,7 +11489,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="36" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="C122" s="36">
         <v>0.0</v>
@@ -11474,19 +11498,19 @@
         <v>939</v>
       </c>
       <c r="E122" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F122" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G122" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H122" s="37" t="s">
-        <v>1487</v>
+        <v>1495</v>
       </c>
       <c r="I122" s="37" t="s">
-        <v>1488</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="123">
@@ -11495,7 +11519,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>1489</v>
+        <v>1497</v>
       </c>
       <c r="C123" s="36">
         <v>0.0</v>
@@ -11504,19 +11528,19 @@
         <v>939</v>
       </c>
       <c r="E123" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F123" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G123" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H123" s="37" t="s">
-        <v>1490</v>
+        <v>1498</v>
       </c>
       <c r="I123" s="37" t="s">
-        <v>1491</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="124">
@@ -11525,7 +11549,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="36" t="s">
-        <v>1492</v>
+        <v>1500</v>
       </c>
       <c r="C124" s="36">
         <v>0.0</v>
@@ -11534,19 +11558,19 @@
         <v>939</v>
       </c>
       <c r="E124" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F124" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G124" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H124" s="37" t="s">
-        <v>1493</v>
+        <v>1501</v>
       </c>
       <c r="I124" s="37" t="s">
-        <v>1494</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="125">
@@ -11564,19 +11588,19 @@
         <v>939</v>
       </c>
       <c r="E125" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F125" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G125" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H125" s="37" t="s">
-        <v>1495</v>
+        <v>1503</v>
       </c>
       <c r="I125" s="37" t="s">
-        <v>1496</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="126">
@@ -11594,19 +11618,19 @@
         <v>939</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F126" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G126" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H126" s="37" t="s">
-        <v>1497</v>
+        <v>1505</v>
       </c>
       <c r="I126" s="37" t="s">
-        <v>1498</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="127">
@@ -11615,28 +11639,28 @@
         <v>125</v>
       </c>
       <c r="B127" s="36" t="s">
-        <v>1499</v>
+        <v>1507</v>
       </c>
       <c r="C127" s="36">
         <v>0.0</v>
       </c>
       <c r="D127" s="38" t="s">
-        <v>939</v>
+        <v>961</v>
       </c>
       <c r="E127" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F127" s="38" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="G127" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H127" s="37" t="s">
-        <v>1500</v>
+        <v>1508</v>
       </c>
       <c r="I127" s="37" t="s">
-        <v>1500</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="128">
@@ -11645,28 +11669,28 @@
         <v>126</v>
       </c>
       <c r="B128" s="36" t="s">
-        <v>1501</v>
+        <v>1509</v>
       </c>
       <c r="C128" s="36">
         <v>1.0</v>
       </c>
       <c r="D128" s="38" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="E128" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F128" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G128" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H128" s="37" t="s">
-        <v>1502</v>
+        <v>1510</v>
       </c>
       <c r="I128" s="37" t="s">
-        <v>1502</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="129">
@@ -11675,28 +11699,28 @@
         <v>127</v>
       </c>
       <c r="B129" s="36" t="s">
-        <v>1503</v>
+        <v>1511</v>
       </c>
       <c r="C129" s="36">
         <v>0.0</v>
       </c>
       <c r="D129" s="38" t="s">
-        <v>939</v>
+        <v>965</v>
       </c>
       <c r="E129" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F129" s="38" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="G129" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H129" s="37" t="s">
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="I129" s="37" t="s">
-        <v>1504</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="130">
@@ -11705,28 +11729,28 @@
         <v>128</v>
       </c>
       <c r="B130" s="36" t="s">
-        <v>1505</v>
+        <v>1513</v>
       </c>
       <c r="C130" s="36">
         <v>1.0</v>
       </c>
       <c r="D130" s="38" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="E130" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F130" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G130" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H130" s="37" t="s">
-        <v>1506</v>
+        <v>1514</v>
       </c>
       <c r="I130" s="37" t="s">
-        <v>1506</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="131">
@@ -11735,28 +11759,28 @@
         <v>129</v>
       </c>
       <c r="B131" s="36" t="s">
-        <v>1507</v>
+        <v>1515</v>
       </c>
       <c r="C131" s="36">
         <v>0.0</v>
       </c>
       <c r="D131" s="38" t="s">
-        <v>939</v>
+        <v>969</v>
       </c>
       <c r="E131" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F131" s="38" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="G131" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H131" s="37" t="s">
-        <v>1508</v>
+        <v>1516</v>
       </c>
       <c r="I131" s="37" t="s">
-        <v>1508</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="132">
@@ -11765,28 +11789,28 @@
         <v>130</v>
       </c>
       <c r="B132" s="36" t="s">
-        <v>1509</v>
+        <v>1517</v>
       </c>
       <c r="C132" s="36">
         <v>1.0</v>
       </c>
       <c r="D132" s="38" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="E132" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F132" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G132" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H132" s="37" t="s">
-        <v>1510</v>
+        <v>1518</v>
       </c>
       <c r="I132" s="37" t="s">
-        <v>1510</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="133">
@@ -11795,28 +11819,28 @@
         <v>131</v>
       </c>
       <c r="B133" s="36" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="C133" s="36">
         <v>0.0</v>
       </c>
       <c r="D133" s="38" t="s">
-        <v>939</v>
+        <v>973</v>
       </c>
       <c r="E133" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F133" s="38" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="G133" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H133" s="37" t="s">
-        <v>1511</v>
+        <v>1519</v>
       </c>
       <c r="I133" s="37" t="s">
-        <v>1512</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="134">
@@ -11825,7 +11849,7 @@
         <v>132</v>
       </c>
       <c r="B134" s="36" t="s">
-        <v>1513</v>
+        <v>1521</v>
       </c>
       <c r="C134" s="36">
         <v>1.0</v>
@@ -11834,19 +11858,19 @@
         <v>957</v>
       </c>
       <c r="E134" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F134" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G134" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H134" s="37" t="s">
-        <v>1514</v>
+        <v>1522</v>
       </c>
       <c r="I134" s="37" t="s">
-        <v>1514</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="135">
@@ -11855,7 +11879,7 @@
         <v>133</v>
       </c>
       <c r="B135" s="36" t="s">
-        <v>1515</v>
+        <v>1523</v>
       </c>
       <c r="C135" s="36">
         <v>1.0</v>
@@ -11864,19 +11888,19 @@
         <v>959</v>
       </c>
       <c r="E135" s="44" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F135" s="38" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G135" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H135" s="37" t="s">
-        <v>1516</v>
+        <v>1524</v>
       </c>
       <c r="I135" s="37" t="s">
-        <v>1516</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="136">
@@ -11885,7 +11909,7 @@
         <v>134</v>
       </c>
       <c r="B136" s="36" t="s">
-        <v>1517</v>
+        <v>1525</v>
       </c>
       <c r="C136" s="36">
         <v>0.0</v>
@@ -11894,19 +11918,19 @@
         <v>939</v>
       </c>
       <c r="E136" s="44" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="F136" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="G136" s="38" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="H136" s="37" t="s">
-        <v>1518</v>
+        <v>1526</v>
       </c>
       <c r="I136" s="37" t="s">
-        <v>1518</v>
+        <v>1526</v>
       </c>
     </row>
   </sheetData>
@@ -11948,34 +11972,34 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1519</v>
+        <v>1527</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>1520</v>
+        <v>1528</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1521</v>
+        <v>1529</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1522</v>
+        <v>1530</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>1523</v>
+        <v>1531</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>1524</v>
+        <v>1532</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>1525</v>
+        <v>1533</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>1526</v>
+        <v>1534</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>1527</v>
+        <v>1535</v>
       </c>
       <c r="K1" s="63" t="s">
-        <v>1528</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="2" ht="186.0" customHeight="1">
@@ -11984,7 +12008,7 @@
         <v>-1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>1529</v>
+        <v>1537</v>
       </c>
       <c r="C2" s="65" t="s">
         <v>323</v>
@@ -12020,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>1530</v>
+        <v>1538</v>
       </c>
       <c r="C3" s="65" t="s">
         <v>871</v>
@@ -12029,10 +12053,10 @@
         <v>956</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>1531</v>
+        <v>1539</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1532</v>
+        <v>1540</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>321</v>
@@ -12056,19 +12080,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1533</v>
+        <v>1541</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>1534</v>
+        <v>1542</v>
       </c>
       <c r="D4" s="66" t="s">
         <v>956</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1534</v>
+        <v>1542</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1535</v>
+        <v>1543</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>321</v>
@@ -12092,19 +12116,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1536</v>
+        <v>1544</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>1537</v>
+        <v>1545</v>
       </c>
       <c r="D5" s="66" t="s">
         <v>956</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1537</v>
+        <v>1545</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1538</v>
+        <v>1546</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>321</v>
@@ -12128,19 +12152,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1539</v>
+        <v>1547</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>1540</v>
+        <v>1548</v>
       </c>
       <c r="D6" s="66" t="s">
         <v>956</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1540</v>
+        <v>1548</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1541</v>
+        <v>1549</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>321</v>
@@ -12164,25 +12188,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1542</v>
+        <v>1550</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1543</v>
+        <v>1551</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>1544</v>
+        <v>1552</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>1543</v>
+        <v>1551</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>1545</v>
+        <v>1553</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>1544</v>
+        <v>1552</v>
       </c>
       <c r="I7" s="35" t="s">
         <v>618</v>
@@ -12200,25 +12224,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>1546</v>
+        <v>1554</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>1547</v>
+        <v>1555</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>1544</v>
+        <v>1552</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>1547</v>
+        <v>1555</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>1548</v>
+        <v>1556</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>1544</v>
+        <v>1552</v>
       </c>
       <c r="I8" s="35" t="s">
         <v>618</v>
@@ -12248,7 +12272,7 @@
         <v>908</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>1549</v>
+        <v>1557</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>321</v>
@@ -12272,25 +12296,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>1550</v>
+        <v>1558</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>1551</v>
+        <v>1559</v>
       </c>
       <c r="D10" s="66" t="s">
         <v>952</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1551</v>
+        <v>1559</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1552</v>
+        <v>1560</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>1553</v>
+        <v>1561</v>
       </c>
       <c r="I10" s="35" t="s">
         <v>681</v>
@@ -12308,25 +12332,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1555</v>
+        <v>1563</v>
       </c>
       <c r="D11" s="66" t="s">
-        <v>1544</v>
+        <v>1552</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1555</v>
+        <v>1563</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>1556</v>
+        <v>1564</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>1544</v>
+        <v>1552</v>
       </c>
       <c r="I11" s="35" t="s">
         <v>618</v>
@@ -12344,19 +12368,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1557</v>
+        <v>1565</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1558</v>
+        <v>1566</v>
       </c>
       <c r="D12" s="66" t="s">
         <v>951</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>1558</v>
+        <v>1566</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>1559</v>
+        <v>1567</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>321</v>
@@ -12380,19 +12404,19 @@
         <v>10</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>1560</v>
+        <v>1568</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1561</v>
+        <v>1569</v>
       </c>
       <c r="D13" s="66" t="s">
         <v>951</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>1561</v>
+        <v>1569</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>1562</v>
+        <v>1570</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>321</v>
@@ -12419,13 +12443,13 @@
         <v>21</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>1563</v>
+        <v>1571</v>
       </c>
       <c r="D14" s="66" t="s">
         <v>939</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>1563</v>
+        <v>1571</v>
       </c>
       <c r="F14" s="35" t="s">
         <v>347</v>
@@ -12452,7 +12476,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1564</v>
+        <v>1572</v>
       </c>
       <c r="C15" s="65" t="s">
         <v>323</v>
@@ -12515,7 +12539,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1565</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="2">
@@ -12542,7 +12566,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1566</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="5">
@@ -12551,7 +12575,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1567</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="6">
@@ -12563,7 +12587,7 @@
         <v>49</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1568</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="8">
@@ -12571,7 +12595,7 @@
         <v>0.0</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1569</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="9">
@@ -12579,7 +12603,7 @@
         <v>1.0</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1570</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="10">
@@ -12587,7 +12611,7 @@
         <v>2.0</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1571</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="11">
@@ -12595,7 +12619,7 @@
         <v>3.0</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1572</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="12">
@@ -12603,7 +12627,7 @@
         <v>4.0</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1573</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="13">
@@ -12611,7 +12635,7 @@
         <v>5.0</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1574</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="15">
@@ -12619,7 +12643,7 @@
         <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1575</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="16">
@@ -12637,7 +12661,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1576</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="18">
@@ -12682,7 +12706,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1577</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="23">
@@ -12699,7 +12723,7 @@
         <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1578</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="26">
@@ -12744,7 +12768,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1579</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="31">
@@ -12771,7 +12795,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1580</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="34">
@@ -12789,7 +12813,7 @@
         <v>9</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1581</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="36">
@@ -12851,7 +12875,7 @@
         <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1582</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="44">
@@ -12860,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="45">
@@ -12869,7 +12893,7 @@
         <v>1</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1583</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="46">
@@ -12878,7 +12902,7 @@
         <v>2</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="47">
@@ -12887,7 +12911,7 @@
         <v>3</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1585</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="48">
@@ -12896,7 +12920,7 @@
         <v>4</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1586</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="49">
@@ -12905,7 +12929,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1587</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="50">
@@ -12914,7 +12938,7 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1588</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="51">
@@ -12923,7 +12947,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1589</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="52">
@@ -12932,7 +12956,7 @@
         <v>8</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1590</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="53">
@@ -12941,7 +12965,7 @@
         <v>9</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="54">
@@ -12950,7 +12974,7 @@
         <v>10</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="55">
@@ -12959,7 +12983,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1591</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="56">
@@ -12968,7 +12992,7 @@
         <v>12</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1592</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="57">
@@ -12977,7 +13001,7 @@
         <v>13</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1593</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="58">
@@ -12986,7 +13010,7 @@
         <v>14</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1594</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="59">
@@ -12995,7 +13019,7 @@
         <v>15</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1595</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="61">
@@ -13003,7 +13027,7 @@
         <v>49</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1596</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="62">
@@ -13056,7 +13080,7 @@
         <v>49</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1597</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="69">
@@ -13121,7 +13145,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1598</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="2">
@@ -13139,7 +13163,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1599</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="4">
@@ -13148,7 +13172,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1600</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="5">
@@ -13229,7 +13253,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1601</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="14">
@@ -13274,7 +13298,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1602</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="19">
@@ -13418,7 +13442,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1603</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="36">
@@ -13426,16 +13450,16 @@
         <v>49</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1604</v>
+        <v>1612</v>
       </c>
       <c r="C36" s="68" t="s">
         <v>312</v>
       </c>
       <c r="D36" s="68" t="s">
-        <v>1605</v>
+        <v>1613</v>
       </c>
       <c r="E36" s="68" t="s">
-        <v>1606</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="37">
@@ -13444,7 +13468,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1607</v>
+        <v>1615</v>
       </c>
       <c r="C37" s="38" t="s">
         <v>321</v>
@@ -13463,10 +13487,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1608</v>
+        <v>1616</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="D38" s="38" t="s">
         <v>888</v>
@@ -13482,10 +13506,10 @@
         <v>2</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1609</v>
+        <v>1617</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="D39" s="38" t="s">
         <v>916</v>
@@ -13504,7 +13528,7 @@
         <v>44</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="D40" s="38" t="s">
         <v>45</v>
@@ -13520,7 +13544,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1610</v>
+        <v>1618</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>454</v>
@@ -13538,19 +13562,19 @@
         <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1611</v>
+        <v>1619</v>
       </c>
       <c r="C43" s="67" t="s">
-        <v>1612</v>
+        <v>1620</v>
       </c>
       <c r="D43" s="67" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="E43" s="68" t="s">
-        <v>1613</v>
+        <v>1621</v>
       </c>
       <c r="F43" s="67" t="s">
-        <v>1614</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="44">
@@ -13562,13 +13586,13 @@
         <v>700</v>
       </c>
       <c r="C44" s="44" t="s">
-        <v>1607</v>
+        <v>1615</v>
       </c>
       <c r="D44" s="44" t="s">
         <v>703</v>
       </c>
       <c r="E44" s="48" t="s">
-        <v>1615</v>
+        <v>1623</v>
       </c>
       <c r="F44" s="43" t="b">
         <v>0</v>
@@ -13583,13 +13607,13 @@
         <v>712</v>
       </c>
       <c r="C45" s="44" t="s">
-        <v>1608</v>
+        <v>1616</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>1615</v>
+        <v>1623</v>
       </c>
       <c r="F45" s="43" t="b">
         <v>0</v>
@@ -13604,13 +13628,13 @@
         <v>729</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>1608</v>
+        <v>1616</v>
       </c>
       <c r="D46" s="44" t="s">
         <v>749</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>1615</v>
+        <v>1623</v>
       </c>
       <c r="F46" s="43" t="b">
         <v>0</v>
@@ -13625,13 +13649,13 @@
         <v>734</v>
       </c>
       <c r="C47" s="44" t="s">
-        <v>1609</v>
+        <v>1617</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>1615</v>
+        <v>1623</v>
       </c>
       <c r="F47" s="43" t="b">
         <v>0</v>
@@ -13649,10 +13673,10 @@
         <v>44</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>1396</v>
+        <v>1404</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>1615</v>
+        <v>1623</v>
       </c>
       <c r="F48" s="43" t="b">
         <v>0</v>
@@ -13664,16 +13688,16 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1616</v>
+        <v>1624</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>44</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>1399</v>
+        <v>1407</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>1615</v>
+        <v>1623</v>
       </c>
       <c r="F49" s="43" t="b">
         <v>0</v>
@@ -13685,16 +13709,16 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1617</v>
+        <v>1625</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>44</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>1402</v>
+        <v>1410</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>1615</v>
+        <v>1623</v>
       </c>
       <c r="F50" s="43" t="b">
         <v>1</v>
@@ -13706,16 +13730,16 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C51" s="44" t="s">
         <v>1618</v>
-      </c>
-      <c r="C51" s="44" t="s">
-        <v>1610</v>
       </c>
       <c r="D51" s="44" t="s">
         <v>703</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>1615</v>
+        <v>1623</v>
       </c>
       <c r="F51" s="43" t="b">
         <v>0</v>
@@ -13726,10 +13750,10 @@
         <v>49</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1619</v>
+        <v>1627</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>1620</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="54">
@@ -13738,7 +13762,7 @@
         <v>0</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1615</v>
+        <v>1623</v>
       </c>
       <c r="C54" s="51" t="s">
         <v>463</v>
@@ -13749,7 +13773,7 @@
         <v>49</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1621</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="57">
@@ -14759,16 +14783,16 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1622</v>
+        <v>1630</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1623</v>
+        <v>1631</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1624</v>
+        <v>1632</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1625</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="2">
@@ -14780,7 +14804,7 @@
         <v>324</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1626</v>
+        <v>1634</v>
       </c>
       <c r="D2" s="70" t="s">
         <v>321</v>
@@ -14798,7 +14822,7 @@
         <v>440</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1627</v>
+        <v>1635</v>
       </c>
       <c r="D3" s="70" t="s">
         <v>321</v>
@@ -14813,10 +14837,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1628</v>
+        <v>1636</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1626</v>
+        <v>1634</v>
       </c>
       <c r="D4" s="70" t="s">
         <v>321</v>
@@ -14854,7 +14878,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1568</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="2">
@@ -14881,7 +14905,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1629</v>
+        <v>1637</v>
       </c>
     </row>
   </sheetData>
@@ -14907,21 +14931,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1630</v>
+        <v>1638</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1631</v>
+        <v>1639</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1632</v>
+        <v>1640</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1633</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="s">
-        <v>1634</v>
+        <v>1642</v>
       </c>
       <c r="B2" s="71">
         <v>5.0</v>
@@ -14935,7 +14959,7 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>1635</v>
+        <v>1643</v>
       </c>
       <c r="B3" s="71">
         <v>4.0</v>
@@ -14949,7 +14973,7 @@
     </row>
     <row r="4">
       <c r="A4" s="37" t="s">
-        <v>1636</v>
+        <v>1644</v>
       </c>
       <c r="B4" s="71">
         <v>2.0</v>
@@ -14963,7 +14987,7 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>1637</v>
+        <v>1645</v>
       </c>
       <c r="B5" s="71">
         <v>5.0</v>
@@ -14977,7 +15001,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>1638</v>
+        <v>1646</v>
       </c>
       <c r="B6" s="71">
         <v>4.0</v>
@@ -14991,7 +15015,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>1639</v>
+        <v>1647</v>
       </c>
       <c r="B7" s="71">
         <v>4.0</v>
@@ -15005,7 +15029,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>1640</v>
+        <v>1648</v>
       </c>
       <c r="B8" s="71">
         <v>2.0</v>
@@ -15019,7 +15043,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="B9" s="71">
         <v>5.0</v>
@@ -30977,6 +31001,66 @@
       <c r="C22" s="36" t="s">
         <v>940</v>
       </c>
+      <c r="D22" s="36" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>21</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>969</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>940</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>22</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>971</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>940</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>23</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>973</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>940</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>24</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>975</v>
+      </c>
+      <c r="C26" s="36" t="s">
+        <v>940</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -31009,13 +31093,13 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>26</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
     </row>
     <row r="2">
@@ -31030,7 +31114,7 @@
         <v>320</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
     </row>
     <row r="3">
@@ -31045,7 +31129,7 @@
         <v>320</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
     </row>
     <row r="4">
@@ -31057,10 +31141,10 @@
         <v>746</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
     </row>
     <row r="5">
@@ -31069,13 +31153,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
     </row>
     <row r="6">
@@ -31087,10 +31171,10 @@
         <v>760</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
     </row>
     <row r="7">
@@ -31102,10 +31186,10 @@
         <v>762</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
     </row>
     <row r="8">
@@ -31114,13 +31198,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
     </row>
     <row r="9">
@@ -31132,10 +31216,10 @@
         <v>764</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
     </row>
     <row r="10">
@@ -31144,13 +31228,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
     </row>
     <row r="11">
@@ -31162,10 +31246,10 @@
         <v>765</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
     </row>
     <row r="12">
@@ -31180,7 +31264,7 @@
         <v>406</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
     </row>
     <row r="13">
@@ -31195,7 +31279,7 @@
         <v>408</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
     </row>
     <row r="14">
@@ -31204,13 +31288,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
     </row>
     <row r="15">
@@ -31222,10 +31306,10 @@
         <v>772</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
     </row>
     <row r="16">
@@ -31234,13 +31318,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="17">
@@ -31252,10 +31336,10 @@
         <v>797</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="18">
@@ -31270,7 +31354,7 @@
         <v>387</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="19">
@@ -31285,7 +31369,7 @@
         <v>326</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="20">
@@ -31294,13 +31378,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="C20" s="39" t="s">
         <v>387</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="21">
@@ -31315,7 +31399,7 @@
         <v>35</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="22">
@@ -31330,7 +31414,7 @@
         <v>35</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="23">
@@ -31339,13 +31423,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="C23" s="39" t="s">
         <v>320</v>
       </c>
       <c r="D23" s="41" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
     </row>
     <row r="25">
@@ -31353,25 +31437,25 @@
         <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>457</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
       <c r="H25" s="28" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="26">
@@ -31380,7 +31464,7 @@
         <v>0</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="C26" s="37" t="s">
         <v>463</v>
@@ -31407,7 +31491,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="C27" s="37" t="s">
         <v>463</v>
@@ -31434,7 +31518,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="C28" s="40" t="s">
         <v>463</v>
@@ -31446,13 +31530,13 @@
         <v>467</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="G28" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="40" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="29">
@@ -31461,7 +31545,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>463</v>
@@ -31473,13 +31557,13 @@
         <v>467</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="G29" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H29" s="40" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="30">
@@ -31488,7 +31572,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>463</v>
@@ -31506,7 +31590,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="40" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="31">
@@ -31515,7 +31599,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>463</v>
@@ -31524,7 +31608,7 @@
         <v>464</v>
       </c>
       <c r="E31" s="40" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>702</v>
@@ -31533,7 +31617,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="40" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="32">
@@ -31542,7 +31626,7 @@
         <v>6</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="C32" s="40" t="s">
         <v>463</v>
@@ -31560,7 +31644,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="40" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="33">
@@ -31569,7 +31653,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="C33" s="40" t="s">
         <v>463</v>
@@ -31581,13 +31665,13 @@
         <v>467</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="G33" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H33" s="40" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="34">
@@ -31596,7 +31680,7 @@
         <v>8</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="C34" s="40" t="s">
         <v>463</v>
@@ -31614,7 +31698,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="40" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="35">
@@ -31623,7 +31707,7 @@
         <v>9</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="C35" s="40" t="s">
         <v>463</v>
@@ -31635,13 +31719,13 @@
         <v>467</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="G35" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H35" s="40" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="36">
@@ -31650,7 +31734,7 @@
         <v>10</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="C36" s="40" t="s">
         <v>463</v>
@@ -31662,13 +31746,13 @@
         <v>830</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="G36" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H36" s="40" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="37">
@@ -31677,7 +31761,7 @@
         <v>11</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="C37" s="40" t="s">
         <v>831</v>
@@ -31689,13 +31773,13 @@
         <v>467</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="G37" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H37" s="40" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="38">
@@ -31704,7 +31788,7 @@
         <v>12</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
       <c r="C38" s="40" t="s">
         <v>463</v>
@@ -31716,13 +31800,13 @@
         <v>467</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="G38" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H38" s="40" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="39">
@@ -31731,7 +31815,7 @@
         <v>13</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
       <c r="C39" s="40" t="s">
         <v>831</v>
@@ -31740,16 +31824,16 @@
         <v>529</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="G39" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H39" s="40" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="40">
@@ -31758,7 +31842,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="C40" s="40" t="s">
         <v>463</v>
@@ -31776,7 +31860,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="40" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="41">
@@ -31785,7 +31869,7 @@
         <v>15</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="C41" s="40" t="s">
         <v>463</v>
@@ -31803,7 +31887,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="42">
@@ -31812,7 +31896,7 @@
         <v>16</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="C42" s="40" t="s">
         <v>463</v>
@@ -31830,7 +31914,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="40" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="43">
@@ -31839,7 +31923,7 @@
         <v>17</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>463</v>
@@ -31857,7 +31941,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="40" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="44">
@@ -31866,7 +31950,7 @@
         <v>18</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>463</v>
@@ -31878,13 +31962,13 @@
         <v>467</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="G44" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H44" s="40" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="45">
@@ -31893,7 +31977,7 @@
         <v>19</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="C45" s="40" t="s">
         <v>463</v>
@@ -31905,13 +31989,13 @@
         <v>467</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="G45" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H45" s="40" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="46">
@@ -31920,7 +32004,7 @@
         <v>20</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="C46" s="40" t="s">
         <v>463</v>
@@ -31929,16 +32013,16 @@
         <v>464</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="G46" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="40" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="47">
@@ -31947,7 +32031,7 @@
         <v>21</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="C47" s="40" t="s">
         <v>463</v>
@@ -31965,7 +32049,7 @@
         <v>0</v>
       </c>
       <c r="H47" s="40" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="48">
@@ -31974,7 +32058,7 @@
         <v>22</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="C48" s="40" t="s">
         <v>463</v>
@@ -31986,13 +32070,13 @@
         <v>467</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="G48" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H48" s="40" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="49">
@@ -32001,7 +32085,7 @@
         <v>23</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="C49" s="40" t="s">
         <v>463</v>
@@ -32013,13 +32097,13 @@
         <v>835</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="G49" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H49" s="40" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="50">
@@ -32028,7 +32112,7 @@
         <v>24</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="C50" s="40" t="s">
         <v>836</v>
@@ -32037,16 +32121,16 @@
         <v>464</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="G50" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H50" s="40" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="51">
@@ -32055,7 +32139,7 @@
         <v>25</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="C51" s="40" t="s">
         <v>463</v>
@@ -32073,7 +32157,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="40" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="52">
@@ -32082,7 +32166,7 @@
         <v>26</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="C52" s="40" t="s">
         <v>463</v>
@@ -32094,13 +32178,13 @@
         <v>467</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="G52" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="40" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="53">
@@ -32109,7 +32193,7 @@
         <v>27</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="C53" s="40" t="s">
         <v>463</v>
@@ -32127,7 +32211,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="40" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="54">
@@ -32136,7 +32220,7 @@
         <v>28</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="C54" s="40" t="s">
         <v>463</v>
@@ -32148,13 +32232,13 @@
         <v>841</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="G54" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H54" s="40" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="55">
@@ -32163,7 +32247,7 @@
         <v>29</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="C55" s="40" t="s">
         <v>463</v>
@@ -32181,7 +32265,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="40" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="56">
@@ -32190,7 +32274,7 @@
         <v>30</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="C56" s="40" t="s">
         <v>463</v>
@@ -32208,7 +32292,7 @@
         <v>0</v>
       </c>
       <c r="H56" s="40" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="57">
@@ -32217,7 +32301,7 @@
         <v>31</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="C57" s="40" t="s">
         <v>463</v>
@@ -32235,7 +32319,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="40" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="58">
@@ -32244,7 +32328,7 @@
         <v>32</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="C58" s="40" t="s">
         <v>463</v>
@@ -32262,7 +32346,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="40" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="59">
@@ -32271,7 +32355,7 @@
         <v>33</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="C59" s="40" t="s">
         <v>463</v>
@@ -32289,7 +32373,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="40" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="60">
@@ -32298,7 +32382,7 @@
         <v>34</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="C60" s="40" t="s">
         <v>463</v>
@@ -32316,7 +32400,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="40" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="61">
@@ -32325,7 +32409,7 @@
         <v>35</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="C61" s="37" t="s">
         <v>463</v>
@@ -32442,10 +32526,10 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
       <c r="C1" s="56" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="2">
@@ -32457,7 +32541,7 @@
         <v>701</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="3">
@@ -32469,7 +32553,7 @@
         <v>732</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="4">
@@ -32478,10 +32562,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="6">
@@ -32489,13 +32573,13 @@
         <v>49</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="7">
@@ -32504,7 +32588,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>703</v>
@@ -32519,10 +32603,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="D8" s="57" t="s">
         <v>467</v>
@@ -32534,10 +32618,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="D9" s="57" t="s">
         <v>705</v>
@@ -32549,10 +32633,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="D10" s="57" t="s">
         <v>707</v>
@@ -32564,7 +32648,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>703</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -39,7 +39,7 @@
     <definedName name="Interval_Dialog_Options">DIALOGS!$A$25:$H$61</definedName>
     <definedName name="Interval_Memento">EVENTS!$A$43:$F$51</definedName>
     <definedName name="Interval_autoInsertDialog">FN!$A$7:$I$8</definedName>
-    <definedName name="Interval_Sounds">SOUNDS!$A$1:$D$26</definedName>
+    <definedName name="Interval_Sounds">SOUNDS!$A$1:$D$32</definedName>
     <definedName name="Interval_Action_Conditions">ACTION_CONDS!$A$1:$H$61</definedName>
   </definedNames>
   <calcPr/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5561" uniqueCount="1649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5579" uniqueCount="1661">
   <si>
     <t>NewItem</t>
   </si>
@@ -3027,6 +3027,42 @@
   </si>
   <si>
     <t>SOUND_FIK_1_OP_3_0_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_MAINCHAR_NONSENSE</t>
+  </si>
+  <si>
+    <t>SOUND_MAINCHAR_NONSENSE_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_MAINCHAR_NONSENSE_OBSERVE</t>
+  </si>
+  <si>
+    <t>SOUND_MAINCHAR_NONSENSE_OBSERVE_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_MAINCHAR_NONSENSE_TALK</t>
+  </si>
+  <si>
+    <t>SOUND_MAINCHAR_NONSENSE_TALK_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_PHRASE_DIALOG_MANYO_BCKG_CROWD_1</t>
+  </si>
+  <si>
+    <t>SOUND_PHRASE_DIALOG_MANYO_BCKG_CROWD_1_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_PHRASE_DIALOG_MANYO_BCKG_CROWD_2</t>
+  </si>
+  <si>
+    <t>SOUND_PHRASE_DIALOG_MANYO_BCKG_CROWD_2_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_PHRASE_DIALOG_MANYO_BCKG_CROWD_3</t>
+  </si>
+  <si>
+    <t>SOUND_PHRASE_DIALOG_MANYO_BCKG_CROWD_3_SPANISH</t>
   </si>
   <si>
     <t>SOUND_LAST</t>
@@ -6320,7 +6356,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D26" displayName="Table_sounds" name="Table_sounds" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D32" displayName="Table_sounds" name="Table_sounds" id="12">
   <tableColumns count="4">
     <tableColumn name="N" id="1"/>
     <tableColumn name="SOUND_ID" id="2"/>
@@ -7166,13 +7202,13 @@
         <v>49</v>
       </c>
       <c r="B1" s="59" t="s">
-        <v>1088</v>
+        <v>1100</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>1089</v>
+        <v>1101</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>1090</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="2">
@@ -7195,10 +7231,10 @@
         <v>327</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1091</v>
+        <v>1103</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>1091</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="4">
@@ -7207,13 +7243,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1092</v>
+        <v>1104</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1093</v>
+        <v>1105</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>1094</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="5">
@@ -7222,13 +7258,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1095</v>
+        <v>1107</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>1096</v>
+        <v>1108</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>1097</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="6">
@@ -7237,13 +7273,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1098</v>
+        <v>1110</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>1099</v>
+        <v>1111</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>1100</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="7">
@@ -7255,10 +7291,10 @@
         <v>330</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>1101</v>
+        <v>1113</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>1102</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="8">
@@ -7270,10 +7306,10 @@
         <v>351</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1103</v>
+        <v>1115</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>1103</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="9">
@@ -7285,10 +7321,10 @@
         <v>358</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>1104</v>
+        <v>1116</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>1105</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="10">
@@ -7300,10 +7336,10 @@
         <v>336</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>1106</v>
+        <v>1118</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>1107</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="11">
@@ -7312,13 +7348,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1108</v>
+        <v>1120</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>1110</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="12">
@@ -7327,13 +7363,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1111</v>
+        <v>1123</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>1112</v>
+        <v>1124</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>1113</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="13">
@@ -7345,10 +7381,10 @@
         <v>341</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>1114</v>
+        <v>1126</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>1115</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="14">
@@ -7360,10 +7396,10 @@
         <v>348</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>1116</v>
+        <v>1128</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>1117</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="15">
@@ -7372,13 +7408,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1118</v>
+        <v>1130</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>1119</v>
+        <v>1131</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>1120</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="16">
@@ -7390,10 +7426,10 @@
         <v>361</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>1121</v>
+        <v>1133</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>1122</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="17">
@@ -7405,10 +7441,10 @@
         <v>366</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>1123</v>
+        <v>1135</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>1124</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="18">
@@ -7420,10 +7456,10 @@
         <v>369</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>1125</v>
+        <v>1137</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>1126</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="19">
@@ -7435,10 +7471,10 @@
         <v>373</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>1127</v>
+        <v>1139</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>1128</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="20">
@@ -7450,10 +7486,10 @@
         <v>376</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>1129</v>
+        <v>1141</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="21">
@@ -7465,10 +7501,10 @@
         <v>379</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>1131</v>
+        <v>1143</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>1132</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="22">
@@ -7480,10 +7516,10 @@
         <v>381</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>1133</v>
+        <v>1145</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>1134</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="23">
@@ -7495,10 +7531,10 @@
         <v>383</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>1135</v>
+        <v>1147</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>1136</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="24">
@@ -7510,10 +7546,10 @@
         <v>385</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>1137</v>
+        <v>1149</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>1138</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="25">
@@ -7525,10 +7561,10 @@
         <v>388</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>1139</v>
+        <v>1151</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>1140</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="26">
@@ -7540,10 +7576,10 @@
         <v>392</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>1141</v>
+        <v>1153</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>1142</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="27">
@@ -7555,10 +7591,10 @@
         <v>397</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>1143</v>
+        <v>1155</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>1144</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="28">
@@ -7570,10 +7606,10 @@
         <v>399</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>1145</v>
+        <v>1157</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="29">
@@ -7585,10 +7621,10 @@
         <v>403</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>1147</v>
+        <v>1159</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>1148</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="30">
@@ -7597,13 +7633,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>1149</v>
+        <v>1161</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>1150</v>
+        <v>1162</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>1151</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="31">
@@ -7615,10 +7651,10 @@
         <v>407</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>1152</v>
+        <v>1164</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>1153</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="32">
@@ -7630,10 +7666,10 @@
         <v>409</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>1154</v>
+        <v>1166</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>1155</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="33">
@@ -7642,13 +7678,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>1156</v>
+        <v>1168</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>1157</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="34">
@@ -7660,10 +7696,10 @@
         <v>413</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>1158</v>
+        <v>1170</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>1159</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="35">
@@ -7675,10 +7711,10 @@
         <v>417</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>1160</v>
+        <v>1172</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>1161</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="36">
@@ -7690,10 +7726,10 @@
         <v>420</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>1162</v>
+        <v>1174</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>1163</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="37">
@@ -7705,10 +7741,10 @@
         <v>425</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>1164</v>
+        <v>1176</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>1165</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="38">
@@ -7720,10 +7756,10 @@
         <v>430</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>1166</v>
+        <v>1178</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>1167</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="39">
@@ -7735,10 +7771,10 @@
         <v>434</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>1168</v>
+        <v>1180</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>1168</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="40">
@@ -7750,10 +7786,10 @@
         <v>438</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>1169</v>
+        <v>1181</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>1170</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="41">
@@ -7765,10 +7801,10 @@
         <v>442</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>1171</v>
+        <v>1183</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>1172</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="42">
@@ -7780,10 +7816,10 @@
         <v>445</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>1173</v>
+        <v>1185</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>1174</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="43">
@@ -7795,10 +7831,10 @@
         <v>11</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>1173</v>
+        <v>1185</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>1175</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="44">
@@ -7810,10 +7846,10 @@
         <v>450</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>1176</v>
+        <v>1188</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>1176</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="45">
@@ -7825,10 +7861,10 @@
         <v>454</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>1177</v>
+        <v>1189</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>1178</v>
+        <v>1190</v>
       </c>
     </row>
   </sheetData>
@@ -7863,28 +7899,28 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1179</v>
+        <v>1191</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1180</v>
+        <v>1192</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1181</v>
+        <v>1193</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1182</v>
+        <v>1194</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1183</v>
+        <v>1195</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1184</v>
+        <v>1196</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1185</v>
+        <v>1197</v>
       </c>
       <c r="I1" s="61" t="s">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="2">
@@ -7902,13 +7938,13 @@
         <v>939</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="F2" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H2" s="62"/>
       <c r="I2" s="37"/>
@@ -7925,22 +7961,22 @@
         <v>0.0</v>
       </c>
       <c r="D3" s="38" t="s">
-        <v>939</v>
+        <v>975</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F3" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>1189</v>
+        <v>1201</v>
       </c>
       <c r="I3" s="37" t="s">
-        <v>1190</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="4">
@@ -7955,22 +7991,22 @@
         <v>0.0</v>
       </c>
       <c r="D4" s="38" t="s">
-        <v>939</v>
+        <v>977</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G4" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1191</v>
+        <v>1203</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1192</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="5">
@@ -7985,22 +8021,22 @@
         <v>0.0</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>939</v>
+        <v>979</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>1193</v>
+        <v>1205</v>
       </c>
       <c r="I5" s="37" t="s">
-        <v>1194</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="6">
@@ -8009,7 +8045,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1195</v>
+        <v>1207</v>
       </c>
       <c r="C6" s="36">
         <v>0.0</v>
@@ -8018,19 +8054,19 @@
         <v>939</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>1196</v>
+        <v>1208</v>
       </c>
       <c r="I6" s="37" t="s">
-        <v>1197</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="7">
@@ -8039,7 +8075,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1198</v>
+        <v>1210</v>
       </c>
       <c r="C7" s="36">
         <v>0.0</v>
@@ -8048,19 +8084,19 @@
         <v>939</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>1199</v>
+        <v>1211</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>1200</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="8">
@@ -8078,19 +8114,19 @@
         <v>939</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>1201</v>
+        <v>1213</v>
       </c>
       <c r="I8" s="37" t="s">
-        <v>1202</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="9">
@@ -8099,7 +8135,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1203</v>
+        <v>1215</v>
       </c>
       <c r="C9" s="36">
         <v>0.0</v>
@@ -8108,19 +8144,19 @@
         <v>939</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>1204</v>
+        <v>1216</v>
       </c>
       <c r="I9" s="37" t="s">
-        <v>1205</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="10">
@@ -8129,7 +8165,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1206</v>
+        <v>1218</v>
       </c>
       <c r="C10" s="36">
         <v>0.0</v>
@@ -8138,19 +8174,19 @@
         <v>939</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>1207</v>
+        <v>1219</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>1208</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="11">
@@ -8159,7 +8195,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1209</v>
+        <v>1221</v>
       </c>
       <c r="C11" s="36">
         <v>1.0</v>
@@ -8168,19 +8204,19 @@
         <v>939</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>1211</v>
+        <v>1223</v>
       </c>
       <c r="I11" s="37" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="12">
@@ -8189,7 +8225,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1213</v>
+        <v>1225</v>
       </c>
       <c r="C12" s="36">
         <v>0.0</v>
@@ -8198,19 +8234,19 @@
         <v>939</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1214</v>
+        <v>1226</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>1215</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="13">
@@ -8219,7 +8255,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1216</v>
+        <v>1228</v>
       </c>
       <c r="C13" s="36">
         <v>0.0</v>
@@ -8228,19 +8264,19 @@
         <v>939</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H13" s="37" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="I13" s="37" t="s">
-        <v>1218</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="14">
@@ -8249,7 +8285,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1219</v>
+        <v>1231</v>
       </c>
       <c r="C14" s="36">
         <v>1.0</v>
@@ -8258,19 +8294,19 @@
         <v>939</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>1221</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="15">
@@ -8279,7 +8315,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="C15" s="36">
         <v>1.0</v>
@@ -8288,19 +8324,19 @@
         <v>939</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1223</v>
+        <v>1235</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1224</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="16">
@@ -8309,7 +8345,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>1021</v>
+        <v>1033</v>
       </c>
       <c r="C16" s="36">
         <v>0.0</v>
@@ -8318,19 +8354,19 @@
         <v>939</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>1225</v>
+        <v>1237</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>1226</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="17">
@@ -8339,7 +8375,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1024</v>
+        <v>1036</v>
       </c>
       <c r="C17" s="36">
         <v>0.0</v>
@@ -8348,19 +8384,19 @@
         <v>939</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>1227</v>
+        <v>1239</v>
       </c>
       <c r="I17" s="37" t="s">
-        <v>1228</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="18">
@@ -8369,7 +8405,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1229</v>
+        <v>1241</v>
       </c>
       <c r="C18" s="36">
         <v>0.0</v>
@@ -8378,19 +8414,19 @@
         <v>939</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>1230</v>
+        <v>1242</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>1231</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="19">
@@ -8408,19 +8444,19 @@
         <v>939</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>1232</v>
+        <v>1244</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>1233</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="20">
@@ -8438,19 +8474,19 @@
         <v>939</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>1234</v>
+        <v>1246</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>1235</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="21">
@@ -8468,19 +8504,19 @@
         <v>939</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>1236</v>
+        <v>1248</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>1237</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="22">
@@ -8498,19 +8534,19 @@
         <v>939</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1238</v>
+        <v>1250</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1239</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="23">
@@ -8528,19 +8564,19 @@
         <v>939</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>1240</v>
+        <v>1252</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>1241</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="24">
@@ -8558,19 +8594,19 @@
         <v>939</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G24" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1242</v>
+        <v>1254</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1243</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="25">
@@ -8588,19 +8624,19 @@
         <v>939</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>1244</v>
+        <v>1256</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>1245</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="26">
@@ -8618,19 +8654,19 @@
         <v>939</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G26" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>1246</v>
+        <v>1258</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="27">
@@ -8639,7 +8675,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1248</v>
+        <v>1260</v>
       </c>
       <c r="C27" s="36">
         <v>0.0</v>
@@ -8648,19 +8684,19 @@
         <v>939</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>1249</v>
+        <v>1261</v>
       </c>
       <c r="I27" s="37" t="s">
-        <v>1250</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="28">
@@ -8669,7 +8705,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1251</v>
+        <v>1263</v>
       </c>
       <c r="C28" s="36">
         <v>1.0</v>
@@ -8678,19 +8714,19 @@
         <v>939</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>1252</v>
+        <v>1264</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>1253</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="29">
@@ -8699,7 +8735,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>1083</v>
+        <v>1095</v>
       </c>
       <c r="C29" s="36">
         <v>0.0</v>
@@ -8708,19 +8744,19 @@
         <v>939</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>1254</v>
+        <v>1266</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>1255</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="30">
@@ -8729,7 +8765,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1085</v>
+        <v>1097</v>
       </c>
       <c r="C30" s="36">
         <v>0.0</v>
@@ -8738,19 +8774,19 @@
         <v>939</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>1256</v>
+        <v>1268</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>1257</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="31">
@@ -8759,7 +8795,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1087</v>
+        <v>1099</v>
       </c>
       <c r="C31" s="36">
         <v>0.0</v>
@@ -8768,19 +8804,19 @@
         <v>939</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>1258</v>
+        <v>1270</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>1259</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="32">
@@ -8798,19 +8834,19 @@
         <v>939</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G32" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>1260</v>
+        <v>1272</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>1261</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="33">
@@ -8819,7 +8855,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1026</v>
+        <v>1038</v>
       </c>
       <c r="C33" s="36">
         <v>0.0</v>
@@ -8828,19 +8864,19 @@
         <v>939</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1262</v>
+        <v>1274</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1263</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="34">
@@ -8849,7 +8885,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1264</v>
+        <v>1276</v>
       </c>
       <c r="C34" s="36">
         <v>1.0</v>
@@ -8858,19 +8894,19 @@
         <v>939</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G34" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>1265</v>
+        <v>1277</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>1266</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="35">
@@ -8879,7 +8915,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
       <c r="C35" s="36">
         <v>1.0</v>
@@ -8888,19 +8924,19 @@
         <v>939</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G35" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>1268</v>
+        <v>1280</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>1269</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="36">
@@ -8918,19 +8954,19 @@
         <v>939</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G36" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>1270</v>
+        <v>1282</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>1271</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="37">
@@ -8939,7 +8975,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1272</v>
+        <v>1284</v>
       </c>
       <c r="C37" s="36">
         <v>0.0</v>
@@ -8948,19 +8984,19 @@
         <v>939</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G37" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>1273</v>
+        <v>1285</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>1274</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="38">
@@ -8969,7 +9005,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1275</v>
+        <v>1287</v>
       </c>
       <c r="C38" s="36">
         <v>1.0</v>
@@ -8978,19 +9014,19 @@
         <v>939</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G38" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>1276</v>
+        <v>1288</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>1277</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="39">
@@ -8999,7 +9035,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1278</v>
+        <v>1290</v>
       </c>
       <c r="C39" s="36">
         <v>0.0</v>
@@ -9008,19 +9044,19 @@
         <v>939</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G39" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>1279</v>
+        <v>1291</v>
       </c>
       <c r="I39" s="37" t="s">
-        <v>1280</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="40">
@@ -9029,7 +9065,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1281</v>
+        <v>1293</v>
       </c>
       <c r="C40" s="36">
         <v>1.0</v>
@@ -9038,19 +9074,19 @@
         <v>939</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G40" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>1282</v>
+        <v>1294</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>1283</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="41">
@@ -9059,7 +9095,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1284</v>
+        <v>1296</v>
       </c>
       <c r="C41" s="36">
         <v>0.0</v>
@@ -9068,19 +9104,19 @@
         <v>939</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G41" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>1285</v>
+        <v>1297</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>1286</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="42">
@@ -9089,7 +9125,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1287</v>
+        <v>1299</v>
       </c>
       <c r="C42" s="36">
         <v>1.0</v>
@@ -9098,19 +9134,19 @@
         <v>939</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G42" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>1288</v>
+        <v>1300</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>1289</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="43">
@@ -9119,7 +9155,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1290</v>
+        <v>1302</v>
       </c>
       <c r="C43" s="36">
         <v>0.0</v>
@@ -9128,19 +9164,19 @@
         <v>939</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G43" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>1291</v>
+        <v>1303</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>1292</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="44">
@@ -9149,7 +9185,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1293</v>
+        <v>1305</v>
       </c>
       <c r="C44" s="36">
         <v>1.0</v>
@@ -9158,19 +9194,19 @@
         <v>939</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G44" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>1294</v>
+        <v>1306</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>1295</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="45">
@@ -9179,7 +9215,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1296</v>
+        <v>1308</v>
       </c>
       <c r="C45" s="36">
         <v>0.0</v>
@@ -9188,19 +9224,19 @@
         <v>939</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G45" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>1297</v>
+        <v>1309</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>1298</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="46">
@@ -9209,7 +9245,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1299</v>
+        <v>1311</v>
       </c>
       <c r="C46" s="36">
         <v>1.0</v>
@@ -9218,19 +9254,19 @@
         <v>939</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G46" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1300</v>
+        <v>1312</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1301</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="47">
@@ -9239,7 +9275,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1302</v>
+        <v>1314</v>
       </c>
       <c r="C47" s="36">
         <v>1.0</v>
@@ -9248,19 +9284,19 @@
         <v>939</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G47" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H47" s="37" t="s">
-        <v>1303</v>
+        <v>1315</v>
       </c>
       <c r="I47" s="37" t="s">
-        <v>1304</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="48">
@@ -9269,7 +9305,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1305</v>
+        <v>1317</v>
       </c>
       <c r="C48" s="36">
         <v>0.0</v>
@@ -9278,19 +9314,19 @@
         <v>939</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G48" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>1306</v>
+        <v>1318</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>1307</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="49">
@@ -9299,7 +9335,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1308</v>
+        <v>1320</v>
       </c>
       <c r="C49" s="36">
         <v>1.0</v>
@@ -9308,19 +9344,19 @@
         <v>939</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G49" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>1309</v>
+        <v>1321</v>
       </c>
       <c r="I49" s="37" t="s">
-        <v>1310</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="50">
@@ -9329,7 +9365,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1311</v>
+        <v>1323</v>
       </c>
       <c r="C50" s="36">
         <v>0.0</v>
@@ -9338,19 +9374,19 @@
         <v>939</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G50" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>1312</v>
+        <v>1324</v>
       </c>
       <c r="I50" s="37" t="s">
-        <v>1313</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="51">
@@ -9359,7 +9395,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1314</v>
+        <v>1326</v>
       </c>
       <c r="C51" s="36">
         <v>0.0</v>
@@ -9368,19 +9404,19 @@
         <v>939</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G51" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H51" s="37" t="s">
-        <v>1315</v>
+        <v>1327</v>
       </c>
       <c r="I51" s="37" t="s">
-        <v>1316</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="52">
@@ -9389,7 +9425,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1317</v>
+        <v>1329</v>
       </c>
       <c r="C52" s="36">
         <v>1.0</v>
@@ -9398,19 +9434,19 @@
         <v>939</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G52" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H52" s="37" t="s">
-        <v>1318</v>
+        <v>1330</v>
       </c>
       <c r="I52" s="37" t="s">
-        <v>1319</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="53">
@@ -9419,7 +9455,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1320</v>
+        <v>1332</v>
       </c>
       <c r="C53" s="36">
         <v>1.0</v>
@@ -9428,19 +9464,19 @@
         <v>939</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G53" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>1321</v>
+        <v>1333</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>1322</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="54">
@@ -9449,7 +9485,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1323</v>
+        <v>1335</v>
       </c>
       <c r="C54" s="36">
         <v>1.0</v>
@@ -9458,19 +9494,19 @@
         <v>939</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G54" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>1324</v>
+        <v>1336</v>
       </c>
       <c r="I54" s="37" t="s">
-        <v>1325</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="55">
@@ -9479,7 +9515,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1326</v>
+        <v>1338</v>
       </c>
       <c r="C55" s="36">
         <v>0.0</v>
@@ -9488,19 +9524,19 @@
         <v>939</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F55" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G55" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>1327</v>
+        <v>1339</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>1328</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="56">
@@ -9509,7 +9545,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1039</v>
+        <v>1051</v>
       </c>
       <c r="C56" s="36">
         <v>0.0</v>
@@ -9518,19 +9554,19 @@
         <v>939</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F56" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G56" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H56" s="37" t="s">
-        <v>1329</v>
+        <v>1341</v>
       </c>
       <c r="I56" s="37" t="s">
-        <v>1330</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="57">
@@ -9539,7 +9575,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1331</v>
+        <v>1343</v>
       </c>
       <c r="C57" s="36">
         <v>0.0</v>
@@ -9548,19 +9584,19 @@
         <v>939</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F57" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G57" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>1332</v>
+        <v>1344</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>1333</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="58">
@@ -9569,7 +9605,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="C58" s="36">
         <v>1.0</v>
@@ -9578,19 +9614,19 @@
         <v>939</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G58" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>1334</v>
+        <v>1346</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>1335</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="59">
@@ -9608,19 +9644,19 @@
         <v>939</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G59" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>1336</v>
+        <v>1348</v>
       </c>
       <c r="I59" s="37" t="s">
-        <v>1337</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="60">
@@ -9629,28 +9665,28 @@
         <v>58</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1338</v>
+        <v>1350</v>
       </c>
       <c r="C60" s="36">
         <v>0.0</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>939</v>
+        <v>981</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="F60" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G60" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>1340</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="61">
@@ -9659,28 +9695,28 @@
         <v>59</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1341</v>
+        <v>1353</v>
       </c>
       <c r="C61" s="36">
         <v>0.0</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>939</v>
+        <v>983</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="F61" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G61" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>1342</v>
+        <v>1354</v>
       </c>
       <c r="I61" s="37" t="s">
-        <v>1343</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="62">
@@ -9689,28 +9725,28 @@
         <v>60</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1344</v>
+        <v>1356</v>
       </c>
       <c r="C62" s="36">
         <v>0.0</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>939</v>
+        <v>985</v>
       </c>
       <c r="E62" s="44" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="F62" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G62" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>1345</v>
+        <v>1357</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>1346</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="63">
@@ -9728,19 +9764,19 @@
         <v>939</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F63" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G63" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>1347</v>
+        <v>1359</v>
       </c>
       <c r="I63" s="37" t="s">
-        <v>1348</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="64">
@@ -9749,7 +9785,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1349</v>
+        <v>1361</v>
       </c>
       <c r="C64" s="36">
         <v>0.0</v>
@@ -9758,19 +9794,19 @@
         <v>946</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F64" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G64" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>1350</v>
+        <v>1362</v>
       </c>
       <c r="I64" s="37" t="s">
-        <v>1350</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="65">
@@ -9779,7 +9815,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1351</v>
+        <v>1363</v>
       </c>
       <c r="C65" s="36">
         <v>0.0</v>
@@ -9788,19 +9824,19 @@
         <v>947</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F65" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G65" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>1352</v>
+        <v>1364</v>
       </c>
       <c r="I65" s="37" t="s">
-        <v>1353</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="66">
@@ -9809,7 +9845,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1354</v>
+        <v>1366</v>
       </c>
       <c r="C66" s="36">
         <v>0.0</v>
@@ -9818,19 +9854,19 @@
         <v>948</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F66" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G66" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>1355</v>
+        <v>1367</v>
       </c>
       <c r="I66" s="37" t="s">
-        <v>1356</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="67">
@@ -9839,7 +9875,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1357</v>
+        <v>1369</v>
       </c>
       <c r="C67" s="36">
         <v>0.0</v>
@@ -9848,19 +9884,19 @@
         <v>949</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F67" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G67" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H67" s="37" t="s">
-        <v>1358</v>
+        <v>1370</v>
       </c>
       <c r="I67" s="37" t="s">
-        <v>1359</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="68">
@@ -9869,7 +9905,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1360</v>
+        <v>1372</v>
       </c>
       <c r="C68" s="36">
         <v>0.0</v>
@@ -9878,19 +9914,19 @@
         <v>939</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F68" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G68" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>1361</v>
+        <v>1373</v>
       </c>
       <c r="I68" s="37" t="s">
-        <v>1362</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="69">
@@ -9899,7 +9935,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1363</v>
+        <v>1375</v>
       </c>
       <c r="C69" s="36">
         <v>1.0</v>
@@ -9908,19 +9944,19 @@
         <v>939</v>
       </c>
       <c r="E69" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F69" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G69" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H69" s="37" t="s">
-        <v>1364</v>
+        <v>1376</v>
       </c>
       <c r="I69" s="37" t="s">
-        <v>1365</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="70">
@@ -9929,7 +9965,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1366</v>
+        <v>1378</v>
       </c>
       <c r="C70" s="36">
         <v>0.0</v>
@@ -9938,19 +9974,19 @@
         <v>939</v>
       </c>
       <c r="E70" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F70" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>1367</v>
+        <v>1379</v>
       </c>
       <c r="I70" s="37" t="s">
-        <v>1368</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="71">
@@ -9959,7 +9995,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1369</v>
+        <v>1381</v>
       </c>
       <c r="C71" s="36">
         <v>1.0</v>
@@ -9968,19 +10004,19 @@
         <v>939</v>
       </c>
       <c r="E71" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G71" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H71" s="37" t="s">
-        <v>1370</v>
+        <v>1382</v>
       </c>
       <c r="I71" s="37" t="s">
-        <v>1371</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="72">
@@ -9989,7 +10025,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1372</v>
+        <v>1384</v>
       </c>
       <c r="C72" s="36">
         <v>0.0</v>
@@ -9998,19 +10034,19 @@
         <v>939</v>
       </c>
       <c r="E72" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F72" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G72" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H72" s="37" t="s">
-        <v>1373</v>
+        <v>1385</v>
       </c>
       <c r="I72" s="37" t="s">
-        <v>1374</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="73">
@@ -10019,7 +10055,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>1375</v>
+        <v>1387</v>
       </c>
       <c r="C73" s="36">
         <v>1.0</v>
@@ -10028,19 +10064,19 @@
         <v>939</v>
       </c>
       <c r="E73" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F73" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G73" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H73" s="37" t="s">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="I73" s="37" t="s">
-        <v>1377</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="74">
@@ -10049,7 +10085,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="C74" s="36">
         <v>0.0</v>
@@ -10058,19 +10094,19 @@
         <v>939</v>
       </c>
       <c r="E74" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F74" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G74" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H74" s="37" t="s">
-        <v>1379</v>
+        <v>1391</v>
       </c>
       <c r="I74" s="37" t="s">
-        <v>1380</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="75">
@@ -10079,7 +10115,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>1381</v>
+        <v>1393</v>
       </c>
       <c r="C75" s="36">
         <v>1.0</v>
@@ -10088,19 +10124,19 @@
         <v>939</v>
       </c>
       <c r="E75" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F75" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G75" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H75" s="37" t="s">
-        <v>1382</v>
+        <v>1394</v>
       </c>
       <c r="I75" s="37" t="s">
-        <v>1383</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="76">
@@ -10109,7 +10145,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1384</v>
+        <v>1396</v>
       </c>
       <c r="C76" s="36">
         <v>0.0</v>
@@ -10118,19 +10154,19 @@
         <v>939</v>
       </c>
       <c r="E76" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F76" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G76" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H76" s="37" t="s">
-        <v>1385</v>
+        <v>1397</v>
       </c>
       <c r="I76" s="37" t="s">
-        <v>1386</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="77">
@@ -10139,7 +10175,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1387</v>
+        <v>1399</v>
       </c>
       <c r="C77" s="36">
         <v>1.0</v>
@@ -10148,19 +10184,19 @@
         <v>939</v>
       </c>
       <c r="E77" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F77" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G77" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H77" s="37" t="s">
-        <v>1388</v>
+        <v>1400</v>
       </c>
       <c r="I77" s="37" t="s">
-        <v>1389</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="78">
@@ -10169,7 +10205,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>1390</v>
+        <v>1402</v>
       </c>
       <c r="C78" s="36">
         <v>0.0</v>
@@ -10178,19 +10214,19 @@
         <v>939</v>
       </c>
       <c r="E78" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F78" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G78" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H78" s="37" t="s">
-        <v>1391</v>
+        <v>1403</v>
       </c>
       <c r="I78" s="37" t="s">
-        <v>1392</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="79">
@@ -10199,7 +10235,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>1051</v>
+        <v>1063</v>
       </c>
       <c r="C79" s="36">
         <v>0.0</v>
@@ -10208,19 +10244,19 @@
         <v>939</v>
       </c>
       <c r="E79" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F79" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G79" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H79" s="37" t="s">
-        <v>1393</v>
+        <v>1405</v>
       </c>
       <c r="I79" s="37" t="s">
-        <v>1394</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="80">
@@ -10229,7 +10265,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>1395</v>
+        <v>1407</v>
       </c>
       <c r="C80" s="36">
         <v>1.0</v>
@@ -10238,19 +10274,19 @@
         <v>939</v>
       </c>
       <c r="E80" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F80" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G80" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H80" s="37" t="s">
-        <v>1396</v>
+        <v>1408</v>
       </c>
       <c r="I80" s="37" t="s">
-        <v>1397</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="81">
@@ -10259,7 +10295,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="C81" s="36">
         <v>1.0</v>
@@ -10268,19 +10304,19 @@
         <v>939</v>
       </c>
       <c r="E81" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F81" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G81" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H81" s="37" t="s">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="I81" s="37" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="82">
@@ -10289,7 +10325,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>1401</v>
+        <v>1413</v>
       </c>
       <c r="C82" s="36">
         <v>1.0</v>
@@ -10298,19 +10334,19 @@
         <v>939</v>
       </c>
       <c r="E82" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F82" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G82" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H82" s="37" t="s">
-        <v>1402</v>
+        <v>1414</v>
       </c>
       <c r="I82" s="37" t="s">
-        <v>1403</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="83">
@@ -10319,7 +10355,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>1404</v>
+        <v>1416</v>
       </c>
       <c r="C83" s="36">
         <v>0.0</v>
@@ -10328,19 +10364,19 @@
         <v>939</v>
       </c>
       <c r="E83" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F83" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G83" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H83" s="37" t="s">
-        <v>1405</v>
+        <v>1417</v>
       </c>
       <c r="I83" s="37" t="s">
-        <v>1406</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="84">
@@ -10349,7 +10385,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>1407</v>
+        <v>1419</v>
       </c>
       <c r="C84" s="36">
         <v>0.0</v>
@@ -10358,19 +10394,19 @@
         <v>939</v>
       </c>
       <c r="E84" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F84" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G84" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H84" s="37" t="s">
-        <v>1408</v>
+        <v>1420</v>
       </c>
       <c r="I84" s="37" t="s">
-        <v>1409</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="85">
@@ -10379,7 +10415,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="36" t="s">
-        <v>1410</v>
+        <v>1422</v>
       </c>
       <c r="C85" s="36">
         <v>0.0</v>
@@ -10388,19 +10424,19 @@
         <v>939</v>
       </c>
       <c r="E85" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F85" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G85" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H85" s="37" t="s">
-        <v>1411</v>
+        <v>1423</v>
       </c>
       <c r="I85" s="37" t="s">
-        <v>1412</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="86">
@@ -10418,19 +10454,19 @@
         <v>939</v>
       </c>
       <c r="E86" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F86" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G86" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H86" s="37" t="s">
-        <v>1413</v>
+        <v>1425</v>
       </c>
       <c r="I86" s="37" t="s">
-        <v>1414</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="87">
@@ -10448,19 +10484,19 @@
         <v>939</v>
       </c>
       <c r="E87" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F87" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G87" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H87" s="37" t="s">
-        <v>1415</v>
+        <v>1427</v>
       </c>
       <c r="I87" s="37" t="s">
-        <v>1415</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="88">
@@ -10478,19 +10514,19 @@
         <v>939</v>
       </c>
       <c r="E88" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F88" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G88" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H88" s="37" t="s">
-        <v>1416</v>
+        <v>1428</v>
       </c>
       <c r="I88" s="37" t="s">
-        <v>1417</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="89">
@@ -10508,19 +10544,19 @@
         <v>939</v>
       </c>
       <c r="E89" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F89" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G89" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H89" s="37" t="s">
-        <v>1418</v>
+        <v>1430</v>
       </c>
       <c r="I89" s="37" t="s">
-        <v>1419</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="90">
@@ -10538,19 +10574,19 @@
         <v>939</v>
       </c>
       <c r="E90" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F90" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G90" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H90" s="37" t="s">
-        <v>1420</v>
+        <v>1432</v>
       </c>
       <c r="I90" s="37" t="s">
-        <v>1421</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="91">
@@ -10568,19 +10604,19 @@
         <v>939</v>
       </c>
       <c r="E91" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F91" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G91" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H91" s="37" t="s">
-        <v>1422</v>
+        <v>1434</v>
       </c>
       <c r="I91" s="37" t="s">
-        <v>1423</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="92">
@@ -10598,19 +10634,19 @@
         <v>939</v>
       </c>
       <c r="E92" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F92" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G92" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H92" s="37" t="s">
-        <v>1424</v>
+        <v>1436</v>
       </c>
       <c r="I92" s="37" t="s">
-        <v>1425</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="93">
@@ -10628,19 +10664,19 @@
         <v>939</v>
       </c>
       <c r="E93" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F93" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G93" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H93" s="37" t="s">
-        <v>1426</v>
+        <v>1438</v>
       </c>
       <c r="I93" s="37" t="s">
-        <v>1427</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="94">
@@ -10658,19 +10694,19 @@
         <v>939</v>
       </c>
       <c r="E94" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F94" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G94" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H94" s="37" t="s">
-        <v>1428</v>
+        <v>1440</v>
       </c>
       <c r="I94" s="37" t="s">
-        <v>1429</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="95">
@@ -10688,19 +10724,19 @@
         <v>944</v>
       </c>
       <c r="E95" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F95" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G95" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H95" s="37" t="s">
-        <v>1430</v>
+        <v>1442</v>
       </c>
       <c r="I95" s="37" t="s">
-        <v>1431</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="96">
@@ -10718,19 +10754,19 @@
         <v>939</v>
       </c>
       <c r="E96" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F96" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G96" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H96" s="37" t="s">
-        <v>1432</v>
+        <v>1444</v>
       </c>
       <c r="I96" s="37" t="s">
-        <v>1433</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="97">
@@ -10748,19 +10784,19 @@
         <v>939</v>
       </c>
       <c r="E97" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F97" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G97" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H97" s="37" t="s">
-        <v>1434</v>
+        <v>1446</v>
       </c>
       <c r="I97" s="37" t="s">
-        <v>1435</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="98">
@@ -10778,19 +10814,19 @@
         <v>939</v>
       </c>
       <c r="E98" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F98" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G98" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H98" s="37" t="s">
-        <v>1436</v>
+        <v>1448</v>
       </c>
       <c r="I98" s="37" t="s">
-        <v>1437</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="99">
@@ -10808,19 +10844,19 @@
         <v>939</v>
       </c>
       <c r="E99" s="44" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="F99" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G99" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H99" s="37" t="s">
-        <v>1438</v>
+        <v>1450</v>
       </c>
       <c r="I99" s="37" t="s">
-        <v>1439</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="100">
@@ -10838,19 +10874,19 @@
         <v>939</v>
       </c>
       <c r="E100" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F100" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G100" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H100" s="37" t="s">
-        <v>1440</v>
+        <v>1452</v>
       </c>
       <c r="I100" s="37" t="s">
-        <v>1441</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="101">
@@ -10868,19 +10904,19 @@
         <v>939</v>
       </c>
       <c r="E101" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F101" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G101" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H101" s="37" t="s">
-        <v>1442</v>
+        <v>1454</v>
       </c>
       <c r="I101" s="37" t="s">
-        <v>1443</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="102">
@@ -10898,19 +10934,19 @@
         <v>939</v>
       </c>
       <c r="E102" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F102" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G102" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H102" s="37" t="s">
-        <v>1444</v>
+        <v>1456</v>
       </c>
       <c r="I102" s="37" t="s">
-        <v>1445</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="103">
@@ -10919,7 +10955,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="36" t="s">
-        <v>1446</v>
+        <v>1458</v>
       </c>
       <c r="C103" s="36">
         <v>0.0</v>
@@ -10928,19 +10964,19 @@
         <v>939</v>
       </c>
       <c r="E103" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F103" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G103" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H103" s="37" t="s">
-        <v>1447</v>
+        <v>1459</v>
       </c>
       <c r="I103" s="37" t="s">
-        <v>1448</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="104">
@@ -10949,7 +10985,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>1449</v>
+        <v>1461</v>
       </c>
       <c r="C104" s="36">
         <v>1.0</v>
@@ -10958,19 +10994,19 @@
         <v>939</v>
       </c>
       <c r="E104" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F104" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G104" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H104" s="37" t="s">
-        <v>1450</v>
+        <v>1462</v>
       </c>
       <c r="I104" s="37" t="s">
-        <v>1451</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="105">
@@ -10979,7 +11015,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>1452</v>
+        <v>1464</v>
       </c>
       <c r="C105" s="36">
         <v>0.0</v>
@@ -10988,19 +11024,19 @@
         <v>939</v>
       </c>
       <c r="E105" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F105" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G105" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H105" s="37" t="s">
-        <v>1453</v>
+        <v>1465</v>
       </c>
       <c r="I105" s="37" t="s">
-        <v>1454</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="106">
@@ -11009,7 +11045,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>1455</v>
+        <v>1467</v>
       </c>
       <c r="C106" s="36">
         <v>1.0</v>
@@ -11018,19 +11054,19 @@
         <v>939</v>
       </c>
       <c r="E106" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F106" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G106" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H106" s="37" t="s">
-        <v>1456</v>
+        <v>1468</v>
       </c>
       <c r="I106" s="37" t="s">
-        <v>1457</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="107">
@@ -11039,7 +11075,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>1458</v>
+        <v>1470</v>
       </c>
       <c r="C107" s="36">
         <v>0.0</v>
@@ -11048,19 +11084,19 @@
         <v>939</v>
       </c>
       <c r="E107" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F107" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G107" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H107" s="37" t="s">
-        <v>1459</v>
+        <v>1471</v>
       </c>
       <c r="I107" s="37" t="s">
-        <v>1460</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="108">
@@ -11069,7 +11105,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>1461</v>
+        <v>1473</v>
       </c>
       <c r="C108" s="36">
         <v>1.0</v>
@@ -11078,19 +11114,19 @@
         <v>939</v>
       </c>
       <c r="E108" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F108" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G108" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H108" s="37" t="s">
-        <v>1462</v>
+        <v>1474</v>
       </c>
       <c r="I108" s="37" t="s">
-        <v>1462</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="109">
@@ -11099,7 +11135,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>1463</v>
+        <v>1475</v>
       </c>
       <c r="C109" s="36">
         <v>0.0</v>
@@ -11108,19 +11144,19 @@
         <v>939</v>
       </c>
       <c r="E109" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F109" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G109" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H109" s="37" t="s">
-        <v>1464</v>
+        <v>1476</v>
       </c>
       <c r="I109" s="37" t="s">
-        <v>1465</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="110">
@@ -11129,7 +11165,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>1466</v>
+        <v>1478</v>
       </c>
       <c r="C110" s="36">
         <v>1.0</v>
@@ -11138,19 +11174,19 @@
         <v>939</v>
       </c>
       <c r="E110" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F110" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G110" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H110" s="37" t="s">
-        <v>1467</v>
+        <v>1479</v>
       </c>
       <c r="I110" s="37" t="s">
-        <v>1468</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="111">
@@ -11159,7 +11195,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>1469</v>
+        <v>1481</v>
       </c>
       <c r="C111" s="36">
         <v>0.0</v>
@@ -11168,19 +11204,19 @@
         <v>939</v>
       </c>
       <c r="E111" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F111" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G111" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H111" s="37" t="s">
-        <v>1470</v>
+        <v>1482</v>
       </c>
       <c r="I111" s="37" t="s">
-        <v>1471</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="112">
@@ -11189,7 +11225,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="36" t="s">
-        <v>1472</v>
+        <v>1484</v>
       </c>
       <c r="C112" s="36">
         <v>1.0</v>
@@ -11198,19 +11234,19 @@
         <v>939</v>
       </c>
       <c r="E112" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F112" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G112" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H112" s="37" t="s">
-        <v>1473</v>
+        <v>1485</v>
       </c>
       <c r="I112" s="37" t="s">
-        <v>1474</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="113">
@@ -11219,7 +11255,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>1475</v>
+        <v>1487</v>
       </c>
       <c r="C113" s="36">
         <v>0.0</v>
@@ -11228,19 +11264,19 @@
         <v>939</v>
       </c>
       <c r="E113" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F113" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G113" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H113" s="37" t="s">
-        <v>1476</v>
+        <v>1488</v>
       </c>
       <c r="I113" s="37" t="s">
-        <v>1477</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="114">
@@ -11249,7 +11285,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>1059</v>
+        <v>1071</v>
       </c>
       <c r="C114" s="36">
         <v>0.0</v>
@@ -11258,19 +11294,19 @@
         <v>939</v>
       </c>
       <c r="E114" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F114" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G114" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H114" s="37" t="s">
-        <v>1478</v>
+        <v>1490</v>
       </c>
       <c r="I114" s="37" t="s">
-        <v>1479</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="115">
@@ -11279,7 +11315,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>1480</v>
+        <v>1492</v>
       </c>
       <c r="C115" s="36">
         <v>0.0</v>
@@ -11288,19 +11324,19 @@
         <v>939</v>
       </c>
       <c r="E115" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F115" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G115" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H115" s="37" t="s">
-        <v>1481</v>
+        <v>1493</v>
       </c>
       <c r="I115" s="37" t="s">
-        <v>1482</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="116">
@@ -11309,7 +11345,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="36" t="s">
-        <v>1483</v>
+        <v>1495</v>
       </c>
       <c r="C116" s="36">
         <v>1.0</v>
@@ -11318,19 +11354,19 @@
         <v>939</v>
       </c>
       <c r="E116" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F116" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G116" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H116" s="37" t="s">
-        <v>1484</v>
+        <v>1496</v>
       </c>
       <c r="I116" s="37" t="s">
-        <v>1485</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="117">
@@ -11348,19 +11384,19 @@
         <v>939</v>
       </c>
       <c r="E117" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F117" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G117" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H117" s="37" t="s">
-        <v>1486</v>
+        <v>1498</v>
       </c>
       <c r="I117" s="37" t="s">
-        <v>1487</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="118">
@@ -11378,19 +11414,19 @@
         <v>942</v>
       </c>
       <c r="E118" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F118" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G118" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H118" s="37" t="s">
-        <v>1488</v>
+        <v>1500</v>
       </c>
       <c r="I118" s="37" t="s">
-        <v>1489</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="119">
@@ -11408,19 +11444,19 @@
         <v>939</v>
       </c>
       <c r="E119" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F119" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G119" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H119" s="37" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="I119" s="37" t="s">
-        <v>1491</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="120">
@@ -11438,16 +11474,16 @@
         <v>939</v>
       </c>
       <c r="E120" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F120" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G120" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H120" s="37" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="I120" s="37" t="s">
         <v>14</v>
@@ -11459,7 +11495,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>1061</v>
+        <v>1073</v>
       </c>
       <c r="C121" s="36">
         <v>0.0</v>
@@ -11468,19 +11504,19 @@
         <v>939</v>
       </c>
       <c r="E121" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F121" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G121" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H121" s="37" t="s">
-        <v>1493</v>
+        <v>1505</v>
       </c>
       <c r="I121" s="37" t="s">
-        <v>1494</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="122">
@@ -11489,7 +11525,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="36" t="s">
-        <v>1062</v>
+        <v>1074</v>
       </c>
       <c r="C122" s="36">
         <v>0.0</v>
@@ -11498,19 +11534,19 @@
         <v>939</v>
       </c>
       <c r="E122" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F122" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G122" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H122" s="37" t="s">
-        <v>1495</v>
+        <v>1507</v>
       </c>
       <c r="I122" s="37" t="s">
-        <v>1496</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="123">
@@ -11519,7 +11555,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>1497</v>
+        <v>1509</v>
       </c>
       <c r="C123" s="36">
         <v>0.0</v>
@@ -11528,19 +11564,19 @@
         <v>939</v>
       </c>
       <c r="E123" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F123" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G123" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H123" s="37" t="s">
-        <v>1498</v>
+        <v>1510</v>
       </c>
       <c r="I123" s="37" t="s">
-        <v>1499</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="124">
@@ -11549,7 +11585,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="36" t="s">
-        <v>1500</v>
+        <v>1512</v>
       </c>
       <c r="C124" s="36">
         <v>0.0</v>
@@ -11558,19 +11594,19 @@
         <v>939</v>
       </c>
       <c r="E124" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F124" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G124" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H124" s="37" t="s">
-        <v>1501</v>
+        <v>1513</v>
       </c>
       <c r="I124" s="37" t="s">
-        <v>1502</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="125">
@@ -11588,19 +11624,19 @@
         <v>939</v>
       </c>
       <c r="E125" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F125" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G125" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H125" s="37" t="s">
-        <v>1503</v>
+        <v>1515</v>
       </c>
       <c r="I125" s="37" t="s">
-        <v>1504</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="126">
@@ -11618,19 +11654,19 @@
         <v>939</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F126" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G126" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H126" s="37" t="s">
-        <v>1505</v>
+        <v>1517</v>
       </c>
       <c r="I126" s="37" t="s">
-        <v>1506</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="127">
@@ -11639,7 +11675,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="36" t="s">
-        <v>1507</v>
+        <v>1519</v>
       </c>
       <c r="C127" s="36">
         <v>0.0</v>
@@ -11648,19 +11684,19 @@
         <v>961</v>
       </c>
       <c r="E127" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F127" s="38" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="G127" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H127" s="37" t="s">
-        <v>1508</v>
+        <v>1520</v>
       </c>
       <c r="I127" s="37" t="s">
-        <v>1508</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="128">
@@ -11669,7 +11705,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="36" t="s">
-        <v>1509</v>
+        <v>1521</v>
       </c>
       <c r="C128" s="36">
         <v>1.0</v>
@@ -11678,19 +11714,19 @@
         <v>963</v>
       </c>
       <c r="E128" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F128" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G128" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H128" s="37" t="s">
-        <v>1510</v>
+        <v>1522</v>
       </c>
       <c r="I128" s="37" t="s">
-        <v>1510</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="129">
@@ -11699,7 +11735,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="36" t="s">
-        <v>1511</v>
+        <v>1523</v>
       </c>
       <c r="C129" s="36">
         <v>0.0</v>
@@ -11708,19 +11744,19 @@
         <v>965</v>
       </c>
       <c r="E129" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F129" s="38" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="G129" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H129" s="37" t="s">
-        <v>1512</v>
+        <v>1524</v>
       </c>
       <c r="I129" s="37" t="s">
-        <v>1512</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="130">
@@ -11729,7 +11765,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="36" t="s">
-        <v>1513</v>
+        <v>1525</v>
       </c>
       <c r="C130" s="36">
         <v>1.0</v>
@@ -11738,19 +11774,19 @@
         <v>967</v>
       </c>
       <c r="E130" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F130" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G130" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H130" s="37" t="s">
-        <v>1514</v>
+        <v>1526</v>
       </c>
       <c r="I130" s="37" t="s">
-        <v>1514</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="131">
@@ -11759,7 +11795,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="36" t="s">
-        <v>1515</v>
+        <v>1527</v>
       </c>
       <c r="C131" s="36">
         <v>0.0</v>
@@ -11768,19 +11804,19 @@
         <v>969</v>
       </c>
       <c r="E131" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F131" s="38" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="G131" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H131" s="37" t="s">
-        <v>1516</v>
+        <v>1528</v>
       </c>
       <c r="I131" s="37" t="s">
-        <v>1516</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="132">
@@ -11789,7 +11825,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="36" t="s">
-        <v>1517</v>
+        <v>1529</v>
       </c>
       <c r="C132" s="36">
         <v>1.0</v>
@@ -11798,19 +11834,19 @@
         <v>971</v>
       </c>
       <c r="E132" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F132" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G132" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H132" s="37" t="s">
-        <v>1518</v>
+        <v>1530</v>
       </c>
       <c r="I132" s="37" t="s">
-        <v>1518</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="133">
@@ -11819,7 +11855,7 @@
         <v>131</v>
       </c>
       <c r="B133" s="36" t="s">
-        <v>1071</v>
+        <v>1083</v>
       </c>
       <c r="C133" s="36">
         <v>0.0</v>
@@ -11828,19 +11864,19 @@
         <v>973</v>
       </c>
       <c r="E133" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F133" s="38" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="G133" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H133" s="37" t="s">
-        <v>1519</v>
+        <v>1531</v>
       </c>
       <c r="I133" s="37" t="s">
-        <v>1520</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="134">
@@ -11849,7 +11885,7 @@
         <v>132</v>
       </c>
       <c r="B134" s="36" t="s">
-        <v>1521</v>
+        <v>1533</v>
       </c>
       <c r="C134" s="36">
         <v>1.0</v>
@@ -11858,19 +11894,19 @@
         <v>957</v>
       </c>
       <c r="E134" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F134" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G134" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H134" s="37" t="s">
-        <v>1522</v>
+        <v>1534</v>
       </c>
       <c r="I134" s="37" t="s">
-        <v>1522</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="135">
@@ -11879,7 +11915,7 @@
         <v>133</v>
       </c>
       <c r="B135" s="36" t="s">
-        <v>1523</v>
+        <v>1535</v>
       </c>
       <c r="C135" s="36">
         <v>1.0</v>
@@ -11888,19 +11924,19 @@
         <v>959</v>
       </c>
       <c r="E135" s="44" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="F135" s="38" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="G135" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H135" s="37" t="s">
-        <v>1524</v>
+        <v>1536</v>
       </c>
       <c r="I135" s="37" t="s">
-        <v>1524</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="136">
@@ -11909,7 +11945,7 @@
         <v>134</v>
       </c>
       <c r="B136" s="36" t="s">
-        <v>1525</v>
+        <v>1537</v>
       </c>
       <c r="C136" s="36">
         <v>0.0</v>
@@ -11918,19 +11954,19 @@
         <v>939</v>
       </c>
       <c r="E136" s="44" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F136" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="G136" s="38" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="H136" s="37" t="s">
-        <v>1526</v>
+        <v>1538</v>
       </c>
       <c r="I136" s="37" t="s">
-        <v>1526</v>
+        <v>1538</v>
       </c>
     </row>
   </sheetData>
@@ -11972,34 +12008,34 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1527</v>
+        <v>1539</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>1528</v>
+        <v>1540</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1529</v>
+        <v>1541</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1530</v>
+        <v>1542</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>1531</v>
+        <v>1543</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>1532</v>
+        <v>1544</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>1533</v>
+        <v>1545</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>1534</v>
+        <v>1546</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>1535</v>
+        <v>1547</v>
       </c>
       <c r="K1" s="63" t="s">
-        <v>1536</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="2" ht="186.0" customHeight="1">
@@ -12008,7 +12044,7 @@
         <v>-1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>1537</v>
+        <v>1549</v>
       </c>
       <c r="C2" s="65" t="s">
         <v>323</v>
@@ -12044,7 +12080,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>1538</v>
+        <v>1550</v>
       </c>
       <c r="C3" s="65" t="s">
         <v>871</v>
@@ -12053,10 +12089,10 @@
         <v>956</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>1539</v>
+        <v>1551</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1540</v>
+        <v>1552</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>321</v>
@@ -12080,19 +12116,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1541</v>
+        <v>1553</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>1542</v>
+        <v>1554</v>
       </c>
       <c r="D4" s="66" t="s">
         <v>956</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1542</v>
+        <v>1554</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1543</v>
+        <v>1555</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>321</v>
@@ -12116,19 +12152,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1544</v>
+        <v>1556</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>1545</v>
+        <v>1557</v>
       </c>
       <c r="D5" s="66" t="s">
         <v>956</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1545</v>
+        <v>1557</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1546</v>
+        <v>1558</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>321</v>
@@ -12152,19 +12188,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1547</v>
+        <v>1559</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>1548</v>
+        <v>1560</v>
       </c>
       <c r="D6" s="66" t="s">
         <v>956</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1548</v>
+        <v>1560</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1549</v>
+        <v>1561</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>321</v>
@@ -12188,25 +12224,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1550</v>
+        <v>1562</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1551</v>
+        <v>1563</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>1552</v>
+        <v>1564</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>1551</v>
+        <v>1563</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>1553</v>
+        <v>1565</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>1552</v>
+        <v>1564</v>
       </c>
       <c r="I7" s="35" t="s">
         <v>618</v>
@@ -12224,25 +12260,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>1554</v>
+        <v>1566</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>1552</v>
+        <v>1564</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>1552</v>
+        <v>1564</v>
       </c>
       <c r="I8" s="35" t="s">
         <v>618</v>
@@ -12272,7 +12308,7 @@
         <v>908</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>321</v>
@@ -12296,25 +12332,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>1558</v>
+        <v>1570</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>1559</v>
+        <v>1571</v>
       </c>
       <c r="D10" s="66" t="s">
         <v>952</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1559</v>
+        <v>1571</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1560</v>
+        <v>1572</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>1561</v>
+        <v>1573</v>
       </c>
       <c r="I10" s="35" t="s">
         <v>681</v>
@@ -12332,25 +12368,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1563</v>
+        <v>1575</v>
       </c>
       <c r="D11" s="66" t="s">
-        <v>1552</v>
+        <v>1564</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1563</v>
+        <v>1575</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>1564</v>
+        <v>1576</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>1552</v>
+        <v>1564</v>
       </c>
       <c r="I11" s="35" t="s">
         <v>618</v>
@@ -12368,19 +12404,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1565</v>
+        <v>1577</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1566</v>
+        <v>1578</v>
       </c>
       <c r="D12" s="66" t="s">
         <v>951</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>1566</v>
+        <v>1578</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>1567</v>
+        <v>1579</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>321</v>
@@ -12404,19 +12440,19 @@
         <v>10</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1569</v>
+        <v>1581</v>
       </c>
       <c r="D13" s="66" t="s">
         <v>951</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>1569</v>
+        <v>1581</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>1570</v>
+        <v>1582</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>321</v>
@@ -12443,13 +12479,13 @@
         <v>21</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>1571</v>
+        <v>1583</v>
       </c>
       <c r="D14" s="66" t="s">
         <v>939</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>1571</v>
+        <v>1583</v>
       </c>
       <c r="F14" s="35" t="s">
         <v>347</v>
@@ -12476,7 +12512,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1572</v>
+        <v>1584</v>
       </c>
       <c r="C15" s="65" t="s">
         <v>323</v>
@@ -12539,7 +12575,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1573</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="2">
@@ -12566,7 +12602,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1574</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="5">
@@ -12575,7 +12611,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1575</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="6">
@@ -12587,7 +12623,7 @@
         <v>49</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1576</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="8">
@@ -12595,7 +12631,7 @@
         <v>0.0</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1577</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="9">
@@ -12603,7 +12639,7 @@
         <v>1.0</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1578</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="10">
@@ -12611,7 +12647,7 @@
         <v>2.0</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1579</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="11">
@@ -12619,7 +12655,7 @@
         <v>3.0</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1580</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="12">
@@ -12627,7 +12663,7 @@
         <v>4.0</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1581</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="13">
@@ -12635,7 +12671,7 @@
         <v>5.0</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1582</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="15">
@@ -12643,7 +12679,7 @@
         <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1583</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="16">
@@ -12661,7 +12697,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1584</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="18">
@@ -12706,7 +12742,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1585</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="23">
@@ -12723,7 +12759,7 @@
         <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1586</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="26">
@@ -12768,7 +12804,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1587</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="31">
@@ -12795,7 +12831,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1588</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="34">
@@ -12813,7 +12849,7 @@
         <v>9</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1589</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="36">
@@ -12875,7 +12911,7 @@
         <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1590</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="44">
@@ -12884,7 +12920,7 @@
         <v>0</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="45">
@@ -12893,7 +12929,7 @@
         <v>1</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1591</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="46">
@@ -12902,7 +12938,7 @@
         <v>2</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1592</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="47">
@@ -12911,7 +12947,7 @@
         <v>3</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1593</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="48">
@@ -12920,7 +12956,7 @@
         <v>4</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1594</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="49">
@@ -12929,7 +12965,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1595</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="50">
@@ -12938,7 +12974,7 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1596</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="51">
@@ -12947,7 +12983,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1597</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="52">
@@ -12956,7 +12992,7 @@
         <v>8</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1598</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="53">
@@ -12965,7 +13001,7 @@
         <v>9</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="54">
@@ -12974,7 +13010,7 @@
         <v>10</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="55">
@@ -12983,7 +13019,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1599</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="56">
@@ -12992,7 +13028,7 @@
         <v>12</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1600</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="57">
@@ -13001,7 +13037,7 @@
         <v>13</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1601</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="58">
@@ -13010,7 +13046,7 @@
         <v>14</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1602</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="59">
@@ -13019,7 +13055,7 @@
         <v>15</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1603</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="61">
@@ -13027,7 +13063,7 @@
         <v>49</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1604</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="62">
@@ -13080,7 +13116,7 @@
         <v>49</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1605</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="69">
@@ -13145,7 +13181,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1606</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="2">
@@ -13163,7 +13199,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1607</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="4">
@@ -13172,7 +13208,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1608</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="5">
@@ -13253,7 +13289,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1609</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="14">
@@ -13298,7 +13334,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1610</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="19">
@@ -13442,7 +13478,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1611</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="36">
@@ -13450,16 +13486,16 @@
         <v>49</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1612</v>
+        <v>1624</v>
       </c>
       <c r="C36" s="68" t="s">
         <v>312</v>
       </c>
       <c r="D36" s="68" t="s">
-        <v>1613</v>
+        <v>1625</v>
       </c>
       <c r="E36" s="68" t="s">
-        <v>1614</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="37">
@@ -13468,7 +13504,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1615</v>
+        <v>1627</v>
       </c>
       <c r="C37" s="38" t="s">
         <v>321</v>
@@ -13487,10 +13523,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1616</v>
+        <v>1628</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1118</v>
+        <v>1130</v>
       </c>
       <c r="D38" s="38" t="s">
         <v>888</v>
@@ -13506,10 +13542,10 @@
         <v>2</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1617</v>
+        <v>1629</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1149</v>
+        <v>1161</v>
       </c>
       <c r="D39" s="38" t="s">
         <v>916</v>
@@ -13528,7 +13564,7 @@
         <v>44</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1156</v>
+        <v>1168</v>
       </c>
       <c r="D40" s="38" t="s">
         <v>45</v>
@@ -13544,7 +13580,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1618</v>
+        <v>1630</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>454</v>
@@ -13562,19 +13598,19 @@
         <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1619</v>
+        <v>1631</v>
       </c>
       <c r="C43" s="67" t="s">
-        <v>1620</v>
+        <v>1632</v>
       </c>
       <c r="D43" s="67" t="s">
-        <v>1081</v>
+        <v>1093</v>
       </c>
       <c r="E43" s="68" t="s">
-        <v>1621</v>
+        <v>1633</v>
       </c>
       <c r="F43" s="67" t="s">
-        <v>1622</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="44">
@@ -13586,13 +13622,13 @@
         <v>700</v>
       </c>
       <c r="C44" s="44" t="s">
-        <v>1615</v>
+        <v>1627</v>
       </c>
       <c r="D44" s="44" t="s">
         <v>703</v>
       </c>
       <c r="E44" s="48" t="s">
-        <v>1623</v>
+        <v>1635</v>
       </c>
       <c r="F44" s="43" t="b">
         <v>0</v>
@@ -13607,13 +13643,13 @@
         <v>712</v>
       </c>
       <c r="C45" s="44" t="s">
-        <v>1616</v>
+        <v>1628</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>1229</v>
+        <v>1241</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>1623</v>
+        <v>1635</v>
       </c>
       <c r="F45" s="43" t="b">
         <v>0</v>
@@ -13628,13 +13664,13 @@
         <v>729</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>1616</v>
+        <v>1628</v>
       </c>
       <c r="D46" s="44" t="s">
         <v>749</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>1623</v>
+        <v>1635</v>
       </c>
       <c r="F46" s="43" t="b">
         <v>0</v>
@@ -13649,13 +13685,13 @@
         <v>734</v>
       </c>
       <c r="C47" s="44" t="s">
-        <v>1617</v>
+        <v>1629</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>1331</v>
+        <v>1343</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>1623</v>
+        <v>1635</v>
       </c>
       <c r="F47" s="43" t="b">
         <v>0</v>
@@ -13673,10 +13709,10 @@
         <v>44</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>1404</v>
+        <v>1416</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>1623</v>
+        <v>1635</v>
       </c>
       <c r="F48" s="43" t="b">
         <v>0</v>
@@ -13688,16 +13724,16 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1624</v>
+        <v>1636</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>44</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>1407</v>
+        <v>1419</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>1623</v>
+        <v>1635</v>
       </c>
       <c r="F49" s="43" t="b">
         <v>0</v>
@@ -13709,16 +13745,16 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1625</v>
+        <v>1637</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>44</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>1410</v>
+        <v>1422</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>1623</v>
+        <v>1635</v>
       </c>
       <c r="F50" s="43" t="b">
         <v>1</v>
@@ -13730,16 +13766,16 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1626</v>
+        <v>1638</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>1618</v>
+        <v>1630</v>
       </c>
       <c r="D51" s="44" t="s">
         <v>703</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>1623</v>
+        <v>1635</v>
       </c>
       <c r="F51" s="43" t="b">
         <v>0</v>
@@ -13750,10 +13786,10 @@
         <v>49</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1627</v>
+        <v>1639</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>1628</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="54">
@@ -13762,7 +13798,7 @@
         <v>0</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1623</v>
+        <v>1635</v>
       </c>
       <c r="C54" s="51" t="s">
         <v>463</v>
@@ -13773,7 +13809,7 @@
         <v>49</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1629</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="57">
@@ -14783,16 +14819,16 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1630</v>
+        <v>1642</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1631</v>
+        <v>1643</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1632</v>
+        <v>1644</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1633</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="2">
@@ -14804,7 +14840,7 @@
         <v>324</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1634</v>
+        <v>1646</v>
       </c>
       <c r="D2" s="70" t="s">
         <v>321</v>
@@ -14822,7 +14858,7 @@
         <v>440</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1635</v>
+        <v>1647</v>
       </c>
       <c r="D3" s="70" t="s">
         <v>321</v>
@@ -14837,10 +14873,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1636</v>
+        <v>1648</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1634</v>
+        <v>1646</v>
       </c>
       <c r="D4" s="70" t="s">
         <v>321</v>
@@ -14878,7 +14914,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1576</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="2">
@@ -14905,7 +14941,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1637</v>
+        <v>1649</v>
       </c>
     </row>
   </sheetData>
@@ -14931,21 +14967,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1638</v>
+        <v>1650</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1639</v>
+        <v>1651</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1640</v>
+        <v>1652</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1641</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="s">
-        <v>1642</v>
+        <v>1654</v>
       </c>
       <c r="B2" s="71">
         <v>5.0</v>
@@ -14959,7 +14995,7 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>1643</v>
+        <v>1655</v>
       </c>
       <c r="B3" s="71">
         <v>4.0</v>
@@ -14973,7 +15009,7 @@
     </row>
     <row r="4">
       <c r="A4" s="37" t="s">
-        <v>1644</v>
+        <v>1656</v>
       </c>
       <c r="B4" s="71">
         <v>2.0</v>
@@ -14987,7 +15023,7 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>1645</v>
+        <v>1657</v>
       </c>
       <c r="B5" s="71">
         <v>5.0</v>
@@ -15001,7 +15037,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>1646</v>
+        <v>1658</v>
       </c>
       <c r="B6" s="71">
         <v>4.0</v>
@@ -15015,7 +15051,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>1647</v>
+        <v>1659</v>
       </c>
       <c r="B7" s="71">
         <v>4.0</v>
@@ -15029,7 +15065,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>1648</v>
+        <v>1660</v>
       </c>
       <c r="B8" s="71">
         <v>2.0</v>
@@ -15043,7 +15079,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>1177</v>
+        <v>1189</v>
       </c>
       <c r="B9" s="71">
         <v>5.0</v>
@@ -31061,6 +31097,96 @@
       <c r="C26" s="36" t="s">
         <v>940</v>
       </c>
+      <c r="D26" s="36" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>25</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>977</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>940</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>26</v>
+      </c>
+      <c r="B28" s="36" t="s">
+        <v>979</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>940</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>27</v>
+      </c>
+      <c r="B29" s="36" t="s">
+        <v>981</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>940</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>28</v>
+      </c>
+      <c r="B30" s="36" t="s">
+        <v>983</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>940</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>29</v>
+      </c>
+      <c r="B31" s="36" t="s">
+        <v>985</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>940</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>30</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>987</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>940</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -31093,13 +31219,13 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>976</v>
+        <v>988</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>26</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>977</v>
+        <v>989</v>
       </c>
     </row>
     <row r="2">
@@ -31114,7 +31240,7 @@
         <v>320</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>978</v>
+        <v>990</v>
       </c>
     </row>
     <row r="3">
@@ -31129,7 +31255,7 @@
         <v>320</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>979</v>
+        <v>991</v>
       </c>
     </row>
     <row r="4">
@@ -31141,10 +31267,10 @@
         <v>746</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>980</v>
+        <v>992</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>981</v>
+        <v>993</v>
       </c>
     </row>
     <row r="5">
@@ -31153,13 +31279,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>982</v>
+        <v>994</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>980</v>
+        <v>992</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>983</v>
+        <v>995</v>
       </c>
     </row>
     <row r="6">
@@ -31171,10 +31297,10 @@
         <v>760</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>980</v>
+        <v>992</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>984</v>
+        <v>996</v>
       </c>
     </row>
     <row r="7">
@@ -31186,10 +31312,10 @@
         <v>762</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>985</v>
+        <v>997</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>986</v>
+        <v>998</v>
       </c>
     </row>
     <row r="8">
@@ -31198,13 +31324,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>985</v>
+        <v>997</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
@@ -31216,10 +31342,10 @@
         <v>764</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="10">
@@ -31228,13 +31354,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>992</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="11">
@@ -31246,10 +31372,10 @@
         <v>765</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>993</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="12">
@@ -31264,7 +31390,7 @@
         <v>406</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="13">
@@ -31279,7 +31405,7 @@
         <v>408</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>995</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="14">
@@ -31288,13 +31414,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>997</v>
+        <v>1009</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>998</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="15">
@@ -31306,10 +31432,10 @@
         <v>772</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>997</v>
+        <v>1009</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="16">
@@ -31318,13 +31444,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>1000</v>
+        <v>1012</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>1001</v>
+        <v>1013</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>1002</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="17">
@@ -31336,10 +31462,10 @@
         <v>797</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>1001</v>
+        <v>1013</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>1003</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="18">
@@ -31354,7 +31480,7 @@
         <v>387</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>1004</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="19">
@@ -31369,7 +31495,7 @@
         <v>326</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="20">
@@ -31378,13 +31504,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>1006</v>
+        <v>1018</v>
       </c>
       <c r="C20" s="39" t="s">
         <v>387</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>1007</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="21">
@@ -31399,7 +31525,7 @@
         <v>35</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>1008</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="22">
@@ -31414,7 +31540,7 @@
         <v>35</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="23">
@@ -31423,13 +31549,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>1010</v>
+        <v>1022</v>
       </c>
       <c r="C23" s="39" t="s">
         <v>320</v>
       </c>
       <c r="D23" s="41" t="s">
-        <v>978</v>
+        <v>990</v>
       </c>
     </row>
     <row r="25">
@@ -31437,25 +31563,25 @@
         <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1011</v>
+        <v>1023</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>457</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>1012</v>
+        <v>1024</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>1013</v>
+        <v>1025</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>1014</v>
+        <v>1026</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>1015</v>
+        <v>1027</v>
       </c>
       <c r="H25" s="28" t="s">
-        <v>1016</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="26">
@@ -31464,7 +31590,7 @@
         <v>0</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>978</v>
+        <v>990</v>
       </c>
       <c r="C26" s="37" t="s">
         <v>463</v>
@@ -31491,7 +31617,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>979</v>
+        <v>991</v>
       </c>
       <c r="C27" s="37" t="s">
         <v>463</v>
@@ -31518,7 +31644,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>981</v>
+        <v>993</v>
       </c>
       <c r="C28" s="40" t="s">
         <v>463</v>
@@ -31530,13 +31656,13 @@
         <v>467</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>982</v>
+        <v>994</v>
       </c>
       <c r="G28" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="40" t="s">
-        <v>1017</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="29">
@@ -31545,7 +31671,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>1018</v>
+        <v>1030</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>463</v>
@@ -31557,13 +31683,13 @@
         <v>467</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>982</v>
+        <v>994</v>
       </c>
       <c r="G29" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H29" s="40" t="s">
-        <v>1019</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="30">
@@ -31572,7 +31698,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1020</v>
+        <v>1032</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>463</v>
@@ -31590,7 +31716,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="40" t="s">
-        <v>1021</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="31">
@@ -31599,7 +31725,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1022</v>
+        <v>1034</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>463</v>
@@ -31608,7 +31734,7 @@
         <v>464</v>
       </c>
       <c r="E31" s="40" t="s">
-        <v>1023</v>
+        <v>1035</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>702</v>
@@ -31617,7 +31743,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="40" t="s">
-        <v>1024</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="32">
@@ -31626,7 +31752,7 @@
         <v>6</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>984</v>
+        <v>996</v>
       </c>
       <c r="C32" s="40" t="s">
         <v>463</v>
@@ -31644,7 +31770,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="40" t="s">
-        <v>1025</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="33">
@@ -31653,7 +31779,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>986</v>
+        <v>998</v>
       </c>
       <c r="C33" s="40" t="s">
         <v>463</v>
@@ -31665,13 +31791,13 @@
         <v>467</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="G33" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H33" s="40" t="s">
-        <v>1026</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="34">
@@ -31680,7 +31806,7 @@
         <v>8</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="C34" s="40" t="s">
         <v>463</v>
@@ -31698,7 +31824,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="40" t="s">
-        <v>1027</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="35">
@@ -31707,7 +31833,7 @@
         <v>9</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="C35" s="40" t="s">
         <v>463</v>
@@ -31719,13 +31845,13 @@
         <v>467</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
       <c r="G35" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H35" s="40" t="s">
-        <v>1028</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="36">
@@ -31734,7 +31860,7 @@
         <v>10</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1029</v>
+        <v>1041</v>
       </c>
       <c r="C36" s="40" t="s">
         <v>463</v>
@@ -31746,13 +31872,13 @@
         <v>830</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
       <c r="G36" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H36" s="40" t="s">
-        <v>1030</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="37">
@@ -31761,7 +31887,7 @@
         <v>11</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1031</v>
+        <v>1043</v>
       </c>
       <c r="C37" s="40" t="s">
         <v>831</v>
@@ -31773,13 +31899,13 @@
         <v>467</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
       <c r="G37" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H37" s="40" t="s">
-        <v>1032</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="38">
@@ -31788,7 +31914,7 @@
         <v>12</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1033</v>
+        <v>1045</v>
       </c>
       <c r="C38" s="40" t="s">
         <v>463</v>
@@ -31800,13 +31926,13 @@
         <v>467</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
       <c r="G38" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H38" s="40" t="s">
-        <v>1034</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="39">
@@ -31815,7 +31941,7 @@
         <v>13</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="C39" s="40" t="s">
         <v>831</v>
@@ -31824,16 +31950,16 @@
         <v>529</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>1036</v>
+        <v>1048</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
       <c r="G39" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H39" s="40" t="s">
-        <v>1037</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="40">
@@ -31842,7 +31968,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1038</v>
+        <v>1050</v>
       </c>
       <c r="C40" s="40" t="s">
         <v>463</v>
@@ -31860,7 +31986,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="40" t="s">
-        <v>1039</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="41">
@@ -31869,7 +31995,7 @@
         <v>15</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>993</v>
+        <v>1005</v>
       </c>
       <c r="C41" s="40" t="s">
         <v>463</v>
@@ -31887,7 +32013,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="42">
@@ -31896,7 +32022,7 @@
         <v>16</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="C42" s="40" t="s">
         <v>463</v>
@@ -31914,7 +32040,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="40" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="43">
@@ -31923,7 +32049,7 @@
         <v>17</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>995</v>
+        <v>1007</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>463</v>
@@ -31941,7 +32067,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="40" t="s">
-        <v>1042</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="44">
@@ -31950,7 +32076,7 @@
         <v>18</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1043</v>
+        <v>1055</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>463</v>
@@ -31962,13 +32088,13 @@
         <v>467</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="G44" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H44" s="40" t="s">
-        <v>1044</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="45">
@@ -31977,7 +32103,7 @@
         <v>19</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1045</v>
+        <v>1057</v>
       </c>
       <c r="C45" s="40" t="s">
         <v>463</v>
@@ -31989,13 +32115,13 @@
         <v>467</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="G45" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H45" s="40" t="s">
-        <v>1046</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="46">
@@ -32004,7 +32130,7 @@
         <v>20</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1047</v>
+        <v>1059</v>
       </c>
       <c r="C46" s="40" t="s">
         <v>463</v>
@@ -32013,16 +32139,16 @@
         <v>464</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>1048</v>
+        <v>1060</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="G46" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="40" t="s">
-        <v>1049</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="47">
@@ -32031,7 +32157,7 @@
         <v>21</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1050</v>
+        <v>1062</v>
       </c>
       <c r="C47" s="40" t="s">
         <v>463</v>
@@ -32049,7 +32175,7 @@
         <v>0</v>
       </c>
       <c r="H47" s="40" t="s">
-        <v>1051</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="48">
@@ -32058,7 +32184,7 @@
         <v>22</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
       <c r="C48" s="40" t="s">
         <v>463</v>
@@ -32070,13 +32196,13 @@
         <v>467</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="G48" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H48" s="40" t="s">
-        <v>1052</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="49">
@@ -32085,7 +32211,7 @@
         <v>23</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1053</v>
+        <v>1065</v>
       </c>
       <c r="C49" s="40" t="s">
         <v>463</v>
@@ -32097,13 +32223,13 @@
         <v>835</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>1000</v>
+        <v>1012</v>
       </c>
       <c r="G49" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H49" s="40" t="s">
-        <v>1054</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="50">
@@ -32112,7 +32238,7 @@
         <v>24</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1055</v>
+        <v>1067</v>
       </c>
       <c r="C50" s="40" t="s">
         <v>836</v>
@@ -32121,16 +32247,16 @@
         <v>464</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>1056</v>
+        <v>1068</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>1000</v>
+        <v>1012</v>
       </c>
       <c r="G50" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H50" s="40" t="s">
-        <v>1057</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="51">
@@ -32139,7 +32265,7 @@
         <v>25</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1058</v>
+        <v>1070</v>
       </c>
       <c r="C51" s="40" t="s">
         <v>463</v>
@@ -32157,7 +32283,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="40" t="s">
-        <v>1059</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="52">
@@ -32166,7 +32292,7 @@
         <v>26</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1003</v>
+        <v>1015</v>
       </c>
       <c r="C52" s="40" t="s">
         <v>463</v>
@@ -32178,13 +32304,13 @@
         <v>467</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>1000</v>
+        <v>1012</v>
       </c>
       <c r="G52" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="40" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="53">
@@ -32193,7 +32319,7 @@
         <v>27</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1004</v>
+        <v>1016</v>
       </c>
       <c r="C53" s="40" t="s">
         <v>463</v>
@@ -32211,7 +32337,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="40" t="s">
-        <v>1061</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="54">
@@ -32220,7 +32346,7 @@
         <v>28</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
       <c r="C54" s="40" t="s">
         <v>463</v>
@@ -32232,13 +32358,13 @@
         <v>841</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>1006</v>
+        <v>1018</v>
       </c>
       <c r="G54" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H54" s="40" t="s">
-        <v>1062</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="55">
@@ -32247,7 +32373,7 @@
         <v>29</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1007</v>
+        <v>1019</v>
       </c>
       <c r="C55" s="40" t="s">
         <v>463</v>
@@ -32265,7 +32391,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="40" t="s">
-        <v>1063</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="56">
@@ -32274,7 +32400,7 @@
         <v>30</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1064</v>
+        <v>1076</v>
       </c>
       <c r="C56" s="40" t="s">
         <v>463</v>
@@ -32292,7 +32418,7 @@
         <v>0</v>
       </c>
       <c r="H56" s="40" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="57">
@@ -32301,7 +32427,7 @@
         <v>31</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="C57" s="40" t="s">
         <v>463</v>
@@ -32319,7 +32445,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="40" t="s">
-        <v>1067</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="58">
@@ -32328,7 +32454,7 @@
         <v>32</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1068</v>
+        <v>1080</v>
       </c>
       <c r="C58" s="40" t="s">
         <v>463</v>
@@ -32346,7 +32472,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="40" t="s">
-        <v>1069</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="59">
@@ -32355,7 +32481,7 @@
         <v>33</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1070</v>
+        <v>1082</v>
       </c>
       <c r="C59" s="40" t="s">
         <v>463</v>
@@ -32373,7 +32499,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="40" t="s">
-        <v>1071</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="60">
@@ -32382,7 +32508,7 @@
         <v>34</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="C60" s="40" t="s">
         <v>463</v>
@@ -32400,7 +32526,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="40" t="s">
-        <v>1072</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="61">
@@ -32409,7 +32535,7 @@
         <v>35</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1073</v>
+        <v>1085</v>
       </c>
       <c r="C61" s="37" t="s">
         <v>463</v>
@@ -32526,10 +32652,10 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1074</v>
+        <v>1086</v>
       </c>
       <c r="C1" s="56" t="s">
-        <v>1075</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="2">
@@ -32541,7 +32667,7 @@
         <v>701</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>1076</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="3">
@@ -32553,7 +32679,7 @@
         <v>732</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>1077</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="4">
@@ -32562,10 +32688,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1078</v>
+        <v>1090</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>1079</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="6">
@@ -32573,13 +32699,13 @@
         <v>49</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1080</v>
+        <v>1092</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1081</v>
+        <v>1093</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>1013</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="7">
@@ -32588,7 +32714,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1076</v>
+        <v>1088</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>703</v>
@@ -32603,10 +32729,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1082</v>
+        <v>1094</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>1083</v>
+        <v>1095</v>
       </c>
       <c r="D8" s="57" t="s">
         <v>467</v>
@@ -32618,10 +32744,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1084</v>
+        <v>1096</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>1085</v>
+        <v>1097</v>
       </c>
       <c r="D9" s="57" t="s">
         <v>705</v>
@@ -32633,10 +32759,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1086</v>
+        <v>1098</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>1087</v>
+        <v>1099</v>
       </c>
       <c r="D10" s="57" t="s">
         <v>707</v>
@@ -32648,7 +32774,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1079</v>
+        <v>1091</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>703</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -39,7 +39,7 @@
     <definedName name="Interval_Dialog_Options">DIALOGS!$A$25:$H$61</definedName>
     <definedName name="Interval_Memento">EVENTS!$A$43:$F$51</definedName>
     <definedName name="Interval_autoInsertDialog">FN!$A$7:$I$8</definedName>
-    <definedName name="Interval_Sounds">SOUNDS!$A$1:$D$32</definedName>
+    <definedName name="Interval_Sounds">SOUNDS!$A$1:$D$33</definedName>
     <definedName name="Interval_Action_Conditions">ACTION_CONDS!$A$1:$H$61</definedName>
   </definedNames>
   <calcPr/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5579" uniqueCount="1661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5582" uniqueCount="1660">
   <si>
     <t>NewItem</t>
   </si>
@@ -4694,6 +4694,9 @@
     <t>PHRASE_DIALOG_FIK_1_OPTION_2_1</t>
   </si>
   <si>
+    <t>ANIMATION_TRIGGER_TWO</t>
+  </si>
+  <si>
     <t>El que tengo aquí colgado</t>
   </si>
   <si>
@@ -4853,9 +4856,6 @@
     <t>ITEM_GENERIC_DOOR1, ITEM_NPC_FIK</t>
   </si>
   <si>
-    <t>BACKGROUND_CITY1_EXTRAPERLO, BACKGROUND_CITY1_EXTRAPERLO</t>
-  </si>
-  <si>
     <t>ROOM_LAST</t>
   </si>
   <si>
@@ -4916,9 +4916,6 @@
     <t>ANIMATION_TRIGGER_ONE</t>
   </si>
   <si>
-    <t>ANIMATION_TRIGGER_TWO</t>
-  </si>
-  <si>
     <t>ANIMATION_TRIGGER_THREE</t>
   </si>
   <si>
@@ -4931,10 +4928,10 @@
     <t>ANIMATION_TRIGGER_SIX</t>
   </si>
   <si>
-    <t>ANIMATION_TRIGGER_SPECIAL_ONE</t>
-  </si>
-  <si>
-    <t>ANIMATION_TRIGGER_SPECIAL_TWO</t>
+    <t>ANIMATION_TRIGGER_SEVEN</t>
+  </si>
+  <si>
+    <t>ANIMATION_TRIGGER_EIGHT</t>
   </si>
   <si>
     <t>ANIMATION_TRIGGER_WALK_FRONT</t>
@@ -6356,7 +6353,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D32" displayName="Table_sounds" name="Table_sounds" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D33" displayName="Table_sounds" name="Table_sounds" id="12">
   <tableColumns count="4">
     <tableColumn name="N" id="1"/>
     <tableColumn name="SOUND_ID" id="2"/>
@@ -11834,7 +11831,7 @@
         <v>971</v>
       </c>
       <c r="E132" s="44" t="s">
-        <v>1222</v>
+        <v>1530</v>
       </c>
       <c r="F132" s="38" t="s">
         <v>1200</v>
@@ -11843,10 +11840,10 @@
         <v>1199</v>
       </c>
       <c r="H132" s="37" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="I132" s="37" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="133">
@@ -11873,10 +11870,10 @@
         <v>1199</v>
       </c>
       <c r="H133" s="37" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="I133" s="37" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="134">
@@ -11885,7 +11882,7 @@
         <v>132</v>
       </c>
       <c r="B134" s="36" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="C134" s="36">
         <v>1.0</v>
@@ -11903,10 +11900,10 @@
         <v>1199</v>
       </c>
       <c r="H134" s="37" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="I134" s="37" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="135">
@@ -11915,7 +11912,7 @@
         <v>133</v>
       </c>
       <c r="B135" s="36" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="C135" s="36">
         <v>1.0</v>
@@ -11933,10 +11930,10 @@
         <v>1199</v>
       </c>
       <c r="H135" s="37" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="I135" s="37" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="136">
@@ -11945,7 +11942,7 @@
         <v>134</v>
       </c>
       <c r="B136" s="36" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="C136" s="36">
         <v>0.0</v>
@@ -11963,10 +11960,10 @@
         <v>1199</v>
       </c>
       <c r="H136" s="37" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="I136" s="37" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
   </sheetData>
@@ -11991,9 +11988,9 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="25.0"/>
-    <col customWidth="1" min="3" max="3" width="45.71"/>
+    <col customWidth="1" min="3" max="3" width="53.43"/>
     <col customWidth="1" min="4" max="4" width="25.29"/>
-    <col customWidth="1" min="5" max="5" width="41.71"/>
+    <col customWidth="1" min="5" max="5" width="54.71"/>
     <col customWidth="1" min="6" max="6" width="42.0"/>
     <col customWidth="1" min="7" max="7" width="19.86"/>
     <col customWidth="1" min="8" max="8" width="20.86"/>
@@ -12008,34 +12005,34 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="K1" s="63" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="2" ht="186.0" customHeight="1">
@@ -12044,7 +12041,7 @@
         <v>-1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="C2" s="65" t="s">
         <v>323</v>
@@ -12080,7 +12077,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="C3" s="65" t="s">
         <v>871</v>
@@ -12089,10 +12086,10 @@
         <v>956</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>321</v>
@@ -12116,19 +12113,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="D4" s="66" t="s">
         <v>956</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>321</v>
@@ -12152,19 +12149,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="D5" s="66" t="s">
         <v>956</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>321</v>
@@ -12188,19 +12185,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="D6" s="66" t="s">
         <v>956</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>321</v>
@@ -12224,25 +12221,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="D7" s="66" t="s">
+        <v>1565</v>
+      </c>
+      <c r="E7" s="35" t="s">
         <v>1564</v>
       </c>
-      <c r="E7" s="35" t="s">
-        <v>1563</v>
-      </c>
       <c r="F7" s="35" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="I7" s="35" t="s">
         <v>618</v>
@@ -12260,25 +12257,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="I8" s="35" t="s">
         <v>618</v>
@@ -12308,7 +12305,7 @@
         <v>908</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>321</v>
@@ -12332,25 +12329,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="D10" s="66" t="s">
         <v>952</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="I10" s="35" t="s">
         <v>681</v>
@@ -12368,25 +12365,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="D11" s="66" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="I11" s="35" t="s">
         <v>618</v>
@@ -12404,19 +12401,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="D12" s="66" t="s">
         <v>951</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>321</v>
@@ -12440,19 +12437,19 @@
         <v>10</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="D13" s="66" t="s">
         <v>951</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>321</v>
@@ -12479,13 +12476,13 @@
         <v>21</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>1583</v>
+        <v>22</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>939</v>
+        <v>23</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>1583</v>
+        <v>22</v>
       </c>
       <c r="F14" s="35" t="s">
         <v>347</v>
@@ -12938,7 +12935,7 @@
         <v>2</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1604</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="47">
@@ -12947,7 +12944,7 @@
         <v>3</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="48">
@@ -12956,7 +12953,7 @@
         <v>4</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="49">
@@ -12965,7 +12962,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="50">
@@ -12974,7 +12971,7 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="51">
@@ -12983,7 +12980,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="52">
@@ -12992,7 +12989,7 @@
         <v>8</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="53">
@@ -13019,7 +13016,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="56">
@@ -13028,7 +13025,7 @@
         <v>12</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="57">
@@ -13037,7 +13034,7 @@
         <v>13</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="58">
@@ -13046,7 +13043,7 @@
         <v>14</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="59">
@@ -13055,7 +13052,7 @@
         <v>15</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="61">
@@ -13063,7 +13060,7 @@
         <v>49</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="62">
@@ -13116,7 +13113,7 @@
         <v>49</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="69">
@@ -13181,7 +13178,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="2">
@@ -13199,7 +13196,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="4">
@@ -13208,7 +13205,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="5">
@@ -13289,7 +13286,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="14">
@@ -13334,7 +13331,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="19">
@@ -13478,7 +13475,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="36">
@@ -13486,16 +13483,16 @@
         <v>49</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="C36" s="68" t="s">
         <v>312</v>
       </c>
       <c r="D36" s="68" t="s">
+        <v>1624</v>
+      </c>
+      <c r="E36" s="68" t="s">
         <v>1625</v>
-      </c>
-      <c r="E36" s="68" t="s">
-        <v>1626</v>
       </c>
     </row>
     <row r="37">
@@ -13504,7 +13501,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="C37" s="38" t="s">
         <v>321</v>
@@ -13523,7 +13520,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="C38" s="38" t="s">
         <v>1130</v>
@@ -13542,7 +13539,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="C39" s="38" t="s">
         <v>1161</v>
@@ -13580,7 +13577,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>454</v>
@@ -13598,19 +13595,19 @@
         <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C43" s="67" t="s">
         <v>1631</v>
-      </c>
-      <c r="C43" s="67" t="s">
-        <v>1632</v>
       </c>
       <c r="D43" s="67" t="s">
         <v>1093</v>
       </c>
       <c r="E43" s="68" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F43" s="67" t="s">
         <v>1633</v>
-      </c>
-      <c r="F43" s="67" t="s">
-        <v>1634</v>
       </c>
     </row>
     <row r="44">
@@ -13622,13 +13619,13 @@
         <v>700</v>
       </c>
       <c r="C44" s="44" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="D44" s="44" t="s">
         <v>703</v>
       </c>
       <c r="E44" s="48" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="F44" s="43" t="b">
         <v>0</v>
@@ -13643,13 +13640,13 @@
         <v>712</v>
       </c>
       <c r="C45" s="44" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="D45" s="44" t="s">
         <v>1241</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="F45" s="43" t="b">
         <v>0</v>
@@ -13664,13 +13661,13 @@
         <v>729</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="D46" s="44" t="s">
         <v>749</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="F46" s="43" t="b">
         <v>0</v>
@@ -13685,13 +13682,13 @@
         <v>734</v>
       </c>
       <c r="C47" s="44" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="D47" s="44" t="s">
         <v>1343</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="F47" s="43" t="b">
         <v>0</v>
@@ -13712,7 +13709,7 @@
         <v>1416</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="F48" s="43" t="b">
         <v>0</v>
@@ -13724,7 +13721,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>44</v>
@@ -13733,7 +13730,7 @@
         <v>1419</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="F49" s="43" t="b">
         <v>0</v>
@@ -13745,7 +13742,7 @@
         <v>6</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>44</v>
@@ -13754,7 +13751,7 @@
         <v>1422</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="F50" s="43" t="b">
         <v>1</v>
@@ -13766,16 +13763,16 @@
         <v>7</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="D51" s="44" t="s">
         <v>703</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="F51" s="43" t="b">
         <v>0</v>
@@ -13786,10 +13783,10 @@
         <v>49</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C53" s="28" t="s">
         <v>1639</v>
-      </c>
-      <c r="C53" s="28" t="s">
-        <v>1640</v>
       </c>
     </row>
     <row r="54">
@@ -13798,7 +13795,7 @@
         <v>0</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C54" s="51" t="s">
         <v>463</v>
@@ -13809,7 +13806,7 @@
         <v>49</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="57">
@@ -14819,16 +14816,16 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1642</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1643</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1644</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="2">
@@ -14840,7 +14837,7 @@
         <v>324</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="D2" s="70" t="s">
         <v>321</v>
@@ -14858,7 +14855,7 @@
         <v>440</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="D3" s="70" t="s">
         <v>321</v>
@@ -14873,10 +14870,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="D4" s="70" t="s">
         <v>321</v>
@@ -14941,7 +14938,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
     </row>
   </sheetData>
@@ -14967,21 +14964,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1650</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1651</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1652</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1653</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B2" s="71">
         <v>5.0</v>
@@ -14995,7 +14992,7 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="B3" s="71">
         <v>4.0</v>
@@ -15009,7 +15006,7 @@
     </row>
     <row r="4">
       <c r="A4" s="37" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="B4" s="71">
         <v>2.0</v>
@@ -15023,7 +15020,7 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="B5" s="71">
         <v>5.0</v>
@@ -15037,7 +15034,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="B6" s="71">
         <v>4.0</v>
@@ -15051,7 +15048,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="B7" s="71">
         <v>4.0</v>
@@ -15065,7 +15062,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="B8" s="71">
         <v>2.0</v>
@@ -31182,9 +31179,24 @@
         <v>30</v>
       </c>
       <c r="B32" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>940</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>31</v>
+      </c>
+      <c r="B33" s="36" t="s">
         <v>987</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C33" s="36" t="s">
         <v>940</v>
       </c>
     </row>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -39,7 +39,7 @@
     <definedName name="Interval_Dialog_Options">DIALOGS!$A$27:$H$68</definedName>
     <definedName name="Interval_Memento">EVENTS!$A$44:$F$52</definedName>
     <definedName name="Interval_autoInsertDialog">FN!$A$7:$I$8</definedName>
-    <definedName name="Interval_Sounds">SOUNDS!$A$1:$D$46</definedName>
+    <definedName name="Interval_Sounds">SOUNDS!$A$1:$D$47</definedName>
     <definedName name="Interval_Action_Conditions">ACTION_CONDS!$A$1:$H$62</definedName>
   </definedNames>
   <calcPr/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6034" uniqueCount="1753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6037" uniqueCount="1754">
   <si>
     <t>NewItem</t>
   </si>
@@ -3224,6 +3224,9 @@
     <t>SOUND_AMBIENCE_INSIDE_PUB</t>
   </si>
   <si>
+    <t>SOUND_AMBIENCE_OUTSIDE_PUB</t>
+  </si>
+  <si>
     <t>SOUND_LAST</t>
   </si>
   <si>
@@ -5135,7 +5138,7 @@
     <t>ITEM_GENERIC_DOOR1, ITEM_NPC_FIK, ITEM_DOOR_EXTRAPERLO, ITEM_FOREGROUND_EXTRP_WALL, ITEM_DOOR_EXTRAPERLO_REAL</t>
   </si>
   <si>
-    <t>MUSIC_SOUTH_NEIGH, SOUND_AMBIENCE_INSIDE_PUB, SOUND_AMBIENCE_CITY_NIGHT</t>
+    <t>MUSIC_SOUTH_NEIGH, SOUND_AMBIENCE_CITY_NIGHT, SOUND_AMBIENCE_OUTSIDE_PUB</t>
   </si>
   <si>
     <t>BACKGROUND_CITY1_EXTRAPERLO, SPRITE_EXTRAPERLO_BAR_FOREGROUND</t>
@@ -6633,7 +6636,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D46" displayName="Table_sounds" name="Table_sounds" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D47" displayName="Table_sounds" name="Table_sounds" id="12">
   <tableColumns count="4">
     <tableColumn name="N" id="1"/>
     <tableColumn name="SOUND_ID" id="2"/>
@@ -7479,13 +7482,13 @@
         <v>49</v>
       </c>
       <c r="B1" s="59" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="2">
@@ -7508,10 +7511,10 @@
         <v>327</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="4">
@@ -7520,13 +7523,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="5">
@@ -7535,13 +7538,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="6">
@@ -7550,13 +7553,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="7">
@@ -7568,10 +7571,10 @@
         <v>330</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="8">
@@ -7583,10 +7586,10 @@
         <v>351</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="9">
@@ -7598,10 +7601,10 @@
         <v>358</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="10">
@@ -7613,10 +7616,10 @@
         <v>336</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="11">
@@ -7625,13 +7628,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="12">
@@ -7640,13 +7643,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="13">
@@ -7658,10 +7661,10 @@
         <v>341</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="14">
@@ -7673,10 +7676,10 @@
         <v>348</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="15">
@@ -7685,13 +7688,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="16">
@@ -7703,10 +7706,10 @@
         <v>361</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="17">
@@ -7718,10 +7721,10 @@
         <v>366</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="18">
@@ -7733,10 +7736,10 @@
         <v>369</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="19">
@@ -7748,10 +7751,10 @@
         <v>373</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="20">
@@ -7763,10 +7766,10 @@
         <v>376</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="21">
@@ -7778,10 +7781,10 @@
         <v>379</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="22">
@@ -7793,10 +7796,10 @@
         <v>381</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="23">
@@ -7808,10 +7811,10 @@
         <v>383</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="24">
@@ -7823,10 +7826,10 @@
         <v>385</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="25">
@@ -7838,10 +7841,10 @@
         <v>388</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="26">
@@ -7853,10 +7856,10 @@
         <v>392</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="27">
@@ -7868,10 +7871,10 @@
         <v>397</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="28">
@@ -7883,10 +7886,10 @@
         <v>399</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="29">
@@ -7898,10 +7901,10 @@
         <v>403</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="30">
@@ -7910,13 +7913,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="31">
@@ -7928,10 +7931,10 @@
         <v>407</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="32">
@@ -7943,10 +7946,10 @@
         <v>409</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="33">
@@ -7955,13 +7958,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="34">
@@ -7973,10 +7976,10 @@
         <v>413</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="35">
@@ -7988,10 +7991,10 @@
         <v>417</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="36">
@@ -8003,10 +8006,10 @@
         <v>420</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="37">
@@ -8018,10 +8021,10 @@
         <v>425</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="38">
@@ -8033,10 +8036,10 @@
         <v>430</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="39">
@@ -8048,10 +8051,10 @@
         <v>434</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="40">
@@ -8063,10 +8066,10 @@
         <v>438</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="41">
@@ -8078,10 +8081,10 @@
         <v>442</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="42">
@@ -8093,10 +8096,10 @@
         <v>445</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="43">
@@ -8108,10 +8111,10 @@
         <v>11</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="44">
@@ -8123,10 +8126,10 @@
         <v>450</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="45">
@@ -8138,10 +8141,10 @@
         <v>458</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="46">
@@ -8153,10 +8156,10 @@
         <v>464</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
   </sheetData>
@@ -8191,28 +8194,28 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="I1" s="61" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="2">
@@ -8256,7 +8259,7 @@
         <v>1026</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>724</v>
@@ -8265,10 +8268,10 @@
         <v>724</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="I3" s="37" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="4">
@@ -8286,7 +8289,7 @@
         <v>1028</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F4" s="38" t="s">
         <v>724</v>
@@ -8295,10 +8298,10 @@
         <v>724</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="5">
@@ -8316,7 +8319,7 @@
         <v>1030</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F5" s="38" t="s">
         <v>724</v>
@@ -8325,10 +8328,10 @@
         <v>724</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="I5" s="37" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="6">
@@ -8337,7 +8340,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C6" s="36">
         <v>0.0</v>
@@ -8346,7 +8349,7 @@
         <v>968</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>724</v>
@@ -8355,10 +8358,10 @@
         <v>724</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="I6" s="37" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="7">
@@ -8367,7 +8370,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C7" s="36">
         <v>0.0</v>
@@ -8376,7 +8379,7 @@
         <v>968</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F7" s="38" t="s">
         <v>724</v>
@@ -8385,10 +8388,10 @@
         <v>724</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="8">
@@ -8406,7 +8409,7 @@
         <v>968</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>724</v>
@@ -8415,10 +8418,10 @@
         <v>724</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="I8" s="37" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="9">
@@ -8427,7 +8430,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C9" s="36">
         <v>0.0</v>
@@ -8436,7 +8439,7 @@
         <v>968</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F9" s="38" t="s">
         <v>724</v>
@@ -8445,10 +8448,10 @@
         <v>724</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="I9" s="37" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="10">
@@ -8457,7 +8460,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C10" s="36">
         <v>0.0</v>
@@ -8466,7 +8469,7 @@
         <v>968</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F10" s="38" t="s">
         <v>724</v>
@@ -8475,10 +8478,10 @@
         <v>724</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="11">
@@ -8487,7 +8490,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C11" s="36">
         <v>1.0</v>
@@ -8496,19 +8499,19 @@
         <v>968</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G11" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="I11" s="37" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="12">
@@ -8517,7 +8520,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="C12" s="36">
         <v>0.0</v>
@@ -8526,7 +8529,7 @@
         <v>968</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>724</v>
@@ -8535,10 +8538,10 @@
         <v>724</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="13">
@@ -8547,7 +8550,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="C13" s="36">
         <v>0.0</v>
@@ -8556,7 +8559,7 @@
         <v>968</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>724</v>
@@ -8565,10 +8568,10 @@
         <v>724</v>
       </c>
       <c r="H13" s="37" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="I13" s="37" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="14">
@@ -8577,7 +8580,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="C14" s="36">
         <v>1.0</v>
@@ -8586,19 +8589,19 @@
         <v>968</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G14" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="15">
@@ -8607,7 +8610,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="C15" s="36">
         <v>1.0</v>
@@ -8616,19 +8619,19 @@
         <v>968</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G15" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="16">
@@ -8637,7 +8640,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C16" s="36">
         <v>0.0</v>
@@ -8646,7 +8649,7 @@
         <v>968</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>724</v>
@@ -8655,10 +8658,10 @@
         <v>724</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="17">
@@ -8667,7 +8670,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C17" s="36">
         <v>0.0</v>
@@ -8676,7 +8679,7 @@
         <v>968</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>724</v>
@@ -8685,10 +8688,10 @@
         <v>724</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="I17" s="37" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="18">
@@ -8697,7 +8700,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="C18" s="36">
         <v>0.0</v>
@@ -8706,7 +8709,7 @@
         <v>968</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>724</v>
@@ -8715,10 +8718,10 @@
         <v>724</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="19">
@@ -8736,7 +8739,7 @@
         <v>968</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F19" s="38" t="s">
         <v>724</v>
@@ -8745,10 +8748,10 @@
         <v>724</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="20">
@@ -8766,7 +8769,7 @@
         <v>968</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F20" s="38" t="s">
         <v>724</v>
@@ -8775,10 +8778,10 @@
         <v>724</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="21">
@@ -8796,7 +8799,7 @@
         <v>968</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F21" s="38" t="s">
         <v>724</v>
@@ -8805,10 +8808,10 @@
         <v>724</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="22">
@@ -8826,7 +8829,7 @@
         <v>968</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F22" s="38" t="s">
         <v>724</v>
@@ -8835,10 +8838,10 @@
         <v>724</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="23">
@@ -8856,7 +8859,7 @@
         <v>968</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F23" s="38" t="s">
         <v>724</v>
@@ -8865,10 +8868,10 @@
         <v>724</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="24">
@@ -8886,7 +8889,7 @@
         <v>968</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F24" s="38" t="s">
         <v>724</v>
@@ -8895,10 +8898,10 @@
         <v>724</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="25">
@@ -8916,7 +8919,7 @@
         <v>968</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F25" s="38" t="s">
         <v>724</v>
@@ -8925,10 +8928,10 @@
         <v>724</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="26">
@@ -8946,7 +8949,7 @@
         <v>968</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F26" s="38" t="s">
         <v>724</v>
@@ -8955,10 +8958,10 @@
         <v>724</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="27">
@@ -8967,7 +8970,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C27" s="36">
         <v>0.0</v>
@@ -8976,7 +8979,7 @@
         <v>968</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F27" s="38" t="s">
         <v>724</v>
@@ -8985,10 +8988,10 @@
         <v>724</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="I27" s="37" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="28">
@@ -8997,7 +9000,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C28" s="36">
         <v>1.0</v>
@@ -9006,19 +9009,19 @@
         <v>968</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G28" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="29">
@@ -9027,7 +9030,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C29" s="36">
         <v>0.0</v>
@@ -9036,7 +9039,7 @@
         <v>968</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>724</v>
@@ -9045,10 +9048,10 @@
         <v>724</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="30">
@@ -9057,7 +9060,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C30" s="36">
         <v>0.0</v>
@@ -9066,7 +9069,7 @@
         <v>968</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F30" s="38" t="s">
         <v>724</v>
@@ -9075,10 +9078,10 @@
         <v>724</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="31">
@@ -9087,7 +9090,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="C31" s="36">
         <v>0.0</v>
@@ -9096,7 +9099,7 @@
         <v>968</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>724</v>
@@ -9105,10 +9108,10 @@
         <v>724</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="32">
@@ -9126,7 +9129,7 @@
         <v>968</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F32" s="38" t="s">
         <v>724</v>
@@ -9135,10 +9138,10 @@
         <v>724</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="33">
@@ -9147,7 +9150,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C33" s="36">
         <v>0.0</v>
@@ -9156,7 +9159,7 @@
         <v>968</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F33" s="38" t="s">
         <v>724</v>
@@ -9165,10 +9168,10 @@
         <v>724</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="34">
@@ -9177,7 +9180,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C34" s="36">
         <v>1.0</v>
@@ -9186,19 +9189,19 @@
         <v>968</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G34" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="35">
@@ -9207,7 +9210,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="C35" s="36">
         <v>1.0</v>
@@ -9216,19 +9219,19 @@
         <v>968</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G35" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="36">
@@ -9246,7 +9249,7 @@
         <v>968</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F36" s="38" t="s">
         <v>724</v>
@@ -9255,10 +9258,10 @@
         <v>724</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="37">
@@ -9267,7 +9270,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="C37" s="36">
         <v>0.0</v>
@@ -9276,7 +9279,7 @@
         <v>968</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F37" s="38" t="s">
         <v>724</v>
@@ -9285,10 +9288,10 @@
         <v>724</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="38">
@@ -9297,7 +9300,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="C38" s="36">
         <v>1.0</v>
@@ -9306,19 +9309,19 @@
         <v>968</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G38" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="39">
@@ -9327,7 +9330,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="C39" s="36">
         <v>0.0</v>
@@ -9336,7 +9339,7 @@
         <v>968</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F39" s="38" t="s">
         <v>724</v>
@@ -9345,10 +9348,10 @@
         <v>724</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="I39" s="37" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="40">
@@ -9357,7 +9360,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="C40" s="36">
         <v>1.0</v>
@@ -9366,19 +9369,19 @@
         <v>968</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G40" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="41">
@@ -9387,7 +9390,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="C41" s="36">
         <v>0.0</v>
@@ -9396,7 +9399,7 @@
         <v>968</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F41" s="38" t="s">
         <v>724</v>
@@ -9405,10 +9408,10 @@
         <v>724</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="42">
@@ -9417,7 +9420,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="C42" s="36">
         <v>1.0</v>
@@ -9426,19 +9429,19 @@
         <v>968</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G42" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="43">
@@ -9447,7 +9450,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="C43" s="36">
         <v>0.0</v>
@@ -9456,7 +9459,7 @@
         <v>968</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F43" s="38" t="s">
         <v>724</v>
@@ -9465,10 +9468,10 @@
         <v>724</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="44">
@@ -9477,7 +9480,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="C44" s="36">
         <v>1.0</v>
@@ -9486,19 +9489,19 @@
         <v>968</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G44" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="45">
@@ -9507,7 +9510,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="C45" s="36">
         <v>0.0</v>
@@ -9516,7 +9519,7 @@
         <v>968</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F45" s="38" t="s">
         <v>724</v>
@@ -9525,10 +9528,10 @@
         <v>724</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="46">
@@ -9537,7 +9540,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="C46" s="36">
         <v>1.0</v>
@@ -9546,19 +9549,19 @@
         <v>968</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G46" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="47">
@@ -9567,7 +9570,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="C47" s="36">
         <v>1.0</v>
@@ -9576,19 +9579,19 @@
         <v>968</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G47" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H47" s="37" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="I47" s="37" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="48">
@@ -9597,7 +9600,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="C48" s="36">
         <v>0.0</v>
@@ -9606,7 +9609,7 @@
         <v>968</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F48" s="38" t="s">
         <v>724</v>
@@ -9615,10 +9618,10 @@
         <v>724</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="49">
@@ -9627,7 +9630,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="C49" s="36">
         <v>1.0</v>
@@ -9636,19 +9639,19 @@
         <v>968</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G49" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="I49" s="37" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="50">
@@ -9657,7 +9660,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="C50" s="36">
         <v>0.0</v>
@@ -9666,7 +9669,7 @@
         <v>968</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F50" s="38" t="s">
         <v>724</v>
@@ -9675,10 +9678,10 @@
         <v>724</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="I50" s="37" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="51">
@@ -9687,7 +9690,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="C51" s="36">
         <v>0.0</v>
@@ -9696,7 +9699,7 @@
         <v>968</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F51" s="38" t="s">
         <v>724</v>
@@ -9705,10 +9708,10 @@
         <v>724</v>
       </c>
       <c r="H51" s="37" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="I51" s="37" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="52">
@@ -9717,7 +9720,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="C52" s="36">
         <v>1.0</v>
@@ -9726,19 +9729,19 @@
         <v>968</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G52" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H52" s="37" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="I52" s="37" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="53">
@@ -9747,7 +9750,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="C53" s="36">
         <v>1.0</v>
@@ -9756,19 +9759,19 @@
         <v>968</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G53" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="54">
@@ -9777,7 +9780,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="C54" s="36">
         <v>1.0</v>
@@ -9786,19 +9789,19 @@
         <v>968</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G54" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="I54" s="37" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="55">
@@ -9807,7 +9810,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="C55" s="36">
         <v>0.0</v>
@@ -9816,7 +9819,7 @@
         <v>968</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F55" s="38" t="s">
         <v>724</v>
@@ -9825,10 +9828,10 @@
         <v>724</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="56">
@@ -9837,7 +9840,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C56" s="36">
         <v>0.0</v>
@@ -9846,7 +9849,7 @@
         <v>968</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F56" s="38" t="s">
         <v>724</v>
@@ -9855,10 +9858,10 @@
         <v>724</v>
       </c>
       <c r="H56" s="37" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="I56" s="37" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="57">
@@ -9867,7 +9870,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="C57" s="36">
         <v>0.0</v>
@@ -9876,7 +9879,7 @@
         <v>968</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F57" s="38" t="s">
         <v>724</v>
@@ -9885,10 +9888,10 @@
         <v>724</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="58">
@@ -9897,7 +9900,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C58" s="36">
         <v>1.0</v>
@@ -9906,19 +9909,19 @@
         <v>968</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G58" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="59">
@@ -9936,7 +9939,7 @@
         <v>968</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F59" s="38" t="s">
         <v>724</v>
@@ -9945,10 +9948,10 @@
         <v>724</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="I59" s="37" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="60">
@@ -9957,7 +9960,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="C60" s="36">
         <v>0.0</v>
@@ -9975,10 +9978,10 @@
         <v>724</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="61">
@@ -9987,7 +9990,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="C61" s="36">
         <v>0.0</v>
@@ -10005,10 +10008,10 @@
         <v>724</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="I61" s="37" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="62">
@@ -10017,7 +10020,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="C62" s="36">
         <v>0.0</v>
@@ -10035,10 +10038,10 @@
         <v>724</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="63">
@@ -10056,7 +10059,7 @@
         <v>968</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F63" s="38" t="s">
         <v>724</v>
@@ -10065,10 +10068,10 @@
         <v>724</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="I63" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="64">
@@ -10077,7 +10080,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="C64" s="36">
         <v>0.0</v>
@@ -10086,7 +10089,7 @@
         <v>975</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F64" s="38" t="s">
         <v>724</v>
@@ -10095,10 +10098,10 @@
         <v>724</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="I64" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="65">
@@ -10107,7 +10110,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="C65" s="36">
         <v>0.0</v>
@@ -10116,7 +10119,7 @@
         <v>976</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F65" s="38" t="s">
         <v>724</v>
@@ -10125,10 +10128,10 @@
         <v>724</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="I65" s="37" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="66">
@@ -10137,7 +10140,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C66" s="36">
         <v>0.0</v>
@@ -10146,7 +10149,7 @@
         <v>977</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F66" s="38" t="s">
         <v>724</v>
@@ -10155,10 +10158,10 @@
         <v>724</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="I66" s="37" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="67">
@@ -10167,7 +10170,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="C67" s="36">
         <v>0.0</v>
@@ -10176,7 +10179,7 @@
         <v>978</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F67" s="38" t="s">
         <v>724</v>
@@ -10185,10 +10188,10 @@
         <v>724</v>
       </c>
       <c r="H67" s="37" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="I67" s="37" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="68">
@@ -10197,7 +10200,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="C68" s="36">
         <v>0.0</v>
@@ -10206,7 +10209,7 @@
         <v>968</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F68" s="38" t="s">
         <v>724</v>
@@ -10215,10 +10218,10 @@
         <v>724</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="I68" s="37" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="69">
@@ -10227,7 +10230,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C69" s="36">
         <v>1.0</v>
@@ -10236,19 +10239,19 @@
         <v>968</v>
       </c>
       <c r="E69" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F69" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G69" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H69" s="37" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="I69" s="37" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="70">
@@ -10257,7 +10260,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="C70" s="36">
         <v>0.0</v>
@@ -10266,7 +10269,7 @@
         <v>968</v>
       </c>
       <c r="E70" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F70" s="38" t="s">
         <v>724</v>
@@ -10275,10 +10278,10 @@
         <v>724</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="I70" s="37" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="71">
@@ -10287,7 +10290,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="C71" s="36">
         <v>1.0</v>
@@ -10296,19 +10299,19 @@
         <v>968</v>
       </c>
       <c r="E71" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G71" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H71" s="37" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="I71" s="37" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="72">
@@ -10317,7 +10320,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="C72" s="36">
         <v>0.0</v>
@@ -10326,7 +10329,7 @@
         <v>968</v>
       </c>
       <c r="E72" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F72" s="38" t="s">
         <v>724</v>
@@ -10335,10 +10338,10 @@
         <v>724</v>
       </c>
       <c r="H72" s="37" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="I72" s="37" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="73">
@@ -10347,7 +10350,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="C73" s="36">
         <v>1.0</v>
@@ -10356,19 +10359,19 @@
         <v>968</v>
       </c>
       <c r="E73" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F73" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G73" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H73" s="37" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="I73" s="37" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="74">
@@ -10377,7 +10380,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C74" s="36">
         <v>0.0</v>
@@ -10386,7 +10389,7 @@
         <v>968</v>
       </c>
       <c r="E74" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F74" s="38" t="s">
         <v>724</v>
@@ -10395,10 +10398,10 @@
         <v>724</v>
       </c>
       <c r="H74" s="37" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="I74" s="37" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="75">
@@ -10407,7 +10410,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="C75" s="36">
         <v>1.0</v>
@@ -10416,19 +10419,19 @@
         <v>968</v>
       </c>
       <c r="E75" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F75" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G75" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H75" s="37" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="I75" s="37" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="76">
@@ -10437,7 +10440,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="C76" s="36">
         <v>0.0</v>
@@ -10446,7 +10449,7 @@
         <v>968</v>
       </c>
       <c r="E76" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F76" s="38" t="s">
         <v>724</v>
@@ -10455,10 +10458,10 @@
         <v>724</v>
       </c>
       <c r="H76" s="37" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="I76" s="37" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="77">
@@ -10467,7 +10470,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="C77" s="36">
         <v>1.0</v>
@@ -10476,19 +10479,19 @@
         <v>968</v>
       </c>
       <c r="E77" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F77" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G77" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H77" s="37" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="I77" s="37" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="78">
@@ -10497,7 +10500,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="C78" s="36">
         <v>0.0</v>
@@ -10506,7 +10509,7 @@
         <v>968</v>
       </c>
       <c r="E78" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F78" s="38" t="s">
         <v>724</v>
@@ -10515,10 +10518,10 @@
         <v>724</v>
       </c>
       <c r="H78" s="37" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="I78" s="37" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="79">
@@ -10527,7 +10530,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C79" s="36">
         <v>0.0</v>
@@ -10536,7 +10539,7 @@
         <v>968</v>
       </c>
       <c r="E79" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F79" s="38" t="s">
         <v>724</v>
@@ -10545,10 +10548,10 @@
         <v>724</v>
       </c>
       <c r="H79" s="37" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="I79" s="37" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="80">
@@ -10557,7 +10560,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="C80" s="36">
         <v>1.0</v>
@@ -10566,19 +10569,19 @@
         <v>968</v>
       </c>
       <c r="E80" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F80" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G80" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H80" s="37" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="I80" s="37" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="81">
@@ -10587,7 +10590,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="C81" s="36">
         <v>1.0</v>
@@ -10596,19 +10599,19 @@
         <v>968</v>
       </c>
       <c r="E81" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F81" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G81" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H81" s="37" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="I81" s="37" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="82">
@@ -10617,7 +10620,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C82" s="36">
         <v>1.0</v>
@@ -10626,19 +10629,19 @@
         <v>968</v>
       </c>
       <c r="E82" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F82" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G82" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H82" s="37" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="I82" s="37" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="83">
@@ -10647,7 +10650,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C83" s="36">
         <v>0.0</v>
@@ -10656,7 +10659,7 @@
         <v>968</v>
       </c>
       <c r="E83" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F83" s="38" t="s">
         <v>724</v>
@@ -10665,10 +10668,10 @@
         <v>724</v>
       </c>
       <c r="H83" s="37" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="I83" s="37" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="84">
@@ -10677,7 +10680,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="C84" s="36">
         <v>0.0</v>
@@ -10686,7 +10689,7 @@
         <v>968</v>
       </c>
       <c r="E84" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F84" s="38" t="s">
         <v>724</v>
@@ -10695,10 +10698,10 @@
         <v>724</v>
       </c>
       <c r="H84" s="37" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="I84" s="37" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="85">
@@ -10707,7 +10710,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="36" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="C85" s="36">
         <v>0.0</v>
@@ -10716,7 +10719,7 @@
         <v>968</v>
       </c>
       <c r="E85" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F85" s="38" t="s">
         <v>724</v>
@@ -10725,10 +10728,10 @@
         <v>724</v>
       </c>
       <c r="H85" s="37" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="I85" s="37" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="86">
@@ -10746,7 +10749,7 @@
         <v>968</v>
       </c>
       <c r="E86" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F86" s="38" t="s">
         <v>724</v>
@@ -10755,10 +10758,10 @@
         <v>724</v>
       </c>
       <c r="H86" s="37" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="I86" s="37" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="87">
@@ -10776,7 +10779,7 @@
         <v>968</v>
       </c>
       <c r="E87" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F87" s="38" t="s">
         <v>724</v>
@@ -10785,10 +10788,10 @@
         <v>724</v>
       </c>
       <c r="H87" s="37" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="I87" s="37" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="88">
@@ -10806,7 +10809,7 @@
         <v>968</v>
       </c>
       <c r="E88" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F88" s="38" t="s">
         <v>724</v>
@@ -10815,10 +10818,10 @@
         <v>724</v>
       </c>
       <c r="H88" s="37" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="I88" s="37" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="89">
@@ -10836,7 +10839,7 @@
         <v>968</v>
       </c>
       <c r="E89" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F89" s="38" t="s">
         <v>724</v>
@@ -10845,10 +10848,10 @@
         <v>724</v>
       </c>
       <c r="H89" s="37" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="I89" s="37" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="90">
@@ -10866,7 +10869,7 @@
         <v>968</v>
       </c>
       <c r="E90" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F90" s="38" t="s">
         <v>724</v>
@@ -10875,10 +10878,10 @@
         <v>724</v>
       </c>
       <c r="H90" s="37" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="I90" s="37" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="91">
@@ -10896,7 +10899,7 @@
         <v>968</v>
       </c>
       <c r="E91" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F91" s="38" t="s">
         <v>724</v>
@@ -10905,10 +10908,10 @@
         <v>724</v>
       </c>
       <c r="H91" s="37" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="I91" s="37" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="92">
@@ -10926,7 +10929,7 @@
         <v>968</v>
       </c>
       <c r="E92" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F92" s="38" t="s">
         <v>724</v>
@@ -10935,10 +10938,10 @@
         <v>724</v>
       </c>
       <c r="H92" s="37" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="I92" s="37" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="93">
@@ -10956,7 +10959,7 @@
         <v>968</v>
       </c>
       <c r="E93" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F93" s="38" t="s">
         <v>724</v>
@@ -10965,10 +10968,10 @@
         <v>724</v>
       </c>
       <c r="H93" s="37" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="I93" s="37" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="94">
@@ -10986,7 +10989,7 @@
         <v>968</v>
       </c>
       <c r="E94" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F94" s="38" t="s">
         <v>724</v>
@@ -10995,10 +10998,10 @@
         <v>724</v>
       </c>
       <c r="H94" s="37" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="I94" s="37" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="95">
@@ -11016,7 +11019,7 @@
         <v>973</v>
       </c>
       <c r="E95" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F95" s="38" t="s">
         <v>724</v>
@@ -11025,10 +11028,10 @@
         <v>724</v>
       </c>
       <c r="H95" s="37" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="I95" s="37" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="96">
@@ -11046,7 +11049,7 @@
         <v>968</v>
       </c>
       <c r="E96" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F96" s="38" t="s">
         <v>724</v>
@@ -11055,10 +11058,10 @@
         <v>724</v>
       </c>
       <c r="H96" s="37" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="I96" s="37" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="97">
@@ -11076,7 +11079,7 @@
         <v>968</v>
       </c>
       <c r="E97" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F97" s="38" t="s">
         <v>724</v>
@@ -11085,10 +11088,10 @@
         <v>724</v>
       </c>
       <c r="H97" s="37" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="I97" s="37" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="98">
@@ -11106,7 +11109,7 @@
         <v>968</v>
       </c>
       <c r="E98" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F98" s="38" t="s">
         <v>724</v>
@@ -11115,10 +11118,10 @@
         <v>724</v>
       </c>
       <c r="H98" s="37" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="I98" s="37" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="99">
@@ -11145,10 +11148,10 @@
         <v>724</v>
       </c>
       <c r="H99" s="37" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="I99" s="37" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="100">
@@ -11166,7 +11169,7 @@
         <v>968</v>
       </c>
       <c r="E100" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F100" s="38" t="s">
         <v>724</v>
@@ -11175,10 +11178,10 @@
         <v>724</v>
       </c>
       <c r="H100" s="37" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="I100" s="37" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="101">
@@ -11196,7 +11199,7 @@
         <v>968</v>
       </c>
       <c r="E101" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F101" s="38" t="s">
         <v>724</v>
@@ -11205,10 +11208,10 @@
         <v>724</v>
       </c>
       <c r="H101" s="37" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="I101" s="37" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="102">
@@ -11226,7 +11229,7 @@
         <v>968</v>
       </c>
       <c r="E102" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F102" s="38" t="s">
         <v>724</v>
@@ -11235,10 +11238,10 @@
         <v>724</v>
       </c>
       <c r="H102" s="37" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="I102" s="37" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="103">
@@ -11247,7 +11250,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="36" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="C103" s="36">
         <v>0.0</v>
@@ -11256,7 +11259,7 @@
         <v>968</v>
       </c>
       <c r="E103" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F103" s="38" t="s">
         <v>724</v>
@@ -11265,10 +11268,10 @@
         <v>724</v>
       </c>
       <c r="H103" s="37" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="I103" s="37" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="104">
@@ -11277,7 +11280,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="C104" s="36">
         <v>1.0</v>
@@ -11286,19 +11289,19 @@
         <v>968</v>
       </c>
       <c r="E104" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F104" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G104" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H104" s="37" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="I104" s="37" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="105">
@@ -11307,7 +11310,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="C105" s="36">
         <v>0.0</v>
@@ -11316,7 +11319,7 @@
         <v>968</v>
       </c>
       <c r="E105" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F105" s="38" t="s">
         <v>724</v>
@@ -11325,10 +11328,10 @@
         <v>724</v>
       </c>
       <c r="H105" s="37" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="I105" s="37" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="106">
@@ -11337,7 +11340,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="C106" s="36">
         <v>1.0</v>
@@ -11346,19 +11349,19 @@
         <v>968</v>
       </c>
       <c r="E106" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F106" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G106" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H106" s="37" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="I106" s="37" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="107">
@@ -11367,7 +11370,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="C107" s="36">
         <v>0.0</v>
@@ -11376,7 +11379,7 @@
         <v>968</v>
       </c>
       <c r="E107" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F107" s="38" t="s">
         <v>724</v>
@@ -11385,10 +11388,10 @@
         <v>724</v>
       </c>
       <c r="H107" s="37" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="I107" s="37" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="108">
@@ -11397,7 +11400,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="C108" s="36">
         <v>1.0</v>
@@ -11406,19 +11409,19 @@
         <v>968</v>
       </c>
       <c r="E108" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F108" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G108" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H108" s="37" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="I108" s="37" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="109">
@@ -11427,7 +11430,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="C109" s="36">
         <v>0.0</v>
@@ -11436,7 +11439,7 @@
         <v>968</v>
       </c>
       <c r="E109" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F109" s="38" t="s">
         <v>724</v>
@@ -11445,10 +11448,10 @@
         <v>724</v>
       </c>
       <c r="H109" s="37" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="I109" s="37" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="110">
@@ -11457,7 +11460,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="C110" s="36">
         <v>1.0</v>
@@ -11466,19 +11469,19 @@
         <v>968</v>
       </c>
       <c r="E110" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F110" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G110" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H110" s="37" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="I110" s="37" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="111">
@@ -11487,7 +11490,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="C111" s="36">
         <v>0.0</v>
@@ -11496,7 +11499,7 @@
         <v>968</v>
       </c>
       <c r="E111" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F111" s="38" t="s">
         <v>724</v>
@@ -11505,10 +11508,10 @@
         <v>724</v>
       </c>
       <c r="H111" s="37" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="I111" s="37" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="112">
@@ -11517,7 +11520,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="36" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="C112" s="36">
         <v>1.0</v>
@@ -11526,19 +11529,19 @@
         <v>968</v>
       </c>
       <c r="E112" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F112" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G112" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H112" s="37" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="I112" s="37" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="113">
@@ -11547,7 +11550,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="C113" s="36">
         <v>0.0</v>
@@ -11556,7 +11559,7 @@
         <v>968</v>
       </c>
       <c r="E113" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F113" s="38" t="s">
         <v>724</v>
@@ -11565,10 +11568,10 @@
         <v>724</v>
       </c>
       <c r="H113" s="37" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="I113" s="37" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="114">
@@ -11577,7 +11580,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C114" s="36">
         <v>0.0</v>
@@ -11586,7 +11589,7 @@
         <v>968</v>
       </c>
       <c r="E114" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F114" s="38" t="s">
         <v>724</v>
@@ -11595,10 +11598,10 @@
         <v>724</v>
       </c>
       <c r="H114" s="37" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="I114" s="37" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="115">
@@ -11607,7 +11610,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="C115" s="36">
         <v>0.0</v>
@@ -11616,7 +11619,7 @@
         <v>968</v>
       </c>
       <c r="E115" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F115" s="38" t="s">
         <v>724</v>
@@ -11625,10 +11628,10 @@
         <v>724</v>
       </c>
       <c r="H115" s="37" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="I115" s="37" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="116">
@@ -11637,7 +11640,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="36" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="C116" s="36">
         <v>1.0</v>
@@ -11646,19 +11649,19 @@
         <v>968</v>
       </c>
       <c r="E116" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F116" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G116" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H116" s="37" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="I116" s="37" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="117">
@@ -11676,7 +11679,7 @@
         <v>968</v>
       </c>
       <c r="E117" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F117" s="38" t="s">
         <v>724</v>
@@ -11685,10 +11688,10 @@
         <v>724</v>
       </c>
       <c r="H117" s="37" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="I117" s="37" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="118">
@@ -11706,7 +11709,7 @@
         <v>971</v>
       </c>
       <c r="E118" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F118" s="38" t="s">
         <v>724</v>
@@ -11715,10 +11718,10 @@
         <v>724</v>
       </c>
       <c r="H118" s="37" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="I118" s="37" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="119">
@@ -11736,7 +11739,7 @@
         <v>968</v>
       </c>
       <c r="E119" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F119" s="38" t="s">
         <v>724</v>
@@ -11745,10 +11748,10 @@
         <v>724</v>
       </c>
       <c r="H119" s="37" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="I119" s="37" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="120">
@@ -11766,7 +11769,7 @@
         <v>968</v>
       </c>
       <c r="E120" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F120" s="38" t="s">
         <v>724</v>
@@ -11775,7 +11778,7 @@
         <v>724</v>
       </c>
       <c r="H120" s="37" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="I120" s="37" t="s">
         <v>14</v>
@@ -11787,7 +11790,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C121" s="36">
         <v>0.0</v>
@@ -11796,7 +11799,7 @@
         <v>968</v>
       </c>
       <c r="E121" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F121" s="38" t="s">
         <v>724</v>
@@ -11805,10 +11808,10 @@
         <v>724</v>
       </c>
       <c r="H121" s="37" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="I121" s="37" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="122">
@@ -11817,7 +11820,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="36" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C122" s="36">
         <v>0.0</v>
@@ -11826,7 +11829,7 @@
         <v>968</v>
       </c>
       <c r="E122" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F122" s="38" t="s">
         <v>724</v>
@@ -11835,10 +11838,10 @@
         <v>724</v>
       </c>
       <c r="H122" s="37" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="I122" s="37" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="123">
@@ -11847,7 +11850,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="C123" s="36">
         <v>0.0</v>
@@ -11856,7 +11859,7 @@
         <v>968</v>
       </c>
       <c r="E123" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F123" s="38" t="s">
         <v>724</v>
@@ -11865,10 +11868,10 @@
         <v>724</v>
       </c>
       <c r="H123" s="37" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="I123" s="37" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="124">
@@ -11877,7 +11880,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="36" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="C124" s="36">
         <v>0.0</v>
@@ -11886,7 +11889,7 @@
         <v>968</v>
       </c>
       <c r="E124" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F124" s="38" t="s">
         <v>724</v>
@@ -11895,10 +11898,10 @@
         <v>724</v>
       </c>
       <c r="H124" s="37" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="I124" s="37" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="125">
@@ -11916,7 +11919,7 @@
         <v>968</v>
       </c>
       <c r="E125" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F125" s="38" t="s">
         <v>724</v>
@@ -11925,10 +11928,10 @@
         <v>724</v>
       </c>
       <c r="H125" s="37" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="I125" s="37" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="126">
@@ -11946,7 +11949,7 @@
         <v>968</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F126" s="38" t="s">
         <v>724</v>
@@ -11955,10 +11958,10 @@
         <v>724</v>
       </c>
       <c r="H126" s="37" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="I126" s="37" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="127">
@@ -11967,7 +11970,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="36" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="C127" s="36">
         <v>0.0</v>
@@ -11976,19 +11979,19 @@
         <v>990</v>
       </c>
       <c r="E127" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F127" s="38" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G127" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H127" s="37" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="I127" s="37" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="128">
@@ -11997,7 +12000,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="36" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="C128" s="36">
         <v>1.0</v>
@@ -12006,19 +12009,19 @@
         <v>992</v>
       </c>
       <c r="E128" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F128" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G128" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H128" s="37" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="I128" s="37" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="129">
@@ -12027,7 +12030,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="36" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="C129" s="36">
         <v>0.0</v>
@@ -12036,19 +12039,19 @@
         <v>994</v>
       </c>
       <c r="E129" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F129" s="38" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G129" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H129" s="37" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="I129" s="37" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="130">
@@ -12057,7 +12060,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="36" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="C130" s="36">
         <v>1.0</v>
@@ -12066,19 +12069,19 @@
         <v>996</v>
       </c>
       <c r="E130" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F130" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G130" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H130" s="37" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="I130" s="37" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="131">
@@ -12087,7 +12090,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="36" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="C131" s="36">
         <v>0.0</v>
@@ -12096,19 +12099,19 @@
         <v>998</v>
       </c>
       <c r="E131" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F131" s="38" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G131" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H131" s="37" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="I131" s="37" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="132">
@@ -12117,7 +12120,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="36" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="C132" s="36">
         <v>1.0</v>
@@ -12126,19 +12129,19 @@
         <v>1000</v>
       </c>
       <c r="E132" s="44" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="F132" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G132" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H132" s="37" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="I132" s="37" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="133">
@@ -12147,7 +12150,7 @@
         <v>131</v>
       </c>
       <c r="B133" s="36" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="C133" s="36">
         <v>0.0</v>
@@ -12156,19 +12159,19 @@
         <v>1002</v>
       </c>
       <c r="E133" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F133" s="38" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G133" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H133" s="37" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="I133" s="37" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="134">
@@ -12177,7 +12180,7 @@
         <v>132</v>
       </c>
       <c r="B134" s="36" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="C134" s="36">
         <v>1.0</v>
@@ -12186,19 +12189,19 @@
         <v>1004</v>
       </c>
       <c r="E134" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F134" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G134" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H134" s="37" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="I134" s="37" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="135">
@@ -12207,7 +12210,7 @@
         <v>133</v>
       </c>
       <c r="B135" s="36" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="C135" s="36">
         <v>0.0</v>
@@ -12216,19 +12219,19 @@
         <v>968</v>
       </c>
       <c r="E135" s="44" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="F135" s="38" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G135" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H135" s="37" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="I135" s="37" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="136">
@@ -12237,7 +12240,7 @@
         <v>134</v>
       </c>
       <c r="B136" s="36" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C136" s="36">
         <v>0.0</v>
@@ -12246,19 +12249,19 @@
         <v>1006</v>
       </c>
       <c r="E136" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F136" s="38" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G136" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H136" s="37" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="I136" s="37" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="137">
@@ -12267,7 +12270,7 @@
         <v>135</v>
       </c>
       <c r="B137" s="36" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="C137" s="36">
         <v>1.0</v>
@@ -12276,19 +12279,19 @@
         <v>986</v>
       </c>
       <c r="E137" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F137" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G137" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H137" s="37" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="I137" s="37" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="138">
@@ -12297,7 +12300,7 @@
         <v>136</v>
       </c>
       <c r="B138" s="36" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="C138" s="36">
         <v>1.0</v>
@@ -12306,19 +12309,19 @@
         <v>988</v>
       </c>
       <c r="E138" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F138" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G138" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H138" s="37" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="I138" s="37" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="139">
@@ -12327,7 +12330,7 @@
         <v>137</v>
       </c>
       <c r="B139" s="36" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="C139" s="36">
         <v>0.0</v>
@@ -12336,19 +12339,19 @@
         <v>1008</v>
       </c>
       <c r="E139" s="44" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="F139" s="38" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G139" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H139" s="37" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="I139" s="37" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="140">
@@ -12357,7 +12360,7 @@
         <v>138</v>
       </c>
       <c r="B140" s="36" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="C140" s="36">
         <v>1.0</v>
@@ -12366,19 +12369,19 @@
         <v>1010</v>
       </c>
       <c r="E140" s="44" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="F140" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G140" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H140" s="37" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="I140" s="37" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="141">
@@ -12387,7 +12390,7 @@
         <v>139</v>
       </c>
       <c r="B141" s="36" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="C141" s="36">
         <v>0.0</v>
@@ -12396,19 +12399,19 @@
         <v>1012</v>
       </c>
       <c r="E141" s="44" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="F141" s="38" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G141" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H141" s="37" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="I141" s="37" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="142">
@@ -12417,7 +12420,7 @@
         <v>140</v>
       </c>
       <c r="B142" s="36" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="C142" s="36">
         <v>1.0</v>
@@ -12426,19 +12429,19 @@
         <v>1014</v>
       </c>
       <c r="E142" s="44" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="F142" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G142" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H142" s="37" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="I142" s="37" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="143">
@@ -12447,7 +12450,7 @@
         <v>141</v>
       </c>
       <c r="B143" s="36" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="C143" s="36">
         <v>0.0</v>
@@ -12456,19 +12459,19 @@
         <v>1016</v>
       </c>
       <c r="E143" s="44" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="F143" s="38" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G143" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H143" s="37" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="I143" s="37" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="144">
@@ -12477,7 +12480,7 @@
         <v>142</v>
       </c>
       <c r="B144" s="36" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="C144" s="36">
         <v>1.0</v>
@@ -12486,19 +12489,19 @@
         <v>1018</v>
       </c>
       <c r="E144" s="44" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="F144" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G144" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H144" s="37" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I144" s="37" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="145">
@@ -12507,7 +12510,7 @@
         <v>143</v>
       </c>
       <c r="B145" s="36" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="C145" s="36">
         <v>0.0</v>
@@ -12516,19 +12519,19 @@
         <v>1020</v>
       </c>
       <c r="E145" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F145" s="38" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G145" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H145" s="37" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="I145" s="37" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="146">
@@ -12537,7 +12540,7 @@
         <v>144</v>
       </c>
       <c r="B146" s="36" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="C146" s="36">
         <v>1.0</v>
@@ -12546,19 +12549,19 @@
         <v>1022</v>
       </c>
       <c r="E146" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F146" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G146" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H146" s="37" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="I146" s="37" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="147">
@@ -12567,7 +12570,7 @@
         <v>145</v>
       </c>
       <c r="B147" s="36" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C147" s="36">
         <v>1.0</v>
@@ -12576,19 +12579,19 @@
         <v>1024</v>
       </c>
       <c r="E147" s="44" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F147" s="38" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G147" s="38" t="s">
         <v>724</v>
       </c>
       <c r="H147" s="37" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="I147" s="37" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="148">
@@ -12597,7 +12600,7 @@
         <v>146</v>
       </c>
       <c r="B148" s="36" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="C148" s="36">
         <v>0.0</v>
@@ -12606,7 +12609,7 @@
         <v>968</v>
       </c>
       <c r="E148" s="44" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F148" s="38" t="s">
         <v>724</v>
@@ -12615,10 +12618,10 @@
         <v>724</v>
       </c>
       <c r="H148" s="37" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="I148" s="37" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
   </sheetData>
@@ -12660,34 +12663,34 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="K1" s="63" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="2" ht="186.0" customHeight="1">
@@ -12696,7 +12699,7 @@
         <v>-1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="C2" s="65" t="s">
         <v>323</v>
@@ -12732,7 +12735,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="C3" s="65" t="s">
         <v>899</v>
@@ -12741,10 +12744,10 @@
         <v>985</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>321</v>
@@ -12768,19 +12771,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="D4" s="66" t="s">
         <v>985</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>321</v>
@@ -12804,19 +12807,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="D5" s="66" t="s">
         <v>985</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>321</v>
@@ -12840,19 +12843,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="D6" s="66" t="s">
         <v>985</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>321</v>
@@ -12876,25 +12879,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="D7" s="66" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E7" s="35" t="s">
         <v>1656</v>
       </c>
-      <c r="E7" s="35" t="s">
-        <v>1655</v>
-      </c>
       <c r="F7" s="35" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="I7" s="35" t="s">
         <v>630</v>
@@ -12912,25 +12915,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="I8" s="35" t="s">
         <v>630</v>
@@ -12960,7 +12963,7 @@
         <v>936</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>321</v>
@@ -12984,25 +12987,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="D10" s="66" t="s">
         <v>981</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="I10" s="35" t="s">
         <v>693</v>
@@ -13020,25 +13023,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D11" s="66" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="I11" s="35" t="s">
         <v>630</v>
@@ -13056,19 +13059,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="D12" s="66" t="s">
         <v>980</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>321</v>
@@ -13092,25 +13095,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="D13" s="66" t="s">
+        <v>1676</v>
+      </c>
+      <c r="E13" s="35" t="s">
         <v>1675</v>
       </c>
-      <c r="E13" s="35" t="s">
-        <v>1674</v>
-      </c>
       <c r="F13" s="35" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>321</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="I13" s="35" t="s">
         <v>630</v>
@@ -13137,7 +13140,7 @@
         <v>23</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="F14" s="35" t="s">
         <v>347</v>
@@ -13146,7 +13149,7 @@
         <v>321</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="I14" s="35" t="s">
         <v>630</v>
@@ -13164,7 +13167,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="C15" s="65" t="s">
         <v>323</v>
@@ -13227,7 +13230,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="2">
@@ -13254,7 +13257,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="5">
@@ -13263,7 +13266,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="6">
@@ -13275,7 +13278,7 @@
         <v>49</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="8">
@@ -13283,7 +13286,7 @@
         <v>0.0</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="9">
@@ -13291,7 +13294,7 @@
         <v>1.0</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="10">
@@ -13299,7 +13302,7 @@
         <v>2.0</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="11">
@@ -13307,7 +13310,7 @@
         <v>3.0</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="12">
@@ -13315,7 +13318,7 @@
         <v>4.0</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="13">
@@ -13323,7 +13326,7 @@
         <v>5.0</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="15">
@@ -13331,7 +13334,7 @@
         <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="16">
@@ -13349,7 +13352,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="18">
@@ -13394,7 +13397,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="23">
@@ -13411,7 +13414,7 @@
         <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="26">
@@ -13456,7 +13459,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="31">
@@ -13492,7 +13495,7 @@
         <v>8</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="35">
@@ -13510,7 +13513,7 @@
         <v>10</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="37">
@@ -13572,7 +13575,7 @@
         <v>49</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="45">
@@ -13599,7 +13602,7 @@
         <v>2</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="48">
@@ -13608,7 +13611,7 @@
         <v>3</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="49">
@@ -13617,7 +13620,7 @@
         <v>4</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="50">
@@ -13626,7 +13629,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="51">
@@ -13635,7 +13638,7 @@
         <v>6</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="52">
@@ -13644,7 +13647,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="53">
@@ -13653,7 +13656,7 @@
         <v>8</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="54">
@@ -13662,7 +13665,7 @@
         <v>9</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="55">
@@ -13671,7 +13674,7 @@
         <v>10</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="56">
@@ -13680,7 +13683,7 @@
         <v>11</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="57">
@@ -13689,7 +13692,7 @@
         <v>12</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="58">
@@ -13698,7 +13701,7 @@
         <v>13</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="59">
@@ -13707,7 +13710,7 @@
         <v>14</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="60">
@@ -13716,7 +13719,7 @@
         <v>15</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="62">
@@ -13724,7 +13727,7 @@
         <v>49</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="63">
@@ -13777,7 +13780,7 @@
         <v>49</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="70">
@@ -13842,7 +13845,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="2">
@@ -13860,7 +13863,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="4">
@@ -13869,7 +13872,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="5">
@@ -13950,7 +13953,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="14">
@@ -13995,7 +13998,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="19">
@@ -14148,7 +14151,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="37">
@@ -14156,16 +14159,16 @@
         <v>49</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="C37" s="68" t="s">
         <v>312</v>
       </c>
       <c r="D37" s="68" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="E37" s="68" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="38">
@@ -14174,7 +14177,7 @@
         <v>0</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="C38" s="38" t="s">
         <v>321</v>
@@ -14193,10 +14196,10 @@
         <v>1</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D39" s="38" t="s">
         <v>916</v>
@@ -14212,10 +14215,10 @@
         <v>2</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="D40" s="38" t="s">
         <v>944</v>
@@ -14234,7 +14237,7 @@
         <v>44</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="D41" s="38" t="s">
         <v>45</v>
@@ -14250,7 +14253,7 @@
         <v>4</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="C42" s="38" t="s">
         <v>464</v>
@@ -14268,19 +14271,19 @@
         <v>49</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="C44" s="67" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="D44" s="67" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="E44" s="68" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="F44" s="67" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="45">
@@ -14292,13 +14295,13 @@
         <v>720</v>
       </c>
       <c r="C45" s="44" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="D45" s="44" t="s">
         <v>723</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="F45" s="43" t="b">
         <v>0</v>
@@ -14313,13 +14316,13 @@
         <v>733</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="D46" s="44" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="F46" s="43" t="b">
         <v>0</v>
@@ -14334,13 +14337,13 @@
         <v>750</v>
       </c>
       <c r="C47" s="44" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="D47" s="44" t="s">
         <v>770</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="F47" s="43" t="b">
         <v>0</v>
@@ -14355,13 +14358,13 @@
         <v>755</v>
       </c>
       <c r="C48" s="44" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="F48" s="43" t="b">
         <v>0</v>
@@ -14379,10 +14382,10 @@
         <v>44</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="F49" s="43" t="b">
         <v>0</v>
@@ -14394,16 +14397,16 @@
         <v>5</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>44</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="F50" s="43" t="b">
         <v>0</v>
@@ -14415,16 +14418,16 @@
         <v>6</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="C51" s="44" t="s">
         <v>44</v>
       </c>
       <c r="D51" s="44" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="F51" s="43" t="b">
         <v>1</v>
@@ -14436,16 +14439,16 @@
         <v>7</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="C52" s="44" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="D52" s="44" t="s">
         <v>723</v>
       </c>
       <c r="E52" s="48" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="F52" s="43" t="b">
         <v>0</v>
@@ -14456,10 +14459,10 @@
         <v>49</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="55">
@@ -14468,7 +14471,7 @@
         <v>0</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="C55" s="51" t="s">
         <v>473</v>
@@ -14479,7 +14482,7 @@
         <v>49</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="58">
@@ -15495,16 +15498,16 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="2">
@@ -15516,7 +15519,7 @@
         <v>324</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="D2" s="70" t="s">
         <v>321</v>
@@ -15534,7 +15537,7 @@
         <v>440</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="D3" s="70" t="s">
         <v>321</v>
@@ -15549,10 +15552,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="D4" s="70" t="s">
         <v>321</v>
@@ -15590,7 +15593,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="2">
@@ -15617,7 +15620,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
   </sheetData>
@@ -15643,21 +15646,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B2" s="71">
         <v>5.0</v>
@@ -15671,7 +15674,7 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B3" s="71">
         <v>4.0</v>
@@ -15685,7 +15688,7 @@
     </row>
     <row r="4">
       <c r="A4" s="37" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B4" s="71">
         <v>2.0</v>
@@ -15699,7 +15702,7 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B5" s="71">
         <v>5.0</v>
@@ -15713,7 +15716,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B6" s="71">
         <v>4.0</v>
@@ -15727,7 +15730,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B7" s="71">
         <v>4.0</v>
@@ -15741,7 +15744,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B8" s="71">
         <v>2.0</v>
@@ -15755,7 +15758,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B9" s="71">
         <v>5.0</v>
@@ -33113,6 +33116,21 @@
       <c r="C46" s="36" t="s">
         <v>969</v>
       </c>
+      <c r="D46" s="36" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="52">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>45</v>
+      </c>
+      <c r="B47" s="36" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C47" s="36" t="s">
+        <v>969</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -33145,13 +33163,13 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>26</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="2">
@@ -33166,7 +33184,7 @@
         <v>320</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="3">
@@ -33181,7 +33199,7 @@
         <v>320</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="4">
@@ -33193,10 +33211,10 @@
         <v>767</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="5">
@@ -33205,13 +33223,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="6">
@@ -33223,10 +33241,10 @@
         <v>781</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="7">
@@ -33238,10 +33256,10 @@
         <v>783</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="8">
@@ -33250,13 +33268,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="9">
@@ -33268,10 +33286,10 @@
         <v>785</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="10">
@@ -33280,13 +33298,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="11">
@@ -33298,10 +33316,10 @@
         <v>786</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="12">
@@ -33316,7 +33334,7 @@
         <v>406</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="13">
@@ -33331,7 +33349,7 @@
         <v>408</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="14">
@@ -33340,13 +33358,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="15">
@@ -33358,10 +33376,10 @@
         <v>793</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="16">
@@ -33370,13 +33388,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="17">
@@ -33388,10 +33406,10 @@
         <v>818</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="18">
@@ -33406,7 +33424,7 @@
         <v>387</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="19">
@@ -33421,7 +33439,7 @@
         <v>326</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="20">
@@ -33430,13 +33448,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C20" s="39" t="s">
         <v>387</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="21">
@@ -33451,7 +33469,7 @@
         <v>35</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="22">
@@ -33466,7 +33484,7 @@
         <v>35</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="23">
@@ -33475,13 +33493,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C23" s="39" t="s">
         <v>35</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="24">
@@ -33496,7 +33514,7 @@
         <v>35</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="25">
@@ -33505,13 +33523,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C25" s="39" t="s">
         <v>320</v>
       </c>
       <c r="D25" s="41" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="27">
@@ -33519,25 +33537,25 @@
         <v>49</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>467</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H27" s="28" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="28">
@@ -33546,7 +33564,7 @@
         <v>0</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C28" s="37" t="s">
         <v>473</v>
@@ -33573,7 +33591,7 @@
         <v>1</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C29" s="37" t="s">
         <v>473</v>
@@ -33600,7 +33618,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>473</v>
@@ -33612,13 +33630,13 @@
         <v>477</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="G30" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="40" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="31">
@@ -33627,7 +33645,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>473</v>
@@ -33639,13 +33657,13 @@
         <v>477</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="G31" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H31" s="40" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="32">
@@ -33654,7 +33672,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C32" s="40" t="s">
         <v>473</v>
@@ -33672,7 +33690,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="40" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="33">
@@ -33681,7 +33699,7 @@
         <v>5</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C33" s="40" t="s">
         <v>473</v>
@@ -33690,7 +33708,7 @@
         <v>474</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F33" s="38" t="s">
         <v>722</v>
@@ -33699,7 +33717,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="40" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="34">
@@ -33708,7 +33726,7 @@
         <v>6</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C34" s="40" t="s">
         <v>473</v>
@@ -33726,7 +33744,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="40" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="35">
@@ -33735,7 +33753,7 @@
         <v>7</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C35" s="40" t="s">
         <v>473</v>
@@ -33747,13 +33765,13 @@
         <v>477</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="G35" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H35" s="40" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="36">
@@ -33762,7 +33780,7 @@
         <v>8</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C36" s="40" t="s">
         <v>473</v>
@@ -33780,7 +33798,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="40" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="37">
@@ -33789,7 +33807,7 @@
         <v>9</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C37" s="40" t="s">
         <v>473</v>
@@ -33801,13 +33819,13 @@
         <v>477</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="G37" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H37" s="40" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="38">
@@ -33816,7 +33834,7 @@
         <v>10</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C38" s="40" t="s">
         <v>473</v>
@@ -33828,13 +33846,13 @@
         <v>851</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="G38" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H38" s="40" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="39">
@@ -33843,7 +33861,7 @@
         <v>11</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C39" s="40" t="s">
         <v>852</v>
@@ -33855,13 +33873,13 @@
         <v>477</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="G39" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H39" s="40" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="40">
@@ -33870,7 +33888,7 @@
         <v>12</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C40" s="40" t="s">
         <v>473</v>
@@ -33882,13 +33900,13 @@
         <v>477</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="G40" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H40" s="40" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="41">
@@ -33897,7 +33915,7 @@
         <v>13</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C41" s="40" t="s">
         <v>852</v>
@@ -33906,16 +33924,16 @@
         <v>539</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="G41" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="42">
@@ -33924,7 +33942,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C42" s="40" t="s">
         <v>473</v>
@@ -33942,7 +33960,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="40" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="43">
@@ -33951,7 +33969,7 @@
         <v>15</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>473</v>
@@ -33969,7 +33987,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="40" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="44">
@@ -33978,7 +33996,7 @@
         <v>16</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>473</v>
@@ -33996,7 +34014,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="40" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="45">
@@ -34005,7 +34023,7 @@
         <v>17</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C45" s="40" t="s">
         <v>473</v>
@@ -34023,7 +34041,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="40" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="46">
@@ -34032,7 +34050,7 @@
         <v>18</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C46" s="40" t="s">
         <v>473</v>
@@ -34044,13 +34062,13 @@
         <v>477</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="G46" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="40" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="47">
@@ -34059,7 +34077,7 @@
         <v>19</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C47" s="40" t="s">
         <v>473</v>
@@ -34071,13 +34089,13 @@
         <v>477</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="G47" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H47" s="40" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="48">
@@ -34086,7 +34104,7 @@
         <v>20</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C48" s="40" t="s">
         <v>473</v>
@@ -34095,16 +34113,16 @@
         <v>474</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="G48" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="40" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="49">
@@ -34113,7 +34131,7 @@
         <v>21</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C49" s="40" t="s">
         <v>473</v>
@@ -34131,7 +34149,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="40" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="50">
@@ -34140,7 +34158,7 @@
         <v>22</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C50" s="40" t="s">
         <v>473</v>
@@ -34152,13 +34170,13 @@
         <v>477</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="G50" s="54" t="b">
         <v>1</v>
       </c>
       <c r="H50" s="40" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="51">
@@ -34167,7 +34185,7 @@
         <v>23</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C51" s="40" t="s">
         <v>473</v>
@@ -34179,13 +34197,13 @@
         <v>856</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="G51" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H51" s="40" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="52">
@@ -34194,7 +34212,7 @@
         <v>24</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C52" s="40" t="s">
         <v>857</v>
@@ -34203,16 +34221,16 @@
         <v>474</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="G52" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="40" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="53">
@@ -34221,7 +34239,7 @@
         <v>25</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C53" s="40" t="s">
         <v>473</v>
@@ -34239,7 +34257,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="40" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="54">
@@ -34248,7 +34266,7 @@
         <v>26</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C54" s="40" t="s">
         <v>473</v>
@@ -34260,13 +34278,13 @@
         <v>477</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="G54" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H54" s="40" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="55">
@@ -34275,7 +34293,7 @@
         <v>27</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C55" s="40" t="s">
         <v>473</v>
@@ -34293,7 +34311,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="40" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="56">
@@ -34302,7 +34320,7 @@
         <v>28</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C56" s="40" t="s">
         <v>473</v>
@@ -34314,13 +34332,13 @@
         <v>862</v>
       </c>
       <c r="F56" s="38" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="G56" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H56" s="40" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="57">
@@ -34329,7 +34347,7 @@
         <v>29</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C57" s="40" t="s">
         <v>473</v>
@@ -34347,7 +34365,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="40" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="58">
@@ -34356,7 +34374,7 @@
         <v>30</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="C58" s="40" t="s">
         <v>473</v>
@@ -34374,7 +34392,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="40" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="59">
@@ -34383,7 +34401,7 @@
         <v>31</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C59" s="40" t="s">
         <v>473</v>
@@ -34395,13 +34413,13 @@
         <v>477</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="G59" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H59" s="40" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="60">
@@ -34410,7 +34428,7 @@
         <v>32</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C60" s="40" t="s">
         <v>473</v>
@@ -34428,7 +34446,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="40" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="61">
@@ -34437,7 +34455,7 @@
         <v>33</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C61" s="40" t="s">
         <v>473</v>
@@ -34455,7 +34473,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="40" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="62">
@@ -34464,7 +34482,7 @@
         <v>34</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C62" s="40" t="s">
         <v>473</v>
@@ -34482,7 +34500,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="40" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="63">
@@ -34491,7 +34509,7 @@
         <v>35</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="C63" s="40" t="s">
         <v>473</v>
@@ -34509,7 +34527,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="40" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="64">
@@ -34518,7 +34536,7 @@
         <v>36</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C64" s="40" t="s">
         <v>473</v>
@@ -34536,7 +34554,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="40" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="65">
@@ -34545,7 +34563,7 @@
         <v>37</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="C65" s="40" t="s">
         <v>473</v>
@@ -34563,7 +34581,7 @@
         <v>0</v>
       </c>
       <c r="H65" s="40" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="66">
@@ -34572,7 +34590,7 @@
         <v>38</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C66" s="40" t="s">
         <v>848</v>
@@ -34590,7 +34608,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="40" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="67">
@@ -34599,7 +34617,7 @@
         <v>39</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C67" s="40" t="s">
         <v>473</v>
@@ -34617,7 +34635,7 @@
         <v>0</v>
       </c>
       <c r="H67" s="40" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="68">
@@ -34626,7 +34644,7 @@
         <v>40</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C68" s="37" t="s">
         <v>473</v>
@@ -34743,10 +34761,10 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C1" s="56" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="2">
@@ -34758,7 +34776,7 @@
         <v>721</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="3">
@@ -34770,7 +34788,7 @@
         <v>753</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="4">
@@ -34779,10 +34797,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="6">
@@ -34790,13 +34808,13 @@
         <v>49</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="7">
@@ -34805,7 +34823,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>723</v>
@@ -34820,10 +34838,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="D8" s="57" t="s">
         <v>477</v>
@@ -34835,10 +34853,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="D9" s="57" t="s">
         <v>726</v>
@@ -34850,10 +34868,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D10" s="57" t="s">
         <v>728</v>
@@ -34865,7 +34883,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>723</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -2219,13 +2219,13 @@
     <t>UNCHAIN_EXTRAPERLO_DOOR</t>
   </si>
   <si>
+    <t>ACTION_SPAWN_EXTRAPERLO_DOOR</t>
+  </si>
+  <si>
+    <t>UNCHAIN_SHOW_EXTRAPERLO_DOOR_OPENED</t>
+  </si>
+  <si>
     <t>EVENT_EXTRAPERLO_SAID_PHRASE</t>
-  </si>
-  <si>
-    <t>ACTION_SPAWN_EXTRAPERLO_DOOR</t>
-  </si>
-  <si>
-    <t>UNCHAIN_SHOW_EXTRAPERLO_DOOR_OPENED</t>
   </si>
   <si>
     <t>ACTION_SPAWN_EXTRAPERLO_WALL, ACTION_DESPAWN_EXTRAPERLO_DOOR, ACTION_SPAWN_EXTRAPERLO_DOOR_REAL</t>
@@ -14608,7 +14608,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="35">
@@ -25226,16 +25226,16 @@
         <v>0</v>
       </c>
       <c r="F94" s="44" t="s">
-        <v>705</v>
+        <v>479</v>
       </c>
       <c r="G94" s="39" t="s">
-        <v>479</v>
+        <v>627</v>
       </c>
       <c r="H94" s="44" t="s">
         <v>545</v>
       </c>
       <c r="I94" s="39" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="95">
@@ -25244,7 +25244,7 @@
         <v>29</v>
       </c>
       <c r="B95" s="45" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C95" s="43" t="b">
         <v>0</v>
@@ -25259,7 +25259,7 @@
         <v>479</v>
       </c>
       <c r="G95" s="39" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="H95" s="44" t="s">
         <v>545</v>
@@ -31594,7 +31594,7 @@
         <v>727</v>
       </c>
       <c r="I229" s="48" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="J229" s="44" t="s">
         <v>728</v>
@@ -31669,7 +31669,7 @@
         <v>131</v>
       </c>
       <c r="B231" s="45" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C231" s="43" t="b">
         <v>0</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -13384,7 +13384,7 @@
         <v>1344</v>
       </c>
       <c r="F162" s="38" t="s">
-        <v>1366</v>
+        <v>893</v>
       </c>
       <c r="G162" s="38" t="s">
         <v>737</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -39,7 +39,7 @@
     <definedName name="Interval_Dialog_Options">DIALOGS!$A$36:$H$90</definedName>
     <definedName name="Interval_Memento">EVENTS!$A$47:$F$55</definedName>
     <definedName name="Interval_autoInsertDialog">FN!$A$7:$K$8</definedName>
-    <definedName name="Interval_Sounds">SOUNDS!$A$1:$D$65</definedName>
+    <definedName name="Interval_Sounds">SOUNDS!$A$1:$D$84</definedName>
     <definedName name="Interval_Action_Conditions">ACTION_CONDS!$A$1:$H$69</definedName>
   </definedNames>
   <calcPr/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6732" uniqueCount="1956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6789" uniqueCount="1994">
   <si>
     <t>NewItem</t>
   </si>
@@ -3485,6 +3485,120 @@
     <t>SOUND_TAKE_UNKNOWN_WOMEN_SPANISH</t>
   </si>
   <si>
+    <t>SOUND_OBSERVE_EXTRAPERLO_ARTURO</t>
+  </si>
+  <si>
+    <t>SOUND_OBSERVE_EXTRAPERLO_ARTURO_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_INTRO_1</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_INTRO_1_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_0_0</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_0_0_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_0_1</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_0_1_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_0_2</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_0_2_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_0_3</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_0_3_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_1_0</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_1_0_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_1_1</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_1_1_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_1_2</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_1_2_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_1_3</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_1_3_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_1_4</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_1_4_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_0</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_0_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_1</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_1_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_2</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_2_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_3</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_3_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_4</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_4_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_5</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_5_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_6</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_6_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_7</t>
+  </si>
+  <si>
+    <t>SOUND_ARTURO_EXTRAPERLO_OP_2_7_SPANISH</t>
+  </si>
+  <si>
     <t>SOUND_LAST</t>
   </si>
   <si>
@@ -3641,7 +3755,7 @@
     <t>DIALOG_UNKNOWN_GIRLS_OPTION_INTRO_1</t>
   </si>
   <si>
-    <t>DIALOG_ARTURO_EXTRAPERLO_OPTION_0, DIALOG_ARTURO_EXTRAPERLO_OPTION_1, DIALOG_ARTURO_EXTRAPERLO_OPTION_2</t>
+    <t>DIALOG_ARTURO_EXTRAPERLO_OPTION_0, DIALOG_ARTURO_EXTRAPERLO_OPTION_1, DIALOG_ARTURO_EXTRAPERLO_OPTION_2, DIALOG_FIK_1_OPTION_3</t>
   </si>
   <si>
     <t>DIALOG_ARTURO_EXTRAPERLO_OPTION_INTRO</t>
@@ -7245,7 +7359,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D65" displayName="Table_sounds" name="Table_sounds" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D84" displayName="Table_sounds" name="Table_sounds" id="12">
   <tableColumns count="4">
     <tableColumn name="N" id="1"/>
     <tableColumn name="SOUND_ID" id="2"/>
@@ -8103,13 +8217,13 @@
         <v>50</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>1285</v>
+        <v>1323</v>
       </c>
       <c r="C1" s="59" t="s">
-        <v>1286</v>
+        <v>1324</v>
       </c>
       <c r="D1" s="59" t="s">
-        <v>1287</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="2">
@@ -8132,10 +8246,10 @@
         <v>328</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1288</v>
+        <v>1326</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>1288</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="4">
@@ -8144,13 +8258,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1289</v>
+        <v>1327</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1290</v>
+        <v>1328</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>1291</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="5">
@@ -8159,13 +8273,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1292</v>
+        <v>1330</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>1293</v>
+        <v>1331</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>1294</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="6">
@@ -8174,13 +8288,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1295</v>
+        <v>1333</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>1296</v>
+        <v>1334</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>1297</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="7">
@@ -8192,10 +8306,10 @@
         <v>331</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>1298</v>
+        <v>1336</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>1299</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="8">
@@ -8207,10 +8321,10 @@
         <v>352</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1300</v>
+        <v>1338</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>1300</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="9">
@@ -8222,10 +8336,10 @@
         <v>359</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>1301</v>
+        <v>1339</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>1302</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="10">
@@ -8237,10 +8351,10 @@
         <v>337</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>1303</v>
+        <v>1341</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>1304</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="11">
@@ -8249,13 +8363,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1305</v>
+        <v>1343</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>1306</v>
+        <v>1344</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>1307</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="12">
@@ -8264,13 +8378,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1308</v>
+        <v>1346</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>1309</v>
+        <v>1347</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>1310</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="13">
@@ -8282,10 +8396,10 @@
         <v>342</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>1311</v>
+        <v>1349</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>1312</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="14">
@@ -8297,10 +8411,10 @@
         <v>349</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>1313</v>
+        <v>1351</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>1314</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="15">
@@ -8309,13 +8423,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1315</v>
+        <v>1353</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>1316</v>
+        <v>1354</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>1317</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="16">
@@ -8327,10 +8441,10 @@
         <v>362</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>1318</v>
+        <v>1356</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>1319</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="17">
@@ -8342,10 +8456,10 @@
         <v>367</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>1320</v>
+        <v>1358</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>1321</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="18">
@@ -8357,10 +8471,10 @@
         <v>370</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>1322</v>
+        <v>1360</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>1323</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="19">
@@ -8372,10 +8486,10 @@
         <v>374</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>1324</v>
+        <v>1362</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>1325</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="20">
@@ -8387,10 +8501,10 @@
         <v>377</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>1326</v>
+        <v>1364</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>1327</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="21">
@@ -8402,10 +8516,10 @@
         <v>380</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>1328</v>
+        <v>1366</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>1329</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="22">
@@ -8417,10 +8531,10 @@
         <v>382</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>1330</v>
+        <v>1368</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>1331</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="23">
@@ -8432,10 +8546,10 @@
         <v>384</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>1332</v>
+        <v>1370</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>1333</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="24">
@@ -8447,10 +8561,10 @@
         <v>386</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>1334</v>
+        <v>1372</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>1335</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="25">
@@ -8462,10 +8576,10 @@
         <v>389</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>1336</v>
+        <v>1374</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>1337</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="26">
@@ -8477,10 +8591,10 @@
         <v>393</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>1338</v>
+        <v>1376</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>1339</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="27">
@@ -8492,10 +8606,10 @@
         <v>398</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>1340</v>
+        <v>1378</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>1341</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="28">
@@ -8507,10 +8621,10 @@
         <v>400</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>1342</v>
+        <v>1380</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>1343</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="29">
@@ -8522,10 +8636,10 @@
         <v>404</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>1344</v>
+        <v>1382</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>1345</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="30">
@@ -8534,13 +8648,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>1346</v>
+        <v>1384</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>1347</v>
+        <v>1385</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>1348</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="31">
@@ -8552,10 +8666,10 @@
         <v>408</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>1349</v>
+        <v>1387</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>1350</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="32">
@@ -8567,10 +8681,10 @@
         <v>410</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>1351</v>
+        <v>1389</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>1352</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="33">
@@ -8579,13 +8693,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>1353</v>
+        <v>1391</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>47</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>1354</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="34">
@@ -8597,10 +8711,10 @@
         <v>414</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>1355</v>
+        <v>1393</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>1356</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="35">
@@ -8612,10 +8726,10 @@
         <v>418</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>1357</v>
+        <v>1395</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>1358</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="36">
@@ -8627,10 +8741,10 @@
         <v>421</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>1359</v>
+        <v>1397</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>1360</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="37">
@@ -8642,10 +8756,10 @@
         <v>426</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>1361</v>
+        <v>1399</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>1362</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="38">
@@ -8657,10 +8771,10 @@
         <v>431</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>1363</v>
+        <v>1401</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>1364</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="39">
@@ -8672,10 +8786,10 @@
         <v>11</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>1365</v>
+        <v>1403</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>1365</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="40">
@@ -8687,10 +8801,10 @@
         <v>438</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>1366</v>
+        <v>1404</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>1367</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="41">
@@ -8702,10 +8816,10 @@
         <v>442</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>1368</v>
+        <v>1406</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>1369</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="42">
@@ -8717,10 +8831,10 @@
         <v>445</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>1370</v>
+        <v>1408</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>1371</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="43">
@@ -8732,10 +8846,10 @@
         <v>449</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>1370</v>
+        <v>1408</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>1372</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="44">
@@ -8747,10 +8861,10 @@
         <v>452</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>1373</v>
+        <v>1411</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>1373</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="45">
@@ -8762,10 +8876,10 @@
         <v>460</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>1374</v>
+        <v>1412</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>1375</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="46">
@@ -8777,10 +8891,10 @@
         <v>466</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>1376</v>
+        <v>1414</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>1376</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="47">
@@ -8792,10 +8906,10 @@
         <v>470</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>1377</v>
+        <v>1415</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>1378</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="48">
@@ -8807,10 +8921,10 @@
         <v>474</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>1379</v>
+        <v>1417</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>1380</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="49">
@@ -8822,10 +8936,10 @@
         <v>479</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>1381</v>
+        <v>1419</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>1382</v>
+        <v>1420</v>
       </c>
     </row>
   </sheetData>
@@ -8860,28 +8974,28 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1383</v>
+        <v>1421</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1384</v>
+        <v>1422</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1385</v>
+        <v>1423</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1386</v>
+        <v>1424</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1387</v>
+        <v>1425</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1388</v>
+        <v>1426</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1389</v>
+        <v>1427</v>
       </c>
       <c r="I1" s="62" t="s">
-        <v>1390</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="2">
@@ -8925,7 +9039,7 @@
         <v>1079</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>753</v>
@@ -8934,10 +9048,10 @@
         <v>753</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>1392</v>
+        <v>1430</v>
       </c>
       <c r="I3" s="37" t="s">
-        <v>1393</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="4">
@@ -8955,7 +9069,7 @@
         <v>1081</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F4" s="38" t="s">
         <v>753</v>
@@ -8964,10 +9078,10 @@
         <v>753</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1394</v>
+        <v>1432</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1395</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="5">
@@ -8985,7 +9099,7 @@
         <v>1083</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F5" s="38" t="s">
         <v>753</v>
@@ -8994,10 +9108,10 @@
         <v>753</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>1396</v>
+        <v>1434</v>
       </c>
       <c r="I5" s="37" t="s">
-        <v>1397</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="6">
@@ -9006,7 +9120,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1398</v>
+        <v>1436</v>
       </c>
       <c r="C6" s="36">
         <v>0.0</v>
@@ -9015,7 +9129,7 @@
         <v>1021</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>753</v>
@@ -9024,10 +9138,10 @@
         <v>753</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>1399</v>
+        <v>1437</v>
       </c>
       <c r="I6" s="37" t="s">
-        <v>1400</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="7">
@@ -9036,7 +9150,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1401</v>
+        <v>1439</v>
       </c>
       <c r="C7" s="36">
         <v>0.0</v>
@@ -9045,7 +9159,7 @@
         <v>1021</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F7" s="38" t="s">
         <v>753</v>
@@ -9054,10 +9168,10 @@
         <v>753</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>1402</v>
+        <v>1440</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>1403</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="8">
@@ -9075,7 +9189,7 @@
         <v>1021</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>753</v>
@@ -9084,10 +9198,10 @@
         <v>753</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>1404</v>
+        <v>1442</v>
       </c>
       <c r="I8" s="37" t="s">
-        <v>1405</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="9">
@@ -9096,7 +9210,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1406</v>
+        <v>1444</v>
       </c>
       <c r="C9" s="36">
         <v>0.0</v>
@@ -9105,7 +9219,7 @@
         <v>1021</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F9" s="38" t="s">
         <v>753</v>
@@ -9114,10 +9228,10 @@
         <v>753</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>1407</v>
+        <v>1445</v>
       </c>
       <c r="I9" s="37" t="s">
-        <v>1408</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="10">
@@ -9126,7 +9240,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1409</v>
+        <v>1447</v>
       </c>
       <c r="C10" s="36">
         <v>0.0</v>
@@ -9135,7 +9249,7 @@
         <v>1021</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F10" s="38" t="s">
         <v>753</v>
@@ -9144,10 +9258,10 @@
         <v>753</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>1410</v>
+        <v>1448</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>1411</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="11">
@@ -9156,7 +9270,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1412</v>
+        <v>1450</v>
       </c>
       <c r="C11" s="36">
         <v>1.0</v>
@@ -9165,19 +9279,19 @@
         <v>1021</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G11" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>1414</v>
+        <v>1452</v>
       </c>
       <c r="I11" s="37" t="s">
-        <v>1415</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="12">
@@ -9186,7 +9300,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1416</v>
+        <v>1454</v>
       </c>
       <c r="C12" s="36">
         <v>0.0</v>
@@ -9195,7 +9309,7 @@
         <v>1021</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>753</v>
@@ -9204,10 +9318,10 @@
         <v>753</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1417</v>
+        <v>1455</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>1418</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="13">
@@ -9216,7 +9330,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1419</v>
+        <v>1457</v>
       </c>
       <c r="C13" s="36">
         <v>0.0</v>
@@ -9225,7 +9339,7 @@
         <v>1021</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>753</v>
@@ -9234,10 +9348,10 @@
         <v>753</v>
       </c>
       <c r="H13" s="37" t="s">
-        <v>1420</v>
+        <v>1458</v>
       </c>
       <c r="I13" s="37" t="s">
-        <v>1421</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="14">
@@ -9246,7 +9360,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1422</v>
+        <v>1460</v>
       </c>
       <c r="C14" s="36">
         <v>1.0</v>
@@ -9255,19 +9369,19 @@
         <v>1021</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G14" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>1423</v>
+        <v>1461</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>1424</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="15">
@@ -9276,7 +9390,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>1425</v>
+        <v>1463</v>
       </c>
       <c r="C15" s="36">
         <v>1.0</v>
@@ -9285,19 +9399,19 @@
         <v>1021</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G15" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1426</v>
+        <v>1464</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1427</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="16">
@@ -9306,7 +9420,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>1192</v>
+        <v>1230</v>
       </c>
       <c r="C16" s="36">
         <v>0.0</v>
@@ -9315,7 +9429,7 @@
         <v>1021</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>753</v>
@@ -9324,10 +9438,10 @@
         <v>753</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>1428</v>
+        <v>1466</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>1429</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="17">
@@ -9336,7 +9450,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1195</v>
+        <v>1233</v>
       </c>
       <c r="C17" s="36">
         <v>0.0</v>
@@ -9345,7 +9459,7 @@
         <v>1021</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>753</v>
@@ -9354,10 +9468,10 @@
         <v>753</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>1430</v>
+        <v>1468</v>
       </c>
       <c r="I17" s="37" t="s">
-        <v>1431</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="18">
@@ -9366,7 +9480,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1432</v>
+        <v>1470</v>
       </c>
       <c r="C18" s="36">
         <v>0.0</v>
@@ -9375,7 +9489,7 @@
         <v>1021</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>753</v>
@@ -9384,10 +9498,10 @@
         <v>753</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>1433</v>
+        <v>1471</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>1434</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="19">
@@ -9405,7 +9519,7 @@
         <v>1021</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F19" s="38" t="s">
         <v>753</v>
@@ -9414,10 +9528,10 @@
         <v>753</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>1435</v>
+        <v>1473</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>1436</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="20">
@@ -9435,7 +9549,7 @@
         <v>1021</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F20" s="38" t="s">
         <v>753</v>
@@ -9444,10 +9558,10 @@
         <v>753</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>1437</v>
+        <v>1475</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>1438</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="21">
@@ -9465,7 +9579,7 @@
         <v>1021</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F21" s="38" t="s">
         <v>753</v>
@@ -9474,10 +9588,10 @@
         <v>753</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>1439</v>
+        <v>1477</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>1440</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="22">
@@ -9495,7 +9609,7 @@
         <v>1021</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F22" s="38" t="s">
         <v>753</v>
@@ -9504,10 +9618,10 @@
         <v>753</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1441</v>
+        <v>1479</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1442</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="23">
@@ -9525,7 +9639,7 @@
         <v>1021</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F23" s="38" t="s">
         <v>753</v>
@@ -9534,10 +9648,10 @@
         <v>753</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>1443</v>
+        <v>1481</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>1444</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="24">
@@ -9555,7 +9669,7 @@
         <v>1021</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F24" s="38" t="s">
         <v>753</v>
@@ -9564,10 +9678,10 @@
         <v>753</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1445</v>
+        <v>1483</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1446</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="25">
@@ -9585,7 +9699,7 @@
         <v>1021</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F25" s="38" t="s">
         <v>753</v>
@@ -9594,10 +9708,10 @@
         <v>753</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>1447</v>
+        <v>1485</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>1448</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="26">
@@ -9615,7 +9729,7 @@
         <v>1021</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F26" s="38" t="s">
         <v>753</v>
@@ -9624,10 +9738,10 @@
         <v>753</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>1449</v>
+        <v>1487</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>1450</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="27">
@@ -9636,7 +9750,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1451</v>
+        <v>1489</v>
       </c>
       <c r="C27" s="36">
         <v>0.0</v>
@@ -9645,7 +9759,7 @@
         <v>1021</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F27" s="38" t="s">
         <v>753</v>
@@ -9654,10 +9768,10 @@
         <v>753</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>1452</v>
+        <v>1490</v>
       </c>
       <c r="I27" s="37" t="s">
-        <v>1453</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="28">
@@ -9666,7 +9780,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1454</v>
+        <v>1492</v>
       </c>
       <c r="C28" s="36">
         <v>1.0</v>
@@ -9675,19 +9789,19 @@
         <v>1021</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G28" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>1455</v>
+        <v>1493</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>1456</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="29">
@@ -9696,7 +9810,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>1280</v>
+        <v>1318</v>
       </c>
       <c r="C29" s="36">
         <v>0.0</v>
@@ -9705,7 +9819,7 @@
         <v>1021</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>753</v>
@@ -9714,10 +9828,10 @@
         <v>753</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>1457</v>
+        <v>1495</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>1458</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="30">
@@ -9726,7 +9840,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1282</v>
+        <v>1320</v>
       </c>
       <c r="C30" s="36">
         <v>0.0</v>
@@ -9735,7 +9849,7 @@
         <v>1021</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F30" s="38" t="s">
         <v>753</v>
@@ -9744,10 +9858,10 @@
         <v>753</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>1459</v>
+        <v>1497</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>1460</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="31">
@@ -9756,7 +9870,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1284</v>
+        <v>1322</v>
       </c>
       <c r="C31" s="36">
         <v>0.0</v>
@@ -9765,7 +9879,7 @@
         <v>1021</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>753</v>
@@ -9774,10 +9888,10 @@
         <v>753</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>1461</v>
+        <v>1499</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>1462</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="32">
@@ -9795,7 +9909,7 @@
         <v>1021</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F32" s="38" t="s">
         <v>753</v>
@@ -9804,10 +9918,10 @@
         <v>753</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>1463</v>
+        <v>1501</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>1464</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="33">
@@ -9816,7 +9930,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1197</v>
+        <v>1235</v>
       </c>
       <c r="C33" s="36">
         <v>0.0</v>
@@ -9825,7 +9939,7 @@
         <v>1021</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F33" s="38" t="s">
         <v>753</v>
@@ -9834,10 +9948,10 @@
         <v>753</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1465</v>
+        <v>1503</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1466</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="34">
@@ -9846,7 +9960,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1467</v>
+        <v>1505</v>
       </c>
       <c r="C34" s="36">
         <v>1.0</v>
@@ -9855,19 +9969,19 @@
         <v>1021</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G34" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>1468</v>
+        <v>1506</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>1469</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="35">
@@ -9876,7 +9990,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1470</v>
+        <v>1508</v>
       </c>
       <c r="C35" s="36">
         <v>1.0</v>
@@ -9885,19 +9999,19 @@
         <v>1021</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G35" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>1471</v>
+        <v>1509</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>1472</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="36">
@@ -9915,7 +10029,7 @@
         <v>1021</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F36" s="38" t="s">
         <v>753</v>
@@ -9924,10 +10038,10 @@
         <v>753</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>1473</v>
+        <v>1511</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>1474</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="37">
@@ -9936,7 +10050,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1475</v>
+        <v>1513</v>
       </c>
       <c r="C37" s="36">
         <v>0.0</v>
@@ -9945,7 +10059,7 @@
         <v>1021</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F37" s="38" t="s">
         <v>753</v>
@@ -9954,10 +10068,10 @@
         <v>753</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>1476</v>
+        <v>1514</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>1477</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="38">
@@ -9966,7 +10080,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1478</v>
+        <v>1516</v>
       </c>
       <c r="C38" s="36">
         <v>1.0</v>
@@ -9975,19 +10089,19 @@
         <v>1021</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G38" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>1479</v>
+        <v>1517</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>1480</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="39">
@@ -9996,7 +10110,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1481</v>
+        <v>1519</v>
       </c>
       <c r="C39" s="36">
         <v>0.0</v>
@@ -10005,7 +10119,7 @@
         <v>1021</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F39" s="38" t="s">
         <v>753</v>
@@ -10014,10 +10128,10 @@
         <v>753</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>1482</v>
+        <v>1520</v>
       </c>
       <c r="I39" s="37" t="s">
-        <v>1483</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="40">
@@ -10026,7 +10140,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1484</v>
+        <v>1522</v>
       </c>
       <c r="C40" s="36">
         <v>1.0</v>
@@ -10035,19 +10149,19 @@
         <v>1021</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G40" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>1485</v>
+        <v>1523</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>1486</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="41">
@@ -10056,7 +10170,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1487</v>
+        <v>1525</v>
       </c>
       <c r="C41" s="36">
         <v>0.0</v>
@@ -10065,7 +10179,7 @@
         <v>1021</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F41" s="38" t="s">
         <v>753</v>
@@ -10074,10 +10188,10 @@
         <v>753</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>1488</v>
+        <v>1526</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>1489</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="42">
@@ -10086,7 +10200,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1490</v>
+        <v>1528</v>
       </c>
       <c r="C42" s="36">
         <v>1.0</v>
@@ -10095,19 +10209,19 @@
         <v>1021</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G42" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>1491</v>
+        <v>1529</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>1492</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="43">
@@ -10116,7 +10230,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1493</v>
+        <v>1531</v>
       </c>
       <c r="C43" s="36">
         <v>0.0</v>
@@ -10125,7 +10239,7 @@
         <v>1021</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F43" s="38" t="s">
         <v>753</v>
@@ -10134,10 +10248,10 @@
         <v>753</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>1494</v>
+        <v>1532</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>1495</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="44">
@@ -10146,7 +10260,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1496</v>
+        <v>1534</v>
       </c>
       <c r="C44" s="36">
         <v>1.0</v>
@@ -10155,19 +10269,19 @@
         <v>1021</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G44" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>1497</v>
+        <v>1535</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>1498</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="45">
@@ -10176,7 +10290,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1499</v>
+        <v>1537</v>
       </c>
       <c r="C45" s="36">
         <v>0.0</v>
@@ -10185,7 +10299,7 @@
         <v>1021</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F45" s="38" t="s">
         <v>753</v>
@@ -10194,10 +10308,10 @@
         <v>753</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>1500</v>
+        <v>1538</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>1501</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="46">
@@ -10206,7 +10320,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1502</v>
+        <v>1540</v>
       </c>
       <c r="C46" s="36">
         <v>1.0</v>
@@ -10215,19 +10329,19 @@
         <v>1021</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G46" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1503</v>
+        <v>1541</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1504</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="47">
@@ -10236,7 +10350,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1505</v>
+        <v>1543</v>
       </c>
       <c r="C47" s="36">
         <v>1.0</v>
@@ -10245,19 +10359,19 @@
         <v>1021</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G47" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H47" s="37" t="s">
-        <v>1506</v>
+        <v>1544</v>
       </c>
       <c r="I47" s="37" t="s">
-        <v>1507</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="48">
@@ -10266,7 +10380,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1508</v>
+        <v>1546</v>
       </c>
       <c r="C48" s="36">
         <v>0.0</v>
@@ -10275,7 +10389,7 @@
         <v>1021</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F48" s="38" t="s">
         <v>753</v>
@@ -10284,10 +10398,10 @@
         <v>753</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>1509</v>
+        <v>1547</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>1510</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="49">
@@ -10296,7 +10410,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1511</v>
+        <v>1549</v>
       </c>
       <c r="C49" s="36">
         <v>1.0</v>
@@ -10305,19 +10419,19 @@
         <v>1021</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G49" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>1512</v>
+        <v>1550</v>
       </c>
       <c r="I49" s="37" t="s">
-        <v>1513</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="50">
@@ -10326,7 +10440,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1514</v>
+        <v>1552</v>
       </c>
       <c r="C50" s="36">
         <v>0.0</v>
@@ -10335,7 +10449,7 @@
         <v>1021</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F50" s="38" t="s">
         <v>753</v>
@@ -10344,10 +10458,10 @@
         <v>753</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>1515</v>
+        <v>1553</v>
       </c>
       <c r="I50" s="37" t="s">
-        <v>1516</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="51">
@@ -10356,7 +10470,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1517</v>
+        <v>1555</v>
       </c>
       <c r="C51" s="36">
         <v>0.0</v>
@@ -10365,7 +10479,7 @@
         <v>1021</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F51" s="38" t="s">
         <v>753</v>
@@ -10374,10 +10488,10 @@
         <v>753</v>
       </c>
       <c r="H51" s="37" t="s">
-        <v>1518</v>
+        <v>1556</v>
       </c>
       <c r="I51" s="37" t="s">
-        <v>1519</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="52">
@@ -10386,7 +10500,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1520</v>
+        <v>1558</v>
       </c>
       <c r="C52" s="36">
         <v>1.0</v>
@@ -10395,19 +10509,19 @@
         <v>1021</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G52" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H52" s="37" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="I52" s="37" t="s">
-        <v>1522</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="53">
@@ -10416,7 +10530,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1523</v>
+        <v>1561</v>
       </c>
       <c r="C53" s="36">
         <v>1.0</v>
@@ -10425,19 +10539,19 @@
         <v>1021</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G53" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>1524</v>
+        <v>1562</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>1525</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="54">
@@ -10446,7 +10560,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1526</v>
+        <v>1564</v>
       </c>
       <c r="C54" s="36">
         <v>1.0</v>
@@ -10455,19 +10569,19 @@
         <v>1021</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G54" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>1527</v>
+        <v>1565</v>
       </c>
       <c r="I54" s="37" t="s">
-        <v>1528</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="55">
@@ -10476,7 +10590,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1529</v>
+        <v>1567</v>
       </c>
       <c r="C55" s="36">
         <v>0.0</v>
@@ -10485,7 +10599,7 @@
         <v>1021</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F55" s="38" t="s">
         <v>753</v>
@@ -10494,10 +10608,10 @@
         <v>753</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>1530</v>
+        <v>1568</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>1531</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="56">
@@ -10506,7 +10620,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1210</v>
+        <v>1248</v>
       </c>
       <c r="C56" s="36">
         <v>0.0</v>
@@ -10515,7 +10629,7 @@
         <v>1021</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F56" s="38" t="s">
         <v>753</v>
@@ -10524,10 +10638,10 @@
         <v>753</v>
       </c>
       <c r="H56" s="37" t="s">
-        <v>1532</v>
+        <v>1570</v>
       </c>
       <c r="I56" s="37" t="s">
-        <v>1533</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="57">
@@ -10536,7 +10650,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1534</v>
+        <v>1572</v>
       </c>
       <c r="C57" s="36">
         <v>0.0</v>
@@ -10545,7 +10659,7 @@
         <v>1021</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F57" s="38" t="s">
         <v>753</v>
@@ -10554,10 +10668,10 @@
         <v>753</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>1535</v>
+        <v>1573</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>1536</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="58">
@@ -10566,7 +10680,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1211</v>
+        <v>1249</v>
       </c>
       <c r="C58" s="36">
         <v>1.0</v>
@@ -10575,19 +10689,19 @@
         <v>1021</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G58" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>1537</v>
+        <v>1575</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>1538</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="59">
@@ -10605,7 +10719,7 @@
         <v>1021</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F59" s="38" t="s">
         <v>753</v>
@@ -10614,10 +10728,10 @@
         <v>753</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>1539</v>
+        <v>1577</v>
       </c>
       <c r="I59" s="37" t="s">
-        <v>1540</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="60">
@@ -10626,7 +10740,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1541</v>
+        <v>1579</v>
       </c>
       <c r="C60" s="36">
         <v>0.0</v>
@@ -10644,10 +10758,10 @@
         <v>753</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>1542</v>
+        <v>1580</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="61">
@@ -10656,7 +10770,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1544</v>
+        <v>1582</v>
       </c>
       <c r="C61" s="36">
         <v>0.0</v>
@@ -10674,10 +10788,10 @@
         <v>753</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>1545</v>
+        <v>1583</v>
       </c>
       <c r="I61" s="37" t="s">
-        <v>1546</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="62">
@@ -10686,7 +10800,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1547</v>
+        <v>1585</v>
       </c>
       <c r="C62" s="36">
         <v>0.0</v>
@@ -10704,10 +10818,10 @@
         <v>753</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>1548</v>
+        <v>1586</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>1549</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="63">
@@ -10725,7 +10839,7 @@
         <v>1021</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F63" s="38" t="s">
         <v>753</v>
@@ -10734,10 +10848,10 @@
         <v>753</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>1550</v>
+        <v>1588</v>
       </c>
       <c r="I63" s="37" t="s">
-        <v>1551</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="64">
@@ -10746,7 +10860,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1552</v>
+        <v>1590</v>
       </c>
       <c r="C64" s="36">
         <v>0.0</v>
@@ -10755,7 +10869,7 @@
         <v>1028</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F64" s="38" t="s">
         <v>753</v>
@@ -10764,10 +10878,10 @@
         <v>753</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>1553</v>
+        <v>1591</v>
       </c>
       <c r="I64" s="37" t="s">
-        <v>1553</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="65">
@@ -10776,7 +10890,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1554</v>
+        <v>1592</v>
       </c>
       <c r="C65" s="36">
         <v>0.0</v>
@@ -10785,7 +10899,7 @@
         <v>1029</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F65" s="38" t="s">
         <v>753</v>
@@ -10794,10 +10908,10 @@
         <v>753</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>1555</v>
+        <v>1593</v>
       </c>
       <c r="I65" s="37" t="s">
-        <v>1556</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="66">
@@ -10806,7 +10920,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1557</v>
+        <v>1595</v>
       </c>
       <c r="C66" s="36">
         <v>0.0</v>
@@ -10815,7 +10929,7 @@
         <v>1030</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F66" s="38" t="s">
         <v>753</v>
@@ -10824,10 +10938,10 @@
         <v>753</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>1558</v>
+        <v>1596</v>
       </c>
       <c r="I66" s="37" t="s">
-        <v>1559</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="67">
@@ -10836,7 +10950,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1560</v>
+        <v>1598</v>
       </c>
       <c r="C67" s="36">
         <v>0.0</v>
@@ -10845,7 +10959,7 @@
         <v>1031</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F67" s="38" t="s">
         <v>753</v>
@@ -10854,10 +10968,10 @@
         <v>753</v>
       </c>
       <c r="H67" s="37" t="s">
-        <v>1561</v>
+        <v>1599</v>
       </c>
       <c r="I67" s="37" t="s">
-        <v>1562</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="68">
@@ -10866,7 +10980,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1563</v>
+        <v>1601</v>
       </c>
       <c r="C68" s="36">
         <v>0.0</v>
@@ -10875,7 +10989,7 @@
         <v>1021</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F68" s="38" t="s">
         <v>753</v>
@@ -10884,10 +10998,10 @@
         <v>753</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="I68" s="37" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="69">
@@ -10896,7 +11010,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1566</v>
+        <v>1604</v>
       </c>
       <c r="C69" s="36">
         <v>1.0</v>
@@ -10905,19 +11019,19 @@
         <v>1021</v>
       </c>
       <c r="E69" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F69" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G69" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H69" s="37" t="s">
-        <v>1567</v>
+        <v>1605</v>
       </c>
       <c r="I69" s="37" t="s">
-        <v>1568</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="70">
@@ -10926,7 +11040,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1569</v>
+        <v>1607</v>
       </c>
       <c r="C70" s="36">
         <v>0.0</v>
@@ -10935,7 +11049,7 @@
         <v>1021</v>
       </c>
       <c r="E70" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F70" s="38" t="s">
         <v>753</v>
@@ -10944,10 +11058,10 @@
         <v>753</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="I70" s="37" t="s">
-        <v>1571</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="71">
@@ -10956,7 +11070,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1572</v>
+        <v>1610</v>
       </c>
       <c r="C71" s="36">
         <v>1.0</v>
@@ -10965,19 +11079,19 @@
         <v>1021</v>
       </c>
       <c r="E71" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G71" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H71" s="37" t="s">
-        <v>1573</v>
+        <v>1611</v>
       </c>
       <c r="I71" s="37" t="s">
-        <v>1574</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="72">
@@ -10986,7 +11100,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1575</v>
+        <v>1613</v>
       </c>
       <c r="C72" s="36">
         <v>0.0</v>
@@ -10995,7 +11109,7 @@
         <v>1021</v>
       </c>
       <c r="E72" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F72" s="38" t="s">
         <v>753</v>
@@ -11004,10 +11118,10 @@
         <v>753</v>
       </c>
       <c r="H72" s="37" t="s">
-        <v>1576</v>
+        <v>1614</v>
       </c>
       <c r="I72" s="37" t="s">
-        <v>1577</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="73">
@@ -11016,7 +11130,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>1578</v>
+        <v>1616</v>
       </c>
       <c r="C73" s="36">
         <v>1.0</v>
@@ -11025,19 +11139,19 @@
         <v>1021</v>
       </c>
       <c r="E73" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F73" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G73" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H73" s="37" t="s">
-        <v>1579</v>
+        <v>1617</v>
       </c>
       <c r="I73" s="37" t="s">
-        <v>1580</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="74">
@@ -11046,7 +11160,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>1581</v>
+        <v>1619</v>
       </c>
       <c r="C74" s="36">
         <v>0.0</v>
@@ -11055,7 +11169,7 @@
         <v>1021</v>
       </c>
       <c r="E74" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F74" s="38" t="s">
         <v>753</v>
@@ -11064,10 +11178,10 @@
         <v>753</v>
       </c>
       <c r="H74" s="37" t="s">
-        <v>1582</v>
+        <v>1620</v>
       </c>
       <c r="I74" s="37" t="s">
-        <v>1583</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="75">
@@ -11076,7 +11190,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>1584</v>
+        <v>1622</v>
       </c>
       <c r="C75" s="36">
         <v>1.0</v>
@@ -11085,19 +11199,19 @@
         <v>1021</v>
       </c>
       <c r="E75" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F75" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G75" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H75" s="37" t="s">
-        <v>1585</v>
+        <v>1623</v>
       </c>
       <c r="I75" s="37" t="s">
-        <v>1586</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="76">
@@ -11106,7 +11220,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1587</v>
+        <v>1625</v>
       </c>
       <c r="C76" s="36">
         <v>0.0</v>
@@ -11115,7 +11229,7 @@
         <v>1021</v>
       </c>
       <c r="E76" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F76" s="38" t="s">
         <v>753</v>
@@ -11124,10 +11238,10 @@
         <v>753</v>
       </c>
       <c r="H76" s="37" t="s">
-        <v>1588</v>
+        <v>1626</v>
       </c>
       <c r="I76" s="37" t="s">
-        <v>1589</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="77">
@@ -11136,7 +11250,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="C77" s="36">
         <v>1.0</v>
@@ -11145,19 +11259,19 @@
         <v>1021</v>
       </c>
       <c r="E77" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F77" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G77" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H77" s="37" t="s">
-        <v>1591</v>
+        <v>1629</v>
       </c>
       <c r="I77" s="37" t="s">
-        <v>1592</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="78">
@@ -11166,7 +11280,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>1593</v>
+        <v>1631</v>
       </c>
       <c r="C78" s="36">
         <v>0.0</v>
@@ -11175,7 +11289,7 @@
         <v>1021</v>
       </c>
       <c r="E78" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F78" s="38" t="s">
         <v>753</v>
@@ -11184,10 +11298,10 @@
         <v>753</v>
       </c>
       <c r="H78" s="37" t="s">
-        <v>1594</v>
+        <v>1632</v>
       </c>
       <c r="I78" s="37" t="s">
-        <v>1595</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="79">
@@ -11196,7 +11310,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>1222</v>
+        <v>1260</v>
       </c>
       <c r="C79" s="36">
         <v>0.0</v>
@@ -11205,7 +11319,7 @@
         <v>1021</v>
       </c>
       <c r="E79" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F79" s="38" t="s">
         <v>753</v>
@@ -11214,10 +11328,10 @@
         <v>753</v>
       </c>
       <c r="H79" s="37" t="s">
-        <v>1596</v>
+        <v>1634</v>
       </c>
       <c r="I79" s="37" t="s">
-        <v>1597</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="80">
@@ -11226,7 +11340,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>1598</v>
+        <v>1636</v>
       </c>
       <c r="C80" s="36">
         <v>1.0</v>
@@ -11235,19 +11349,19 @@
         <v>1021</v>
       </c>
       <c r="E80" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F80" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G80" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H80" s="37" t="s">
-        <v>1599</v>
+        <v>1637</v>
       </c>
       <c r="I80" s="37" t="s">
-        <v>1600</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="81">
@@ -11256,7 +11370,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1601</v>
+        <v>1639</v>
       </c>
       <c r="C81" s="36">
         <v>1.0</v>
@@ -11265,19 +11379,19 @@
         <v>1021</v>
       </c>
       <c r="E81" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F81" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G81" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H81" s="37" t="s">
-        <v>1602</v>
+        <v>1640</v>
       </c>
       <c r="I81" s="37" t="s">
-        <v>1603</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="82">
@@ -11286,7 +11400,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>1604</v>
+        <v>1642</v>
       </c>
       <c r="C82" s="36">
         <v>1.0</v>
@@ -11295,19 +11409,19 @@
         <v>1021</v>
       </c>
       <c r="E82" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F82" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G82" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H82" s="37" t="s">
-        <v>1605</v>
+        <v>1643</v>
       </c>
       <c r="I82" s="37" t="s">
-        <v>1606</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="83">
@@ -11316,7 +11430,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>1607</v>
+        <v>1645</v>
       </c>
       <c r="C83" s="36">
         <v>0.0</v>
@@ -11325,7 +11439,7 @@
         <v>1021</v>
       </c>
       <c r="E83" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F83" s="38" t="s">
         <v>753</v>
@@ -11334,10 +11448,10 @@
         <v>753</v>
       </c>
       <c r="H83" s="37" t="s">
-        <v>1608</v>
+        <v>1646</v>
       </c>
       <c r="I83" s="37" t="s">
-        <v>1609</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="84">
@@ -11346,7 +11460,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>1610</v>
+        <v>1648</v>
       </c>
       <c r="C84" s="36">
         <v>0.0</v>
@@ -11355,7 +11469,7 @@
         <v>1021</v>
       </c>
       <c r="E84" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F84" s="38" t="s">
         <v>753</v>
@@ -11364,10 +11478,10 @@
         <v>753</v>
       </c>
       <c r="H84" s="37" t="s">
-        <v>1611</v>
+        <v>1649</v>
       </c>
       <c r="I84" s="37" t="s">
-        <v>1612</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="85">
@@ -11376,7 +11490,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="36" t="s">
-        <v>1613</v>
+        <v>1651</v>
       </c>
       <c r="C85" s="36">
         <v>0.0</v>
@@ -11385,7 +11499,7 @@
         <v>1021</v>
       </c>
       <c r="E85" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F85" s="38" t="s">
         <v>753</v>
@@ -11394,10 +11508,10 @@
         <v>753</v>
       </c>
       <c r="H85" s="37" t="s">
-        <v>1614</v>
+        <v>1652</v>
       </c>
       <c r="I85" s="37" t="s">
-        <v>1615</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="86">
@@ -11415,7 +11529,7 @@
         <v>1021</v>
       </c>
       <c r="E86" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F86" s="38" t="s">
         <v>753</v>
@@ -11424,10 +11538,10 @@
         <v>753</v>
       </c>
       <c r="H86" s="37" t="s">
-        <v>1616</v>
+        <v>1654</v>
       </c>
       <c r="I86" s="37" t="s">
-        <v>1617</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="87">
@@ -11445,7 +11559,7 @@
         <v>1021</v>
       </c>
       <c r="E87" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F87" s="38" t="s">
         <v>753</v>
@@ -11454,10 +11568,10 @@
         <v>753</v>
       </c>
       <c r="H87" s="37" t="s">
-        <v>1618</v>
+        <v>1656</v>
       </c>
       <c r="I87" s="37" t="s">
-        <v>1618</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="88">
@@ -11475,7 +11589,7 @@
         <v>1021</v>
       </c>
       <c r="E88" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F88" s="38" t="s">
         <v>753</v>
@@ -11484,10 +11598,10 @@
         <v>753</v>
       </c>
       <c r="H88" s="37" t="s">
-        <v>1619</v>
+        <v>1657</v>
       </c>
       <c r="I88" s="37" t="s">
-        <v>1620</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="89">
@@ -11505,7 +11619,7 @@
         <v>1021</v>
       </c>
       <c r="E89" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F89" s="38" t="s">
         <v>753</v>
@@ -11514,10 +11628,10 @@
         <v>753</v>
       </c>
       <c r="H89" s="37" t="s">
-        <v>1621</v>
+        <v>1659</v>
       </c>
       <c r="I89" s="37" t="s">
-        <v>1622</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="90">
@@ -11535,7 +11649,7 @@
         <v>1021</v>
       </c>
       <c r="E90" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F90" s="38" t="s">
         <v>753</v>
@@ -11544,10 +11658,10 @@
         <v>753</v>
       </c>
       <c r="H90" s="37" t="s">
-        <v>1623</v>
+        <v>1661</v>
       </c>
       <c r="I90" s="37" t="s">
-        <v>1624</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="91">
@@ -11565,7 +11679,7 @@
         <v>1021</v>
       </c>
       <c r="E91" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F91" s="38" t="s">
         <v>753</v>
@@ -11574,10 +11688,10 @@
         <v>753</v>
       </c>
       <c r="H91" s="37" t="s">
-        <v>1625</v>
+        <v>1663</v>
       </c>
       <c r="I91" s="37" t="s">
-        <v>1626</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="92">
@@ -11595,7 +11709,7 @@
         <v>1021</v>
       </c>
       <c r="E92" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F92" s="38" t="s">
         <v>753</v>
@@ -11604,10 +11718,10 @@
         <v>753</v>
       </c>
       <c r="H92" s="37" t="s">
-        <v>1627</v>
+        <v>1665</v>
       </c>
       <c r="I92" s="37" t="s">
-        <v>1628</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="93">
@@ -11625,7 +11739,7 @@
         <v>1021</v>
       </c>
       <c r="E93" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F93" s="38" t="s">
         <v>753</v>
@@ -11634,10 +11748,10 @@
         <v>753</v>
       </c>
       <c r="H93" s="37" t="s">
-        <v>1629</v>
+        <v>1667</v>
       </c>
       <c r="I93" s="37" t="s">
-        <v>1630</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="94">
@@ -11655,7 +11769,7 @@
         <v>1021</v>
       </c>
       <c r="E94" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F94" s="38" t="s">
         <v>753</v>
@@ -11664,10 +11778,10 @@
         <v>753</v>
       </c>
       <c r="H94" s="37" t="s">
-        <v>1631</v>
+        <v>1669</v>
       </c>
       <c r="I94" s="37" t="s">
-        <v>1632</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="95">
@@ -11685,7 +11799,7 @@
         <v>1026</v>
       </c>
       <c r="E95" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F95" s="38" t="s">
         <v>753</v>
@@ -11694,10 +11808,10 @@
         <v>753</v>
       </c>
       <c r="H95" s="37" t="s">
-        <v>1633</v>
+        <v>1671</v>
       </c>
       <c r="I95" s="37" t="s">
-        <v>1634</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="96">
@@ -11715,7 +11829,7 @@
         <v>1021</v>
       </c>
       <c r="E96" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F96" s="38" t="s">
         <v>753</v>
@@ -11724,10 +11838,10 @@
         <v>753</v>
       </c>
       <c r="H96" s="37" t="s">
-        <v>1635</v>
+        <v>1673</v>
       </c>
       <c r="I96" s="37" t="s">
-        <v>1636</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="97">
@@ -11745,7 +11859,7 @@
         <v>1021</v>
       </c>
       <c r="E97" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F97" s="38" t="s">
         <v>753</v>
@@ -11754,10 +11868,10 @@
         <v>753</v>
       </c>
       <c r="H97" s="37" t="s">
-        <v>1637</v>
+        <v>1675</v>
       </c>
       <c r="I97" s="37" t="s">
-        <v>1638</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="98">
@@ -11775,7 +11889,7 @@
         <v>1021</v>
       </c>
       <c r="E98" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F98" s="38" t="s">
         <v>753</v>
@@ -11784,10 +11898,10 @@
         <v>753</v>
       </c>
       <c r="H98" s="37" t="s">
-        <v>1639</v>
+        <v>1677</v>
       </c>
       <c r="I98" s="37" t="s">
-        <v>1640</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="99">
@@ -11814,10 +11928,10 @@
         <v>753</v>
       </c>
       <c r="H99" s="37" t="s">
-        <v>1641</v>
+        <v>1679</v>
       </c>
       <c r="I99" s="37" t="s">
-        <v>1642</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="100">
@@ -11835,7 +11949,7 @@
         <v>1021</v>
       </c>
       <c r="E100" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F100" s="38" t="s">
         <v>753</v>
@@ -11844,10 +11958,10 @@
         <v>753</v>
       </c>
       <c r="H100" s="37" t="s">
-        <v>1643</v>
+        <v>1681</v>
       </c>
       <c r="I100" s="37" t="s">
-        <v>1644</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="101">
@@ -11865,7 +11979,7 @@
         <v>1021</v>
       </c>
       <c r="E101" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F101" s="38" t="s">
         <v>753</v>
@@ -11874,10 +11988,10 @@
         <v>753</v>
       </c>
       <c r="H101" s="37" t="s">
-        <v>1645</v>
+        <v>1683</v>
       </c>
       <c r="I101" s="37" t="s">
-        <v>1646</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="102">
@@ -11895,7 +12009,7 @@
         <v>1021</v>
       </c>
       <c r="E102" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F102" s="38" t="s">
         <v>753</v>
@@ -11904,10 +12018,10 @@
         <v>753</v>
       </c>
       <c r="H102" s="37" t="s">
-        <v>1647</v>
+        <v>1685</v>
       </c>
       <c r="I102" s="37" t="s">
-        <v>1648</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="103">
@@ -11916,7 +12030,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="36" t="s">
-        <v>1649</v>
+        <v>1687</v>
       </c>
       <c r="C103" s="36">
         <v>0.0</v>
@@ -11925,7 +12039,7 @@
         <v>1021</v>
       </c>
       <c r="E103" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F103" s="38" t="s">
         <v>753</v>
@@ -11934,10 +12048,10 @@
         <v>753</v>
       </c>
       <c r="H103" s="37" t="s">
-        <v>1650</v>
+        <v>1688</v>
       </c>
       <c r="I103" s="37" t="s">
-        <v>1651</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="104">
@@ -11946,7 +12060,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>1652</v>
+        <v>1690</v>
       </c>
       <c r="C104" s="36">
         <v>1.0</v>
@@ -11955,19 +12069,19 @@
         <v>1021</v>
       </c>
       <c r="E104" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F104" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G104" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H104" s="37" t="s">
-        <v>1653</v>
+        <v>1691</v>
       </c>
       <c r="I104" s="37" t="s">
-        <v>1654</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="105">
@@ -11976,7 +12090,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>1655</v>
+        <v>1693</v>
       </c>
       <c r="C105" s="36">
         <v>0.0</v>
@@ -11985,7 +12099,7 @@
         <v>1021</v>
       </c>
       <c r="E105" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F105" s="38" t="s">
         <v>753</v>
@@ -11994,10 +12108,10 @@
         <v>753</v>
       </c>
       <c r="H105" s="37" t="s">
-        <v>1656</v>
+        <v>1694</v>
       </c>
       <c r="I105" s="37" t="s">
-        <v>1657</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="106">
@@ -12006,7 +12120,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>1658</v>
+        <v>1696</v>
       </c>
       <c r="C106" s="36">
         <v>1.0</v>
@@ -12015,19 +12129,19 @@
         <v>1021</v>
       </c>
       <c r="E106" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F106" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G106" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H106" s="37" t="s">
-        <v>1659</v>
+        <v>1697</v>
       </c>
       <c r="I106" s="37" t="s">
-        <v>1660</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="107">
@@ -12036,7 +12150,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>1661</v>
+        <v>1699</v>
       </c>
       <c r="C107" s="36">
         <v>0.0</v>
@@ -12045,7 +12159,7 @@
         <v>1021</v>
       </c>
       <c r="E107" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F107" s="38" t="s">
         <v>753</v>
@@ -12054,10 +12168,10 @@
         <v>753</v>
       </c>
       <c r="H107" s="37" t="s">
-        <v>1662</v>
+        <v>1700</v>
       </c>
       <c r="I107" s="37" t="s">
-        <v>1663</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="108">
@@ -12066,7 +12180,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>1664</v>
+        <v>1702</v>
       </c>
       <c r="C108" s="36">
         <v>1.0</v>
@@ -12075,19 +12189,19 @@
         <v>1021</v>
       </c>
       <c r="E108" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F108" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G108" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H108" s="37" t="s">
-        <v>1665</v>
+        <v>1703</v>
       </c>
       <c r="I108" s="37" t="s">
-        <v>1665</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="109">
@@ -12096,7 +12210,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>1666</v>
+        <v>1704</v>
       </c>
       <c r="C109" s="36">
         <v>0.0</v>
@@ -12105,7 +12219,7 @@
         <v>1021</v>
       </c>
       <c r="E109" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F109" s="38" t="s">
         <v>753</v>
@@ -12114,10 +12228,10 @@
         <v>753</v>
       </c>
       <c r="H109" s="37" t="s">
-        <v>1667</v>
+        <v>1705</v>
       </c>
       <c r="I109" s="37" t="s">
-        <v>1668</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="110">
@@ -12126,7 +12240,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>1669</v>
+        <v>1707</v>
       </c>
       <c r="C110" s="36">
         <v>1.0</v>
@@ -12135,19 +12249,19 @@
         <v>1021</v>
       </c>
       <c r="E110" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F110" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G110" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H110" s="37" t="s">
-        <v>1670</v>
+        <v>1708</v>
       </c>
       <c r="I110" s="37" t="s">
-        <v>1671</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="111">
@@ -12156,7 +12270,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>1672</v>
+        <v>1710</v>
       </c>
       <c r="C111" s="36">
         <v>0.0</v>
@@ -12165,7 +12279,7 @@
         <v>1021</v>
       </c>
       <c r="E111" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F111" s="38" t="s">
         <v>753</v>
@@ -12174,10 +12288,10 @@
         <v>753</v>
       </c>
       <c r="H111" s="37" t="s">
-        <v>1673</v>
+        <v>1711</v>
       </c>
       <c r="I111" s="37" t="s">
-        <v>1674</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="112">
@@ -12186,7 +12300,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="36" t="s">
-        <v>1675</v>
+        <v>1713</v>
       </c>
       <c r="C112" s="36">
         <v>1.0</v>
@@ -12195,19 +12309,19 @@
         <v>1021</v>
       </c>
       <c r="E112" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F112" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G112" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H112" s="37" t="s">
-        <v>1676</v>
+        <v>1714</v>
       </c>
       <c r="I112" s="37" t="s">
-        <v>1677</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="113">
@@ -12216,7 +12330,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>1678</v>
+        <v>1716</v>
       </c>
       <c r="C113" s="36">
         <v>0.0</v>
@@ -12225,7 +12339,7 @@
         <v>1021</v>
       </c>
       <c r="E113" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F113" s="38" t="s">
         <v>753</v>
@@ -12234,10 +12348,10 @@
         <v>753</v>
       </c>
       <c r="H113" s="37" t="s">
-        <v>1679</v>
+        <v>1717</v>
       </c>
       <c r="I113" s="37" t="s">
-        <v>1680</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="114">
@@ -12246,7 +12360,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>1230</v>
+        <v>1268</v>
       </c>
       <c r="C114" s="36">
         <v>0.0</v>
@@ -12255,7 +12369,7 @@
         <v>1021</v>
       </c>
       <c r="E114" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F114" s="38" t="s">
         <v>753</v>
@@ -12264,10 +12378,10 @@
         <v>753</v>
       </c>
       <c r="H114" s="37" t="s">
-        <v>1681</v>
+        <v>1719</v>
       </c>
       <c r="I114" s="37" t="s">
-        <v>1682</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="115">
@@ -12276,7 +12390,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>1683</v>
+        <v>1721</v>
       </c>
       <c r="C115" s="36">
         <v>0.0</v>
@@ -12285,7 +12399,7 @@
         <v>1021</v>
       </c>
       <c r="E115" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F115" s="38" t="s">
         <v>753</v>
@@ -12294,10 +12408,10 @@
         <v>753</v>
       </c>
       <c r="H115" s="37" t="s">
-        <v>1684</v>
+        <v>1722</v>
       </c>
       <c r="I115" s="37" t="s">
-        <v>1685</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="116">
@@ -12306,7 +12420,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="36" t="s">
-        <v>1686</v>
+        <v>1724</v>
       </c>
       <c r="C116" s="36">
         <v>1.0</v>
@@ -12315,19 +12429,19 @@
         <v>1021</v>
       </c>
       <c r="E116" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F116" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G116" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H116" s="37" t="s">
-        <v>1687</v>
+        <v>1725</v>
       </c>
       <c r="I116" s="37" t="s">
-        <v>1688</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="117">
@@ -12345,7 +12459,7 @@
         <v>1021</v>
       </c>
       <c r="E117" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F117" s="38" t="s">
         <v>753</v>
@@ -12354,10 +12468,10 @@
         <v>753</v>
       </c>
       <c r="H117" s="37" t="s">
-        <v>1689</v>
+        <v>1727</v>
       </c>
       <c r="I117" s="37" t="s">
-        <v>1690</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="118">
@@ -12375,7 +12489,7 @@
         <v>1024</v>
       </c>
       <c r="E118" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F118" s="38" t="s">
         <v>753</v>
@@ -12384,10 +12498,10 @@
         <v>753</v>
       </c>
       <c r="H118" s="37" t="s">
-        <v>1691</v>
+        <v>1729</v>
       </c>
       <c r="I118" s="37" t="s">
-        <v>1692</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="119">
@@ -12405,7 +12519,7 @@
         <v>1021</v>
       </c>
       <c r="E119" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F119" s="38" t="s">
         <v>753</v>
@@ -12414,10 +12528,10 @@
         <v>753</v>
       </c>
       <c r="H119" s="37" t="s">
-        <v>1693</v>
+        <v>1731</v>
       </c>
       <c r="I119" s="37" t="s">
-        <v>1694</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="120">
@@ -12435,7 +12549,7 @@
         <v>1021</v>
       </c>
       <c r="E120" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F120" s="38" t="s">
         <v>753</v>
@@ -12444,10 +12558,10 @@
         <v>753</v>
       </c>
       <c r="H120" s="37" t="s">
-        <v>1695</v>
+        <v>1733</v>
       </c>
       <c r="I120" s="37" t="s">
-        <v>1696</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="121">
@@ -12456,7 +12570,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>1232</v>
+        <v>1270</v>
       </c>
       <c r="C121" s="36">
         <v>0.0</v>
@@ -12465,7 +12579,7 @@
         <v>1021</v>
       </c>
       <c r="E121" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F121" s="38" t="s">
         <v>753</v>
@@ -12474,10 +12588,10 @@
         <v>753</v>
       </c>
       <c r="H121" s="37" t="s">
-        <v>1697</v>
+        <v>1735</v>
       </c>
       <c r="I121" s="37" t="s">
-        <v>1698</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="122">
@@ -12486,7 +12600,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="36" t="s">
-        <v>1233</v>
+        <v>1271</v>
       </c>
       <c r="C122" s="36">
         <v>0.0</v>
@@ -12495,7 +12609,7 @@
         <v>1021</v>
       </c>
       <c r="E122" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F122" s="38" t="s">
         <v>753</v>
@@ -12504,10 +12618,10 @@
         <v>753</v>
       </c>
       <c r="H122" s="37" t="s">
-        <v>1699</v>
+        <v>1737</v>
       </c>
       <c r="I122" s="37" t="s">
-        <v>1700</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="123">
@@ -12516,7 +12630,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>1701</v>
+        <v>1739</v>
       </c>
       <c r="C123" s="36">
         <v>0.0</v>
@@ -12525,7 +12639,7 @@
         <v>1021</v>
       </c>
       <c r="E123" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F123" s="38" t="s">
         <v>753</v>
@@ -12534,10 +12648,10 @@
         <v>753</v>
       </c>
       <c r="H123" s="37" t="s">
-        <v>1702</v>
+        <v>1740</v>
       </c>
       <c r="I123" s="37" t="s">
-        <v>1703</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="124">
@@ -12546,7 +12660,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="36" t="s">
-        <v>1704</v>
+        <v>1742</v>
       </c>
       <c r="C124" s="36">
         <v>0.0</v>
@@ -12555,7 +12669,7 @@
         <v>1021</v>
       </c>
       <c r="E124" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F124" s="38" t="s">
         <v>753</v>
@@ -12564,10 +12678,10 @@
         <v>753</v>
       </c>
       <c r="H124" s="37" t="s">
-        <v>1705</v>
+        <v>1743</v>
       </c>
       <c r="I124" s="37" t="s">
-        <v>1706</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="125">
@@ -12585,7 +12699,7 @@
         <v>1021</v>
       </c>
       <c r="E125" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F125" s="38" t="s">
         <v>753</v>
@@ -12594,10 +12708,10 @@
         <v>753</v>
       </c>
       <c r="H125" s="37" t="s">
-        <v>1707</v>
+        <v>1745</v>
       </c>
       <c r="I125" s="37" t="s">
-        <v>1708</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="126">
@@ -12615,7 +12729,7 @@
         <v>1021</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F126" s="38" t="s">
         <v>753</v>
@@ -12624,10 +12738,10 @@
         <v>753</v>
       </c>
       <c r="H126" s="37" t="s">
-        <v>1709</v>
+        <v>1747</v>
       </c>
       <c r="I126" s="37" t="s">
-        <v>1710</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="127">
@@ -12636,7 +12750,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="36" t="s">
-        <v>1711</v>
+        <v>1749</v>
       </c>
       <c r="C127" s="36">
         <v>0.0</v>
@@ -12645,19 +12759,19 @@
         <v>1043</v>
       </c>
       <c r="E127" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F127" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G127" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H127" s="37" t="s">
-        <v>1712</v>
+        <v>1750</v>
       </c>
       <c r="I127" s="37" t="s">
-        <v>1712</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="128">
@@ -12666,7 +12780,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="36" t="s">
-        <v>1713</v>
+        <v>1751</v>
       </c>
       <c r="C128" s="36">
         <v>1.0</v>
@@ -12675,19 +12789,19 @@
         <v>1045</v>
       </c>
       <c r="E128" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F128" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G128" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H128" s="37" t="s">
-        <v>1714</v>
+        <v>1752</v>
       </c>
       <c r="I128" s="37" t="s">
-        <v>1714</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="129">
@@ -12696,7 +12810,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="36" t="s">
-        <v>1715</v>
+        <v>1753</v>
       </c>
       <c r="C129" s="36">
         <v>0.0</v>
@@ -12705,19 +12819,19 @@
         <v>1047</v>
       </c>
       <c r="E129" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F129" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G129" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H129" s="37" t="s">
-        <v>1716</v>
+        <v>1754</v>
       </c>
       <c r="I129" s="37" t="s">
-        <v>1716</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="130">
@@ -12726,7 +12840,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="36" t="s">
-        <v>1717</v>
+        <v>1755</v>
       </c>
       <c r="C130" s="36">
         <v>1.0</v>
@@ -12735,19 +12849,19 @@
         <v>1049</v>
       </c>
       <c r="E130" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F130" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G130" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H130" s="37" t="s">
-        <v>1718</v>
+        <v>1756</v>
       </c>
       <c r="I130" s="37" t="s">
-        <v>1718</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="131">
@@ -12756,7 +12870,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="36" t="s">
-        <v>1719</v>
+        <v>1757</v>
       </c>
       <c r="C131" s="36">
         <v>0.0</v>
@@ -12765,19 +12879,19 @@
         <v>1051</v>
       </c>
       <c r="E131" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F131" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G131" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H131" s="37" t="s">
-        <v>1720</v>
+        <v>1758</v>
       </c>
       <c r="I131" s="37" t="s">
-        <v>1720</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="132">
@@ -12786,7 +12900,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="36" t="s">
-        <v>1721</v>
+        <v>1759</v>
       </c>
       <c r="C132" s="36">
         <v>1.0</v>
@@ -12795,19 +12909,19 @@
         <v>1053</v>
       </c>
       <c r="E132" s="44" t="s">
-        <v>1722</v>
+        <v>1760</v>
       </c>
       <c r="F132" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G132" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H132" s="37" t="s">
-        <v>1723</v>
+        <v>1761</v>
       </c>
       <c r="I132" s="37" t="s">
-        <v>1723</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="133">
@@ -12816,7 +12930,7 @@
         <v>131</v>
       </c>
       <c r="B133" s="36" t="s">
-        <v>1724</v>
+        <v>1762</v>
       </c>
       <c r="C133" s="36">
         <v>0.0</v>
@@ -12825,19 +12939,19 @@
         <v>1055</v>
       </c>
       <c r="E133" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F133" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G133" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H133" s="37" t="s">
-        <v>1725</v>
+        <v>1763</v>
       </c>
       <c r="I133" s="37" t="s">
-        <v>1725</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="134">
@@ -12846,7 +12960,7 @@
         <v>132</v>
       </c>
       <c r="B134" s="36" t="s">
-        <v>1726</v>
+        <v>1764</v>
       </c>
       <c r="C134" s="36">
         <v>1.0</v>
@@ -12855,19 +12969,19 @@
         <v>1057</v>
       </c>
       <c r="E134" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F134" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G134" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H134" s="37" t="s">
-        <v>1727</v>
+        <v>1765</v>
       </c>
       <c r="I134" s="37" t="s">
-        <v>1727</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="135">
@@ -12876,7 +12990,7 @@
         <v>133</v>
       </c>
       <c r="B135" s="36" t="s">
-        <v>1728</v>
+        <v>1766</v>
       </c>
       <c r="C135" s="36">
         <v>0.0</v>
@@ -12885,19 +12999,19 @@
         <v>1021</v>
       </c>
       <c r="E135" s="44" t="s">
-        <v>1729</v>
+        <v>1767</v>
       </c>
       <c r="F135" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G135" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H135" s="37" t="s">
-        <v>1730</v>
+        <v>1768</v>
       </c>
       <c r="I135" s="37" t="s">
-        <v>1730</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="136">
@@ -12906,7 +13020,7 @@
         <v>134</v>
       </c>
       <c r="B136" s="36" t="s">
-        <v>1242</v>
+        <v>1280</v>
       </c>
       <c r="C136" s="36">
         <v>0.0</v>
@@ -12915,19 +13029,19 @@
         <v>1059</v>
       </c>
       <c r="E136" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F136" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G136" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H136" s="37" t="s">
-        <v>1731</v>
+        <v>1769</v>
       </c>
       <c r="I136" s="37" t="s">
-        <v>1732</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="137">
@@ -12936,7 +13050,7 @@
         <v>135</v>
       </c>
       <c r="B137" s="36" t="s">
-        <v>1733</v>
+        <v>1771</v>
       </c>
       <c r="C137" s="36">
         <v>1.0</v>
@@ -12945,19 +13059,19 @@
         <v>1039</v>
       </c>
       <c r="E137" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F137" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G137" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H137" s="37" t="s">
-        <v>1734</v>
+        <v>1772</v>
       </c>
       <c r="I137" s="37" t="s">
-        <v>1734</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="138">
@@ -12966,7 +13080,7 @@
         <v>136</v>
       </c>
       <c r="B138" s="36" t="s">
-        <v>1735</v>
+        <v>1773</v>
       </c>
       <c r="C138" s="36">
         <v>1.0</v>
@@ -12975,19 +13089,19 @@
         <v>1041</v>
       </c>
       <c r="E138" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F138" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G138" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H138" s="37" t="s">
-        <v>1736</v>
+        <v>1774</v>
       </c>
       <c r="I138" s="37" t="s">
-        <v>1736</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="139">
@@ -12996,7 +13110,7 @@
         <v>137</v>
       </c>
       <c r="B139" s="36" t="s">
-        <v>1737</v>
+        <v>1775</v>
       </c>
       <c r="C139" s="36">
         <v>0.0</v>
@@ -13005,19 +13119,19 @@
         <v>1061</v>
       </c>
       <c r="E139" s="44" t="s">
-        <v>1738</v>
+        <v>1776</v>
       </c>
       <c r="F139" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G139" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H139" s="37" t="s">
-        <v>1739</v>
+        <v>1777</v>
       </c>
       <c r="I139" s="37" t="s">
-        <v>1739</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="140">
@@ -13026,7 +13140,7 @@
         <v>138</v>
       </c>
       <c r="B140" s="36" t="s">
-        <v>1740</v>
+        <v>1778</v>
       </c>
       <c r="C140" s="36">
         <v>1.0</v>
@@ -13035,19 +13149,19 @@
         <v>1063</v>
       </c>
       <c r="E140" s="44" t="s">
-        <v>1722</v>
+        <v>1760</v>
       </c>
       <c r="F140" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G140" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H140" s="37" t="s">
-        <v>1741</v>
+        <v>1779</v>
       </c>
       <c r="I140" s="37" t="s">
-        <v>1741</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="141">
@@ -13056,7 +13170,7 @@
         <v>139</v>
       </c>
       <c r="B141" s="36" t="s">
-        <v>1742</v>
+        <v>1780</v>
       </c>
       <c r="C141" s="36">
         <v>0.0</v>
@@ -13065,19 +13179,19 @@
         <v>1065</v>
       </c>
       <c r="E141" s="44" t="s">
-        <v>1738</v>
+        <v>1776</v>
       </c>
       <c r="F141" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G141" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H141" s="37" t="s">
-        <v>1743</v>
+        <v>1781</v>
       </c>
       <c r="I141" s="37" t="s">
-        <v>1743</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="142">
@@ -13086,7 +13200,7 @@
         <v>140</v>
       </c>
       <c r="B142" s="36" t="s">
-        <v>1744</v>
+        <v>1782</v>
       </c>
       <c r="C142" s="36">
         <v>1.0</v>
@@ -13095,19 +13209,19 @@
         <v>1067</v>
       </c>
       <c r="E142" s="44" t="s">
-        <v>1729</v>
+        <v>1767</v>
       </c>
       <c r="F142" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G142" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H142" s="37" t="s">
-        <v>1745</v>
+        <v>1783</v>
       </c>
       <c r="I142" s="37" t="s">
-        <v>1745</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="143">
@@ -13116,7 +13230,7 @@
         <v>141</v>
       </c>
       <c r="B143" s="36" t="s">
-        <v>1746</v>
+        <v>1784</v>
       </c>
       <c r="C143" s="36">
         <v>0.0</v>
@@ -13125,19 +13239,19 @@
         <v>1069</v>
       </c>
       <c r="E143" s="44" t="s">
-        <v>1738</v>
+        <v>1776</v>
       </c>
       <c r="F143" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G143" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H143" s="37" t="s">
-        <v>1747</v>
+        <v>1785</v>
       </c>
       <c r="I143" s="37" t="s">
-        <v>1747</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="144">
@@ -13146,7 +13260,7 @@
         <v>142</v>
       </c>
       <c r="B144" s="36" t="s">
-        <v>1748</v>
+        <v>1786</v>
       </c>
       <c r="C144" s="36">
         <v>1.0</v>
@@ -13155,19 +13269,19 @@
         <v>1071</v>
       </c>
       <c r="E144" s="44" t="s">
-        <v>1729</v>
+        <v>1767</v>
       </c>
       <c r="F144" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G144" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H144" s="37" t="s">
-        <v>1749</v>
+        <v>1787</v>
       </c>
       <c r="I144" s="37" t="s">
-        <v>1749</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="145">
@@ -13176,7 +13290,7 @@
         <v>143</v>
       </c>
       <c r="B145" s="36" t="s">
-        <v>1750</v>
+        <v>1788</v>
       </c>
       <c r="C145" s="36">
         <v>0.0</v>
@@ -13185,19 +13299,19 @@
         <v>1073</v>
       </c>
       <c r="E145" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F145" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G145" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H145" s="37" t="s">
-        <v>1751</v>
+        <v>1789</v>
       </c>
       <c r="I145" s="37" t="s">
-        <v>1751</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="146">
@@ -13206,7 +13320,7 @@
         <v>144</v>
       </c>
       <c r="B146" s="36" t="s">
-        <v>1752</v>
+        <v>1790</v>
       </c>
       <c r="C146" s="36">
         <v>1.0</v>
@@ -13215,19 +13329,19 @@
         <v>1075</v>
       </c>
       <c r="E146" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F146" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G146" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H146" s="37" t="s">
-        <v>1753</v>
+        <v>1791</v>
       </c>
       <c r="I146" s="37" t="s">
-        <v>1753</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="147">
@@ -13236,7 +13350,7 @@
         <v>145</v>
       </c>
       <c r="B147" s="36" t="s">
-        <v>1252</v>
+        <v>1290</v>
       </c>
       <c r="C147" s="36">
         <v>1.0</v>
@@ -13245,19 +13359,19 @@
         <v>1077</v>
       </c>
       <c r="E147" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F147" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G147" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H147" s="37" t="s">
-        <v>1754</v>
+        <v>1792</v>
       </c>
       <c r="I147" s="37" t="s">
-        <v>1754</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="148">
@@ -13266,7 +13380,7 @@
         <v>146</v>
       </c>
       <c r="B148" s="36" t="s">
-        <v>1755</v>
+        <v>1793</v>
       </c>
       <c r="C148" s="36">
         <v>0.0</v>
@@ -13275,19 +13389,19 @@
         <v>1095</v>
       </c>
       <c r="E148" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F148" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G148" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H148" s="37" t="s">
-        <v>1756</v>
+        <v>1794</v>
       </c>
       <c r="I148" s="37" t="s">
-        <v>1756</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="149">
@@ -13296,7 +13410,7 @@
         <v>147</v>
       </c>
       <c r="B149" s="36" t="s">
-        <v>1757</v>
+        <v>1795</v>
       </c>
       <c r="C149" s="36">
         <v>1.0</v>
@@ -13305,19 +13419,19 @@
         <v>1097</v>
       </c>
       <c r="E149" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F149" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G149" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H149" s="37" t="s">
-        <v>1758</v>
+        <v>1796</v>
       </c>
       <c r="I149" s="37" t="s">
-        <v>1758</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="150">
@@ -13326,7 +13440,7 @@
         <v>148</v>
       </c>
       <c r="B150" s="36" t="s">
-        <v>1759</v>
+        <v>1797</v>
       </c>
       <c r="C150" s="36">
         <v>0.0</v>
@@ -13335,19 +13449,19 @@
         <v>1099</v>
       </c>
       <c r="E150" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F150" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G150" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H150" s="37" t="s">
-        <v>1760</v>
+        <v>1798</v>
       </c>
       <c r="I150" s="37" t="s">
-        <v>1760</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="151">
@@ -13356,7 +13470,7 @@
         <v>149</v>
       </c>
       <c r="B151" s="36" t="s">
-        <v>1761</v>
+        <v>1799</v>
       </c>
       <c r="C151" s="36">
         <v>1.0</v>
@@ -13365,19 +13479,19 @@
         <v>1101</v>
       </c>
       <c r="E151" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F151" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G151" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H151" s="37" t="s">
-        <v>1762</v>
+        <v>1800</v>
       </c>
       <c r="I151" s="37" t="s">
-        <v>1762</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="152">
@@ -13386,7 +13500,7 @@
         <v>150</v>
       </c>
       <c r="B152" s="36" t="s">
-        <v>1763</v>
+        <v>1801</v>
       </c>
       <c r="C152" s="36">
         <v>0.0</v>
@@ -13395,19 +13509,19 @@
         <v>1103</v>
       </c>
       <c r="E152" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F152" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G152" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H152" s="37" t="s">
-        <v>1764</v>
+        <v>1802</v>
       </c>
       <c r="I152" s="37" t="s">
-        <v>1764</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="153">
@@ -13416,7 +13530,7 @@
         <v>151</v>
       </c>
       <c r="B153" s="36" t="s">
-        <v>1765</v>
+        <v>1803</v>
       </c>
       <c r="C153" s="36">
         <v>1.0</v>
@@ -13425,19 +13539,19 @@
         <v>1105</v>
       </c>
       <c r="E153" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F153" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G153" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H153" s="37" t="s">
-        <v>1766</v>
+        <v>1804</v>
       </c>
       <c r="I153" s="37" t="s">
-        <v>1766</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="154">
@@ -13446,7 +13560,7 @@
         <v>152</v>
       </c>
       <c r="B154" s="36" t="s">
-        <v>1767</v>
+        <v>1805</v>
       </c>
       <c r="C154" s="36">
         <v>0.0</v>
@@ -13455,19 +13569,19 @@
         <v>1021</v>
       </c>
       <c r="E154" s="44" t="s">
-        <v>1729</v>
+        <v>1767</v>
       </c>
       <c r="F154" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G154" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H154" s="37" t="s">
-        <v>1730</v>
+        <v>1768</v>
       </c>
       <c r="I154" s="37" t="s">
-        <v>1730</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="155">
@@ -13476,7 +13590,7 @@
         <v>153</v>
       </c>
       <c r="B155" s="36" t="s">
-        <v>1258</v>
+        <v>1296</v>
       </c>
       <c r="C155" s="36">
         <v>1.0</v>
@@ -13485,19 +13599,19 @@
         <v>1094</v>
       </c>
       <c r="E155" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F155" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G155" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H155" s="37" t="s">
-        <v>1768</v>
+        <v>1806</v>
       </c>
       <c r="I155" s="37" t="s">
-        <v>1768</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="156">
@@ -13506,7 +13620,7 @@
         <v>154</v>
       </c>
       <c r="B156" s="36" t="s">
-        <v>1769</v>
+        <v>1807</v>
       </c>
       <c r="C156" s="36">
         <v>1.0</v>
@@ -13515,19 +13629,19 @@
         <v>1106</v>
       </c>
       <c r="E156" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F156" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G156" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H156" s="37" t="s">
-        <v>1770</v>
+        <v>1808</v>
       </c>
       <c r="I156" s="37" t="s">
-        <v>1770</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="157">
@@ -13536,7 +13650,7 @@
         <v>155</v>
       </c>
       <c r="B157" s="36" t="s">
-        <v>1771</v>
+        <v>1809</v>
       </c>
       <c r="C157" s="36">
         <v>0.0</v>
@@ -13545,19 +13659,19 @@
         <v>1108</v>
       </c>
       <c r="E157" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F157" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G157" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H157" s="37" t="s">
-        <v>1772</v>
+        <v>1810</v>
       </c>
       <c r="I157" s="37" t="s">
-        <v>1772</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="158">
@@ -13566,7 +13680,7 @@
         <v>156</v>
       </c>
       <c r="B158" s="36" t="s">
-        <v>1773</v>
+        <v>1811</v>
       </c>
       <c r="C158" s="36">
         <v>1.0</v>
@@ -13575,19 +13689,19 @@
         <v>1110</v>
       </c>
       <c r="E158" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F158" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G158" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H158" s="37" t="s">
-        <v>1774</v>
+        <v>1812</v>
       </c>
       <c r="I158" s="37" t="s">
-        <v>1774</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="159">
@@ -13596,7 +13710,7 @@
         <v>157</v>
       </c>
       <c r="B159" s="36" t="s">
-        <v>1775</v>
+        <v>1813</v>
       </c>
       <c r="C159" s="36">
         <v>0.0</v>
@@ -13605,19 +13719,19 @@
         <v>1112</v>
       </c>
       <c r="E159" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F159" s="38" t="s">
-        <v>1776</v>
+        <v>1814</v>
       </c>
       <c r="G159" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H159" s="37" t="s">
-        <v>1777</v>
+        <v>1815</v>
       </c>
       <c r="I159" s="37" t="s">
-        <v>1777</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="160">
@@ -13626,7 +13740,7 @@
         <v>158</v>
       </c>
       <c r="B160" s="36" t="s">
-        <v>1778</v>
+        <v>1816</v>
       </c>
       <c r="C160" s="36">
         <v>0.0</v>
@@ -13635,19 +13749,19 @@
         <v>1115</v>
       </c>
       <c r="E160" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F160" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G160" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H160" s="37" t="s">
-        <v>1779</v>
+        <v>1817</v>
       </c>
       <c r="I160" s="37" t="s">
-        <v>1779</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="161">
@@ -13656,7 +13770,7 @@
         <v>159</v>
       </c>
       <c r="B161" s="36" t="s">
-        <v>1780</v>
+        <v>1818</v>
       </c>
       <c r="C161" s="36">
         <v>1.0</v>
@@ -13665,19 +13779,19 @@
         <v>1117</v>
       </c>
       <c r="E161" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F161" s="38" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="G161" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H161" s="37" t="s">
-        <v>1781</v>
+        <v>1819</v>
       </c>
       <c r="I161" s="37" t="s">
-        <v>1781</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="162">
@@ -13686,7 +13800,7 @@
         <v>160</v>
       </c>
       <c r="B162" s="36" t="s">
-        <v>1782</v>
+        <v>1820</v>
       </c>
       <c r="C162" s="36">
         <v>0.0</v>
@@ -13695,19 +13809,19 @@
         <v>1119</v>
       </c>
       <c r="E162" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F162" s="38" t="s">
-        <v>1776</v>
+        <v>1814</v>
       </c>
       <c r="G162" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H162" s="37" t="s">
-        <v>1783</v>
+        <v>1821</v>
       </c>
       <c r="I162" s="37" t="s">
-        <v>1783</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="163">
@@ -13716,7 +13830,7 @@
         <v>161</v>
       </c>
       <c r="B163" s="36" t="s">
-        <v>1784</v>
+        <v>1822</v>
       </c>
       <c r="C163" s="36">
         <v>0.0</v>
@@ -13725,19 +13839,19 @@
         <v>1121</v>
       </c>
       <c r="E163" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F163" s="38" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="G163" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H163" s="37" t="s">
-        <v>1785</v>
+        <v>1823</v>
       </c>
       <c r="I163" s="37" t="s">
-        <v>1785</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="164">
@@ -13746,7 +13860,7 @@
         <v>162</v>
       </c>
       <c r="B164" s="36" t="s">
-        <v>1786</v>
+        <v>1824</v>
       </c>
       <c r="C164" s="36">
         <v>1.0</v>
@@ -13755,19 +13869,19 @@
         <v>1123</v>
       </c>
       <c r="E164" s="44" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
       <c r="F164" s="38" t="s">
-        <v>1776</v>
+        <v>1814</v>
       </c>
       <c r="G164" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H164" s="37" t="s">
-        <v>1787</v>
+        <v>1825</v>
       </c>
       <c r="I164" s="37" t="s">
-        <v>1787</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="165">
@@ -13776,7 +13890,7 @@
         <v>163</v>
       </c>
       <c r="B165" s="36" t="s">
-        <v>1788</v>
+        <v>1826</v>
       </c>
       <c r="C165" s="36">
         <v>0.0</v>
@@ -13785,19 +13899,19 @@
         <v>1021</v>
       </c>
       <c r="E165" s="44" t="s">
-        <v>1729</v>
+        <v>1767</v>
       </c>
       <c r="F165" s="38" t="s">
-        <v>1729</v>
+        <v>1767</v>
       </c>
       <c r="G165" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H165" s="37" t="s">
-        <v>1730</v>
+        <v>1768</v>
       </c>
       <c r="I165" s="37" t="s">
-        <v>1730</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="166">
@@ -13815,7 +13929,7 @@
         <v>1125</v>
       </c>
       <c r="E166" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F166" s="38" t="s">
         <v>753</v>
@@ -13824,10 +13938,10 @@
         <v>753</v>
       </c>
       <c r="H166" s="37" t="s">
-        <v>1789</v>
+        <v>1827</v>
       </c>
       <c r="I166" s="37" t="s">
-        <v>1789</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="167">
@@ -13842,10 +13956,10 @@
         <v>0.0</v>
       </c>
       <c r="D167" s="38" t="s">
-        <v>1021</v>
+        <v>1127</v>
       </c>
       <c r="E167" s="44" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="F167" s="38" t="s">
         <v>753</v>
@@ -13866,28 +13980,28 @@
         <v>166</v>
       </c>
       <c r="B168" s="36" t="s">
-        <v>1790</v>
+        <v>1828</v>
       </c>
       <c r="C168" s="36">
         <v>0.0</v>
       </c>
       <c r="D168" s="38" t="s">
-        <v>1021</v>
+        <v>1131</v>
       </c>
       <c r="E168" s="44" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="F168" s="38" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="G168" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H168" s="37" t="s">
-        <v>1791</v>
+        <v>1829</v>
       </c>
       <c r="I168" s="37" t="s">
-        <v>1791</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="169">
@@ -13896,28 +14010,28 @@
         <v>167</v>
       </c>
       <c r="B169" s="36" t="s">
-        <v>1792</v>
+        <v>1830</v>
       </c>
       <c r="C169" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D169" s="38" t="s">
-        <v>1021</v>
+        <v>1133</v>
       </c>
       <c r="E169" s="44" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="F169" s="38" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="G169" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H169" s="37" t="s">
-        <v>1793</v>
+        <v>1831</v>
       </c>
       <c r="I169" s="37" t="s">
-        <v>1793</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="170">
@@ -13926,28 +14040,28 @@
         <v>168</v>
       </c>
       <c r="B170" s="36" t="s">
-        <v>1794</v>
+        <v>1832</v>
       </c>
       <c r="C170" s="36">
         <v>0.0</v>
       </c>
       <c r="D170" s="38" t="s">
-        <v>1021</v>
+        <v>1135</v>
       </c>
       <c r="E170" s="44" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="F170" s="38" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="G170" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H170" s="37" t="s">
-        <v>1795</v>
+        <v>1833</v>
       </c>
       <c r="I170" s="37" t="s">
-        <v>1795</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="171">
@@ -13956,28 +14070,28 @@
         <v>169</v>
       </c>
       <c r="B171" s="36" t="s">
-        <v>1796</v>
+        <v>1834</v>
       </c>
       <c r="C171" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D171" s="38" t="s">
-        <v>1021</v>
+        <v>1137</v>
       </c>
       <c r="E171" s="44" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="F171" s="38" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="G171" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H171" s="37" t="s">
-        <v>1797</v>
+        <v>1835</v>
       </c>
       <c r="I171" s="37" t="s">
-        <v>1797</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="172">
@@ -13986,28 +14100,28 @@
         <v>170</v>
       </c>
       <c r="B172" s="36" t="s">
-        <v>1798</v>
+        <v>1836</v>
       </c>
       <c r="C172" s="36">
         <v>0.0</v>
       </c>
       <c r="D172" s="38" t="s">
-        <v>1021</v>
+        <v>1139</v>
       </c>
       <c r="E172" s="44" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="F172" s="38" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="G172" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H172" s="37" t="s">
-        <v>1799</v>
+        <v>1837</v>
       </c>
       <c r="I172" s="37" t="s">
-        <v>1799</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="173">
@@ -14016,28 +14130,28 @@
         <v>171</v>
       </c>
       <c r="B173" s="36" t="s">
-        <v>1800</v>
+        <v>1838</v>
       </c>
       <c r="C173" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D173" s="38" t="s">
-        <v>1021</v>
+        <v>1141</v>
       </c>
       <c r="E173" s="44" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="F173" s="38" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="G173" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H173" s="37" t="s">
-        <v>1801</v>
+        <v>1839</v>
       </c>
       <c r="I173" s="37" t="s">
-        <v>1801</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="174">
@@ -14046,28 +14160,28 @@
         <v>172</v>
       </c>
       <c r="B174" s="36" t="s">
-        <v>1802</v>
+        <v>1840</v>
       </c>
       <c r="C174" s="36">
         <v>0.0</v>
       </c>
       <c r="D174" s="38" t="s">
-        <v>1021</v>
+        <v>1143</v>
       </c>
       <c r="E174" s="44" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="F174" s="38" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="G174" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H174" s="37" t="s">
-        <v>1803</v>
+        <v>1841</v>
       </c>
       <c r="I174" s="37" t="s">
-        <v>1803</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="175">
@@ -14076,28 +14190,28 @@
         <v>173</v>
       </c>
       <c r="B175" s="36" t="s">
-        <v>1804</v>
+        <v>1842</v>
       </c>
       <c r="C175" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D175" s="38" t="s">
-        <v>1021</v>
+        <v>1145</v>
       </c>
       <c r="E175" s="44" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="F175" s="38" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="G175" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H175" s="37" t="s">
-        <v>1805</v>
+        <v>1843</v>
       </c>
       <c r="I175" s="37" t="s">
-        <v>1805</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="176">
@@ -14106,28 +14220,28 @@
         <v>174</v>
       </c>
       <c r="B176" s="36" t="s">
-        <v>1806</v>
+        <v>1844</v>
       </c>
       <c r="C176" s="36">
         <v>0.0</v>
       </c>
       <c r="D176" s="38" t="s">
-        <v>1021</v>
+        <v>1147</v>
       </c>
       <c r="E176" s="44" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="F176" s="38" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="G176" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H176" s="37" t="s">
-        <v>1807</v>
+        <v>1845</v>
       </c>
       <c r="I176" s="37" t="s">
-        <v>1807</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="177">
@@ -14136,28 +14250,28 @@
         <v>175</v>
       </c>
       <c r="B177" s="36" t="s">
-        <v>1808</v>
+        <v>1846</v>
       </c>
       <c r="C177" s="36">
         <v>0.0</v>
       </c>
       <c r="D177" s="38" t="s">
-        <v>1021</v>
+        <v>1149</v>
       </c>
       <c r="E177" s="44" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="F177" s="38" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="G177" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H177" s="37" t="s">
-        <v>1809</v>
+        <v>1847</v>
       </c>
       <c r="I177" s="37" t="s">
-        <v>1809</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="178">
@@ -14166,28 +14280,28 @@
         <v>176</v>
       </c>
       <c r="B178" s="36" t="s">
-        <v>1810</v>
+        <v>1848</v>
       </c>
       <c r="C178" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D178" s="38" t="s">
-        <v>1021</v>
+        <v>1151</v>
       </c>
       <c r="E178" s="44" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="F178" s="38" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="G178" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H178" s="37" t="s">
-        <v>1811</v>
+        <v>1849</v>
       </c>
       <c r="I178" s="37" t="s">
-        <v>1811</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="179">
@@ -14196,28 +14310,28 @@
         <v>177</v>
       </c>
       <c r="B179" s="36" t="s">
-        <v>1812</v>
+        <v>1850</v>
       </c>
       <c r="C179" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D179" s="38" t="s">
-        <v>1021</v>
+        <v>1153</v>
       </c>
       <c r="E179" s="44" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="F179" s="38" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="G179" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H179" s="37" t="s">
-        <v>1813</v>
+        <v>1851</v>
       </c>
       <c r="I179" s="37" t="s">
-        <v>1813</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="180">
@@ -14226,28 +14340,28 @@
         <v>178</v>
       </c>
       <c r="B180" s="36" t="s">
-        <v>1814</v>
+        <v>1852</v>
       </c>
       <c r="C180" s="36">
         <v>0.0</v>
       </c>
       <c r="D180" s="38" t="s">
-        <v>1021</v>
+        <v>1155</v>
       </c>
       <c r="E180" s="44" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="F180" s="38" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="G180" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H180" s="37" t="s">
-        <v>1815</v>
+        <v>1853</v>
       </c>
       <c r="I180" s="37" t="s">
-        <v>1815</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="181">
@@ -14256,28 +14370,28 @@
         <v>179</v>
       </c>
       <c r="B181" s="36" t="s">
-        <v>1816</v>
+        <v>1854</v>
       </c>
       <c r="C181" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D181" s="38" t="s">
-        <v>1021</v>
+        <v>1157</v>
       </c>
       <c r="E181" s="44" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="F181" s="38" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="G181" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H181" s="37" t="s">
-        <v>1817</v>
+        <v>1855</v>
       </c>
       <c r="I181" s="37" t="s">
-        <v>1817</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="182">
@@ -14286,28 +14400,28 @@
         <v>180</v>
       </c>
       <c r="B182" s="36" t="s">
-        <v>1818</v>
+        <v>1856</v>
       </c>
       <c r="C182" s="36">
         <v>0.0</v>
       </c>
       <c r="D182" s="38" t="s">
-        <v>1021</v>
+        <v>1159</v>
       </c>
       <c r="E182" s="44" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="F182" s="38" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="G182" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H182" s="37" t="s">
-        <v>1819</v>
+        <v>1857</v>
       </c>
       <c r="I182" s="37" t="s">
-        <v>1819</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="183">
@@ -14316,28 +14430,28 @@
         <v>181</v>
       </c>
       <c r="B183" s="36" t="s">
-        <v>1820</v>
+        <v>1858</v>
       </c>
       <c r="C183" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D183" s="38" t="s">
-        <v>1021</v>
+        <v>1161</v>
       </c>
       <c r="E183" s="44" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="F183" s="38" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="G183" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H183" s="37" t="s">
-        <v>1821</v>
+        <v>1859</v>
       </c>
       <c r="I183" s="37" t="s">
-        <v>1821</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="184">
@@ -14346,28 +14460,28 @@
         <v>182</v>
       </c>
       <c r="B184" s="36" t="s">
-        <v>1822</v>
+        <v>1860</v>
       </c>
       <c r="C184" s="36">
         <v>0.0</v>
       </c>
       <c r="D184" s="38" t="s">
-        <v>1021</v>
+        <v>1163</v>
       </c>
       <c r="E184" s="44" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="F184" s="38" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="G184" s="38" t="s">
         <v>753</v>
       </c>
       <c r="H184" s="37" t="s">
-        <v>1823</v>
+        <v>1861</v>
       </c>
       <c r="I184" s="37" t="s">
-        <v>1823</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="185">
@@ -14376,19 +14490,19 @@
         <v>183</v>
       </c>
       <c r="B185" s="36" t="s">
-        <v>1269</v>
+        <v>1307</v>
       </c>
       <c r="C185" s="36">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D185" s="38" t="s">
-        <v>1021</v>
+        <v>1129</v>
       </c>
       <c r="E185" s="44" t="s">
-        <v>753</v>
+        <v>1451</v>
       </c>
       <c r="F185" s="38" t="s">
-        <v>753</v>
+        <v>1429</v>
       </c>
       <c r="G185" s="38" t="s">
         <v>753</v>
@@ -14406,7 +14520,7 @@
         <v>184</v>
       </c>
       <c r="B186" s="36" t="s">
-        <v>1824</v>
+        <v>1862</v>
       </c>
       <c r="C186" s="36">
         <v>0.0</v>
@@ -14415,7 +14529,7 @@
         <v>1021</v>
       </c>
       <c r="E186" s="44" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
       <c r="F186" s="38" t="s">
         <v>753</v>
@@ -14424,10 +14538,10 @@
         <v>753</v>
       </c>
       <c r="H186" s="37" t="s">
-        <v>1825</v>
+        <v>1863</v>
       </c>
       <c r="I186" s="37" t="s">
-        <v>1825</v>
+        <v>1863</v>
       </c>
     </row>
   </sheetData>
@@ -14469,34 +14583,34 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1826</v>
+        <v>1864</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>1827</v>
+        <v>1865</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1828</v>
+        <v>1866</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1829</v>
+        <v>1867</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>1830</v>
+        <v>1868</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>1831</v>
+        <v>1869</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>1832</v>
+        <v>1870</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>1833</v>
+        <v>1871</v>
       </c>
       <c r="J1" s="64" t="s">
-        <v>1834</v>
+        <v>1872</v>
       </c>
       <c r="K1" s="64" t="s">
-        <v>1835</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="2" ht="186.0" customHeight="1">
@@ -14505,7 +14619,7 @@
         <v>-1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>1836</v>
+        <v>1874</v>
       </c>
       <c r="C2" s="66" t="s">
         <v>324</v>
@@ -14541,7 +14655,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>1837</v>
+        <v>1875</v>
       </c>
       <c r="C3" s="66" t="s">
         <v>943</v>
@@ -14550,10 +14664,10 @@
         <v>1038</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>1838</v>
+        <v>1876</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1839</v>
+        <v>1877</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>322</v>
@@ -14577,19 +14691,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1840</v>
+        <v>1878</v>
       </c>
       <c r="C4" s="66" t="s">
-        <v>1841</v>
+        <v>1879</v>
       </c>
       <c r="D4" s="67" t="s">
         <v>1038</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1841</v>
+        <v>1879</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1842</v>
+        <v>1880</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>322</v>
@@ -14613,19 +14727,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1843</v>
+        <v>1881</v>
       </c>
       <c r="C5" s="66" t="s">
-        <v>1844</v>
+        <v>1882</v>
       </c>
       <c r="D5" s="67" t="s">
         <v>1038</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1844</v>
+        <v>1882</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1845</v>
+        <v>1883</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>322</v>
@@ -14649,19 +14763,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1846</v>
+        <v>1884</v>
       </c>
       <c r="C6" s="66" t="s">
-        <v>1847</v>
+        <v>1885</v>
       </c>
       <c r="D6" s="67" t="s">
         <v>1038</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1847</v>
+        <v>1885</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1848</v>
+        <v>1886</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>322</v>
@@ -14685,25 +14799,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1849</v>
+        <v>1887</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1850</v>
+        <v>1888</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>1851</v>
+        <v>1889</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>1850</v>
+        <v>1888</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>1852</v>
+        <v>1890</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>322</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>1851</v>
+        <v>1889</v>
       </c>
       <c r="I7" s="35" t="s">
         <v>659</v>
@@ -14721,25 +14835,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>1853</v>
+        <v>1891</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>1854</v>
+        <v>1892</v>
       </c>
       <c r="D8" s="67" t="s">
-        <v>1851</v>
+        <v>1889</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>1854</v>
+        <v>1892</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>1855</v>
+        <v>1893</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>322</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>1851</v>
+        <v>1889</v>
       </c>
       <c r="I8" s="35" t="s">
         <v>659</v>
@@ -14757,7 +14871,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>1856</v>
+        <v>1894</v>
       </c>
       <c r="C9" s="32" t="s">
         <v>980</v>
@@ -14769,7 +14883,7 @@
         <v>980</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>1857</v>
+        <v>1895</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>322</v>
@@ -14793,25 +14907,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>1858</v>
+        <v>1896</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>1859</v>
+        <v>1897</v>
       </c>
       <c r="D10" s="67" t="s">
         <v>1034</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1859</v>
+        <v>1897</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1860</v>
+        <v>1898</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>322</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>1861</v>
+        <v>1899</v>
       </c>
       <c r="I10" s="35" t="s">
         <v>722</v>
@@ -14829,25 +14943,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1862</v>
+        <v>1900</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1863</v>
+        <v>1901</v>
       </c>
       <c r="D11" s="67" t="s">
-        <v>1851</v>
+        <v>1889</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1863</v>
+        <v>1901</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>1864</v>
+        <v>1902</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>322</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>1865</v>
+        <v>1903</v>
       </c>
       <c r="I11" s="35" t="s">
         <v>659</v>
@@ -14865,19 +14979,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1866</v>
+        <v>1904</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1867</v>
+        <v>1905</v>
       </c>
       <c r="D12" s="67" t="s">
         <v>1033</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>1867</v>
+        <v>1905</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>1868</v>
+        <v>1906</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>322</v>
@@ -14901,25 +15015,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>1869</v>
+        <v>1907</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1870</v>
+        <v>1908</v>
       </c>
       <c r="D13" s="67" t="s">
-        <v>1871</v>
+        <v>1909</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>1870</v>
+        <v>1908</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>1872</v>
+        <v>1910</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>322</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>1873</v>
+        <v>1911</v>
       </c>
       <c r="I13" s="35" t="s">
         <v>659</v>
@@ -14946,16 +15060,16 @@
         <v>22</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>1874</v>
+        <v>1912</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>1875</v>
+        <v>1913</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>322</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>1876</v>
+        <v>1914</v>
       </c>
       <c r="I14" s="35" t="s">
         <v>659</v>
@@ -14982,16 +15096,16 @@
         <v>22</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>1877</v>
+        <v>1915</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>1878</v>
+        <v>1916</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>322</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>1879</v>
+        <v>1917</v>
       </c>
       <c r="I15" s="35" t="s">
         <v>659</v>
@@ -15009,7 +15123,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>1880</v>
+        <v>1918</v>
       </c>
       <c r="C16" s="66" t="s">
         <v>324</v>
@@ -15072,7 +15186,7 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1881</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="2">
@@ -15099,7 +15213,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1882</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="5">
@@ -15108,7 +15222,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1883</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="6">
@@ -15120,7 +15234,7 @@
         <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1884</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="8">
@@ -15128,7 +15242,7 @@
         <v>0.0</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1885</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="9">
@@ -15136,7 +15250,7 @@
         <v>1.0</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1886</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="10">
@@ -15144,7 +15258,7 @@
         <v>2.0</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1887</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="11">
@@ -15152,7 +15266,7 @@
         <v>3.0</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1888</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="12">
@@ -15160,7 +15274,7 @@
         <v>4.0</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1889</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="13">
@@ -15168,7 +15282,7 @@
         <v>5.0</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1890</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="15">
@@ -15176,7 +15290,7 @@
         <v>50</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1891</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="16">
@@ -15194,7 +15308,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1892</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="18">
@@ -15239,7 +15353,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1893</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="23">
@@ -15256,7 +15370,7 @@
         <v>50</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1894</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="26">
@@ -15301,7 +15415,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1895</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="31">
@@ -15337,7 +15451,7 @@
         <v>8</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1896</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="35">
@@ -15355,7 +15469,7 @@
         <v>10</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1897</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="37">
@@ -15417,7 +15531,7 @@
         <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1898</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="45">
@@ -15435,7 +15549,7 @@
         <v>1</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1776</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="47">
@@ -15444,7 +15558,7 @@
         <v>2</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1729</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="48">
@@ -15453,7 +15567,7 @@
         <v>3</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1722</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="49">
@@ -15462,7 +15576,7 @@
         <v>4</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1738</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="50">
@@ -15471,7 +15585,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1899</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="51">
@@ -15480,7 +15594,7 @@
         <v>6</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1900</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="52">
@@ -15489,7 +15603,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1901</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="53">
@@ -15498,7 +15612,7 @@
         <v>8</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1902</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="54">
@@ -15516,7 +15630,7 @@
         <v>10</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1903</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="56">
@@ -15525,7 +15639,7 @@
         <v>11</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1904</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="57">
@@ -15534,7 +15648,7 @@
         <v>12</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1905</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="58">
@@ -15543,7 +15657,7 @@
         <v>13</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1413</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="59">
@@ -15552,7 +15666,7 @@
         <v>14</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1391</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="60">
@@ -15561,7 +15675,7 @@
         <v>15</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1906</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="61">
@@ -15570,7 +15684,7 @@
         <v>16</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1907</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="62">
@@ -15579,7 +15693,7 @@
         <v>17</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1908</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="63">
@@ -15588,7 +15702,7 @@
         <v>18</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>1909</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="64">
@@ -15597,7 +15711,7 @@
         <v>19</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1910</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="66">
@@ -15605,7 +15719,7 @@
         <v>50</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1911</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="67">
@@ -15658,7 +15772,7 @@
         <v>50</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>1912</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="74">
@@ -15723,7 +15837,7 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1913</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="2">
@@ -15741,7 +15855,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1914</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="4">
@@ -15750,7 +15864,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1915</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="5">
@@ -15831,7 +15945,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1916</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="14">
@@ -15876,7 +15990,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1917</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="19">
@@ -16056,7 +16170,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1918</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="40">
@@ -16064,16 +16178,16 @@
         <v>50</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1919</v>
+        <v>1957</v>
       </c>
       <c r="C40" s="69" t="s">
         <v>313</v>
       </c>
       <c r="D40" s="69" t="s">
-        <v>1920</v>
+        <v>1958</v>
       </c>
       <c r="E40" s="69" t="s">
-        <v>1921</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="41">
@@ -16082,7 +16196,7 @@
         <v>0</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1922</v>
+        <v>1960</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>322</v>
@@ -16101,10 +16215,10 @@
         <v>1</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1923</v>
+        <v>1961</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>1315</v>
+        <v>1353</v>
       </c>
       <c r="D42" s="38" t="s">
         <v>960</v>
@@ -16120,10 +16234,10 @@
         <v>2</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1924</v>
+        <v>1962</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>1346</v>
+        <v>1384</v>
       </c>
       <c r="D43" s="38" t="s">
         <v>988</v>
@@ -16142,7 +16256,7 @@
         <v>45</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>1353</v>
+        <v>1391</v>
       </c>
       <c r="D44" s="38" t="s">
         <v>46</v>
@@ -16158,7 +16272,7 @@
         <v>4</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1925</v>
+        <v>1963</v>
       </c>
       <c r="C45" s="38" t="s">
         <v>479</v>
@@ -16176,19 +16290,19 @@
         <v>50</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1926</v>
+        <v>1964</v>
       </c>
       <c r="C47" s="68" t="s">
-        <v>1927</v>
+        <v>1965</v>
       </c>
       <c r="D47" s="68" t="s">
-        <v>1278</v>
+        <v>1316</v>
       </c>
       <c r="E47" s="69" t="s">
-        <v>1928</v>
+        <v>1966</v>
       </c>
       <c r="F47" s="68" t="s">
-        <v>1929</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="48">
@@ -16200,13 +16314,13 @@
         <v>749</v>
       </c>
       <c r="C48" s="44" t="s">
-        <v>1922</v>
+        <v>1960</v>
       </c>
       <c r="D48" s="44" t="s">
         <v>752</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>1930</v>
+        <v>1968</v>
       </c>
       <c r="F48" s="43" t="b">
         <v>0</v>
@@ -16221,13 +16335,13 @@
         <v>762</v>
       </c>
       <c r="C49" s="44" t="s">
-        <v>1923</v>
+        <v>1961</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>1432</v>
+        <v>1470</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>1930</v>
+        <v>1968</v>
       </c>
       <c r="F49" s="43" t="b">
         <v>0</v>
@@ -16242,13 +16356,13 @@
         <v>779</v>
       </c>
       <c r="C50" s="44" t="s">
-        <v>1923</v>
+        <v>1961</v>
       </c>
       <c r="D50" s="44" t="s">
         <v>799</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>1930</v>
+        <v>1968</v>
       </c>
       <c r="F50" s="43" t="b">
         <v>0</v>
@@ -16263,13 +16377,13 @@
         <v>784</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>1924</v>
+        <v>1962</v>
       </c>
       <c r="D51" s="44" t="s">
-        <v>1534</v>
+        <v>1572</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>1930</v>
+        <v>1968</v>
       </c>
       <c r="F51" s="43" t="b">
         <v>0</v>
@@ -16287,10 +16401,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="44" t="s">
-        <v>1607</v>
+        <v>1645</v>
       </c>
       <c r="E52" s="48" t="s">
-        <v>1930</v>
+        <v>1968</v>
       </c>
       <c r="F52" s="43" t="b">
         <v>0</v>
@@ -16302,16 +16416,16 @@
         <v>5</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1931</v>
+        <v>1969</v>
       </c>
       <c r="C53" s="44" t="s">
         <v>45</v>
       </c>
       <c r="D53" s="44" t="s">
-        <v>1610</v>
+        <v>1648</v>
       </c>
       <c r="E53" s="48" t="s">
-        <v>1930</v>
+        <v>1968</v>
       </c>
       <c r="F53" s="43" t="b">
         <v>0</v>
@@ -16323,16 +16437,16 @@
         <v>6</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1932</v>
+        <v>1970</v>
       </c>
       <c r="C54" s="44" t="s">
         <v>45</v>
       </c>
       <c r="D54" s="44" t="s">
-        <v>1613</v>
+        <v>1651</v>
       </c>
       <c r="E54" s="48" t="s">
-        <v>1930</v>
+        <v>1968</v>
       </c>
       <c r="F54" s="43" t="b">
         <v>1</v>
@@ -16344,16 +16458,16 @@
         <v>7</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1933</v>
+        <v>1971</v>
       </c>
       <c r="C55" s="44" t="s">
-        <v>1925</v>
+        <v>1963</v>
       </c>
       <c r="D55" s="44" t="s">
         <v>752</v>
       </c>
       <c r="E55" s="48" t="s">
-        <v>1930</v>
+        <v>1968</v>
       </c>
       <c r="F55" s="43" t="b">
         <v>0</v>
@@ -16364,10 +16478,10 @@
         <v>50</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>1934</v>
+        <v>1972</v>
       </c>
       <c r="C57" s="28" t="s">
-        <v>1935</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="58">
@@ -16376,7 +16490,7 @@
         <v>0</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1930</v>
+        <v>1968</v>
       </c>
       <c r="C58" s="51" t="s">
         <v>488</v>
@@ -16387,7 +16501,7 @@
         <v>50</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1936</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="61">
@@ -17421,16 +17535,16 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1937</v>
+        <v>1975</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1938</v>
+        <v>1976</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1939</v>
+        <v>1977</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1940</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="2">
@@ -17442,7 +17556,7 @@
         <v>325</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1941</v>
+        <v>1979</v>
       </c>
       <c r="D2" s="71" t="s">
         <v>322</v>
@@ -17460,7 +17574,7 @@
         <v>440</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1942</v>
+        <v>1980</v>
       </c>
       <c r="D3" s="71" t="s">
         <v>322</v>
@@ -17475,10 +17589,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1943</v>
+        <v>1981</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1941</v>
+        <v>1979</v>
       </c>
       <c r="D4" s="71" t="s">
         <v>322</v>
@@ -17516,7 +17630,7 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1884</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="2">
@@ -17543,7 +17657,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1944</v>
+        <v>1982</v>
       </c>
     </row>
   </sheetData>
@@ -17569,21 +17683,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1945</v>
+        <v>1983</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1946</v>
+        <v>1984</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1947</v>
+        <v>1985</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1948</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="s">
-        <v>1949</v>
+        <v>1987</v>
       </c>
       <c r="B2" s="72">
         <v>5.0</v>
@@ -17597,7 +17711,7 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>1950</v>
+        <v>1988</v>
       </c>
       <c r="B3" s="72">
         <v>4.0</v>
@@ -17611,7 +17725,7 @@
     </row>
     <row r="4">
       <c r="A4" s="37" t="s">
-        <v>1951</v>
+        <v>1989</v>
       </c>
       <c r="B4" s="72">
         <v>2.0</v>
@@ -17625,7 +17739,7 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>1952</v>
+        <v>1990</v>
       </c>
       <c r="B5" s="72">
         <v>5.0</v>
@@ -17639,7 +17753,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>1953</v>
+        <v>1991</v>
       </c>
       <c r="B6" s="72">
         <v>4.0</v>
@@ -17653,7 +17767,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>1954</v>
+        <v>1992</v>
       </c>
       <c r="B7" s="72">
         <v>4.0</v>
@@ -17667,7 +17781,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>1955</v>
+        <v>1993</v>
       </c>
       <c r="B8" s="72">
         <v>2.0</v>
@@ -17681,7 +17795,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>1381</v>
+        <v>1419</v>
       </c>
       <c r="B9" s="72">
         <v>5.0</v>
@@ -36263,6 +36377,291 @@
       <c r="C65" s="36" t="s">
         <v>1022</v>
       </c>
+      <c r="D65" s="36" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>64</v>
+      </c>
+      <c r="B66" s="36" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C66" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D66" s="36" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>65</v>
+      </c>
+      <c r="B67" s="36" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C67" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D67" s="36" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>66</v>
+      </c>
+      <c r="B68" s="36" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C68" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D68" s="36" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>67</v>
+      </c>
+      <c r="B69" s="36" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C69" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D69" s="36" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>68</v>
+      </c>
+      <c r="B70" s="36" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C70" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D70" s="36" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>69</v>
+      </c>
+      <c r="B71" s="36" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C71" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D71" s="36" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>70</v>
+      </c>
+      <c r="B72" s="36" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C72" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D72" s="36" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>71</v>
+      </c>
+      <c r="B73" s="36" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C73" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D73" s="36" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>72</v>
+      </c>
+      <c r="B74" s="36" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C74" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D74" s="36" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>73</v>
+      </c>
+      <c r="B75" s="36" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C75" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D75" s="36" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>74</v>
+      </c>
+      <c r="B76" s="36" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C76" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D76" s="36" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>75</v>
+      </c>
+      <c r="B77" s="36" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C77" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D77" s="36" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>76</v>
+      </c>
+      <c r="B78" s="36" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C78" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D78" s="36" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>77</v>
+      </c>
+      <c r="B79" s="36" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C79" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D79" s="36" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>78</v>
+      </c>
+      <c r="B80" s="36" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C80" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D80" s="36" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>79</v>
+      </c>
+      <c r="B81" s="36" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C81" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D81" s="36" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>80</v>
+      </c>
+      <c r="B82" s="36" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C82" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D82" s="36" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>81</v>
+      </c>
+      <c r="B83" s="36" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C83" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D83" s="36" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>82</v>
+      </c>
+      <c r="B84" s="36" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C84" s="36" t="s">
+        <v>1022</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -36295,13 +36694,13 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1128</v>
+        <v>1166</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>25</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1129</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="2">
@@ -36316,7 +36715,7 @@
         <v>321</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>1130</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="3">
@@ -36331,7 +36730,7 @@
         <v>321</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>1131</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="4">
@@ -36343,10 +36742,10 @@
         <v>796</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>1132</v>
+        <v>1170</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>1133</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="5">
@@ -36355,13 +36754,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1134</v>
+        <v>1172</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>1132</v>
+        <v>1170</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>1135</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="6">
@@ -36373,10 +36772,10 @@
         <v>810</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>1132</v>
+        <v>1170</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>1136</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="7">
@@ -36388,10 +36787,10 @@
         <v>812</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>1137</v>
+        <v>1175</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>1138</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="8">
@@ -36400,13 +36799,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1139</v>
+        <v>1177</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>1137</v>
+        <v>1175</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>1140</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="9">
@@ -36418,10 +36817,10 @@
         <v>814</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>1141</v>
+        <v>1179</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>1142</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="10">
@@ -36430,13 +36829,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1143</v>
+        <v>1181</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>1141</v>
+        <v>1179</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>1144</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="11">
@@ -36448,10 +36847,10 @@
         <v>815</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>1141</v>
+        <v>1179</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>1145</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="12">
@@ -36466,7 +36865,7 @@
         <v>407</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>1146</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="13">
@@ -36481,7 +36880,7 @@
         <v>409</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>1147</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="14">
@@ -36490,13 +36889,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1148</v>
+        <v>1186</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>1149</v>
+        <v>1187</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>1150</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="15">
@@ -36508,10 +36907,10 @@
         <v>822</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>1149</v>
+        <v>1187</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>1151</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="16">
@@ -36520,13 +36919,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>1152</v>
+        <v>1190</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>1153</v>
+        <v>1191</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>1154</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="17">
@@ -36538,10 +36937,10 @@
         <v>847</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>1153</v>
+        <v>1191</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>1155</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="18">
@@ -36556,7 +36955,7 @@
         <v>388</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>1156</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="19">
@@ -36571,7 +36970,7 @@
         <v>327</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>1157</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="20">
@@ -36580,13 +36979,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>1158</v>
+        <v>1196</v>
       </c>
       <c r="C20" s="39" t="s">
         <v>388</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>1159</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="21">
@@ -36595,13 +36994,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>1160</v>
+        <v>1198</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>1161</v>
+        <v>1199</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>1162</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="22">
@@ -36613,10 +37012,10 @@
         <v>902</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>1161</v>
+        <v>1199</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>1163</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="23">
@@ -36625,13 +37024,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>1164</v>
+        <v>1202</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>1161</v>
+        <v>1199</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>1165</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="24">
@@ -36643,10 +37042,10 @@
         <v>904</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>1161</v>
+        <v>1199</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>1166</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="25">
@@ -36655,13 +37054,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>1167</v>
+        <v>1205</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>1168</v>
+        <v>1206</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>1169</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="26">
@@ -36673,10 +37072,10 @@
         <v>910</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>1168</v>
+        <v>1206</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>1170</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="27">
@@ -36688,10 +37087,10 @@
         <v>918</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>1171</v>
+        <v>1209</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>1172</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="28">
@@ -36700,13 +37099,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1173</v>
+        <v>1211</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>1171</v>
+        <v>1209</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>1174</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="29">
@@ -36718,10 +37117,10 @@
         <v>919</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>1171</v>
+        <v>1209</v>
       </c>
       <c r="D29" s="39" t="s">
-        <v>1175</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="30">
@@ -36730,13 +37129,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1176</v>
+        <v>1214</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>1171</v>
+        <v>1209</v>
       </c>
       <c r="D30" s="39" t="s">
-        <v>1130</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="31">
@@ -36748,10 +37147,10 @@
         <v>920</v>
       </c>
       <c r="C31" s="39" t="s">
-        <v>1177</v>
+        <v>1215</v>
       </c>
       <c r="D31" s="39" t="s">
-        <v>1178</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="32">
@@ -36766,7 +37165,7 @@
         <v>36</v>
       </c>
       <c r="D32" s="39" t="s">
-        <v>1179</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="33">
@@ -36781,7 +37180,7 @@
         <v>36</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>1180</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="34">
@@ -36790,13 +37189,13 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1181</v>
+        <v>1219</v>
       </c>
       <c r="C34" s="39" t="s">
         <v>321</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>1130</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="36">
@@ -36804,25 +37203,25 @@
         <v>50</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1182</v>
+        <v>1220</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>482</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>1183</v>
+        <v>1221</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>1184</v>
+        <v>1222</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>1185</v>
+        <v>1223</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>1186</v>
+        <v>1224</v>
       </c>
       <c r="H36" s="28" t="s">
-        <v>1187</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="37">
@@ -36831,7 +37230,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1130</v>
+        <v>1168</v>
       </c>
       <c r="C37" s="37" t="s">
         <v>488</v>
@@ -36858,7 +37257,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1131</v>
+        <v>1169</v>
       </c>
       <c r="C38" s="37" t="s">
         <v>488</v>
@@ -36885,7 +37284,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1133</v>
+        <v>1171</v>
       </c>
       <c r="C39" s="40" t="s">
         <v>488</v>
@@ -36897,13 +37296,13 @@
         <v>491</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1134</v>
+        <v>1172</v>
       </c>
       <c r="G39" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H39" s="40" t="s">
-        <v>1188</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="40">
@@ -36912,7 +37311,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1189</v>
+        <v>1227</v>
       </c>
       <c r="C40" s="40" t="s">
         <v>488</v>
@@ -36924,13 +37323,13 @@
         <v>491</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1134</v>
+        <v>1172</v>
       </c>
       <c r="G40" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H40" s="40" t="s">
-        <v>1190</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="41">
@@ -36939,7 +37338,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1191</v>
+        <v>1229</v>
       </c>
       <c r="C41" s="40" t="s">
         <v>488</v>
@@ -36957,7 +37356,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>1192</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="42">
@@ -36966,7 +37365,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1193</v>
+        <v>1231</v>
       </c>
       <c r="C42" s="40" t="s">
         <v>488</v>
@@ -36975,7 +37374,7 @@
         <v>489</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>1194</v>
+        <v>1232</v>
       </c>
       <c r="F42" s="38" t="s">
         <v>751</v>
@@ -36984,7 +37383,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="40" t="s">
-        <v>1195</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="43">
@@ -36993,7 +37392,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1136</v>
+        <v>1174</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>488</v>
@@ -37011,7 +37410,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="40" t="s">
-        <v>1196</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="44">
@@ -37020,7 +37419,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1138</v>
+        <v>1176</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>488</v>
@@ -37032,13 +37431,13 @@
         <v>491</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>1139</v>
+        <v>1177</v>
       </c>
       <c r="G44" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H44" s="40" t="s">
-        <v>1197</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="45">
@@ -37047,7 +37446,7 @@
         <v>8</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1140</v>
+        <v>1178</v>
       </c>
       <c r="C45" s="40" t="s">
         <v>488</v>
@@ -37065,7 +37464,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="40" t="s">
-        <v>1198</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="46">
@@ -37074,7 +37473,7 @@
         <v>9</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1142</v>
+        <v>1180</v>
       </c>
       <c r="C46" s="40" t="s">
         <v>488</v>
@@ -37086,13 +37485,13 @@
         <v>491</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1143</v>
+        <v>1181</v>
       </c>
       <c r="G46" s="55" t="b">
         <v>1</v>
       </c>
       <c r="H46" s="40" t="s">
-        <v>1199</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="47">
@@ -37101,7 +37500,7 @@
         <v>10</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1200</v>
+        <v>1238</v>
       </c>
       <c r="C47" s="40" t="s">
         <v>488</v>
@@ -37113,13 +37512,13 @@
         <v>880</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>1143</v>
+        <v>1181</v>
       </c>
       <c r="G47" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H47" s="40" t="s">
-        <v>1201</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="48">
@@ -37128,7 +37527,7 @@
         <v>11</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1202</v>
+        <v>1240</v>
       </c>
       <c r="C48" s="40" t="s">
         <v>881</v>
@@ -37140,13 +37539,13 @@
         <v>491</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>1143</v>
+        <v>1181</v>
       </c>
       <c r="G48" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="40" t="s">
-        <v>1203</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="49">
@@ -37155,7 +37554,7 @@
         <v>12</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1204</v>
+        <v>1242</v>
       </c>
       <c r="C49" s="40" t="s">
         <v>488</v>
@@ -37167,13 +37566,13 @@
         <v>491</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>1143</v>
+        <v>1181</v>
       </c>
       <c r="G49" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H49" s="40" t="s">
-        <v>1205</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="50">
@@ -37182,7 +37581,7 @@
         <v>13</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1206</v>
+        <v>1244</v>
       </c>
       <c r="C50" s="40" t="s">
         <v>881</v>
@@ -37191,16 +37590,16 @@
         <v>554</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>1207</v>
+        <v>1245</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>1143</v>
+        <v>1181</v>
       </c>
       <c r="G50" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H50" s="40" t="s">
-        <v>1208</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="51">
@@ -37209,7 +37608,7 @@
         <v>14</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1209</v>
+        <v>1247</v>
       </c>
       <c r="C51" s="40" t="s">
         <v>488</v>
@@ -37227,7 +37626,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="40" t="s">
-        <v>1210</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="52">
@@ -37236,7 +37635,7 @@
         <v>15</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1145</v>
+        <v>1183</v>
       </c>
       <c r="C52" s="40" t="s">
         <v>488</v>
@@ -37254,7 +37653,7 @@
         <v>0</v>
       </c>
       <c r="H52" s="40" t="s">
-        <v>1211</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="53">
@@ -37263,7 +37662,7 @@
         <v>16</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1146</v>
+        <v>1184</v>
       </c>
       <c r="C53" s="40" t="s">
         <v>488</v>
@@ -37281,7 +37680,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="40" t="s">
-        <v>1212</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="54">
@@ -37290,7 +37689,7 @@
         <v>17</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1147</v>
+        <v>1185</v>
       </c>
       <c r="C54" s="40" t="s">
         <v>488</v>
@@ -37308,7 +37707,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="40" t="s">
-        <v>1213</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="55">
@@ -37317,7 +37716,7 @@
         <v>18</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1214</v>
+        <v>1252</v>
       </c>
       <c r="C55" s="40" t="s">
         <v>488</v>
@@ -37329,13 +37728,13 @@
         <v>491</v>
       </c>
       <c r="F55" s="38" t="s">
-        <v>1148</v>
+        <v>1186</v>
       </c>
       <c r="G55" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H55" s="40" t="s">
-        <v>1215</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="56">
@@ -37344,7 +37743,7 @@
         <v>19</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1216</v>
+        <v>1254</v>
       </c>
       <c r="C56" s="40" t="s">
         <v>488</v>
@@ -37356,13 +37755,13 @@
         <v>491</v>
       </c>
       <c r="F56" s="38" t="s">
-        <v>1148</v>
+        <v>1186</v>
       </c>
       <c r="G56" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H56" s="40" t="s">
-        <v>1217</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="57">
@@ -37371,7 +37770,7 @@
         <v>20</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1218</v>
+        <v>1256</v>
       </c>
       <c r="C57" s="40" t="s">
         <v>488</v>
@@ -37380,16 +37779,16 @@
         <v>489</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>1219</v>
+        <v>1257</v>
       </c>
       <c r="F57" s="38" t="s">
-        <v>1148</v>
+        <v>1186</v>
       </c>
       <c r="G57" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H57" s="40" t="s">
-        <v>1220</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="58">
@@ -37398,7 +37797,7 @@
         <v>21</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1221</v>
+        <v>1259</v>
       </c>
       <c r="C58" s="40" t="s">
         <v>488</v>
@@ -37416,7 +37815,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="40" t="s">
-        <v>1222</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="59">
@@ -37425,7 +37824,7 @@
         <v>22</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1151</v>
+        <v>1189</v>
       </c>
       <c r="C59" s="40" t="s">
         <v>488</v>
@@ -37437,13 +37836,13 @@
         <v>491</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>1148</v>
+        <v>1186</v>
       </c>
       <c r="G59" s="55" t="b">
         <v>1</v>
       </c>
       <c r="H59" s="40" t="s">
-        <v>1223</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="60">
@@ -37452,7 +37851,7 @@
         <v>23</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1224</v>
+        <v>1262</v>
       </c>
       <c r="C60" s="40" t="s">
         <v>488</v>
@@ -37464,13 +37863,13 @@
         <v>885</v>
       </c>
       <c r="F60" s="38" t="s">
-        <v>1152</v>
+        <v>1190</v>
       </c>
       <c r="G60" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H60" s="40" t="s">
-        <v>1225</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="61">
@@ -37479,7 +37878,7 @@
         <v>24</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1226</v>
+        <v>1264</v>
       </c>
       <c r="C61" s="40" t="s">
         <v>886</v>
@@ -37488,16 +37887,16 @@
         <v>489</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>1227</v>
+        <v>1265</v>
       </c>
       <c r="F61" s="38" t="s">
-        <v>1152</v>
+        <v>1190</v>
       </c>
       <c r="G61" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H61" s="40" t="s">
-        <v>1228</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="62">
@@ -37506,7 +37905,7 @@
         <v>25</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1229</v>
+        <v>1267</v>
       </c>
       <c r="C62" s="40" t="s">
         <v>488</v>
@@ -37524,7 +37923,7 @@
         <v>0</v>
       </c>
       <c r="H62" s="40" t="s">
-        <v>1230</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="63">
@@ -37533,7 +37932,7 @@
         <v>26</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>1155</v>
+        <v>1193</v>
       </c>
       <c r="C63" s="40" t="s">
         <v>488</v>
@@ -37545,13 +37944,13 @@
         <v>491</v>
       </c>
       <c r="F63" s="38" t="s">
-        <v>1152</v>
+        <v>1190</v>
       </c>
       <c r="G63" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H63" s="40" t="s">
-        <v>1231</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="64">
@@ -37560,7 +37959,7 @@
         <v>27</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1156</v>
+        <v>1194</v>
       </c>
       <c r="C64" s="40" t="s">
         <v>488</v>
@@ -37578,7 +37977,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="40" t="s">
-        <v>1232</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="65">
@@ -37587,7 +37986,7 @@
         <v>28</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1157</v>
+        <v>1195</v>
       </c>
       <c r="C65" s="40" t="s">
         <v>488</v>
@@ -37599,13 +37998,13 @@
         <v>891</v>
       </c>
       <c r="F65" s="38" t="s">
-        <v>1158</v>
+        <v>1196</v>
       </c>
       <c r="G65" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H65" s="40" t="s">
-        <v>1233</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="66">
@@ -37614,7 +38013,7 @@
         <v>29</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1159</v>
+        <v>1197</v>
       </c>
       <c r="C66" s="40" t="s">
         <v>488</v>
@@ -37632,7 +38031,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="40" t="s">
-        <v>1234</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="67">
@@ -37641,7 +38040,7 @@
         <v>30</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1235</v>
+        <v>1273</v>
       </c>
       <c r="C67" s="40" t="s">
         <v>488</v>
@@ -37653,13 +38052,13 @@
         <v>491</v>
       </c>
       <c r="F67" s="38" t="s">
-        <v>1160</v>
+        <v>1198</v>
       </c>
       <c r="G67" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H67" s="40" t="s">
-        <v>1236</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="68">
@@ -37668,7 +38067,7 @@
         <v>31</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1237</v>
+        <v>1275</v>
       </c>
       <c r="C68" s="40" t="s">
         <v>488</v>
@@ -37680,13 +38079,13 @@
         <v>491</v>
       </c>
       <c r="F68" s="38" t="s">
-        <v>1164</v>
+        <v>1202</v>
       </c>
       <c r="G68" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H68" s="40" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="69">
@@ -37695,7 +38094,7 @@
         <v>32</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1239</v>
+        <v>1277</v>
       </c>
       <c r="C69" s="40" t="s">
         <v>488</v>
@@ -37713,7 +38112,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="40" t="s">
-        <v>1240</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="70">
@@ -37722,7 +38121,7 @@
         <v>33</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1241</v>
+        <v>1279</v>
       </c>
       <c r="C70" s="40" t="s">
         <v>488</v>
@@ -37740,7 +38139,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="40" t="s">
-        <v>1242</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="71">
@@ -37749,7 +38148,7 @@
         <v>34</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1163</v>
+        <v>1201</v>
       </c>
       <c r="C71" s="40" t="s">
         <v>488</v>
@@ -37761,13 +38160,13 @@
         <v>491</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>1160</v>
+        <v>1198</v>
       </c>
       <c r="G71" s="55" t="b">
         <v>1</v>
       </c>
       <c r="H71" s="40" t="s">
-        <v>1243</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="72">
@@ -37776,7 +38175,7 @@
         <v>35</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1244</v>
+        <v>1282</v>
       </c>
       <c r="C72" s="40" t="s">
         <v>488</v>
@@ -37788,13 +38187,13 @@
         <v>491</v>
       </c>
       <c r="F72" s="38" t="s">
-        <v>1160</v>
+        <v>1198</v>
       </c>
       <c r="G72" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H72" s="40" t="s">
-        <v>1245</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="73">
@@ -37803,7 +38202,7 @@
         <v>36</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>1246</v>
+        <v>1284</v>
       </c>
       <c r="C73" s="40" t="s">
         <v>488</v>
@@ -37815,13 +38214,13 @@
         <v>491</v>
       </c>
       <c r="F73" s="38" t="s">
-        <v>1160</v>
+        <v>1198</v>
       </c>
       <c r="G73" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H73" s="40" t="s">
-        <v>1247</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="74">
@@ -37830,7 +38229,7 @@
         <v>37</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>1248</v>
+        <v>1286</v>
       </c>
       <c r="C74" s="40" t="s">
         <v>488</v>
@@ -37842,13 +38241,13 @@
         <v>491</v>
       </c>
       <c r="F74" s="38" t="s">
-        <v>1160</v>
+        <v>1198</v>
       </c>
       <c r="G74" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H74" s="40" t="s">
-        <v>1249</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="75">
@@ -37857,7 +38256,7 @@
         <v>38</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>1250</v>
+        <v>1288</v>
       </c>
       <c r="C75" s="40" t="s">
         <v>877</v>
@@ -37875,7 +38274,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="40" t="s">
-        <v>1251</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="76">
@@ -37884,7 +38283,7 @@
         <v>39</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1166</v>
+        <v>1204</v>
       </c>
       <c r="C76" s="40" t="s">
         <v>488</v>
@@ -37902,7 +38301,7 @@
         <v>0</v>
       </c>
       <c r="H76" s="40" t="s">
-        <v>1252</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="77">
@@ -37911,7 +38310,7 @@
         <v>40</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1253</v>
+        <v>1291</v>
       </c>
       <c r="C77" s="40" t="s">
         <v>488</v>
@@ -37923,13 +38322,13 @@
         <v>491</v>
       </c>
       <c r="F77" s="38" t="s">
-        <v>1167</v>
+        <v>1205</v>
       </c>
       <c r="G77" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H77" s="40" t="s">
-        <v>1254</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="78">
@@ -37938,7 +38337,7 @@
         <v>41</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="C78" s="40" t="s">
         <v>488</v>
@@ -37950,13 +38349,13 @@
         <v>491</v>
       </c>
       <c r="F78" s="38" t="s">
-        <v>1167</v>
+        <v>1205</v>
       </c>
       <c r="G78" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H78" s="40" t="s">
-        <v>1256</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="79">
@@ -37965,7 +38364,7 @@
         <v>42</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="C79" s="40" t="s">
         <v>488</v>
@@ -37983,7 +38382,7 @@
         <v>0</v>
       </c>
       <c r="H79" s="40" t="s">
-        <v>1242</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="80">
@@ -37992,7 +38391,7 @@
         <v>43</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>1170</v>
+        <v>1208</v>
       </c>
       <c r="C80" s="40" t="s">
         <v>488</v>
@@ -38004,13 +38403,13 @@
         <v>491</v>
       </c>
       <c r="F80" s="38" t="s">
-        <v>1167</v>
+        <v>1205</v>
       </c>
       <c r="G80" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H80" s="40" t="s">
-        <v>1258</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="81">
@@ -38019,7 +38418,7 @@
         <v>44</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1172</v>
+        <v>1210</v>
       </c>
       <c r="C81" s="40" t="s">
         <v>488</v>
@@ -38037,7 +38436,7 @@
         <v>0</v>
       </c>
       <c r="H81" s="40" t="s">
-        <v>1259</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="82">
@@ -38046,7 +38445,7 @@
         <v>45</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>1174</v>
+        <v>1212</v>
       </c>
       <c r="C82" s="40" t="s">
         <v>488</v>
@@ -38073,7 +38472,7 @@
         <v>46</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>1175</v>
+        <v>1213</v>
       </c>
       <c r="C83" s="40" t="s">
         <v>488</v>
@@ -38091,7 +38490,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="40" t="s">
-        <v>1260</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="84">
@@ -38100,7 +38499,7 @@
         <v>47</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>1261</v>
+        <v>1299</v>
       </c>
       <c r="C84" s="40" t="s">
         <v>488</v>
@@ -38127,7 +38526,7 @@
         <v>48</v>
       </c>
       <c r="B85" s="36" t="s">
-        <v>1178</v>
+        <v>1216</v>
       </c>
       <c r="C85" s="40" t="s">
         <v>488</v>
@@ -38145,7 +38544,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="40" t="s">
-        <v>1262</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="86">
@@ -38154,7 +38553,7 @@
         <v>49</v>
       </c>
       <c r="B86" s="36" t="s">
-        <v>1263</v>
+        <v>1301</v>
       </c>
       <c r="C86" s="40" t="s">
         <v>488</v>
@@ -38172,7 +38571,7 @@
         <v>0</v>
       </c>
       <c r="H86" s="40" t="s">
-        <v>1264</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="87">
@@ -38181,7 +38580,7 @@
         <v>50</v>
       </c>
       <c r="B87" s="36" t="s">
-        <v>1265</v>
+        <v>1303</v>
       </c>
       <c r="C87" s="40" t="s">
         <v>488</v>
@@ -38199,7 +38598,7 @@
         <v>0</v>
       </c>
       <c r="H87" s="40" t="s">
-        <v>1266</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="88">
@@ -38208,7 +38607,7 @@
         <v>51</v>
       </c>
       <c r="B88" s="36" t="s">
-        <v>1267</v>
+        <v>1305</v>
       </c>
       <c r="C88" s="40" t="s">
         <v>488</v>
@@ -38226,7 +38625,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="40" t="s">
-        <v>1268</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="89">
@@ -38235,7 +38634,7 @@
         <v>52</v>
       </c>
       <c r="B89" s="36" t="s">
-        <v>1180</v>
+        <v>1218</v>
       </c>
       <c r="C89" s="40" t="s">
         <v>488</v>
@@ -38253,7 +38652,7 @@
         <v>0</v>
       </c>
       <c r="H89" s="40" t="s">
-        <v>1269</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="90">
@@ -38262,7 +38661,7 @@
         <v>53</v>
       </c>
       <c r="B90" s="36" t="s">
-        <v>1270</v>
+        <v>1308</v>
       </c>
       <c r="C90" s="37" t="s">
         <v>488</v>
@@ -38379,10 +38778,10 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1271</v>
+        <v>1309</v>
       </c>
       <c r="C1" s="57" t="s">
-        <v>1272</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="2">
@@ -38394,7 +38793,7 @@
         <v>750</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>1273</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="3">
@@ -38406,7 +38805,7 @@
         <v>782</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>1274</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="4">
@@ -38415,10 +38814,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1275</v>
+        <v>1313</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>1276</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="6">
@@ -38426,13 +38825,13 @@
         <v>50</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1277</v>
+        <v>1315</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1278</v>
+        <v>1316</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>1184</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="7">
@@ -38441,7 +38840,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1273</v>
+        <v>1311</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>752</v>
@@ -38456,10 +38855,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1279</v>
+        <v>1317</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>1280</v>
+        <v>1318</v>
       </c>
       <c r="D8" s="58" t="s">
         <v>491</v>
@@ -38471,10 +38870,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1281</v>
+        <v>1319</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>1282</v>
+        <v>1320</v>
       </c>
       <c r="D9" s="58" t="s">
         <v>755</v>
@@ -38486,10 +38885,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1283</v>
+        <v>1321</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>1284</v>
+        <v>1322</v>
       </c>
       <c r="D10" s="58" t="s">
         <v>757</v>
@@ -38501,7 +38900,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1276</v>
+        <v>1314</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>752</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -39,7 +39,7 @@
     <definedName name="Interval_Dialog_Options">DIALOGS!$A$36:$H$90</definedName>
     <definedName name="Interval_Memento">EVENTS!$A$47:$F$55</definedName>
     <definedName name="Interval_autoInsertDialog">FN!$A$7:$L$8</definedName>
-    <definedName name="Interval_Sounds">SOUNDS!$A$1:$D$84</definedName>
+    <definedName name="Interval_Sounds">SOUNDS!$A$1:$D$88</definedName>
     <definedName name="Interval_Action_Conditions">ACTION_CONDS!$A$1:$H$69</definedName>
   </definedNames>
   <calcPr/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7048" uniqueCount="2009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7060" uniqueCount="2013">
   <si>
     <t>NewItem</t>
   </si>
@@ -3639,6 +3639,18 @@
   </si>
   <si>
     <t>SOUND_ARTURO_EXTRAPERLO_OP_2_7_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_CARD_PLACE_1</t>
+  </si>
+  <si>
+    <t>SOUND_CARD_PLACE_2</t>
+  </si>
+  <si>
+    <t>SOUND_CARD_PLACE_3</t>
+  </si>
+  <si>
+    <t>SOUND_CARD_TAKEBACK</t>
   </si>
   <si>
     <t>SOUND_LAST</t>
@@ -7411,7 +7423,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D84" displayName="Table_sounds" name="Table_sounds" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D88" displayName="Table_sounds" name="Table_sounds" id="12">
   <tableColumns count="4">
     <tableColumn name="N" id="1"/>
     <tableColumn name="SOUND_ID" id="2"/>
@@ -8288,13 +8300,13 @@
         <v>51</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="C1" s="59" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="D1" s="59" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="2">
@@ -8317,10 +8329,10 @@
         <v>334</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="4">
@@ -8329,13 +8341,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="5">
@@ -8344,13 +8356,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="6">
@@ -8359,13 +8371,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="7">
@@ -8377,10 +8389,10 @@
         <v>337</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="8">
@@ -8392,10 +8404,10 @@
         <v>358</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="9">
@@ -8407,10 +8419,10 @@
         <v>365</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="10">
@@ -8422,10 +8434,10 @@
         <v>343</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="11">
@@ -8434,13 +8446,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="12">
@@ -8449,13 +8461,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="13">
@@ -8467,10 +8479,10 @@
         <v>348</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="14">
@@ -8482,10 +8494,10 @@
         <v>355</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="15">
@@ -8494,13 +8506,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="16">
@@ -8512,10 +8524,10 @@
         <v>368</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="17">
@@ -8527,10 +8539,10 @@
         <v>373</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="18">
@@ -8542,10 +8554,10 @@
         <v>376</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="19">
@@ -8557,10 +8569,10 @@
         <v>380</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="20">
@@ -8572,10 +8584,10 @@
         <v>383</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="21">
@@ -8587,10 +8599,10 @@
         <v>386</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="22">
@@ -8602,10 +8614,10 @@
         <v>388</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="23">
@@ -8617,10 +8629,10 @@
         <v>390</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="24">
@@ -8632,10 +8644,10 @@
         <v>392</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="25">
@@ -8647,10 +8659,10 @@
         <v>395</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="26">
@@ -8662,10 +8674,10 @@
         <v>399</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="27">
@@ -8677,10 +8689,10 @@
         <v>404</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="28">
@@ -8692,10 +8704,10 @@
         <v>406</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="29">
@@ -8707,10 +8719,10 @@
         <v>410</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="30">
@@ -8719,13 +8731,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="31">
@@ -8737,10 +8749,10 @@
         <v>414</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="32">
@@ -8752,10 +8764,10 @@
         <v>416</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="33">
@@ -8764,13 +8776,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>48</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="34">
@@ -8782,10 +8794,10 @@
         <v>420</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="35">
@@ -8797,10 +8809,10 @@
         <v>424</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="36">
@@ -8812,10 +8824,10 @@
         <v>427</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="37">
@@ -8827,10 +8839,10 @@
         <v>432</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="38">
@@ -8842,10 +8854,10 @@
         <v>437</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="39">
@@ -8857,10 +8869,10 @@
         <v>11</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="40">
@@ -8872,10 +8884,10 @@
         <v>444</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="41">
@@ -8887,10 +8899,10 @@
         <v>448</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="42">
@@ -8902,10 +8914,10 @@
         <v>451</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="43">
@@ -8917,10 +8929,10 @@
         <v>455</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="44">
@@ -8932,10 +8944,10 @@
         <v>458</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="45">
@@ -8947,10 +8959,10 @@
         <v>466</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="46">
@@ -8962,10 +8974,10 @@
         <v>472</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="47">
@@ -8977,10 +8989,10 @@
         <v>476</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="48">
@@ -8992,10 +9004,10 @@
         <v>480</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="49">
@@ -9007,10 +9019,10 @@
         <v>485</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
     </row>
   </sheetData>
@@ -9045,28 +9057,28 @@
         <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="I1" s="62" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="2">
@@ -9110,7 +9122,7 @@
         <v>1093</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>760</v>
@@ -9119,10 +9131,10 @@
         <v>760</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="I3" s="37" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="4">
@@ -9140,7 +9152,7 @@
         <v>1095</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F4" s="38" t="s">
         <v>760</v>
@@ -9149,10 +9161,10 @@
         <v>760</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="5">
@@ -9170,7 +9182,7 @@
         <v>1097</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F5" s="38" t="s">
         <v>760</v>
@@ -9179,10 +9191,10 @@
         <v>760</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="I5" s="37" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="6">
@@ -9191,7 +9203,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="C6" s="36">
         <v>0.0</v>
@@ -9200,7 +9212,7 @@
         <v>1035</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>760</v>
@@ -9209,10 +9221,10 @@
         <v>760</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="I6" s="37" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="7">
@@ -9221,7 +9233,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="C7" s="36">
         <v>0.0</v>
@@ -9230,7 +9242,7 @@
         <v>1035</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F7" s="38" t="s">
         <v>760</v>
@@ -9239,10 +9251,10 @@
         <v>760</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="8">
@@ -9260,7 +9272,7 @@
         <v>1035</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>760</v>
@@ -9269,10 +9281,10 @@
         <v>760</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="I8" s="37" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="9">
@@ -9281,7 +9293,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="C9" s="36">
         <v>0.0</v>
@@ -9290,7 +9302,7 @@
         <v>1035</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F9" s="38" t="s">
         <v>760</v>
@@ -9299,10 +9311,10 @@
         <v>760</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="I9" s="37" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="10">
@@ -9311,7 +9323,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="C10" s="36">
         <v>0.0</v>
@@ -9320,7 +9332,7 @@
         <v>1035</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F10" s="38" t="s">
         <v>760</v>
@@ -9329,10 +9341,10 @@
         <v>760</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="11">
@@ -9341,7 +9353,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="C11" s="36">
         <v>1.0</v>
@@ -9350,19 +9362,19 @@
         <v>1035</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G11" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="I11" s="37" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="12">
@@ -9371,7 +9383,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="C12" s="36">
         <v>0.0</v>
@@ -9380,7 +9392,7 @@
         <v>1035</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>760</v>
@@ -9389,10 +9401,10 @@
         <v>760</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="13">
@@ -9401,7 +9413,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="C13" s="36">
         <v>0.0</v>
@@ -9410,7 +9422,7 @@
         <v>1035</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>760</v>
@@ -9419,10 +9431,10 @@
         <v>760</v>
       </c>
       <c r="H13" s="37" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="I13" s="37" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="14">
@@ -9431,7 +9443,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="C14" s="36">
         <v>1.0</v>
@@ -9440,19 +9452,19 @@
         <v>1035</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G14" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="15">
@@ -9461,7 +9473,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="C15" s="36">
         <v>1.0</v>
@@ -9470,19 +9482,19 @@
         <v>1035</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G15" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="16">
@@ -9491,7 +9503,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="C16" s="36">
         <v>0.0</v>
@@ -9500,7 +9512,7 @@
         <v>1035</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>760</v>
@@ -9509,10 +9521,10 @@
         <v>760</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="17">
@@ -9521,7 +9533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="C17" s="36">
         <v>0.0</v>
@@ -9530,7 +9542,7 @@
         <v>1035</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>760</v>
@@ -9539,10 +9551,10 @@
         <v>760</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="I17" s="37" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="18">
@@ -9551,7 +9563,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="C18" s="36">
         <v>0.0</v>
@@ -9560,7 +9572,7 @@
         <v>1035</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>760</v>
@@ -9569,10 +9581,10 @@
         <v>760</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="19">
@@ -9590,7 +9602,7 @@
         <v>1035</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F19" s="38" t="s">
         <v>760</v>
@@ -9599,10 +9611,10 @@
         <v>760</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="20">
@@ -9620,7 +9632,7 @@
         <v>1035</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F20" s="38" t="s">
         <v>760</v>
@@ -9629,10 +9641,10 @@
         <v>760</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="21">
@@ -9650,7 +9662,7 @@
         <v>1035</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F21" s="38" t="s">
         <v>760</v>
@@ -9659,10 +9671,10 @@
         <v>760</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="22">
@@ -9680,7 +9692,7 @@
         <v>1035</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F22" s="38" t="s">
         <v>760</v>
@@ -9689,10 +9701,10 @@
         <v>760</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="23">
@@ -9710,7 +9722,7 @@
         <v>1035</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F23" s="38" t="s">
         <v>760</v>
@@ -9719,10 +9731,10 @@
         <v>760</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="24">
@@ -9740,7 +9752,7 @@
         <v>1035</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F24" s="38" t="s">
         <v>760</v>
@@ -9749,10 +9761,10 @@
         <v>760</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="25">
@@ -9770,7 +9782,7 @@
         <v>1035</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F25" s="38" t="s">
         <v>760</v>
@@ -9779,10 +9791,10 @@
         <v>760</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="26">
@@ -9800,7 +9812,7 @@
         <v>1035</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F26" s="38" t="s">
         <v>760</v>
@@ -9809,10 +9821,10 @@
         <v>760</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="27">
@@ -9821,7 +9833,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="C27" s="36">
         <v>0.0</v>
@@ -9830,7 +9842,7 @@
         <v>1035</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F27" s="38" t="s">
         <v>760</v>
@@ -9839,10 +9851,10 @@
         <v>760</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="I27" s="37" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="28">
@@ -9851,7 +9863,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
       <c r="C28" s="36">
         <v>1.0</v>
@@ -9860,19 +9872,19 @@
         <v>1035</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G28" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="29">
@@ -9881,7 +9893,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="C29" s="36">
         <v>0.0</v>
@@ -9890,7 +9902,7 @@
         <v>1035</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>760</v>
@@ -9899,10 +9911,10 @@
         <v>760</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="30">
@@ -9911,7 +9923,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="C30" s="36">
         <v>0.0</v>
@@ -9920,7 +9932,7 @@
         <v>1035</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F30" s="38" t="s">
         <v>760</v>
@@ -9929,10 +9941,10 @@
         <v>760</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="31">
@@ -9941,7 +9953,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="C31" s="36">
         <v>0.0</v>
@@ -9950,7 +9962,7 @@
         <v>1035</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>760</v>
@@ -9959,10 +9971,10 @@
         <v>760</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="32">
@@ -9980,7 +9992,7 @@
         <v>1035</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F32" s="38" t="s">
         <v>760</v>
@@ -9989,10 +10001,10 @@
         <v>760</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="33">
@@ -10001,7 +10013,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="C33" s="36">
         <v>0.0</v>
@@ -10010,7 +10022,7 @@
         <v>1035</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F33" s="38" t="s">
         <v>760</v>
@@ -10019,10 +10031,10 @@
         <v>760</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="34">
@@ -10031,7 +10043,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
       <c r="C34" s="36">
         <v>1.0</v>
@@ -10040,19 +10052,19 @@
         <v>1035</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G34" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="35">
@@ -10061,7 +10073,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
       <c r="C35" s="36">
         <v>1.0</v>
@@ -10070,19 +10082,19 @@
         <v>1035</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G35" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="36">
@@ -10100,7 +10112,7 @@
         <v>1035</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F36" s="38" t="s">
         <v>760</v>
@@ -10109,10 +10121,10 @@
         <v>760</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="37">
@@ -10121,7 +10133,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="C37" s="36">
         <v>0.0</v>
@@ -10130,7 +10142,7 @@
         <v>1035</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F37" s="38" t="s">
         <v>760</v>
@@ -10139,10 +10151,10 @@
         <v>760</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="38">
@@ -10151,7 +10163,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
       <c r="C38" s="36">
         <v>1.0</v>
@@ -10160,19 +10172,19 @@
         <v>1035</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G38" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="39">
@@ -10181,7 +10193,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1533</v>
+        <v>1537</v>
       </c>
       <c r="C39" s="36">
         <v>0.0</v>
@@ -10190,7 +10202,7 @@
         <v>1035</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F39" s="38" t="s">
         <v>760</v>
@@ -10199,10 +10211,10 @@
         <v>760</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="I39" s="37" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="40">
@@ -10211,7 +10223,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="C40" s="36">
         <v>1.0</v>
@@ -10220,19 +10232,19 @@
         <v>1035</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G40" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="41">
@@ -10241,7 +10253,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
       <c r="C41" s="36">
         <v>0.0</v>
@@ -10250,7 +10262,7 @@
         <v>1035</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F41" s="38" t="s">
         <v>760</v>
@@ -10259,10 +10271,10 @@
         <v>760</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="42">
@@ -10271,7 +10283,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="C42" s="36">
         <v>1.0</v>
@@ -10280,19 +10292,19 @@
         <v>1035</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G42" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="43">
@@ -10301,7 +10313,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
       <c r="C43" s="36">
         <v>0.0</v>
@@ -10310,7 +10322,7 @@
         <v>1035</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F43" s="38" t="s">
         <v>760</v>
@@ -10319,10 +10331,10 @@
         <v>760</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="44">
@@ -10331,7 +10343,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="C44" s="36">
         <v>1.0</v>
@@ -10340,19 +10352,19 @@
         <v>1035</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G44" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="45">
@@ -10361,7 +10373,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="C45" s="36">
         <v>0.0</v>
@@ -10370,7 +10382,7 @@
         <v>1035</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F45" s="38" t="s">
         <v>760</v>
@@ -10379,10 +10391,10 @@
         <v>760</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="46">
@@ -10391,7 +10403,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
       <c r="C46" s="36">
         <v>1.0</v>
@@ -10400,19 +10412,19 @@
         <v>1035</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G46" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="47">
@@ -10421,7 +10433,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="C47" s="36">
         <v>1.0</v>
@@ -10430,19 +10442,19 @@
         <v>1035</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G47" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H47" s="37" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="I47" s="37" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="48">
@@ -10451,7 +10463,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="C48" s="36">
         <v>0.0</v>
@@ -10460,7 +10472,7 @@
         <v>1035</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F48" s="38" t="s">
         <v>760</v>
@@ -10469,10 +10481,10 @@
         <v>760</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="49">
@@ -10481,7 +10493,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="C49" s="36">
         <v>1.0</v>
@@ -10490,19 +10502,19 @@
         <v>1035</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G49" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
       <c r="I49" s="37" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="50">
@@ -10511,7 +10523,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="C50" s="36">
         <v>0.0</v>
@@ -10520,7 +10532,7 @@
         <v>1035</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F50" s="38" t="s">
         <v>760</v>
@@ -10529,10 +10541,10 @@
         <v>760</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
       <c r="I50" s="37" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="51">
@@ -10541,7 +10553,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
       <c r="C51" s="36">
         <v>0.0</v>
@@ -10550,7 +10562,7 @@
         <v>1035</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F51" s="38" t="s">
         <v>760</v>
@@ -10559,10 +10571,10 @@
         <v>760</v>
       </c>
       <c r="H51" s="37" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="I51" s="37" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="52">
@@ -10571,7 +10583,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="C52" s="36">
         <v>1.0</v>
@@ -10580,19 +10592,19 @@
         <v>1035</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G52" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H52" s="37" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
       <c r="I52" s="37" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="53">
@@ -10601,7 +10613,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="C53" s="36">
         <v>1.0</v>
@@ -10610,19 +10622,19 @@
         <v>1035</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G53" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="54">
@@ -10631,7 +10643,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="C54" s="36">
         <v>1.0</v>
@@ -10640,19 +10652,19 @@
         <v>1035</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G54" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="I54" s="37" t="s">
-        <v>1580</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="55">
@@ -10661,7 +10673,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1581</v>
+        <v>1585</v>
       </c>
       <c r="C55" s="36">
         <v>0.0</v>
@@ -10670,7 +10682,7 @@
         <v>1035</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F55" s="38" t="s">
         <v>760</v>
@@ -10679,10 +10691,10 @@
         <v>760</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="56">
@@ -10691,7 +10703,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="C56" s="36">
         <v>0.0</v>
@@ -10700,7 +10712,7 @@
         <v>1035</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F56" s="38" t="s">
         <v>760</v>
@@ -10709,10 +10721,10 @@
         <v>760</v>
       </c>
       <c r="H56" s="37" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="I56" s="37" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="57">
@@ -10721,7 +10733,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="C57" s="36">
         <v>0.0</v>
@@ -10730,7 +10742,7 @@
         <v>1035</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F57" s="38" t="s">
         <v>760</v>
@@ -10739,10 +10751,10 @@
         <v>760</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>1587</v>
+        <v>1591</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>1588</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="58">
@@ -10751,7 +10763,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="C58" s="36">
         <v>1.0</v>
@@ -10760,19 +10772,19 @@
         <v>1035</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G58" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>1589</v>
+        <v>1593</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>1590</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="59">
@@ -10790,7 +10802,7 @@
         <v>1035</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F59" s="38" t="s">
         <v>760</v>
@@ -10799,10 +10811,10 @@
         <v>760</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="I59" s="37" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="60">
@@ -10811,7 +10823,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="C60" s="36">
         <v>0.0</v>
@@ -10829,10 +10841,10 @@
         <v>760</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>1594</v>
+        <v>1598</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>1595</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="61">
@@ -10841,7 +10853,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1596</v>
+        <v>1600</v>
       </c>
       <c r="C61" s="36">
         <v>0.0</v>
@@ -10859,10 +10871,10 @@
         <v>760</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>1597</v>
+        <v>1601</v>
       </c>
       <c r="I61" s="37" t="s">
-        <v>1598</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="62">
@@ -10871,7 +10883,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="C62" s="36">
         <v>0.0</v>
@@ -10889,10 +10901,10 @@
         <v>760</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="63">
@@ -10910,7 +10922,7 @@
         <v>1035</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F63" s="38" t="s">
         <v>760</v>
@@ -10919,10 +10931,10 @@
         <v>760</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="I63" s="37" t="s">
-        <v>1603</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="64">
@@ -10931,7 +10943,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="C64" s="36">
         <v>0.0</v>
@@ -10940,7 +10952,7 @@
         <v>1042</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F64" s="38" t="s">
         <v>760</v>
@@ -10949,10 +10961,10 @@
         <v>760</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>1605</v>
+        <v>1609</v>
       </c>
       <c r="I64" s="37" t="s">
-        <v>1605</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="65">
@@ -10961,7 +10973,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1606</v>
+        <v>1610</v>
       </c>
       <c r="C65" s="36">
         <v>0.0</v>
@@ -10970,7 +10982,7 @@
         <v>1043</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F65" s="38" t="s">
         <v>760</v>
@@ -10979,10 +10991,10 @@
         <v>760</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="I65" s="37" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="66">
@@ -10991,7 +11003,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="C66" s="36">
         <v>0.0</v>
@@ -11000,7 +11012,7 @@
         <v>1044</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F66" s="38" t="s">
         <v>760</v>
@@ -11009,10 +11021,10 @@
         <v>760</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="I66" s="37" t="s">
-        <v>1611</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="67">
@@ -11021,7 +11033,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="C67" s="36">
         <v>0.0</v>
@@ -11030,7 +11042,7 @@
         <v>1045</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F67" s="38" t="s">
         <v>760</v>
@@ -11039,10 +11051,10 @@
         <v>760</v>
       </c>
       <c r="H67" s="37" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="I67" s="37" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="68">
@@ -11051,7 +11063,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="C68" s="36">
         <v>0.0</v>
@@ -11060,7 +11072,7 @@
         <v>1035</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F68" s="38" t="s">
         <v>760</v>
@@ -11069,10 +11081,10 @@
         <v>760</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="I68" s="37" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="69">
@@ -11081,7 +11093,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="C69" s="36">
         <v>1.0</v>
@@ -11090,19 +11102,19 @@
         <v>1035</v>
       </c>
       <c r="E69" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F69" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G69" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H69" s="37" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="I69" s="37" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="70">
@@ -11111,7 +11123,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1621</v>
+        <v>1625</v>
       </c>
       <c r="C70" s="36">
         <v>0.0</v>
@@ -11120,7 +11132,7 @@
         <v>1035</v>
       </c>
       <c r="E70" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F70" s="38" t="s">
         <v>760</v>
@@ -11129,10 +11141,10 @@
         <v>760</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>1622</v>
+        <v>1626</v>
       </c>
       <c r="I70" s="37" t="s">
-        <v>1623</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="71">
@@ -11141,7 +11153,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="C71" s="36">
         <v>1.0</v>
@@ -11150,19 +11162,19 @@
         <v>1035</v>
       </c>
       <c r="E71" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G71" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H71" s="37" t="s">
-        <v>1625</v>
+        <v>1629</v>
       </c>
       <c r="I71" s="37" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="72">
@@ -11171,7 +11183,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="C72" s="36">
         <v>0.0</v>
@@ -11180,7 +11192,7 @@
         <v>1035</v>
       </c>
       <c r="E72" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F72" s="38" t="s">
         <v>760</v>
@@ -11189,10 +11201,10 @@
         <v>760</v>
       </c>
       <c r="H72" s="37" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="I72" s="37" t="s">
-        <v>1629</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="73">
@@ -11201,7 +11213,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="C73" s="36">
         <v>1.0</v>
@@ -11210,19 +11222,19 @@
         <v>1035</v>
       </c>
       <c r="E73" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F73" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G73" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H73" s="37" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="I73" s="37" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="74">
@@ -11231,7 +11243,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="C74" s="36">
         <v>0.0</v>
@@ -11240,7 +11252,7 @@
         <v>1035</v>
       </c>
       <c r="E74" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F74" s="38" t="s">
         <v>760</v>
@@ -11249,10 +11261,10 @@
         <v>760</v>
       </c>
       <c r="H74" s="37" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
       <c r="I74" s="37" t="s">
-        <v>1635</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="75">
@@ -11261,7 +11273,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>1636</v>
+        <v>1640</v>
       </c>
       <c r="C75" s="36">
         <v>1.0</v>
@@ -11270,19 +11282,19 @@
         <v>1035</v>
       </c>
       <c r="E75" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F75" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G75" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H75" s="37" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="I75" s="37" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="76">
@@ -11291,7 +11303,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1639</v>
+        <v>1643</v>
       </c>
       <c r="C76" s="36">
         <v>0.0</v>
@@ -11300,7 +11312,7 @@
         <v>1035</v>
       </c>
       <c r="E76" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F76" s="38" t="s">
         <v>760</v>
@@ -11309,10 +11321,10 @@
         <v>760</v>
       </c>
       <c r="H76" s="37" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
       <c r="I76" s="37" t="s">
-        <v>1641</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="77">
@@ -11321,7 +11333,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="C77" s="36">
         <v>1.0</v>
@@ -11330,19 +11342,19 @@
         <v>1035</v>
       </c>
       <c r="E77" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F77" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G77" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H77" s="37" t="s">
-        <v>1643</v>
+        <v>1647</v>
       </c>
       <c r="I77" s="37" t="s">
-        <v>1644</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="78">
@@ -11351,7 +11363,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>1645</v>
+        <v>1649</v>
       </c>
       <c r="C78" s="36">
         <v>0.0</v>
@@ -11360,7 +11372,7 @@
         <v>1035</v>
       </c>
       <c r="E78" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F78" s="38" t="s">
         <v>760</v>
@@ -11369,10 +11381,10 @@
         <v>760</v>
       </c>
       <c r="H78" s="37" t="s">
-        <v>1646</v>
+        <v>1650</v>
       </c>
       <c r="I78" s="37" t="s">
-        <v>1647</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="79">
@@ -11381,7 +11393,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="C79" s="36">
         <v>0.0</v>
@@ -11390,7 +11402,7 @@
         <v>1035</v>
       </c>
       <c r="E79" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F79" s="38" t="s">
         <v>760</v>
@@ -11399,10 +11411,10 @@
         <v>760</v>
       </c>
       <c r="H79" s="37" t="s">
-        <v>1648</v>
+        <v>1652</v>
       </c>
       <c r="I79" s="37" t="s">
-        <v>1649</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="80">
@@ -11411,7 +11423,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>1650</v>
+        <v>1654</v>
       </c>
       <c r="C80" s="36">
         <v>1.0</v>
@@ -11420,19 +11432,19 @@
         <v>1035</v>
       </c>
       <c r="E80" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F80" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G80" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H80" s="37" t="s">
-        <v>1651</v>
+        <v>1655</v>
       </c>
       <c r="I80" s="37" t="s">
-        <v>1652</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="81">
@@ -11441,7 +11453,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="C81" s="36">
         <v>1.0</v>
@@ -11450,19 +11462,19 @@
         <v>1035</v>
       </c>
       <c r="E81" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F81" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G81" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H81" s="37" t="s">
-        <v>1654</v>
+        <v>1658</v>
       </c>
       <c r="I81" s="37" t="s">
-        <v>1655</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="82">
@@ -11471,7 +11483,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="C82" s="36">
         <v>1.0</v>
@@ -11480,19 +11492,19 @@
         <v>1035</v>
       </c>
       <c r="E82" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F82" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G82" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H82" s="37" t="s">
-        <v>1657</v>
+        <v>1661</v>
       </c>
       <c r="I82" s="37" t="s">
-        <v>1658</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="83">
@@ -11501,7 +11513,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="C83" s="36">
         <v>0.0</v>
@@ -11510,7 +11522,7 @@
         <v>1035</v>
       </c>
       <c r="E83" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F83" s="38" t="s">
         <v>760</v>
@@ -11519,10 +11531,10 @@
         <v>760</v>
       </c>
       <c r="H83" s="37" t="s">
-        <v>1660</v>
+        <v>1664</v>
       </c>
       <c r="I83" s="37" t="s">
-        <v>1661</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="84">
@@ -11531,7 +11543,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>1662</v>
+        <v>1666</v>
       </c>
       <c r="C84" s="36">
         <v>0.0</v>
@@ -11540,7 +11552,7 @@
         <v>1035</v>
       </c>
       <c r="E84" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F84" s="38" t="s">
         <v>760</v>
@@ -11549,10 +11561,10 @@
         <v>760</v>
       </c>
       <c r="H84" s="37" t="s">
-        <v>1663</v>
+        <v>1667</v>
       </c>
       <c r="I84" s="37" t="s">
-        <v>1664</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="85">
@@ -11561,7 +11573,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="36" t="s">
-        <v>1665</v>
+        <v>1669</v>
       </c>
       <c r="C85" s="36">
         <v>0.0</v>
@@ -11570,7 +11582,7 @@
         <v>1035</v>
       </c>
       <c r="E85" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F85" s="38" t="s">
         <v>760</v>
@@ -11579,10 +11591,10 @@
         <v>760</v>
       </c>
       <c r="H85" s="37" t="s">
-        <v>1666</v>
+        <v>1670</v>
       </c>
       <c r="I85" s="37" t="s">
-        <v>1667</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="86">
@@ -11600,7 +11612,7 @@
         <v>1035</v>
       </c>
       <c r="E86" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F86" s="38" t="s">
         <v>760</v>
@@ -11609,10 +11621,10 @@
         <v>760</v>
       </c>
       <c r="H86" s="37" t="s">
-        <v>1668</v>
+        <v>1672</v>
       </c>
       <c r="I86" s="37" t="s">
-        <v>1669</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="87">
@@ -11630,7 +11642,7 @@
         <v>1035</v>
       </c>
       <c r="E87" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F87" s="38" t="s">
         <v>760</v>
@@ -11639,10 +11651,10 @@
         <v>760</v>
       </c>
       <c r="H87" s="37" t="s">
-        <v>1670</v>
+        <v>1674</v>
       </c>
       <c r="I87" s="37" t="s">
-        <v>1670</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="88">
@@ -11660,7 +11672,7 @@
         <v>1035</v>
       </c>
       <c r="E88" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F88" s="38" t="s">
         <v>760</v>
@@ -11669,10 +11681,10 @@
         <v>760</v>
       </c>
       <c r="H88" s="37" t="s">
-        <v>1671</v>
+        <v>1675</v>
       </c>
       <c r="I88" s="37" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="89">
@@ -11690,7 +11702,7 @@
         <v>1035</v>
       </c>
       <c r="E89" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F89" s="38" t="s">
         <v>760</v>
@@ -11699,10 +11711,10 @@
         <v>760</v>
       </c>
       <c r="H89" s="37" t="s">
-        <v>1673</v>
+        <v>1677</v>
       </c>
       <c r="I89" s="37" t="s">
-        <v>1674</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="90">
@@ -11720,7 +11732,7 @@
         <v>1035</v>
       </c>
       <c r="E90" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F90" s="38" t="s">
         <v>760</v>
@@ -11729,10 +11741,10 @@
         <v>760</v>
       </c>
       <c r="H90" s="37" t="s">
-        <v>1675</v>
+        <v>1679</v>
       </c>
       <c r="I90" s="37" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="91">
@@ -11750,7 +11762,7 @@
         <v>1035</v>
       </c>
       <c r="E91" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F91" s="38" t="s">
         <v>760</v>
@@ -11759,10 +11771,10 @@
         <v>760</v>
       </c>
       <c r="H91" s="37" t="s">
-        <v>1677</v>
+        <v>1681</v>
       </c>
       <c r="I91" s="37" t="s">
-        <v>1678</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="92">
@@ -11780,7 +11792,7 @@
         <v>1035</v>
       </c>
       <c r="E92" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F92" s="38" t="s">
         <v>760</v>
@@ -11789,10 +11801,10 @@
         <v>760</v>
       </c>
       <c r="H92" s="37" t="s">
-        <v>1679</v>
+        <v>1683</v>
       </c>
       <c r="I92" s="37" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="93">
@@ -11810,7 +11822,7 @@
         <v>1035</v>
       </c>
       <c r="E93" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F93" s="38" t="s">
         <v>760</v>
@@ -11819,10 +11831,10 @@
         <v>760</v>
       </c>
       <c r="H93" s="37" t="s">
-        <v>1681</v>
+        <v>1685</v>
       </c>
       <c r="I93" s="37" t="s">
-        <v>1682</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="94">
@@ -11840,7 +11852,7 @@
         <v>1035</v>
       </c>
       <c r="E94" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F94" s="38" t="s">
         <v>760</v>
@@ -11849,10 +11861,10 @@
         <v>760</v>
       </c>
       <c r="H94" s="37" t="s">
-        <v>1683</v>
+        <v>1687</v>
       </c>
       <c r="I94" s="37" t="s">
-        <v>1684</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="95">
@@ -11870,7 +11882,7 @@
         <v>1040</v>
       </c>
       <c r="E95" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F95" s="38" t="s">
         <v>760</v>
@@ -11879,10 +11891,10 @@
         <v>760</v>
       </c>
       <c r="H95" s="37" t="s">
-        <v>1685</v>
+        <v>1689</v>
       </c>
       <c r="I95" s="37" t="s">
-        <v>1686</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="96">
@@ -11900,7 +11912,7 @@
         <v>1035</v>
       </c>
       <c r="E96" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F96" s="38" t="s">
         <v>760</v>
@@ -11909,10 +11921,10 @@
         <v>760</v>
       </c>
       <c r="H96" s="37" t="s">
-        <v>1687</v>
+        <v>1691</v>
       </c>
       <c r="I96" s="37" t="s">
-        <v>1688</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="97">
@@ -11930,7 +11942,7 @@
         <v>1035</v>
       </c>
       <c r="E97" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F97" s="38" t="s">
         <v>760</v>
@@ -11939,10 +11951,10 @@
         <v>760</v>
       </c>
       <c r="H97" s="37" t="s">
-        <v>1689</v>
+        <v>1693</v>
       </c>
       <c r="I97" s="37" t="s">
-        <v>1690</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="98">
@@ -11960,7 +11972,7 @@
         <v>1035</v>
       </c>
       <c r="E98" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F98" s="38" t="s">
         <v>760</v>
@@ -11969,10 +11981,10 @@
         <v>760</v>
       </c>
       <c r="H98" s="37" t="s">
-        <v>1691</v>
+        <v>1695</v>
       </c>
       <c r="I98" s="37" t="s">
-        <v>1692</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="99">
@@ -11999,10 +12011,10 @@
         <v>760</v>
       </c>
       <c r="H99" s="37" t="s">
-        <v>1693</v>
+        <v>1697</v>
       </c>
       <c r="I99" s="37" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="100">
@@ -12020,7 +12032,7 @@
         <v>1035</v>
       </c>
       <c r="E100" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F100" s="38" t="s">
         <v>760</v>
@@ -12029,10 +12041,10 @@
         <v>760</v>
       </c>
       <c r="H100" s="37" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="I100" s="37" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="101">
@@ -12050,7 +12062,7 @@
         <v>1035</v>
       </c>
       <c r="E101" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F101" s="38" t="s">
         <v>760</v>
@@ -12059,10 +12071,10 @@
         <v>760</v>
       </c>
       <c r="H101" s="37" t="s">
-        <v>1697</v>
+        <v>1701</v>
       </c>
       <c r="I101" s="37" t="s">
-        <v>1698</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="102">
@@ -12080,7 +12092,7 @@
         <v>1035</v>
       </c>
       <c r="E102" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F102" s="38" t="s">
         <v>760</v>
@@ -12089,10 +12101,10 @@
         <v>760</v>
       </c>
       <c r="H102" s="37" t="s">
-        <v>1699</v>
+        <v>1703</v>
       </c>
       <c r="I102" s="37" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="103">
@@ -12101,7 +12113,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="36" t="s">
-        <v>1701</v>
+        <v>1705</v>
       </c>
       <c r="C103" s="36">
         <v>0.0</v>
@@ -12110,7 +12122,7 @@
         <v>1035</v>
       </c>
       <c r="E103" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F103" s="38" t="s">
         <v>760</v>
@@ -12119,10 +12131,10 @@
         <v>760</v>
       </c>
       <c r="H103" s="37" t="s">
-        <v>1702</v>
+        <v>1706</v>
       </c>
       <c r="I103" s="37" t="s">
-        <v>1703</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="104">
@@ -12131,7 +12143,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="C104" s="36">
         <v>1.0</v>
@@ -12140,19 +12152,19 @@
         <v>1035</v>
       </c>
       <c r="E104" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F104" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G104" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H104" s="37" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="I104" s="37" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="105">
@@ -12161,7 +12173,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="C105" s="36">
         <v>0.0</v>
@@ -12170,7 +12182,7 @@
         <v>1035</v>
       </c>
       <c r="E105" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F105" s="38" t="s">
         <v>760</v>
@@ -12179,10 +12191,10 @@
         <v>760</v>
       </c>
       <c r="H105" s="37" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
       <c r="I105" s="37" t="s">
-        <v>1709</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="106">
@@ -12191,7 +12203,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>1710</v>
+        <v>1714</v>
       </c>
       <c r="C106" s="36">
         <v>1.0</v>
@@ -12200,19 +12212,19 @@
         <v>1035</v>
       </c>
       <c r="E106" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F106" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G106" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H106" s="37" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
       <c r="I106" s="37" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="107">
@@ -12221,7 +12233,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="C107" s="36">
         <v>0.0</v>
@@ -12230,7 +12242,7 @@
         <v>1035</v>
       </c>
       <c r="E107" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F107" s="38" t="s">
         <v>760</v>
@@ -12239,10 +12251,10 @@
         <v>760</v>
       </c>
       <c r="H107" s="37" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="I107" s="37" t="s">
-        <v>1715</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="108">
@@ -12251,7 +12263,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>1716</v>
+        <v>1720</v>
       </c>
       <c r="C108" s="36">
         <v>1.0</v>
@@ -12260,19 +12272,19 @@
         <v>1035</v>
       </c>
       <c r="E108" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F108" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G108" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H108" s="37" t="s">
-        <v>1717</v>
+        <v>1721</v>
       </c>
       <c r="I108" s="37" t="s">
-        <v>1717</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="109">
@@ -12281,7 +12293,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>1718</v>
+        <v>1722</v>
       </c>
       <c r="C109" s="36">
         <v>0.0</v>
@@ -12290,7 +12302,7 @@
         <v>1035</v>
       </c>
       <c r="E109" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F109" s="38" t="s">
         <v>760</v>
@@ -12299,10 +12311,10 @@
         <v>760</v>
       </c>
       <c r="H109" s="37" t="s">
-        <v>1719</v>
+        <v>1723</v>
       </c>
       <c r="I109" s="37" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="110">
@@ -12311,7 +12323,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="C110" s="36">
         <v>1.0</v>
@@ -12320,19 +12332,19 @@
         <v>1035</v>
       </c>
       <c r="E110" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F110" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G110" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H110" s="37" t="s">
-        <v>1722</v>
+        <v>1726</v>
       </c>
       <c r="I110" s="37" t="s">
-        <v>1723</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="111">
@@ -12341,7 +12353,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>1724</v>
+        <v>1728</v>
       </c>
       <c r="C111" s="36">
         <v>0.0</v>
@@ -12350,7 +12362,7 @@
         <v>1035</v>
       </c>
       <c r="E111" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F111" s="38" t="s">
         <v>760</v>
@@ -12359,10 +12371,10 @@
         <v>760</v>
       </c>
       <c r="H111" s="37" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="I111" s="37" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="112">
@@ -12371,7 +12383,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="36" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="C112" s="36">
         <v>1.0</v>
@@ -12380,19 +12392,19 @@
         <v>1035</v>
       </c>
       <c r="E112" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F112" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G112" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H112" s="37" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="I112" s="37" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="113">
@@ -12401,7 +12413,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>1730</v>
+        <v>1734</v>
       </c>
       <c r="C113" s="36">
         <v>0.0</v>
@@ -12410,7 +12422,7 @@
         <v>1035</v>
       </c>
       <c r="E113" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F113" s="38" t="s">
         <v>760</v>
@@ -12419,10 +12431,10 @@
         <v>760</v>
       </c>
       <c r="H113" s="37" t="s">
-        <v>1731</v>
+        <v>1735</v>
       </c>
       <c r="I113" s="37" t="s">
-        <v>1732</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="114">
@@ -12431,7 +12443,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="C114" s="36">
         <v>0.0</v>
@@ -12440,7 +12452,7 @@
         <v>1035</v>
       </c>
       <c r="E114" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F114" s="38" t="s">
         <v>760</v>
@@ -12449,10 +12461,10 @@
         <v>760</v>
       </c>
       <c r="H114" s="37" t="s">
-        <v>1733</v>
+        <v>1737</v>
       </c>
       <c r="I114" s="37" t="s">
-        <v>1734</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="115">
@@ -12461,7 +12473,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>1735</v>
+        <v>1739</v>
       </c>
       <c r="C115" s="36">
         <v>0.0</v>
@@ -12470,7 +12482,7 @@
         <v>1035</v>
       </c>
       <c r="E115" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F115" s="38" t="s">
         <v>760</v>
@@ -12479,10 +12491,10 @@
         <v>760</v>
       </c>
       <c r="H115" s="37" t="s">
-        <v>1736</v>
+        <v>1740</v>
       </c>
       <c r="I115" s="37" t="s">
-        <v>1737</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="116">
@@ -12491,7 +12503,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="36" t="s">
-        <v>1738</v>
+        <v>1742</v>
       </c>
       <c r="C116" s="36">
         <v>1.0</v>
@@ -12500,19 +12512,19 @@
         <v>1035</v>
       </c>
       <c r="E116" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F116" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G116" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H116" s="37" t="s">
-        <v>1739</v>
+        <v>1743</v>
       </c>
       <c r="I116" s="37" t="s">
-        <v>1740</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="117">
@@ -12530,7 +12542,7 @@
         <v>1035</v>
       </c>
       <c r="E117" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F117" s="38" t="s">
         <v>760</v>
@@ -12539,10 +12551,10 @@
         <v>760</v>
       </c>
       <c r="H117" s="37" t="s">
-        <v>1741</v>
+        <v>1745</v>
       </c>
       <c r="I117" s="37" t="s">
-        <v>1742</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="118">
@@ -12560,7 +12572,7 @@
         <v>1038</v>
       </c>
       <c r="E118" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F118" s="38" t="s">
         <v>760</v>
@@ -12569,10 +12581,10 @@
         <v>760</v>
       </c>
       <c r="H118" s="37" t="s">
-        <v>1743</v>
+        <v>1747</v>
       </c>
       <c r="I118" s="37" t="s">
-        <v>1744</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="119">
@@ -12590,7 +12602,7 @@
         <v>1035</v>
       </c>
       <c r="E119" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F119" s="38" t="s">
         <v>760</v>
@@ -12599,10 +12611,10 @@
         <v>760</v>
       </c>
       <c r="H119" s="37" t="s">
-        <v>1745</v>
+        <v>1749</v>
       </c>
       <c r="I119" s="37" t="s">
-        <v>1746</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="120">
@@ -12620,7 +12632,7 @@
         <v>1035</v>
       </c>
       <c r="E120" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F120" s="38" t="s">
         <v>760</v>
@@ -12629,10 +12641,10 @@
         <v>760</v>
       </c>
       <c r="H120" s="37" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="I120" s="37" t="s">
-        <v>1748</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="121">
@@ -12641,7 +12653,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="C121" s="36">
         <v>0.0</v>
@@ -12650,7 +12662,7 @@
         <v>1035</v>
       </c>
       <c r="E121" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F121" s="38" t="s">
         <v>760</v>
@@ -12659,10 +12671,10 @@
         <v>760</v>
       </c>
       <c r="H121" s="37" t="s">
-        <v>1749</v>
+        <v>1753</v>
       </c>
       <c r="I121" s="37" t="s">
-        <v>1750</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="122">
@@ -12671,7 +12683,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="36" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="C122" s="36">
         <v>0.0</v>
@@ -12680,7 +12692,7 @@
         <v>1035</v>
       </c>
       <c r="E122" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F122" s="38" t="s">
         <v>760</v>
@@ -12689,10 +12701,10 @@
         <v>760</v>
       </c>
       <c r="H122" s="37" t="s">
-        <v>1751</v>
+        <v>1755</v>
       </c>
       <c r="I122" s="37" t="s">
-        <v>1752</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="123">
@@ -12701,7 +12713,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>1753</v>
+        <v>1757</v>
       </c>
       <c r="C123" s="36">
         <v>0.0</v>
@@ -12710,7 +12722,7 @@
         <v>1035</v>
       </c>
       <c r="E123" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F123" s="38" t="s">
         <v>760</v>
@@ -12719,10 +12731,10 @@
         <v>760</v>
       </c>
       <c r="H123" s="37" t="s">
-        <v>1754</v>
+        <v>1758</v>
       </c>
       <c r="I123" s="37" t="s">
-        <v>1755</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="124">
@@ -12731,7 +12743,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="36" t="s">
-        <v>1756</v>
+        <v>1760</v>
       </c>
       <c r="C124" s="36">
         <v>0.0</v>
@@ -12740,7 +12752,7 @@
         <v>1035</v>
       </c>
       <c r="E124" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F124" s="38" t="s">
         <v>760</v>
@@ -12749,10 +12761,10 @@
         <v>760</v>
       </c>
       <c r="H124" s="37" t="s">
-        <v>1757</v>
+        <v>1761</v>
       </c>
       <c r="I124" s="37" t="s">
-        <v>1758</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="125">
@@ -12770,7 +12782,7 @@
         <v>1035</v>
       </c>
       <c r="E125" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F125" s="38" t="s">
         <v>760</v>
@@ -12779,10 +12791,10 @@
         <v>760</v>
       </c>
       <c r="H125" s="37" t="s">
-        <v>1759</v>
+        <v>1763</v>
       </c>
       <c r="I125" s="37" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="126">
@@ -12800,7 +12812,7 @@
         <v>1035</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F126" s="38" t="s">
         <v>760</v>
@@ -12809,10 +12821,10 @@
         <v>760</v>
       </c>
       <c r="H126" s="37" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="I126" s="37" t="s">
-        <v>1762</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="127">
@@ -12821,7 +12833,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="36" t="s">
-        <v>1763</v>
+        <v>1767</v>
       </c>
       <c r="C127" s="36">
         <v>0.0</v>
@@ -12830,19 +12842,19 @@
         <v>1057</v>
       </c>
       <c r="E127" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F127" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G127" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H127" s="37" t="s">
-        <v>1764</v>
+        <v>1768</v>
       </c>
       <c r="I127" s="37" t="s">
-        <v>1764</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="128">
@@ -12851,7 +12863,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="36" t="s">
-        <v>1765</v>
+        <v>1769</v>
       </c>
       <c r="C128" s="36">
         <v>1.0</v>
@@ -12860,19 +12872,19 @@
         <v>1059</v>
       </c>
       <c r="E128" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F128" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G128" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H128" s="37" t="s">
-        <v>1766</v>
+        <v>1770</v>
       </c>
       <c r="I128" s="37" t="s">
-        <v>1766</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="129">
@@ -12881,7 +12893,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="36" t="s">
-        <v>1767</v>
+        <v>1771</v>
       </c>
       <c r="C129" s="36">
         <v>0.0</v>
@@ -12890,19 +12902,19 @@
         <v>1061</v>
       </c>
       <c r="E129" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F129" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G129" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H129" s="37" t="s">
-        <v>1768</v>
+        <v>1772</v>
       </c>
       <c r="I129" s="37" t="s">
-        <v>1768</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="130">
@@ -12911,7 +12923,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="36" t="s">
-        <v>1769</v>
+        <v>1773</v>
       </c>
       <c r="C130" s="36">
         <v>1.0</v>
@@ -12920,19 +12932,19 @@
         <v>1063</v>
       </c>
       <c r="E130" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F130" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G130" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H130" s="37" t="s">
-        <v>1770</v>
+        <v>1774</v>
       </c>
       <c r="I130" s="37" t="s">
-        <v>1770</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="131">
@@ -12941,7 +12953,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="36" t="s">
-        <v>1771</v>
+        <v>1775</v>
       </c>
       <c r="C131" s="36">
         <v>0.0</v>
@@ -12950,19 +12962,19 @@
         <v>1065</v>
       </c>
       <c r="E131" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F131" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G131" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H131" s="37" t="s">
-        <v>1772</v>
+        <v>1776</v>
       </c>
       <c r="I131" s="37" t="s">
-        <v>1772</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="132">
@@ -12971,7 +12983,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="36" t="s">
-        <v>1773</v>
+        <v>1777</v>
       </c>
       <c r="C132" s="36">
         <v>1.0</v>
@@ -12980,19 +12992,19 @@
         <v>1067</v>
       </c>
       <c r="E132" s="44" t="s">
-        <v>1774</v>
+        <v>1778</v>
       </c>
       <c r="F132" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G132" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H132" s="37" t="s">
-        <v>1775</v>
+        <v>1779</v>
       </c>
       <c r="I132" s="37" t="s">
-        <v>1775</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="133">
@@ -13001,7 +13013,7 @@
         <v>131</v>
       </c>
       <c r="B133" s="36" t="s">
-        <v>1776</v>
+        <v>1780</v>
       </c>
       <c r="C133" s="36">
         <v>0.0</v>
@@ -13010,19 +13022,19 @@
         <v>1069</v>
       </c>
       <c r="E133" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F133" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G133" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H133" s="37" t="s">
-        <v>1777</v>
+        <v>1781</v>
       </c>
       <c r="I133" s="37" t="s">
-        <v>1777</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="134">
@@ -13031,7 +13043,7 @@
         <v>132</v>
       </c>
       <c r="B134" s="36" t="s">
-        <v>1778</v>
+        <v>1782</v>
       </c>
       <c r="C134" s="36">
         <v>1.0</v>
@@ -13040,19 +13052,19 @@
         <v>1071</v>
       </c>
       <c r="E134" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F134" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G134" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H134" s="37" t="s">
-        <v>1779</v>
+        <v>1783</v>
       </c>
       <c r="I134" s="37" t="s">
-        <v>1779</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="135">
@@ -13061,7 +13073,7 @@
         <v>133</v>
       </c>
       <c r="B135" s="36" t="s">
-        <v>1780</v>
+        <v>1784</v>
       </c>
       <c r="C135" s="36">
         <v>0.0</v>
@@ -13070,19 +13082,19 @@
         <v>1035</v>
       </c>
       <c r="E135" s="44" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="F135" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G135" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H135" s="37" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
       <c r="I135" s="37" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="136">
@@ -13091,7 +13103,7 @@
         <v>134</v>
       </c>
       <c r="B136" s="36" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="C136" s="36">
         <v>0.0</v>
@@ -13100,19 +13112,19 @@
         <v>1073</v>
       </c>
       <c r="E136" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F136" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G136" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H136" s="37" t="s">
-        <v>1783</v>
+        <v>1787</v>
       </c>
       <c r="I136" s="37" t="s">
-        <v>1784</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="137">
@@ -13121,7 +13133,7 @@
         <v>135</v>
       </c>
       <c r="B137" s="36" t="s">
-        <v>1785</v>
+        <v>1789</v>
       </c>
       <c r="C137" s="36">
         <v>1.0</v>
@@ -13130,19 +13142,19 @@
         <v>1053</v>
       </c>
       <c r="E137" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F137" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G137" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H137" s="37" t="s">
-        <v>1786</v>
+        <v>1790</v>
       </c>
       <c r="I137" s="37" t="s">
-        <v>1786</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="138">
@@ -13151,7 +13163,7 @@
         <v>136</v>
       </c>
       <c r="B138" s="36" t="s">
-        <v>1787</v>
+        <v>1791</v>
       </c>
       <c r="C138" s="36">
         <v>1.0</v>
@@ -13160,19 +13172,19 @@
         <v>1055</v>
       </c>
       <c r="E138" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F138" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G138" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H138" s="37" t="s">
-        <v>1788</v>
+        <v>1792</v>
       </c>
       <c r="I138" s="37" t="s">
-        <v>1788</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="139">
@@ -13181,7 +13193,7 @@
         <v>137</v>
       </c>
       <c r="B139" s="36" t="s">
-        <v>1789</v>
+        <v>1793</v>
       </c>
       <c r="C139" s="36">
         <v>0.0</v>
@@ -13190,19 +13202,19 @@
         <v>1075</v>
       </c>
       <c r="E139" s="44" t="s">
-        <v>1790</v>
+        <v>1794</v>
       </c>
       <c r="F139" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G139" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H139" s="37" t="s">
-        <v>1791</v>
+        <v>1795</v>
       </c>
       <c r="I139" s="37" t="s">
-        <v>1791</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="140">
@@ -13211,7 +13223,7 @@
         <v>138</v>
       </c>
       <c r="B140" s="36" t="s">
-        <v>1792</v>
+        <v>1796</v>
       </c>
       <c r="C140" s="36">
         <v>1.0</v>
@@ -13220,19 +13232,19 @@
         <v>1077</v>
       </c>
       <c r="E140" s="44" t="s">
-        <v>1774</v>
+        <v>1778</v>
       </c>
       <c r="F140" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G140" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H140" s="37" t="s">
-        <v>1793</v>
+        <v>1797</v>
       </c>
       <c r="I140" s="37" t="s">
-        <v>1793</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="141">
@@ -13241,7 +13253,7 @@
         <v>139</v>
       </c>
       <c r="B141" s="36" t="s">
-        <v>1794</v>
+        <v>1798</v>
       </c>
       <c r="C141" s="36">
         <v>0.0</v>
@@ -13250,19 +13262,19 @@
         <v>1079</v>
       </c>
       <c r="E141" s="44" t="s">
-        <v>1790</v>
+        <v>1794</v>
       </c>
       <c r="F141" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G141" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H141" s="37" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
       <c r="I141" s="37" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="142">
@@ -13271,7 +13283,7 @@
         <v>140</v>
       </c>
       <c r="B142" s="36" t="s">
-        <v>1796</v>
+        <v>1800</v>
       </c>
       <c r="C142" s="36">
         <v>1.0</v>
@@ -13280,19 +13292,19 @@
         <v>1081</v>
       </c>
       <c r="E142" s="44" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="F142" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G142" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H142" s="37" t="s">
-        <v>1797</v>
+        <v>1801</v>
       </c>
       <c r="I142" s="37" t="s">
-        <v>1797</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="143">
@@ -13301,7 +13313,7 @@
         <v>141</v>
       </c>
       <c r="B143" s="36" t="s">
-        <v>1798</v>
+        <v>1802</v>
       </c>
       <c r="C143" s="36">
         <v>0.0</v>
@@ -13310,19 +13322,19 @@
         <v>1083</v>
       </c>
       <c r="E143" s="44" t="s">
-        <v>1790</v>
+        <v>1794</v>
       </c>
       <c r="F143" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G143" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H143" s="37" t="s">
-        <v>1799</v>
+        <v>1803</v>
       </c>
       <c r="I143" s="37" t="s">
-        <v>1799</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="144">
@@ -13331,7 +13343,7 @@
         <v>142</v>
       </c>
       <c r="B144" s="36" t="s">
-        <v>1800</v>
+        <v>1804</v>
       </c>
       <c r="C144" s="36">
         <v>1.0</v>
@@ -13340,19 +13352,19 @@
         <v>1085</v>
       </c>
       <c r="E144" s="44" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="F144" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G144" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H144" s="37" t="s">
-        <v>1801</v>
+        <v>1805</v>
       </c>
       <c r="I144" s="37" t="s">
-        <v>1801</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="145">
@@ -13361,7 +13373,7 @@
         <v>143</v>
       </c>
       <c r="B145" s="36" t="s">
-        <v>1802</v>
+        <v>1806</v>
       </c>
       <c r="C145" s="36">
         <v>0.0</v>
@@ -13370,19 +13382,19 @@
         <v>1087</v>
       </c>
       <c r="E145" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F145" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G145" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H145" s="37" t="s">
-        <v>1803</v>
+        <v>1807</v>
       </c>
       <c r="I145" s="37" t="s">
-        <v>1803</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="146">
@@ -13391,7 +13403,7 @@
         <v>144</v>
       </c>
       <c r="B146" s="36" t="s">
-        <v>1804</v>
+        <v>1808</v>
       </c>
       <c r="C146" s="36">
         <v>1.0</v>
@@ -13400,19 +13412,19 @@
         <v>1089</v>
       </c>
       <c r="E146" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F146" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G146" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H146" s="37" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
       <c r="I146" s="37" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="147">
@@ -13421,7 +13433,7 @@
         <v>145</v>
       </c>
       <c r="B147" s="36" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="C147" s="36">
         <v>1.0</v>
@@ -13430,19 +13442,19 @@
         <v>1091</v>
       </c>
       <c r="E147" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F147" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G147" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H147" s="37" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
       <c r="I147" s="37" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="148">
@@ -13451,7 +13463,7 @@
         <v>146</v>
       </c>
       <c r="B148" s="36" t="s">
-        <v>1807</v>
+        <v>1811</v>
       </c>
       <c r="C148" s="36">
         <v>0.0</v>
@@ -13460,19 +13472,19 @@
         <v>1109</v>
       </c>
       <c r="E148" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F148" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G148" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H148" s="37" t="s">
-        <v>1808</v>
+        <v>1812</v>
       </c>
       <c r="I148" s="37" t="s">
-        <v>1808</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="149">
@@ -13481,7 +13493,7 @@
         <v>147</v>
       </c>
       <c r="B149" s="36" t="s">
-        <v>1809</v>
+        <v>1813</v>
       </c>
       <c r="C149" s="36">
         <v>1.0</v>
@@ -13490,19 +13502,19 @@
         <v>1111</v>
       </c>
       <c r="E149" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F149" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G149" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H149" s="37" t="s">
-        <v>1810</v>
+        <v>1814</v>
       </c>
       <c r="I149" s="37" t="s">
-        <v>1810</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="150">
@@ -13511,7 +13523,7 @@
         <v>148</v>
       </c>
       <c r="B150" s="36" t="s">
-        <v>1811</v>
+        <v>1815</v>
       </c>
       <c r="C150" s="36">
         <v>0.0</v>
@@ -13520,19 +13532,19 @@
         <v>1113</v>
       </c>
       <c r="E150" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F150" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G150" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H150" s="37" t="s">
-        <v>1812</v>
+        <v>1816</v>
       </c>
       <c r="I150" s="37" t="s">
-        <v>1812</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="151">
@@ -13541,7 +13553,7 @@
         <v>149</v>
       </c>
       <c r="B151" s="36" t="s">
-        <v>1813</v>
+        <v>1817</v>
       </c>
       <c r="C151" s="36">
         <v>1.0</v>
@@ -13550,19 +13562,19 @@
         <v>1115</v>
       </c>
       <c r="E151" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F151" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G151" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H151" s="37" t="s">
-        <v>1814</v>
+        <v>1818</v>
       </c>
       <c r="I151" s="37" t="s">
-        <v>1814</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="152">
@@ -13571,7 +13583,7 @@
         <v>150</v>
       </c>
       <c r="B152" s="36" t="s">
-        <v>1815</v>
+        <v>1819</v>
       </c>
       <c r="C152" s="36">
         <v>0.0</v>
@@ -13580,19 +13592,19 @@
         <v>1117</v>
       </c>
       <c r="E152" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F152" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G152" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H152" s="37" t="s">
-        <v>1816</v>
+        <v>1820</v>
       </c>
       <c r="I152" s="37" t="s">
-        <v>1816</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="153">
@@ -13601,7 +13613,7 @@
         <v>151</v>
       </c>
       <c r="B153" s="36" t="s">
-        <v>1817</v>
+        <v>1821</v>
       </c>
       <c r="C153" s="36">
         <v>1.0</v>
@@ -13610,19 +13622,19 @@
         <v>1119</v>
       </c>
       <c r="E153" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F153" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G153" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H153" s="37" t="s">
-        <v>1818</v>
+        <v>1822</v>
       </c>
       <c r="I153" s="37" t="s">
-        <v>1818</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="154">
@@ -13631,7 +13643,7 @@
         <v>152</v>
       </c>
       <c r="B154" s="36" t="s">
-        <v>1819</v>
+        <v>1823</v>
       </c>
       <c r="C154" s="36">
         <v>0.0</v>
@@ -13640,19 +13652,19 @@
         <v>1035</v>
       </c>
       <c r="E154" s="44" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="F154" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G154" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H154" s="37" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
       <c r="I154" s="37" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="155">
@@ -13661,7 +13673,7 @@
         <v>153</v>
       </c>
       <c r="B155" s="36" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="C155" s="36">
         <v>1.0</v>
@@ -13670,19 +13682,19 @@
         <v>1108</v>
       </c>
       <c r="E155" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F155" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G155" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H155" s="37" t="s">
-        <v>1820</v>
+        <v>1824</v>
       </c>
       <c r="I155" s="37" t="s">
-        <v>1820</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="156">
@@ -13691,7 +13703,7 @@
         <v>154</v>
       </c>
       <c r="B156" s="36" t="s">
-        <v>1821</v>
+        <v>1825</v>
       </c>
       <c r="C156" s="36">
         <v>1.0</v>
@@ -13700,19 +13712,19 @@
         <v>1120</v>
       </c>
       <c r="E156" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F156" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G156" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H156" s="37" t="s">
-        <v>1822</v>
+        <v>1826</v>
       </c>
       <c r="I156" s="37" t="s">
-        <v>1822</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="157">
@@ -13721,7 +13733,7 @@
         <v>155</v>
       </c>
       <c r="B157" s="36" t="s">
-        <v>1823</v>
+        <v>1827</v>
       </c>
       <c r="C157" s="36">
         <v>0.0</v>
@@ -13730,19 +13742,19 @@
         <v>1122</v>
       </c>
       <c r="E157" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F157" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G157" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H157" s="37" t="s">
-        <v>1824</v>
+        <v>1828</v>
       </c>
       <c r="I157" s="37" t="s">
-        <v>1824</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="158">
@@ -13751,7 +13763,7 @@
         <v>156</v>
       </c>
       <c r="B158" s="36" t="s">
-        <v>1825</v>
+        <v>1829</v>
       </c>
       <c r="C158" s="36">
         <v>1.0</v>
@@ -13760,19 +13772,19 @@
         <v>1124</v>
       </c>
       <c r="E158" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F158" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G158" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H158" s="37" t="s">
-        <v>1826</v>
+        <v>1830</v>
       </c>
       <c r="I158" s="37" t="s">
-        <v>1826</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="159">
@@ -13781,7 +13793,7 @@
         <v>157</v>
       </c>
       <c r="B159" s="36" t="s">
-        <v>1827</v>
+        <v>1831</v>
       </c>
       <c r="C159" s="36">
         <v>0.0</v>
@@ -13790,19 +13802,19 @@
         <v>1126</v>
       </c>
       <c r="E159" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F159" s="38" t="s">
-        <v>1828</v>
+        <v>1832</v>
       </c>
       <c r="G159" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H159" s="37" t="s">
-        <v>1829</v>
+        <v>1833</v>
       </c>
       <c r="I159" s="37" t="s">
-        <v>1829</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="160">
@@ -13811,7 +13823,7 @@
         <v>158</v>
       </c>
       <c r="B160" s="36" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
       <c r="C160" s="36">
         <v>0.0</v>
@@ -13820,19 +13832,19 @@
         <v>1129</v>
       </c>
       <c r="E160" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F160" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G160" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H160" s="37" t="s">
-        <v>1831</v>
+        <v>1835</v>
       </c>
       <c r="I160" s="37" t="s">
-        <v>1831</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="161">
@@ -13841,7 +13853,7 @@
         <v>159</v>
       </c>
       <c r="B161" s="36" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="C161" s="36">
         <v>1.0</v>
@@ -13850,19 +13862,19 @@
         <v>1131</v>
       </c>
       <c r="E161" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F161" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G161" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H161" s="37" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
       <c r="I161" s="37" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="162">
@@ -13871,7 +13883,7 @@
         <v>160</v>
       </c>
       <c r="B162" s="36" t="s">
-        <v>1834</v>
+        <v>1838</v>
       </c>
       <c r="C162" s="36">
         <v>0.0</v>
@@ -13880,19 +13892,19 @@
         <v>1133</v>
       </c>
       <c r="E162" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F162" s="38" t="s">
-        <v>1828</v>
+        <v>1832</v>
       </c>
       <c r="G162" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H162" s="37" t="s">
-        <v>1835</v>
+        <v>1839</v>
       </c>
       <c r="I162" s="37" t="s">
-        <v>1835</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="163">
@@ -13901,7 +13913,7 @@
         <v>161</v>
       </c>
       <c r="B163" s="36" t="s">
-        <v>1836</v>
+        <v>1840</v>
       </c>
       <c r="C163" s="36">
         <v>0.0</v>
@@ -13910,19 +13922,19 @@
         <v>1135</v>
       </c>
       <c r="E163" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F163" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G163" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H163" s="37" t="s">
-        <v>1837</v>
+        <v>1841</v>
       </c>
       <c r="I163" s="37" t="s">
-        <v>1837</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="164">
@@ -13931,7 +13943,7 @@
         <v>162</v>
       </c>
       <c r="B164" s="36" t="s">
-        <v>1838</v>
+        <v>1842</v>
       </c>
       <c r="C164" s="36">
         <v>1.0</v>
@@ -13940,19 +13952,19 @@
         <v>1137</v>
       </c>
       <c r="E164" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F164" s="38" t="s">
-        <v>1828</v>
+        <v>1832</v>
       </c>
       <c r="G164" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H164" s="37" t="s">
-        <v>1839</v>
+        <v>1843</v>
       </c>
       <c r="I164" s="37" t="s">
-        <v>1839</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="165">
@@ -13961,7 +13973,7 @@
         <v>163</v>
       </c>
       <c r="B165" s="36" t="s">
-        <v>1840</v>
+        <v>1844</v>
       </c>
       <c r="C165" s="36">
         <v>0.0</v>
@@ -13970,19 +13982,19 @@
         <v>1035</v>
       </c>
       <c r="E165" s="44" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="F165" s="38" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="G165" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H165" s="37" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
       <c r="I165" s="37" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="166">
@@ -14000,7 +14012,7 @@
         <v>1139</v>
       </c>
       <c r="E166" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F166" s="38" t="s">
         <v>760</v>
@@ -14009,10 +14021,10 @@
         <v>760</v>
       </c>
       <c r="H166" s="37" t="s">
-        <v>1841</v>
+        <v>1845</v>
       </c>
       <c r="I166" s="37" t="s">
-        <v>1841</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="167">
@@ -14030,7 +14042,7 @@
         <v>1141</v>
       </c>
       <c r="E167" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F167" s="38" t="s">
         <v>760</v>
@@ -14051,7 +14063,7 @@
         <v>166</v>
       </c>
       <c r="B168" s="36" t="s">
-        <v>1842</v>
+        <v>1846</v>
       </c>
       <c r="C168" s="36">
         <v>0.0</v>
@@ -14060,19 +14072,19 @@
         <v>1145</v>
       </c>
       <c r="E168" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F168" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G168" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H168" s="37" t="s">
-        <v>1843</v>
+        <v>1847</v>
       </c>
       <c r="I168" s="37" t="s">
-        <v>1843</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="169">
@@ -14081,7 +14093,7 @@
         <v>167</v>
       </c>
       <c r="B169" s="36" t="s">
-        <v>1844</v>
+        <v>1848</v>
       </c>
       <c r="C169" s="36">
         <v>1.0</v>
@@ -14090,19 +14102,19 @@
         <v>1147</v>
       </c>
       <c r="E169" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F169" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G169" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H169" s="37" t="s">
-        <v>1845</v>
+        <v>1849</v>
       </c>
       <c r="I169" s="37" t="s">
-        <v>1845</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="170">
@@ -14111,7 +14123,7 @@
         <v>168</v>
       </c>
       <c r="B170" s="36" t="s">
-        <v>1846</v>
+        <v>1850</v>
       </c>
       <c r="C170" s="36">
         <v>0.0</v>
@@ -14120,19 +14132,19 @@
         <v>1149</v>
       </c>
       <c r="E170" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F170" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G170" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H170" s="37" t="s">
-        <v>1847</v>
+        <v>1851</v>
       </c>
       <c r="I170" s="37" t="s">
-        <v>1847</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="171">
@@ -14141,7 +14153,7 @@
         <v>169</v>
       </c>
       <c r="B171" s="36" t="s">
-        <v>1848</v>
+        <v>1852</v>
       </c>
       <c r="C171" s="36">
         <v>1.0</v>
@@ -14150,19 +14162,19 @@
         <v>1151</v>
       </c>
       <c r="E171" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F171" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G171" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H171" s="37" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="I171" s="37" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="172">
@@ -14171,7 +14183,7 @@
         <v>170</v>
       </c>
       <c r="B172" s="36" t="s">
-        <v>1850</v>
+        <v>1854</v>
       </c>
       <c r="C172" s="36">
         <v>0.0</v>
@@ -14180,19 +14192,19 @@
         <v>1153</v>
       </c>
       <c r="E172" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F172" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G172" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H172" s="37" t="s">
-        <v>1851</v>
+        <v>1855</v>
       </c>
       <c r="I172" s="37" t="s">
-        <v>1851</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="173">
@@ -14201,7 +14213,7 @@
         <v>171</v>
       </c>
       <c r="B173" s="36" t="s">
-        <v>1852</v>
+        <v>1856</v>
       </c>
       <c r="C173" s="36">
         <v>1.0</v>
@@ -14210,19 +14222,19 @@
         <v>1155</v>
       </c>
       <c r="E173" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F173" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G173" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H173" s="37" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="I173" s="37" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="174">
@@ -14231,7 +14243,7 @@
         <v>172</v>
       </c>
       <c r="B174" s="36" t="s">
-        <v>1854</v>
+        <v>1858</v>
       </c>
       <c r="C174" s="36">
         <v>0.0</v>
@@ -14240,19 +14252,19 @@
         <v>1157</v>
       </c>
       <c r="E174" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F174" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G174" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H174" s="37" t="s">
-        <v>1855</v>
+        <v>1859</v>
       </c>
       <c r="I174" s="37" t="s">
-        <v>1855</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="175">
@@ -14261,7 +14273,7 @@
         <v>173</v>
       </c>
       <c r="B175" s="36" t="s">
-        <v>1856</v>
+        <v>1860</v>
       </c>
       <c r="C175" s="36">
         <v>1.0</v>
@@ -14270,19 +14282,19 @@
         <v>1159</v>
       </c>
       <c r="E175" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F175" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G175" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H175" s="37" t="s">
-        <v>1857</v>
+        <v>1861</v>
       </c>
       <c r="I175" s="37" t="s">
-        <v>1857</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="176">
@@ -14291,7 +14303,7 @@
         <v>174</v>
       </c>
       <c r="B176" s="36" t="s">
-        <v>1858</v>
+        <v>1862</v>
       </c>
       <c r="C176" s="36">
         <v>0.0</v>
@@ -14300,19 +14312,19 @@
         <v>1161</v>
       </c>
       <c r="E176" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F176" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G176" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H176" s="37" t="s">
-        <v>1859</v>
+        <v>1863</v>
       </c>
       <c r="I176" s="37" t="s">
-        <v>1859</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="177">
@@ -14321,7 +14333,7 @@
         <v>175</v>
       </c>
       <c r="B177" s="36" t="s">
-        <v>1860</v>
+        <v>1864</v>
       </c>
       <c r="C177" s="36">
         <v>0.0</v>
@@ -14330,19 +14342,19 @@
         <v>1163</v>
       </c>
       <c r="E177" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F177" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G177" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H177" s="37" t="s">
-        <v>1861</v>
+        <v>1865</v>
       </c>
       <c r="I177" s="37" t="s">
-        <v>1861</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="178">
@@ -14351,7 +14363,7 @@
         <v>176</v>
       </c>
       <c r="B178" s="36" t="s">
-        <v>1862</v>
+        <v>1866</v>
       </c>
       <c r="C178" s="36">
         <v>1.0</v>
@@ -14360,19 +14372,19 @@
         <v>1165</v>
       </c>
       <c r="E178" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F178" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G178" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H178" s="37" t="s">
-        <v>1863</v>
+        <v>1867</v>
       </c>
       <c r="I178" s="37" t="s">
-        <v>1863</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="179">
@@ -14381,7 +14393,7 @@
         <v>177</v>
       </c>
       <c r="B179" s="36" t="s">
-        <v>1864</v>
+        <v>1868</v>
       </c>
       <c r="C179" s="36">
         <v>1.0</v>
@@ -14390,19 +14402,19 @@
         <v>1167</v>
       </c>
       <c r="E179" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F179" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G179" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H179" s="37" t="s">
-        <v>1865</v>
+        <v>1869</v>
       </c>
       <c r="I179" s="37" t="s">
-        <v>1865</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="180">
@@ -14411,7 +14423,7 @@
         <v>178</v>
       </c>
       <c r="B180" s="36" t="s">
-        <v>1866</v>
+        <v>1870</v>
       </c>
       <c r="C180" s="36">
         <v>0.0</v>
@@ -14420,19 +14432,19 @@
         <v>1169</v>
       </c>
       <c r="E180" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F180" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G180" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H180" s="37" t="s">
-        <v>1867</v>
+        <v>1871</v>
       </c>
       <c r="I180" s="37" t="s">
-        <v>1867</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="181">
@@ -14441,7 +14453,7 @@
         <v>179</v>
       </c>
       <c r="B181" s="36" t="s">
-        <v>1868</v>
+        <v>1872</v>
       </c>
       <c r="C181" s="36">
         <v>1.0</v>
@@ -14450,19 +14462,19 @@
         <v>1171</v>
       </c>
       <c r="E181" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F181" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G181" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H181" s="37" t="s">
-        <v>1869</v>
+        <v>1873</v>
       </c>
       <c r="I181" s="37" t="s">
-        <v>1869</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="182">
@@ -14471,7 +14483,7 @@
         <v>180</v>
       </c>
       <c r="B182" s="36" t="s">
-        <v>1870</v>
+        <v>1874</v>
       </c>
       <c r="C182" s="36">
         <v>0.0</v>
@@ -14480,19 +14492,19 @@
         <v>1173</v>
       </c>
       <c r="E182" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F182" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G182" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H182" s="37" t="s">
-        <v>1871</v>
+        <v>1875</v>
       </c>
       <c r="I182" s="37" t="s">
-        <v>1871</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="183">
@@ -14501,7 +14513,7 @@
         <v>181</v>
       </c>
       <c r="B183" s="36" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="C183" s="36">
         <v>1.0</v>
@@ -14510,19 +14522,19 @@
         <v>1175</v>
       </c>
       <c r="E183" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F183" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G183" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H183" s="37" t="s">
-        <v>1873</v>
+        <v>1877</v>
       </c>
       <c r="I183" s="37" t="s">
-        <v>1873</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="184">
@@ -14531,7 +14543,7 @@
         <v>182</v>
       </c>
       <c r="B184" s="36" t="s">
-        <v>1874</v>
+        <v>1878</v>
       </c>
       <c r="C184" s="36">
         <v>0.0</v>
@@ -14540,19 +14552,19 @@
         <v>1177</v>
       </c>
       <c r="E184" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F184" s="38" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G184" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H184" s="37" t="s">
-        <v>1875</v>
+        <v>1879</v>
       </c>
       <c r="I184" s="37" t="s">
-        <v>1875</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="185">
@@ -14561,7 +14573,7 @@
         <v>183</v>
       </c>
       <c r="B185" s="36" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="C185" s="36">
         <v>1.0</v>
@@ -14570,10 +14582,10 @@
         <v>1143</v>
       </c>
       <c r="E185" s="44" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F185" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G185" s="38" t="s">
         <v>760</v>
@@ -14591,7 +14603,7 @@
         <v>184</v>
       </c>
       <c r="B186" s="36" t="s">
-        <v>1876</v>
+        <v>1880</v>
       </c>
       <c r="C186" s="36">
         <v>0.0</v>
@@ -14600,7 +14612,7 @@
         <v>1035</v>
       </c>
       <c r="E186" s="44" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F186" s="38" t="s">
         <v>760</v>
@@ -14609,10 +14621,10 @@
         <v>760</v>
       </c>
       <c r="H186" s="37" t="s">
-        <v>1877</v>
+        <v>1881</v>
       </c>
       <c r="I186" s="37" t="s">
-        <v>1877</v>
+        <v>1881</v>
       </c>
     </row>
   </sheetData>
@@ -14654,34 +14666,34 @@
         <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1878</v>
+        <v>1882</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>1879</v>
+        <v>1883</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1880</v>
+        <v>1884</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1881</v>
+        <v>1885</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>1882</v>
+        <v>1886</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>1883</v>
+        <v>1887</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>1884</v>
+        <v>1888</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>1885</v>
+        <v>1889</v>
       </c>
       <c r="J1" s="64" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
       <c r="K1" s="64" t="s">
-        <v>1887</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="2" ht="186.0" customHeight="1">
@@ -14690,7 +14702,7 @@
         <v>-1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>1888</v>
+        <v>1892</v>
       </c>
       <c r="C2" s="66" t="s">
         <v>330</v>
@@ -14726,7 +14738,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>1889</v>
+        <v>1893</v>
       </c>
       <c r="C3" s="66" t="s">
         <v>954</v>
@@ -14735,10 +14747,10 @@
         <v>1052</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>1890</v>
+        <v>1894</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1891</v>
+        <v>1895</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>328</v>
@@ -14762,19 +14774,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1892</v>
+        <v>1896</v>
       </c>
       <c r="C4" s="66" t="s">
-        <v>1893</v>
+        <v>1897</v>
       </c>
       <c r="D4" s="67" t="s">
         <v>1052</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1893</v>
+        <v>1897</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1894</v>
+        <v>1898</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>328</v>
@@ -14798,19 +14810,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1895</v>
+        <v>1899</v>
       </c>
       <c r="C5" s="66" t="s">
-        <v>1896</v>
+        <v>1900</v>
       </c>
       <c r="D5" s="67" t="s">
         <v>1052</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1896</v>
+        <v>1900</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1897</v>
+        <v>1901</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>328</v>
@@ -14834,19 +14846,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1898</v>
+        <v>1902</v>
       </c>
       <c r="C6" s="66" t="s">
-        <v>1899</v>
+        <v>1903</v>
       </c>
       <c r="D6" s="67" t="s">
         <v>1052</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1899</v>
+        <v>1903</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1900</v>
+        <v>1904</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>328</v>
@@ -14870,25 +14882,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1902</v>
+        <v>1906</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>1902</v>
+        <v>1906</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>1904</v>
+        <v>1908</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>328</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="I7" s="35" t="s">
         <v>665</v>
@@ -14906,25 +14918,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>1905</v>
+        <v>1909</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>1906</v>
+        <v>1910</v>
       </c>
       <c r="D8" s="67" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>1906</v>
+        <v>1910</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>1907</v>
+        <v>1911</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>328</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="I8" s="35" t="s">
         <v>665</v>
@@ -14942,7 +14954,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>1908</v>
+        <v>1912</v>
       </c>
       <c r="C9" s="32" t="s">
         <v>991</v>
@@ -14954,7 +14966,7 @@
         <v>991</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>1909</v>
+        <v>1913</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>328</v>
@@ -14978,25 +14990,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>1910</v>
+        <v>1914</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>1911</v>
+        <v>1915</v>
       </c>
       <c r="D10" s="67" t="s">
         <v>1048</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1911</v>
+        <v>1915</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1912</v>
+        <v>1916</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>328</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>1913</v>
+        <v>1917</v>
       </c>
       <c r="I10" s="35" t="s">
         <v>728</v>
@@ -15014,25 +15026,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1915</v>
+        <v>1919</v>
       </c>
       <c r="D11" s="67" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1915</v>
+        <v>1919</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>1916</v>
+        <v>1920</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>328</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>1917</v>
+        <v>1921</v>
       </c>
       <c r="I11" s="35" t="s">
         <v>665</v>
@@ -15050,19 +15062,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1918</v>
+        <v>1922</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1919</v>
+        <v>1923</v>
       </c>
       <c r="D12" s="67" t="s">
         <v>1047</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>1919</v>
+        <v>1923</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>328</v>
@@ -15086,25 +15098,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>1921</v>
+        <v>1925</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1922</v>
+        <v>1926</v>
       </c>
       <c r="D13" s="67" t="s">
-        <v>1923</v>
+        <v>1927</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>1922</v>
+        <v>1926</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>1924</v>
+        <v>1928</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>328</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>1925</v>
+        <v>1929</v>
       </c>
       <c r="I13" s="35" t="s">
         <v>665</v>
@@ -15131,16 +15143,16 @@
         <v>22</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>1927</v>
+        <v>1931</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>328</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>1928</v>
+        <v>1932</v>
       </c>
       <c r="I14" s="35" t="s">
         <v>665</v>
@@ -15167,16 +15179,16 @@
         <v>22</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>1929</v>
+        <v>1933</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>1930</v>
+        <v>1934</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>328</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>1931</v>
+        <v>1935</v>
       </c>
       <c r="I15" s="35" t="s">
         <v>665</v>
@@ -15194,7 +15206,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="C16" s="66" t="s">
         <v>330</v>
@@ -15257,7 +15269,7 @@
         <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1933</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="2">
@@ -15284,7 +15296,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1934</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="5">
@@ -15293,7 +15305,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1935</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="6">
@@ -15305,7 +15317,7 @@
         <v>51</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1936</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="8">
@@ -15313,7 +15325,7 @@
         <v>0.0</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1937</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="9">
@@ -15321,7 +15333,7 @@
         <v>1.0</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1938</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="10">
@@ -15329,7 +15341,7 @@
         <v>2.0</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="11">
@@ -15337,7 +15349,7 @@
         <v>3.0</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1940</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="12">
@@ -15345,7 +15357,7 @@
         <v>4.0</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1941</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="13">
@@ -15353,7 +15365,7 @@
         <v>5.0</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1942</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="15">
@@ -15361,7 +15373,7 @@
         <v>51</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1943</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="16">
@@ -15379,7 +15391,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1944</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="18">
@@ -15424,7 +15436,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1945</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="23">
@@ -15441,7 +15453,7 @@
         <v>51</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1946</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="26">
@@ -15486,7 +15498,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="31">
@@ -15522,7 +15534,7 @@
         <v>8</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1948</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="35">
@@ -15540,7 +15552,7 @@
         <v>10</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="37">
@@ -15611,7 +15623,7 @@
         <v>51</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1950</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="46">
@@ -15629,7 +15641,7 @@
         <v>1</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1828</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="48">
@@ -15638,7 +15650,7 @@
         <v>2</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="49">
@@ -15647,7 +15659,7 @@
         <v>3</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1774</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="50">
@@ -15656,7 +15668,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1790</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="51">
@@ -15665,7 +15677,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="52">
@@ -15674,7 +15686,7 @@
         <v>6</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1952</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="53">
@@ -15683,7 +15695,7 @@
         <v>7</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1953</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="54">
@@ -15692,7 +15704,7 @@
         <v>8</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1954</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="55">
@@ -15710,7 +15722,7 @@
         <v>10</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1955</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="57">
@@ -15719,7 +15731,7 @@
         <v>11</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1956</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="58">
@@ -15728,7 +15740,7 @@
         <v>12</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="59">
@@ -15737,7 +15749,7 @@
         <v>13</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="60">
@@ -15746,7 +15758,7 @@
         <v>14</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="61">
@@ -15755,7 +15767,7 @@
         <v>15</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="62">
@@ -15764,7 +15776,7 @@
         <v>16</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="63">
@@ -15773,7 +15785,7 @@
         <v>17</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>1960</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="64">
@@ -15782,7 +15794,7 @@
         <v>18</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="65">
@@ -15791,7 +15803,7 @@
         <v>19</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1962</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="67">
@@ -15799,7 +15811,7 @@
         <v>51</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="68">
@@ -15852,7 +15864,7 @@
         <v>51</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>1964</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="75">
@@ -15917,7 +15929,7 @@
         <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1965</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="2">
@@ -15935,7 +15947,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1966</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="4">
@@ -15944,7 +15956,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1967</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="5">
@@ -16025,7 +16037,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1968</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="14">
@@ -16070,7 +16082,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1969</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="19">
@@ -16250,7 +16262,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1970</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="40">
@@ -16258,16 +16270,16 @@
         <v>51</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1971</v>
+        <v>1975</v>
       </c>
       <c r="C40" s="69" t="s">
         <v>319</v>
       </c>
       <c r="D40" s="69" t="s">
-        <v>1972</v>
+        <v>1976</v>
       </c>
       <c r="E40" s="69" t="s">
-        <v>1973</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="41">
@@ -16276,7 +16288,7 @@
         <v>0</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1974</v>
+        <v>1978</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>328</v>
@@ -16295,10 +16307,10 @@
         <v>1</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1975</v>
+        <v>1979</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="D42" s="38" t="s">
         <v>971</v>
@@ -16314,10 +16326,10 @@
         <v>2</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1976</v>
+        <v>1980</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="D43" s="38" t="s">
         <v>999</v>
@@ -16336,7 +16348,7 @@
         <v>46</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="D44" s="38" t="s">
         <v>47</v>
@@ -16352,7 +16364,7 @@
         <v>4</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1977</v>
+        <v>1981</v>
       </c>
       <c r="C45" s="38" t="s">
         <v>485</v>
@@ -16370,19 +16382,19 @@
         <v>51</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1978</v>
+        <v>1982</v>
       </c>
       <c r="C47" s="68" t="s">
-        <v>1979</v>
+        <v>1983</v>
       </c>
       <c r="D47" s="68" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="E47" s="69" t="s">
-        <v>1980</v>
+        <v>1984</v>
       </c>
       <c r="F47" s="68" t="s">
-        <v>1981</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="48">
@@ -16394,13 +16406,13 @@
         <v>756</v>
       </c>
       <c r="C48" s="44" t="s">
-        <v>1974</v>
+        <v>1978</v>
       </c>
       <c r="D48" s="44" t="s">
         <v>759</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="F48" s="43" t="b">
         <v>0</v>
@@ -16415,13 +16427,13 @@
         <v>770</v>
       </c>
       <c r="C49" s="44" t="s">
-        <v>1975</v>
+        <v>1979</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="F49" s="43" t="b">
         <v>0</v>
@@ -16436,13 +16448,13 @@
         <v>787</v>
       </c>
       <c r="C50" s="44" t="s">
-        <v>1975</v>
+        <v>1979</v>
       </c>
       <c r="D50" s="44" t="s">
         <v>807</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="F50" s="43" t="b">
         <v>0</v>
@@ -16457,13 +16469,13 @@
         <v>792</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>1976</v>
+        <v>1980</v>
       </c>
       <c r="D51" s="44" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="F51" s="43" t="b">
         <v>0</v>
@@ -16481,10 +16493,10 @@
         <v>46</v>
       </c>
       <c r="D52" s="44" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="E52" s="48" t="s">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="F52" s="43" t="b">
         <v>0</v>
@@ -16496,16 +16508,16 @@
         <v>5</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1983</v>
+        <v>1987</v>
       </c>
       <c r="C53" s="44" t="s">
         <v>46</v>
       </c>
       <c r="D53" s="44" t="s">
-        <v>1662</v>
+        <v>1666</v>
       </c>
       <c r="E53" s="48" t="s">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="F53" s="43" t="b">
         <v>0</v>
@@ -16517,16 +16529,16 @@
         <v>6</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1984</v>
+        <v>1988</v>
       </c>
       <c r="C54" s="44" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="44" t="s">
-        <v>1665</v>
+        <v>1669</v>
       </c>
       <c r="E54" s="48" t="s">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="F54" s="43" t="b">
         <v>1</v>
@@ -16538,16 +16550,16 @@
         <v>7</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1985</v>
+        <v>1989</v>
       </c>
       <c r="C55" s="44" t="s">
-        <v>1977</v>
+        <v>1981</v>
       </c>
       <c r="D55" s="44" t="s">
         <v>759</v>
       </c>
       <c r="E55" s="48" t="s">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="F55" s="43" t="b">
         <v>0</v>
@@ -16558,10 +16570,10 @@
         <v>51</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>1986</v>
+        <v>1990</v>
       </c>
       <c r="C57" s="28" t="s">
-        <v>1987</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="58">
@@ -16570,7 +16582,7 @@
         <v>0</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="C58" s="51" t="s">
         <v>494</v>
@@ -16581,7 +16593,7 @@
         <v>51</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1988</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="61">
@@ -17615,16 +17627,16 @@
         <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1989</v>
+        <v>1993</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1990</v>
+        <v>1994</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1991</v>
+        <v>1995</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="2">
@@ -17636,7 +17648,7 @@
         <v>331</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1993</v>
+        <v>1997</v>
       </c>
       <c r="D2" s="71" t="s">
         <v>328</v>
@@ -17654,7 +17666,7 @@
         <v>446</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1994</v>
+        <v>1998</v>
       </c>
       <c r="D3" s="71" t="s">
         <v>328</v>
@@ -17669,10 +17681,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1995</v>
+        <v>1999</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1993</v>
+        <v>1997</v>
       </c>
       <c r="D4" s="71" t="s">
         <v>328</v>
@@ -17710,7 +17722,7 @@
         <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1936</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="2">
@@ -17737,7 +17749,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1996</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6">
@@ -17745,7 +17757,7 @@
         <v>51</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1997</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="7">
@@ -17790,21 +17802,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1998</v>
+        <v>2002</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2001</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="s">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="B2" s="72">
         <v>5.0</v>
@@ -17818,7 +17830,7 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="B3" s="72">
         <v>4.0</v>
@@ -17832,7 +17844,7 @@
     </row>
     <row r="4">
       <c r="A4" s="37" t="s">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="B4" s="72">
         <v>2.0</v>
@@ -17846,7 +17858,7 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="B5" s="72">
         <v>5.0</v>
@@ -17860,7 +17872,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="B6" s="72">
         <v>4.0</v>
@@ -17874,7 +17886,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="B7" s="72">
         <v>4.0</v>
@@ -17888,7 +17900,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="B8" s="72">
         <v>2.0</v>
@@ -17902,7 +17914,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="B9" s="72">
         <v>5.0</v>
@@ -37557,6 +37569,66 @@
       <c r="C84" s="36" t="s">
         <v>1036</v>
       </c>
+      <c r="D84" s="36" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>83</v>
+      </c>
+      <c r="B85" s="36" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C85" s="36" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D85" s="36" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>84</v>
+      </c>
+      <c r="B86" s="36" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C86" s="36" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D86" s="36" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>85</v>
+      </c>
+      <c r="B87" s="36" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C87" s="36" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D87" s="36" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="53">
+        <f>ROW() - ROW(Table_sounds[N])</f>
+        <v>86</v>
+      </c>
+      <c r="B88" s="36" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C88" s="36" t="s">
+        <v>1036</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -37589,13 +37661,13 @@
         <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>25</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="2">
@@ -37610,7 +37682,7 @@
         <v>327</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="3">
@@ -37625,7 +37697,7 @@
         <v>327</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="4">
@@ -37637,10 +37709,10 @@
         <v>804</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="5">
@@ -37649,13 +37721,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="6">
@@ -37667,10 +37739,10 @@
         <v>818</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="7">
@@ -37682,10 +37754,10 @@
         <v>820</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="8">
@@ -37694,13 +37766,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="9">
@@ -37712,10 +37784,10 @@
         <v>822</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="10">
@@ -37724,13 +37796,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="11">
@@ -37742,10 +37814,10 @@
         <v>823</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="12">
@@ -37760,7 +37832,7 @@
         <v>413</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="13">
@@ -37775,7 +37847,7 @@
         <v>415</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="14">
@@ -37784,13 +37856,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="15">
@@ -37802,10 +37874,10 @@
         <v>830</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="16">
@@ -37814,13 +37886,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="17">
@@ -37832,10 +37904,10 @@
         <v>855</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="18">
@@ -37850,7 +37922,7 @@
         <v>394</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="19">
@@ -37865,7 +37937,7 @@
         <v>333</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="20">
@@ -37874,13 +37946,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="C20" s="39" t="s">
         <v>394</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="21">
@@ -37889,13 +37961,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="22">
@@ -37907,10 +37979,10 @@
         <v>910</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="23">
@@ -37919,13 +37991,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="24">
@@ -37937,10 +38009,10 @@
         <v>912</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="25">
@@ -37949,13 +38021,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="26">
@@ -37967,10 +38039,10 @@
         <v>918</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="27">
@@ -37982,10 +38054,10 @@
         <v>926</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="28">
@@ -37994,13 +38066,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="29">
@@ -38012,10 +38084,10 @@
         <v>927</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="D29" s="39" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="30">
@@ -38024,13 +38096,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="D30" s="39" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="31">
@@ -38042,10 +38114,10 @@
         <v>928</v>
       </c>
       <c r="C31" s="39" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="D31" s="39" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="32">
@@ -38060,7 +38132,7 @@
         <v>37</v>
       </c>
       <c r="D32" s="39" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="33">
@@ -38075,7 +38147,7 @@
         <v>37</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="34">
@@ -38084,13 +38156,13 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="C34" s="39" t="s">
         <v>327</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="36">
@@ -38098,25 +38170,25 @@
         <v>51</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>488</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="H36" s="28" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="37">
@@ -38125,7 +38197,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="C37" s="37" t="s">
         <v>494</v>
@@ -38152,7 +38224,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="C38" s="37" t="s">
         <v>494</v>
@@ -38179,7 +38251,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="C39" s="40" t="s">
         <v>494</v>
@@ -38191,13 +38263,13 @@
         <v>497</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="G39" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H39" s="40" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="40">
@@ -38206,7 +38278,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="C40" s="40" t="s">
         <v>494</v>
@@ -38218,13 +38290,13 @@
         <v>497</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="G40" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H40" s="40" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="41">
@@ -38233,7 +38305,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="C41" s="40" t="s">
         <v>494</v>
@@ -38251,7 +38323,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="42">
@@ -38260,7 +38332,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="C42" s="40" t="s">
         <v>494</v>
@@ -38269,7 +38341,7 @@
         <v>495</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="F42" s="38" t="s">
         <v>758</v>
@@ -38278,7 +38350,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="40" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="43">
@@ -38287,7 +38359,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>494</v>
@@ -38305,7 +38377,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="40" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="44">
@@ -38314,7 +38386,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>494</v>
@@ -38326,13 +38398,13 @@
         <v>497</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="G44" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H44" s="40" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="45">
@@ -38341,7 +38413,7 @@
         <v>8</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C45" s="40" t="s">
         <v>494</v>
@@ -38359,7 +38431,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="40" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="46">
@@ -38368,7 +38440,7 @@
         <v>9</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="C46" s="40" t="s">
         <v>494</v>
@@ -38380,13 +38452,13 @@
         <v>497</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="G46" s="55" t="b">
         <v>1</v>
       </c>
       <c r="H46" s="40" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="47">
@@ -38395,7 +38467,7 @@
         <v>10</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="C47" s="40" t="s">
         <v>494</v>
@@ -38407,13 +38479,13 @@
         <v>888</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="G47" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H47" s="40" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="48">
@@ -38422,7 +38494,7 @@
         <v>11</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="C48" s="40" t="s">
         <v>889</v>
@@ -38434,13 +38506,13 @@
         <v>497</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="G48" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="40" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="49">
@@ -38449,7 +38521,7 @@
         <v>12</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="C49" s="40" t="s">
         <v>494</v>
@@ -38461,13 +38533,13 @@
         <v>497</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="G49" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H49" s="40" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="50">
@@ -38476,7 +38548,7 @@
         <v>13</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="C50" s="40" t="s">
         <v>889</v>
@@ -38485,16 +38557,16 @@
         <v>560</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="G50" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H50" s="40" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="51">
@@ -38503,7 +38575,7 @@
         <v>14</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="C51" s="40" t="s">
         <v>494</v>
@@ -38521,7 +38593,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="40" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="52">
@@ -38530,7 +38602,7 @@
         <v>15</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="C52" s="40" t="s">
         <v>494</v>
@@ -38548,7 +38620,7 @@
         <v>0</v>
       </c>
       <c r="H52" s="40" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="53">
@@ -38557,7 +38629,7 @@
         <v>16</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="C53" s="40" t="s">
         <v>494</v>
@@ -38575,7 +38647,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="40" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="54">
@@ -38584,7 +38656,7 @@
         <v>17</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="C54" s="40" t="s">
         <v>494</v>
@@ -38602,7 +38674,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="40" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="55">
@@ -38611,7 +38683,7 @@
         <v>18</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="C55" s="40" t="s">
         <v>494</v>
@@ -38623,13 +38695,13 @@
         <v>497</v>
       </c>
       <c r="F55" s="38" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="G55" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H55" s="40" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="56">
@@ -38638,7 +38710,7 @@
         <v>19</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="C56" s="40" t="s">
         <v>494</v>
@@ -38650,13 +38722,13 @@
         <v>497</v>
       </c>
       <c r="F56" s="38" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="G56" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H56" s="40" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="57">
@@ -38665,7 +38737,7 @@
         <v>20</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="C57" s="40" t="s">
         <v>494</v>
@@ -38674,16 +38746,16 @@
         <v>495</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="F57" s="38" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="G57" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H57" s="40" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="58">
@@ -38692,7 +38764,7 @@
         <v>21</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="C58" s="40" t="s">
         <v>494</v>
@@ -38710,7 +38782,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="40" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="59">
@@ -38719,7 +38791,7 @@
         <v>22</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="C59" s="40" t="s">
         <v>494</v>
@@ -38731,13 +38803,13 @@
         <v>497</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="G59" s="55" t="b">
         <v>1</v>
       </c>
       <c r="H59" s="40" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="60">
@@ -38746,7 +38818,7 @@
         <v>23</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="C60" s="40" t="s">
         <v>494</v>
@@ -38758,13 +38830,13 @@
         <v>893</v>
       </c>
       <c r="F60" s="38" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="G60" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H60" s="40" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="61">
@@ -38773,7 +38845,7 @@
         <v>24</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="C61" s="40" t="s">
         <v>894</v>
@@ -38782,16 +38854,16 @@
         <v>495</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="F61" s="38" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="G61" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H61" s="40" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="62">
@@ -38800,7 +38872,7 @@
         <v>25</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="C62" s="40" t="s">
         <v>494</v>
@@ -38818,7 +38890,7 @@
         <v>0</v>
       </c>
       <c r="H62" s="40" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="63">
@@ -38827,7 +38899,7 @@
         <v>26</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="C63" s="40" t="s">
         <v>494</v>
@@ -38839,13 +38911,13 @@
         <v>497</v>
       </c>
       <c r="F63" s="38" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="G63" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H63" s="40" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="64">
@@ -38854,7 +38926,7 @@
         <v>27</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="C64" s="40" t="s">
         <v>494</v>
@@ -38872,7 +38944,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="40" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="65">
@@ -38881,7 +38953,7 @@
         <v>28</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="C65" s="40" t="s">
         <v>494</v>
@@ -38893,13 +38965,13 @@
         <v>899</v>
       </c>
       <c r="F65" s="38" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="G65" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H65" s="40" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="66">
@@ -38908,7 +38980,7 @@
         <v>29</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="C66" s="40" t="s">
         <v>494</v>
@@ -38926,7 +38998,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="40" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="67">
@@ -38935,7 +39007,7 @@
         <v>30</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="C67" s="40" t="s">
         <v>494</v>
@@ -38947,13 +39019,13 @@
         <v>497</v>
       </c>
       <c r="F67" s="38" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="G67" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H67" s="40" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="68">
@@ -38962,7 +39034,7 @@
         <v>31</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="C68" s="40" t="s">
         <v>494</v>
@@ -38974,13 +39046,13 @@
         <v>497</v>
       </c>
       <c r="F68" s="38" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="G68" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H68" s="40" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="69">
@@ -38989,7 +39061,7 @@
         <v>32</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="C69" s="40" t="s">
         <v>494</v>
@@ -39007,7 +39079,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="40" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="70">
@@ -39016,7 +39088,7 @@
         <v>33</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="C70" s="40" t="s">
         <v>494</v>
@@ -39034,7 +39106,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="40" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="71">
@@ -39043,7 +39115,7 @@
         <v>34</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="C71" s="40" t="s">
         <v>494</v>
@@ -39055,13 +39127,13 @@
         <v>497</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="G71" s="55" t="b">
         <v>1</v>
       </c>
       <c r="H71" s="40" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="72">
@@ -39070,7 +39142,7 @@
         <v>35</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="C72" s="40" t="s">
         <v>494</v>
@@ -39082,13 +39154,13 @@
         <v>497</v>
       </c>
       <c r="F72" s="38" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="G72" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H72" s="40" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="73">
@@ -39097,7 +39169,7 @@
         <v>36</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="C73" s="40" t="s">
         <v>494</v>
@@ -39109,13 +39181,13 @@
         <v>497</v>
       </c>
       <c r="F73" s="38" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="G73" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H73" s="40" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="74">
@@ -39124,7 +39196,7 @@
         <v>37</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="C74" s="40" t="s">
         <v>494</v>
@@ -39136,13 +39208,13 @@
         <v>497</v>
       </c>
       <c r="F74" s="38" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="G74" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H74" s="40" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="75">
@@ -39151,7 +39223,7 @@
         <v>38</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C75" s="40" t="s">
         <v>885</v>
@@ -39169,7 +39241,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="40" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="76">
@@ -39178,7 +39250,7 @@
         <v>39</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="C76" s="40" t="s">
         <v>494</v>
@@ -39196,7 +39268,7 @@
         <v>0</v>
       </c>
       <c r="H76" s="40" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="77">
@@ -39205,7 +39277,7 @@
         <v>40</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="C77" s="40" t="s">
         <v>494</v>
@@ -39217,13 +39289,13 @@
         <v>497</v>
       </c>
       <c r="F77" s="38" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="G77" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H77" s="40" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="78">
@@ -39232,7 +39304,7 @@
         <v>41</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="C78" s="40" t="s">
         <v>494</v>
@@ -39244,13 +39316,13 @@
         <v>497</v>
       </c>
       <c r="F78" s="38" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="G78" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H78" s="40" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="79">
@@ -39259,7 +39331,7 @@
         <v>42</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="C79" s="40" t="s">
         <v>494</v>
@@ -39277,7 +39349,7 @@
         <v>0</v>
       </c>
       <c r="H79" s="40" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="80">
@@ -39286,7 +39358,7 @@
         <v>43</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="C80" s="40" t="s">
         <v>494</v>
@@ -39298,13 +39370,13 @@
         <v>497</v>
       </c>
       <c r="F80" s="38" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="G80" s="55" t="b">
         <v>0</v>
       </c>
       <c r="H80" s="40" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="81">
@@ -39313,7 +39385,7 @@
         <v>44</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="C81" s="40" t="s">
         <v>494</v>
@@ -39331,7 +39403,7 @@
         <v>0</v>
       </c>
       <c r="H81" s="40" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="82">
@@ -39340,7 +39412,7 @@
         <v>45</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="C82" s="40" t="s">
         <v>494</v>
@@ -39367,7 +39439,7 @@
         <v>46</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="C83" s="40" t="s">
         <v>494</v>
@@ -39385,7 +39457,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="40" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="84">
@@ -39394,7 +39466,7 @@
         <v>47</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="C84" s="40" t="s">
         <v>494</v>
@@ -39421,7 +39493,7 @@
         <v>48</v>
       </c>
       <c r="B85" s="36" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="C85" s="40" t="s">
         <v>494</v>
@@ -39439,7 +39511,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="40" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="86">
@@ -39448,7 +39520,7 @@
         <v>49</v>
       </c>
       <c r="B86" s="36" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="C86" s="40" t="s">
         <v>494</v>
@@ -39466,7 +39538,7 @@
         <v>0</v>
       </c>
       <c r="H86" s="40" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="87">
@@ -39475,7 +39547,7 @@
         <v>50</v>
       </c>
       <c r="B87" s="36" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="C87" s="40" t="s">
         <v>494</v>
@@ -39493,7 +39565,7 @@
         <v>0</v>
       </c>
       <c r="H87" s="40" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="88">
@@ -39502,7 +39574,7 @@
         <v>51</v>
       </c>
       <c r="B88" s="36" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="C88" s="40" t="s">
         <v>494</v>
@@ -39520,7 +39592,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="40" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="89">
@@ -39529,7 +39601,7 @@
         <v>52</v>
       </c>
       <c r="B89" s="36" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="C89" s="40" t="s">
         <v>494</v>
@@ -39547,7 +39619,7 @@
         <v>0</v>
       </c>
       <c r="H89" s="40" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="90">
@@ -39556,7 +39628,7 @@
         <v>53</v>
       </c>
       <c r="B90" s="36" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="C90" s="37" t="s">
         <v>494</v>
@@ -39673,10 +39745,10 @@
         <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="C1" s="57" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="2">
@@ -39688,7 +39760,7 @@
         <v>757</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="3">
@@ -39700,7 +39772,7 @@
         <v>790</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="4">
@@ -39709,10 +39781,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="6">
@@ -39720,13 +39792,13 @@
         <v>51</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="7">
@@ -39735,7 +39807,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>759</v>
@@ -39750,10 +39822,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="D8" s="58" t="s">
         <v>497</v>
@@ -39765,10 +39837,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="D9" s="58" t="s">
         <v>763</v>
@@ -39780,10 +39852,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="D10" s="58" t="s">
         <v>765</v>
@@ -39795,7 +39867,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>759</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -21897,7 +21897,7 @@
         <v>75</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="Q30" s="13" t="s">
         <v>132</v>

--- a/VARMAP_Generator/VARMAP.xlsx
+++ b/VARMAP_Generator/VARMAP.xlsx
@@ -33,13 +33,13 @@
     <definedName name="Interval_autoInsertItem">FN!$A$1:$J$2</definedName>
     <definedName name="Interval_Unchain_Conditions">ACTION_CONDS!$A$71:$I$103</definedName>
     <definedName name="Interval_Actions">ACTION_CONDS!$A$105:$P$254</definedName>
-    <definedName name="Interval_Phrases">PHRASES!$A$1:$I$186</definedName>
+    <definedName name="Interval_Phrases">PHRASES!$A$1:$I$193</definedName>
     <definedName name="Interval_sprites">SPRITES!$A$1:$C$74</definedName>
     <definedName name="Interval_Items">ITEMS!$A$1:$J$51</definedName>
     <definedName name="Interval_Dialog_Options">DIALOGS!$A$36:$H$90</definedName>
     <definedName name="Interval_Memento">EVENTS!$A$47:$F$55</definedName>
     <definedName name="Interval_autoInsertDialog">FN!$A$7:$L$8</definedName>
-    <definedName name="Interval_Sounds">SOUNDS!$A$1:$D$88</definedName>
+    <definedName name="Interval_Sounds">SOUNDS!$A$1:$D$95</definedName>
     <definedName name="Interval_Action_Conditions">ACTION_CONDS!$A$1:$H$69</definedName>
   </definedNames>
   <calcPr/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7060" uniqueCount="2013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7130" uniqueCount="2041">
   <si>
     <t>NewItem</t>
   </si>
@@ -554,7 +554,7 @@
     <t>MODULE_LOADING_COMPLETED</t>
   </si>
   <si>
-    <t>LODING_COMPLETED_DELEGATE</t>
+    <t>LOADING_COMPLETED_DELEGATE</t>
   </si>
   <si>
     <t>GameMasterClass.LoadingCompletedService</t>
@@ -3653,6 +3653,48 @@
     <t>SOUND_CARD_TAKEBACK</t>
   </si>
   <si>
+    <t>SOUND_CARDS1_MAINCHAR_TAUNT1</t>
+  </si>
+  <si>
+    <t>SOUND_CARDS1_MAINCHAR_TAUNT_1_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_CARDS1_MAINCHAR_TAUNT2</t>
+  </si>
+  <si>
+    <t>SOUND_CARDS1_MAINCHAR_TAUNT_2_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_CARDS1_MAINCHAR_TAUNT3</t>
+  </si>
+  <si>
+    <t>SOUND_CARDS1_MAINCHAR_TAUNT_3_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_CARDS1_MAINCHAR_TAUNT4</t>
+  </si>
+  <si>
+    <t>SOUND_CARDS1_MAINCHAR_TAUNT_4_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_CARDS1_TAUNT_ARTURO_1</t>
+  </si>
+  <si>
+    <t>SOUND_CARDS1_TAUNT_ARTURO_1_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_CARDS1_TAUNT_ARTURO_2</t>
+  </si>
+  <si>
+    <t>SOUND_CARDS1_TAUNT_ARTURO_2_SPANISH</t>
+  </si>
+  <si>
+    <t>SOUND_CARDS1_TAUNT_ARTURO_3</t>
+  </si>
+  <si>
+    <t>SOUND_CARDS1_TAUNT_ARTURO_3_SPANISH</t>
+  </si>
+  <si>
     <t>SOUND_LAST</t>
   </si>
   <si>
@@ -5742,6 +5784,48 @@
   </si>
   <si>
     <t>Bien. Suficiente por hoy</t>
+  </si>
+  <si>
+    <t>PHRASE_CARDS1_ARTURO_TAUNT_1</t>
+  </si>
+  <si>
+    <t>Te falta calle! Como tiras esa carta ahora?</t>
+  </si>
+  <si>
+    <t>PHRASE_CARDS1_ARTURO_TAUNT_2</t>
+  </si>
+  <si>
+    <t>Madre mía qué jugadón</t>
+  </si>
+  <si>
+    <t>PHRASE_CARDS1_ARTURO_TAUNT_3</t>
+  </si>
+  <si>
+    <t>Me llevo la muestra</t>
+  </si>
+  <si>
+    <t>PHRASE_CARDS1_MAINCHAR_TAUNT_1</t>
+  </si>
+  <si>
+    <t>Boum! En tu cara! A ver si remontas eso!</t>
+  </si>
+  <si>
+    <t>PHRASE_CARDS1_MAINCHAR_TAUNT_2</t>
+  </si>
+  <si>
+    <t>Por mi cara bonita</t>
+  </si>
+  <si>
+    <t>PHRASE_CARDS1_MAINCHAR_TAUNT_3</t>
+  </si>
+  <si>
+    <t>Recolector oficial de basura</t>
+  </si>
+  <si>
+    <t>PHRASE_CARDS1_MAINCHAR_TAUNT_4</t>
+  </si>
+  <si>
+    <t>A ver si te voy a tener que enseñar yo a jugar a ti</t>
   </si>
   <si>
     <t>PHRASE_DIALOG_LAST</t>
@@ -7423,7 +7507,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D88" displayName="Table_sounds" name="Table_sounds" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D95" displayName="Table_sounds" name="Table_sounds" id="12">
   <tableColumns count="4">
     <tableColumn name="N" id="1"/>
     <tableColumn name="SOUND_ID" id="2"/>
@@ -7498,7 +7582,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I186" displayName="Table_Phrases" name="Table_Phrases" id="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I193" displayName="Table_Phrases" name="Table_Phrases" id="18">
   <tableColumns count="9">
     <tableColumn name="N" id="1"/>
     <tableColumn name="PHRASE_ID" id="2"/>
@@ -8300,13 +8384,13 @@
         <v>51</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>1341</v>
+        <v>1355</v>
       </c>
       <c r="C1" s="59" t="s">
-        <v>1342</v>
+        <v>1356</v>
       </c>
       <c r="D1" s="59" t="s">
-        <v>1343</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="2">
@@ -8329,10 +8413,10 @@
         <v>334</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1344</v>
+        <v>1358</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>1344</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="4">
@@ -8341,13 +8425,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1345</v>
+        <v>1359</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1346</v>
+        <v>1360</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>1347</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="5">
@@ -8356,13 +8440,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1348</v>
+        <v>1362</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>1349</v>
+        <v>1363</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>1350</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="6">
@@ -8371,13 +8455,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1351</v>
+        <v>1365</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>1352</v>
+        <v>1366</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>1353</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="7">
@@ -8389,10 +8473,10 @@
         <v>337</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>1354</v>
+        <v>1368</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>1355</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="8">
@@ -8404,10 +8488,10 @@
         <v>358</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1356</v>
+        <v>1370</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>1356</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="9">
@@ -8419,10 +8503,10 @@
         <v>365</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>1357</v>
+        <v>1371</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>1358</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="10">
@@ -8434,10 +8518,10 @@
         <v>343</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>1359</v>
+        <v>1373</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>1360</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="11">
@@ -8446,13 +8530,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1361</v>
+        <v>1375</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>1362</v>
+        <v>1376</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>1363</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="12">
@@ -8461,13 +8545,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1364</v>
+        <v>1378</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>1365</v>
+        <v>1379</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>1366</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="13">
@@ -8479,10 +8563,10 @@
         <v>348</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>1367</v>
+        <v>1381</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>1368</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="14">
@@ -8494,10 +8578,10 @@
         <v>355</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>1369</v>
+        <v>1383</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>1370</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="15">
@@ -8506,13 +8590,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1371</v>
+        <v>1385</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>1372</v>
+        <v>1386</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>1373</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="16">
@@ -8524,10 +8608,10 @@
         <v>368</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>1374</v>
+        <v>1388</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>1375</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="17">
@@ -8539,10 +8623,10 @@
         <v>373</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>1376</v>
+        <v>1390</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>1377</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="18">
@@ -8554,10 +8638,10 @@
         <v>376</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>1378</v>
+        <v>1392</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>1379</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="19">
@@ -8569,10 +8653,10 @@
         <v>380</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>1380</v>
+        <v>1394</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>1381</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="20">
@@ -8584,10 +8668,10 @@
         <v>383</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>1382</v>
+        <v>1396</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>1383</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="21">
@@ -8599,10 +8683,10 @@
         <v>386</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>1384</v>
+        <v>1398</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>1385</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="22">
@@ -8614,10 +8698,10 @@
         <v>388</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>1386</v>
+        <v>1400</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>1387</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="23">
@@ -8629,10 +8713,10 @@
         <v>390</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>1388</v>
+        <v>1402</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>1389</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="24">
@@ -8644,10 +8728,10 @@
         <v>392</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>1390</v>
+        <v>1404</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>1391</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="25">
@@ -8659,10 +8743,10 @@
         <v>395</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>1392</v>
+        <v>1406</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>1393</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="26">
@@ -8674,10 +8758,10 @@
         <v>399</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>1394</v>
+        <v>1408</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>1395</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="27">
@@ -8689,10 +8773,10 @@
         <v>404</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>1396</v>
+        <v>1410</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>1397</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="28">
@@ -8704,10 +8788,10 @@
         <v>406</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>1398</v>
+        <v>1412</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>1399</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="29">
@@ -8719,10 +8803,10 @@
         <v>410</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>1400</v>
+        <v>1414</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>1401</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="30">
@@ -8731,13 +8815,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>1402</v>
+        <v>1416</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>1403</v>
+        <v>1417</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>1404</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="31">
@@ -8749,10 +8833,10 @@
         <v>414</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>1405</v>
+        <v>1419</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>1406</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="32">
@@ -8764,10 +8848,10 @@
         <v>416</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>1407</v>
+        <v>1421</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>1408</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="33">
@@ -8776,13 +8860,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>1409</v>
+        <v>1423</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>48</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="34">
@@ -8794,10 +8878,10 @@
         <v>420</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>1411</v>
+        <v>1425</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>1412</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="35">
@@ -8809,10 +8893,10 @@
         <v>424</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>1413</v>
+        <v>1427</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>1414</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="36">
@@ -8824,10 +8908,10 @@
         <v>427</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>1415</v>
+        <v>1429</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>1416</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="37">
@@ -8839,10 +8923,10 @@
         <v>432</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>1417</v>
+        <v>1431</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>1418</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="38">
@@ -8854,10 +8938,10 @@
         <v>437</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>1419</v>
+        <v>1433</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>1420</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="39">
@@ -8869,10 +8953,10 @@
         <v>11</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>1421</v>
+        <v>1435</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>1421</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="40">
@@ -8884,10 +8968,10 @@
         <v>444</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>1422</v>
+        <v>1436</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>1423</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="41">
@@ -8899,10 +8983,10 @@
         <v>448</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>1424</v>
+        <v>1438</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>1425</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="42">
@@ -8914,10 +8998,10 @@
         <v>451</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>1426</v>
+        <v>1440</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>1427</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="43">
@@ -8929,10 +9013,10 @@
         <v>455</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>1426</v>
+        <v>1440</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>1428</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="44">
@@ -8944,10 +9028,10 @@
         <v>458</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>1429</v>
+        <v>1443</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>1429</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="45">
@@ -8959,10 +9043,10 @@
         <v>466</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>1430</v>
+        <v>1444</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>1431</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="46">
@@ -8974,10 +9058,10 @@
         <v>472</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>1432</v>
+        <v>1446</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>1432</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="47">
@@ -8989,10 +9073,10 @@
         <v>476</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>1433</v>
+        <v>1447</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>1434</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="48">
@@ -9004,10 +9088,10 @@
         <v>480</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>1435</v>
+        <v>1449</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>1436</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="49">
@@ -9019,10 +9103,10 @@
         <v>485</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>1437</v>
+        <v>1451</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>1438</v>
+        <v>1452</v>
       </c>
     </row>
   </sheetData>
@@ -9057,28 +9141,28 @@
         <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1439</v>
+        <v>1453</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1440</v>
+        <v>1454</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1441</v>
+        <v>1455</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1442</v>
+        <v>1456</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1443</v>
+        <v>1457</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1444</v>
+        <v>1458</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1445</v>
+        <v>1459</v>
       </c>
       <c r="I1" s="62" t="s">
-        <v>1446</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="2">
@@ -9122,7 +9206,7 @@
         <v>1093</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>760</v>
@@ -9131,10 +9215,10 @@
         <v>760</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>1448</v>
+        <v>1462</v>
       </c>
       <c r="I3" s="37" t="s">
-        <v>1449</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="4">
@@ -9152,7 +9236,7 @@
         <v>1095</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F4" s="38" t="s">
         <v>760</v>
@@ -9161,10 +9245,10 @@
         <v>760</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1450</v>
+        <v>1464</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1451</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="5">
@@ -9182,7 +9266,7 @@
         <v>1097</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F5" s="38" t="s">
         <v>760</v>
@@ -9191,10 +9275,10 @@
         <v>760</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>1452</v>
+        <v>1466</v>
       </c>
       <c r="I5" s="37" t="s">
-        <v>1453</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="6">
@@ -9203,7 +9287,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1454</v>
+        <v>1468</v>
       </c>
       <c r="C6" s="36">
         <v>0.0</v>
@@ -9212,7 +9296,7 @@
         <v>1035</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>760</v>
@@ -9221,10 +9305,10 @@
         <v>760</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>1455</v>
+        <v>1469</v>
       </c>
       <c r="I6" s="37" t="s">
-        <v>1456</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="7">
@@ -9233,7 +9317,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1457</v>
+        <v>1471</v>
       </c>
       <c r="C7" s="36">
         <v>0.0</v>
@@ -9242,7 +9326,7 @@
         <v>1035</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F7" s="38" t="s">
         <v>760</v>
@@ -9251,10 +9335,10 @@
         <v>760</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>1458</v>
+        <v>1472</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>1459</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="8">
@@ -9272,7 +9356,7 @@
         <v>1035</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>760</v>
@@ -9281,10 +9365,10 @@
         <v>760</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>1460</v>
+        <v>1474</v>
       </c>
       <c r="I8" s="37" t="s">
-        <v>1461</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="9">
@@ -9293,7 +9377,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1462</v>
+        <v>1476</v>
       </c>
       <c r="C9" s="36">
         <v>0.0</v>
@@ -9302,7 +9386,7 @@
         <v>1035</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F9" s="38" t="s">
         <v>760</v>
@@ -9311,10 +9395,10 @@
         <v>760</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>1463</v>
+        <v>1477</v>
       </c>
       <c r="I9" s="37" t="s">
-        <v>1464</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="10">
@@ -9323,7 +9407,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1465</v>
+        <v>1479</v>
       </c>
       <c r="C10" s="36">
         <v>0.0</v>
@@ -9332,7 +9416,7 @@
         <v>1035</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F10" s="38" t="s">
         <v>760</v>
@@ -9341,10 +9425,10 @@
         <v>760</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>1466</v>
+        <v>1480</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>1467</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="11">
@@ -9353,7 +9437,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1468</v>
+        <v>1482</v>
       </c>
       <c r="C11" s="36">
         <v>1.0</v>
@@ -9362,19 +9446,19 @@
         <v>1035</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G11" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>1470</v>
+        <v>1484</v>
       </c>
       <c r="I11" s="37" t="s">
-        <v>1471</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="12">
@@ -9383,7 +9467,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>1472</v>
+        <v>1486</v>
       </c>
       <c r="C12" s="36">
         <v>0.0</v>
@@ -9392,7 +9476,7 @@
         <v>1035</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>760</v>
@@ -9401,10 +9485,10 @@
         <v>760</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1473</v>
+        <v>1487</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>1474</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="13">
@@ -9413,7 +9497,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>1475</v>
+        <v>1489</v>
       </c>
       <c r="C13" s="36">
         <v>0.0</v>
@@ -9422,7 +9506,7 @@
         <v>1035</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>760</v>
@@ -9431,10 +9515,10 @@
         <v>760</v>
       </c>
       <c r="H13" s="37" t="s">
-        <v>1476</v>
+        <v>1490</v>
       </c>
       <c r="I13" s="37" t="s">
-        <v>1477</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="14">
@@ -9443,7 +9527,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1478</v>
+        <v>1492</v>
       </c>
       <c r="C14" s="36">
         <v>1.0</v>
@@ -9452,19 +9536,19 @@
         <v>1035</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G14" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>1479</v>
+        <v>1493</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>1480</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="15">
@@ -9473,7 +9557,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>1481</v>
+        <v>1495</v>
       </c>
       <c r="C15" s="36">
         <v>1.0</v>
@@ -9482,19 +9566,19 @@
         <v>1035</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G15" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1482</v>
+        <v>1496</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1483</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="16">
@@ -9503,7 +9587,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>1248</v>
+        <v>1262</v>
       </c>
       <c r="C16" s="36">
         <v>0.0</v>
@@ -9512,7 +9596,7 @@
         <v>1035</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>760</v>
@@ -9521,10 +9605,10 @@
         <v>760</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>1484</v>
+        <v>1498</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>1485</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="17">
@@ -9533,7 +9617,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1251</v>
+        <v>1265</v>
       </c>
       <c r="C17" s="36">
         <v>0.0</v>
@@ -9542,7 +9626,7 @@
         <v>1035</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>760</v>
@@ -9551,10 +9635,10 @@
         <v>760</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>1486</v>
+        <v>1500</v>
       </c>
       <c r="I17" s="37" t="s">
-        <v>1487</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="18">
@@ -9563,7 +9647,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1488</v>
+        <v>1502</v>
       </c>
       <c r="C18" s="36">
         <v>0.0</v>
@@ -9572,7 +9656,7 @@
         <v>1035</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>760</v>
@@ -9581,10 +9665,10 @@
         <v>760</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>1489</v>
+        <v>1503</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>1490</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="19">
@@ -9602,7 +9686,7 @@
         <v>1035</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F19" s="38" t="s">
         <v>760</v>
@@ -9611,10 +9695,10 @@
         <v>760</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>1491</v>
+        <v>1505</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>1492</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="20">
@@ -9632,7 +9716,7 @@
         <v>1035</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F20" s="38" t="s">
         <v>760</v>
@@ -9641,10 +9725,10 @@
         <v>760</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>1493</v>
+        <v>1507</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>1494</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="21">
@@ -9662,7 +9746,7 @@
         <v>1035</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F21" s="38" t="s">
         <v>760</v>
@@ -9671,10 +9755,10 @@
         <v>760</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>1495</v>
+        <v>1509</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>1496</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="22">
@@ -9692,7 +9776,7 @@
         <v>1035</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F22" s="38" t="s">
         <v>760</v>
@@ -9701,10 +9785,10 @@
         <v>760</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1497</v>
+        <v>1511</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1498</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="23">
@@ -9722,7 +9806,7 @@
         <v>1035</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F23" s="38" t="s">
         <v>760</v>
@@ -9731,10 +9815,10 @@
         <v>760</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>1499</v>
+        <v>1513</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>1500</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="24">
@@ -9752,7 +9836,7 @@
         <v>1035</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F24" s="38" t="s">
         <v>760</v>
@@ -9761,10 +9845,10 @@
         <v>760</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1501</v>
+        <v>1515</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1502</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="25">
@@ -9782,7 +9866,7 @@
         <v>1035</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F25" s="38" t="s">
         <v>760</v>
@@ -9791,10 +9875,10 @@
         <v>760</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>1503</v>
+        <v>1517</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>1504</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="26">
@@ -9812,7 +9896,7 @@
         <v>1035</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F26" s="38" t="s">
         <v>760</v>
@@ -9821,10 +9905,10 @@
         <v>760</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>1505</v>
+        <v>1519</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>1506</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="27">
@@ -9833,7 +9917,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1507</v>
+        <v>1521</v>
       </c>
       <c r="C27" s="36">
         <v>0.0</v>
@@ -9842,7 +9926,7 @@
         <v>1035</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F27" s="38" t="s">
         <v>760</v>
@@ -9851,10 +9935,10 @@
         <v>760</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>1508</v>
+        <v>1522</v>
       </c>
       <c r="I27" s="37" t="s">
-        <v>1509</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="28">
@@ -9863,7 +9947,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1510</v>
+        <v>1524</v>
       </c>
       <c r="C28" s="36">
         <v>1.0</v>
@@ -9872,19 +9956,19 @@
         <v>1035</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G28" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>1511</v>
+        <v>1525</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>1512</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="29">
@@ -9893,7 +9977,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>1336</v>
+        <v>1350</v>
       </c>
       <c r="C29" s="36">
         <v>0.0</v>
@@ -9902,7 +9986,7 @@
         <v>1035</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>760</v>
@@ -9911,10 +9995,10 @@
         <v>760</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>1513</v>
+        <v>1527</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>1514</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="30">
@@ -9923,7 +10007,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>1338</v>
+        <v>1352</v>
       </c>
       <c r="C30" s="36">
         <v>0.0</v>
@@ -9932,7 +10016,7 @@
         <v>1035</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F30" s="38" t="s">
         <v>760</v>
@@ -9941,10 +10025,10 @@
         <v>760</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>1515</v>
+        <v>1529</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>1516</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="31">
@@ -9953,7 +10037,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1340</v>
+        <v>1354</v>
       </c>
       <c r="C31" s="36">
         <v>0.0</v>
@@ -9962,7 +10046,7 @@
         <v>1035</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>760</v>
@@ -9971,10 +10055,10 @@
         <v>760</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>1517</v>
+        <v>1531</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>1518</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="32">
@@ -9992,7 +10076,7 @@
         <v>1035</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F32" s="38" t="s">
         <v>760</v>
@@ -10001,10 +10085,10 @@
         <v>760</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>1519</v>
+        <v>1533</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>1520</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="33">
@@ -10013,7 +10097,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1253</v>
+        <v>1267</v>
       </c>
       <c r="C33" s="36">
         <v>0.0</v>
@@ -10022,7 +10106,7 @@
         <v>1035</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F33" s="38" t="s">
         <v>760</v>
@@ -10031,10 +10115,10 @@
         <v>760</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1521</v>
+        <v>1535</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1522</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="34">
@@ -10043,7 +10127,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1523</v>
+        <v>1537</v>
       </c>
       <c r="C34" s="36">
         <v>1.0</v>
@@ -10052,19 +10136,19 @@
         <v>1035</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G34" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>1524</v>
+        <v>1538</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>1525</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="35">
@@ -10073,7 +10157,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1526</v>
+        <v>1540</v>
       </c>
       <c r="C35" s="36">
         <v>1.0</v>
@@ -10082,19 +10166,19 @@
         <v>1035</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G35" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>1527</v>
+        <v>1541</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>1528</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="36">
@@ -10112,7 +10196,7 @@
         <v>1035</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F36" s="38" t="s">
         <v>760</v>
@@ -10121,10 +10205,10 @@
         <v>760</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>1529</v>
+        <v>1543</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>1530</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="37">
@@ -10133,7 +10217,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1531</v>
+        <v>1545</v>
       </c>
       <c r="C37" s="36">
         <v>0.0</v>
@@ -10142,7 +10226,7 @@
         <v>1035</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F37" s="38" t="s">
         <v>760</v>
@@ -10151,10 +10235,10 @@
         <v>760</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>1532</v>
+        <v>1546</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>1533</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="38">
@@ -10163,7 +10247,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1534</v>
+        <v>1548</v>
       </c>
       <c r="C38" s="36">
         <v>1.0</v>
@@ -10172,19 +10256,19 @@
         <v>1035</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G38" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>1535</v>
+        <v>1549</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>1536</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="39">
@@ -10193,7 +10277,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1537</v>
+        <v>1551</v>
       </c>
       <c r="C39" s="36">
         <v>0.0</v>
@@ -10202,7 +10286,7 @@
         <v>1035</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F39" s="38" t="s">
         <v>760</v>
@@ -10211,10 +10295,10 @@
         <v>760</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="I39" s="37" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="40">
@@ -10223,7 +10307,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1540</v>
+        <v>1554</v>
       </c>
       <c r="C40" s="36">
         <v>1.0</v>
@@ -10232,19 +10316,19 @@
         <v>1035</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G40" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>1542</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="41">
@@ -10253,7 +10337,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1543</v>
+        <v>1557</v>
       </c>
       <c r="C41" s="36">
         <v>0.0</v>
@@ -10262,7 +10346,7 @@
         <v>1035</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F41" s="38" t="s">
         <v>760</v>
@@ -10271,10 +10355,10 @@
         <v>760</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>1544</v>
+        <v>1558</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>1545</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="42">
@@ -10283,7 +10367,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1546</v>
+        <v>1560</v>
       </c>
       <c r="C42" s="36">
         <v>1.0</v>
@@ -10292,19 +10376,19 @@
         <v>1035</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G42" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>1547</v>
+        <v>1561</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>1548</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="43">
@@ -10313,7 +10397,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1549</v>
+        <v>1563</v>
       </c>
       <c r="C43" s="36">
         <v>0.0</v>
@@ -10322,7 +10406,7 @@
         <v>1035</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F43" s="38" t="s">
         <v>760</v>
@@ -10331,10 +10415,10 @@
         <v>760</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>1551</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="44">
@@ -10343,7 +10427,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1552</v>
+        <v>1566</v>
       </c>
       <c r="C44" s="36">
         <v>1.0</v>
@@ -10352,19 +10436,19 @@
         <v>1035</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G44" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>1553</v>
+        <v>1567</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>1554</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="45">
@@ -10373,7 +10457,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="C45" s="36">
         <v>0.0</v>
@@ -10382,7 +10466,7 @@
         <v>1035</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F45" s="38" t="s">
         <v>760</v>
@@ -10391,10 +10475,10 @@
         <v>760</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>1556</v>
+        <v>1570</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>1557</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="46">
@@ -10403,7 +10487,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>1558</v>
+        <v>1572</v>
       </c>
       <c r="C46" s="36">
         <v>1.0</v>
@@ -10412,19 +10496,19 @@
         <v>1035</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G46" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1559</v>
+        <v>1573</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1560</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="47">
@@ -10433,7 +10517,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1561</v>
+        <v>1575</v>
       </c>
       <c r="C47" s="36">
         <v>1.0</v>
@@ -10442,19 +10526,19 @@
         <v>1035</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G47" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H47" s="37" t="s">
-        <v>1562</v>
+        <v>1576</v>
       </c>
       <c r="I47" s="37" t="s">
-        <v>1563</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="48">
@@ -10463,7 +10547,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>1564</v>
+        <v>1578</v>
       </c>
       <c r="C48" s="36">
         <v>0.0</v>
@@ -10472,7 +10556,7 @@
         <v>1035</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F48" s="38" t="s">
         <v>760</v>
@@ -10481,10 +10565,10 @@
         <v>760</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>1565</v>
+        <v>1579</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>1566</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="49">
@@ -10493,7 +10577,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>1567</v>
+        <v>1581</v>
       </c>
       <c r="C49" s="36">
         <v>1.0</v>
@@ -10502,19 +10586,19 @@
         <v>1035</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G49" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>1568</v>
+        <v>1582</v>
       </c>
       <c r="I49" s="37" t="s">
-        <v>1569</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="50">
@@ -10523,7 +10607,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>1570</v>
+        <v>1584</v>
       </c>
       <c r="C50" s="36">
         <v>0.0</v>
@@ -10532,7 +10616,7 @@
         <v>1035</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F50" s="38" t="s">
         <v>760</v>
@@ -10541,10 +10625,10 @@
         <v>760</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="I50" s="37" t="s">
-        <v>1572</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="51">
@@ -10553,7 +10637,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1573</v>
+        <v>1587</v>
       </c>
       <c r="C51" s="36">
         <v>0.0</v>
@@ -10562,7 +10646,7 @@
         <v>1035</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F51" s="38" t="s">
         <v>760</v>
@@ -10571,10 +10655,10 @@
         <v>760</v>
       </c>
       <c r="H51" s="37" t="s">
-        <v>1574</v>
+        <v>1588</v>
       </c>
       <c r="I51" s="37" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="52">
@@ -10583,7 +10667,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1576</v>
+        <v>1590</v>
       </c>
       <c r="C52" s="36">
         <v>1.0</v>
@@ -10592,19 +10676,19 @@
         <v>1035</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G52" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H52" s="37" t="s">
-        <v>1577</v>
+        <v>1591</v>
       </c>
       <c r="I52" s="37" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="53">
@@ -10613,7 +10697,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1579</v>
+        <v>1593</v>
       </c>
       <c r="C53" s="36">
         <v>1.0</v>
@@ -10622,19 +10706,19 @@
         <v>1035</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G53" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>1580</v>
+        <v>1594</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>1581</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="54">
@@ -10643,7 +10727,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>1582</v>
+        <v>1596</v>
       </c>
       <c r="C54" s="36">
         <v>1.0</v>
@@ -10652,19 +10736,19 @@
         <v>1035</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G54" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>1583</v>
+        <v>1597</v>
       </c>
       <c r="I54" s="37" t="s">
-        <v>1584</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="55">
@@ -10673,7 +10757,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1585</v>
+        <v>1599</v>
       </c>
       <c r="C55" s="36">
         <v>0.0</v>
@@ -10682,7 +10766,7 @@
         <v>1035</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F55" s="38" t="s">
         <v>760</v>
@@ -10691,10 +10775,10 @@
         <v>760</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>1586</v>
+        <v>1600</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>1587</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="56">
@@ -10703,7 +10787,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1266</v>
+        <v>1280</v>
       </c>
       <c r="C56" s="36">
         <v>0.0</v>
@@ -10712,7 +10796,7 @@
         <v>1035</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F56" s="38" t="s">
         <v>760</v>
@@ -10721,10 +10805,10 @@
         <v>760</v>
       </c>
       <c r="H56" s="37" t="s">
-        <v>1588</v>
+        <v>1602</v>
       </c>
       <c r="I56" s="37" t="s">
-        <v>1589</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="57">
@@ -10733,7 +10817,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1590</v>
+        <v>1604</v>
       </c>
       <c r="C57" s="36">
         <v>0.0</v>
@@ -10742,7 +10826,7 @@
         <v>1035</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F57" s="38" t="s">
         <v>760</v>
@@ -10751,10 +10835,10 @@
         <v>760</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>1591</v>
+        <v>1605</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>1592</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="58">
@@ -10763,7 +10847,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="C58" s="36">
         <v>1.0</v>
@@ -10772,19 +10856,19 @@
         <v>1035</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G58" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>1593</v>
+        <v>1607</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>1594</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="59">
@@ -10802,7 +10886,7 @@
         <v>1035</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F59" s="38" t="s">
         <v>760</v>
@@ -10811,10 +10895,10 @@
         <v>760</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>1595</v>
+        <v>1609</v>
       </c>
       <c r="I59" s="37" t="s">
-        <v>1596</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="60">
@@ -10823,7 +10907,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1597</v>
+        <v>1611</v>
       </c>
       <c r="C60" s="36">
         <v>0.0</v>
@@ -10841,10 +10925,10 @@
         <v>760</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>1598</v>
+        <v>1612</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>1599</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="61">
@@ -10853,7 +10937,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1600</v>
+        <v>1614</v>
       </c>
       <c r="C61" s="36">
         <v>0.0</v>
@@ -10871,10 +10955,10 @@
         <v>760</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>1601</v>
+        <v>1615</v>
       </c>
       <c r="I61" s="37" t="s">
-        <v>1602</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="62">
@@ -10883,7 +10967,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1603</v>
+        <v>1617</v>
       </c>
       <c r="C62" s="36">
         <v>0.0</v>
@@ -10901,10 +10985,10 @@
         <v>760</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>1604</v>
+        <v>1618</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>1605</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="63">
@@ -10922,7 +11006,7 @@
         <v>1035</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F63" s="38" t="s">
         <v>760</v>
@@ -10931,10 +11015,10 @@
         <v>760</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>1606</v>
+        <v>1620</v>
       </c>
       <c r="I63" s="37" t="s">
-        <v>1607</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="64">
@@ -10943,7 +11027,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>1608</v>
+        <v>1622</v>
       </c>
       <c r="C64" s="36">
         <v>0.0</v>
@@ -10952,7 +11036,7 @@
         <v>1042</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F64" s="38" t="s">
         <v>760</v>
@@ -10961,10 +11045,10 @@
         <v>760</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>1609</v>
+        <v>1623</v>
       </c>
       <c r="I64" s="37" t="s">
-        <v>1609</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="65">
@@ -10973,7 +11057,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1610</v>
+        <v>1624</v>
       </c>
       <c r="C65" s="36">
         <v>0.0</v>
@@ -10982,7 +11066,7 @@
         <v>1043</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F65" s="38" t="s">
         <v>760</v>
@@ -10991,10 +11075,10 @@
         <v>760</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>1611</v>
+        <v>1625</v>
       </c>
       <c r="I65" s="37" t="s">
-        <v>1612</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="66">
@@ -11003,7 +11087,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1613</v>
+        <v>1627</v>
       </c>
       <c r="C66" s="36">
         <v>0.0</v>
@@ -11012,7 +11096,7 @@
         <v>1044</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F66" s="38" t="s">
         <v>760</v>
@@ -11021,10 +11105,10 @@
         <v>760</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>1614</v>
+        <v>1628</v>
       </c>
       <c r="I66" s="37" t="s">
-        <v>1615</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="67">
@@ -11033,7 +11117,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>1616</v>
+        <v>1630</v>
       </c>
       <c r="C67" s="36">
         <v>0.0</v>
@@ -11042,7 +11126,7 @@
         <v>1045</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F67" s="38" t="s">
         <v>760</v>
@@ -11051,10 +11135,10 @@
         <v>760</v>
       </c>
       <c r="H67" s="37" t="s">
-        <v>1617</v>
+        <v>1631</v>
       </c>
       <c r="I67" s="37" t="s">
-        <v>1618</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="68">
@@ -11063,7 +11147,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>1619</v>
+        <v>1633</v>
       </c>
       <c r="C68" s="36">
         <v>0.0</v>
@@ -11072,7 +11156,7 @@
         <v>1035</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F68" s="38" t="s">
         <v>760</v>
@@ -11081,10 +11165,10 @@
         <v>760</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>1620</v>
+        <v>1634</v>
       </c>
       <c r="I68" s="37" t="s">
-        <v>1621</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="69">
@@ -11093,7 +11177,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>1622</v>
+        <v>1636</v>
       </c>
       <c r="C69" s="36">
         <v>1.0</v>
@@ -11102,19 +11186,19 @@
         <v>1035</v>
       </c>
       <c r="E69" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F69" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G69" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H69" s="37" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
       <c r="I69" s="37" t="s">
-        <v>1624</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="70">
@@ -11123,7 +11207,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1625</v>
+        <v>1639</v>
       </c>
       <c r="C70" s="36">
         <v>0.0</v>
@@ -11132,7 +11216,7 @@
         <v>1035</v>
       </c>
       <c r="E70" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F70" s="38" t="s">
         <v>760</v>
@@ -11141,10 +11225,10 @@
         <v>760</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>1626</v>
+        <v>1640</v>
       </c>
       <c r="I70" s="37" t="s">
-        <v>1627</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="71">
@@ -11153,7 +11237,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>1628</v>
+        <v>1642</v>
       </c>
       <c r="C71" s="36">
         <v>1.0</v>
@@ -11162,19 +11246,19 @@
         <v>1035</v>
       </c>
       <c r="E71" s="44" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="G71" s="38" t="s">
         <v>760</v>
       </c>
       <c r="H71" s="37" t="s">
-        <v>1629</v>
+        <v>1643</v>
       </c>
       <c r="I71" s="37" t="s">
-        <v>1630</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="72">
@@ -11183,7 +11267,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1631</v>
+        <v>1645</v>
       </c>
       <c r="C72" s="36">
         <v>0.0</v>
@@ -11192,7 +11276,7 @@
         <v>1035</v>
       </c>
       <c r="E72" s="44" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
       <c r="F72" s="38" t="s">
         <v>760</v>
@@ -11201,10 +11285,10 @@
         <v>760</v>
       </c>
       <c r="H72" s="37" t="s">
-        <v>1632</v>
+        <v>1646</v>
       </c>
       <c r="I72" s="37" t="s">
-        <v>1